--- a/data/CULT.MI.xlsx
+++ b/data/CULT.MI.xlsx
@@ -47,19 +47,19 @@
     <t xml:space="preserve">4.57666730880737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59486484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60851335525513</t>
+    <t xml:space="preserve">4.59486532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60851383209229</t>
   </si>
   <si>
     <t xml:space="preserve">4.58576631546021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48931932449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56301927566528</t>
+    <t xml:space="preserve">4.48931980133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5630202293396</t>
   </si>
   <si>
     <t xml:space="preserve">4.51297616958618</t>
@@ -74,25 +74,25 @@
     <t xml:space="preserve">4.21271800994873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18178272247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23091602325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36375665664673</t>
+    <t xml:space="preserve">4.1817831993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23091459274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36375713348389</t>
   </si>
   <si>
     <t xml:space="preserve">4.38195419311523</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35101842880249</t>
+    <t xml:space="preserve">4.35101890563965</t>
   </si>
   <si>
     <t xml:space="preserve">4.28914737701416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24183368682861</t>
+    <t xml:space="preserve">4.24183416366577</t>
   </si>
   <si>
     <t xml:space="preserve">4.22909498214722</t>
@@ -125,55 +125,55 @@
     <t xml:space="preserve">4.32008361816406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24911212921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97979068756104</t>
+    <t xml:space="preserve">4.24911308288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9797899723053</t>
   </si>
   <si>
     <t xml:space="preserve">4.06895780563354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0543999671936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98524928092957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05075979232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07259702682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03802251815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04530096054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03074264526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01254606246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04894113540649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05985927581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07623672485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91245937347412</t>
+    <t xml:space="preserve">4.05439949035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98524975776672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0507607460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07259750366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0380220413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04530143737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03074312210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01254510879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04894065856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05985832214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07623720169067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91245889663696</t>
   </si>
   <si>
     <t xml:space="preserve">3.99070906639099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01072645187378</t>
+    <t xml:space="preserve">4.01072549819946</t>
   </si>
   <si>
     <t xml:space="preserve">3.92155790328979</t>
@@ -182,67 +182,67 @@
     <t xml:space="preserve">4.00162649154663</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05803966522217</t>
+    <t xml:space="preserve">4.05803871154785</t>
   </si>
   <si>
     <t xml:space="preserve">4.21635675430298</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2218165397644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18542194366455</t>
+    <t xml:space="preserve">4.22181701660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18542146682739</t>
   </si>
   <si>
     <t xml:space="preserve">4.16176462173462</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35465812683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28186750411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26731109619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39287233352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36739635467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17814302444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27458953857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31826257705688</t>
+    <t xml:space="preserve">4.35465717315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28186893463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26731061935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39287376403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36739683151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17814350128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27458906173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31826305389404</t>
   </si>
   <si>
     <t xml:space="preserve">4.35647821426392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26549005508423</t>
+    <t xml:space="preserve">4.26549100875854</t>
   </si>
   <si>
     <t xml:space="preserve">4.26367044448853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27640914916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14902687072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35829782485962</t>
+    <t xml:space="preserve">4.27640867233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14902591705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3582968711853</t>
   </si>
   <si>
     <t xml:space="preserve">4.35283803939819</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29460525512695</t>
+    <t xml:space="preserve">4.29460573196411</t>
   </si>
   <si>
     <t xml:space="preserve">4.2036190032959</t>
@@ -254,37 +254,37 @@
     <t xml:space="preserve">4.34009981155396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42926836013794</t>
+    <t xml:space="preserve">4.42926788330078</t>
   </si>
   <si>
     <t xml:space="preserve">4.34919929504395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33646154403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33100175857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32190227508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4674825668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45838451385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28550815582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83057069778442</t>
+    <t xml:space="preserve">4.33646011352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33100128173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32190322875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46748208999634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45838403701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2855076789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.830570936203</t>
   </si>
   <si>
     <t xml:space="preserve">3.90336060523987</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88516283035278</t>
+    <t xml:space="preserve">3.88516306877136</t>
   </si>
   <si>
     <t xml:space="preserve">3.87606430053711</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">4.00344705581665</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93065738677979</t>
+    <t xml:space="preserve">3.93065643310547</t>
   </si>
   <si>
     <t xml:space="preserve">3.99434733390808</t>
@@ -305,43 +305,43 @@
     <t xml:space="preserve">3.96705174446106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86696577072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84876894950867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85786652565002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81237316131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80327439308167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77597832679749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97615098953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94885444641113</t>
+    <t xml:space="preserve">3.86696481704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84876799583435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85786628723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8123733997345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80327415466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77597808837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97615027427673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94885468482971</t>
   </si>
   <si>
     <t xml:space="preserve">4.13992786407471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16722345352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33528327941895</t>
+    <t xml:space="preserve">4.16722393035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33528280258179</t>
   </si>
   <si>
     <t xml:space="preserve">4.21485900878906</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31675672531128</t>
+    <t xml:space="preserve">4.31675624847412</t>
   </si>
   <si>
     <t xml:space="preserve">4.42791795730591</t>
@@ -350,37 +350,37 @@
     <t xml:space="preserve">4.19633150100708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16854190826416</t>
+    <t xml:space="preserve">4.168541431427</t>
   </si>
   <si>
     <t xml:space="preserve">4.29822969436646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30749368667603</t>
+    <t xml:space="preserve">4.30749225616455</t>
   </si>
   <si>
     <t xml:space="preserve">4.27970266342163</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3908634185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40012693405151</t>
+    <t xml:space="preserve">4.39086389541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40012788772583</t>
   </si>
   <si>
     <t xml:space="preserve">4.35381031036377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08517122268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93695616722107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00180053710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97400975227356</t>
+    <t xml:space="preserve">4.08517074584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93695545196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00179958343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97400951385498</t>
   </si>
   <si>
     <t xml:space="preserve">4.03885364532471</t>
@@ -389,31 +389,31 @@
     <t xml:space="preserve">3.9462194442749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95548272132874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23338603973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22412252426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24264860153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11296129226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26117610931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91843008995056</t>
+    <t xml:space="preserve">3.95548295974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23338651657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22412204742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24264907836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11296081542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26117563247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91842913627625</t>
   </si>
   <si>
     <t xml:space="preserve">3.89990234375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89063858985901</t>
+    <t xml:space="preserve">3.89063882827759</t>
   </si>
   <si>
     <t xml:space="preserve">4.07590770721436</t>
@@ -422,91 +422,91 @@
     <t xml:space="preserve">4.06664323806763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7980043888092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73316049575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86284852027893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71463370323181</t>
+    <t xml:space="preserve">3.79800486564636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73316073417664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86284899711609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71463394165039</t>
   </si>
   <si>
     <t xml:space="preserve">3.70537042617798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77021431922913</t>
+    <t xml:space="preserve">3.77021479606628</t>
   </si>
   <si>
     <t xml:space="preserve">3.3904139995575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44599485397339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58494567871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68684363365173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60347270965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52010154724121</t>
+    <t xml:space="preserve">3.44599461555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58494544029236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68684387207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60347294807434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52010178565979</t>
   </si>
   <si>
     <t xml:space="preserve">3.37188720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46452116966248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53862857818604</t>
+    <t xml:space="preserve">3.46452140808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53862881660461</t>
   </si>
   <si>
     <t xml:space="preserve">3.52936553955078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45525813102722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34409689903259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07545733451843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14956474304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29777932167053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31630659103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23293542861938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24219942092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02914071083069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20514559745789</t>
+    <t xml:space="preserve">3.45525789260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34409642219543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07545757293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14956521987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29777956008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31630611419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23293566703796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24219870567322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02914047241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20514583587646</t>
   </si>
   <si>
     <t xml:space="preserve">3.25146222114563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10324740409851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15882849693298</t>
+    <t xml:space="preserve">3.10324764251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1588282585144</t>
   </si>
   <si>
     <t xml:space="preserve">2.91797924041748</t>
@@ -521,19 +521,19 @@
     <t xml:space="preserve">2.87166213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96429657936096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85313510894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83460807800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84387159347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72344732284546</t>
+    <t xml:space="preserve">2.96429634094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85313534736633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83460831642151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84387183189392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72344708442688</t>
   </si>
   <si>
     <t xml:space="preserve">2.76050114631653</t>
@@ -548,43 +548,43 @@
     <t xml:space="preserve">2.67713046073914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38070058822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36217355728149</t>
+    <t xml:space="preserve">2.38070034980774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36217379570007</t>
   </si>
   <si>
     <t xml:space="preserve">2.29732966423035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31585645675659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35291004180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26953959465027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2324857711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28806638717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08427095413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13058805465698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22322225570679</t>
+    <t xml:space="preserve">2.31585621833801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35291028022766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26953935623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23248529434204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28806614875793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0842707157135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1305878162384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22322249412537</t>
   </si>
   <si>
     <t xml:space="preserve">2.24174904823303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11206126213074</t>
+    <t xml:space="preserve">2.11206102371216</t>
   </si>
   <si>
     <t xml:space="preserve">2.17690515518188</t>
@@ -593,19 +593,19 @@
     <t xml:space="preserve">2.03795385360718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99163663387299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88047564029694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9453192949295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92679262161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16764163970947</t>
+    <t xml:space="preserve">1.99163627624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88047552108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94531941413879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92679250240326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16764140129089</t>
   </si>
   <si>
     <t xml:space="preserve">2.13985133171082</t>
@@ -617,49 +617,49 @@
     <t xml:space="preserve">2.4084906578064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48259830474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42701745033264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38996410369873</t>
+    <t xml:space="preserve">2.48259806632996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42701768875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38996362686157</t>
   </si>
   <si>
     <t xml:space="preserve">2.46583580970764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50406551361084</t>
+    <t xml:space="preserve">2.50406575202942</t>
   </si>
   <si>
     <t xml:space="preserve">2.65698575973511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71433067321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5422956943512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58052587509155</t>
+    <t xml:space="preserve">2.71433091163635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54229545593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58052563667297</t>
   </si>
   <si>
     <t xml:space="preserve">2.52318096160889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42760586738586</t>
+    <t xml:space="preserve">2.42760610580444</t>
   </si>
   <si>
     <t xml:space="preserve">2.38937568664551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48495101928711</t>
+    <t xml:space="preserve">2.48495078086853</t>
   </si>
   <si>
     <t xml:space="preserve">2.61875581741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56141114234924</t>
+    <t xml:space="preserve">2.56141066551208</t>
   </si>
   <si>
     <t xml:space="preserve">2.63787078857422</t>
@@ -668,28 +668,28 @@
     <t xml:space="preserve">2.73344564437866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69521570205688</t>
+    <t xml:space="preserve">2.69521594047546</t>
   </si>
   <si>
     <t xml:space="preserve">2.75256085395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80990600585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82902121543884</t>
+    <t xml:space="preserve">2.8099057674408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82902073860168</t>
   </si>
   <si>
     <t xml:space="preserve">2.84813594818115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05840086936951</t>
+    <t xml:space="preserve">3.05840110778809</t>
   </si>
   <si>
     <t xml:space="preserve">2.86725091934204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77167558670044</t>
+    <t xml:space="preserve">2.77167582511902</t>
   </si>
   <si>
     <t xml:space="preserve">2.676100730896</t>
@@ -701,28 +701,28 @@
     <t xml:space="preserve">2.44672083854675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3702609539032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09663081169128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34512567520142</t>
+    <t xml:space="preserve">2.37026071548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09663128852844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34512615203857</t>
   </si>
   <si>
     <t xml:space="preserve">3.45981597900391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74654102325439</t>
+    <t xml:space="preserve">3.74654150009155</t>
   </si>
   <si>
     <t xml:space="preserve">3.76565623283386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01415109634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10972690582275</t>
+    <t xml:space="preserve">4.01415157318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10972595214844</t>
   </si>
   <si>
     <t xml:space="preserve">3.97592091560364</t>
@@ -734,43 +734,43 @@
     <t xml:space="preserve">3.82300114631653</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4407012462616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40247106552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36424136161804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68919610977173</t>
+    <t xml:space="preserve">3.44070100784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40247082710266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36424112319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68919587135315</t>
   </si>
   <si>
     <t xml:space="preserve">3.72742652893066</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7083113193512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57450604438782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55539131164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51716089248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63185143470764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5362765789032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61273622512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65096592903137</t>
+    <t xml:space="preserve">3.70831155776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5745062828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55539107322693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51716136932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63185095787048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53627634048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61273598670959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65096616744995</t>
   </si>
   <si>
     <t xml:space="preserve">3.24955105781555</t>
@@ -782,34 +782,34 @@
     <t xml:space="preserve">3.42158579826355</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30689597129822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38335609436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59362101554871</t>
+    <t xml:space="preserve">3.3068962097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38335633277893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59362125396729</t>
   </si>
   <si>
     <t xml:space="preserve">3.47893118858337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49804592132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28778147697449</t>
+    <t xml:space="preserve">3.49804639816284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28778123855591</t>
   </si>
   <si>
     <t xml:space="preserve">3.67008113861084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80388641357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93769145011902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03326559066772</t>
+    <t xml:space="preserve">3.80388617515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93769097328186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03326606750488</t>
   </si>
   <si>
     <t xml:space="preserve">4.18618679046631</t>
@@ -818,106 +818,106 @@
     <t xml:space="preserve">4.30087661743164</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53025531768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51114082336426</t>
+    <t xml:space="preserve">4.53025579452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51114130020142</t>
   </si>
   <si>
     <t xml:space="preserve">4.58760166168213</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49202632904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43468141555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62583160400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7405219078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75963640213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7022910118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68317604064941</t>
+    <t xml:space="preserve">4.49202585220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43468189239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62583208084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74052143096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75963687896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70229148864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68317651748657</t>
   </si>
   <si>
     <t xml:space="preserve">4.77875137329102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5684871673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66406154632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72140645980835</t>
+    <t xml:space="preserve">4.56848669052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66406202316284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72140693664551</t>
   </si>
   <si>
     <t xml:space="preserve">4.87432622909546</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96990203857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92211484909058</t>
+    <t xml:space="preserve">4.96990156173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92211389541626</t>
   </si>
   <si>
     <t xml:space="preserve">5.11326456069946</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16105175018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20883846282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25662660598755</t>
+    <t xml:space="preserve">5.16105127334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20883941650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25662708282471</t>
   </si>
   <si>
     <t xml:space="preserve">5.30441427230835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44777679443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63892698287964</t>
+    <t xml:space="preserve">5.44777631759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6389274597168</t>
   </si>
   <si>
     <t xml:space="preserve">5.591139793396</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81332635879517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71643781661987</t>
+    <t xml:space="preserve">5.81332683563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71643877029419</t>
   </si>
   <si>
     <t xml:space="preserve">5.42577171325684</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13510465621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8444390296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82506132125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80568361282349</t>
+    <t xml:space="preserve">5.13510513305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84443855285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8250617980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80568313598633</t>
   </si>
   <si>
     <t xml:space="preserve">4.59252738952637</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55377244949341</t>
+    <t xml:space="preserve">4.55377197265625</t>
   </si>
   <si>
     <t xml:space="preserve">4.76692771911621</t>
@@ -926,16 +926,16 @@
     <t xml:space="preserve">5.03821659088135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9897723197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08666038513184</t>
+    <t xml:space="preserve">4.98977184295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08665990829468</t>
   </si>
   <si>
     <t xml:space="preserve">5.18354988098145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9413275718689</t>
+    <t xml:space="preserve">4.94132709503174</t>
   </si>
   <si>
     <t xml:space="preserve">5.23199415206909</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">4.74755001068115</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28043794631958</t>
+    <t xml:space="preserve">5.2804388999939</t>
   </si>
   <si>
     <t xml:space="preserve">4.89288330078125</t>
@@ -953,7 +953,7 @@
     <t xml:space="preserve">4.63128423690796</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53439426422119</t>
+    <t xml:space="preserve">4.53439521789551</t>
   </si>
   <si>
     <t xml:space="preserve">4.67003917694092</t>
@@ -965,55 +965,55 @@
     <t xml:space="preserve">4.72817277908325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70879507064819</t>
+    <t xml:space="preserve">4.70879459381104</t>
   </si>
   <si>
     <t xml:space="preserve">5.91021537780762</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61954879760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32888269424438</t>
+    <t xml:space="preserve">5.61954927444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32888317108154</t>
   </si>
   <si>
     <t xml:space="preserve">5.37732744216919</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57110500335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47421598434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66799354553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7337703704834</t>
+    <t xml:space="preserve">5.57110548019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47421550750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66799402236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73376989364624</t>
   </si>
   <si>
     <t xml:space="preserve">6.29777050018311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4431037902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68532609939575</t>
+    <t xml:space="preserve">6.44310331344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68532562255859</t>
   </si>
   <si>
     <t xml:space="preserve">6.5884370803833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63688135147095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24932622909546</t>
+    <t xml:space="preserve">6.63688182830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24932670593262</t>
   </si>
   <si>
     <t xml:space="preserve">6.34621524810791</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53999280929565</t>
+    <t xml:space="preserve">6.5399923324585</t>
   </si>
   <si>
     <t xml:space="preserve">6.3946590423584</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">8.71999073028564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.993323802948</t>
+    <t xml:space="preserve">7.99332332611084</t>
   </si>
   <si>
     <t xml:space="preserve">8.09021377563477</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">8.04176807403564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94487953186035</t>
+    <t xml:space="preserve">7.94488048553467</t>
   </si>
   <si>
     <t xml:space="preserve">7.84799098968506</t>
@@ -1040,43 +1040,43 @@
     <t xml:space="preserve">7.89643526077271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38087749481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.270209312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88265514373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1733207702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9795446395874</t>
+    <t xml:space="preserve">8.38087940216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2702102661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88265419006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1733198165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97954368591309</t>
   </si>
   <si>
     <t xml:space="preserve">10.0764331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2390975952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6266527175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0799856185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2737627029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.983097076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4364280700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3395404815674</t>
+    <t xml:space="preserve">11.2390985488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6266536712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.079984664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2737636566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9830961227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.436427116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3395395278931</t>
   </si>
   <si>
     <t xml:space="preserve">15.0177612304688</t>
@@ -1085,16 +1085,16 @@
     <t xml:space="preserve">16.1669788360596</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1930665969849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0956745147705</t>
+    <t xml:space="preserve">15.1930656433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0956735610962</t>
   </si>
   <si>
     <t xml:space="preserve">14.9008903503418</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6348009109497</t>
+    <t xml:space="preserve">13.634801864624</t>
   </si>
   <si>
     <t xml:space="preserve">12.0765390396118</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">13.4400196075439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9269762039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0243682861328</t>
+    <t xml:space="preserve">13.9269771575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0243673324585</t>
   </si>
   <si>
     <t xml:space="preserve">14.2191514968872</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8035001754761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4139347076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6087160110474</t>
+    <t xml:space="preserve">14.8034982681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4139337539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6087169647217</t>
   </si>
   <si>
     <t xml:space="preserve">14.7061080932617</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">14.5113248825073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3426275253296</t>
+    <t xml:space="preserve">13.3426284790039</t>
   </si>
   <si>
     <t xml:space="preserve">14.1217594146729</t>
@@ -1160,13 +1160,13 @@
     <t xml:space="preserve">12.5634965896606</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1739301681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.686972618103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1026248931885</t>
+    <t xml:space="preserve">12.1739292144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6869735717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1026239395142</t>
   </si>
   <si>
     <t xml:space="preserve">9.93392658233643</t>
@@ -1175,10 +1175,10 @@
     <t xml:space="preserve">10.7130584716797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2000160217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9791469573975</t>
+    <t xml:space="preserve">11.2000169754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9791479110718</t>
   </si>
   <si>
     <t xml:space="preserve">11.8817558288574</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">10.9078416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2974071502686</t>
+    <t xml:space="preserve">11.2974081039429</t>
   </si>
   <si>
     <t xml:space="preserve">11.3947992324829</t>
@@ -1196,13 +1196,13 @@
     <t xml:space="preserve">11.589581489563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0052328109741</t>
+    <t xml:space="preserve">11.0052318572998</t>
   </si>
   <si>
     <t xml:space="preserve">11.7843647003174</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4921903610229</t>
+    <t xml:space="preserve">11.4921913146973</t>
   </si>
   <si>
     <t xml:space="preserve">10.810450553894</t>
@@ -1211,16 +1211,16 @@
     <t xml:space="preserve">10.4208850860596</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2261009216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3234920501709</t>
+    <t xml:space="preserve">10.2260999679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3234930038452</t>
   </si>
   <si>
     <t xml:space="preserve">10.1287107467651</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0313196182251</t>
+    <t xml:space="preserve">10.0313186645508</t>
   </si>
   <si>
     <t xml:space="preserve">9.73914432525635</t>
@@ -1229,52 +1229,52 @@
     <t xml:space="preserve">9.54436111450195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83653545379639</t>
+    <t xml:space="preserve">9.8365364074707</t>
   </si>
   <si>
     <t xml:space="preserve">9.34957885742188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49566650390625</t>
+    <t xml:space="preserve">9.49566555023193</t>
   </si>
   <si>
     <t xml:space="preserve">12.2713222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9530620574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6800231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7321949005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1704549789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3652391433716</t>
+    <t xml:space="preserve">12.9530611038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6800222396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7321929931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1704559326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3652381896973</t>
   </si>
   <si>
     <t xml:space="preserve">14.0730628967285</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1443700790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5364561080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5854682922363</t>
+    <t xml:space="preserve">15.1443691253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5364570617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.585467338562</t>
   </si>
   <si>
     <t xml:space="preserve">15.6344785690308</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1933813095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4874448776245</t>
+    <t xml:space="preserve">15.193380355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4874467849731</t>
   </si>
   <si>
     <t xml:space="preserve">15.4384346008301</t>
@@ -1283,13 +1283,13 @@
     <t xml:space="preserve">15.2423915863037</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3894233703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9973373413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8993148803711</t>
+    <t xml:space="preserve">15.3894243240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9973363876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8993139266968</t>
   </si>
   <si>
     <t xml:space="preserve">15.0463485717773</t>
@@ -1307,22 +1307,22 @@
     <t xml:space="preserve">13.7230529785156</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8210763931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3601951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6250305175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8700857162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6740417480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7720651626587</t>
+    <t xml:space="preserve">13.8210744857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3601942062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6250314712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8700866699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6740427017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7720642089844</t>
   </si>
   <si>
     <t xml:space="preserve">14.0171184539795</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">14.9483261108398</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4092054367065</t>
+    <t xml:space="preserve">14.4092063903809</t>
   </si>
   <si>
     <t xml:space="preserve">14.8503036499023</t>
@@ -1349,19 +1349,19 @@
     <t xml:space="preserve">14.6052494049072</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7032709121704</t>
+    <t xml:space="preserve">14.7032718658447</t>
   </si>
   <si>
     <t xml:space="preserve">14.5562391281128</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5072288513184</t>
+    <t xml:space="preserve">14.507227897644</t>
   </si>
   <si>
     <t xml:space="preserve">14.0661296844482</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3309659957886</t>
+    <t xml:space="preserve">13.3309669494629</t>
   </si>
   <si>
     <t xml:space="preserve">13.4779987335205</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">13.2819547653198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8898668289185</t>
+    <t xml:space="preserve">12.8898677825928</t>
   </si>
   <si>
     <t xml:space="preserve">12.7428350448608</t>
@@ -1379,43 +1379,43 @@
     <t xml:space="preserve">12.987889289856</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1349229812622</t>
+    <t xml:space="preserve">13.1349220275879</t>
   </si>
   <si>
     <t xml:space="preserve">12.3507480621338</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7626161575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3215198516846</t>
+    <t xml:space="preserve">11.7626171112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3215188980103</t>
   </si>
   <si>
     <t xml:space="preserve">12.3017377853394</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0859117507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4289875030518</t>
+    <t xml:space="preserve">13.0859127044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4289884567261</t>
   </si>
   <si>
     <t xml:space="preserve">15.8305215835571</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7325000762939</t>
+    <t xml:space="preserve">15.7324991226196</t>
   </si>
   <si>
     <t xml:space="preserve">15.8795328140259</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9775543212891</t>
+    <t xml:space="preserve">15.9775533676147</t>
   </si>
   <si>
     <t xml:space="preserve">16.3696422576904</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6834897994995</t>
+    <t xml:space="preserve">15.6834888458252</t>
   </si>
   <si>
     <t xml:space="preserve">15.7815113067627</t>
@@ -1424,13 +1424,13 @@
     <t xml:space="preserve">16.2226085662842</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0265655517578</t>
+    <t xml:space="preserve">16.0265674591064</t>
   </si>
   <si>
     <t xml:space="preserve">16.0755767822266</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9285449981689</t>
+    <t xml:space="preserve">15.9285440444946</t>
   </si>
   <si>
     <t xml:space="preserve">16.1735973358154</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">16.2716197967529</t>
   </si>
   <si>
-    <t xml:space="preserve">16.320629119873</t>
+    <t xml:space="preserve">16.3206310272217</t>
   </si>
   <si>
     <t xml:space="preserve">18.7221660614014</t>
@@ -1448,10 +1448,10 @@
     <t xml:space="preserve">19.0162315368652</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7023830413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.604362487793</t>
+    <t xml:space="preserve">19.7023849487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6043605804443</t>
   </si>
   <si>
     <t xml:space="preserve">19.8004055023193</t>
@@ -1460,40 +1460,40 @@
     <t xml:space="preserve">20.0944690704346</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9173221588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.545015335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5252323150635</t>
+    <t xml:space="preserve">23.9173202514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5450172424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5252342224121</t>
   </si>
   <si>
     <t xml:space="preserve">24.7995166778564</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2311706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7806224822998</t>
+    <t xml:space="preserve">23.2311687469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7806243896484</t>
   </si>
   <si>
     <t xml:space="preserve">21.1727104187012</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4865589141846</t>
+    <t xml:space="preserve">20.4865570068359</t>
   </si>
   <si>
     <t xml:space="preserve">20.6826019287109</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3687534332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6430397033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9955596923828</t>
+    <t xml:space="preserve">21.3687553405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6430377960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9955615997314</t>
   </si>
   <si>
     <t xml:space="preserve">25.2896270751953</t>
@@ -1508,19 +1508,19 @@
     <t xml:space="preserve">24.5054512023926</t>
   </si>
   <si>
-    <t xml:space="preserve">24.015344619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.623254776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8390808105469</t>
+    <t xml:space="preserve">24.0153427124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6232566833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8390789031982</t>
   </si>
   <si>
     <t xml:space="preserve">23.3291893005371</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9371032714844</t>
+    <t xml:space="preserve">22.937105178833</t>
   </si>
   <si>
     <t xml:space="preserve">23.7212772369385</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">24.1133651733398</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0351238250732</t>
+    <t xml:space="preserve">23.0351257324219</t>
   </si>
   <si>
     <t xml:space="preserve">23.1331481933594</t>
@@ -1544,10 +1544,10 @@
     <t xml:space="preserve">23.819299697876</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2509498596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7608432769775</t>
+    <t xml:space="preserve">22.2509517669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7608413696289</t>
   </si>
   <si>
     <t xml:space="preserve">21.9568843841553</t>
@@ -1556,25 +1556,25 @@
     <t xml:space="preserve">22.1529273986816</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7711753845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6439247131348</t>
+    <t xml:space="preserve">18.7711772918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3300800323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6439266204834</t>
   </si>
   <si>
     <t xml:space="preserve">18.5261211395264</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9964466094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5845794677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1924953460693</t>
+    <t xml:space="preserve">19.9964485168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5845775604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1924934387207</t>
   </si>
   <si>
     <t xml:space="preserve">19.8984260559082</t>
@@ -56863,7 +56863,7 @@
     </row>
     <row r="2093">
       <c r="A2093" s="1" t="n">
-        <v>45940.5637268518</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2093" t="n">
         <v>1375</v>
@@ -56884,6 +56884,32 @@
         <v>667</v>
       </c>
       <c r="H2093" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" s="1" t="n">
+        <v>45943.3930671296</v>
+      </c>
+      <c r="B2094" t="n">
+        <v>1750</v>
+      </c>
+      <c r="C2094" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="D2094" t="n">
+        <v>14</v>
+      </c>
+      <c r="E2094" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="F2094" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G2094" t="s">
+        <v>665</v>
+      </c>
+      <c r="H2094" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CULT.MI.xlsx
+++ b/data/CULT.MI.xlsx
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68585252761841</t>
+    <t xml:space="preserve">4.68585348129272</t>
   </si>
   <si>
     <t xml:space="preserve">CULT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57666730880737</t>
+    <t xml:space="preserve">4.57666778564453</t>
   </si>
   <si>
     <t xml:space="preserve">4.59486532211304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60851383209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58576631546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48931980133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5630202293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51297616958618</t>
+    <t xml:space="preserve">4.60851335525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58576679229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48931932449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56301927566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51297569274902</t>
   </si>
   <si>
     <t xml:space="preserve">4.46020364761353</t>
@@ -71,25 +71,25 @@
     <t xml:space="preserve">4.29824638366699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21271800994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1817831993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23091459274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36375713348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38195419311523</t>
+    <t xml:space="preserve">4.21271848678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18178224563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23091554641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36375761032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38195466995239</t>
   </si>
   <si>
     <t xml:space="preserve">4.35101890563965</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28914737701416</t>
+    <t xml:space="preserve">4.28914785385132</t>
   </si>
   <si>
     <t xml:space="preserve">4.24183416366577</t>
@@ -107,55 +107,55 @@
     <t xml:space="preserve">4.10899209976196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9961678981781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04712104797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0398416519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96341252326965</t>
+    <t xml:space="preserve">3.99616765975952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04712057113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03984212875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96341276168823</t>
   </si>
   <si>
     <t xml:space="preserve">4.07441711425781</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32008361816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24911308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9797899723053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06895780563354</t>
+    <t xml:space="preserve">4.3200831413269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24911260604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97979021072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0689582824707</t>
   </si>
   <si>
     <t xml:space="preserve">4.05439949035645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98524975776672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0507607460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07259750366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0380220413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04530143737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03074312210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01254510879517</t>
+    <t xml:space="preserve">3.98524880409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05075979232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07259702682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03802251815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04530191421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03074264526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01254606246948</t>
   </si>
   <si>
     <t xml:space="preserve">4.04894065856934</t>
@@ -167,94 +167,94 @@
     <t xml:space="preserve">4.07623720169067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91245889663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99070906639099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01072549819946</t>
+    <t xml:space="preserve">3.9124596118927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99070858955383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01072597503662</t>
   </si>
   <si>
     <t xml:space="preserve">3.92155790328979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00162649154663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05803871154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21635675430298</t>
+    <t xml:space="preserve">4.00162696838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05803918838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21635723114014</t>
   </si>
   <si>
     <t xml:space="preserve">4.22181701660156</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18542146682739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16176462173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35465717315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28186893463135</t>
+    <t xml:space="preserve">4.18542098999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16176414489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3546576499939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28186750411987</t>
   </si>
   <si>
     <t xml:space="preserve">4.26731061935425</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39287376403809</t>
+    <t xml:space="preserve">4.39287281036377</t>
   </si>
   <si>
     <t xml:space="preserve">4.36739683151245</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17814350128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27458906173706</t>
+    <t xml:space="preserve">4.17814254760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27458953857422</t>
   </si>
   <si>
     <t xml:space="preserve">4.31826305389404</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35647821426392</t>
+    <t xml:space="preserve">4.35647773742676</t>
   </si>
   <si>
     <t xml:space="preserve">4.26549100875854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26367044448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27640867233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14902591705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3582968711853</t>
+    <t xml:space="preserve">4.26367092132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27640914916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14902687072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35829782485962</t>
   </si>
   <si>
     <t xml:space="preserve">4.35283803939819</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29460573196411</t>
+    <t xml:space="preserve">4.29460668563843</t>
   </si>
   <si>
     <t xml:space="preserve">4.2036190032959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24001407623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34009981155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42926788330078</t>
+    <t xml:space="preserve">4.24001455307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34010076522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42926740646362</t>
   </si>
   <si>
     <t xml:space="preserve">4.34919929504395</t>
@@ -263,10 +263,10 @@
     <t xml:space="preserve">4.33646011352539</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33100128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32190322875977</t>
+    <t xml:space="preserve">4.33100175857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32190275192261</t>
   </si>
   <si>
     <t xml:space="preserve">4.46748208999634</t>
@@ -278,64 +278,64 @@
     <t xml:space="preserve">4.2855076789856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.830570936203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90336060523987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88516306877136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87606430053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00344705581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93065643310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99434733390808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08533477783203</t>
+    <t xml:space="preserve">3.83057069778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90336036682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88516402244568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87606477737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00344657897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93065667152405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99434781074524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08533525466919</t>
   </si>
   <si>
     <t xml:space="preserve">3.96705174446106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86696481704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84876799583435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85786628723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8123733997345</t>
+    <t xml:space="preserve">3.86696577072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84876775741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85786652565002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81237292289734</t>
   </si>
   <si>
     <t xml:space="preserve">3.80327415466309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77597808837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97615027427673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94885468482971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13992786407471</t>
+    <t xml:space="preserve">3.77597832679749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97615003585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94885444641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13992881774902</t>
   </si>
   <si>
     <t xml:space="preserve">4.16722393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33528280258179</t>
+    <t xml:space="preserve">4.33528327941895</t>
   </si>
   <si>
     <t xml:space="preserve">4.21485900878906</t>
@@ -347,25 +347,25 @@
     <t xml:space="preserve">4.42791795730591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19633150100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.168541431427</t>
+    <t xml:space="preserve">4.1963324546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16854095458984</t>
   </si>
   <si>
     <t xml:space="preserve">4.29822969436646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30749225616455</t>
+    <t xml:space="preserve">4.30749368667603</t>
   </si>
   <si>
     <t xml:space="preserve">4.27970266342163</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39086389541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40012788772583</t>
+    <t xml:space="preserve">4.3908634185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40012693405151</t>
   </si>
   <si>
     <t xml:space="preserve">4.35381031036377</t>
@@ -374,28 +374,28 @@
     <t xml:space="preserve">4.08517074584961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93695545196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00179958343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97400951385498</t>
+    <t xml:space="preserve">3.93695616722107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00180006027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97400975227356</t>
   </si>
   <si>
     <t xml:space="preserve">4.03885364532471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9462194442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95548295974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23338651657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22412204742432</t>
+    <t xml:space="preserve">3.94621992111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95548343658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23338603973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22412252426147</t>
   </si>
   <si>
     <t xml:space="preserve">4.24264907836914</t>
@@ -413,31 +413,31 @@
     <t xml:space="preserve">3.89990234375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89063882827759</t>
+    <t xml:space="preserve">3.89063835144043</t>
   </si>
   <si>
     <t xml:space="preserve">4.07590770721436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06664323806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79800486564636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73316073417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86284899711609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71463394165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70537042617798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77021479606628</t>
+    <t xml:space="preserve">4.06664419174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7980043888092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73316097259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86284875869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71463370323181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70537066459656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77021455764771</t>
   </si>
   <si>
     <t xml:space="preserve">3.3904139995575</t>
@@ -446,94 +446,94 @@
     <t xml:space="preserve">3.44599461555481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58494544029236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68684387207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60347294807434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52010178565979</t>
+    <t xml:space="preserve">3.58494567871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68684363365173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60347270965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52010226249695</t>
   </si>
   <si>
     <t xml:space="preserve">3.37188720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46452140808105</t>
+    <t xml:space="preserve">3.46452116966248</t>
   </si>
   <si>
     <t xml:space="preserve">3.53862881660461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52936553955078</t>
+    <t xml:space="preserve">3.5293653011322</t>
   </si>
   <si>
     <t xml:space="preserve">3.45525789260864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34409642219543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07545757293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14956521987915</t>
+    <t xml:space="preserve">3.34409689903259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07545733451843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14956474304199</t>
   </si>
   <si>
     <t xml:space="preserve">3.29777956008911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31630611419678</t>
+    <t xml:space="preserve">3.31630635261536</t>
   </si>
   <si>
     <t xml:space="preserve">3.23293566703796</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24219870567322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02914047241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20514583587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25146222114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10324764251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1588282585144</t>
+    <t xml:space="preserve">3.24219918251038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02914071083069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20514535903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25146245956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10324740409851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15882849693298</t>
   </si>
   <si>
     <t xml:space="preserve">2.91797924041748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74197435379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77902770042419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87166213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96429634094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85313534736633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83460831642151</t>
+    <t xml:space="preserve">2.74197459220886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77902793884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.871661901474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9642961025238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85313510894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83460807800293</t>
   </si>
   <si>
     <t xml:space="preserve">2.84387183189392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72344708442688</t>
+    <t xml:space="preserve">2.72344732284546</t>
   </si>
   <si>
     <t xml:space="preserve">2.76050114631653</t>
@@ -542,37 +542,37 @@
     <t xml:space="preserve">2.76976442337036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63081312179565</t>
+    <t xml:space="preserve">2.63081288337708</t>
   </si>
   <si>
     <t xml:space="preserve">2.67713046073914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38070034980774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36217379570007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29732966423035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31585621833801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35291028022766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26953935623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23248529434204</t>
+    <t xml:space="preserve">2.38070058822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36217355728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29732942581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31585645675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35291004180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26953959465027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2324857711792</t>
   </si>
   <si>
     <t xml:space="preserve">2.28806614875793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0842707157135</t>
+    <t xml:space="preserve">2.08427047729492</t>
   </si>
   <si>
     <t xml:space="preserve">2.1305878162384</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">2.24174904823303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11206102371216</t>
+    <t xml:space="preserve">2.11206126213074</t>
   </si>
   <si>
     <t xml:space="preserve">2.17690515518188</t>
@@ -593,19 +593,19 @@
     <t xml:space="preserve">2.03795385360718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99163627624512</t>
+    <t xml:space="preserve">1.99163687229156</t>
   </si>
   <si>
     <t xml:space="preserve">1.88047552108765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94531941413879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92679250240326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16764140129089</t>
+    <t xml:space="preserve">1.94531917572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92679262161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16764163970947</t>
   </si>
   <si>
     <t xml:space="preserve">2.13985133171082</t>
@@ -614,28 +614,28 @@
     <t xml:space="preserve">2.21395897865295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4084906578064</t>
+    <t xml:space="preserve">2.40849041938782</t>
   </si>
   <si>
     <t xml:space="preserve">2.48259806632996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42701768875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38996362686157</t>
+    <t xml:space="preserve">2.42701745033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38996410369873</t>
   </si>
   <si>
     <t xml:space="preserve">2.46583580970764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50406575202942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65698575973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71433091163635</t>
+    <t xml:space="preserve">2.504065990448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65698599815369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71433067321777</t>
   </si>
   <si>
     <t xml:space="preserve">2.54229545593262</t>
@@ -647,25 +647,25 @@
     <t xml:space="preserve">2.52318096160889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42760610580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38937568664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48495078086853</t>
+    <t xml:space="preserve">2.42760562896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38937592506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48495054244995</t>
   </si>
   <si>
     <t xml:space="preserve">2.61875581741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56141066551208</t>
+    <t xml:space="preserve">2.56141090393066</t>
   </si>
   <si>
     <t xml:space="preserve">2.63787078857422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73344564437866</t>
+    <t xml:space="preserve">2.73344612121582</t>
   </si>
   <si>
     <t xml:space="preserve">2.69521594047546</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">2.75256085395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8099057674408</t>
+    <t xml:space="preserve">2.80990552902222</t>
   </si>
   <si>
     <t xml:space="preserve">2.82902073860168</t>
@@ -683,19 +683,19 @@
     <t xml:space="preserve">2.84813594818115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05840110778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86725091934204</t>
+    <t xml:space="preserve">3.05840086936951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86725115776062</t>
   </si>
   <si>
     <t xml:space="preserve">2.77167582511902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.676100730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59964060783386</t>
+    <t xml:space="preserve">2.67610096931458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59964084625244</t>
   </si>
   <si>
     <t xml:space="preserve">2.44672083854675</t>
@@ -704,16 +704,16 @@
     <t xml:space="preserve">2.37026071548462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09663128852844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34512615203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45981597900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74654150009155</t>
+    <t xml:space="preserve">3.09663105010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34512591362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45981621742249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74654126167297</t>
   </si>
   <si>
     <t xml:space="preserve">3.76565623283386</t>
@@ -725,52 +725,52 @@
     <t xml:space="preserve">4.10972595214844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97592091560364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88034629821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82300114631653</t>
+    <t xml:space="preserve">3.9759213924408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88034605979919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82300138473511</t>
   </si>
   <si>
     <t xml:space="preserve">3.44070100784302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40247082710266</t>
+    <t xml:space="preserve">3.40247106552124</t>
   </si>
   <si>
     <t xml:space="preserve">3.36424112319946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68919587135315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72742652893066</t>
+    <t xml:space="preserve">3.68919610977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72742629051208</t>
   </si>
   <si>
     <t xml:space="preserve">3.70831155776978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5745062828064</t>
+    <t xml:space="preserve">3.57450604438782</t>
   </si>
   <si>
     <t xml:space="preserve">3.55539107322693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51716136932373</t>
+    <t xml:space="preserve">3.51716113090515</t>
   </si>
   <si>
     <t xml:space="preserve">3.63185095787048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53627634048462</t>
+    <t xml:space="preserve">3.53627586364746</t>
   </si>
   <si>
     <t xml:space="preserve">3.61273598670959</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65096616744995</t>
+    <t xml:space="preserve">3.65096640586853</t>
   </si>
   <si>
     <t xml:space="preserve">3.24955105781555</t>
@@ -779,10 +779,10 @@
     <t xml:space="preserve">3.32601118087769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42158579826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3068962097168</t>
+    <t xml:space="preserve">3.42158603668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30689597129822</t>
   </si>
   <si>
     <t xml:space="preserve">3.38335633277893</t>
@@ -794,19 +794,19 @@
     <t xml:space="preserve">3.47893118858337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49804639816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28778123855591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67008113861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80388617515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93769097328186</t>
+    <t xml:space="preserve">3.49804615974426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28778100013733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67008090019226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80388593673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93769121170044</t>
   </si>
   <si>
     <t xml:space="preserve">4.03326606750488</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">4.30087661743164</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53025579452515</t>
+    <t xml:space="preserve">4.53025674819946</t>
   </si>
   <si>
     <t xml:space="preserve">4.51114130020142</t>
@@ -830,10 +830,10 @@
     <t xml:space="preserve">4.49202585220337</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43468189239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62583208084106</t>
+    <t xml:space="preserve">4.4346809387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62583160400391</t>
   </si>
   <si>
     <t xml:space="preserve">4.74052143096924</t>
@@ -845,10 +845,10 @@
     <t xml:space="preserve">4.70229148864746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68317651748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77875137329102</t>
+    <t xml:space="preserve">4.68317699432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77875185012817</t>
   </si>
   <si>
     <t xml:space="preserve">4.56848669052124</t>
@@ -857,64 +857,64 @@
     <t xml:space="preserve">4.66406202316284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72140693664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87432622909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96990156173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92211389541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11326456069946</t>
+    <t xml:space="preserve">4.72140645980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87432670593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9699010848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92211437225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1132640838623</t>
   </si>
   <si>
     <t xml:space="preserve">5.16105127334595</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20883941650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25662708282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30441427230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44777631759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6389274597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.591139793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81332683563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71643877029419</t>
+    <t xml:space="preserve">5.20883893966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25662660598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30441474914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44777679443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63892650604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59113883972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81332731246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71643781661987</t>
   </si>
   <si>
     <t xml:space="preserve">5.42577171325684</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13510513305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84443855285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8250617980957</t>
+    <t xml:space="preserve">5.1351056098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8444390296936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82506132125854</t>
   </si>
   <si>
     <t xml:space="preserve">4.80568313598633</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59252738952637</t>
+    <t xml:space="preserve">4.59252834320068</t>
   </si>
   <si>
     <t xml:space="preserve">4.55377197265625</t>
@@ -923,43 +923,43 @@
     <t xml:space="preserve">4.76692771911621</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03821659088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98977184295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08665990829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18354988098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94132709503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23199415206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74755001068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2804388999939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89288330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63128423690796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53439521789551</t>
+    <t xml:space="preserve">5.03821611404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9897723197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08666038513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18354940414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94132804870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23199367523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74755048751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28043842315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89288377761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6312837600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53439474105835</t>
   </si>
   <si>
     <t xml:space="preserve">4.67003917694092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78630590438843</t>
+    <t xml:space="preserve">4.78630542755127</t>
   </si>
   <si>
     <t xml:space="preserve">4.72817277908325</t>
@@ -971,22 +971,22 @@
     <t xml:space="preserve">5.91021537780762</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61954927444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32888317108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37732744216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57110548019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47421550750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66799402236938</t>
+    <t xml:space="preserve">5.61954879760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32888269424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37732791900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57110500335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47421598434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66799306869507</t>
   </si>
   <si>
     <t xml:space="preserve">6.73376989364624</t>
@@ -995,34 +995,34 @@
     <t xml:space="preserve">6.29777050018311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44310331344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68532562255859</t>
+    <t xml:space="preserve">6.4431037902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68532657623291</t>
   </si>
   <si>
     <t xml:space="preserve">6.5884370803833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63688182830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24932670593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34621524810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5399923324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3946590423584</t>
+    <t xml:space="preserve">6.63688135147095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24932622909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34621477127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53999280929565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39465951919556</t>
   </si>
   <si>
     <t xml:space="preserve">8.71999073028564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99332332611084</t>
+    <t xml:space="preserve">7.99332475662231</t>
   </si>
   <si>
     <t xml:space="preserve">8.09021377563477</t>
@@ -1031,52 +1031,52 @@
     <t xml:space="preserve">8.04176807403564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94488048553467</t>
+    <t xml:space="preserve">7.94487953186035</t>
   </si>
   <si>
     <t xml:space="preserve">7.84799098968506</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89643526077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38087940216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2702102661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88265419006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1733198165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97954368591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0764331817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2390985488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6266536712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.079984664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2737636566162</t>
+    <t xml:space="preserve">7.89643621444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38087749481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2702112197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88265609741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1733207702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9795446395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0764322280884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2390975952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.626654624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0799856185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2737627029419</t>
   </si>
   <si>
     <t xml:space="preserve">12.9830961227417</t>
   </si>
   <si>
-    <t xml:space="preserve">14.436427116394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3395395278931</t>
+    <t xml:space="preserve">14.4364280700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3395385742188</t>
   </si>
   <si>
     <t xml:space="preserve">15.0177612304688</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">15.1930656433105</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0956735610962</t>
+    <t xml:space="preserve">15.0956745147705</t>
   </si>
   <si>
     <t xml:space="preserve">14.9008903503418</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">12.4661045074463</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4400196075439</t>
+    <t xml:space="preserve">13.4400205612183</t>
   </si>
   <si>
     <t xml:space="preserve">13.9269771575928</t>
@@ -1112,70 +1112,70 @@
     <t xml:space="preserve">14.0243673324585</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2191514968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8034982681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4139337539673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6087169647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7061080932617</t>
+    <t xml:space="preserve">14.2191524505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8034992218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.413932800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6087160110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.706109046936</t>
   </si>
   <si>
     <t xml:space="preserve">14.5113248825073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3426284790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1217594146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3165416717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8295850753784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.537410736084</t>
+    <t xml:space="preserve">13.3426275253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1217584609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3165426254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8295841217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5374097824097</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452363967896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8556699752808</t>
+    <t xml:space="preserve">12.8556709289551</t>
   </si>
   <si>
     <t xml:space="preserve">12.3687133789062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.758279800415</t>
+    <t xml:space="preserve">12.7582788467407</t>
   </si>
   <si>
     <t xml:space="preserve">12.5634965896606</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1739292144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6869735717773</t>
+    <t xml:space="preserve">12.1739301681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6869745254517</t>
   </si>
   <si>
     <t xml:space="preserve">11.1026239395142</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93392658233643</t>
+    <t xml:space="preserve">9.93392753601074</t>
   </si>
   <si>
     <t xml:space="preserve">10.7130584716797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2000169754028</t>
+    <t xml:space="preserve">11.2000160217285</t>
   </si>
   <si>
     <t xml:space="preserve">11.9791479110718</t>
@@ -1187,46 +1187,46 @@
     <t xml:space="preserve">10.9078416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2974081039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3947992324829</t>
+    <t xml:space="preserve">11.2974071502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3947982788086</t>
   </si>
   <si>
     <t xml:space="preserve">11.589581489563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0052318572998</t>
+    <t xml:space="preserve">11.0052328109741</t>
   </si>
   <si>
     <t xml:space="preserve">11.7843647003174</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4921913146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.810450553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4208850860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2260999679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3234930038452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1287107467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0313186645508</t>
+    <t xml:space="preserve">11.4921903610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8104515075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4208841323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2261009216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3234939575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1287097930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0313196182251</t>
   </si>
   <si>
     <t xml:space="preserve">9.73914432525635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54436111450195</t>
+    <t xml:space="preserve">9.54436206817627</t>
   </si>
   <si>
     <t xml:space="preserve">9.8365364074707</t>
@@ -1235,34 +1235,34 @@
     <t xml:space="preserve">9.34957885742188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49566555023193</t>
+    <t xml:space="preserve">9.49566650390625</t>
   </si>
   <si>
     <t xml:space="preserve">12.2713222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9530611038208</t>
+    <t xml:space="preserve">12.9530620574951</t>
   </si>
   <si>
     <t xml:space="preserve">15.6800222396851</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7321929931641</t>
+    <t xml:space="preserve">13.7321939468384</t>
   </si>
   <si>
     <t xml:space="preserve">14.1704559326172</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3652381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0730628967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1443691253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5364570617676</t>
+    <t xml:space="preserve">14.3652372360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0730638504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1443700790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5364561080933</t>
   </si>
   <si>
     <t xml:space="preserve">15.585467338562</t>
@@ -1274,22 +1274,22 @@
     <t xml:space="preserve">15.193380355835</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4874467849731</t>
+    <t xml:space="preserve">15.4874458312988</t>
   </si>
   <si>
     <t xml:space="preserve">15.4384346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2423915863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3894243240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9973363876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8993139266968</t>
+    <t xml:space="preserve">15.2423906326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3894233703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9973373413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8993148803711</t>
   </si>
   <si>
     <t xml:space="preserve">15.0463485717773</t>
@@ -1301,43 +1301,43 @@
     <t xml:space="preserve">13.9190969467163</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1641511917114</t>
+    <t xml:space="preserve">14.1641502380371</t>
   </si>
   <si>
     <t xml:space="preserve">13.7230529785156</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8210744857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3601942062378</t>
+    <t xml:space="preserve">13.8210754394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3601951599121</t>
   </si>
   <si>
     <t xml:space="preserve">13.6250314712524</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8700866699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6740427017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7720642089844</t>
+    <t xml:space="preserve">13.8700847625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6740417480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7720651626587</t>
   </si>
   <si>
     <t xml:space="preserve">14.0171184539795</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1839332580566</t>
+    <t xml:space="preserve">13.1839323043823</t>
   </si>
   <si>
     <t xml:space="preserve">13.5270099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9483261108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4092063903809</t>
+    <t xml:space="preserve">14.9483251571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4092054367065</t>
   </si>
   <si>
     <t xml:space="preserve">14.8503036499023</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">14.6052494049072</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7032718658447</t>
+    <t xml:space="preserve">14.7032709121704</t>
   </si>
   <si>
     <t xml:space="preserve">14.5562391281128</t>
@@ -1358,25 +1358,25 @@
     <t xml:space="preserve">14.507227897644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0661296844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3309669494629</t>
+    <t xml:space="preserve">14.0661306381226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3309659957886</t>
   </si>
   <si>
     <t xml:space="preserve">13.4779987335205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2819547653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8898677825928</t>
+    <t xml:space="preserve">13.2819557189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8898668289185</t>
   </si>
   <si>
     <t xml:space="preserve">12.7428350448608</t>
   </si>
   <si>
-    <t xml:space="preserve">12.987889289856</t>
+    <t xml:space="preserve">12.9878902435303</t>
   </si>
   <si>
     <t xml:space="preserve">13.1349220275879</t>
@@ -1391,16 +1391,16 @@
     <t xml:space="preserve">11.3215188980103</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3017377853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0859127044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4289884567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8305215835571</t>
+    <t xml:space="preserve">12.301736831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0859117507935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4289875030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8305225372314</t>
   </si>
   <si>
     <t xml:space="preserve">15.7324991226196</t>
@@ -1409,22 +1409,22 @@
     <t xml:space="preserve">15.8795328140259</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9775533676147</t>
+    <t xml:space="preserve">15.9775552749634</t>
   </si>
   <si>
     <t xml:space="preserve">16.3696422576904</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6834888458252</t>
+    <t xml:space="preserve">15.6834897994995</t>
   </si>
   <si>
     <t xml:space="preserve">15.7815113067627</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2226085662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0265674591064</t>
+    <t xml:space="preserve">16.2226104736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0265655517578</t>
   </si>
   <si>
     <t xml:space="preserve">16.0755767822266</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">15.9285440444946</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1735973358154</t>
+    <t xml:space="preserve">16.1735992431641</t>
   </si>
   <si>
     <t xml:space="preserve">16.2716197967529</t>
@@ -1445,13 +1445,13 @@
     <t xml:space="preserve">18.7221660614014</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0162315368652</t>
+    <t xml:space="preserve">19.0162296295166</t>
   </si>
   <si>
     <t xml:space="preserve">19.7023849487305</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6043605804443</t>
+    <t xml:space="preserve">19.604362487793</t>
   </si>
   <si>
     <t xml:space="preserve">19.8004055023193</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">23.9173202514648</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5450172424316</t>
+    <t xml:space="preserve">22.545015335083</t>
   </si>
   <si>
     <t xml:space="preserve">23.5252342224121</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">20.4865570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6826019287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3687553405762</t>
+    <t xml:space="preserve">20.6826038360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3687534332275</t>
   </si>
   <si>
     <t xml:space="preserve">22.6430377960205</t>
@@ -1496,49 +1496,49 @@
     <t xml:space="preserve">24.9955615997314</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2896270751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6034755706787</t>
+    <t xml:space="preserve">25.2896251678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6034736633301</t>
   </si>
   <si>
     <t xml:space="preserve">24.8975391387939</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5054512023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0153427124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6232566833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8390789031982</t>
+    <t xml:space="preserve">24.5054531097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.015344619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.623254776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8390808105469</t>
   </si>
   <si>
     <t xml:space="preserve">23.3291893005371</t>
   </si>
   <si>
-    <t xml:space="preserve">22.937105178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7212772369385</t>
+    <t xml:space="preserve">22.9371032714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7212791442871</t>
   </si>
   <si>
     <t xml:space="preserve">24.1133651733398</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0351257324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1331481933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2113876342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4074287414551</t>
+    <t xml:space="preserve">23.0351238250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1331462860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2113857269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4074306488037</t>
   </si>
   <si>
     <t xml:space="preserve">23.819299697876</t>
@@ -1553,16 +1553,16 @@
     <t xml:space="preserve">21.9568843841553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1529273986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7711772918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3300800323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6439266204834</t>
+    <t xml:space="preserve">22.1529293060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7711753845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6439247131348</t>
   </si>
   <si>
     <t xml:space="preserve">18.5261211395264</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">19.9964485168457</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5845775604248</t>
+    <t xml:space="preserve">20.5845794677734</t>
   </si>
   <si>
     <t xml:space="preserve">20.1924934387207</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">19.8984260559082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3885364532471</t>
+    <t xml:space="preserve">20.3885345458984</t>
   </si>
   <si>
     <t xml:space="preserve">19.4049549102783</t>
@@ -1595,10 +1595,10 @@
     <t xml:space="preserve">19.5527095794678</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7989635467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6019592285156</t>
+    <t xml:space="preserve">19.7989654541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.601957321167</t>
   </si>
   <si>
     <t xml:space="preserve">18.9616947174072</t>
@@ -1628,13 +1628,13 @@
     <t xml:space="preserve">20.4884796142578</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5869827270508</t>
+    <t xml:space="preserve">20.5869808197021</t>
   </si>
   <si>
     <t xml:space="preserve">19.9959678649902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4542045593262</t>
+    <t xml:space="preserve">19.4542064666748</t>
   </si>
   <si>
     <t xml:space="preserve">19.5034561157227</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">19.207950592041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0259227752686</t>
+    <t xml:space="preserve">18.0259208679199</t>
   </si>
   <si>
     <t xml:space="preserve">18.075174331665</t>
@@ -1670,19 +1670,19 @@
     <t xml:space="preserve">17.9274196624756</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9766693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4349098205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.173677444458</t>
+    <t xml:space="preserve">17.9766712188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.434907913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1736755371094</t>
   </si>
   <si>
     <t xml:space="preserve">18.4199314117432</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7839870452881</t>
+    <t xml:space="preserve">20.7839889526367</t>
   </si>
   <si>
     <t xml:space="preserve">20.3899784088135</t>
@@ -1691,10 +1691,10 @@
     <t xml:space="preserve">19.7004623413086</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9124450683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.109447479248</t>
+    <t xml:space="preserve">18.9124431610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1094455718994</t>
   </si>
   <si>
     <t xml:space="preserve">18.8631916046143</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">18.5184326171875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7154369354248</t>
+    <t xml:space="preserve">18.7154388427734</t>
   </si>
   <si>
     <t xml:space="preserve">18.2229270935059</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">17.7796649932861</t>
   </si>
   <si>
-    <t xml:space="preserve">18.567684173584</t>
+    <t xml:space="preserve">18.5676860809326</t>
   </si>
   <si>
     <t xml:space="preserve">17.7304153442383</t>
@@ -1724,16 +1724,16 @@
     <t xml:space="preserve">18.2721767425537</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6811656951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8781681060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1244239807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6319122314453</t>
+    <t xml:space="preserve">17.6811637878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8781700134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1244258880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6319141387939</t>
   </si>
   <si>
     <t xml:space="preserve">17.4841594696045</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">17.3856582641602</t>
   </si>
   <si>
-    <t xml:space="preserve">17.533411026001</t>
+    <t xml:space="preserve">17.5334091186523</t>
   </si>
   <si>
     <t xml:space="preserve">17.1886520385742</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">16.4991359710693</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8931446075439</t>
+    <t xml:space="preserve">16.8931465148926</t>
   </si>
   <si>
     <t xml:space="preserve">16.4498863220215</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">16.6468906402588</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7946434020996</t>
+    <t xml:space="preserve">16.794641494751</t>
   </si>
   <si>
     <t xml:space="preserve">16.7453918457031</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">14.6275930404663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9723510742188</t>
+    <t xml:space="preserve">14.9723501205444</t>
   </si>
   <si>
     <t xml:space="preserve">14.7260942459106</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">15.1201047897339</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3663606643677</t>
+    <t xml:space="preserve">15.3663597106934</t>
   </si>
   <si>
     <t xml:space="preserve">15.464861869812</t>
@@ -1805,16 +1805,16 @@
     <t xml:space="preserve">14.7753458023071</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4798383712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2828350067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5783424377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0858297348022</t>
+    <t xml:space="preserve">14.4798393249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2828340530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5783414840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0858306884766</t>
   </si>
   <si>
     <t xml:space="preserve">14.2335834503174</t>
@@ -56889,7 +56889,7 @@
     </row>
     <row r="2094">
       <c r="A2094" s="1" t="n">
-        <v>45943.3930671296</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2094" t="n">
         <v>1750</v>
@@ -56910,6 +56910,32 @@
         <v>665</v>
       </c>
       <c r="H2094" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" s="1" t="n">
+        <v>45944.6494212963</v>
+      </c>
+      <c r="B2095" t="n">
+        <v>2125</v>
+      </c>
+      <c r="C2095" t="n">
+        <v>14.6999998092651</v>
+      </c>
+      <c r="D2095" t="n">
+        <v>13.6000003814697</v>
+      </c>
+      <c r="E2095" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="F2095" t="n">
+        <v>13.8999996185303</v>
+      </c>
+      <c r="G2095" t="s">
+        <v>705</v>
+      </c>
+      <c r="H2095" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CULT.MI.xlsx
+++ b/data/CULT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="709">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,49 +38,49 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68585252761841</t>
+    <t xml:space="preserve">4.68585300445557</t>
   </si>
   <si>
     <t xml:space="preserve">CULT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57666778564453</t>
+    <t xml:space="preserve">4.57666730880737</t>
   </si>
   <si>
     <t xml:space="preserve">4.59486532211304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60851287841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58576679229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48932027816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56301879882812</t>
+    <t xml:space="preserve">4.60851383209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58576631546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48931932449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56301975250244</t>
   </si>
   <si>
     <t xml:space="preserve">4.51297616958618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46020364761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29824542999268</t>
+    <t xml:space="preserve">4.46020412445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29824590682983</t>
   </si>
   <si>
     <t xml:space="preserve">4.21271753311157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18178224563599</t>
+    <t xml:space="preserve">4.18178272247314</t>
   </si>
   <si>
     <t xml:space="preserve">4.23091554641724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36375665664673</t>
+    <t xml:space="preserve">4.36375713348389</t>
   </si>
   <si>
     <t xml:space="preserve">4.38195466995239</t>
@@ -104,109 +104,109 @@
     <t xml:space="preserve">4.09443426132202</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10899257659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99616765975952</t>
+    <t xml:space="preserve">4.10899209976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9961678981781</t>
   </si>
   <si>
     <t xml:space="preserve">4.04712104797363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03984117507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96341180801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07441759109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32008266448975</t>
+    <t xml:space="preserve">4.0398416519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96341300010681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07441711425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32008361816406</t>
   </si>
   <si>
     <t xml:space="preserve">4.24911308288574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97978973388672</t>
+    <t xml:space="preserve">3.97978949546814</t>
   </si>
   <si>
     <t xml:space="preserve">4.06895732879639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0543999671936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98524951934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0507607460022</t>
+    <t xml:space="preserve">4.05439949035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98524975776672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05076026916504</t>
   </si>
   <si>
     <t xml:space="preserve">4.07259750366211</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0380220413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04530096054077</t>
+    <t xml:space="preserve">4.03802299499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04530143737793</t>
   </si>
   <si>
     <t xml:space="preserve">4.03074359893799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01254558563232</t>
+    <t xml:space="preserve">4.01254510879517</t>
   </si>
   <si>
     <t xml:space="preserve">4.04894113540649</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05985832214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07623672485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9124596118927</t>
+    <t xml:space="preserve">4.05985879898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07623624801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91246032714844</t>
   </si>
   <si>
     <t xml:space="preserve">3.99070858955383</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01072597503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92155766487122</t>
+    <t xml:space="preserve">4.0107250213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92155838012695</t>
   </si>
   <si>
     <t xml:space="preserve">4.00162696838379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05803966522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21635627746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2218165397644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18542098999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16176509857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35465812683105</t>
+    <t xml:space="preserve">4.05803871154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21635770797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22181701660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18542146682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16176462173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3546576499939</t>
   </si>
   <si>
     <t xml:space="preserve">4.28186845779419</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26731014251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39287281036377</t>
+    <t xml:space="preserve">4.26731061935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39287328720093</t>
   </si>
   <si>
     <t xml:space="preserve">4.36739683151245</t>
@@ -218,16 +218,16 @@
     <t xml:space="preserve">4.27458906173706</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31826305389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35647821426392</t>
+    <t xml:space="preserve">4.3182635307312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35647773742676</t>
   </si>
   <si>
     <t xml:space="preserve">4.26549053192139</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26367092132568</t>
+    <t xml:space="preserve">4.26367044448853</t>
   </si>
   <si>
     <t xml:space="preserve">4.27640867233276</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">4.14902687072754</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35829734802246</t>
+    <t xml:space="preserve">4.35829782485962</t>
   </si>
   <si>
     <t xml:space="preserve">4.35283803939819</t>
@@ -245,10 +245,10 @@
     <t xml:space="preserve">4.29460620880127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20361852645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24001455307007</t>
+    <t xml:space="preserve">4.2036190032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24001407623291</t>
   </si>
   <si>
     <t xml:space="preserve">4.34009981155396</t>
@@ -263,13 +263,13 @@
     <t xml:space="preserve">4.33646059036255</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33100080490112</t>
+    <t xml:space="preserve">4.33100175857544</t>
   </si>
   <si>
     <t xml:space="preserve">4.32190275192261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46748304367065</t>
+    <t xml:space="preserve">4.4674825668335</t>
   </si>
   <si>
     <t xml:space="preserve">4.45838403701782</t>
@@ -278,76 +278,76 @@
     <t xml:space="preserve">4.28550720214844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83057022094727</t>
+    <t xml:space="preserve">3.83057069778442</t>
   </si>
   <si>
     <t xml:space="preserve">3.90336060523987</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88516330718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87606501579285</t>
+    <t xml:space="preserve">3.8851625919342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87606453895569</t>
   </si>
   <si>
     <t xml:space="preserve">4.00344657897949</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93065738677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99434757232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08533573150635</t>
+    <t xml:space="preserve">3.93065714836121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99434733390808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08533477783203</t>
   </si>
   <si>
     <t xml:space="preserve">3.96705174446106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86696577072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84876847267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85786700248718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81237316131592</t>
+    <t xml:space="preserve">3.86696481704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84876823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8578667640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81237292289734</t>
   </si>
   <si>
     <t xml:space="preserve">3.80327415466309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77597808837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97615003585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94885492324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13992834091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16722440719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33528327941895</t>
+    <t xml:space="preserve">3.77597784996033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97615027427673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94885516166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13992881774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16722393035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33528280258179</t>
   </si>
   <si>
     <t xml:space="preserve">4.21485900878906</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31675672531128</t>
+    <t xml:space="preserve">4.31675624847412</t>
   </si>
   <si>
     <t xml:space="preserve">4.42791748046875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19633197784424</t>
+    <t xml:space="preserve">4.19633150100708</t>
   </si>
   <si>
     <t xml:space="preserve">4.168541431427</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">4.30749320983887</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27970218658447</t>
+    <t xml:space="preserve">4.27970314025879</t>
   </si>
   <si>
     <t xml:space="preserve">4.39086389541626</t>
@@ -371,76 +371,76 @@
     <t xml:space="preserve">4.35381031036377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08517074584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93695616722107</t>
+    <t xml:space="preserve">4.08517122268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93695545196533</t>
   </si>
   <si>
     <t xml:space="preserve">4.00180006027222</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97400975227356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03885316848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94621992111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95548319816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23338556289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22412157058716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24264860153198</t>
+    <t xml:space="preserve">3.97400999069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03885412216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9462194442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95548295974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23338651657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22412252426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24264907836914</t>
   </si>
   <si>
     <t xml:space="preserve">4.11296081542969</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26117563247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91842913627625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89990186691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89063835144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0759072303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06664323806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79800462722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73316073417664</t>
+    <t xml:space="preserve">4.26117610931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9184296131134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89990234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89063811302185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07590770721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06664371490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79800486564636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73316097259521</t>
   </si>
   <si>
     <t xml:space="preserve">3.86284875869751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71463418006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70537066459656</t>
+    <t xml:space="preserve">3.71463394165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70537042617798</t>
   </si>
   <si>
     <t xml:space="preserve">3.77021479606628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3904139995575</t>
+    <t xml:space="preserve">3.39041423797607</t>
   </si>
   <si>
     <t xml:space="preserve">3.44599461555481</t>
@@ -449,25 +449,25 @@
     <t xml:space="preserve">3.58494567871094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68684363365173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60347294807434</t>
+    <t xml:space="preserve">3.68684387207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60347270965576</t>
   </si>
   <si>
     <t xml:space="preserve">3.52010202407837</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37188720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46452116966248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53862881660461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5293653011322</t>
+    <t xml:space="preserve">3.37188744544983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46452140808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53862857818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52936553955078</t>
   </si>
   <si>
     <t xml:space="preserve">3.45525813102722</t>
@@ -482,28 +482,28 @@
     <t xml:space="preserve">3.14956498146057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29777956008911</t>
+    <t xml:space="preserve">3.29777979850769</t>
   </si>
   <si>
     <t xml:space="preserve">3.31630659103394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23293566703796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24219918251038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02913999557495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20514535903931</t>
+    <t xml:space="preserve">3.23293590545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2421989440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02914023399353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20514559745789</t>
   </si>
   <si>
     <t xml:space="preserve">3.25146269798279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10324764251709</t>
+    <t xml:space="preserve">3.10324788093567</t>
   </si>
   <si>
     <t xml:space="preserve">3.15882849693298</t>
@@ -521,31 +521,31 @@
     <t xml:space="preserve">2.871661901474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9642961025238</t>
+    <t xml:space="preserve">2.96429634094238</t>
   </si>
   <si>
     <t xml:space="preserve">2.85313510894775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83460831642151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84387183189392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72344732284546</t>
+    <t xml:space="preserve">2.83460855484009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8438720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72344708442688</t>
   </si>
   <si>
     <t xml:space="preserve">2.76050090789795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76976442337036</t>
+    <t xml:space="preserve">2.76976418495178</t>
   </si>
   <si>
     <t xml:space="preserve">2.63081288337708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67713022232056</t>
+    <t xml:space="preserve">2.67713046073914</t>
   </si>
   <si>
     <t xml:space="preserve">2.38070058822632</t>
@@ -560,37 +560,37 @@
     <t xml:space="preserve">2.31585645675659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35291028022766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26953935623169</t>
+    <t xml:space="preserve">2.35291051864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26953959465027</t>
   </si>
   <si>
     <t xml:space="preserve">2.2324857711792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28806614875793</t>
+    <t xml:space="preserve">2.28806638717651</t>
   </si>
   <si>
     <t xml:space="preserve">2.0842707157135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1305878162384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22322225570679</t>
+    <t xml:space="preserve">2.13058805465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22322249412537</t>
   </si>
   <si>
     <t xml:space="preserve">2.24174928665161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11206078529358</t>
+    <t xml:space="preserve">2.11206126213074</t>
   </si>
   <si>
     <t xml:space="preserve">2.17690515518188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0379536151886</t>
+    <t xml:space="preserve">2.03795385360718</t>
   </si>
   <si>
     <t xml:space="preserve">1.99163675308228</t>
@@ -599,121 +599,121 @@
     <t xml:space="preserve">1.88047540187836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94531917572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92679250240326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16764163970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13985109329224</t>
+    <t xml:space="preserve">1.94531905651093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92679262161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16764140129089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13985157012939</t>
   </si>
   <si>
     <t xml:space="preserve">2.21395874023438</t>
   </si>
   <si>
+    <t xml:space="preserve">2.40849089622498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48259830474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42701745033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38996362686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46583580970764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50406551361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65698575973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71433067321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54229593276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58052587509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52318096160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42760610580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38937568664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48495078086853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61875557899475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56141090393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63787078857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73344564437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69521594047546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75256109237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80990600585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82902073860168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84813594818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05840110778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86725091934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77167558670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.676100730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59964060783386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44672083854675</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.4084906578064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48259806632996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42701768875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38996410369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46583604812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50406551361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65698575973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71433067321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5422956943512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58052587509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52318096160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42760610580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38937592506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48495078086853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61875581741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56141090393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6378710269928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73344588279724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69521594047546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75256085395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8099057674408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82902121543884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84813570976257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05840086936951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86725068092346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7716760635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67610096931458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59964084625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44672060012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40849089622498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37026047706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09663081169128</t>
+    <t xml:space="preserve">2.37026071548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09663128852844</t>
   </si>
   <si>
     <t xml:space="preserve">3.34512591362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45981621742249</t>
+    <t xml:space="preserve">3.45981597900391</t>
   </si>
   <si>
     <t xml:space="preserve">3.74654126167297</t>
@@ -722,22 +722,22 @@
     <t xml:space="preserve">3.76565623283386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01415157318115</t>
+    <t xml:space="preserve">4.01415109634399</t>
   </si>
   <si>
     <t xml:space="preserve">4.10972690582275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97592115402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88034582138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82300114631653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4407012462616</t>
+    <t xml:space="preserve">3.9759213924408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88034629821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82300138473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44070100784302</t>
   </si>
   <si>
     <t xml:space="preserve">3.40247106552124</t>
@@ -746,10 +746,10 @@
     <t xml:space="preserve">3.36424112319946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68919634819031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72742605209351</t>
+    <t xml:space="preserve">3.68919610977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72742629051208</t>
   </si>
   <si>
     <t xml:space="preserve">3.7083113193512</t>
@@ -758,7 +758,7 @@
     <t xml:space="preserve">3.57450604438782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55539131164551</t>
+    <t xml:space="preserve">3.55539107322693</t>
   </si>
   <si>
     <t xml:space="preserve">3.51716113090515</t>
@@ -767,91 +767,91 @@
     <t xml:space="preserve">3.63185119628906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53627634048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61273622512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65096616744995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24955129623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32601070404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42158603668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30689597129822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38335633277893</t>
+    <t xml:space="preserve">3.5362765789032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61273598670959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65096592903137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24955105781555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32601118087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42158627510071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3068962097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38335609436035</t>
   </si>
   <si>
     <t xml:space="preserve">3.59362125396729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47893095016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49804592132568</t>
+    <t xml:space="preserve">3.47893118858337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49804615974426</t>
   </si>
   <si>
     <t xml:space="preserve">3.28778123855591</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67008066177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80388617515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93769121170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03326559066772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18618631362915</t>
+    <t xml:space="preserve">3.67008113861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80388641357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93769097328186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03326606750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18618679046631</t>
   </si>
   <si>
     <t xml:space="preserve">4.30087614059448</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5302562713623</t>
+    <t xml:space="preserve">4.53025579452515</t>
   </si>
   <si>
     <t xml:space="preserve">4.51114130020142</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58760166168213</t>
+    <t xml:space="preserve">4.58760213851929</t>
   </si>
   <si>
     <t xml:space="preserve">4.49202632904053</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43468141555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62583160400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74052095413208</t>
+    <t xml:space="preserve">4.43468189239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62583208084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74052143096924</t>
   </si>
   <si>
     <t xml:space="preserve">4.75963640213013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7022910118103</t>
+    <t xml:space="preserve">4.70229196548462</t>
   </si>
   <si>
     <t xml:space="preserve">4.68317651748657</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77875185012817</t>
+    <t xml:space="preserve">4.77875137329102</t>
   </si>
   <si>
     <t xml:space="preserve">4.56848621368408</t>
@@ -863,16 +863,16 @@
     <t xml:space="preserve">4.72140645980835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87432622909546</t>
+    <t xml:space="preserve">4.87432670593262</t>
   </si>
   <si>
     <t xml:space="preserve">4.96990156173706</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92211389541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11326360702515</t>
+    <t xml:space="preserve">4.92211437225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11326456069946</t>
   </si>
   <si>
     <t xml:space="preserve">5.16105175018311</t>
@@ -881,34 +881,34 @@
     <t xml:space="preserve">5.20883893966675</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25662660598755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30441474914551</t>
+    <t xml:space="preserve">5.25662708282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30441427230835</t>
   </si>
   <si>
     <t xml:space="preserve">5.44777631759644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63892650604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59113931655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81332635879517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71643781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42577123641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1351056098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8444390296936</t>
+    <t xml:space="preserve">5.63892698287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.591139793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81332683563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71643829345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42577171325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13510465621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84443855285645</t>
   </si>
   <si>
     <t xml:space="preserve">4.82506132125854</t>
@@ -917,31 +917,31 @@
     <t xml:space="preserve">4.80568313598633</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59252834320068</t>
+    <t xml:space="preserve">4.59252738952637</t>
   </si>
   <si>
     <t xml:space="preserve">4.55377244949341</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76692771911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03821659088135</t>
+    <t xml:space="preserve">4.76692819595337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03821611404419</t>
   </si>
   <si>
     <t xml:space="preserve">4.9897723197937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08666086196899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18354940414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94132709503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23199462890625</t>
+    <t xml:space="preserve">5.08666038513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18354988098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9413275718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23199415206909</t>
   </si>
   <si>
     <t xml:space="preserve">4.74755001068115</t>
@@ -953,13 +953,13 @@
     <t xml:space="preserve">4.89288330078125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63128328323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53439521789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67003965377808</t>
+    <t xml:space="preserve">4.6312837600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53439474105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67003917694092</t>
   </si>
   <si>
     <t xml:space="preserve">4.78630542755127</t>
@@ -968,16 +968,16 @@
     <t xml:space="preserve">4.72817230224609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70879459381104</t>
+    <t xml:space="preserve">4.70879507064819</t>
   </si>
   <si>
     <t xml:space="preserve">5.91021585464478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61954927444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32888269424438</t>
+    <t xml:space="preserve">5.61954879760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32888317108154</t>
   </si>
   <si>
     <t xml:space="preserve">5.37732744216919</t>
@@ -989,31 +989,31 @@
     <t xml:space="preserve">5.47421598434448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66799354553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73376941680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29777050018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4431037902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68532562255859</t>
+    <t xml:space="preserve">5.66799402236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73376989364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29777002334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44310426712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68532609939575</t>
   </si>
   <si>
     <t xml:space="preserve">6.5884370803833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63688135147095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24932622909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34621524810791</t>
+    <t xml:space="preserve">6.63688087463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2493257522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34621477127075</t>
   </si>
   <si>
     <t xml:space="preserve">6.53999280929565</t>
@@ -1022,73 +1022,73 @@
     <t xml:space="preserve">6.39465951919556</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71999073028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99332523345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09021282196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04176807403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94488000869751</t>
+    <t xml:space="preserve">8.71998977661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99332332611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09021377563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04176902770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94488048553467</t>
   </si>
   <si>
     <t xml:space="preserve">7.84799098968506</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89643573760986</t>
+    <t xml:space="preserve">7.89643478393555</t>
   </si>
   <si>
     <t xml:space="preserve">8.38087844848633</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2702112197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88265419006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.173321723938</t>
+    <t xml:space="preserve">10.270209312439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88265514373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1733207702637</t>
   </si>
   <si>
     <t xml:space="preserve">9.9795446395874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0764331817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2390985488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6266527175903</t>
+    <t xml:space="preserve">10.0764322280884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2390975952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6266536712646</t>
   </si>
   <si>
     <t xml:space="preserve">13.0799856185913</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2737627029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9830951690674</t>
+    <t xml:space="preserve">13.2737617492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.983097076416</t>
   </si>
   <si>
     <t xml:space="preserve">14.4364280700684</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3395395278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0177602767944</t>
+    <t xml:space="preserve">14.3395404815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0177612304688</t>
   </si>
   <si>
     <t xml:space="preserve">16.1669788360596</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1930646896362</t>
+    <t xml:space="preserve">15.1930656433105</t>
   </si>
   <si>
     <t xml:space="preserve">15.0956735610962</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">14.9008913040161</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6348028182983</t>
+    <t xml:space="preserve">13.634801864624</t>
   </si>
   <si>
     <t xml:space="preserve">12.0765390396118</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">13.9269771575928</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0243673324585</t>
+    <t xml:space="preserve">14.0243663787842</t>
   </si>
   <si>
     <t xml:space="preserve">14.2191514968872</t>
@@ -1121,31 +1121,31 @@
     <t xml:space="preserve">14.8034992218018</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4139337539673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6087160110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.706109046936</t>
+    <t xml:space="preserve">14.4139347076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6087169647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7061080932617</t>
   </si>
   <si>
     <t xml:space="preserve">14.5113248825073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3426284790039</t>
+    <t xml:space="preserve">13.3426275253296</t>
   </si>
   <si>
     <t xml:space="preserve">14.1217594146729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3165416717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8295841217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5374097824097</t>
+    <t xml:space="preserve">14.3165407180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8295850753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.537410736084</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452363967896</t>
@@ -1157,10 +1157,10 @@
     <t xml:space="preserve">12.3687133789062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7582788467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5634965896606</t>
+    <t xml:space="preserve">12.758279800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5634956359863</t>
   </si>
   <si>
     <t xml:space="preserve">12.1739301681519</t>
@@ -1190,37 +1190,37 @@
     <t xml:space="preserve">10.9078416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2974081039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3947982788086</t>
+    <t xml:space="preserve">11.2974071502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3947992324829</t>
   </si>
   <si>
     <t xml:space="preserve">11.589581489563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0052328109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7843647003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4921903610229</t>
+    <t xml:space="preserve">11.0052318572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7843656539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4921913146973</t>
   </si>
   <si>
     <t xml:space="preserve">10.810450553894</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4208841323853</t>
+    <t xml:space="preserve">10.4208850860596</t>
   </si>
   <si>
     <t xml:space="preserve">10.2261009216309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3234939575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1287097930908</t>
+    <t xml:space="preserve">10.3234930038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1287107467651</t>
   </si>
   <si>
     <t xml:space="preserve">10.0313196182251</t>
@@ -1229,16 +1229,16 @@
     <t xml:space="preserve">9.73914432525635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54436206817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8365364074707</t>
+    <t xml:space="preserve">9.54436111450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83653736114502</t>
   </si>
   <si>
     <t xml:space="preserve">9.34957885742188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49566650390625</t>
+    <t xml:space="preserve">9.49566555023193</t>
   </si>
   <si>
     <t xml:space="preserve">12.2713222503662</t>
@@ -1247,16 +1247,16 @@
     <t xml:space="preserve">12.9530620574951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6800231933594</t>
+    <t xml:space="preserve">15.6800222396851</t>
   </si>
   <si>
     <t xml:space="preserve">13.7321939468384</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1704559326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3652372360229</t>
+    <t xml:space="preserve">14.1704549789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3652381896973</t>
   </si>
   <si>
     <t xml:space="preserve">14.0730628967285</t>
@@ -1265,13 +1265,13 @@
     <t xml:space="preserve">15.1443691253662</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5364561080933</t>
+    <t xml:space="preserve">15.5364570617676</t>
   </si>
   <si>
     <t xml:space="preserve">15.585467338562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6344785690308</t>
+    <t xml:space="preserve">15.6344776153564</t>
   </si>
   <si>
     <t xml:space="preserve">15.193380355835</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">15.4384346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2423906326294</t>
+    <t xml:space="preserve">15.2423915863037</t>
   </si>
   <si>
     <t xml:space="preserve">15.3894233703613</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">13.9190969467163</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1641502380371</t>
+    <t xml:space="preserve">14.1641511917114</t>
   </si>
   <si>
     <t xml:space="preserve">13.7230529785156</t>
@@ -1313,31 +1313,31 @@
     <t xml:space="preserve">13.8210754394531</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3601951599121</t>
+    <t xml:space="preserve">14.3601942062378</t>
   </si>
   <si>
     <t xml:space="preserve">13.6250314712524</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8700847625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6740417480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7720651626587</t>
+    <t xml:space="preserve">13.8700857162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6740427017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7720642089844</t>
   </si>
   <si>
     <t xml:space="preserve">14.0171184539795</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1839323043823</t>
+    <t xml:space="preserve">13.1839332580566</t>
   </si>
   <si>
     <t xml:space="preserve">13.5270099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9483251571655</t>
+    <t xml:space="preserve">14.9483261108398</t>
   </si>
   <si>
     <t xml:space="preserve">14.4092054367065</t>
@@ -1346,43 +1346,43 @@
     <t xml:space="preserve">14.8503036499023</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7522821426392</t>
+    <t xml:space="preserve">14.7522830963135</t>
   </si>
   <si>
     <t xml:space="preserve">14.6052494049072</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7032709121704</t>
+    <t xml:space="preserve">14.7032718658447</t>
   </si>
   <si>
     <t xml:space="preserve">14.5562391281128</t>
   </si>
   <si>
-    <t xml:space="preserve">14.507227897644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0661306381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3309659957886</t>
+    <t xml:space="preserve">14.5072288513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0661296844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3309669494629</t>
   </si>
   <si>
     <t xml:space="preserve">13.4779987335205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2819557189941</t>
+    <t xml:space="preserve">13.2819547653198</t>
   </si>
   <si>
     <t xml:space="preserve">12.8898668289185</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7428350448608</t>
+    <t xml:space="preserve">12.7428340911865</t>
   </si>
   <si>
     <t xml:space="preserve">12.9878902435303</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1349220275879</t>
+    <t xml:space="preserve">13.1349229812622</t>
   </si>
   <si>
     <t xml:space="preserve">12.3507480621338</t>
@@ -1394,16 +1394,16 @@
     <t xml:space="preserve">11.3215188980103</t>
   </si>
   <si>
-    <t xml:space="preserve">12.301736831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0859117507935</t>
+    <t xml:space="preserve">12.3017377853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0859127044678</t>
   </si>
   <si>
     <t xml:space="preserve">13.4289875030518</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8305225372314</t>
+    <t xml:space="preserve">15.8305215835571</t>
   </si>
   <si>
     <t xml:space="preserve">15.7324991226196</t>
@@ -1412,19 +1412,19 @@
     <t xml:space="preserve">15.8795328140259</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9775552749634</t>
+    <t xml:space="preserve">15.9775533676147</t>
   </si>
   <si>
     <t xml:space="preserve">16.3696422576904</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6834897994995</t>
+    <t xml:space="preserve">15.6834888458252</t>
   </si>
   <si>
     <t xml:space="preserve">15.7815113067627</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2226104736328</t>
+    <t xml:space="preserve">16.2226085662842</t>
   </si>
   <si>
     <t xml:space="preserve">16.0265655517578</t>
@@ -1436,13 +1436,13 @@
     <t xml:space="preserve">15.9285440444946</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1735992431641</t>
+    <t xml:space="preserve">16.1735973358154</t>
   </si>
   <si>
     <t xml:space="preserve">16.2716197967529</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3206310272217</t>
+    <t xml:space="preserve">16.320629119873</t>
   </si>
   <si>
     <t xml:space="preserve">18.7221660614014</t>
@@ -1451,193 +1451,196 @@
     <t xml:space="preserve">19.0162296295166</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7023849487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.604362487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8004055023193</t>
+    <t xml:space="preserve">19.7023830413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6043605804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.800407409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0944709777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9173202514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.545015335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5252342224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7995166778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2311706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7806243896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1727104187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4865589141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6826019287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3687534332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6430377960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9955596923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2896251678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6034755706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8975391387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5054531097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.015344619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6232566833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8390808105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3291893005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.937105178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7212791442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1133651733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0351257324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1331481933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2113876342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4074287414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8192977905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2509498596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7608413696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9568843841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1529273986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7711753845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6439266204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5261211395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9964485168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5845794677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1924934387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8984279632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3885364532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4049549102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6512107849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3557014465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5527095794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7989635467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6019592285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9616947174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0601978302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0109443664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1586990356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2914772033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1929721832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1779956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9809913635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4884796142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5869827270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9959678649902</t>
   </si>
   <si>
     <t xml:space="preserve">20.0944690704346</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9173202514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.545015335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5252342224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7995166778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2311687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7806243896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1727104187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4865570068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6826038360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3687534332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6430377960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9955615997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2896251678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6034736633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8975391387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5054531097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.015344619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.623254776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8390808105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3291893005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9371032714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7212791442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1133651733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0351238250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1331462860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2113857269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4074306488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.819299697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2509517669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7608413696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9568843841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1529293060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7711753845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6439247131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5261211395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9964485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5845794677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1924934387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8984260559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3885345458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4049549102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6512107849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3557014465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5527095794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7989654541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.601957321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9616947174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0601978302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0109443664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1586990356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2914772033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1929721832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1779956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9809913635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4884796142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5869808197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9959678649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4542064666748</t>
+    <t xml:space="preserve">19.4542045593262</t>
   </si>
   <si>
     <t xml:space="preserve">19.5034561157227</t>
@@ -1649,7 +1652,7 @@
     <t xml:space="preserve">19.207950592041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0259208679199</t>
+    <t xml:space="preserve">18.0259227752686</t>
   </si>
   <si>
     <t xml:space="preserve">18.075174331665</t>
@@ -1673,19 +1676,19 @@
     <t xml:space="preserve">17.9274196624756</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9766712188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.434907913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1736755371094</t>
+    <t xml:space="preserve">17.9766693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4349098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.173677444458</t>
   </si>
   <si>
     <t xml:space="preserve">18.4199314117432</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7839889526367</t>
+    <t xml:space="preserve">20.7839870452881</t>
   </si>
   <si>
     <t xml:space="preserve">20.3899784088135</t>
@@ -1694,10 +1697,10 @@
     <t xml:space="preserve">19.7004623413086</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9124431610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1094455718994</t>
+    <t xml:space="preserve">18.9124450683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.109447479248</t>
   </si>
   <si>
     <t xml:space="preserve">18.8631916046143</t>
@@ -1706,7 +1709,7 @@
     <t xml:space="preserve">18.5184326171875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7154388427734</t>
+    <t xml:space="preserve">18.7154369354248</t>
   </si>
   <si>
     <t xml:space="preserve">18.2229270935059</t>
@@ -1715,7 +1718,7 @@
     <t xml:space="preserve">17.7796649932861</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5676860809326</t>
+    <t xml:space="preserve">18.567684173584</t>
   </si>
   <si>
     <t xml:space="preserve">17.7304153442383</t>
@@ -1727,16 +1730,16 @@
     <t xml:space="preserve">18.2721767425537</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6811637878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8781700134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1244258880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6319141387939</t>
+    <t xml:space="preserve">17.6811656951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8781681060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1244239807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6319122314453</t>
   </si>
   <si>
     <t xml:space="preserve">17.4841594696045</t>
@@ -1745,7 +1748,7 @@
     <t xml:space="preserve">17.3856582641602</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5334091186523</t>
+    <t xml:space="preserve">17.533411026001</t>
   </si>
   <si>
     <t xml:space="preserve">17.1886520385742</t>
@@ -1760,7 +1763,7 @@
     <t xml:space="preserve">16.4991359710693</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8931465148926</t>
+    <t xml:space="preserve">16.8931446075439</t>
   </si>
   <si>
     <t xml:space="preserve">16.4498863220215</t>
@@ -1772,7 +1775,7 @@
     <t xml:space="preserve">16.6468906402588</t>
   </si>
   <si>
-    <t xml:space="preserve">16.794641494751</t>
+    <t xml:space="preserve">16.7946434020996</t>
   </si>
   <si>
     <t xml:space="preserve">16.7453918457031</t>
@@ -1784,7 +1787,7 @@
     <t xml:space="preserve">14.6275930404663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9723501205444</t>
+    <t xml:space="preserve">14.9723510742188</t>
   </si>
   <si>
     <t xml:space="preserve">14.7260942459106</t>
@@ -1799,7 +1802,7 @@
     <t xml:space="preserve">15.1201047897339</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3663597106934</t>
+    <t xml:space="preserve">15.3663606643677</t>
   </si>
   <si>
     <t xml:space="preserve">15.464861869812</t>
@@ -1808,16 +1811,16 @@
     <t xml:space="preserve">14.7753458023071</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4798393249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2828340530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5783414840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0858306884766</t>
+    <t xml:space="preserve">14.4798383712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2828350067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5783424377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0858297348022</t>
   </si>
   <si>
     <t xml:space="preserve">14.2335834503174</t>
@@ -41440,7 +41443,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1499" t="s">
-        <v>482</v>
+        <v>541</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41492,7 +41495,7 @@
         <v>19.75</v>
       </c>
       <c r="G1501" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41596,7 +41599,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1505" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41622,7 +41625,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1506" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41674,7 +41677,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1508" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41700,7 +41703,7 @@
         <v>19.5</v>
       </c>
       <c r="G1509" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41726,7 +41729,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1510" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41752,7 +41755,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1511" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41778,7 +41781,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1512" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41804,7 +41807,7 @@
         <v>19.5</v>
       </c>
       <c r="G1513" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41830,7 +41833,7 @@
         <v>19.5</v>
       </c>
       <c r="G1514" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41856,7 +41859,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1515" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41882,7 +41885,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1516" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41908,7 +41911,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1517" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -41934,7 +41937,7 @@
         <v>18.75</v>
       </c>
       <c r="G1518" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -41960,7 +41963,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1519" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41986,7 +41989,7 @@
         <v>17.5</v>
       </c>
       <c r="G1520" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42012,7 +42015,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1521" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42038,7 +42041,7 @@
         <v>18.25</v>
       </c>
       <c r="G1522" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42064,7 +42067,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1523" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42090,7 +42093,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1524" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42116,7 +42119,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1525" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42142,7 +42145,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1526" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42168,7 +42171,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1527" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42194,7 +42197,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1528" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42220,7 +42223,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1529" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42350,7 +42353,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1534" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42376,7 +42379,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1535" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42428,7 +42431,7 @@
         <v>20</v>
       </c>
       <c r="G1537" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42506,7 +42509,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1540" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42532,7 +42535,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1541" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42558,7 +42561,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1542" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42610,7 +42613,7 @@
         <v>19.5</v>
       </c>
       <c r="G1544" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42636,7 +42639,7 @@
         <v>19.5</v>
       </c>
       <c r="G1545" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42714,7 +42717,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1548" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42740,7 +42743,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G1549" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42870,7 +42873,7 @@
         <v>19.5</v>
       </c>
       <c r="G1554" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42896,7 +42899,7 @@
         <v>19.5</v>
       </c>
       <c r="G1555" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42922,7 +42925,7 @@
         <v>19.5</v>
       </c>
       <c r="G1556" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42974,7 +42977,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1558" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43000,7 +43003,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1559" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43026,7 +43029,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1560" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43052,7 +43055,7 @@
         <v>19</v>
       </c>
       <c r="G1561" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43078,7 +43081,7 @@
         <v>19</v>
       </c>
       <c r="G1562" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43104,7 +43107,7 @@
         <v>19</v>
       </c>
       <c r="G1563" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43130,7 +43133,7 @@
         <v>19</v>
       </c>
       <c r="G1564" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43156,7 +43159,7 @@
         <v>19</v>
       </c>
       <c r="G1565" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43182,7 +43185,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1566" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43208,7 +43211,7 @@
         <v>19</v>
       </c>
       <c r="G1567" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43234,7 +43237,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1568" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43260,7 +43263,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1569" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43286,7 +43289,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1570" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43312,7 +43315,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1571" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -43338,7 +43341,7 @@
         <v>19</v>
       </c>
       <c r="G1572" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43364,7 +43367,7 @@
         <v>19</v>
       </c>
       <c r="G1573" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43390,7 +43393,7 @@
         <v>19</v>
       </c>
       <c r="G1574" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43416,7 +43419,7 @@
         <v>18.75</v>
       </c>
       <c r="G1575" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43442,7 +43445,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1576" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43468,7 +43471,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1577" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43494,7 +43497,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1578" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43520,7 +43523,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1579" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43546,7 +43549,7 @@
         <v>19</v>
       </c>
       <c r="G1580" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43572,7 +43575,7 @@
         <v>19</v>
       </c>
       <c r="G1581" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43598,7 +43601,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1582" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43624,7 +43627,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1583" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43650,7 +43653,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1584" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43676,7 +43679,7 @@
         <v>18.75</v>
       </c>
       <c r="G1585" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43702,7 +43705,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1586" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43728,7 +43731,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1587" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43754,7 +43757,7 @@
         <v>18.5</v>
       </c>
       <c r="G1588" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43780,7 +43783,7 @@
         <v>18.5</v>
       </c>
       <c r="G1589" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43806,7 +43809,7 @@
         <v>18.5</v>
       </c>
       <c r="G1590" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43832,7 +43835,7 @@
         <v>18.5</v>
       </c>
       <c r="G1591" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43858,7 +43861,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1592" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43884,7 +43887,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1593" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43910,7 +43913,7 @@
         <v>18</v>
       </c>
       <c r="G1594" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43936,7 +43939,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1595" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -43962,7 +43965,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1596" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43988,7 +43991,7 @@
         <v>18.5</v>
       </c>
       <c r="G1597" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44014,7 +44017,7 @@
         <v>18.5</v>
       </c>
       <c r="G1598" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44040,7 +44043,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1599" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44066,7 +44069,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1600" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44092,7 +44095,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1601" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44118,7 +44121,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1602" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44144,7 +44147,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1603" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44170,7 +44173,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1604" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44196,7 +44199,7 @@
         <v>18.25</v>
       </c>
       <c r="G1605" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44222,7 +44225,7 @@
         <v>18</v>
       </c>
       <c r="G1606" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -44248,7 +44251,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1607" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -44274,7 +44277,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1608" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -44300,7 +44303,7 @@
         <v>18</v>
       </c>
       <c r="G1609" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44326,7 +44329,7 @@
         <v>18.25</v>
       </c>
       <c r="G1610" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -44352,7 +44355,7 @@
         <v>18.25</v>
       </c>
       <c r="G1611" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44378,7 +44381,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1612" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44404,7 +44407,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1613" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44430,7 +44433,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1614" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44456,7 +44459,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1615" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44482,7 +44485,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1616" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44508,7 +44511,7 @@
         <v>18</v>
       </c>
       <c r="G1617" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44534,7 +44537,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1618" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44560,7 +44563,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1619" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44586,7 +44589,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1620" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44612,7 +44615,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1621" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44638,7 +44641,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1622" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44664,7 +44667,7 @@
         <v>18</v>
       </c>
       <c r="G1623" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44690,7 +44693,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1624" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44716,7 +44719,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1625" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44742,7 +44745,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1626" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44768,7 +44771,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1627" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44794,7 +44797,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1628" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44820,7 +44823,7 @@
         <v>18.25</v>
       </c>
       <c r="G1629" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44846,7 +44849,7 @@
         <v>18.25</v>
       </c>
       <c r="G1630" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44872,7 +44875,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1631" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44898,7 +44901,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1632" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44924,7 +44927,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1633" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44950,7 +44953,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1634" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44976,7 +44979,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1635" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45002,7 +45005,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1636" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45028,7 +45031,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1637" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45054,7 +45057,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1638" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45080,7 +45083,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1639" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45106,7 +45109,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1640" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45132,7 +45135,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1641" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -45158,7 +45161,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1642" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45184,7 +45187,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1643" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45210,7 +45213,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1644" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -45236,7 +45239,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1645" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -45262,7 +45265,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1646" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -45288,7 +45291,7 @@
         <v>18</v>
       </c>
       <c r="G1647" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -45314,7 +45317,7 @@
         <v>18.25</v>
       </c>
       <c r="G1648" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -45340,7 +45343,7 @@
         <v>18.25</v>
       </c>
       <c r="G1649" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -45366,7 +45369,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1650" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45392,7 +45395,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1651" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -45418,7 +45421,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1652" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45444,7 +45447,7 @@
         <v>18</v>
       </c>
       <c r="G1653" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45470,7 +45473,7 @@
         <v>18</v>
       </c>
       <c r="G1654" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45496,7 +45499,7 @@
         <v>18</v>
       </c>
       <c r="G1655" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45522,7 +45525,7 @@
         <v>18</v>
       </c>
       <c r="G1656" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45548,7 +45551,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1657" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45574,7 +45577,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1658" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45600,7 +45603,7 @@
         <v>17.75</v>
       </c>
       <c r="G1659" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45626,7 +45629,7 @@
         <v>18</v>
       </c>
       <c r="G1660" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45652,7 +45655,7 @@
         <v>18</v>
       </c>
       <c r="G1661" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45678,7 +45681,7 @@
         <v>18</v>
       </c>
       <c r="G1662" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45704,7 +45707,7 @@
         <v>18</v>
       </c>
       <c r="G1663" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45730,7 +45733,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1664" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45756,7 +45759,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1665" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45782,7 +45785,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1666" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45808,7 +45811,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1667" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45834,7 +45837,7 @@
         <v>17.5</v>
       </c>
       <c r="G1668" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45860,7 +45863,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1669" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45886,7 +45889,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1670" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45912,7 +45915,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1671" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45938,7 +45941,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1672" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45964,7 +45967,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1673" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45990,7 +45993,7 @@
         <v>16.75</v>
       </c>
       <c r="G1674" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -46016,7 +46019,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1675" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -46042,7 +46045,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1676" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -46068,7 +46071,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1677" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -46094,7 +46097,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1678" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -46120,7 +46123,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1679" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -46146,7 +46149,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1680" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -46172,7 +46175,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1681" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -46198,7 +46201,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1682" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -46224,7 +46227,7 @@
         <v>17</v>
       </c>
       <c r="G1683" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -46250,7 +46253,7 @@
         <v>17</v>
       </c>
       <c r="G1684" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -46276,7 +46279,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1685" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -46302,7 +46305,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1686" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -46328,7 +46331,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1687" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -46354,7 +46357,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46380,7 +46383,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1689" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -46406,7 +46409,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1690" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -46432,7 +46435,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1691" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46458,7 +46461,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1692" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46484,7 +46487,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1693" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -46510,7 +46513,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46536,7 +46539,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1695" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46562,7 +46565,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1696" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46588,7 +46591,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1697" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46614,7 +46617,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1698" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46640,7 +46643,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1699" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46666,7 +46669,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1700" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46692,7 +46695,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1701" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46718,7 +46721,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1702" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46744,7 +46747,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1703" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46770,7 +46773,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1704" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46796,7 +46799,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1705" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46822,7 +46825,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1706" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46848,7 +46851,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1707" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46874,7 +46877,7 @@
         <v>15</v>
       </c>
       <c r="G1708" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46900,7 +46903,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1709" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46926,7 +46929,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1710" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46952,7 +46955,7 @@
         <v>14.5</v>
       </c>
       <c r="G1711" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46978,7 +46981,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1712" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -47004,7 +47007,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1713" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47030,7 +47033,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1714" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -47056,7 +47059,7 @@
         <v>15</v>
       </c>
       <c r="G1715" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -47082,7 +47085,7 @@
         <v>15</v>
       </c>
       <c r="G1716" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47108,7 +47111,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1717" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -47134,7 +47137,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1718" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -47160,7 +47163,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -47186,7 +47189,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1720" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -47212,7 +47215,7 @@
         <v>14.25</v>
       </c>
       <c r="G1721" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -47238,7 +47241,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1722" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -47264,7 +47267,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1723" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -47290,7 +47293,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1724" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -47316,7 +47319,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1725" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -47342,7 +47345,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1726" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47368,7 +47371,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1727" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47394,7 +47397,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1728" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -47420,7 +47423,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1729" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47446,7 +47449,7 @@
         <v>14.75</v>
       </c>
       <c r="G1730" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47472,7 +47475,7 @@
         <v>14.75</v>
       </c>
       <c r="G1731" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47498,7 +47501,7 @@
         <v>14.75</v>
       </c>
       <c r="G1732" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47524,7 +47527,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1733" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47550,7 +47553,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1734" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47576,7 +47579,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1735" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47602,7 +47605,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1736" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47628,7 +47631,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1737" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47654,7 +47657,7 @@
         <v>13.25</v>
       </c>
       <c r="G1738" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47680,7 +47683,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1739" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47706,7 +47709,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1740" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47732,7 +47735,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1741" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47758,7 +47761,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1742" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47784,7 +47787,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1743" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47810,7 +47813,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1744" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47836,7 +47839,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1745" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47862,7 +47865,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1746" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47888,7 +47891,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1747" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47914,7 +47917,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1748" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47940,7 +47943,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1749" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47966,7 +47969,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1750" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47992,7 +47995,7 @@
         <v>12.75</v>
       </c>
       <c r="G1751" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -48018,7 +48021,7 @@
         <v>12.5</v>
       </c>
       <c r="G1752" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -48044,7 +48047,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1753" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -48070,7 +48073,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1754" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -48096,7 +48099,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1755" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -48122,7 +48125,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1756" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -48148,7 +48151,7 @@
         <v>12.25</v>
       </c>
       <c r="G1757" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -48174,7 +48177,7 @@
         <v>12.25</v>
       </c>
       <c r="G1758" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -48200,7 +48203,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1759" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -48226,7 +48229,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1760" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -48252,7 +48255,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1761" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -48278,7 +48281,7 @@
         <v>12.75</v>
       </c>
       <c r="G1762" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -48304,7 +48307,7 @@
         <v>12.75</v>
       </c>
       <c r="G1763" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -48330,7 +48333,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1764" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -48356,7 +48359,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1765" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48382,7 +48385,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1766" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48408,7 +48411,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1767" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48434,7 +48437,7 @@
         <v>12.5</v>
       </c>
       <c r="G1768" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48460,7 +48463,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1769" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48486,7 +48489,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1770" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48512,7 +48515,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1771" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48538,7 +48541,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1772" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48564,7 +48567,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1773" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48590,7 +48593,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1774" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48616,7 +48619,7 @@
         <v>12.75</v>
       </c>
       <c r="G1775" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48642,7 +48645,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1776" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48668,7 +48671,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1777" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48694,7 +48697,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1778" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48720,7 +48723,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1779" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48746,7 +48749,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1780" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48772,7 +48775,7 @@
         <v>13</v>
       </c>
       <c r="G1781" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48798,7 +48801,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1782" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48824,7 +48827,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1783" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48850,7 +48853,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1784" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48876,7 +48879,7 @@
         <v>12.75</v>
       </c>
       <c r="G1785" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48902,7 +48905,7 @@
         <v>12.75</v>
       </c>
       <c r="G1786" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48928,7 +48931,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48954,7 +48957,7 @@
         <v>12.5</v>
       </c>
       <c r="G1788" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48980,7 +48983,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1789" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -49006,7 +49009,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1790" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -49032,7 +49035,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1791" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -49058,7 +49061,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1792" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -49084,7 +49087,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1793" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -49110,7 +49113,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1794" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -49136,7 +49139,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1795" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -49162,7 +49165,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1796" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -49188,7 +49191,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1797" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -49214,7 +49217,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1798" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -49240,7 +49243,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1799" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -49266,7 +49269,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1800" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -49292,7 +49295,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1801" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -49318,7 +49321,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1802" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -49344,7 +49347,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1803" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49370,7 +49373,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1804" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49396,7 +49399,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1805" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49422,7 +49425,7 @@
         <v>12.75</v>
       </c>
       <c r="G1806" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49448,7 +49451,7 @@
         <v>12.75</v>
       </c>
       <c r="G1807" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49474,7 +49477,7 @@
         <v>12.75</v>
       </c>
       <c r="G1808" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49500,7 +49503,7 @@
         <v>12.75</v>
       </c>
       <c r="G1809" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49526,7 +49529,7 @@
         <v>12.75</v>
       </c>
       <c r="G1810" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49552,7 +49555,7 @@
         <v>12.75</v>
       </c>
       <c r="G1811" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49578,7 +49581,7 @@
         <v>12.75</v>
       </c>
       <c r="G1812" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49604,7 +49607,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1813" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49630,7 +49633,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1814" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49656,7 +49659,7 @@
         <v>12.75</v>
       </c>
       <c r="G1815" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49682,7 +49685,7 @@
         <v>12.75</v>
       </c>
       <c r="G1816" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49708,7 +49711,7 @@
         <v>12.75</v>
       </c>
       <c r="G1817" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49734,7 +49737,7 @@
         <v>12.75</v>
       </c>
       <c r="G1818" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49760,7 +49763,7 @@
         <v>12.75</v>
       </c>
       <c r="G1819" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49786,7 +49789,7 @@
         <v>12.75</v>
       </c>
       <c r="G1820" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49812,7 +49815,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1821" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49838,7 +49841,7 @@
         <v>12.5</v>
       </c>
       <c r="G1822" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49864,7 +49867,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1823" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49890,7 +49893,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1824" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49916,7 +49919,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1825" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49942,7 +49945,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1826" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49968,7 +49971,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1827" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49994,7 +49997,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1828" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -50020,7 +50023,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1829" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -50046,7 +50049,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1830" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -50072,7 +50075,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1831" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -50098,7 +50101,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1832" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -50124,7 +50127,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1833" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -50150,7 +50153,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1834" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -50176,7 +50179,7 @@
         <v>12.5</v>
       </c>
       <c r="G1835" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -50202,7 +50205,7 @@
         <v>12.5</v>
       </c>
       <c r="G1836" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -50228,7 +50231,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1837" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -50254,7 +50257,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1838" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -50280,7 +50283,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1839" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -50306,7 +50309,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -50332,7 +50335,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1841" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50358,7 +50361,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1842" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50384,7 +50387,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1843" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50410,7 +50413,7 @@
         <v>12.75</v>
       </c>
       <c r="G1844" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50436,7 +50439,7 @@
         <v>12.75</v>
       </c>
       <c r="G1845" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50462,7 +50465,7 @@
         <v>12.75</v>
       </c>
       <c r="G1846" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50488,7 +50491,7 @@
         <v>12.75</v>
       </c>
       <c r="G1847" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50514,7 +50517,7 @@
         <v>12.75</v>
       </c>
       <c r="G1848" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50540,7 +50543,7 @@
         <v>12.75</v>
       </c>
       <c r="G1849" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50566,7 +50569,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1850" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50592,7 +50595,7 @@
         <v>13.25</v>
       </c>
       <c r="G1851" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50618,7 +50621,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1852" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50644,7 +50647,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1853" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50670,7 +50673,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1854" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50696,7 +50699,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1855" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50722,7 +50725,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1856" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50748,7 +50751,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1857" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50774,7 +50777,7 @@
         <v>13</v>
       </c>
       <c r="G1858" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50800,7 +50803,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1859" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50826,7 +50829,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1860" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50852,7 +50855,7 @@
         <v>13.25</v>
       </c>
       <c r="G1861" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50878,7 +50881,7 @@
         <v>13.25</v>
       </c>
       <c r="G1862" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50904,7 +50907,7 @@
         <v>13.25</v>
       </c>
       <c r="G1863" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50930,7 +50933,7 @@
         <v>13.25</v>
       </c>
       <c r="G1864" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50956,7 +50959,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1865" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50982,7 +50985,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1866" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -51008,7 +51011,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1867" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -51034,7 +51037,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1868" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -51060,7 +51063,7 @@
         <v>12.5</v>
       </c>
       <c r="G1869" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -51086,7 +51089,7 @@
         <v>12.5</v>
       </c>
       <c r="G1870" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -51112,7 +51115,7 @@
         <v>12.5</v>
       </c>
       <c r="G1871" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -51138,7 +51141,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1872" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -51164,7 +51167,7 @@
         <v>12.5</v>
       </c>
       <c r="G1873" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -51190,7 +51193,7 @@
         <v>12.5</v>
       </c>
       <c r="G1874" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -51216,7 +51219,7 @@
         <v>12.5</v>
       </c>
       <c r="G1875" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -51242,7 +51245,7 @@
         <v>12.5</v>
       </c>
       <c r="G1876" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -51268,7 +51271,7 @@
         <v>12.25</v>
       </c>
       <c r="G1877" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -51294,7 +51297,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1878" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -51320,7 +51323,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1879" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -51346,7 +51349,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1880" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51372,7 +51375,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1881" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51398,7 +51401,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1882" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51424,7 +51427,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1883" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51450,7 +51453,7 @@
         <v>12.5</v>
       </c>
       <c r="G1884" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51476,7 +51479,7 @@
         <v>12.5</v>
       </c>
       <c r="G1885" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51502,7 +51505,7 @@
         <v>12.5</v>
       </c>
       <c r="G1886" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51528,7 +51531,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1887" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51554,7 +51557,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1888" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51580,7 +51583,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1889" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51606,7 +51609,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1890" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51632,7 +51635,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1891" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51658,7 +51661,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1892" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51684,7 +51687,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1893" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51710,7 +51713,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1894" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51736,7 +51739,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1895" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51762,7 +51765,7 @@
         <v>14.75</v>
       </c>
       <c r="G1896" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51788,7 +51791,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1897" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51814,7 +51817,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1898" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51840,7 +51843,7 @@
         <v>14.25</v>
       </c>
       <c r="G1899" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51866,7 +51869,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1900" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51892,7 +51895,7 @@
         <v>14</v>
       </c>
       <c r="G1901" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51918,7 +51921,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1902" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51944,7 +51947,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1903" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51970,7 +51973,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1904" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51996,7 +51999,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1905" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52022,7 +52025,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1906" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52048,7 +52051,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52074,7 +52077,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1908" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52100,7 +52103,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1909" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52126,7 +52129,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1910" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -52152,7 +52155,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1911" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -52178,7 +52181,7 @@
         <v>13.25</v>
       </c>
       <c r="G1912" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -52204,7 +52207,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1913" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -52230,7 +52233,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1914" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -52256,7 +52259,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1915" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -52282,7 +52285,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1916" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -52308,7 +52311,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1917" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -52334,7 +52337,7 @@
         <v>12.75</v>
       </c>
       <c r="G1918" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52360,7 +52363,7 @@
         <v>13</v>
       </c>
       <c r="G1919" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52386,7 +52389,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1920" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52412,7 +52415,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1921" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52438,7 +52441,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1922" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52464,7 +52467,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1923" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52490,7 +52493,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1924" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52516,7 +52519,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1925" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52542,7 +52545,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1926" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52568,7 +52571,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1927" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52594,7 +52597,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1928" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52620,7 +52623,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1929" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52646,7 +52649,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1930" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52672,7 +52675,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1931" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52698,7 +52701,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1932" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52724,7 +52727,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1933" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52750,7 +52753,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1934" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52776,7 +52779,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1935" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52802,7 +52805,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1936" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52828,7 +52831,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1937" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52854,7 +52857,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1938" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52880,7 +52883,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1939" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52906,7 +52909,7 @@
         <v>12.5</v>
       </c>
       <c r="G1940" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52932,7 +52935,7 @@
         <v>12.75</v>
       </c>
       <c r="G1941" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52958,7 +52961,7 @@
         <v>12.75</v>
       </c>
       <c r="G1942" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52984,7 +52987,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1943" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53010,7 +53013,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1944" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53036,7 +53039,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1945" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53062,7 +53065,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1946" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53088,7 +53091,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1947" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53114,7 +53117,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1948" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -53140,7 +53143,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1949" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -53166,7 +53169,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1950" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -53192,7 +53195,7 @@
         <v>12.25</v>
       </c>
       <c r="G1951" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -53218,7 +53221,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1952" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -53244,7 +53247,7 @@
         <v>12.5</v>
       </c>
       <c r="G1953" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -53270,7 +53273,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1954" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -53296,7 +53299,7 @@
         <v>12.25</v>
       </c>
       <c r="G1955" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -53322,7 +53325,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1956" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -53348,7 +53351,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1957" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53374,7 +53377,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1958" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53400,7 +53403,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1959" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53426,7 +53429,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1960" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53452,7 +53455,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1961" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53478,7 +53481,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1962" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53504,7 +53507,7 @@
         <v>10.5</v>
       </c>
       <c r="G1963" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53530,7 +53533,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1964" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53556,7 +53559,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1965" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53582,7 +53585,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1966" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53608,7 +53611,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1967" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53634,7 +53637,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1968" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53660,7 +53663,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1969" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53686,7 +53689,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1970" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53712,7 +53715,7 @@
         <v>12</v>
       </c>
       <c r="G1971" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53738,7 +53741,7 @@
         <v>12</v>
       </c>
       <c r="G1972" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53764,7 +53767,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1973" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53790,7 +53793,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1974" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53816,7 +53819,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1975" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53842,7 +53845,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1976" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53868,7 +53871,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1977" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53894,7 +53897,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1978" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53920,7 +53923,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1979" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53946,7 +53949,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1980" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53972,7 +53975,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1981" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53998,7 +54001,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1982" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54024,7 +54027,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54050,7 +54053,7 @@
         <v>13</v>
       </c>
       <c r="G1984" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54076,7 +54079,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1985" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54102,7 +54105,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1986" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -54128,7 +54131,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1987" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -54154,7 +54157,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1988" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -54180,7 +54183,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1989" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -54206,7 +54209,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1990" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -54232,7 +54235,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1991" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -54258,7 +54261,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1992" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -54284,7 +54287,7 @@
         <v>13.5</v>
       </c>
       <c r="G1993" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -54310,7 +54313,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1994" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -54336,7 +54339,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1995" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54362,7 +54365,7 @@
         <v>14.5</v>
       </c>
       <c r="G1996" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54388,7 +54391,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1997" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54414,7 +54417,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1998" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54440,7 +54443,7 @@
         <v>15</v>
       </c>
       <c r="G1999" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54466,7 +54469,7 @@
         <v>15.5</v>
       </c>
       <c r="G2000" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54492,7 +54495,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2001" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54518,7 +54521,7 @@
         <v>15.5</v>
       </c>
       <c r="G2002" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54544,7 +54547,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2003" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54570,7 +54573,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2004" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54596,7 +54599,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2005" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54622,7 +54625,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2006" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54648,7 +54651,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2007" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54674,7 +54677,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2008" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54700,7 +54703,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2009" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54726,7 +54729,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2010" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54752,7 +54755,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2011" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54778,7 +54781,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2012" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54804,7 +54807,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2013" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54830,7 +54833,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2014" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54856,7 +54859,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2015" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54882,7 +54885,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2016" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54908,7 +54911,7 @@
         <v>16</v>
       </c>
       <c r="G2017" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54934,7 +54937,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2018" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54960,7 +54963,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2019" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54986,7 +54989,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2020" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55012,7 +55015,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2021" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55038,7 +55041,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2022" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55064,7 +55067,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2023" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55090,7 +55093,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2024" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -55116,7 +55119,7 @@
         <v>17.5</v>
       </c>
       <c r="G2025" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -55142,7 +55145,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2026" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -55168,7 +55171,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2027" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -55194,7 +55197,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2028" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -55220,7 +55223,7 @@
         <v>17.5</v>
       </c>
       <c r="G2029" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -55246,7 +55249,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2030" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -55272,7 +55275,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2031" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -55298,7 +55301,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2032" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -55324,7 +55327,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2033" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -55350,7 +55353,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2034" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -55376,7 +55379,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2035" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -55402,7 +55405,7 @@
         <v>17.5</v>
       </c>
       <c r="G2036" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -55428,7 +55431,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2037" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55454,7 +55457,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2038" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55480,7 +55483,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2039" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55506,7 +55509,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2040" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55532,7 +55535,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2041" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55558,7 +55561,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2042" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55584,7 +55587,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2043" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55610,7 +55613,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2044" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55636,7 +55639,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2045" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55662,7 +55665,7 @@
         <v>13</v>
       </c>
       <c r="G2046" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55688,7 +55691,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2047" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55714,7 +55717,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2048" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55740,7 +55743,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2049" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55766,7 +55769,7 @@
         <v>12</v>
       </c>
       <c r="G2050" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55792,7 +55795,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2051" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55818,7 +55821,7 @@
         <v>12</v>
       </c>
       <c r="G2052" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55844,7 +55847,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2053" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55870,7 +55873,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2054" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55896,7 +55899,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2055" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55922,7 +55925,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2056" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55948,7 +55951,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2057" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55974,7 +55977,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2058" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -56000,7 +56003,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2059" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -56026,7 +56029,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2060" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -56052,7 +56055,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2061" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -56078,7 +56081,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2062" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -56104,7 +56107,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2063" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -56130,7 +56133,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2064" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -56156,7 +56159,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2065" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -56182,7 +56185,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2066" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -56208,7 +56211,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2067" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -56234,7 +56237,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2068" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -56260,7 +56263,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2069" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -56286,7 +56289,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2070" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -56312,7 +56315,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2071" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -56338,7 +56341,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2072" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -56364,7 +56367,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2073" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -56390,7 +56393,7 @@
         <v>14</v>
       </c>
       <c r="G2074" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -56416,7 +56419,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2075" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56442,7 +56445,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2076" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56468,7 +56471,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2077" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56494,7 +56497,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2078" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56520,7 +56523,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2079" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -56546,7 +56549,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2080" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -56572,7 +56575,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2081" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56598,7 +56601,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2082" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56624,7 +56627,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2083" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56650,7 +56653,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2084" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56676,7 +56679,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2085" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56702,7 +56705,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2086" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56728,7 +56731,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2087" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56754,7 +56757,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2088" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56780,7 +56783,7 @@
         <v>15.5</v>
       </c>
       <c r="G2089" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56806,7 +56809,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2090" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56832,7 +56835,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2091" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56858,7 +56861,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2092" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56884,7 +56887,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2093" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56910,7 +56913,7 @@
         <v>14.5</v>
       </c>
       <c r="G2094" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56936,7 +56939,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2095" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56962,7 +56965,7 @@
         <v>15</v>
       </c>
       <c r="G2096" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56988,7 +56991,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2097" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -57014,7 +57017,7 @@
         <v>15</v>
       </c>
       <c r="G2098" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -57040,7 +57043,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2099" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -57048,7 +57051,7 @@
     </row>
     <row r="2100">
       <c r="A2100" s="1" t="n">
-        <v>45951.6495023148</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2100" t="n">
         <v>1750</v>
@@ -57066,9 +57069,35 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2100" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2100" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" s="1" t="n">
+        <v>45952.6493865741</v>
+      </c>
+      <c r="B2101" t="n">
+        <v>2875</v>
+      </c>
+      <c r="C2101" t="n">
+        <v>15.1000003814697</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E2101" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="F2101" t="n">
+        <v>15</v>
+      </c>
+      <c r="G2101" t="s">
+        <v>670</v>
+      </c>
+      <c r="H2101" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CULT.MI.xlsx
+++ b/data/CULT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="707">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68585252761841</t>
+    <t xml:space="preserve">4.68585157394409</t>
   </si>
   <si>
     <t xml:space="preserve">CULT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57666730880737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59486532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60851335525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58576631546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48931932449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56301879882812</t>
+    <t xml:space="preserve">4.57666778564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59486436843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60851287841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58576679229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48931980133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5630202293396</t>
   </si>
   <si>
     <t xml:space="preserve">4.51297616958618</t>
@@ -68,46 +68,46 @@
     <t xml:space="preserve">4.46020412445068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29824590682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21271848678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18178176879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23091554641724</t>
+    <t xml:space="preserve">4.29824638366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21271800994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18178224563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23091506958008</t>
   </si>
   <si>
     <t xml:space="preserve">4.36375713348389</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38195514678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35101842880249</t>
+    <t xml:space="preserve">4.38195419311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35101890563965</t>
   </si>
   <si>
     <t xml:space="preserve">4.28914737701416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24183464050293</t>
+    <t xml:space="preserve">4.24183368682861</t>
   </si>
   <si>
     <t xml:space="preserve">4.22909545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10535287857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09443378448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10899257659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9961678981781</t>
+    <t xml:space="preserve">4.1053524017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09443426132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10899114608765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99616813659668</t>
   </si>
   <si>
     <t xml:space="preserve">4.04712104797363</t>
@@ -116,10 +116,10 @@
     <t xml:space="preserve">4.0398416519165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96341252326965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07441711425781</t>
+    <t xml:space="preserve">3.96341180801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07441759109497</t>
   </si>
   <si>
     <t xml:space="preserve">4.3200831413269</t>
@@ -128,25 +128,25 @@
     <t xml:space="preserve">4.24911308288574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97979044914246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06895732879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05439901351929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98524880409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0507607460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07259702682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03802251815796</t>
+    <t xml:space="preserve">3.97978973388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06895780563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05439949035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9852499961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05076122283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07259798049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0380220413208</t>
   </si>
   <si>
     <t xml:space="preserve">4.04530143737793</t>
@@ -164,82 +164,82 @@
     <t xml:space="preserve">4.05985879898071</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07623672485352</t>
+    <t xml:space="preserve">4.07623720169067</t>
   </si>
   <si>
     <t xml:space="preserve">3.9124596118927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99070811271667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01072597503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92155790328979</t>
+    <t xml:space="preserve">3.99070906639099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01072549819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92155814170837</t>
   </si>
   <si>
     <t xml:space="preserve">4.00162696838379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05803871154785</t>
+    <t xml:space="preserve">4.05803918838501</t>
   </si>
   <si>
     <t xml:space="preserve">4.21635675430298</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22181606292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18542146682739</t>
+    <t xml:space="preserve">4.2218165397644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18542194366455</t>
   </si>
   <si>
     <t xml:space="preserve">4.16176509857178</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35465812683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28186750411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26731061935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39287328720093</t>
+    <t xml:space="preserve">4.3546576499939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28186845779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26731014251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39287281036377</t>
   </si>
   <si>
     <t xml:space="preserve">4.36739683151245</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17814350128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27458953857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3182635307312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35647821426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26549053192139</t>
+    <t xml:space="preserve">4.17814207077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27458906173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31826257705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35647773742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26549100875854</t>
   </si>
   <si>
     <t xml:space="preserve">4.26367044448853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27640914916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14902639389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35829734802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35283803939819</t>
+    <t xml:space="preserve">4.27640867233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14902687072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35829782485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35283851623535</t>
   </si>
   <si>
     <t xml:space="preserve">4.29460620880127</t>
@@ -248,187 +248,187 @@
     <t xml:space="preserve">4.2036190032959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24001502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34009981155396</t>
+    <t xml:space="preserve">4.24001407623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34010076522827</t>
   </si>
   <si>
     <t xml:space="preserve">4.42926788330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34919881820679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33646059036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33100175857544</t>
+    <t xml:space="preserve">4.3491997718811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33646154403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33100128173828</t>
   </si>
   <si>
     <t xml:space="preserve">4.32190275192261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4674825668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45838451385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28550720214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83057117462158</t>
+    <t xml:space="preserve">4.46748208999634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45838403701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28550815582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83057069778442</t>
   </si>
   <si>
     <t xml:space="preserve">3.90336036682129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88516330718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87606453895569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00344657897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93065714836121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99434781074524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08533573150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96705222129822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86696577072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84876823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85786628723145</t>
+    <t xml:space="preserve">3.88516306877136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87606477737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00344705581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93065667152405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99434757232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08533525466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96705174446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86696553230286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84876799583435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8578667640686</t>
   </si>
   <si>
     <t xml:space="preserve">3.81237316131592</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80327439308167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77597832679749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97615027427673</t>
+    <t xml:space="preserve">3.80327486991882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77597784996033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97615051269531</t>
   </si>
   <si>
     <t xml:space="preserve">3.94885492324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13992881774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16722393035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33528280258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21485996246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31675672531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42791748046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1963324546814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16854095458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2982292175293</t>
+    <t xml:space="preserve">4.13992786407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16722440719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33528327941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21485900878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31675624847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42791795730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19633197784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.168541431427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29822969436646</t>
   </si>
   <si>
     <t xml:space="preserve">4.30749273300171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27970266342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39086389541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40012693405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35381078720093</t>
+    <t xml:space="preserve">4.27970218658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3908634185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40012741088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35380983352661</t>
   </si>
   <si>
     <t xml:space="preserve">4.08517122268677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93695640563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00180006027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97400951385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03885412216187</t>
+    <t xml:space="preserve">3.93695592880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00179958343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97400975227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03885364532471</t>
   </si>
   <si>
     <t xml:space="preserve">3.94621968269348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95548319816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23338556289673</t>
+    <t xml:space="preserve">3.95548272132874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23338603973389</t>
   </si>
   <si>
     <t xml:space="preserve">4.22412204742432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24264860153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11296081542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26117563247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91842937469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89990258216858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89063858985901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0759072303772</t>
+    <t xml:space="preserve">4.24264907836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11296129226685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26117610931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91842865943909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89990234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89063835144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07590770721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.06664371490479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79800415039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73316073417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86284875869751</t>
+    <t xml:space="preserve">3.79800486564636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73316097259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86284852027893</t>
   </si>
   <si>
     <t xml:space="preserve">3.71463394165039</t>
@@ -437,55 +437,55 @@
     <t xml:space="preserve">3.70537042617798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77021479606628</t>
+    <t xml:space="preserve">3.77021431922913</t>
   </si>
   <si>
     <t xml:space="preserve">3.3904139995575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44599461555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58494544029236</t>
+    <t xml:space="preserve">3.44599437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58494591712952</t>
   </si>
   <si>
     <t xml:space="preserve">3.68684363365173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60347270965576</t>
+    <t xml:space="preserve">3.60347294807434</t>
   </si>
   <si>
     <t xml:space="preserve">3.52010178565979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37188720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46452116966248</t>
+    <t xml:space="preserve">3.37188696861267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46452164649963</t>
   </si>
   <si>
     <t xml:space="preserve">3.53862881660461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52936553955078</t>
+    <t xml:space="preserve">3.52936506271362</t>
   </si>
   <si>
     <t xml:space="preserve">3.45525789260864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34409666061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07545757293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14956498146057</t>
+    <t xml:space="preserve">3.34409642219543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07545733451843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14956521987915</t>
   </si>
   <si>
     <t xml:space="preserve">3.29777956008911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31630635261536</t>
+    <t xml:space="preserve">3.31630659103394</t>
   </si>
   <si>
     <t xml:space="preserve">3.23293566703796</t>
@@ -500,22 +500,22 @@
     <t xml:space="preserve">3.20514559745789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25146245956421</t>
+    <t xml:space="preserve">3.25146269798279</t>
   </si>
   <si>
     <t xml:space="preserve">3.10324764251709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15882849693298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91797924041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74197435379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77902793884277</t>
+    <t xml:space="preserve">3.1588282585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9179790019989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7419741153717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77902770042419</t>
   </si>
   <si>
     <t xml:space="preserve">2.87166213989258</t>
@@ -530,34 +530,34 @@
     <t xml:space="preserve">2.83460831642151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8438720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72344732284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76050114631653</t>
+    <t xml:space="preserve">2.84387183189392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72344756126404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76050090789795</t>
   </si>
   <si>
     <t xml:space="preserve">2.76976442337036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63081288337708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67713046073914</t>
+    <t xml:space="preserve">2.63081312179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67713022232056</t>
   </si>
   <si>
     <t xml:space="preserve">2.38070034980774</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36217355728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29732942581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31585645675659</t>
+    <t xml:space="preserve">2.36217379570007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29732966423035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31585669517517</t>
   </si>
   <si>
     <t xml:space="preserve">2.35291051864624</t>
@@ -566,85 +566,85 @@
     <t xml:space="preserve">2.26953935623169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23248553276062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28806638717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08427047729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1305878162384</t>
+    <t xml:space="preserve">2.2324857711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28806662559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0842707157135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13058805465698</t>
   </si>
   <si>
     <t xml:space="preserve">2.22322225570679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24174904823303</t>
+    <t xml:space="preserve">2.24174928665161</t>
   </si>
   <si>
     <t xml:space="preserve">2.11206102371216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17690539360046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0379536151886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9916365146637</t>
+    <t xml:space="preserve">2.17690491676331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03795385360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99163675308228</t>
   </si>
   <si>
     <t xml:space="preserve">1.88047552108765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9453192949295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92679262161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16764140129089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13985133171082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21395874023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4084906578064</t>
+    <t xml:space="preserve">1.94531917572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92679250240326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16764163970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13985109329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21395897865295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40849089622498</t>
   </si>
   <si>
     <t xml:space="preserve">2.48259806632996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42701768875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38996386528015</t>
+    <t xml:space="preserve">2.4270179271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38996410369873</t>
   </si>
   <si>
     <t xml:space="preserve">2.46583580970764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50406575202942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65698552131653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71433091163635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54229593276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58052587509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52318120002747</t>
+    <t xml:space="preserve">2.50406551361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65698575973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71433067321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5422956943512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58052611351013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52318096160889</t>
   </si>
   <si>
     <t xml:space="preserve">2.42760586738586</t>
@@ -656,43 +656,43 @@
     <t xml:space="preserve">2.48495078086853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61875581741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56141066551208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6378710269928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73344588279724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69521570205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75256085395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80990600585938</t>
+    <t xml:space="preserve">2.61875605583191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56141090393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63787055015564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73344564437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69521594047546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75256109237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8099057674408</t>
   </si>
   <si>
     <t xml:space="preserve">2.82902097702026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84813570976257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05840110778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86725068092346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77167582511902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.676100730896</t>
+    <t xml:space="preserve">2.84813594818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05840086936951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86725091934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7716760635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67610096931458</t>
   </si>
   <si>
     <t xml:space="preserve">2.59964084625244</t>
@@ -707,10 +707,10 @@
     <t xml:space="preserve">3.09663105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34512591362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45981597900391</t>
+    <t xml:space="preserve">3.34512615203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45981621742249</t>
   </si>
   <si>
     <t xml:space="preserve">3.74654126167297</t>
@@ -725,19 +725,19 @@
     <t xml:space="preserve">4.1097264289856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97592091560364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88034629821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82300114631653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44070100784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40247106552124</t>
+    <t xml:space="preserve">3.97592115402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88034582138062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82300138473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4407012462616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40247082710266</t>
   </si>
   <si>
     <t xml:space="preserve">3.36424088478088</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">3.57450604438782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55539107322693</t>
+    <t xml:space="preserve">3.55539131164551</t>
   </si>
   <si>
     <t xml:space="preserve">3.51716113090515</t>
@@ -764,7 +764,7 @@
     <t xml:space="preserve">3.63185119628906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53627610206604</t>
+    <t xml:space="preserve">3.53627634048462</t>
   </si>
   <si>
     <t xml:space="preserve">3.61273622512817</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">3.65096616744995</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24955105781555</t>
+    <t xml:space="preserve">3.24955129623413</t>
   </si>
   <si>
     <t xml:space="preserve">3.32601094245911</t>
@@ -785,16 +785,16 @@
     <t xml:space="preserve">3.30689597129822</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38335633277893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59362149238586</t>
+    <t xml:space="preserve">3.38335609436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59362101554871</t>
   </si>
   <si>
     <t xml:space="preserve">3.47893118858337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49804615974426</t>
+    <t xml:space="preserve">3.49804592132568</t>
   </si>
   <si>
     <t xml:space="preserve">3.28778123855591</t>
@@ -803,25 +803,25 @@
     <t xml:space="preserve">3.67008113861084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80388617515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93769145011902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03326606750488</t>
+    <t xml:space="preserve">3.80388641357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93769073486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03326559066772</t>
   </si>
   <si>
     <t xml:space="preserve">4.18618679046631</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30087661743164</t>
+    <t xml:space="preserve">4.30087614059448</t>
   </si>
   <si>
     <t xml:space="preserve">4.5302562713623</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51114130020142</t>
+    <t xml:space="preserve">4.51114082336426</t>
   </si>
   <si>
     <t xml:space="preserve">4.58760166168213</t>
@@ -833,25 +833,25 @@
     <t xml:space="preserve">4.43468141555786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62583160400391</t>
+    <t xml:space="preserve">4.62583208084106</t>
   </si>
   <si>
     <t xml:space="preserve">4.74052143096924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75963592529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70229148864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68317699432373</t>
+    <t xml:space="preserve">4.75963687896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70229053497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68317651748657</t>
   </si>
   <si>
     <t xml:space="preserve">4.77875185012817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56848621368408</t>
+    <t xml:space="preserve">4.56848669052124</t>
   </si>
   <si>
     <t xml:space="preserve">4.66406154632568</t>
@@ -860,97 +860,97 @@
     <t xml:space="preserve">4.72140693664551</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87432718276978</t>
+    <t xml:space="preserve">4.8743257522583</t>
   </si>
   <si>
     <t xml:space="preserve">4.96990156173706</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92211484909058</t>
+    <t xml:space="preserve">4.92211437225342</t>
   </si>
   <si>
     <t xml:space="preserve">5.11326456069946</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16105175018311</t>
+    <t xml:space="preserve">5.16105222702026</t>
   </si>
   <si>
     <t xml:space="preserve">5.20883941650391</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25662708282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30441474914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44777631759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63892698287964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59113883972168</t>
+    <t xml:space="preserve">5.25662660598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30441427230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44777584075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63892650604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59113931655884</t>
   </si>
   <si>
     <t xml:space="preserve">5.81332635879517</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71643781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42577171325684</t>
+    <t xml:space="preserve">5.71643829345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42577123641968</t>
   </si>
   <si>
     <t xml:space="preserve">5.1351056098938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84443950653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82506084442139</t>
+    <t xml:space="preserve">4.84443855285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8250617980957</t>
   </si>
   <si>
     <t xml:space="preserve">4.80568313598633</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59252738952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55377244949341</t>
+    <t xml:space="preserve">4.59252834320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55377292633057</t>
   </si>
   <si>
     <t xml:space="preserve">4.76692771911621</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03821611404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9897723197937</t>
+    <t xml:space="preserve">5.03821659088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98977184295654</t>
   </si>
   <si>
     <t xml:space="preserve">5.08666086196899</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18354940414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9413275718689</t>
+    <t xml:space="preserve">5.18354988098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94132709503174</t>
   </si>
   <si>
     <t xml:space="preserve">5.23199415206909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74755048751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2804388999939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89288330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63128423690796</t>
+    <t xml:space="preserve">4.74755001068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28043842315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89288282394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6312837600708</t>
   </si>
   <si>
     <t xml:space="preserve">4.53439474105835</t>
@@ -968,16 +968,16 @@
     <t xml:space="preserve">4.70879459381104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91021490097046</t>
+    <t xml:space="preserve">5.91021585464478</t>
   </si>
   <si>
     <t xml:space="preserve">5.61954927444458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32888317108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37732791900635</t>
+    <t xml:space="preserve">5.32888269424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37732696533203</t>
   </si>
   <si>
     <t xml:space="preserve">5.57110500335693</t>
@@ -986,16 +986,16 @@
     <t xml:space="preserve">5.47421598434448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66799306869507</t>
+    <t xml:space="preserve">5.66799402236938</t>
   </si>
   <si>
     <t xml:space="preserve">6.73376989364624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29777097702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4431037902832</t>
+    <t xml:space="preserve">6.29777050018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44310331344604</t>
   </si>
   <si>
     <t xml:space="preserve">6.68532562255859</t>
@@ -1004,58 +1004,58 @@
     <t xml:space="preserve">6.5884370803833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63688087463379</t>
+    <t xml:space="preserve">6.63688135147095</t>
   </si>
   <si>
     <t xml:space="preserve">6.24932622909546</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34621524810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5399923324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39465951919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71998977661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99332427978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09021377563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04176902770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94487953186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84799194335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89643573760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38087844848633</t>
+    <t xml:space="preserve">6.34621477127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53999280929565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3946590423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71999073028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99332523345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09021472930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04176807403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94488000869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84799098968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89643621444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38087749481201</t>
   </si>
   <si>
     <t xml:space="preserve">10.2702112197876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88265514373779</t>
+    <t xml:space="preserve">9.88265419006348</t>
   </si>
   <si>
     <t xml:space="preserve">10.173321723938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9795446395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0764322280884</t>
+    <t xml:space="preserve">9.97954368591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0764331817627</t>
   </si>
   <si>
     <t xml:space="preserve">11.2390985488892</t>
@@ -1064,49 +1064,49 @@
     <t xml:space="preserve">11.6266527175903</t>
   </si>
   <si>
-    <t xml:space="preserve">13.079984664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2737617492676</t>
+    <t xml:space="preserve">13.0799856185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2737627029419</t>
   </si>
   <si>
     <t xml:space="preserve">12.9830951690674</t>
   </si>
   <si>
-    <t xml:space="preserve">14.436427116394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3395385742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0177612304688</t>
+    <t xml:space="preserve">14.4364290237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3395395278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0177602767944</t>
   </si>
   <si>
     <t xml:space="preserve">16.1669788360596</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1930656433105</t>
+    <t xml:space="preserve">15.1930646896362</t>
   </si>
   <si>
     <t xml:space="preserve">15.0956735610962</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9008913040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6348009109497</t>
+    <t xml:space="preserve">14.9008903503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6348028182983</t>
   </si>
   <si>
     <t xml:space="preserve">12.0765390396118</t>
   </si>
   <si>
-    <t xml:space="preserve">12.466103553772</t>
+    <t xml:space="preserve">12.4661045074463</t>
   </si>
   <si>
     <t xml:space="preserve">13.4400196075439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9269771575928</t>
+    <t xml:space="preserve">13.9269762039185</t>
   </si>
   <si>
     <t xml:space="preserve">14.0243673324585</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">14.2191514968872</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8034992218018</t>
+    <t xml:space="preserve">14.8035001754761</t>
   </si>
   <si>
     <t xml:space="preserve">14.4139337539673</t>
@@ -1124,22 +1124,22 @@
     <t xml:space="preserve">14.6087169647217</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7061080932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5113248825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3426265716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1217594146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3165416717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8295850753784</t>
+    <t xml:space="preserve">14.706109046936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5113258361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3426284790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1217584609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3165426254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8295841217041</t>
   </si>
   <si>
     <t xml:space="preserve">13.537410736084</t>
@@ -1154,13 +1154,13 @@
     <t xml:space="preserve">12.3687133789062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7582788467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5634956359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1739292144775</t>
+    <t xml:space="preserve">12.7582778930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5634965896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1739301681519</t>
   </si>
   <si>
     <t xml:space="preserve">11.6869735717773</t>
@@ -1169,49 +1169,49 @@
     <t xml:space="preserve">11.1026239395142</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93392753601074</t>
+    <t xml:space="preserve">9.93392658233643</t>
   </si>
   <si>
     <t xml:space="preserve">10.7130584716797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2000160217285</t>
+    <t xml:space="preserve">11.2000169754028</t>
   </si>
   <si>
     <t xml:space="preserve">11.9791479110718</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8817548751831</t>
+    <t xml:space="preserve">11.8817558288574</t>
   </si>
   <si>
     <t xml:space="preserve">10.9078416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2974071502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3947982788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5895805358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0052318572998</t>
+    <t xml:space="preserve">11.2974081039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3947992324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.589581489563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0052328109741</t>
   </si>
   <si>
     <t xml:space="preserve">11.7843647003174</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4921903610229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8104515075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4208841323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2261018753052</t>
+    <t xml:space="preserve">11.4921913146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8104496002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4208850860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2261009216309</t>
   </si>
   <si>
     <t xml:space="preserve">10.3234939575195</t>
@@ -1220,16 +1220,16 @@
     <t xml:space="preserve">10.1287097930908</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0313196182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73914527893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54436111450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8365364074707</t>
+    <t xml:space="preserve">10.0313186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73914337158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54436206817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83653545379639</t>
   </si>
   <si>
     <t xml:space="preserve">9.34957981109619</t>
@@ -1238,37 +1238,37 @@
     <t xml:space="preserve">9.49566555023193</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2713222503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9530620574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6800231933594</t>
+    <t xml:space="preserve">12.2713232040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9530611038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6800222396851</t>
   </si>
   <si>
     <t xml:space="preserve">13.7321939468384</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1704559326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3652372360229</t>
+    <t xml:space="preserve">14.1704549789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3652381896973</t>
   </si>
   <si>
     <t xml:space="preserve">14.0730628967285</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1443691253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5364570617676</t>
+    <t xml:space="preserve">15.1443700790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5364561080933</t>
   </si>
   <si>
     <t xml:space="preserve">15.585467338562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6344776153564</t>
+    <t xml:space="preserve">15.6344785690308</t>
   </si>
   <si>
     <t xml:space="preserve">15.193380355835</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">15.4874458312988</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4384346008301</t>
+    <t xml:space="preserve">15.4384355545044</t>
   </si>
   <si>
     <t xml:space="preserve">15.2423915863037</t>
@@ -1295,13 +1295,13 @@
     <t xml:space="preserve">15.0463485717773</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6542596817017</t>
+    <t xml:space="preserve">14.654260635376</t>
   </si>
   <si>
     <t xml:space="preserve">13.9190969467163</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1641511917114</t>
+    <t xml:space="preserve">14.1641502380371</t>
   </si>
   <si>
     <t xml:space="preserve">13.7230529785156</t>
@@ -1328,13 +1328,13 @@
     <t xml:space="preserve">14.0171184539795</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1839332580566</t>
+    <t xml:space="preserve">13.1839323043823</t>
   </si>
   <si>
     <t xml:space="preserve">13.5270099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9483261108398</t>
+    <t xml:space="preserve">14.9483251571655</t>
   </si>
   <si>
     <t xml:space="preserve">14.4092054367065</t>
@@ -1343,43 +1343,43 @@
     <t xml:space="preserve">14.8503036499023</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7522830963135</t>
+    <t xml:space="preserve">14.7522821426392</t>
   </si>
   <si>
     <t xml:space="preserve">14.6052494049072</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7032718658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5562391281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5072288513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0661296844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3309669494629</t>
+    <t xml:space="preserve">14.7032709121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5562381744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.507227897644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0661306381226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3309659957886</t>
   </si>
   <si>
     <t xml:space="preserve">13.4779987335205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2819547653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8898668289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7428340911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9878902435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1349229812622</t>
+    <t xml:space="preserve">13.2819557189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8898677825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7428350448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.987889289856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1349220275879</t>
   </si>
   <si>
     <t xml:space="preserve">12.3507480621338</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">11.7626171112061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3215188980103</t>
+    <t xml:space="preserve">11.3215198516846</t>
   </si>
   <si>
     <t xml:space="preserve">12.3017377853394</t>
@@ -1409,13 +1409,13 @@
     <t xml:space="preserve">15.8795328140259</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9775533676147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3696422576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6834888458252</t>
+    <t xml:space="preserve">15.9775552749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3696441650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6834897994995</t>
   </si>
   <si>
     <t xml:space="preserve">15.7815113067627</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">16.2716197967529</t>
   </si>
   <si>
-    <t xml:space="preserve">16.320629119873</t>
+    <t xml:space="preserve">16.3206310272217</t>
   </si>
   <si>
     <t xml:space="preserve">18.7221660614014</t>
@@ -1451,13 +1451,13 @@
     <t xml:space="preserve">19.7023830413818</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6043605804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.800407409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0944709777832</t>
+    <t xml:space="preserve">19.604362487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8004055023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0944690704346</t>
   </si>
   <si>
     <t xml:space="preserve">23.9173202514648</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">24.7995166778564</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2311706542969</t>
+    <t xml:space="preserve">23.2311687469482</t>
   </si>
   <si>
     <t xml:space="preserve">20.7806243896484</t>
@@ -1481,19 +1481,19 @@
     <t xml:space="preserve">21.1727104187012</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4865589141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6826019287109</t>
+    <t xml:space="preserve">20.4865570068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6826038360596</t>
   </si>
   <si>
     <t xml:space="preserve">21.3687534332275</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6430377960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9955596923828</t>
+    <t xml:space="preserve">22.6430397033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9955615997314</t>
   </si>
   <si>
     <t xml:space="preserve">25.2896251678467</t>
@@ -1508,19 +1508,19 @@
     <t xml:space="preserve">24.5054531097412</t>
   </si>
   <si>
-    <t xml:space="preserve">24.015344619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6232566833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8390808105469</t>
+    <t xml:space="preserve">24.0153427124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.623254776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8390789031982</t>
   </si>
   <si>
     <t xml:space="preserve">23.3291893005371</t>
   </si>
   <si>
-    <t xml:space="preserve">22.937105178833</t>
+    <t xml:space="preserve">22.9371032714844</t>
   </si>
   <si>
     <t xml:space="preserve">23.7212791442871</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">23.0351257324219</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1331481933594</t>
+    <t xml:space="preserve">23.1331462860107</t>
   </si>
   <si>
     <t xml:space="preserve">24.2113876342773</t>
@@ -1541,10 +1541,10 @@
     <t xml:space="preserve">24.4074287414551</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8192977905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2509498596191</t>
+    <t xml:space="preserve">23.819299697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2509517669678</t>
   </si>
   <si>
     <t xml:space="preserve">21.7608413696289</t>
@@ -1553,16 +1553,16 @@
     <t xml:space="preserve">21.9568843841553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1529273986816</t>
+    <t xml:space="preserve">22.1529293060303</t>
   </si>
   <si>
     <t xml:space="preserve">18.7711753845215</t>
   </si>
   <si>
-    <t xml:space="preserve">18.330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6439266204834</t>
+    <t xml:space="preserve">18.3300800323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6439247131348</t>
   </si>
   <si>
     <t xml:space="preserve">18.5261211395264</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">19.8984279632568</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3885364532471</t>
+    <t xml:space="preserve">20.3885345458984</t>
   </si>
   <si>
     <t xml:space="preserve">19.4049549102783</t>
@@ -1595,10 +1595,10 @@
     <t xml:space="preserve">19.5527095794678</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7989635467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6019592285156</t>
+    <t xml:space="preserve">19.7989654541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.601957321167</t>
   </si>
   <si>
     <t xml:space="preserve">18.9616947174072</t>
@@ -1628,16 +1628,13 @@
     <t xml:space="preserve">20.4884796142578</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5869827270508</t>
+    <t xml:space="preserve">20.5869808197021</t>
   </si>
   <si>
     <t xml:space="preserve">19.9959678649902</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0944690704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4542045593262</t>
+    <t xml:space="preserve">19.4542064666748</t>
   </si>
   <si>
     <t xml:space="preserve">19.5034561157227</t>
@@ -1649,7 +1646,7 @@
     <t xml:space="preserve">19.207950592041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0259227752686</t>
+    <t xml:space="preserve">18.0259208679199</t>
   </si>
   <si>
     <t xml:space="preserve">18.075174331665</t>
@@ -1673,19 +1670,19 @@
     <t xml:space="preserve">17.9274196624756</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9766693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4349098205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.173677444458</t>
+    <t xml:space="preserve">17.9766712188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.434907913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1736755371094</t>
   </si>
   <si>
     <t xml:space="preserve">18.4199314117432</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7839870452881</t>
+    <t xml:space="preserve">20.7839889526367</t>
   </si>
   <si>
     <t xml:space="preserve">20.3899784088135</t>
@@ -1694,10 +1691,10 @@
     <t xml:space="preserve">19.7004623413086</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9124450683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.109447479248</t>
+    <t xml:space="preserve">18.9124431610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1094455718994</t>
   </si>
   <si>
     <t xml:space="preserve">18.8631916046143</t>
@@ -1706,7 +1703,7 @@
     <t xml:space="preserve">18.5184326171875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7154369354248</t>
+    <t xml:space="preserve">18.7154388427734</t>
   </si>
   <si>
     <t xml:space="preserve">18.2229270935059</t>
@@ -1715,7 +1712,7 @@
     <t xml:space="preserve">17.7796649932861</t>
   </si>
   <si>
-    <t xml:space="preserve">18.567684173584</t>
+    <t xml:space="preserve">18.5676860809326</t>
   </si>
   <si>
     <t xml:space="preserve">17.7304153442383</t>
@@ -1727,16 +1724,16 @@
     <t xml:space="preserve">18.2721767425537</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6811656951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8781681060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1244239807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6319122314453</t>
+    <t xml:space="preserve">17.6811637878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8781700134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1244258880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6319141387939</t>
   </si>
   <si>
     <t xml:space="preserve">17.4841594696045</t>
@@ -1745,7 +1742,7 @@
     <t xml:space="preserve">17.3856582641602</t>
   </si>
   <si>
-    <t xml:space="preserve">17.533411026001</t>
+    <t xml:space="preserve">17.5334091186523</t>
   </si>
   <si>
     <t xml:space="preserve">17.1886520385742</t>
@@ -1760,7 +1757,7 @@
     <t xml:space="preserve">16.4991359710693</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8931446075439</t>
+    <t xml:space="preserve">16.8931465148926</t>
   </si>
   <si>
     <t xml:space="preserve">16.4498863220215</t>
@@ -1772,7 +1769,7 @@
     <t xml:space="preserve">16.6468906402588</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7946434020996</t>
+    <t xml:space="preserve">16.794641494751</t>
   </si>
   <si>
     <t xml:space="preserve">16.7453918457031</t>
@@ -1784,7 +1781,7 @@
     <t xml:space="preserve">14.6275930404663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9723510742188</t>
+    <t xml:space="preserve">14.9723501205444</t>
   </si>
   <si>
     <t xml:space="preserve">14.7260942459106</t>
@@ -1799,7 +1796,7 @@
     <t xml:space="preserve">15.1201047897339</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3663606643677</t>
+    <t xml:space="preserve">15.3663597106934</t>
   </si>
   <si>
     <t xml:space="preserve">15.464861869812</t>
@@ -1808,16 +1805,16 @@
     <t xml:space="preserve">14.7753458023071</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4798383712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2828350067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5783424377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0858297348022</t>
+    <t xml:space="preserve">14.4798393249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2828340530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5783414840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0858306884766</t>
   </si>
   <si>
     <t xml:space="preserve">14.2335834503174</t>
@@ -41440,7 +41437,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1499" t="s">
-        <v>540</v>
+        <v>481</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41492,7 +41489,7 @@
         <v>19.75</v>
       </c>
       <c r="G1501" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41596,7 +41593,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1505" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41622,7 +41619,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1506" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41674,7 +41671,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1508" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41700,7 +41697,7 @@
         <v>19.5</v>
       </c>
       <c r="G1509" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41726,7 +41723,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1510" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41752,7 +41749,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1511" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41778,7 +41775,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1512" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41804,7 +41801,7 @@
         <v>19.5</v>
       </c>
       <c r="G1513" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41830,7 +41827,7 @@
         <v>19.5</v>
       </c>
       <c r="G1514" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41856,7 +41853,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1515" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41882,7 +41879,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1516" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41908,7 +41905,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1517" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -41934,7 +41931,7 @@
         <v>18.75</v>
       </c>
       <c r="G1518" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -41960,7 +41957,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1519" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41986,7 +41983,7 @@
         <v>17.5</v>
       </c>
       <c r="G1520" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42012,7 +42009,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1521" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42038,7 +42035,7 @@
         <v>18.25</v>
       </c>
       <c r="G1522" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42064,7 +42061,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1523" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42090,7 +42087,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1524" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42116,7 +42113,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1525" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42142,7 +42139,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1526" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42168,7 +42165,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1527" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42194,7 +42191,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1528" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42220,7 +42217,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1529" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42350,7 +42347,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1534" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42376,7 +42373,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1535" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42428,7 +42425,7 @@
         <v>20</v>
       </c>
       <c r="G1537" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42506,7 +42503,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1540" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42532,7 +42529,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1541" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42558,7 +42555,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1542" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42610,7 +42607,7 @@
         <v>19.5</v>
       </c>
       <c r="G1544" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42636,7 +42633,7 @@
         <v>19.5</v>
       </c>
       <c r="G1545" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42714,7 +42711,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1548" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42740,7 +42737,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G1549" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42870,7 +42867,7 @@
         <v>19.5</v>
       </c>
       <c r="G1554" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42896,7 +42893,7 @@
         <v>19.5</v>
       </c>
       <c r="G1555" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42922,7 +42919,7 @@
         <v>19.5</v>
       </c>
       <c r="G1556" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42974,7 +42971,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1558" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43000,7 +42997,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1559" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43026,7 +43023,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1560" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43052,7 +43049,7 @@
         <v>19</v>
       </c>
       <c r="G1561" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43078,7 +43075,7 @@
         <v>19</v>
       </c>
       <c r="G1562" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43104,7 +43101,7 @@
         <v>19</v>
       </c>
       <c r="G1563" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43130,7 +43127,7 @@
         <v>19</v>
       </c>
       <c r="G1564" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43156,7 +43153,7 @@
         <v>19</v>
       </c>
       <c r="G1565" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43182,7 +43179,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1566" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43208,7 +43205,7 @@
         <v>19</v>
       </c>
       <c r="G1567" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43234,7 +43231,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1568" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43260,7 +43257,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1569" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43286,7 +43283,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1570" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43312,7 +43309,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1571" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -43338,7 +43335,7 @@
         <v>19</v>
       </c>
       <c r="G1572" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43364,7 +43361,7 @@
         <v>19</v>
       </c>
       <c r="G1573" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43390,7 +43387,7 @@
         <v>19</v>
       </c>
       <c r="G1574" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43416,7 +43413,7 @@
         <v>18.75</v>
       </c>
       <c r="G1575" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43442,7 +43439,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1576" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43468,7 +43465,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1577" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43494,7 +43491,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1578" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43520,7 +43517,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1579" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43546,7 +43543,7 @@
         <v>19</v>
       </c>
       <c r="G1580" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43572,7 +43569,7 @@
         <v>19</v>
       </c>
       <c r="G1581" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43598,7 +43595,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1582" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43624,7 +43621,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1583" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43650,7 +43647,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1584" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43676,7 +43673,7 @@
         <v>18.75</v>
       </c>
       <c r="G1585" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43702,7 +43699,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1586" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43728,7 +43725,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1587" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43754,7 +43751,7 @@
         <v>18.5</v>
       </c>
       <c r="G1588" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43780,7 +43777,7 @@
         <v>18.5</v>
       </c>
       <c r="G1589" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43806,7 +43803,7 @@
         <v>18.5</v>
       </c>
       <c r="G1590" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43832,7 +43829,7 @@
         <v>18.5</v>
       </c>
       <c r="G1591" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43858,7 +43855,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1592" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43884,7 +43881,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1593" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43910,7 +43907,7 @@
         <v>18</v>
       </c>
       <c r="G1594" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43936,7 +43933,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1595" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -43962,7 +43959,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1596" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43988,7 +43985,7 @@
         <v>18.5</v>
       </c>
       <c r="G1597" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44014,7 +44011,7 @@
         <v>18.5</v>
       </c>
       <c r="G1598" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44040,7 +44037,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1599" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44066,7 +44063,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1600" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44092,7 +44089,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1601" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44118,7 +44115,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1602" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44144,7 +44141,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1603" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44170,7 +44167,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1604" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44196,7 +44193,7 @@
         <v>18.25</v>
       </c>
       <c r="G1605" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44222,7 +44219,7 @@
         <v>18</v>
       </c>
       <c r="G1606" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -44248,7 +44245,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1607" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -44274,7 +44271,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1608" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -44300,7 +44297,7 @@
         <v>18</v>
       </c>
       <c r="G1609" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44326,7 +44323,7 @@
         <v>18.25</v>
       </c>
       <c r="G1610" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -44352,7 +44349,7 @@
         <v>18.25</v>
       </c>
       <c r="G1611" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44378,7 +44375,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1612" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44404,7 +44401,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1613" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44430,7 +44427,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1614" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44456,7 +44453,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1615" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44482,7 +44479,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1616" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44508,7 +44505,7 @@
         <v>18</v>
       </c>
       <c r="G1617" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44534,7 +44531,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1618" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44560,7 +44557,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1619" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44586,7 +44583,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1620" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44612,7 +44609,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1621" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44638,7 +44635,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1622" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44664,7 +44661,7 @@
         <v>18</v>
       </c>
       <c r="G1623" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44690,7 +44687,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1624" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44716,7 +44713,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1625" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44742,7 +44739,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1626" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44768,7 +44765,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1627" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44794,7 +44791,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1628" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44820,7 +44817,7 @@
         <v>18.25</v>
       </c>
       <c r="G1629" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44846,7 +44843,7 @@
         <v>18.25</v>
       </c>
       <c r="G1630" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44872,7 +44869,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1631" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44898,7 +44895,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1632" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44924,7 +44921,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1633" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44950,7 +44947,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1634" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44976,7 +44973,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1635" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45002,7 +44999,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1636" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45028,7 +45025,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1637" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45054,7 +45051,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1638" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45080,7 +45077,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1639" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45106,7 +45103,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1640" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45132,7 +45129,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1641" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -45158,7 +45155,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1642" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45184,7 +45181,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1643" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45210,7 +45207,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1644" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -45236,7 +45233,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1645" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -45262,7 +45259,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1646" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -45288,7 +45285,7 @@
         <v>18</v>
       </c>
       <c r="G1647" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -45314,7 +45311,7 @@
         <v>18.25</v>
       </c>
       <c r="G1648" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -45340,7 +45337,7 @@
         <v>18.25</v>
       </c>
       <c r="G1649" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -45366,7 +45363,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1650" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45392,7 +45389,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1651" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -45418,7 +45415,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1652" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45444,7 +45441,7 @@
         <v>18</v>
       </c>
       <c r="G1653" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45470,7 +45467,7 @@
         <v>18</v>
       </c>
       <c r="G1654" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45496,7 +45493,7 @@
         <v>18</v>
       </c>
       <c r="G1655" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45522,7 +45519,7 @@
         <v>18</v>
       </c>
       <c r="G1656" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45548,7 +45545,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1657" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45574,7 +45571,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1658" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45600,7 +45597,7 @@
         <v>17.75</v>
       </c>
       <c r="G1659" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45626,7 +45623,7 @@
         <v>18</v>
       </c>
       <c r="G1660" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45652,7 +45649,7 @@
         <v>18</v>
       </c>
       <c r="G1661" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45678,7 +45675,7 @@
         <v>18</v>
       </c>
       <c r="G1662" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45704,7 +45701,7 @@
         <v>18</v>
       </c>
       <c r="G1663" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45730,7 +45727,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1664" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45756,7 +45753,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1665" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45782,7 +45779,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1666" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45808,7 +45805,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1667" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45834,7 +45831,7 @@
         <v>17.5</v>
       </c>
       <c r="G1668" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45860,7 +45857,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1669" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45886,7 +45883,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1670" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45912,7 +45909,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1671" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45938,7 +45935,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1672" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45964,7 +45961,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1673" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45990,7 +45987,7 @@
         <v>16.75</v>
       </c>
       <c r="G1674" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -46016,7 +46013,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1675" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -46042,7 +46039,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1676" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -46068,7 +46065,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1677" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -46094,7 +46091,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1678" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -46120,7 +46117,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1679" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -46146,7 +46143,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1680" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -46172,7 +46169,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1681" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -46198,7 +46195,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1682" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -46224,7 +46221,7 @@
         <v>17</v>
       </c>
       <c r="G1683" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -46250,7 +46247,7 @@
         <v>17</v>
       </c>
       <c r="G1684" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -46276,7 +46273,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1685" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -46302,7 +46299,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1686" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -46328,7 +46325,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1687" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -46354,7 +46351,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46380,7 +46377,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1689" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -46406,7 +46403,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1690" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -46432,7 +46429,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1691" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46458,7 +46455,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1692" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46484,7 +46481,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1693" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -46510,7 +46507,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46536,7 +46533,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1695" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46562,7 +46559,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1696" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46588,7 +46585,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1697" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46614,7 +46611,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1698" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46640,7 +46637,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1699" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46666,7 +46663,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1700" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46692,7 +46689,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1701" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46718,7 +46715,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1702" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46744,7 +46741,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1703" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46770,7 +46767,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1704" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46796,7 +46793,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1705" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46822,7 +46819,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1706" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46848,7 +46845,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1707" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46874,7 +46871,7 @@
         <v>15</v>
       </c>
       <c r="G1708" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46900,7 +46897,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1709" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46926,7 +46923,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1710" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46952,7 +46949,7 @@
         <v>14.5</v>
       </c>
       <c r="G1711" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46978,7 +46975,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1712" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -47004,7 +47001,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1713" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47030,7 +47027,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1714" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -47056,7 +47053,7 @@
         <v>15</v>
       </c>
       <c r="G1715" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -47082,7 +47079,7 @@
         <v>15</v>
       </c>
       <c r="G1716" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47108,7 +47105,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1717" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -47134,7 +47131,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1718" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -47160,7 +47157,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -47186,7 +47183,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1720" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -47212,7 +47209,7 @@
         <v>14.25</v>
       </c>
       <c r="G1721" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -47238,7 +47235,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1722" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -47264,7 +47261,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1723" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -47290,7 +47287,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1724" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -47316,7 +47313,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1725" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -47342,7 +47339,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1726" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47368,7 +47365,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1727" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47394,7 +47391,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1728" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -47420,7 +47417,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1729" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47446,7 +47443,7 @@
         <v>14.75</v>
       </c>
       <c r="G1730" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47472,7 +47469,7 @@
         <v>14.75</v>
       </c>
       <c r="G1731" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47498,7 +47495,7 @@
         <v>14.75</v>
       </c>
       <c r="G1732" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47524,7 +47521,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1733" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47550,7 +47547,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1734" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47576,7 +47573,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1735" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47602,7 +47599,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1736" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47628,7 +47625,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1737" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47654,7 +47651,7 @@
         <v>13.25</v>
       </c>
       <c r="G1738" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47680,7 +47677,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1739" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47706,7 +47703,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1740" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47732,7 +47729,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1741" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47758,7 +47755,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1742" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47784,7 +47781,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1743" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47810,7 +47807,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1744" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47836,7 +47833,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1745" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47862,7 +47859,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1746" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47888,7 +47885,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1747" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47914,7 +47911,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1748" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47940,7 +47937,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1749" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47966,7 +47963,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1750" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47992,7 +47989,7 @@
         <v>12.75</v>
       </c>
       <c r="G1751" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -48018,7 +48015,7 @@
         <v>12.5</v>
       </c>
       <c r="G1752" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -48044,7 +48041,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1753" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -48070,7 +48067,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1754" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -48096,7 +48093,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1755" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -48122,7 +48119,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1756" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -48148,7 +48145,7 @@
         <v>12.25</v>
       </c>
       <c r="G1757" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -48174,7 +48171,7 @@
         <v>12.25</v>
       </c>
       <c r="G1758" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -48200,7 +48197,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1759" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -48226,7 +48223,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1760" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -48252,7 +48249,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1761" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -48278,7 +48275,7 @@
         <v>12.75</v>
       </c>
       <c r="G1762" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -48304,7 +48301,7 @@
         <v>12.75</v>
       </c>
       <c r="G1763" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -48330,7 +48327,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1764" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -48356,7 +48353,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1765" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48382,7 +48379,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1766" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48408,7 +48405,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1767" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48434,7 +48431,7 @@
         <v>12.5</v>
       </c>
       <c r="G1768" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48460,7 +48457,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1769" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48486,7 +48483,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1770" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48512,7 +48509,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1771" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48538,7 +48535,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1772" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48564,7 +48561,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1773" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48590,7 +48587,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1774" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48616,7 +48613,7 @@
         <v>12.75</v>
       </c>
       <c r="G1775" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48642,7 +48639,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1776" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48668,7 +48665,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1777" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48694,7 +48691,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1778" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48720,7 +48717,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1779" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48746,7 +48743,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1780" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48772,7 +48769,7 @@
         <v>13</v>
       </c>
       <c r="G1781" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48798,7 +48795,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1782" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48824,7 +48821,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1783" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48850,7 +48847,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1784" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48876,7 +48873,7 @@
         <v>12.75</v>
       </c>
       <c r="G1785" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48902,7 +48899,7 @@
         <v>12.75</v>
       </c>
       <c r="G1786" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48928,7 +48925,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48954,7 +48951,7 @@
         <v>12.5</v>
       </c>
       <c r="G1788" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48980,7 +48977,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1789" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -49006,7 +49003,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1790" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -49032,7 +49029,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1791" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -49058,7 +49055,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1792" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -49084,7 +49081,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1793" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -49110,7 +49107,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1794" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -49136,7 +49133,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1795" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -49162,7 +49159,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1796" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -49188,7 +49185,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1797" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -49214,7 +49211,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1798" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -49240,7 +49237,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1799" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -49266,7 +49263,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1800" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -49292,7 +49289,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1801" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -49318,7 +49315,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1802" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -49344,7 +49341,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1803" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49370,7 +49367,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1804" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49396,7 +49393,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1805" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49422,7 +49419,7 @@
         <v>12.75</v>
       </c>
       <c r="G1806" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49448,7 +49445,7 @@
         <v>12.75</v>
       </c>
       <c r="G1807" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49474,7 +49471,7 @@
         <v>12.75</v>
       </c>
       <c r="G1808" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49500,7 +49497,7 @@
         <v>12.75</v>
       </c>
       <c r="G1809" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49526,7 +49523,7 @@
         <v>12.75</v>
       </c>
       <c r="G1810" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49552,7 +49549,7 @@
         <v>12.75</v>
       </c>
       <c r="G1811" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49578,7 +49575,7 @@
         <v>12.75</v>
       </c>
       <c r="G1812" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49604,7 +49601,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1813" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49630,7 +49627,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1814" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49656,7 +49653,7 @@
         <v>12.75</v>
       </c>
       <c r="G1815" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49682,7 +49679,7 @@
         <v>12.75</v>
       </c>
       <c r="G1816" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49708,7 +49705,7 @@
         <v>12.75</v>
       </c>
       <c r="G1817" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49734,7 +49731,7 @@
         <v>12.75</v>
       </c>
       <c r="G1818" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49760,7 +49757,7 @@
         <v>12.75</v>
       </c>
       <c r="G1819" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49786,7 +49783,7 @@
         <v>12.75</v>
       </c>
       <c r="G1820" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49812,7 +49809,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1821" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49838,7 +49835,7 @@
         <v>12.5</v>
       </c>
       <c r="G1822" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49864,7 +49861,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1823" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49890,7 +49887,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1824" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49916,7 +49913,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1825" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49942,7 +49939,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1826" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49968,7 +49965,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1827" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49994,7 +49991,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1828" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -50020,7 +50017,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1829" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -50046,7 +50043,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1830" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -50072,7 +50069,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1831" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -50098,7 +50095,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1832" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -50124,7 +50121,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1833" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -50150,7 +50147,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1834" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -50176,7 +50173,7 @@
         <v>12.5</v>
       </c>
       <c r="G1835" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -50202,7 +50199,7 @@
         <v>12.5</v>
       </c>
       <c r="G1836" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -50228,7 +50225,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1837" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -50254,7 +50251,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1838" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -50280,7 +50277,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1839" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -50306,7 +50303,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -50332,7 +50329,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1841" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50358,7 +50355,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1842" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50384,7 +50381,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1843" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50410,7 +50407,7 @@
         <v>12.75</v>
       </c>
       <c r="G1844" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50436,7 +50433,7 @@
         <v>12.75</v>
       </c>
       <c r="G1845" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50462,7 +50459,7 @@
         <v>12.75</v>
       </c>
       <c r="G1846" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50488,7 +50485,7 @@
         <v>12.75</v>
       </c>
       <c r="G1847" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50514,7 +50511,7 @@
         <v>12.75</v>
       </c>
       <c r="G1848" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50540,7 +50537,7 @@
         <v>12.75</v>
       </c>
       <c r="G1849" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50566,7 +50563,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1850" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50592,7 +50589,7 @@
         <v>13.25</v>
       </c>
       <c r="G1851" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50618,7 +50615,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1852" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50644,7 +50641,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1853" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50670,7 +50667,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1854" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50696,7 +50693,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1855" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50722,7 +50719,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1856" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50748,7 +50745,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1857" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50774,7 +50771,7 @@
         <v>13</v>
       </c>
       <c r="G1858" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50800,7 +50797,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1859" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50826,7 +50823,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1860" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50852,7 +50849,7 @@
         <v>13.25</v>
       </c>
       <c r="G1861" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50878,7 +50875,7 @@
         <v>13.25</v>
       </c>
       <c r="G1862" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50904,7 +50901,7 @@
         <v>13.25</v>
       </c>
       <c r="G1863" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50930,7 +50927,7 @@
         <v>13.25</v>
       </c>
       <c r="G1864" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50956,7 +50953,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1865" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50982,7 +50979,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1866" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -51008,7 +51005,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1867" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -51034,7 +51031,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1868" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -51060,7 +51057,7 @@
         <v>12.5</v>
       </c>
       <c r="G1869" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -51086,7 +51083,7 @@
         <v>12.5</v>
       </c>
       <c r="G1870" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -51112,7 +51109,7 @@
         <v>12.5</v>
       </c>
       <c r="G1871" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -51138,7 +51135,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1872" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -51164,7 +51161,7 @@
         <v>12.5</v>
       </c>
       <c r="G1873" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -51190,7 +51187,7 @@
         <v>12.5</v>
       </c>
       <c r="G1874" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -51216,7 +51213,7 @@
         <v>12.5</v>
       </c>
       <c r="G1875" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -51242,7 +51239,7 @@
         <v>12.5</v>
       </c>
       <c r="G1876" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -51268,7 +51265,7 @@
         <v>12.25</v>
       </c>
       <c r="G1877" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -51294,7 +51291,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1878" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -51320,7 +51317,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1879" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -51346,7 +51343,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1880" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51372,7 +51369,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1881" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51398,7 +51395,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1882" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51424,7 +51421,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1883" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51450,7 +51447,7 @@
         <v>12.5</v>
       </c>
       <c r="G1884" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51476,7 +51473,7 @@
         <v>12.5</v>
       </c>
       <c r="G1885" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51502,7 +51499,7 @@
         <v>12.5</v>
       </c>
       <c r="G1886" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51528,7 +51525,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1887" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51554,7 +51551,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1888" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51580,7 +51577,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1889" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51606,7 +51603,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1890" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51632,7 +51629,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1891" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51658,7 +51655,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1892" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51684,7 +51681,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1893" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51710,7 +51707,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1894" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51736,7 +51733,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1895" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51762,7 +51759,7 @@
         <v>14.75</v>
       </c>
       <c r="G1896" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51788,7 +51785,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1897" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51814,7 +51811,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1898" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51840,7 +51837,7 @@
         <v>14.25</v>
       </c>
       <c r="G1899" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51866,7 +51863,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1900" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51892,7 +51889,7 @@
         <v>14</v>
       </c>
       <c r="G1901" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51918,7 +51915,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1902" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51944,7 +51941,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1903" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51970,7 +51967,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1904" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51996,7 +51993,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1905" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52022,7 +52019,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1906" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52048,7 +52045,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52074,7 +52071,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1908" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52100,7 +52097,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1909" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52126,7 +52123,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1910" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -52152,7 +52149,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1911" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -52178,7 +52175,7 @@
         <v>13.25</v>
       </c>
       <c r="G1912" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -52204,7 +52201,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1913" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -52230,7 +52227,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1914" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -52256,7 +52253,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1915" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -52282,7 +52279,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1916" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -52308,7 +52305,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1917" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -52334,7 +52331,7 @@
         <v>12.75</v>
       </c>
       <c r="G1918" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52360,7 +52357,7 @@
         <v>13</v>
       </c>
       <c r="G1919" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52386,7 +52383,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1920" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52412,7 +52409,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1921" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52438,7 +52435,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1922" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52464,7 +52461,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1923" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52490,7 +52487,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1924" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52516,7 +52513,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1925" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52542,7 +52539,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1926" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52568,7 +52565,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1927" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52594,7 +52591,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1928" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52620,7 +52617,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1929" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52646,7 +52643,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1930" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52672,7 +52669,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1931" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52698,7 +52695,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1932" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52724,7 +52721,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1933" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52750,7 +52747,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1934" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52776,7 +52773,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1935" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52802,7 +52799,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1936" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52828,7 +52825,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1937" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52854,7 +52851,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1938" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52880,7 +52877,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1939" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52906,7 +52903,7 @@
         <v>12.5</v>
       </c>
       <c r="G1940" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52932,7 +52929,7 @@
         <v>12.75</v>
       </c>
       <c r="G1941" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52958,7 +52955,7 @@
         <v>12.75</v>
       </c>
       <c r="G1942" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52984,7 +52981,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1943" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53010,7 +53007,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1944" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53036,7 +53033,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1945" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53062,7 +53059,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1946" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53088,7 +53085,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1947" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53114,7 +53111,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1948" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -53140,7 +53137,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1949" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -53166,7 +53163,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1950" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -53192,7 +53189,7 @@
         <v>12.25</v>
       </c>
       <c r="G1951" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -53218,7 +53215,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1952" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -53244,7 +53241,7 @@
         <v>12.5</v>
       </c>
       <c r="G1953" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -53270,7 +53267,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1954" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -53296,7 +53293,7 @@
         <v>12.25</v>
       </c>
       <c r="G1955" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -53322,7 +53319,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1956" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -53348,7 +53345,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1957" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53374,7 +53371,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1958" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53400,7 +53397,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1959" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53426,7 +53423,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1960" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53452,7 +53449,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1961" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53478,7 +53475,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1962" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53504,7 +53501,7 @@
         <v>10.5</v>
       </c>
       <c r="G1963" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53530,7 +53527,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1964" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53556,7 +53553,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1965" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53582,7 +53579,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1966" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53608,7 +53605,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1967" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53634,7 +53631,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1968" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53660,7 +53657,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1969" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53686,7 +53683,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1970" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53712,7 +53709,7 @@
         <v>12</v>
       </c>
       <c r="G1971" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53738,7 +53735,7 @@
         <v>12</v>
       </c>
       <c r="G1972" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53764,7 +53761,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1973" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53790,7 +53787,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1974" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53816,7 +53813,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1975" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53842,7 +53839,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1976" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53868,7 +53865,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1977" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53894,7 +53891,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1978" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53920,7 +53917,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1979" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53946,7 +53943,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1980" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53972,7 +53969,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1981" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53998,7 +53995,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1982" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54024,7 +54021,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54050,7 +54047,7 @@
         <v>13</v>
       </c>
       <c r="G1984" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54076,7 +54073,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1985" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54102,7 +54099,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1986" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -54128,7 +54125,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1987" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -54154,7 +54151,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1988" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -54180,7 +54177,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1989" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -54206,7 +54203,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1990" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -54232,7 +54229,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1991" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -54258,7 +54255,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1992" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -54284,7 +54281,7 @@
         <v>13.5</v>
       </c>
       <c r="G1993" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -54310,7 +54307,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1994" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -54336,7 +54333,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1995" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54362,7 +54359,7 @@
         <v>14.5</v>
       </c>
       <c r="G1996" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54388,7 +54385,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1997" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54414,7 +54411,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1998" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54440,7 +54437,7 @@
         <v>15</v>
       </c>
       <c r="G1999" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54466,7 +54463,7 @@
         <v>15.5</v>
       </c>
       <c r="G2000" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54492,7 +54489,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2001" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54518,7 +54515,7 @@
         <v>15.5</v>
       </c>
       <c r="G2002" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54544,7 +54541,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2003" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54570,7 +54567,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2004" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54596,7 +54593,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2005" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54622,7 +54619,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2006" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54648,7 +54645,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2007" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54674,7 +54671,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2008" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54700,7 +54697,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2009" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54726,7 +54723,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2010" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54752,7 +54749,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2011" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54778,7 +54775,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2012" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54804,7 +54801,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2013" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54830,7 +54827,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2014" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54856,7 +54853,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2015" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54882,7 +54879,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2016" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54908,7 +54905,7 @@
         <v>16</v>
       </c>
       <c r="G2017" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54934,7 +54931,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2018" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54960,7 +54957,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2019" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54986,7 +54983,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2020" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55012,7 +55009,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2021" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55038,7 +55035,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2022" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55064,7 +55061,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2023" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55090,7 +55087,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2024" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -55116,7 +55113,7 @@
         <v>17.5</v>
       </c>
       <c r="G2025" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -55142,7 +55139,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2026" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -55168,7 +55165,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2027" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -55194,7 +55191,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2028" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -55220,7 +55217,7 @@
         <v>17.5</v>
       </c>
       <c r="G2029" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -55246,7 +55243,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2030" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -55272,7 +55269,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2031" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -55298,7 +55295,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2032" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -55324,7 +55321,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2033" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -55350,7 +55347,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2034" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -55376,7 +55373,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2035" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -55402,7 +55399,7 @@
         <v>17.5</v>
       </c>
       <c r="G2036" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -55428,7 +55425,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2037" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55454,7 +55451,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2038" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55480,7 +55477,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2039" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55506,7 +55503,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2040" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55532,7 +55529,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2041" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55558,7 +55555,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2042" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55584,7 +55581,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2043" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55610,7 +55607,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2044" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55636,7 +55633,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2045" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55662,7 +55659,7 @@
         <v>13</v>
       </c>
       <c r="G2046" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55688,7 +55685,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2047" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55714,7 +55711,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2048" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55740,7 +55737,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2049" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55766,7 +55763,7 @@
         <v>12</v>
       </c>
       <c r="G2050" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55792,7 +55789,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2051" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55818,7 +55815,7 @@
         <v>12</v>
       </c>
       <c r="G2052" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55844,7 +55841,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2053" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55870,7 +55867,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2054" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55896,7 +55893,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2055" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55922,7 +55919,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2056" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55948,7 +55945,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2057" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55974,7 +55971,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2058" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -56000,7 +55997,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2059" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -56026,7 +56023,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2060" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -56052,7 +56049,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2061" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -56078,7 +56075,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2062" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -56104,7 +56101,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2063" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -56130,7 +56127,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2064" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -56156,7 +56153,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2065" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -56182,7 +56179,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2066" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -56208,7 +56205,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2067" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -56234,7 +56231,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2068" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -56260,7 +56257,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2069" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -56286,7 +56283,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2070" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -56312,7 +56309,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2071" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -56338,7 +56335,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2072" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -56364,7 +56361,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2073" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -56390,7 +56387,7 @@
         <v>14</v>
       </c>
       <c r="G2074" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -56416,7 +56413,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2075" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56442,7 +56439,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2076" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56468,7 +56465,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2077" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56494,7 +56491,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2078" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56520,7 +56517,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2079" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -56546,7 +56543,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2080" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -56572,7 +56569,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2081" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56598,7 +56595,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2082" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56624,7 +56621,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2083" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56650,7 +56647,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2084" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56676,7 +56673,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2085" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56702,7 +56699,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2086" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56728,7 +56725,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2087" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56754,7 +56751,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2088" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56780,7 +56777,7 @@
         <v>15.5</v>
       </c>
       <c r="G2089" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56806,7 +56803,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2090" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56832,7 +56829,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2091" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56858,7 +56855,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2092" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56884,7 +56881,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2093" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56910,7 +56907,7 @@
         <v>14.5</v>
       </c>
       <c r="G2094" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56936,7 +56933,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2095" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56962,7 +56959,7 @@
         <v>15</v>
       </c>
       <c r="G2096" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56988,7 +56985,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2097" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -57014,7 +57011,7 @@
         <v>15</v>
       </c>
       <c r="G2098" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -57040,7 +57037,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2099" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -57066,7 +57063,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2100" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -57092,7 +57089,7 @@
         <v>15</v>
       </c>
       <c r="G2101" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -57100,7 +57097,7 @@
     </row>
     <row r="2102">
       <c r="A2102" s="1" t="n">
-        <v>45953.6046643518</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2102" t="n">
         <v>1750</v>
@@ -57118,9 +57115,35 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2102" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H2102" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" s="1" t="n">
+        <v>45954.6494560185</v>
+      </c>
+      <c r="B2103" t="n">
+        <v>1750</v>
+      </c>
+      <c r="C2103" t="n">
+        <v>15.1000003814697</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>14.6999998092651</v>
+      </c>
+      <c r="E2103" t="n">
+        <v>14.8999996185303</v>
+      </c>
+      <c r="F2103" t="n">
+        <v>15</v>
+      </c>
+      <c r="G2103" t="s">
+        <v>668</v>
+      </c>
+      <c r="H2103" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CULT.MI.xlsx
+++ b/data/CULT.MI.xlsx
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68585157394409</t>
+    <t xml:space="preserve">4.68585205078125</t>
   </si>
   <si>
     <t xml:space="preserve">CULT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57666778564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59486436843872</t>
+    <t xml:space="preserve">4.57666826248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59486484527588</t>
   </si>
   <si>
     <t xml:space="preserve">4.60851287841797</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58576679229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48931980133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5630202293396</t>
+    <t xml:space="preserve">4.58576631546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48931932449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56301975250244</t>
   </si>
   <si>
     <t xml:space="preserve">4.51297616958618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46020412445068</t>
+    <t xml:space="preserve">4.46020364761353</t>
   </si>
   <si>
     <t xml:space="preserve">4.29824638366699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21271800994873</t>
+    <t xml:space="preserve">4.21271753311157</t>
   </si>
   <si>
     <t xml:space="preserve">4.18178224563599</t>
@@ -98,88 +98,88 @@
     <t xml:space="preserve">4.22909545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1053524017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09443426132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10899114608765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99616813659668</t>
+    <t xml:space="preserve">4.10535287857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09443473815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1089916229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.996169090271</t>
   </si>
   <si>
     <t xml:space="preserve">4.04712104797363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0398416519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96341180801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07441759109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3200831413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24911308288574</t>
+    <t xml:space="preserve">4.03984117507935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96341228485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07441711425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32008361816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24911212921143</t>
   </si>
   <si>
     <t xml:space="preserve">3.97978973388672</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06895780563354</t>
+    <t xml:space="preserve">4.0689582824707</t>
   </si>
   <si>
     <t xml:space="preserve">4.05439949035645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9852499961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05076122283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07259798049927</t>
+    <t xml:space="preserve">3.98524951934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0507607460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07259750366211</t>
   </si>
   <si>
     <t xml:space="preserve">4.0380220413208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04530143737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03074264526367</t>
+    <t xml:space="preserve">4.04530096054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03074312210083</t>
   </si>
   <si>
     <t xml:space="preserve">4.01254606246948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04894113540649</t>
+    <t xml:space="preserve">4.04894065856934</t>
   </si>
   <si>
     <t xml:space="preserve">4.05985879898071</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07623720169067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9124596118927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99070906639099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01072549819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92155814170837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00162696838379</t>
+    <t xml:space="preserve">4.07623672485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91245913505554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99070835113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0107250213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92155766487122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00162601470947</t>
   </si>
   <si>
     <t xml:space="preserve">4.05803918838501</t>
@@ -191,13 +191,13 @@
     <t xml:space="preserve">4.2218165397644</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18542194366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16176509857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3546576499939</t>
+    <t xml:space="preserve">4.18542146682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16176462173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35465812683105</t>
   </si>
   <si>
     <t xml:space="preserve">4.28186845779419</t>
@@ -206,43 +206,43 @@
     <t xml:space="preserve">4.26731014251709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39287281036377</t>
+    <t xml:space="preserve">4.39287328720093</t>
   </si>
   <si>
     <t xml:space="preserve">4.36739683151245</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17814207077026</t>
+    <t xml:space="preserve">4.17814350128174</t>
   </si>
   <si>
     <t xml:space="preserve">4.27458906173706</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31826257705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35647773742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26549100875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26367044448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27640867233276</t>
+    <t xml:space="preserve">4.31826305389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35647821426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26549053192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26367092132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27640914916992</t>
   </si>
   <si>
     <t xml:space="preserve">4.14902687072754</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35829782485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35283851623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29460620880127</t>
+    <t xml:space="preserve">4.35829734802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35283803939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29460668563843</t>
   </si>
   <si>
     <t xml:space="preserve">4.2036190032959</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">4.24001407623291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34010076522827</t>
+    <t xml:space="preserve">4.34010028839111</t>
   </si>
   <si>
     <t xml:space="preserve">4.42926788330078</t>
@@ -260,13 +260,13 @@
     <t xml:space="preserve">4.3491997718811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33646154403687</t>
+    <t xml:space="preserve">4.33646106719971</t>
   </si>
   <si>
     <t xml:space="preserve">4.33100128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32190275192261</t>
+    <t xml:space="preserve">4.32190227508545</t>
   </si>
   <si>
     <t xml:space="preserve">4.46748208999634</t>
@@ -275,16 +275,16 @@
     <t xml:space="preserve">4.45838403701782</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28550815582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83057069778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90336036682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88516306877136</t>
+    <t xml:space="preserve">4.2855076789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83057045936584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90336012840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88516330718994</t>
   </si>
   <si>
     <t xml:space="preserve">3.87606477737427</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">4.00344705581665</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93065667152405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99434757232666</t>
+    <t xml:space="preserve">3.93065714836121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99434781074524</t>
   </si>
   <si>
     <t xml:space="preserve">4.08533525466919</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">3.96705174446106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86696553230286</t>
+    <t xml:space="preserve">3.8669650554657</t>
   </si>
   <si>
     <t xml:space="preserve">3.84876799583435</t>
@@ -314,25 +314,25 @@
     <t xml:space="preserve">3.8578667640686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81237316131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80327486991882</t>
+    <t xml:space="preserve">3.8123733997345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80327463150024</t>
   </si>
   <si>
     <t xml:space="preserve">3.77597784996033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97615051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94885492324829</t>
+    <t xml:space="preserve">3.97615075111389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94885468482971</t>
   </si>
   <si>
     <t xml:space="preserve">4.13992786407471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16722440719604</t>
+    <t xml:space="preserve">4.1672248840332</t>
   </si>
   <si>
     <t xml:space="preserve">4.33528327941895</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">4.21485900878906</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31675624847412</t>
+    <t xml:space="preserve">4.31675672531128</t>
   </si>
   <si>
     <t xml:space="preserve">4.42791795730591</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">4.30749273300171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27970218658447</t>
+    <t xml:space="preserve">4.27970266342163</t>
   </si>
   <si>
     <t xml:space="preserve">4.3908634185791</t>
@@ -368,37 +368,37 @@
     <t xml:space="preserve">4.40012741088867</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35380983352661</t>
+    <t xml:space="preserve">4.35380935668945</t>
   </si>
   <si>
     <t xml:space="preserve">4.08517122268677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93695592880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00179958343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97400975227356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03885364532471</t>
+    <t xml:space="preserve">3.93695569038391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00180006027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97400951385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03885316848755</t>
   </si>
   <si>
     <t xml:space="preserve">3.94621968269348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95548272132874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23338603973389</t>
+    <t xml:space="preserve">3.95548295974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23338651657104</t>
   </si>
   <si>
     <t xml:space="preserve">4.22412204742432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24264907836914</t>
+    <t xml:space="preserve">4.24265003204346</t>
   </si>
   <si>
     <t xml:space="preserve">4.11296129226685</t>
@@ -407,43 +407,43 @@
     <t xml:space="preserve">4.26117610931396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91842865943909</t>
+    <t xml:space="preserve">3.91842913627625</t>
   </si>
   <si>
     <t xml:space="preserve">3.89990234375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89063835144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07590770721436</t>
+    <t xml:space="preserve">3.89063882827759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0759072303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.06664371490479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79800486564636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73316097259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86284852027893</t>
+    <t xml:space="preserve">3.79800462722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73316073417664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86284875869751</t>
   </si>
   <si>
     <t xml:space="preserve">3.71463394165039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70537042617798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77021431922913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3904139995575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44599437713623</t>
+    <t xml:space="preserve">3.7053701877594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77021455764771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39041376113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44599461555481</t>
   </si>
   <si>
     <t xml:space="preserve">3.58494591712952</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">3.52010178565979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37188696861267</t>
+    <t xml:space="preserve">3.37188720703125</t>
   </si>
   <si>
     <t xml:space="preserve">3.46452164649963</t>
@@ -473,10 +473,10 @@
     <t xml:space="preserve">3.45525789260864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34409642219543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07545733451843</t>
+    <t xml:space="preserve">3.34409666061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07545757293701</t>
   </si>
   <si>
     <t xml:space="preserve">3.14956521987915</t>
@@ -485,10 +485,10 @@
     <t xml:space="preserve">3.29777956008911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31630659103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23293566703796</t>
+    <t xml:space="preserve">3.31630635261536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23293590545654</t>
   </si>
   <si>
     <t xml:space="preserve">3.24219918251038</t>
@@ -497,19 +497,19 @@
     <t xml:space="preserve">3.02914023399353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20514559745789</t>
+    <t xml:space="preserve">3.20514535903931</t>
   </si>
   <si>
     <t xml:space="preserve">3.25146269798279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10324764251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1588282585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9179790019989</t>
+    <t xml:space="preserve">3.10324740409851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15882802009583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91797924041748</t>
   </si>
   <si>
     <t xml:space="preserve">2.7419741153717</t>
@@ -518,13 +518,13 @@
     <t xml:space="preserve">2.77902770042419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87166213989258</t>
+    <t xml:space="preserve">2.871661901474</t>
   </si>
   <si>
     <t xml:space="preserve">2.96429634094238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85313510894775</t>
+    <t xml:space="preserve">2.85313487052917</t>
   </si>
   <si>
     <t xml:space="preserve">2.83460831642151</t>
@@ -533,22 +533,22 @@
     <t xml:space="preserve">2.84387183189392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72344756126404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76050090789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76976442337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63081312179565</t>
+    <t xml:space="preserve">2.72344732284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76050114631653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76976466178894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63081288337708</t>
   </si>
   <si>
     <t xml:space="preserve">2.67713022232056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38070034980774</t>
+    <t xml:space="preserve">2.38070058822632</t>
   </si>
   <si>
     <t xml:space="preserve">2.36217379570007</t>
@@ -560,13 +560,13 @@
     <t xml:space="preserve">2.31585669517517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35291051864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26953935623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2324857711792</t>
+    <t xml:space="preserve">2.35291028022766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26953911781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23248553276062</t>
   </si>
   <si>
     <t xml:space="preserve">2.28806662559509</t>
@@ -578,28 +578,28 @@
     <t xml:space="preserve">2.13058805465698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22322225570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24174928665161</t>
+    <t xml:space="preserve">2.22322273254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24174904823303</t>
   </si>
   <si>
     <t xml:space="preserve">2.11206102371216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17690491676331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03795385360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99163675308228</t>
+    <t xml:space="preserve">2.17690467834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0379536151886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9916365146637</t>
   </si>
   <si>
     <t xml:space="preserve">1.88047552108765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94531917572021</t>
+    <t xml:space="preserve">1.94531941413879</t>
   </si>
   <si>
     <t xml:space="preserve">1.92679250240326</t>
@@ -608,76 +608,76 @@
     <t xml:space="preserve">2.16764163970947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13985109329224</t>
+    <t xml:space="preserve">2.13985133171082</t>
   </si>
   <si>
     <t xml:space="preserve">2.21395897865295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40849089622498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48259806632996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4270179271698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38996410369873</t>
+    <t xml:space="preserve">2.4084906578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48259782791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42701768875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38996362686157</t>
   </si>
   <si>
     <t xml:space="preserve">2.46583580970764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50406551361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65698575973511</t>
+    <t xml:space="preserve">2.504065990448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65698552131653</t>
   </si>
   <si>
     <t xml:space="preserve">2.71433067321777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5422956943512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58052611351013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52318096160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42760586738586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38937592506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48495078086853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61875605583191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56141090393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63787055015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73344564437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69521594047546</t>
+    <t xml:space="preserve">2.54229593276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58052587509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52318072319031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42760610580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38937568664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48495101928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61875581741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56141066551208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63787078857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73344540596008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69521570205688</t>
   </si>
   <si>
     <t xml:space="preserve">2.75256109237671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8099057674408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82902097702026</t>
+    <t xml:space="preserve">2.80990600585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82902073860168</t>
   </si>
   <si>
     <t xml:space="preserve">2.84813594818115</t>
@@ -686,13 +686,13 @@
     <t xml:space="preserve">3.05840086936951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86725091934204</t>
+    <t xml:space="preserve">2.86725068092346</t>
   </si>
   <si>
     <t xml:space="preserve">2.7716760635376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67610096931458</t>
+    <t xml:space="preserve">2.67610049247742</t>
   </si>
   <si>
     <t xml:space="preserve">2.59964084625244</t>
@@ -701,85 +701,85 @@
     <t xml:space="preserve">2.44672060012817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37026071548462</t>
+    <t xml:space="preserve">2.3702609539032</t>
   </si>
   <si>
     <t xml:space="preserve">3.09663105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34512615203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45981621742249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74654126167297</t>
+    <t xml:space="preserve">3.34512591362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45981597900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74654102325439</t>
   </si>
   <si>
     <t xml:space="preserve">3.76565623283386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01415109634399</t>
+    <t xml:space="preserve">4.01415157318115</t>
   </si>
   <si>
     <t xml:space="preserve">4.1097264289856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97592115402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88034582138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82300138473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4407012462616</t>
+    <t xml:space="preserve">3.97592091560364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88034629821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82300114631653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44070100784302</t>
   </si>
   <si>
     <t xml:space="preserve">3.40247082710266</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36424088478088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68919610977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72742629051208</t>
+    <t xml:space="preserve">3.36424112319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68919563293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72742605209351</t>
   </si>
   <si>
     <t xml:space="preserve">3.7083113193512</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57450604438782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55539131164551</t>
+    <t xml:space="preserve">3.5745062828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55539107322693</t>
   </si>
   <si>
     <t xml:space="preserve">3.51716113090515</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63185119628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53627634048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61273622512817</t>
+    <t xml:space="preserve">3.63185095787048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53627610206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61273598670959</t>
   </si>
   <si>
     <t xml:space="preserve">3.65096616744995</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24955129623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32601094245911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42158603668213</t>
+    <t xml:space="preserve">3.24955105781555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32601118087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42158555984497</t>
   </si>
   <si>
     <t xml:space="preserve">3.30689597129822</t>
@@ -791,10 +791,10 @@
     <t xml:space="preserve">3.59362101554871</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47893118858337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49804592132568</t>
+    <t xml:space="preserve">3.47893095016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49804639816284</t>
   </si>
   <si>
     <t xml:space="preserve">3.28778123855591</t>
@@ -806,76 +806,76 @@
     <t xml:space="preserve">3.80388641357422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93769073486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03326559066772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18618679046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30087614059448</t>
+    <t xml:space="preserve">3.93769121170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03326606750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18618726730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3008770942688</t>
   </si>
   <si>
     <t xml:space="preserve">4.5302562713623</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51114082336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58760166168213</t>
+    <t xml:space="preserve">4.51114130020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58760213851929</t>
   </si>
   <si>
     <t xml:space="preserve">4.49202632904053</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43468141555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62583208084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74052143096924</t>
+    <t xml:space="preserve">4.43468189239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62583160400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7405219078064</t>
   </si>
   <si>
     <t xml:space="preserve">4.75963687896729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70229053497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68317651748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77875185012817</t>
+    <t xml:space="preserve">4.70229148864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68317699432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77875137329102</t>
   </si>
   <si>
     <t xml:space="preserve">4.56848669052124</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66406154632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72140693664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8743257522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96990156173706</t>
+    <t xml:space="preserve">4.66406202316284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72140741348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87432670593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96990203857422</t>
   </si>
   <si>
     <t xml:space="preserve">4.92211437225342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11326456069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16105222702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20883941650391</t>
+    <t xml:space="preserve">5.1132640838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16105175018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20883893966675</t>
   </si>
   <si>
     <t xml:space="preserve">5.25662660598755</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">5.30441427230835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44777584075928</t>
+    <t xml:space="preserve">5.44777631759644</t>
   </si>
   <si>
     <t xml:space="preserve">5.63892650604248</t>
@@ -893,31 +893,31 @@
     <t xml:space="preserve">5.59113931655884</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81332635879517</t>
+    <t xml:space="preserve">5.81332683563232</t>
   </si>
   <si>
     <t xml:space="preserve">5.71643829345703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42577123641968</t>
+    <t xml:space="preserve">5.42577171325684</t>
   </si>
   <si>
     <t xml:space="preserve">5.1351056098938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84443855285645</t>
+    <t xml:space="preserve">4.8444390296936</t>
   </si>
   <si>
     <t xml:space="preserve">4.8250617980957</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80568313598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59252834320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55377292633057</t>
+    <t xml:space="preserve">4.80568361282349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59252786636353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55377244949341</t>
   </si>
   <si>
     <t xml:space="preserve">4.76692771911621</t>
@@ -926,31 +926,31 @@
     <t xml:space="preserve">5.03821659088135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98977184295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08666086196899</t>
+    <t xml:space="preserve">4.9897723197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08666038513184</t>
   </si>
   <si>
     <t xml:space="preserve">5.18354988098145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94132709503174</t>
+    <t xml:space="preserve">4.9413275718689</t>
   </si>
   <si>
     <t xml:space="preserve">5.23199415206909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74755001068115</t>
+    <t xml:space="preserve">4.74755048751831</t>
   </si>
   <si>
     <t xml:space="preserve">5.28043842315674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89288282394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6312837600708</t>
+    <t xml:space="preserve">4.89288330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63128423690796</t>
   </si>
   <si>
     <t xml:space="preserve">4.53439474105835</t>
@@ -968,13 +968,13 @@
     <t xml:space="preserve">4.70879459381104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91021585464478</t>
+    <t xml:space="preserve">5.91021537780762</t>
   </si>
   <si>
     <t xml:space="preserve">5.61954927444458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32888269424438</t>
+    <t xml:space="preserve">5.32888317108154</t>
   </si>
   <si>
     <t xml:space="preserve">5.37732696533203</t>
@@ -983,7 +983,7 @@
     <t xml:space="preserve">5.57110500335693</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47421598434448</t>
+    <t xml:space="preserve">5.47421550750732</t>
   </si>
   <si>
     <t xml:space="preserve">5.66799402236938</t>
@@ -998,10 +998,10 @@
     <t xml:space="preserve">6.44310331344604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68532562255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5884370803833</t>
+    <t xml:space="preserve">6.68532609939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58843755722046</t>
   </si>
   <si>
     <t xml:space="preserve">6.63688135147095</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">6.24932622909546</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34621477127075</t>
+    <t xml:space="preserve">6.34621524810791</t>
   </si>
   <si>
     <t xml:space="preserve">6.53999280929565</t>
@@ -1022,10 +1022,10 @@
     <t xml:space="preserve">8.71999073028564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99332523345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09021472930908</t>
+    <t xml:space="preserve">7.99332332611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09021377563477</t>
   </si>
   <si>
     <t xml:space="preserve">8.04176807403564</t>
@@ -1037,22 +1037,22 @@
     <t xml:space="preserve">7.84799098968506</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89643621444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38087749481201</t>
+    <t xml:space="preserve">7.89643430709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38087844848633</t>
   </si>
   <si>
     <t xml:space="preserve">10.2702112197876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88265419006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.173321723938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97954368591309</t>
+    <t xml:space="preserve">9.88265514373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1733207702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9795446395874</t>
   </si>
   <si>
     <t xml:space="preserve">10.0764331817627</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">11.2390985488892</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6266527175903</t>
+    <t xml:space="preserve">11.6266536712646</t>
   </si>
   <si>
     <t xml:space="preserve">13.0799856185913</t>
@@ -1070,10 +1070,10 @@
     <t xml:space="preserve">13.2737627029419</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9830951690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4364290237427</t>
+    <t xml:space="preserve">12.9830961227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.436427116394</t>
   </si>
   <si>
     <t xml:space="preserve">14.3395395278931</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">16.1669788360596</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1930646896362</t>
+    <t xml:space="preserve">15.1930656433105</t>
   </si>
   <si>
     <t xml:space="preserve">15.0956735610962</t>
@@ -1094,13 +1094,13 @@
     <t xml:space="preserve">14.9008903503418</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6348028182983</t>
+    <t xml:space="preserve">13.634801864624</t>
   </si>
   <si>
     <t xml:space="preserve">12.0765390396118</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4661045074463</t>
+    <t xml:space="preserve">12.4661054611206</t>
   </si>
   <si>
     <t xml:space="preserve">13.4400196075439</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">14.0243673324585</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2191514968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8035001754761</t>
+    <t xml:space="preserve">14.2191505432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8034982681274</t>
   </si>
   <si>
     <t xml:space="preserve">14.4139337539673</t>
@@ -1124,28 +1124,28 @@
     <t xml:space="preserve">14.6087169647217</t>
   </si>
   <si>
-    <t xml:space="preserve">14.706109046936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5113258361816</t>
+    <t xml:space="preserve">14.7061080932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5113248825073</t>
   </si>
   <si>
     <t xml:space="preserve">13.3426284790039</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1217584609985</t>
+    <t xml:space="preserve">14.1217594146729</t>
   </si>
   <si>
     <t xml:space="preserve">14.3165426254272</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8295841217041</t>
+    <t xml:space="preserve">13.8295850753784</t>
   </si>
   <si>
     <t xml:space="preserve">13.537410736084</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2452363967896</t>
+    <t xml:space="preserve">13.2452373504639</t>
   </si>
   <si>
     <t xml:space="preserve">12.8556699752808</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">12.3687133789062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7582778930664</t>
+    <t xml:space="preserve">12.758279800415</t>
   </si>
   <si>
     <t xml:space="preserve">12.5634965896606</t>
@@ -1166,13 +1166,13 @@
     <t xml:space="preserve">11.6869735717773</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1026239395142</t>
+    <t xml:space="preserve">11.1026248931885</t>
   </si>
   <si>
     <t xml:space="preserve">9.93392658233643</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7130584716797</t>
+    <t xml:space="preserve">10.713059425354</t>
   </si>
   <si>
     <t xml:space="preserve">11.2000169754028</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">11.2974081039429</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3947992324829</t>
+    <t xml:space="preserve">11.3948001861572</t>
   </si>
   <si>
     <t xml:space="preserve">11.589581489563</t>
@@ -1205,7 +1205,7 @@
     <t xml:space="preserve">11.4921913146973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8104496002197</t>
+    <t xml:space="preserve">10.810450553894</t>
   </si>
   <si>
     <t xml:space="preserve">10.4208850860596</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">10.3234939575195</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1287097930908</t>
+    <t xml:space="preserve">10.1287107467651</t>
   </si>
   <si>
     <t xml:space="preserve">10.0313186645508</t>
@@ -1226,19 +1226,19 @@
     <t xml:space="preserve">9.73914337158203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54436206817627</t>
+    <t xml:space="preserve">9.54436111450195</t>
   </si>
   <si>
     <t xml:space="preserve">9.83653545379639</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34957981109619</t>
+    <t xml:space="preserve">9.34957885742188</t>
   </si>
   <si>
     <t xml:space="preserve">9.49566555023193</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2713232040405</t>
+    <t xml:space="preserve">12.2713222503662</t>
   </si>
   <si>
     <t xml:space="preserve">12.9530611038208</t>
@@ -1247,22 +1247,22 @@
     <t xml:space="preserve">15.6800222396851</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7321939468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1704549789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3652381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0730628967285</t>
+    <t xml:space="preserve">13.7321929931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1704559326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3652391433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0730638504028</t>
   </si>
   <si>
     <t xml:space="preserve">15.1443700790405</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5364561080933</t>
+    <t xml:space="preserve">15.5364570617676</t>
   </si>
   <si>
     <t xml:space="preserve">15.585467338562</t>
@@ -1274,40 +1274,40 @@
     <t xml:space="preserve">15.193380355835</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4874458312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4384355545044</t>
+    <t xml:space="preserve">15.4874467849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4384346008301</t>
   </si>
   <si>
     <t xml:space="preserve">15.2423915863037</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3894233703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9973373413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8993148803711</t>
+    <t xml:space="preserve">15.3894243240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9973363876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8993139266968</t>
   </si>
   <si>
     <t xml:space="preserve">15.0463485717773</t>
   </si>
   <si>
-    <t xml:space="preserve">14.654260635376</t>
+    <t xml:space="preserve">14.6542596817017</t>
   </si>
   <si>
     <t xml:space="preserve">13.9190969467163</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1641502380371</t>
+    <t xml:space="preserve">14.1641511917114</t>
   </si>
   <si>
     <t xml:space="preserve">13.7230529785156</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8210754394531</t>
+    <t xml:space="preserve">13.8210744857788</t>
   </si>
   <si>
     <t xml:space="preserve">14.3601942062378</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">13.6250314712524</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8700857162476</t>
+    <t xml:space="preserve">13.8700866699219</t>
   </si>
   <si>
     <t xml:space="preserve">13.6740427017212</t>
@@ -1328,16 +1328,16 @@
     <t xml:space="preserve">14.0171184539795</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1839323043823</t>
+    <t xml:space="preserve">13.1839332580566</t>
   </si>
   <si>
     <t xml:space="preserve">13.5270099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9483251571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4092054367065</t>
+    <t xml:space="preserve">14.9483261108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4092063903809</t>
   </si>
   <si>
     <t xml:space="preserve">14.8503036499023</t>
@@ -1349,25 +1349,25 @@
     <t xml:space="preserve">14.6052494049072</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7032709121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5562381744385</t>
+    <t xml:space="preserve">14.7032718658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5562391281128</t>
   </si>
   <si>
     <t xml:space="preserve">14.507227897644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0661306381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3309659957886</t>
+    <t xml:space="preserve">14.0661296844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3309669494629</t>
   </si>
   <si>
     <t xml:space="preserve">13.4779987335205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2819557189941</t>
+    <t xml:space="preserve">13.2819547653198</t>
   </si>
   <si>
     <t xml:space="preserve">12.8898677825928</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">11.7626171112061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3215198516846</t>
+    <t xml:space="preserve">11.3215188980103</t>
   </si>
   <si>
     <t xml:space="preserve">12.3017377853394</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">13.0859127044678</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4289875030518</t>
+    <t xml:space="preserve">13.4289884567261</t>
   </si>
   <si>
     <t xml:space="preserve">15.8305215835571</t>
@@ -1409,13 +1409,13 @@
     <t xml:space="preserve">15.8795328140259</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9775552749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3696441650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6834897994995</t>
+    <t xml:space="preserve">15.9775533676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3696422576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6834888458252</t>
   </si>
   <si>
     <t xml:space="preserve">15.7815113067627</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">16.2226085662842</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0265655517578</t>
+    <t xml:space="preserve">16.0265674591064</t>
   </si>
   <si>
     <t xml:space="preserve">16.0755767822266</t>
@@ -1445,13 +1445,13 @@
     <t xml:space="preserve">18.7221660614014</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0162296295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7023830413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.604362487793</t>
+    <t xml:space="preserve">19.0162315368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7023849487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6043605804443</t>
   </si>
   <si>
     <t xml:space="preserve">19.8004055023193</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">23.9173202514648</t>
   </si>
   <si>
-    <t xml:space="preserve">22.545015335083</t>
+    <t xml:space="preserve">22.5450172424316</t>
   </si>
   <si>
     <t xml:space="preserve">23.5252342224121</t>
@@ -1484,19 +1484,19 @@
     <t xml:space="preserve">20.4865570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6826038360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3687534332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6430397033691</t>
+    <t xml:space="preserve">20.6826019287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3687553405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6430377960205</t>
   </si>
   <si>
     <t xml:space="preserve">24.9955615997314</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2896251678467</t>
+    <t xml:space="preserve">25.2896270751953</t>
   </si>
   <si>
     <t xml:space="preserve">24.6034755706787</t>
@@ -1505,13 +1505,13 @@
     <t xml:space="preserve">24.8975391387939</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5054531097412</t>
+    <t xml:space="preserve">24.5054512023926</t>
   </si>
   <si>
     <t xml:space="preserve">24.0153427124023</t>
   </si>
   <si>
-    <t xml:space="preserve">23.623254776001</t>
+    <t xml:space="preserve">23.6232566833496</t>
   </si>
   <si>
     <t xml:space="preserve">22.8390789031982</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">23.3291893005371</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9371032714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7212791442871</t>
+    <t xml:space="preserve">22.937105178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7212772369385</t>
   </si>
   <si>
     <t xml:space="preserve">24.1133651733398</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">23.0351257324219</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1331462860107</t>
+    <t xml:space="preserve">23.1331481933594</t>
   </si>
   <si>
     <t xml:space="preserve">24.2113876342773</t>
@@ -1553,16 +1553,16 @@
     <t xml:space="preserve">21.9568843841553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1529293060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7711753845215</t>
+    <t xml:space="preserve">22.1529273986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7711772918701</t>
   </si>
   <si>
     <t xml:space="preserve">18.3300800323486</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6439247131348</t>
+    <t xml:space="preserve">17.6439266204834</t>
   </si>
   <si>
     <t xml:space="preserve">18.5261211395264</t>
@@ -1571,16 +1571,16 @@
     <t xml:space="preserve">19.9964485168457</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5845794677734</t>
+    <t xml:space="preserve">20.5845775604248</t>
   </si>
   <si>
     <t xml:space="preserve">20.1924934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8984279632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3885345458984</t>
+    <t xml:space="preserve">19.8984260559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3885364532471</t>
   </si>
   <si>
     <t xml:space="preserve">19.4049549102783</t>
@@ -1595,10 +1595,10 @@
     <t xml:space="preserve">19.5527095794678</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7989654541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.601957321167</t>
+    <t xml:space="preserve">19.7989635467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6019592285156</t>
   </si>
   <si>
     <t xml:space="preserve">18.9616947174072</t>
@@ -1628,13 +1628,13 @@
     <t xml:space="preserve">20.4884796142578</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5869808197021</t>
+    <t xml:space="preserve">20.5869827270508</t>
   </si>
   <si>
     <t xml:space="preserve">19.9959678649902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4542064666748</t>
+    <t xml:space="preserve">19.4542045593262</t>
   </si>
   <si>
     <t xml:space="preserve">19.5034561157227</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">19.207950592041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0259208679199</t>
+    <t xml:space="preserve">18.0259227752686</t>
   </si>
   <si>
     <t xml:space="preserve">18.075174331665</t>
@@ -1670,19 +1670,19 @@
     <t xml:space="preserve">17.9274196624756</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9766712188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.434907913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1736755371094</t>
+    <t xml:space="preserve">17.9766693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4349098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.173677444458</t>
   </si>
   <si>
     <t xml:space="preserve">18.4199314117432</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7839889526367</t>
+    <t xml:space="preserve">20.7839870452881</t>
   </si>
   <si>
     <t xml:space="preserve">20.3899784088135</t>
@@ -1691,10 +1691,10 @@
     <t xml:space="preserve">19.7004623413086</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9124431610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1094455718994</t>
+    <t xml:space="preserve">18.9124450683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.109447479248</t>
   </si>
   <si>
     <t xml:space="preserve">18.8631916046143</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">18.5184326171875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7154388427734</t>
+    <t xml:space="preserve">18.7154369354248</t>
   </si>
   <si>
     <t xml:space="preserve">18.2229270935059</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">17.7796649932861</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5676860809326</t>
+    <t xml:space="preserve">18.567684173584</t>
   </si>
   <si>
     <t xml:space="preserve">17.7304153442383</t>
@@ -1724,16 +1724,16 @@
     <t xml:space="preserve">18.2721767425537</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6811637878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8781700134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1244258880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6319141387939</t>
+    <t xml:space="preserve">17.6811656951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8781681060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1244239807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6319122314453</t>
   </si>
   <si>
     <t xml:space="preserve">17.4841594696045</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">17.3856582641602</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5334091186523</t>
+    <t xml:space="preserve">17.533411026001</t>
   </si>
   <si>
     <t xml:space="preserve">17.1886520385742</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">16.4991359710693</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8931465148926</t>
+    <t xml:space="preserve">16.8931446075439</t>
   </si>
   <si>
     <t xml:space="preserve">16.4498863220215</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">16.6468906402588</t>
   </si>
   <si>
-    <t xml:space="preserve">16.794641494751</t>
+    <t xml:space="preserve">16.7946434020996</t>
   </si>
   <si>
     <t xml:space="preserve">16.7453918457031</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">14.6275930404663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9723501205444</t>
+    <t xml:space="preserve">14.9723510742188</t>
   </si>
   <si>
     <t xml:space="preserve">14.7260942459106</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">15.1201047897339</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3663597106934</t>
+    <t xml:space="preserve">15.3663606643677</t>
   </si>
   <si>
     <t xml:space="preserve">15.464861869812</t>
@@ -1805,16 +1805,16 @@
     <t xml:space="preserve">14.7753458023071</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4798393249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2828340530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5783414840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0858306884766</t>
+    <t xml:space="preserve">14.4798383712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2828350067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5783424377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0858297348022</t>
   </si>
   <si>
     <t xml:space="preserve">14.2335834503174</t>
@@ -57123,7 +57123,7 @@
     </row>
     <row r="2103">
       <c r="A2103" s="1" t="n">
-        <v>45954.6494560185</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2103" t="n">
         <v>1750</v>
@@ -57144,6 +57144,32 @@
         <v>668</v>
       </c>
       <c r="H2103" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="1" t="n">
+        <v>45957.6388541667</v>
+      </c>
+      <c r="B2104" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C2104" t="n">
+        <v>15.1000003814697</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E2104" t="n">
+        <v>14.6999998092651</v>
+      </c>
+      <c r="F2104" t="n">
+        <v>14.6999998092651</v>
+      </c>
+      <c r="G2104" t="s">
+        <v>701</v>
+      </c>
+      <c r="H2104" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CULT.MI.xlsx
+++ b/data/CULT.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">CULT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57666778564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59486484527588</t>
+    <t xml:space="preserve">4.57666826248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59486532211304</t>
   </si>
   <si>
     <t xml:space="preserve">4.60851287841797</t>
@@ -65,28 +65,28 @@
     <t xml:space="preserve">4.51297616958618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46020317077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29824590682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21271753311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18178272247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23091554641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36375665664673</t>
+    <t xml:space="preserve">4.46020364761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29824638366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21271800994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18178224563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23091506958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36375713348389</t>
   </si>
   <si>
     <t xml:space="preserve">4.38195466995239</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35101842880249</t>
+    <t xml:space="preserve">4.35101938247681</t>
   </si>
   <si>
     <t xml:space="preserve">4.28914737701416</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">4.24183416366577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22909593582153</t>
+    <t xml:space="preserve">4.22909545898438</t>
   </si>
   <si>
     <t xml:space="preserve">4.10535287857056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09443426132202</t>
+    <t xml:space="preserve">4.09443473815918</t>
   </si>
   <si>
     <t xml:space="preserve">4.10899209976196</t>
@@ -113,43 +113,43 @@
     <t xml:space="preserve">4.04712057113647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0398416519165</t>
+    <t xml:space="preserve">4.03984117507935</t>
   </si>
   <si>
     <t xml:space="preserve">3.96341228485107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07441711425781</t>
+    <t xml:space="preserve">4.07441759109497</t>
   </si>
   <si>
     <t xml:space="preserve">4.3200831413269</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24911308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97978949546814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0689582824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0543999671936</t>
+    <t xml:space="preserve">4.2491135597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97979021072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06895780563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05439949035645</t>
   </si>
   <si>
     <t xml:space="preserve">3.98524951934814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0507607460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07259654998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03802251815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04530143737793</t>
+    <t xml:space="preserve">4.05076026916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07259702682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03802156448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04530096054077</t>
   </si>
   <si>
     <t xml:space="preserve">4.03074312210083</t>
@@ -158,19 +158,19 @@
     <t xml:space="preserve">4.01254510879517</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04894065856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05985832214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07623672485352</t>
+    <t xml:space="preserve">4.04894018173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05985879898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07623720169067</t>
   </si>
   <si>
     <t xml:space="preserve">3.91245937347412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99070858955383</t>
+    <t xml:space="preserve">3.99070906639099</t>
   </si>
   <si>
     <t xml:space="preserve">4.01072597503662</t>
@@ -179,22 +179,22 @@
     <t xml:space="preserve">3.92155814170837</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00162649154663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05803871154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21635770797729</t>
+    <t xml:space="preserve">4.00162744522095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05803918838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21635675430298</t>
   </si>
   <si>
     <t xml:space="preserve">4.2218165397644</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18542098999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16176462173462</t>
+    <t xml:space="preserve">4.18542146682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16176414489746</t>
   </si>
   <si>
     <t xml:space="preserve">4.35465812683105</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">4.26731061935425</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39287328720093</t>
+    <t xml:space="preserve">4.39287233352661</t>
   </si>
   <si>
     <t xml:space="preserve">4.36739683151245</t>
@@ -215,46 +215,46 @@
     <t xml:space="preserve">4.17814254760742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27459001541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3182635307312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35647821426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26549100875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26366996765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27640867233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14902687072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35829734802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35283851623535</t>
+    <t xml:space="preserve">4.27458906173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31826305389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35647869110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26549053192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26367044448853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27640914916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14902639389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35829782485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35283899307251</t>
   </si>
   <si>
     <t xml:space="preserve">4.29460620880127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20361995697021</t>
+    <t xml:space="preserve">4.2036190032959</t>
   </si>
   <si>
     <t xml:space="preserve">4.24001455307007</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3400993347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42926836013794</t>
+    <t xml:space="preserve">4.34010076522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42926788330078</t>
   </si>
   <si>
     <t xml:space="preserve">4.34919929504395</t>
@@ -263,61 +263,61 @@
     <t xml:space="preserve">4.33646059036255</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3310022354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32190227508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46748352050781</t>
+    <t xml:space="preserve">4.33100128173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32190275192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46748304367065</t>
   </si>
   <si>
     <t xml:space="preserve">4.45838403701782</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28550815582275</t>
+    <t xml:space="preserve">4.2855076789856</t>
   </si>
   <si>
     <t xml:space="preserve">3.83057069778442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90336132049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88516306877136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87606430053711</t>
+    <t xml:space="preserve">3.90336060523987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88516330718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87606501579285</t>
   </si>
   <si>
     <t xml:space="preserve">4.00344705581665</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93065762519836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99434781074524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08533525466919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96705174446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86696553230286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84876799583435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85786628723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81237268447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80327463150024</t>
+    <t xml:space="preserve">3.93065714836121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99434757232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08533573150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9670512676239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86696577072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84876847267151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85786652565002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8123733997345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80327439308167</t>
   </si>
   <si>
     <t xml:space="preserve">3.77597808837891</t>
@@ -326,13 +326,13 @@
     <t xml:space="preserve">3.97615051269531</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94885396957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13992786407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16722440719604</t>
+    <t xml:space="preserve">3.94885420799255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13992738723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16722393035889</t>
   </si>
   <si>
     <t xml:space="preserve">4.3352837562561</t>
@@ -341,43 +341,43 @@
     <t xml:space="preserve">4.21485900878906</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31675624847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42791795730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19633197784424</t>
+    <t xml:space="preserve">4.31675672531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42791748046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19633150100708</t>
   </si>
   <si>
     <t xml:space="preserve">4.16854190826416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29823017120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30749273300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27970218658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39086437225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40012788772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35380983352661</t>
+    <t xml:space="preserve">4.29822969436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30749320983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27970266342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39086389541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40012693405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35381031036377</t>
   </si>
   <si>
     <t xml:space="preserve">4.08517074584961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93695569038391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00179958343506</t>
+    <t xml:space="preserve">3.93695616722107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00180006027222</t>
   </si>
   <si>
     <t xml:space="preserve">3.97400975227356</t>
@@ -386,28 +386,28 @@
     <t xml:space="preserve">4.03885364532471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94621968269348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95548343658447</t>
+    <t xml:space="preserve">3.94622015953064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95548319816589</t>
   </si>
   <si>
     <t xml:space="preserve">4.23338603973389</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22412204742432</t>
+    <t xml:space="preserve">4.22412157058716</t>
   </si>
   <si>
     <t xml:space="preserve">4.24264907836914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11296129226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26117563247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9184296131134</t>
+    <t xml:space="preserve">4.11296081542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26117610931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91842937469482</t>
   </si>
   <si>
     <t xml:space="preserve">3.89990234375</t>
@@ -416,25 +416,25 @@
     <t xml:space="preserve">3.89063882827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0759072303772</t>
+    <t xml:space="preserve">4.07590770721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.06664371490479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7980043888092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73316073417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86284875869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71463394165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70537042617798</t>
+    <t xml:space="preserve">3.79800510406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73316121101379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86284852027893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71463418006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70537066459656</t>
   </si>
   <si>
     <t xml:space="preserve">3.77021455764771</t>
@@ -446,31 +446,31 @@
     <t xml:space="preserve">3.44599461555481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58494591712952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68684363365173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60347294807434</t>
+    <t xml:space="preserve">3.58494567871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68684339523315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60347318649292</t>
   </si>
   <si>
     <t xml:space="preserve">3.52010202407837</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37188744544983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46452116966248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53862857818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52936506271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45525789260864</t>
+    <t xml:space="preserve">3.37188720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46452140808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53862905502319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5293653011322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45525813102722</t>
   </si>
   <si>
     <t xml:space="preserve">3.34409666061401</t>
@@ -479,37 +479,37 @@
     <t xml:space="preserve">3.07545733451843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14956521987915</t>
+    <t xml:space="preserve">3.14956498146057</t>
   </si>
   <si>
     <t xml:space="preserve">3.29777956008911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31630659103394</t>
+    <t xml:space="preserve">3.31630635261536</t>
   </si>
   <si>
     <t xml:space="preserve">3.23293590545654</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24219942092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02914047241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20514535903931</t>
+    <t xml:space="preserve">3.24219870567322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02914023399353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20514512062073</t>
   </si>
   <si>
     <t xml:space="preserve">3.25146222114563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10324788093567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1588282585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9179790019989</t>
+    <t xml:space="preserve">3.10324764251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15882849693298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91797924041748</t>
   </si>
   <si>
     <t xml:space="preserve">2.7419741153717</t>
@@ -518,19 +518,19 @@
     <t xml:space="preserve">2.77902770042419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87166213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96429657936096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85313487052917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83460807800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84387159347534</t>
+    <t xml:space="preserve">2.871661901474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96429634094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85313558578491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83460831642151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84387183189392</t>
   </si>
   <si>
     <t xml:space="preserve">2.72344732284546</t>
@@ -542,103 +542,103 @@
     <t xml:space="preserve">2.76976442337036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63081288337708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67713022232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38070058822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36217379570007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29732966423035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31585645675659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35291004180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26953959465027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23248553276062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28806614875793</t>
+    <t xml:space="preserve">2.63081312179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67712998390198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38070034980774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36217355728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29732942581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31585669517517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35291028022766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26953935623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2324857711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28806638717651</t>
   </si>
   <si>
     <t xml:space="preserve">2.08427095413208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1305878162384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22322225570679</t>
+    <t xml:space="preserve">2.13058805465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22322249412537</t>
   </si>
   <si>
     <t xml:space="preserve">2.24174904823303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11206102371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17690491676331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0379536151886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99163663387299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88047540187836</t>
+    <t xml:space="preserve">2.11206078529358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17690515518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03795385360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9916365146637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88047552108765</t>
   </si>
   <si>
     <t xml:space="preserve">1.94531941413879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92679250240326</t>
+    <t xml:space="preserve">1.92679262161255</t>
   </si>
   <si>
     <t xml:space="preserve">2.16764187812805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13985109329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21395897865295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40849089622498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48259806632996</t>
+    <t xml:space="preserve">2.13985133171082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21395874023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4084906578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48259830474854</t>
   </si>
   <si>
     <t xml:space="preserve">2.42701768875122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38996386528015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46583580970764</t>
+    <t xml:space="preserve">2.38996410369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46583604812622</t>
   </si>
   <si>
     <t xml:space="preserve">2.50406575202942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65698552131653</t>
+    <t xml:space="preserve">2.65698599815369</t>
   </si>
   <si>
     <t xml:space="preserve">2.71433067321777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54229593276978</t>
+    <t xml:space="preserve">2.54229545593262</t>
   </si>
   <si>
     <t xml:space="preserve">2.58052587509155</t>
@@ -647,22 +647,22 @@
     <t xml:space="preserve">2.52318096160889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42760562896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38937568664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48495101928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61875605583191</t>
+    <t xml:space="preserve">2.42760610580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38937592506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48495078086853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61875581741333</t>
   </si>
   <si>
     <t xml:space="preserve">2.56141066551208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63787055015564</t>
+    <t xml:space="preserve">2.6378710269928</t>
   </si>
   <si>
     <t xml:space="preserve">2.73344588279724</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">2.69521570205688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75256133079529</t>
+    <t xml:space="preserve">2.75256085395813</t>
   </si>
   <si>
     <t xml:space="preserve">2.80990600585938</t>
@@ -680,43 +680,43 @@
     <t xml:space="preserve">2.82902097702026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84813594818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05840110778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86725091934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77167630195618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67610049247742</t>
+    <t xml:space="preserve">2.84813570976257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05840086936951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86725068092346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7716760635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67610096931458</t>
   </si>
   <si>
     <t xml:space="preserve">2.59964084625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44672036170959</t>
+    <t xml:space="preserve">2.44672060012817</t>
   </si>
   <si>
     <t xml:space="preserve">2.37026071548462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09663105010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34512639045715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45981621742249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74654126167297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76565647125244</t>
+    <t xml:space="preserve">3.09663081169128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34512615203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45981597900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74654150009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76565623283386</t>
   </si>
   <si>
     <t xml:space="preserve">4.01415109634399</t>
@@ -725,16 +725,16 @@
     <t xml:space="preserve">4.1097264289856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97592091560364</t>
+    <t xml:space="preserve">3.97592115402222</t>
   </si>
   <si>
     <t xml:space="preserve">3.88034605979919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82300114631653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44070076942444</t>
+    <t xml:space="preserve">3.82300090789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4407012462616</t>
   </si>
   <si>
     <t xml:space="preserve">3.40247106552124</t>
@@ -743,19 +743,19 @@
     <t xml:space="preserve">3.36424112319946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68919587135315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72742629051208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70831108093262</t>
+    <t xml:space="preserve">3.68919610977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72742581367493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7083113193512</t>
   </si>
   <si>
     <t xml:space="preserve">3.57450604438782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55539131164551</t>
+    <t xml:space="preserve">3.55539107322693</t>
   </si>
   <si>
     <t xml:space="preserve">3.51716136932373</t>
@@ -767,19 +767,19 @@
     <t xml:space="preserve">3.53627634048462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61273622512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65096592903137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24955129623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32601094245911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42158603668213</t>
+    <t xml:space="preserve">3.61273646354675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65096640586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24955105781555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32601070404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42158579826355</t>
   </si>
   <si>
     <t xml:space="preserve">3.30689597129822</t>
@@ -788,34 +788,34 @@
     <t xml:space="preserve">3.38335633277893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59362125396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47893142700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49804615974426</t>
+    <t xml:space="preserve">3.59362101554871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47893118858337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49804592132568</t>
   </si>
   <si>
     <t xml:space="preserve">3.28778100013733</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67008113861084</t>
+    <t xml:space="preserve">3.67008090019226</t>
   </si>
   <si>
     <t xml:space="preserve">3.80388617515564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93769097328186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03326606750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18618679046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30087661743164</t>
+    <t xml:space="preserve">3.93769121170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03326559066772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18618631362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30087614059448</t>
   </si>
   <si>
     <t xml:space="preserve">4.53025674819946</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">4.58760166168213</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49202585220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43468189239502</t>
+    <t xml:space="preserve">4.49202632904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43468141555786</t>
   </si>
   <si>
     <t xml:space="preserve">4.62583160400391</t>
@@ -839,22 +839,22 @@
     <t xml:space="preserve">4.74052143096924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75963640213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70229148864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68317699432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77875137329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56848669052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66406202316284</t>
+    <t xml:space="preserve">4.75963592529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7022910118103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68317651748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77875185012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56848621368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66406154632568</t>
   </si>
   <si>
     <t xml:space="preserve">4.72140645980835</t>
@@ -863,10 +863,10 @@
     <t xml:space="preserve">4.87432670593262</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96990203857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9221134185791</t>
+    <t xml:space="preserve">4.96990156173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92211389541626</t>
   </si>
   <si>
     <t xml:space="preserve">5.1132640838623</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">5.20883893966675</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25662708282471</t>
+    <t xml:space="preserve">5.25662660598755</t>
   </si>
   <si>
     <t xml:space="preserve">5.30441474914551</t>
@@ -890,22 +890,22 @@
     <t xml:space="preserve">5.63892650604248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59113931655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81332683563232</t>
+    <t xml:space="preserve">5.59113883972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81332635879517</t>
   </si>
   <si>
     <t xml:space="preserve">5.71643781661987</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42577123641968</t>
+    <t xml:space="preserve">5.42577171325684</t>
   </si>
   <si>
     <t xml:space="preserve">5.1351056098938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8444390296936</t>
+    <t xml:space="preserve">4.84443855285645</t>
   </si>
   <si>
     <t xml:space="preserve">4.82506132125854</t>
@@ -917,16 +917,16 @@
     <t xml:space="preserve">4.59252834320068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55377197265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76692819595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03821659088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98977184295654</t>
+    <t xml:space="preserve">4.55377244949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76692771911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03821611404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9897723197937</t>
   </si>
   <si>
     <t xml:space="preserve">5.08666086196899</t>
@@ -938,19 +938,19 @@
     <t xml:space="preserve">4.9413275718689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23199415206909</t>
+    <t xml:space="preserve">5.23199462890625</t>
   </si>
   <si>
     <t xml:space="preserve">4.74755048751831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28043842315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89288282394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63128423690796</t>
+    <t xml:space="preserve">5.28043794631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89288330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6312837600708</t>
   </si>
   <si>
     <t xml:space="preserve">4.53439474105835</t>
@@ -959,10 +959,10 @@
     <t xml:space="preserve">4.67003917694092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78630590438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72817277908325</t>
+    <t xml:space="preserve">4.78630542755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72817182540894</t>
   </si>
   <si>
     <t xml:space="preserve">4.70879459381104</t>
@@ -980,10 +980,10 @@
     <t xml:space="preserve">5.37732744216919</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57110500335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47421598434448</t>
+    <t xml:space="preserve">5.57110452651978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47421646118164</t>
   </si>
   <si>
     <t xml:space="preserve">5.66799354553223</t>
@@ -998,19 +998,19 @@
     <t xml:space="preserve">6.4431037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68532609939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58843755722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63688135147095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24932670593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34621477127075</t>
+    <t xml:space="preserve">6.68532562255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5884370803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63688087463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24932622909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34621524810791</t>
   </si>
   <si>
     <t xml:space="preserve">6.53999280929565</t>
@@ -1025,22 +1025,22 @@
     <t xml:space="preserve">7.99332427978516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09021377563477</t>
+    <t xml:space="preserve">8.09021282196045</t>
   </si>
   <si>
     <t xml:space="preserve">8.04176807403564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94487953186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84799146652222</t>
+    <t xml:space="preserve">7.94488000869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84799098968506</t>
   </si>
   <si>
     <t xml:space="preserve">7.89643526077271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38087940216064</t>
+    <t xml:space="preserve">8.38087844848633</t>
   </si>
   <si>
     <t xml:space="preserve">10.2702112197876</t>
@@ -1052,22 +1052,22 @@
     <t xml:space="preserve">10.173321723938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97954368591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0764331817627</t>
+    <t xml:space="preserve">9.9795446395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0764322280884</t>
   </si>
   <si>
     <t xml:space="preserve">11.2390985488892</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6266536712646</t>
+    <t xml:space="preserve">11.6266527175903</t>
   </si>
   <si>
     <t xml:space="preserve">13.0799856185913</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2737627029419</t>
+    <t xml:space="preserve">13.2737617492676</t>
   </si>
   <si>
     <t xml:space="preserve">12.9830961227417</t>
@@ -1079,13 +1079,13 @@
     <t xml:space="preserve">14.3395395278931</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0177612304688</t>
+    <t xml:space="preserve">15.0177602767944</t>
   </si>
   <si>
     <t xml:space="preserve">16.1669788360596</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1930656433105</t>
+    <t xml:space="preserve">15.1930646896362</t>
   </si>
   <si>
     <t xml:space="preserve">15.0956735610962</t>
@@ -1094,19 +1094,19 @@
     <t xml:space="preserve">14.9008913040161</t>
   </si>
   <si>
-    <t xml:space="preserve">13.634801864624</t>
+    <t xml:space="preserve">13.6348028182983</t>
   </si>
   <si>
     <t xml:space="preserve">12.0765390396118</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4661054611206</t>
+    <t xml:space="preserve">12.4661045074463</t>
   </si>
   <si>
     <t xml:space="preserve">13.4400196075439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9269762039185</t>
+    <t xml:space="preserve">13.9269771575928</t>
   </si>
   <si>
     <t xml:space="preserve">14.0243673324585</t>
@@ -1124,13 +1124,13 @@
     <t xml:space="preserve">14.6087160110474</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7061080932617</t>
+    <t xml:space="preserve">14.706109046936</t>
   </si>
   <si>
     <t xml:space="preserve">14.5113248825073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3426275253296</t>
+    <t xml:space="preserve">13.3426284790039</t>
   </si>
   <si>
     <t xml:space="preserve">14.1217594146729</t>
@@ -1139,10 +1139,10 @@
     <t xml:space="preserve">14.3165416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8295850753784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.537410736084</t>
+    <t xml:space="preserve">13.8295841217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5374097824097</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452363967896</t>
@@ -1154,25 +1154,25 @@
     <t xml:space="preserve">12.3687133789062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.758279800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5634956359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1739311218262</t>
+    <t xml:space="preserve">12.7582788467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5634965896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1739301681519</t>
   </si>
   <si>
     <t xml:space="preserve">11.6869735717773</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1026248931885</t>
+    <t xml:space="preserve">11.1026239395142</t>
   </si>
   <si>
     <t xml:space="preserve">9.93392658233643</t>
   </si>
   <si>
-    <t xml:space="preserve">10.713059425354</t>
+    <t xml:space="preserve">10.7130584716797</t>
   </si>
   <si>
     <t xml:space="preserve">11.2000160217285</t>
@@ -1190,16 +1190,16 @@
     <t xml:space="preserve">11.2974081039429</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3947992324829</t>
+    <t xml:space="preserve">11.3947982788086</t>
   </si>
   <si>
     <t xml:space="preserve">11.589581489563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0052337646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7843656539917</t>
+    <t xml:space="preserve">11.0052328109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7843647003174</t>
   </si>
   <si>
     <t xml:space="preserve">11.4921903610229</t>
@@ -1208,10 +1208,10 @@
     <t xml:space="preserve">10.810450553894</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4208850860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2261018753052</t>
+    <t xml:space="preserve">10.4208841323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2261009216309</t>
   </si>
   <si>
     <t xml:space="preserve">10.3234939575195</t>
@@ -1220,16 +1220,16 @@
     <t xml:space="preserve">10.1287097930908</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0313186645508</t>
+    <t xml:space="preserve">10.0313196182251</t>
   </si>
   <si>
     <t xml:space="preserve">9.73914432525635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54436111450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83653545379639</t>
+    <t xml:space="preserve">9.54436206817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8365364074707</t>
   </si>
   <si>
     <t xml:space="preserve">9.34957885742188</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">12.9530620574951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6800222396851</t>
+    <t xml:space="preserve">15.6800231933594</t>
   </si>
   <si>
     <t xml:space="preserve">13.7321939468384</t>
@@ -1253,13 +1253,13 @@
     <t xml:space="preserve">14.1704559326172</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3652391433716</t>
+    <t xml:space="preserve">14.3652372360229</t>
   </si>
   <si>
     <t xml:space="preserve">14.0730628967285</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1443700790405</t>
+    <t xml:space="preserve">15.1443691253662</t>
   </si>
   <si>
     <t xml:space="preserve">15.5364561080933</t>
@@ -1277,10 +1277,10 @@
     <t xml:space="preserve">15.4874458312988</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4384355545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2423915863037</t>
+    <t xml:space="preserve">15.4384346008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2423906326294</t>
   </si>
   <si>
     <t xml:space="preserve">15.3894233703613</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">15.0463485717773</t>
   </si>
   <si>
-    <t xml:space="preserve">14.654260635376</t>
+    <t xml:space="preserve">14.6542596817017</t>
   </si>
   <si>
     <t xml:space="preserve">13.9190969467163</t>
@@ -1310,19 +1310,19 @@
     <t xml:space="preserve">13.8210754394531</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3601942062378</t>
+    <t xml:space="preserve">14.3601951599121</t>
   </si>
   <si>
     <t xml:space="preserve">13.6250314712524</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8700857162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6740427017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7720642089844</t>
+    <t xml:space="preserve">13.8700847625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6740417480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7720651626587</t>
   </si>
   <si>
     <t xml:space="preserve">14.0171184539795</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">14.7032709121704</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5562381744385</t>
+    <t xml:space="preserve">14.5562391281128</t>
   </si>
   <si>
     <t xml:space="preserve">14.507227897644</t>
@@ -1370,13 +1370,13 @@
     <t xml:space="preserve">13.2819557189941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8898677825928</t>
+    <t xml:space="preserve">12.8898668289185</t>
   </si>
   <si>
     <t xml:space="preserve">12.7428350448608</t>
   </si>
   <si>
-    <t xml:space="preserve">12.987889289856</t>
+    <t xml:space="preserve">12.9878902435303</t>
   </si>
   <si>
     <t xml:space="preserve">13.1349220275879</t>
@@ -1388,19 +1388,19 @@
     <t xml:space="preserve">11.7626171112061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3215198516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3017377853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0859127044678</t>
+    <t xml:space="preserve">11.3215188980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.301736831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0859117507935</t>
   </si>
   <si>
     <t xml:space="preserve">13.4289875030518</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8305215835571</t>
+    <t xml:space="preserve">15.8305225372314</t>
   </si>
   <si>
     <t xml:space="preserve">15.7324991226196</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">15.9775552749634</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3696441650391</t>
+    <t xml:space="preserve">16.3696422576904</t>
   </si>
   <si>
     <t xml:space="preserve">15.6834897994995</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">15.7815113067627</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2226085662842</t>
+    <t xml:space="preserve">16.2226104736328</t>
   </si>
   <si>
     <t xml:space="preserve">16.0265655517578</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">15.9285440444946</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1735973358154</t>
+    <t xml:space="preserve">16.1735992431641</t>
   </si>
   <si>
     <t xml:space="preserve">16.2716197967529</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">19.0162296295166</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7023830413818</t>
+    <t xml:space="preserve">19.7023849487305</t>
   </si>
   <si>
     <t xml:space="preserve">19.604362487793</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">21.3687534332275</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6430397033691</t>
+    <t xml:space="preserve">22.6430377960205</t>
   </si>
   <si>
     <t xml:space="preserve">24.9955615997314</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">25.2896251678467</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6034755706787</t>
+    <t xml:space="preserve">24.6034736633301</t>
   </si>
   <si>
     <t xml:space="preserve">24.8975391387939</t>
@@ -1508,13 +1508,13 @@
     <t xml:space="preserve">24.5054531097412</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0153427124023</t>
+    <t xml:space="preserve">24.015344619751</t>
   </si>
   <si>
     <t xml:space="preserve">23.623254776001</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8390789031982</t>
+    <t xml:space="preserve">22.8390808105469</t>
   </si>
   <si>
     <t xml:space="preserve">23.3291893005371</t>
@@ -1529,16 +1529,16 @@
     <t xml:space="preserve">24.1133651733398</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0351257324219</t>
+    <t xml:space="preserve">23.0351238250732</t>
   </si>
   <si>
     <t xml:space="preserve">23.1331462860107</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2113876342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4074287414551</t>
+    <t xml:space="preserve">24.2113857269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4074306488037</t>
   </si>
   <si>
     <t xml:space="preserve">23.819299697876</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">18.7711753845215</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3300800323486</t>
+    <t xml:space="preserve">18.330078125</t>
   </si>
   <si>
     <t xml:space="preserve">17.6439247131348</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">20.1924934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8984279632568</t>
+    <t xml:space="preserve">19.8984260559082</t>
   </si>
   <si>
     <t xml:space="preserve">20.3885345458984</t>
@@ -57201,7 +57201,7 @@
     </row>
     <row r="2106">
       <c r="A2106" s="1" t="n">
-        <v>45959.6912037037</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2106" t="n">
         <v>375</v>
@@ -57210,7 +57210,7 @@
         <v>15</v>
       </c>
       <c r="D2106" t="n">
-        <v>15</v>
+        <v>14.8999996185303</v>
       </c>
       <c r="E2106" t="n">
         <v>15</v>
@@ -57222,6 +57222,32 @@
         <v>700</v>
       </c>
       <c r="H2106" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="1" t="n">
+        <v>45960.6911574074</v>
+      </c>
+      <c r="B2107" t="n">
+        <v>1250</v>
+      </c>
+      <c r="C2107" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>14.6000003814697</v>
+      </c>
+      <c r="E2107" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="F2107" t="n">
+        <v>15</v>
+      </c>
+      <c r="G2107" t="s">
+        <v>668</v>
+      </c>
+      <c r="H2107" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CULT.MI.xlsx
+++ b/data/CULT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68585252761841</t>
+    <t xml:space="preserve">4.68585205078125</t>
   </si>
   <si>
     <t xml:space="preserve">CULT.MI</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">4.60851287841797</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58576631546021</t>
+    <t xml:space="preserve">4.58576679229736</t>
   </si>
   <si>
     <t xml:space="preserve">4.48931980133057</t>
@@ -62,28 +62,28 @@
     <t xml:space="preserve">4.56301975250244</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51297616958618</t>
+    <t xml:space="preserve">4.51297664642334</t>
   </si>
   <si>
     <t xml:space="preserve">4.46020364761353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29824638366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21271800994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18178224563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23091506958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36375713348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38195466995239</t>
+    <t xml:space="preserve">4.29824590682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21271753311157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18178176879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23091554641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36375617980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38195562362671</t>
   </si>
   <si>
     <t xml:space="preserve">4.35101938247681</t>
@@ -95,37 +95,37 @@
     <t xml:space="preserve">4.24183416366577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22909545898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10535287857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09443473815918</t>
+    <t xml:space="preserve">4.22909498214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1053524017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09443378448486</t>
   </si>
   <si>
     <t xml:space="preserve">4.10899209976196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99616765975952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04712057113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03984117507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96341228485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07441759109497</t>
+    <t xml:space="preserve">3.99616861343384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04712104797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0398416519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96341252326965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07441711425781</t>
   </si>
   <si>
     <t xml:space="preserve">4.3200831413269</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2491135597229</t>
+    <t xml:space="preserve">4.24911308288574</t>
   </si>
   <si>
     <t xml:space="preserve">3.97979021072388</t>
@@ -134,10 +134,10 @@
     <t xml:space="preserve">4.06895780563354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05439949035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98524951934814</t>
+    <t xml:space="preserve">4.05439901351929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98524975776672</t>
   </si>
   <si>
     <t xml:space="preserve">4.05076026916504</t>
@@ -146,28 +146,28 @@
     <t xml:space="preserve">4.07259702682495</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03802156448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04530096054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03074312210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01254510879517</t>
+    <t xml:space="preserve">4.03802299499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04530048370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03074264526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01254558563232</t>
   </si>
   <si>
     <t xml:space="preserve">4.04894018173218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05985879898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07623720169067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91245937347412</t>
+    <t xml:space="preserve">4.05985927581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07623624801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9124596118927</t>
   </si>
   <si>
     <t xml:space="preserve">3.99070906639099</t>
@@ -176,40 +176,40 @@
     <t xml:space="preserve">4.01072597503662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92155814170837</t>
+    <t xml:space="preserve">3.92155766487122</t>
   </si>
   <si>
     <t xml:space="preserve">4.00162744522095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05803918838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21635675430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2218165397644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18542146682739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16176414489746</t>
+    <t xml:space="preserve">4.05803966522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21635723114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22181701660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18542242050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16176462173462</t>
   </si>
   <si>
     <t xml:space="preserve">4.35465812683105</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28186798095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26731061935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39287233352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36739683151245</t>
+    <t xml:space="preserve">4.28186845779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26731014251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39287328720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36739635467529</t>
   </si>
   <si>
     <t xml:space="preserve">4.17814254760742</t>
@@ -218,88 +218,88 @@
     <t xml:space="preserve">4.27458906173706</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31826305389404</t>
+    <t xml:space="preserve">4.3182635307312</t>
   </si>
   <si>
     <t xml:space="preserve">4.35647869110107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26549053192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26367044448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27640914916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14902639389038</t>
+    <t xml:space="preserve">4.26549005508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26367092132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27640867233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14902687072754</t>
   </si>
   <si>
     <t xml:space="preserve">4.35829782485962</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35283899307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29460620880127</t>
+    <t xml:space="preserve">4.35283803939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29460668563843</t>
   </si>
   <si>
     <t xml:space="preserve">4.2036190032959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24001455307007</t>
+    <t xml:space="preserve">4.24001407623291</t>
   </si>
   <si>
     <t xml:space="preserve">4.34010076522827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42926788330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34919929504395</t>
+    <t xml:space="preserve">4.42926836013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34919881820679</t>
   </si>
   <si>
     <t xml:space="preserve">4.33646059036255</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33100128173828</t>
+    <t xml:space="preserve">4.33100175857544</t>
   </si>
   <si>
     <t xml:space="preserve">4.32190275192261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46748304367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45838403701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2855076789856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83057069778442</t>
+    <t xml:space="preserve">4.46748208999634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45838356018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28550815582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.830570936203</t>
   </si>
   <si>
     <t xml:space="preserve">3.90336060523987</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88516330718994</t>
+    <t xml:space="preserve">3.88516306877136</t>
   </si>
   <si>
     <t xml:space="preserve">3.87606501579285</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00344705581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93065714836121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99434757232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08533573150635</t>
+    <t xml:space="preserve">4.00344610214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93065690994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99434781074524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08533525466919</t>
   </si>
   <si>
     <t xml:space="preserve">3.9670512676239</t>
@@ -308,31 +308,31 @@
     <t xml:space="preserve">3.86696577072144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84876847267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85786652565002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8123733997345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80327439308167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77597808837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97615051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94885420799255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13992738723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16722393035889</t>
+    <t xml:space="preserve">3.84876775741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85786700248718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81237244606018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80327463150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77597784996033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97615003585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94885492324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13992786407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16722440719604</t>
   </si>
   <si>
     <t xml:space="preserve">4.3352837562561</t>
@@ -347,13 +347,13 @@
     <t xml:space="preserve">4.42791748046875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19633150100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16854190826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29822969436646</t>
+    <t xml:space="preserve">4.1963324546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.168541431427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29823017120361</t>
   </si>
   <si>
     <t xml:space="preserve">4.30749320983887</t>
@@ -362,13 +362,13 @@
     <t xml:space="preserve">4.27970266342163</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39086389541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40012693405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35381031036377</t>
+    <t xml:space="preserve">4.3908634185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40012741088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35380983352661</t>
   </si>
   <si>
     <t xml:space="preserve">4.08517074584961</t>
@@ -383,67 +383,67 @@
     <t xml:space="preserve">3.97400975227356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03885364532471</t>
+    <t xml:space="preserve">4.03885316848755</t>
   </si>
   <si>
     <t xml:space="preserve">3.94622015953064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95548319816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23338603973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22412157058716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24264907836914</t>
+    <t xml:space="preserve">3.95548295974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23338556289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22412252426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2426495552063</t>
   </si>
   <si>
     <t xml:space="preserve">4.11296081542969</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26117610931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91842937469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89990234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89063882827759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07590770721436</t>
+    <t xml:space="preserve">4.26117658615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91842889785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89990258216858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89063906669617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07590675354004</t>
   </si>
   <si>
     <t xml:space="preserve">4.06664371490479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79800510406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73316121101379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86284852027893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71463418006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70537066459656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77021455764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3904139995575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44599461555481</t>
+    <t xml:space="preserve">3.79800486564636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73316073417664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86284899711609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71463441848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70537042617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77021431922913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39041376113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44599437713623</t>
   </si>
   <si>
     <t xml:space="preserve">3.58494567871094</t>
@@ -452,79 +452,79 @@
     <t xml:space="preserve">3.68684339523315</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60347318649292</t>
+    <t xml:space="preserve">3.60347270965576</t>
   </si>
   <si>
     <t xml:space="preserve">3.52010202407837</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37188720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46452140808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53862905502319</t>
+    <t xml:space="preserve">3.37188673019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46452116966248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53862881660461</t>
   </si>
   <si>
     <t xml:space="preserve">3.5293653011322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45525813102722</t>
+    <t xml:space="preserve">3.45525789260864</t>
   </si>
   <si>
     <t xml:space="preserve">3.34409666061401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07545733451843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14956498146057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29777956008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31630635261536</t>
+    <t xml:space="preserve">3.07545757293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14956521987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29777979850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31630659103394</t>
   </si>
   <si>
     <t xml:space="preserve">3.23293590545654</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24219870567322</t>
+    <t xml:space="preserve">3.24219918251038</t>
   </si>
   <si>
     <t xml:space="preserve">3.02914023399353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20514512062073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25146222114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10324764251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15882849693298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91797924041748</t>
+    <t xml:space="preserve">3.20514559745789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25146245956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10324740409851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1588282585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91797947883606</t>
   </si>
   <si>
     <t xml:space="preserve">2.7419741153717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77902770042419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.871661901474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96429634094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85313558578491</t>
+    <t xml:space="preserve">2.77902793884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87166213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96429657936096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85313510894775</t>
   </si>
   <si>
     <t xml:space="preserve">2.83460831642151</t>
@@ -533,10 +533,10 @@
     <t xml:space="preserve">2.84387183189392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72344732284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76050090789795</t>
+    <t xml:space="preserve">2.72344756126404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76050114631653</t>
   </si>
   <si>
     <t xml:space="preserve">2.76976442337036</t>
@@ -551,58 +551,58 @@
     <t xml:space="preserve">2.38070034980774</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36217355728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29732942581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31585669517517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35291028022766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26953935623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2324857711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28806638717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08427095413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13058805465698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22322249412537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24174904823303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11206078529358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17690515518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03795385360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9916365146637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88047552108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94531941413879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92679262161255</t>
+    <t xml:space="preserve">2.36217379570007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29732990264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31585645675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35291004180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26953911781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23248529434204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28806614875793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0842707157135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13058829307556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22322225570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24174928665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11206126213074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17690491676331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03795337677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99163675308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88047564029694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94531953334808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92679226398468</t>
   </si>
   <si>
     <t xml:space="preserve">2.16764187812805</t>
@@ -617,13 +617,13 @@
     <t xml:space="preserve">2.4084906578064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48259830474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42701768875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38996410369873</t>
+    <t xml:space="preserve">2.48259806632996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42701745033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38996386528015</t>
   </si>
   <si>
     <t xml:space="preserve">2.46583604812622</t>
@@ -632,22 +632,22 @@
     <t xml:space="preserve">2.50406575202942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65698599815369</t>
+    <t xml:space="preserve">2.65698575973511</t>
   </si>
   <si>
     <t xml:space="preserve">2.71433067321777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54229545593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58052587509155</t>
+    <t xml:space="preserve">2.54229593276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58052563667297</t>
   </si>
   <si>
     <t xml:space="preserve">2.52318096160889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42760610580444</t>
+    <t xml:space="preserve">2.42760586738586</t>
   </si>
   <si>
     <t xml:space="preserve">2.38937592506409</t>
@@ -656,43 +656,43 @@
     <t xml:space="preserve">2.48495078086853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61875581741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56141066551208</t>
+    <t xml:space="preserve">2.61875557899475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56141090393066</t>
   </si>
   <si>
     <t xml:space="preserve">2.6378710269928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73344588279724</t>
+    <t xml:space="preserve">2.73344612121582</t>
   </si>
   <si>
     <t xml:space="preserve">2.69521570205688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75256085395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80990600585938</t>
+    <t xml:space="preserve">2.75256109237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80990624427795</t>
   </si>
   <si>
     <t xml:space="preserve">2.82902097702026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84813570976257</t>
+    <t xml:space="preserve">2.84813594818115</t>
   </si>
   <si>
     <t xml:space="preserve">3.05840086936951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86725068092346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7716760635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67610096931458</t>
+    <t xml:space="preserve">2.86725091934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77167630195618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.676100730896</t>
   </si>
   <si>
     <t xml:space="preserve">2.59964084625244</t>
@@ -713,10 +713,10 @@
     <t xml:space="preserve">3.45981597900391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74654150009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76565623283386</t>
+    <t xml:space="preserve">3.74654102325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76565647125244</t>
   </si>
   <si>
     <t xml:space="preserve">4.01415109634399</t>
@@ -725,112 +725,112 @@
     <t xml:space="preserve">4.1097264289856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97592115402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88034605979919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82300090789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4407012462616</t>
+    <t xml:space="preserve">3.97592091560364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88034677505493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82300114631653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44070076942444</t>
   </si>
   <si>
     <t xml:space="preserve">3.40247106552124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36424112319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68919610977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72742581367493</t>
+    <t xml:space="preserve">3.36424136161804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68919587135315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72742605209351</t>
   </si>
   <si>
     <t xml:space="preserve">3.7083113193512</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57450604438782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55539107322693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51716136932373</t>
+    <t xml:space="preserve">3.57450580596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55539083480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51716089248657</t>
   </si>
   <si>
     <t xml:space="preserve">3.63185119628906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53627634048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61273646354675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65096640586853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24955105781555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32601070404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42158579826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30689597129822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38335633277893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59362101554871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47893118858337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49804592132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28778100013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67008090019226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80388617515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93769121170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03326559066772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18618631362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30087614059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53025674819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51114130020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58760166168213</t>
+    <t xml:space="preserve">3.53627610206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61273598670959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65096592903137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24955153465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32601141929626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42158627510071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3068962097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38335609436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59362125396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47893095016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49804615974426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28778147697449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67008113861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80388641357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93769097328186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03326606750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18618679046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30087661743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5302562713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51114177703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58760213851929</t>
   </si>
   <si>
     <t xml:space="preserve">4.49202632904053</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43468141555786</t>
+    <t xml:space="preserve">4.43468189239502</t>
   </si>
   <si>
     <t xml:space="preserve">4.62583160400391</t>
@@ -839,10 +839,10 @@
     <t xml:space="preserve">4.74052143096924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75963592529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7022910118103</t>
+    <t xml:space="preserve">4.75963640213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70229148864746</t>
   </si>
   <si>
     <t xml:space="preserve">4.68317651748657</t>
@@ -857,22 +857,22 @@
     <t xml:space="preserve">4.66406154632568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72140645980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87432670593262</t>
+    <t xml:space="preserve">4.72140598297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87432622909546</t>
   </si>
   <si>
     <t xml:space="preserve">4.96990156173706</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92211389541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1132640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16105175018311</t>
+    <t xml:space="preserve">4.9221134185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11326456069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16105127334595</t>
   </si>
   <si>
     <t xml:space="preserve">5.20883893966675</t>
@@ -884,16 +884,16 @@
     <t xml:space="preserve">5.30441474914551</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44777631759644</t>
+    <t xml:space="preserve">5.44777679443359</t>
   </si>
   <si>
     <t xml:space="preserve">5.63892650604248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59113883972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81332635879517</t>
+    <t xml:space="preserve">5.591139793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81332683563232</t>
   </si>
   <si>
     <t xml:space="preserve">5.71643781661987</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">5.1351056098938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84443855285645</t>
+    <t xml:space="preserve">4.8444390296936</t>
   </si>
   <si>
     <t xml:space="preserve">4.82506132125854</t>
@@ -917,19 +917,19 @@
     <t xml:space="preserve">4.59252834320068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55377244949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76692771911621</t>
+    <t xml:space="preserve">4.55377292633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76692819595337</t>
   </si>
   <si>
     <t xml:space="preserve">5.03821611404419</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9897723197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08666086196899</t>
+    <t xml:space="preserve">4.98977184295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08666133880615</t>
   </si>
   <si>
     <t xml:space="preserve">5.18354988098145</t>
@@ -938,16 +938,16 @@
     <t xml:space="preserve">4.9413275718689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23199462890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74755048751831</t>
+    <t xml:space="preserve">5.23199415206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74755001068115</t>
   </si>
   <si>
     <t xml:space="preserve">5.28043794631958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89288330078125</t>
+    <t xml:space="preserve">4.89288377761841</t>
   </si>
   <si>
     <t xml:space="preserve">4.6312837600708</t>
@@ -962,13 +962,13 @@
     <t xml:space="preserve">4.78630542755127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72817182540894</t>
+    <t xml:space="preserve">4.72817277908325</t>
   </si>
   <si>
     <t xml:space="preserve">4.70879459381104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91021585464478</t>
+    <t xml:space="preserve">5.91021537780762</t>
   </si>
   <si>
     <t xml:space="preserve">5.61954927444458</t>
@@ -977,16 +977,16 @@
     <t xml:space="preserve">5.32888269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37732744216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57110452651978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47421646118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66799354553223</t>
+    <t xml:space="preserve">5.37732696533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57110500335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47421598434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66799402236938</t>
   </si>
   <si>
     <t xml:space="preserve">6.73376989364624</t>
@@ -1001,46 +1001,46 @@
     <t xml:space="preserve">6.68532562255859</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5884370803833</t>
+    <t xml:space="preserve">6.58843755722046</t>
   </si>
   <si>
     <t xml:space="preserve">6.63688087463379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24932622909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34621524810791</t>
+    <t xml:space="preserve">6.2493257522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34621572494507</t>
   </si>
   <si>
     <t xml:space="preserve">6.53999280929565</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3946590423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71998977661133</t>
+    <t xml:space="preserve">6.39465951919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71999073028564</t>
   </si>
   <si>
     <t xml:space="preserve">7.99332427978516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09021282196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04176807403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94488000869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84799098968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89643526077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38087844848633</t>
+    <t xml:space="preserve">8.09021472930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04176712036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94488096237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84799146652222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89643430709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38087940216064</t>
   </si>
   <si>
     <t xml:space="preserve">10.2702112197876</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">9.88265514373779</t>
   </si>
   <si>
-    <t xml:space="preserve">10.173321723938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9795446395874</t>
+    <t xml:space="preserve">10.1733226776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97954368591309</t>
   </si>
   <si>
     <t xml:space="preserve">10.0764322280884</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">11.2390985488892</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6266527175903</t>
+    <t xml:space="preserve">11.6266536712646</t>
   </si>
   <si>
     <t xml:space="preserve">13.0799856185913</t>
@@ -1070,16 +1070,16 @@
     <t xml:space="preserve">13.2737617492676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9830961227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4364280700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3395395278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0177602767944</t>
+    <t xml:space="preserve">12.9830951690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4364261627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3395385742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0177612304688</t>
   </si>
   <si>
     <t xml:space="preserve">16.1669788360596</t>
@@ -1094,13 +1094,13 @@
     <t xml:space="preserve">14.9008913040161</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6348028182983</t>
+    <t xml:space="preserve">13.634801864624</t>
   </si>
   <si>
     <t xml:space="preserve">12.0765390396118</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4661045074463</t>
+    <t xml:space="preserve">12.4661054611206</t>
   </si>
   <si>
     <t xml:space="preserve">13.4400196075439</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">14.0243673324585</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2191514968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8034992218018</t>
+    <t xml:space="preserve">14.2191505432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8034982681274</t>
   </si>
   <si>
     <t xml:space="preserve">14.4139337539673</t>
@@ -1124,28 +1124,28 @@
     <t xml:space="preserve">14.6087160110474</t>
   </si>
   <si>
-    <t xml:space="preserve">14.706109046936</t>
+    <t xml:space="preserve">14.7061080932617</t>
   </si>
   <si>
     <t xml:space="preserve">14.5113248825073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3426284790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1217594146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3165416717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8295841217041</t>
+    <t xml:space="preserve">13.3426275253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1217584609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3165426254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8295850753784</t>
   </si>
   <si>
     <t xml:space="preserve">13.5374097824097</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2452363967896</t>
+    <t xml:space="preserve">13.2452373504639</t>
   </si>
   <si>
     <t xml:space="preserve">12.8556709289551</t>
@@ -1154,25 +1154,25 @@
     <t xml:space="preserve">12.3687133789062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7582788467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5634965896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1739301681519</t>
+    <t xml:space="preserve">12.758279800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5634956359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1739311218262</t>
   </si>
   <si>
     <t xml:space="preserve">11.6869735717773</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1026239395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93392658233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7130584716797</t>
+    <t xml:space="preserve">11.1026248931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93392562866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.713059425354</t>
   </si>
   <si>
     <t xml:space="preserve">11.2000160217285</t>
@@ -1181,7 +1181,7 @@
     <t xml:space="preserve">11.9791479110718</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8817558288574</t>
+    <t xml:space="preserve">11.8817567825317</t>
   </si>
   <si>
     <t xml:space="preserve">10.9078416824341</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">11.2974081039429</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3947982788086</t>
+    <t xml:space="preserve">11.3947992324829</t>
   </si>
   <si>
     <t xml:space="preserve">11.589581489563</t>
@@ -1205,19 +1205,19 @@
     <t xml:space="preserve">11.4921903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.810450553894</t>
+    <t xml:space="preserve">10.8104515075684</t>
   </si>
   <si>
     <t xml:space="preserve">10.4208841323853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2261009216309</t>
+    <t xml:space="preserve">10.2261018753052</t>
   </si>
   <si>
     <t xml:space="preserve">10.3234939575195</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1287097930908</t>
+    <t xml:space="preserve">10.1287107467651</t>
   </si>
   <si>
     <t xml:space="preserve">10.0313196182251</t>
@@ -1229,10 +1229,10 @@
     <t xml:space="preserve">9.54436206817627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8365364074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34957885742188</t>
+    <t xml:space="preserve">9.83653545379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34957790374756</t>
   </si>
   <si>
     <t xml:space="preserve">9.49566650390625</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">12.9530620574951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6800231933594</t>
+    <t xml:space="preserve">15.6800222396851</t>
   </si>
   <si>
     <t xml:space="preserve">13.7321939468384</t>
@@ -1253,19 +1253,19 @@
     <t xml:space="preserve">14.1704559326172</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3652372360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0730628967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1443691253662</t>
+    <t xml:space="preserve">14.3652381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0730638504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1443700790405</t>
   </si>
   <si>
     <t xml:space="preserve">15.5364561080933</t>
   </si>
   <si>
-    <t xml:space="preserve">15.585467338562</t>
+    <t xml:space="preserve">15.5854682922363</t>
   </si>
   <si>
     <t xml:space="preserve">15.6344785690308</t>
@@ -1274,13 +1274,13 @@
     <t xml:space="preserve">15.193380355835</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4874458312988</t>
+    <t xml:space="preserve">15.4874448776245</t>
   </si>
   <si>
     <t xml:space="preserve">15.4384346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2423906326294</t>
+    <t xml:space="preserve">15.2423915863037</t>
   </si>
   <si>
     <t xml:space="preserve">15.3894233703613</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">14.9973373413086</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8993148803711</t>
+    <t xml:space="preserve">14.8993139266968</t>
   </si>
   <si>
     <t xml:space="preserve">15.0463485717773</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">13.9190969467163</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1641502380371</t>
+    <t xml:space="preserve">14.1641511917114</t>
   </si>
   <si>
     <t xml:space="preserve">13.7230529785156</t>
@@ -1313,10 +1313,10 @@
     <t xml:space="preserve">14.3601951599121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6250314712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8700847625732</t>
+    <t xml:space="preserve">13.6250305175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8700857162476</t>
   </si>
   <si>
     <t xml:space="preserve">13.6740417480469</t>
@@ -1325,19 +1325,19 @@
     <t xml:space="preserve">13.7720651626587</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0171184539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1839323043823</t>
+    <t xml:space="preserve">14.0171194076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1839332580566</t>
   </si>
   <si>
     <t xml:space="preserve">13.5270099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9483251571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4092054367065</t>
+    <t xml:space="preserve">14.9483261108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4092063903809</t>
   </si>
   <si>
     <t xml:space="preserve">14.8503036499023</t>
@@ -1358,10 +1358,10 @@
     <t xml:space="preserve">14.507227897644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0661306381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3309659957886</t>
+    <t xml:space="preserve">14.0661296844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3309669494629</t>
   </si>
   <si>
     <t xml:space="preserve">13.4779987335205</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">12.7428350448608</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9878902435303</t>
+    <t xml:space="preserve">12.987889289856</t>
   </si>
   <si>
     <t xml:space="preserve">13.1349220275879</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">15.8795328140259</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9775552749634</t>
+    <t xml:space="preserve">15.9775543212891</t>
   </si>
   <si>
     <t xml:space="preserve">16.3696422576904</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">15.7815113067627</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2226104736328</t>
+    <t xml:space="preserve">16.2226085662842</t>
   </si>
   <si>
     <t xml:space="preserve">16.0265655517578</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">16.0755767822266</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9285440444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1735992431641</t>
+    <t xml:space="preserve">15.9285430908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1735973358154</t>
   </si>
   <si>
     <t xml:space="preserve">16.2716197967529</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">20.0944690704346</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9173202514648</t>
+    <t xml:space="preserve">23.9173221588135</t>
   </si>
   <si>
     <t xml:space="preserve">22.545015335083</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">23.5252342224121</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7995166778564</t>
+    <t xml:space="preserve">24.7995147705078</t>
   </si>
   <si>
     <t xml:space="preserve">23.2311687469482</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">20.7806243896484</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1727104187012</t>
+    <t xml:space="preserve">21.1727085113525</t>
   </si>
   <si>
     <t xml:space="preserve">20.4865570068359</t>
@@ -1487,13 +1487,13 @@
     <t xml:space="preserve">20.6826038360596</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3687534332275</t>
+    <t xml:space="preserve">21.3687553405762</t>
   </si>
   <si>
     <t xml:space="preserve">22.6430377960205</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9955615997314</t>
+    <t xml:space="preserve">24.9955596923828</t>
   </si>
   <si>
     <t xml:space="preserve">25.2896251678467</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">23.623254776001</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8390808105469</t>
+    <t xml:space="preserve">22.8390827178955</t>
   </si>
   <si>
     <t xml:space="preserve">23.3291893005371</t>
@@ -1523,19 +1523,19 @@
     <t xml:space="preserve">22.9371032714844</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7212791442871</t>
+    <t xml:space="preserve">23.7212772369385</t>
   </si>
   <si>
     <t xml:space="preserve">24.1133651733398</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0351238250732</t>
+    <t xml:space="preserve">23.0351257324219</t>
   </si>
   <si>
     <t xml:space="preserve">23.1331462860107</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2113857269287</t>
+    <t xml:space="preserve">24.2113876342773</t>
   </si>
   <si>
     <t xml:space="preserve">24.4074306488037</t>
@@ -1547,13 +1547,13 @@
     <t xml:space="preserve">22.2509517669678</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7608413696289</t>
+    <t xml:space="preserve">21.7608432769775</t>
   </si>
   <si>
     <t xml:space="preserve">21.9568843841553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1529293060303</t>
+    <t xml:space="preserve">22.1529273986816</t>
   </si>
   <si>
     <t xml:space="preserve">18.7711753845215</t>
@@ -1568,19 +1568,19 @@
     <t xml:space="preserve">18.5261211395264</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9964485168457</t>
+    <t xml:space="preserve">19.9964466094971</t>
   </si>
   <si>
     <t xml:space="preserve">20.5845794677734</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1924934387207</t>
+    <t xml:space="preserve">20.1924953460693</t>
   </si>
   <si>
     <t xml:space="preserve">19.8984260559082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3885345458984</t>
+    <t xml:space="preserve">20.3885364532471</t>
   </si>
   <si>
     <t xml:space="preserve">19.4049549102783</t>
@@ -57227,7 +57227,7 @@
     </row>
     <row r="2107">
       <c r="A2107" s="1" t="n">
-        <v>45960.6911574074</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2107" t="n">
         <v>1250</v>

--- a/data/CULT.MI.xlsx
+++ b/data/CULT.MI.xlsx
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68585252761841</t>
+    <t xml:space="preserve">4.68585348129272</t>
   </si>
   <si>
     <t xml:space="preserve">CULT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57666826248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59486484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60851287841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58576631546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48931980133057</t>
+    <t xml:space="preserve">4.57666683197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5948657989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60851383209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58576583862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48931932449341</t>
   </si>
   <si>
     <t xml:space="preserve">4.56301927566528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51297664642334</t>
+    <t xml:space="preserve">4.51297616958618</t>
   </si>
   <si>
     <t xml:space="preserve">4.46020364761353</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">4.18178272247314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23091506958008</t>
+    <t xml:space="preserve">4.23091554641724</t>
   </si>
   <si>
     <t xml:space="preserve">4.36375713348389</t>
@@ -92,19 +92,19 @@
     <t xml:space="preserve">4.28914737701416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24183464050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22909545898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10535335540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09443426132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10899209976196</t>
+    <t xml:space="preserve">4.24183416366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22909498214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10535383224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09443473815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1089916229248</t>
   </si>
   <si>
     <t xml:space="preserve">3.99616765975952</t>
@@ -116,19 +116,19 @@
     <t xml:space="preserve">4.03984212875366</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96341180801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07441806793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3200831413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2491135597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9797899723053</t>
+    <t xml:space="preserve">3.96341228485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07441711425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32008361816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24911260604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97978973388672</t>
   </si>
   <si>
     <t xml:space="preserve">4.06895780563354</t>
@@ -137,31 +137,31 @@
     <t xml:space="preserve">4.0543999671936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98524904251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0507607460022</t>
+    <t xml:space="preserve">3.98524951934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05076026916504</t>
   </si>
   <si>
     <t xml:space="preserve">4.07259750366211</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0380220413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04530096054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03074312210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01254510879517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04894018173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05985832214355</t>
+    <t xml:space="preserve">4.03802251815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04530143737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03074216842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01254558563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04894065856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05985879898071</t>
   </si>
   <si>
     <t xml:space="preserve">4.07623672485352</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">3.91245913505554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99070906639099</t>
+    <t xml:space="preserve">3.99070930480957</t>
   </si>
   <si>
     <t xml:space="preserve">4.01072597503662</t>
@@ -179,28 +179,28 @@
     <t xml:space="preserve">3.92155814170837</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00162696838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05803918838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21635675430298</t>
+    <t xml:space="preserve">4.00162744522095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05803871154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21635770797729</t>
   </si>
   <si>
     <t xml:space="preserve">4.2218165397644</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18542098999023</t>
+    <t xml:space="preserve">4.18542146682739</t>
   </si>
   <si>
     <t xml:space="preserve">4.16176462173462</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35465860366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28186798095703</t>
+    <t xml:space="preserve">4.35465717315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28186845779419</t>
   </si>
   <si>
     <t xml:space="preserve">4.26731014251709</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">4.39287328720093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36739635467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17814302444458</t>
+    <t xml:space="preserve">4.36739683151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17814159393311</t>
   </si>
   <si>
     <t xml:space="preserve">4.27458953857422</t>
@@ -221,10 +221,10 @@
     <t xml:space="preserve">4.3182635307312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35647821426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26549100875854</t>
+    <t xml:space="preserve">4.35647773742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26549053192139</t>
   </si>
   <si>
     <t xml:space="preserve">4.26367092132568</t>
@@ -233,40 +233,40 @@
     <t xml:space="preserve">4.27640914916992</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14902687072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35829782485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35283803939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29460573196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20361948013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24001312255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34009981155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42926836013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34919929504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33646011352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3310022354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32190275192261</t>
+    <t xml:space="preserve">4.14902639389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35829830169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35283756256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29460668563843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2036190032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24001359939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34010076522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42926788330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3491997718811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33646106719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33100175857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32190179824829</t>
   </si>
   <si>
     <t xml:space="preserve">4.4674825668335</t>
@@ -275,97 +275,97 @@
     <t xml:space="preserve">4.45838403701782</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28550815582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83057117462158</t>
+    <t xml:space="preserve">4.2855076789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83057022094727</t>
   </si>
   <si>
     <t xml:space="preserve">3.90336036682129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88516330718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87606477737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00344705581665</t>
+    <t xml:space="preserve">3.88516354560852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87606430053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00344657897949</t>
   </si>
   <si>
     <t xml:space="preserve">3.93065738677979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99434804916382</t>
+    <t xml:space="preserve">3.99434781074524</t>
   </si>
   <si>
     <t xml:space="preserve">4.08533525466919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96705174446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86696577072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84876823425293</t>
+    <t xml:space="preserve">3.96705150604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86696553230286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84876847267151</t>
   </si>
   <si>
     <t xml:space="preserve">3.8578667640686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81237316131592</t>
+    <t xml:space="preserve">3.81237292289734</t>
   </si>
   <si>
     <t xml:space="preserve">3.80327439308167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77597856521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97615075111389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94885468482971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13992786407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1672248840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33528280258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21485996246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31675624847412</t>
+    <t xml:space="preserve">3.77597832679749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97615051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94885492324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13992834091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16722393035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33528327941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21485948562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31675672531128</t>
   </si>
   <si>
     <t xml:space="preserve">4.42791795730591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19633150100708</t>
+    <t xml:space="preserve">4.19633197784424</t>
   </si>
   <si>
     <t xml:space="preserve">4.16854190826416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29822969436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30749320983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27970314025879</t>
+    <t xml:space="preserve">4.29823017120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30749273300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27970266342163</t>
   </si>
   <si>
     <t xml:space="preserve">4.3908634185791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40012741088867</t>
+    <t xml:space="preserve">4.40012693405151</t>
   </si>
   <si>
     <t xml:space="preserve">4.35381031036377</t>
@@ -374,22 +374,22 @@
     <t xml:space="preserve">4.08517074584961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93695569038391</t>
+    <t xml:space="preserve">3.93695592880249</t>
   </si>
   <si>
     <t xml:space="preserve">4.00180053710938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97400999069214</t>
+    <t xml:space="preserve">3.9740092754364</t>
   </si>
   <si>
     <t xml:space="preserve">4.03885412216187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9462194442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95548295974731</t>
+    <t xml:space="preserve">3.94621968269348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95548319816589</t>
   </si>
   <si>
     <t xml:space="preserve">4.23338556289673</t>
@@ -398,70 +398,70 @@
     <t xml:space="preserve">4.22412252426147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24264812469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11296129226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26117610931396</t>
+    <t xml:space="preserve">4.24264860153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11296081542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26117563247681</t>
   </si>
   <si>
     <t xml:space="preserve">3.91842985153198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89990258216858</t>
+    <t xml:space="preserve">3.89990210533142</t>
   </si>
   <si>
     <t xml:space="preserve">3.89063858985901</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0759072303772</t>
+    <t xml:space="preserve">4.07590675354004</t>
   </si>
   <si>
     <t xml:space="preserve">4.06664371490479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79800415039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73316073417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86284852027893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71463394165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70537042617798</t>
+    <t xml:space="preserve">3.79800486564636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73316121101379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86284875869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71463418006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7053701877594</t>
   </si>
   <si>
     <t xml:space="preserve">3.77021455764771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39041423797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44599461555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58494544029236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68684363365173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60347270965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52010178565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37188744544983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46452140808105</t>
+    <t xml:space="preserve">3.3904139995575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44599437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58494591712952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68684339523315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60347294807434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52010202407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37188720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46452116966248</t>
   </si>
   <si>
     <t xml:space="preserve">3.53862857818604</t>
@@ -470,79 +470,79 @@
     <t xml:space="preserve">3.5293653011322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45525789260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34409666061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07545757293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14956450462341</t>
+    <t xml:space="preserve">3.45525813102722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34409642219543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07545781135559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14956498146057</t>
   </si>
   <si>
     <t xml:space="preserve">3.29777956008911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31630635261536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23293542861938</t>
+    <t xml:space="preserve">3.31630659103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23293566703796</t>
   </si>
   <si>
     <t xml:space="preserve">3.2421989440918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02914047241211</t>
+    <t xml:space="preserve">3.02914023399353</t>
   </si>
   <si>
     <t xml:space="preserve">3.20514559745789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25146269798279</t>
+    <t xml:space="preserve">3.25146293640137</t>
   </si>
   <si>
     <t xml:space="preserve">3.10324764251709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15882849693298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91797924041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74197435379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77902793884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87166237831116</t>
+    <t xml:space="preserve">3.1588282585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9179790019989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74197387695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77902770042419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87166213989258</t>
   </si>
   <si>
     <t xml:space="preserve">2.96429634094238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85313487052917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83460831642151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84387159347534</t>
+    <t xml:space="preserve">2.85313510894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83460855484009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84387183189392</t>
   </si>
   <si>
     <t xml:space="preserve">2.72344732284546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76050114631653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76976418495178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6308126449585</t>
+    <t xml:space="preserve">2.76050090789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76976442337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63081336021423</t>
   </si>
   <si>
     <t xml:space="preserve">2.67713022232056</t>
@@ -551,22 +551,22 @@
     <t xml:space="preserve">2.38070034980774</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36217331886292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29732918739319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31585645675659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35291028022766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26953911781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2324857711792</t>
+    <t xml:space="preserve">2.36217355728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29732942581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31585669517517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35291004180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26953935623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23248553276062</t>
   </si>
   <si>
     <t xml:space="preserve">2.28806638717651</t>
@@ -575,13 +575,13 @@
     <t xml:space="preserve">2.08427095413208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13058805465698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22322249412537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24174904823303</t>
+    <t xml:space="preserve">2.1305878162384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22322225570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24174928665161</t>
   </si>
   <si>
     <t xml:space="preserve">2.11206126213074</t>
@@ -590,10 +590,10 @@
     <t xml:space="preserve">2.17690515518188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0379536151886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99163687229156</t>
+    <t xml:space="preserve">2.03795337677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99163663387299</t>
   </si>
   <si>
     <t xml:space="preserve">1.88047552108765</t>
@@ -602,19 +602,19 @@
     <t xml:space="preserve">1.9453192949295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92679274082184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16764140129089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13985157012939</t>
+    <t xml:space="preserve">1.92679262161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16764163970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13985133171082</t>
   </si>
   <si>
     <t xml:space="preserve">2.21395897865295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40849089622498</t>
+    <t xml:space="preserve">2.4084906578064</t>
   </si>
   <si>
     <t xml:space="preserve">2.48259806632996</t>
@@ -626,28 +626,28 @@
     <t xml:space="preserve">2.38996386528015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46583580970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50406575202942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65698552131653</t>
+    <t xml:space="preserve">2.46583557128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50406551361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65698599815369</t>
   </si>
   <si>
     <t xml:space="preserve">2.71433091163635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5422956943512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58052587509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52318096160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42760610580444</t>
+    <t xml:space="preserve">2.54229617118835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58052611351013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52318120002747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42760586738586</t>
   </si>
   <si>
     <t xml:space="preserve">2.38937592506409</t>
@@ -656,25 +656,25 @@
     <t xml:space="preserve">2.48495078086853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61875581741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56141066551208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63787055015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73344564437866</t>
+    <t xml:space="preserve">2.61875605583191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56141138076782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6378710269928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73344588279724</t>
   </si>
   <si>
     <t xml:space="preserve">2.69521594047546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75256085395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80990624427795</t>
+    <t xml:space="preserve">2.75256109237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80990600585938</t>
   </si>
   <si>
     <t xml:space="preserve">2.82902073860168</t>
@@ -683,52 +683,52 @@
     <t xml:space="preserve">2.84813594818115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05840110778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86725091934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77167582511902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.676100730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59964084625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44672083854675</t>
+    <t xml:space="preserve">3.05840086936951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86725068092346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7716760635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67610096931458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59964108467102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44672060012817</t>
   </si>
   <si>
     <t xml:space="preserve">2.37026071548462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09663128852844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34512615203857</t>
+    <t xml:space="preserve">3.09663081169128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34512591362</t>
   </si>
   <si>
     <t xml:space="preserve">3.45981597900391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74654150009155</t>
+    <t xml:space="preserve">3.74654126167297</t>
   </si>
   <si>
     <t xml:space="preserve">3.76565647125244</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01415061950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10972690582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97592067718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88034558296204</t>
+    <t xml:space="preserve">4.01415109634399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1097264289856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97592115402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88034629821777</t>
   </si>
   <si>
     <t xml:space="preserve">3.82300114631653</t>
@@ -737,28 +737,28 @@
     <t xml:space="preserve">3.44070100784302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40247082710266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36424112319946</t>
+    <t xml:space="preserve">3.40247106552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36424088478088</t>
   </si>
   <si>
     <t xml:space="preserve">3.68919610977173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72742629051208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7083113193512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5745062828064</t>
+    <t xml:space="preserve">3.72742652893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70831108093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57450604438782</t>
   </si>
   <si>
     <t xml:space="preserve">3.55539131164551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51716089248657</t>
+    <t xml:space="preserve">3.51716136932373</t>
   </si>
   <si>
     <t xml:space="preserve">3.63185119628906</t>
@@ -767,10 +767,10 @@
     <t xml:space="preserve">3.53627634048462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61273598670959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65096640586853</t>
+    <t xml:space="preserve">3.61273622512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65096616744995</t>
   </si>
   <si>
     <t xml:space="preserve">3.24955105781555</t>
@@ -785,46 +785,46 @@
     <t xml:space="preserve">3.30689597129822</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38335633277893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59362101554871</t>
+    <t xml:space="preserve">3.38335585594177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59362125396729</t>
   </si>
   <si>
     <t xml:space="preserve">3.47893118858337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49804592132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28778123855591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67008137702942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80388617515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93769097328186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03326559066772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18618726730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30087614059448</t>
+    <t xml:space="preserve">3.49804615974426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28778100013733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67008113861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80388641357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93769145011902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03326606750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18618679046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30087661743164</t>
   </si>
   <si>
     <t xml:space="preserve">4.5302562713623</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51114082336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58760166168213</t>
+    <t xml:space="preserve">4.51114177703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58760213851929</t>
   </si>
   <si>
     <t xml:space="preserve">4.49202632904053</t>
@@ -833,34 +833,34 @@
     <t xml:space="preserve">4.43468141555786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62583160400391</t>
+    <t xml:space="preserve">4.62583208084106</t>
   </si>
   <si>
     <t xml:space="preserve">4.74052143096924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75963687896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7022910118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68317651748657</t>
+    <t xml:space="preserve">4.75963592529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70229196548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68317604064941</t>
   </si>
   <si>
     <t xml:space="preserve">4.77875185012817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5684871673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66406202316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72140645980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87432670593262</t>
+    <t xml:space="preserve">4.56848621368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66406154632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72140598297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87432622909546</t>
   </si>
   <si>
     <t xml:space="preserve">4.96990156173706</t>
@@ -869,10 +869,10 @@
     <t xml:space="preserve">4.92211484909058</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11326456069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16105175018311</t>
+    <t xml:space="preserve">5.1132640838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16105222702026</t>
   </si>
   <si>
     <t xml:space="preserve">5.20883893966675</t>
@@ -881,13 +881,13 @@
     <t xml:space="preserve">5.25662660598755</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30441379547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44777631759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63892650604248</t>
+    <t xml:space="preserve">5.30441427230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44777679443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63892698287964</t>
   </si>
   <si>
     <t xml:space="preserve">5.59113931655884</t>
@@ -899,52 +899,52 @@
     <t xml:space="preserve">5.71643781661987</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42577171325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1351056098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8444390296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8250617980957</t>
+    <t xml:space="preserve">5.42577123641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13510513305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84443855285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82506084442139</t>
   </si>
   <si>
     <t xml:space="preserve">4.80568313598633</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59252834320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55377197265625</t>
+    <t xml:space="preserve">4.59252786636353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55377292633057</t>
   </si>
   <si>
     <t xml:space="preserve">4.76692771911621</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03821611404419</t>
+    <t xml:space="preserve">5.03821563720703</t>
   </si>
   <si>
     <t xml:space="preserve">4.9897723197937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08666086196899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18354988098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9413275718689</t>
+    <t xml:space="preserve">5.08666038513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18354940414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94132709503174</t>
   </si>
   <si>
     <t xml:space="preserve">5.23199415206909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74755001068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28043842315674</t>
+    <t xml:space="preserve">4.74754953384399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28043794631958</t>
   </si>
   <si>
     <t xml:space="preserve">4.89288330078125</t>
@@ -956,13 +956,13 @@
     <t xml:space="preserve">4.53439521789551</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67003870010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78630590438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72817325592041</t>
+    <t xml:space="preserve">4.67003917694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78630542755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72817230224609</t>
   </si>
   <si>
     <t xml:space="preserve">4.70879459381104</t>
@@ -971,25 +971,25 @@
     <t xml:space="preserve">5.91021537780762</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61954927444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32888317108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37732744216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57110500335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47421646118164</t>
+    <t xml:space="preserve">5.61954879760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32888269424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37732696533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57110452651978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47421598434448</t>
   </si>
   <si>
     <t xml:space="preserve">5.66799354553223</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7337703704834</t>
+    <t xml:space="preserve">6.73376941680908</t>
   </si>
   <si>
     <t xml:space="preserve">6.29777050018311</t>
@@ -1004,13 +1004,13 @@
     <t xml:space="preserve">6.5884370803833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63688135147095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2493257522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34621524810791</t>
+    <t xml:space="preserve">6.63688087463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24932622909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34621572494507</t>
   </si>
   <si>
     <t xml:space="preserve">6.53999280929565</t>
@@ -1019,7 +1019,7 @@
     <t xml:space="preserve">6.39465951919556</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71998977661133</t>
+    <t xml:space="preserve">8.71999073028564</t>
   </si>
   <si>
     <t xml:space="preserve">7.993323802948</t>
@@ -1028,37 +1028,37 @@
     <t xml:space="preserve">8.09021472930908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04176807403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94487953186035</t>
+    <t xml:space="preserve">8.04176902770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94488000869751</t>
   </si>
   <si>
     <t xml:space="preserve">7.84799098968506</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89643573760986</t>
+    <t xml:space="preserve">7.89643526077271</t>
   </si>
   <si>
     <t xml:space="preserve">8.38087844848633</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2702112197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88265514373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.173321723938</t>
+    <t xml:space="preserve">10.2702102661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88265419006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1733207702637</t>
   </si>
   <si>
     <t xml:space="preserve">9.9795446395874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0764322280884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2390985488892</t>
+    <t xml:space="preserve">10.0764312744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2390975952148</t>
   </si>
   <si>
     <t xml:space="preserve">11.6266536712646</t>
@@ -1067,19 +1067,19 @@
     <t xml:space="preserve">13.0799856185913</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2737627029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9830961227417</t>
+    <t xml:space="preserve">13.2737617492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.983097076416</t>
   </si>
   <si>
     <t xml:space="preserve">14.4364280700684</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3395395278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0177602767944</t>
+    <t xml:space="preserve">14.3395404815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0177621841431</t>
   </si>
   <si>
     <t xml:space="preserve">16.1669788360596</t>
@@ -1088,10 +1088,10 @@
     <t xml:space="preserve">15.1930656433105</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0956735610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9008913040161</t>
+    <t xml:space="preserve">15.0956745147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9008903503418</t>
   </si>
   <si>
     <t xml:space="preserve">13.634801864624</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">14.0243673324585</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2191514968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8034992218018</t>
+    <t xml:space="preserve">14.2191524505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8035001754761</t>
   </si>
   <si>
     <t xml:space="preserve">14.4139337539673</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">14.7061080932617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5113248825073</t>
+    <t xml:space="preserve">14.5113258361816</t>
   </si>
   <si>
     <t xml:space="preserve">13.3426275253296</t>
@@ -1145,16 +1145,16 @@
     <t xml:space="preserve">13.537410736084</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2452363967896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8556709289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3687133789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.758279800415</t>
+    <t xml:space="preserve">13.2452373504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8556699752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3687143325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7582807540894</t>
   </si>
   <si>
     <t xml:space="preserve">12.5634956359863</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">12.1739311218262</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6869735717773</t>
+    <t xml:space="preserve">11.686972618103</t>
   </si>
   <si>
     <t xml:space="preserve">11.1026248931885</t>
@@ -1172,22 +1172,22 @@
     <t xml:space="preserve">9.93392658233643</t>
   </si>
   <si>
-    <t xml:space="preserve">10.713059425354</t>
+    <t xml:space="preserve">10.7130584716797</t>
   </si>
   <si>
     <t xml:space="preserve">11.2000160217285</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9791479110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8817558288574</t>
+    <t xml:space="preserve">11.9791469573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8817567825317</t>
   </si>
   <si>
     <t xml:space="preserve">10.9078416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2974081039429</t>
+    <t xml:space="preserve">11.2974061965942</t>
   </si>
   <si>
     <t xml:space="preserve">11.3947992324829</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">11.589581489563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0052337646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7843656539917</t>
+    <t xml:space="preserve">11.0052318572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7843647003174</t>
   </si>
   <si>
     <t xml:space="preserve">11.4921903610229</t>
@@ -1208,19 +1208,19 @@
     <t xml:space="preserve">10.810450553894</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4208850860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2261018753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3234939575195</t>
+    <t xml:space="preserve">10.4208841323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2261009216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3234930038452</t>
   </si>
   <si>
     <t xml:space="preserve">10.1287097930908</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0313186645508</t>
+    <t xml:space="preserve">10.0313196182251</t>
   </si>
   <si>
     <t xml:space="preserve">9.73914432525635</t>
@@ -1244,40 +1244,40 @@
     <t xml:space="preserve">12.9530620574951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6800222396851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7321939468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1704559326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3652391433716</t>
+    <t xml:space="preserve">15.6800231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7321949005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1704549789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3652381896973</t>
   </si>
   <si>
     <t xml:space="preserve">14.0730628967285</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1443700790405</t>
+    <t xml:space="preserve">15.1443691253662</t>
   </si>
   <si>
     <t xml:space="preserve">15.5364561080933</t>
   </si>
   <si>
-    <t xml:space="preserve">15.585467338562</t>
+    <t xml:space="preserve">15.5854682922363</t>
   </si>
   <si>
     <t xml:space="preserve">15.6344785690308</t>
   </si>
   <si>
-    <t xml:space="preserve">15.193380355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4874458312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4384355545044</t>
+    <t xml:space="preserve">15.1933813095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4874448776245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4384346008301</t>
   </si>
   <si>
     <t xml:space="preserve">15.2423915863037</t>
@@ -1295,46 +1295,46 @@
     <t xml:space="preserve">15.0463485717773</t>
   </si>
   <si>
-    <t xml:space="preserve">14.654260635376</t>
+    <t xml:space="preserve">14.6542596817017</t>
   </si>
   <si>
     <t xml:space="preserve">13.9190969467163</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1641502380371</t>
+    <t xml:space="preserve">14.1641511917114</t>
   </si>
   <si>
     <t xml:space="preserve">13.7230529785156</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8210754394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3601942062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6250314712524</t>
+    <t xml:space="preserve">13.8210763931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3601951599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6250305175781</t>
   </si>
   <si>
     <t xml:space="preserve">13.8700857162476</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6740427017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7720642089844</t>
+    <t xml:space="preserve">13.6740417480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7720651626587</t>
   </si>
   <si>
     <t xml:space="preserve">14.0171184539795</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1839323043823</t>
+    <t xml:space="preserve">13.1839332580566</t>
   </si>
   <si>
     <t xml:space="preserve">13.5270099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9483251571655</t>
+    <t xml:space="preserve">14.9483261108398</t>
   </si>
   <si>
     <t xml:space="preserve">14.4092054367065</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">14.7032709121704</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5562381744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.507227897644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0661306381226</t>
+    <t xml:space="preserve">14.5562391281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5072288513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0661296844482</t>
   </si>
   <si>
     <t xml:space="preserve">13.3309659957886</t>
@@ -1367,10 +1367,10 @@
     <t xml:space="preserve">13.4779987335205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2819557189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8898677825928</t>
+    <t xml:space="preserve">13.2819547653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8898668289185</t>
   </si>
   <si>
     <t xml:space="preserve">12.7428350448608</t>
@@ -1379,13 +1379,13 @@
     <t xml:space="preserve">12.987889289856</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1349220275879</t>
+    <t xml:space="preserve">13.1349229812622</t>
   </si>
   <si>
     <t xml:space="preserve">12.3507480621338</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7626171112061</t>
+    <t xml:space="preserve">11.7626161575317</t>
   </si>
   <si>
     <t xml:space="preserve">11.3215198516846</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">12.3017377853394</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0859127044678</t>
+    <t xml:space="preserve">13.0859117507935</t>
   </si>
   <si>
     <t xml:space="preserve">13.4289875030518</t>
@@ -1403,16 +1403,16 @@
     <t xml:space="preserve">15.8305215835571</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7324991226196</t>
+    <t xml:space="preserve">15.7325000762939</t>
   </si>
   <si>
     <t xml:space="preserve">15.8795328140259</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9775552749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3696441650391</t>
+    <t xml:space="preserve">15.9775543212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3696422576904</t>
   </si>
   <si>
     <t xml:space="preserve">15.6834897994995</t>
@@ -1430,7 +1430,7 @@
     <t xml:space="preserve">16.0755767822266</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9285440444946</t>
+    <t xml:space="preserve">15.9285449981689</t>
   </si>
   <si>
     <t xml:space="preserve">16.1735973358154</t>
@@ -1439,13 +1439,13 @@
     <t xml:space="preserve">16.2716197967529</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3206310272217</t>
+    <t xml:space="preserve">16.320629119873</t>
   </si>
   <si>
     <t xml:space="preserve">18.7221660614014</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0162296295166</t>
+    <t xml:space="preserve">19.0162315368652</t>
   </si>
   <si>
     <t xml:space="preserve">19.7023830413818</t>
@@ -1460,31 +1460,31 @@
     <t xml:space="preserve">20.0944690704346</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9173202514648</t>
+    <t xml:space="preserve">23.9173221588135</t>
   </si>
   <si>
     <t xml:space="preserve">22.545015335083</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5252342224121</t>
+    <t xml:space="preserve">23.5252323150635</t>
   </si>
   <si>
     <t xml:space="preserve">24.7995166778564</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2311687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7806243896484</t>
+    <t xml:space="preserve">23.2311706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7806224822998</t>
   </si>
   <si>
     <t xml:space="preserve">21.1727104187012</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4865570068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6826038360596</t>
+    <t xml:space="preserve">20.4865589141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6826019287109</t>
   </si>
   <si>
     <t xml:space="preserve">21.3687534332275</t>
@@ -1493,10 +1493,10 @@
     <t xml:space="preserve">22.6430397033691</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9955615997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2896251678467</t>
+    <t xml:space="preserve">24.9955596923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2896270751953</t>
   </si>
   <si>
     <t xml:space="preserve">24.6034755706787</t>
@@ -1505,16 +1505,16 @@
     <t xml:space="preserve">24.8975391387939</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5054531097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0153427124023</t>
+    <t xml:space="preserve">24.5054512023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.015344619751</t>
   </si>
   <si>
     <t xml:space="preserve">23.623254776001</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8390789031982</t>
+    <t xml:space="preserve">22.8390808105469</t>
   </si>
   <si>
     <t xml:space="preserve">23.3291893005371</t>
@@ -1523,16 +1523,16 @@
     <t xml:space="preserve">22.9371032714844</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7212791442871</t>
+    <t xml:space="preserve">23.7212772369385</t>
   </si>
   <si>
     <t xml:space="preserve">24.1133651733398</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0351257324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1331462860107</t>
+    <t xml:space="preserve">23.0351238250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1331481933594</t>
   </si>
   <si>
     <t xml:space="preserve">24.2113876342773</t>
@@ -1544,22 +1544,22 @@
     <t xml:space="preserve">23.819299697876</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2509517669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7608413696289</t>
+    <t xml:space="preserve">22.2509498596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7608432769775</t>
   </si>
   <si>
     <t xml:space="preserve">21.9568843841553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1529293060303</t>
+    <t xml:space="preserve">22.1529273986816</t>
   </si>
   <si>
     <t xml:space="preserve">18.7711753845215</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3300800323486</t>
+    <t xml:space="preserve">18.330078125</t>
   </si>
   <si>
     <t xml:space="preserve">17.6439247131348</t>
@@ -1568,19 +1568,19 @@
     <t xml:space="preserve">18.5261211395264</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9964485168457</t>
+    <t xml:space="preserve">19.9964466094971</t>
   </si>
   <si>
     <t xml:space="preserve">20.5845794677734</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1924934387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8984279632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3885345458984</t>
+    <t xml:space="preserve">20.1924953460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8984260559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3885364532471</t>
   </si>
   <si>
     <t xml:space="preserve">19.4049549102783</t>
@@ -1595,10 +1595,10 @@
     <t xml:space="preserve">19.5527095794678</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7989654541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.601957321167</t>
+    <t xml:space="preserve">19.7989635467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6019592285156</t>
   </si>
   <si>
     <t xml:space="preserve">18.9616947174072</t>
@@ -1628,13 +1628,13 @@
     <t xml:space="preserve">20.4884796142578</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5869808197021</t>
+    <t xml:space="preserve">20.5869827270508</t>
   </si>
   <si>
     <t xml:space="preserve">19.9959678649902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4542064666748</t>
+    <t xml:space="preserve">19.4542045593262</t>
   </si>
   <si>
     <t xml:space="preserve">19.5034561157227</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">19.207950592041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0259208679199</t>
+    <t xml:space="preserve">18.0259227752686</t>
   </si>
   <si>
     <t xml:space="preserve">18.075174331665</t>
@@ -1670,19 +1670,19 @@
     <t xml:space="preserve">17.9274196624756</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9766712188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.434907913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1736755371094</t>
+    <t xml:space="preserve">17.9766693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4349098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.173677444458</t>
   </si>
   <si>
     <t xml:space="preserve">18.4199314117432</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7839889526367</t>
+    <t xml:space="preserve">20.7839870452881</t>
   </si>
   <si>
     <t xml:space="preserve">20.3899784088135</t>
@@ -1691,10 +1691,10 @@
     <t xml:space="preserve">19.7004623413086</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9124431610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1094455718994</t>
+    <t xml:space="preserve">18.9124450683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.109447479248</t>
   </si>
   <si>
     <t xml:space="preserve">18.8631916046143</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">18.5184326171875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7154388427734</t>
+    <t xml:space="preserve">18.7154369354248</t>
   </si>
   <si>
     <t xml:space="preserve">18.2229270935059</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">17.7796649932861</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5676860809326</t>
+    <t xml:space="preserve">18.567684173584</t>
   </si>
   <si>
     <t xml:space="preserve">17.7304153442383</t>
@@ -1724,16 +1724,16 @@
     <t xml:space="preserve">18.2721767425537</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6811637878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8781700134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1244258880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6319141387939</t>
+    <t xml:space="preserve">17.6811656951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8781681060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1244239807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6319122314453</t>
   </si>
   <si>
     <t xml:space="preserve">17.4841594696045</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">17.3856582641602</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5334091186523</t>
+    <t xml:space="preserve">17.533411026001</t>
   </si>
   <si>
     <t xml:space="preserve">17.1886520385742</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">16.4991359710693</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8931465148926</t>
+    <t xml:space="preserve">16.8931446075439</t>
   </si>
   <si>
     <t xml:space="preserve">16.4498863220215</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">16.6468906402588</t>
   </si>
   <si>
-    <t xml:space="preserve">16.794641494751</t>
+    <t xml:space="preserve">16.7946434020996</t>
   </si>
   <si>
     <t xml:space="preserve">16.7453918457031</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">14.6275930404663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9723501205444</t>
+    <t xml:space="preserve">14.9723510742188</t>
   </si>
   <si>
     <t xml:space="preserve">14.7260942459106</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">15.1201047897339</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3663597106934</t>
+    <t xml:space="preserve">15.3663606643677</t>
   </si>
   <si>
     <t xml:space="preserve">15.464861869812</t>
@@ -1805,16 +1805,16 @@
     <t xml:space="preserve">14.7753458023071</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4798393249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2828340530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5783414840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0858306884766</t>
+    <t xml:space="preserve">14.4798383712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2828350067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5783424377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0858297348022</t>
   </si>
   <si>
     <t xml:space="preserve">14.2335834503174</t>
@@ -57331,25 +57331,25 @@
     </row>
     <row r="2111">
       <c r="A2111" s="1" t="n">
-        <v>45967.618912037</v>
+        <v>45968.5900578704</v>
       </c>
       <c r="B2111" t="n">
-        <v>750</v>
+        <v>875</v>
       </c>
       <c r="C2111" t="n">
-        <v>14.3999996185303</v>
+        <v>13.8999996185303</v>
       </c>
       <c r="D2111" t="n">
-        <v>14</v>
+        <v>13.6000003814697</v>
       </c>
       <c r="E2111" t="n">
-        <v>14.3999996185303</v>
+        <v>13.8999996185303</v>
       </c>
       <c r="F2111" t="n">
-        <v>14.1999998092651</v>
+        <v>13.8000001907349</v>
       </c>
       <c r="G2111" t="s">
-        <v>702</v>
+        <v>661</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>

--- a/data/CULT.MI.xlsx
+++ b/data/CULT.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68585348129272</t>
+    <t xml:space="preserve">4.68585252761841</t>
   </si>
   <si>
     <t xml:space="preserve">CULT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57666683197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5948657989502</t>
+    <t xml:space="preserve">4.57666730880737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59486484527588</t>
   </si>
   <si>
     <t xml:space="preserve">4.60851383209229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58576583862305</t>
+    <t xml:space="preserve">4.58576679229736</t>
   </si>
   <si>
     <t xml:space="preserve">4.48931932449341</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56301927566528</t>
+    <t xml:space="preserve">4.56301879882812</t>
   </si>
   <si>
     <t xml:space="preserve">4.51297616958618</t>
@@ -68,94 +68,94 @@
     <t xml:space="preserve">4.46020364761353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29824542999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21271800994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18178272247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23091554641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36375713348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38195466995239</t>
+    <t xml:space="preserve">4.29824638366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21271848678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18178224563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23091506958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36375665664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38195419311523</t>
   </si>
   <si>
     <t xml:space="preserve">4.35101890563965</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28914737701416</t>
+    <t xml:space="preserve">4.289146900177</t>
   </si>
   <si>
     <t xml:space="preserve">4.24183416366577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22909498214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10535383224487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09443473815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1089916229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99616765975952</t>
+    <t xml:space="preserve">4.22909593582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10535287857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09443378448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10899209976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9961678981781</t>
   </si>
   <si>
     <t xml:space="preserve">4.04712057113647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03984212875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96341228485107</t>
+    <t xml:space="preserve">4.0398416519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9634120464325</t>
   </si>
   <si>
     <t xml:space="preserve">4.07441711425781</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32008361816406</t>
+    <t xml:space="preserve">4.32008266448975</t>
   </si>
   <si>
     <t xml:space="preserve">4.24911260604858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97978973388672</t>
+    <t xml:space="preserve">3.97979021072388</t>
   </si>
   <si>
     <t xml:space="preserve">4.06895780563354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0543999671936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98524951934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05076026916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07259750366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03802251815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04530143737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03074216842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01254558563232</t>
+    <t xml:space="preserve">4.05439901351929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98524880409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0507607460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07259798049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03802347183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04530096054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03074312210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01254606246948</t>
   </si>
   <si>
     <t xml:space="preserve">4.04894065856934</t>
@@ -164,55 +164,55 @@
     <t xml:space="preserve">4.05985879898071</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07623672485352</t>
+    <t xml:space="preserve">4.07623720169067</t>
   </si>
   <si>
     <t xml:space="preserve">3.91245913505554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99070930480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01072597503662</t>
+    <t xml:space="preserve">3.99070858955383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01072645187378</t>
   </si>
   <si>
     <t xml:space="preserve">3.92155814170837</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00162744522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05803871154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21635770797729</t>
+    <t xml:space="preserve">4.00162649154663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05803918838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21635675430298</t>
   </si>
   <si>
     <t xml:space="preserve">4.2218165397644</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18542146682739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16176462173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35465717315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28186845779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26731014251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39287328720093</t>
+    <t xml:space="preserve">4.18542098999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16176557540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35465812683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28186798095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26731061935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39287281036377</t>
   </si>
   <si>
     <t xml:space="preserve">4.36739683151245</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17814159393311</t>
+    <t xml:space="preserve">4.17814302444458</t>
   </si>
   <si>
     <t xml:space="preserve">4.27458953857422</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">4.3182635307312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35647773742676</t>
+    <t xml:space="preserve">4.35647821426392</t>
   </si>
   <si>
     <t xml:space="preserve">4.26549053192139</t>
@@ -236,28 +236,28 @@
     <t xml:space="preserve">4.14902639389038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35829830169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35283756256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29460668563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2036190032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24001359939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34010076522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42926788330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3491997718811</t>
+    <t xml:space="preserve">4.35829782485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35283851623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29460573196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20361852645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24001407623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34010028839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42926836013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34919881820679</t>
   </si>
   <si>
     <t xml:space="preserve">4.33646106719971</t>
@@ -266,61 +266,61 @@
     <t xml:space="preserve">4.33100175857544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32190179824829</t>
+    <t xml:space="preserve">4.32190227508545</t>
   </si>
   <si>
     <t xml:space="preserve">4.4674825668335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45838403701782</t>
+    <t xml:space="preserve">4.45838356018066</t>
   </si>
   <si>
     <t xml:space="preserve">4.2855076789856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83057022094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90336036682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88516354560852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87606430053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00344657897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93065738677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99434781074524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08533525466919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96705150604248</t>
+    <t xml:space="preserve">3.83057069778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90336060523987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88516330718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87606453895569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00344705581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93065643310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9943482875824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08533573150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96705174446106</t>
   </si>
   <si>
     <t xml:space="preserve">3.86696553230286</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84876847267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8578667640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81237292289734</t>
+    <t xml:space="preserve">3.84876775741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85786652565002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81237316131592</t>
   </si>
   <si>
     <t xml:space="preserve">3.80327439308167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77597832679749</t>
+    <t xml:space="preserve">3.77597808837891</t>
   </si>
   <si>
     <t xml:space="preserve">3.97615051269531</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">4.16722393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33528327941895</t>
+    <t xml:space="preserve">4.33528232574463</t>
   </si>
   <si>
     <t xml:space="preserve">4.21485948562622</t>
@@ -344,25 +344,25 @@
     <t xml:space="preserve">4.31675672531128</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42791795730591</t>
+    <t xml:space="preserve">4.42791748046875</t>
   </si>
   <si>
     <t xml:space="preserve">4.19633197784424</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16854190826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29823017120361</t>
+    <t xml:space="preserve">4.168541431427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29822969436646</t>
   </si>
   <si>
     <t xml:space="preserve">4.30749273300171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27970266342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3908634185791</t>
+    <t xml:space="preserve">4.27970218658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39086389541626</t>
   </si>
   <si>
     <t xml:space="preserve">4.40012693405151</t>
@@ -371,19 +371,19 @@
     <t xml:space="preserve">4.35381031036377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08517074584961</t>
+    <t xml:space="preserve">4.08517122268677</t>
   </si>
   <si>
     <t xml:space="preserve">3.93695592880249</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00180053710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9740092754364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03885412216187</t>
+    <t xml:space="preserve">4.00179958343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97400975227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03885364532471</t>
   </si>
   <si>
     <t xml:space="preserve">3.94621968269348</t>
@@ -395,67 +395,67 @@
     <t xml:space="preserve">4.23338556289673</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22412252426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24264860153198</t>
+    <t xml:space="preserve">4.22412204742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24264907836914</t>
   </si>
   <si>
     <t xml:space="preserve">4.11296081542969</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26117563247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91842985153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89990210533142</t>
+    <t xml:space="preserve">4.26117515563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91842889785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89990234375</t>
   </si>
   <si>
     <t xml:space="preserve">3.89063858985901</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07590675354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06664371490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79800486564636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73316121101379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86284875869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71463418006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7053701877594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77021455764771</t>
+    <t xml:space="preserve">4.07590770721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06664419174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7980043888092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73316049575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86284852027893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71463394165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70537042617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77021431922913</t>
   </si>
   <si>
     <t xml:space="preserve">3.3904139995575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44599437713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58494591712952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68684339523315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60347294807434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52010202407837</t>
+    <t xml:space="preserve">3.44599485397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58494567871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68684363365173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60347270965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52010178565979</t>
   </si>
   <si>
     <t xml:space="preserve">3.37188720703125</t>
@@ -464,28 +464,28 @@
     <t xml:space="preserve">3.46452116966248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53862857818604</t>
+    <t xml:space="preserve">3.53862881660461</t>
   </si>
   <si>
     <t xml:space="preserve">3.5293653011322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45525813102722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34409642219543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07545781135559</t>
+    <t xml:space="preserve">3.45525765419006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34409689903259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07545733451843</t>
   </si>
   <si>
     <t xml:space="preserve">3.14956498146057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29777956008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31630659103394</t>
+    <t xml:space="preserve">3.29777979850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31630635261536</t>
   </si>
   <si>
     <t xml:space="preserve">3.23293566703796</t>
@@ -500,34 +500,34 @@
     <t xml:space="preserve">3.20514559745789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25146293640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10324764251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1588282585144</t>
+    <t xml:space="preserve">3.25146269798279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10324740409851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15882849693298</t>
   </si>
   <si>
     <t xml:space="preserve">2.9179790019989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74197387695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77902770042419</t>
+    <t xml:space="preserve">2.74197435379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77902793884277</t>
   </si>
   <si>
     <t xml:space="preserve">2.87166213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96429634094238</t>
+    <t xml:space="preserve">2.9642961025238</t>
   </si>
   <si>
     <t xml:space="preserve">2.85313510894775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83460855484009</t>
+    <t xml:space="preserve">2.83460807800293</t>
   </si>
   <si>
     <t xml:space="preserve">2.84387183189392</t>
@@ -542,58 +542,58 @@
     <t xml:space="preserve">2.76976442337036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63081336021423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67713022232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38070034980774</t>
+    <t xml:space="preserve">2.63081312179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67713046073914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38070011138916</t>
   </si>
   <si>
     <t xml:space="preserve">2.36217355728149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29732942581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31585669517517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35291004180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26953935623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23248553276062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28806638717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08427095413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1305878162384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22322225570679</t>
+    <t xml:space="preserve">2.29732966423035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31585645675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35291028022766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26953911781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2324857711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28806662559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0842707157135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13058757781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22322249412537</t>
   </si>
   <si>
     <t xml:space="preserve">2.24174928665161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11206126213074</t>
+    <t xml:space="preserve">2.11206102371216</t>
   </si>
   <si>
     <t xml:space="preserve">2.17690515518188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03795337677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99163663387299</t>
+    <t xml:space="preserve">2.03795385360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9916365146637</t>
   </si>
   <si>
     <t xml:space="preserve">1.88047552108765</t>
@@ -602,52 +602,52 @@
     <t xml:space="preserve">1.9453192949295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92679262161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16764163970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13985133171082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21395897865295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4084906578064</t>
+    <t xml:space="preserve">1.92679250240326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16764116287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13985109329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21395874023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40849089622498</t>
   </si>
   <si>
     <t xml:space="preserve">2.48259806632996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42701745033264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38996386528015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46583557128906</t>
+    <t xml:space="preserve">2.42701768875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38996410369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46583604812622</t>
   </si>
   <si>
     <t xml:space="preserve">2.50406551361084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65698599815369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71433091163635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54229617118835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58052611351013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52318120002747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42760586738586</t>
+    <t xml:space="preserve">2.65698552131653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71433067321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54229593276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58052587509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52318096160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42760610580444</t>
   </si>
   <si>
     <t xml:space="preserve">2.38937592506409</t>
@@ -656,28 +656,28 @@
     <t xml:space="preserve">2.48495078086853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61875605583191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56141138076782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6378710269928</t>
+    <t xml:space="preserve">2.61875581741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56141066551208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63787078857422</t>
   </si>
   <si>
     <t xml:space="preserve">2.73344588279724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69521594047546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75256109237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80990600585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82902073860168</t>
+    <t xml:space="preserve">2.69521570205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75256085395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80990552902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82902097702026</t>
   </si>
   <si>
     <t xml:space="preserve">2.84813594818115</t>
@@ -686,19 +686,19 @@
     <t xml:space="preserve">3.05840086936951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86725068092346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7716760635376</t>
+    <t xml:space="preserve">2.86725091934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77167582511902</t>
   </si>
   <si>
     <t xml:space="preserve">2.67610096931458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59964108467102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44672060012817</t>
+    <t xml:space="preserve">2.59964060783386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44672083854675</t>
   </si>
   <si>
     <t xml:space="preserve">2.37026071548462</t>
@@ -713,13 +713,13 @@
     <t xml:space="preserve">3.45981597900391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74654126167297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76565647125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01415109634399</t>
+    <t xml:space="preserve">3.74654150009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76565623283386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01415157318115</t>
   </si>
   <si>
     <t xml:space="preserve">4.1097264289856</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">3.88034629821777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82300114631653</t>
+    <t xml:space="preserve">3.82300138473511</t>
   </si>
   <si>
     <t xml:space="preserve">3.44070100784302</t>
@@ -746,19 +746,19 @@
     <t xml:space="preserve">3.68919610977173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72742652893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70831108093262</t>
+    <t xml:space="preserve">3.72742629051208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70831155776978</t>
   </si>
   <si>
     <t xml:space="preserve">3.57450604438782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55539131164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51716136932373</t>
+    <t xml:space="preserve">3.55539107322693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51716089248657</t>
   </si>
   <si>
     <t xml:space="preserve">3.63185119628906</t>
@@ -770,67 +770,67 @@
     <t xml:space="preserve">3.61273622512817</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65096616744995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24955105781555</t>
+    <t xml:space="preserve">3.65096592903137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24955129623413</t>
   </si>
   <si>
     <t xml:space="preserve">3.32601094245911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42158579826355</t>
+    <t xml:space="preserve">3.42158603668213</t>
   </si>
   <si>
     <t xml:space="preserve">3.30689597129822</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38335585594177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59362125396729</t>
+    <t xml:space="preserve">3.38335633277893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59362149238586</t>
   </si>
   <si>
     <t xml:space="preserve">3.47893118858337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49804615974426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28778100013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67008113861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80388641357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93769145011902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03326606750488</t>
+    <t xml:space="preserve">3.49804639816284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28778123855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67008090019226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80388617515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9376916885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03326559066772</t>
   </si>
   <si>
     <t xml:space="preserve">4.18618679046631</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30087661743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5302562713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51114177703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58760213851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49202632904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43468141555786</t>
+    <t xml:space="preserve">4.30087614059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53025579452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51114130020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58760166168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49202585220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43468189239502</t>
   </si>
   <si>
     <t xml:space="preserve">4.62583208084106</t>
@@ -842,10 +842,10 @@
     <t xml:space="preserve">4.75963592529297</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70229196548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68317604064941</t>
+    <t xml:space="preserve">4.70229148864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68317699432373</t>
   </si>
   <si>
     <t xml:space="preserve">4.77875185012817</t>
@@ -854,10 +854,10 @@
     <t xml:space="preserve">4.56848621368408</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66406154632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72140598297119</t>
+    <t xml:space="preserve">4.66406202316284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72140693664551</t>
   </si>
   <si>
     <t xml:space="preserve">4.87432622909546</t>
@@ -866,16 +866,16 @@
     <t xml:space="preserve">4.96990156173706</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92211484909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1132640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16105222702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20883893966675</t>
+    <t xml:space="preserve">4.92211437225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11326360702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16105175018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20883941650391</t>
   </si>
   <si>
     <t xml:space="preserve">5.25662660598755</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">5.30441427230835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44777679443359</t>
+    <t xml:space="preserve">5.44777631759644</t>
   </si>
   <si>
     <t xml:space="preserve">5.63892698287964</t>
@@ -896,16 +896,16 @@
     <t xml:space="preserve">5.81332683563232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71643781661987</t>
+    <t xml:space="preserve">5.71643829345703</t>
   </si>
   <si>
     <t xml:space="preserve">5.42577123641968</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13510513305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84443855285645</t>
+    <t xml:space="preserve">5.1351056098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8444390296936</t>
   </si>
   <si>
     <t xml:space="preserve">4.82506084442139</t>
@@ -917,55 +917,55 @@
     <t xml:space="preserve">4.59252786636353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55377292633057</t>
+    <t xml:space="preserve">4.55377197265625</t>
   </si>
   <si>
     <t xml:space="preserve">4.76692771911621</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03821563720703</t>
+    <t xml:space="preserve">5.03821659088135</t>
   </si>
   <si>
     <t xml:space="preserve">4.9897723197937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08666038513184</t>
+    <t xml:space="preserve">5.08666086196899</t>
   </si>
   <si>
     <t xml:space="preserve">5.18354940414429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94132709503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23199415206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74754953384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28043794631958</t>
+    <t xml:space="preserve">4.9413275718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23199462890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74755001068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2804388999939</t>
   </si>
   <si>
     <t xml:space="preserve">4.89288330078125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63128423690796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53439521789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67003917694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78630542755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72817230224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70879459381104</t>
+    <t xml:space="preserve">4.6312837600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53439474105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67003965377808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78630638122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72817277908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70879507064819</t>
   </si>
   <si>
     <t xml:space="preserve">5.91021537780762</t>
@@ -977,10 +977,10 @@
     <t xml:space="preserve">5.32888269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37732696533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57110452651978</t>
+    <t xml:space="preserve">5.37732744216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57110500335693</t>
   </si>
   <si>
     <t xml:space="preserve">5.47421598434448</t>
@@ -998,10 +998,10 @@
     <t xml:space="preserve">6.4431037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68532609939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5884370803833</t>
+    <t xml:space="preserve">6.68532562255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58843755722046</t>
   </si>
   <si>
     <t xml:space="preserve">6.63688087463379</t>
@@ -1010,52 +1010,52 @@
     <t xml:space="preserve">6.24932622909546</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34621572494507</t>
+    <t xml:space="preserve">6.34621524810791</t>
   </si>
   <si>
     <t xml:space="preserve">6.53999280929565</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39465951919556</t>
+    <t xml:space="preserve">6.3946590423584</t>
   </si>
   <si>
     <t xml:space="preserve">8.71999073028564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.993323802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09021472930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04176902770996</t>
+    <t xml:space="preserve">7.99332523345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09021377563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04176807403564</t>
   </si>
   <si>
     <t xml:space="preserve">7.94488000869751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84799098968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89643526077271</t>
+    <t xml:space="preserve">7.84799194335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89643621444702</t>
   </si>
   <si>
     <t xml:space="preserve">8.38087844848633</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2702102661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88265419006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1733207702637</t>
+    <t xml:space="preserve">10.2702112197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88265514373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.173321723938</t>
   </si>
   <si>
     <t xml:space="preserve">9.9795446395874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0764312744141</t>
+    <t xml:space="preserve">10.0764331817627</t>
   </si>
   <si>
     <t xml:space="preserve">11.2390975952148</t>
@@ -1070,16 +1070,16 @@
     <t xml:space="preserve">13.2737617492676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.983097076416</t>
+    <t xml:space="preserve">12.9830951690674</t>
   </si>
   <si>
     <t xml:space="preserve">14.4364280700684</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3395404815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0177621841431</t>
+    <t xml:space="preserve">14.3395385742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0177612304688</t>
   </si>
   <si>
     <t xml:space="preserve">16.1669788360596</t>
@@ -1100,13 +1100,13 @@
     <t xml:space="preserve">12.0765390396118</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4661054611206</t>
+    <t xml:space="preserve">12.4661045074463</t>
   </si>
   <si>
     <t xml:space="preserve">13.4400196075439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9269762039185</t>
+    <t xml:space="preserve">13.9269771575928</t>
   </si>
   <si>
     <t xml:space="preserve">14.0243673324585</t>
@@ -1118,16 +1118,16 @@
     <t xml:space="preserve">14.8035001754761</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4139337539673</t>
+    <t xml:space="preserve">14.413932800293</t>
   </si>
   <si>
     <t xml:space="preserve">14.6087160110474</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7061080932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5113258361816</t>
+    <t xml:space="preserve">14.706109046936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5113248825073</t>
   </si>
   <si>
     <t xml:space="preserve">13.3426275253296</t>
@@ -1136,13 +1136,13 @@
     <t xml:space="preserve">14.1217594146729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3165416717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8295850753784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.537410736084</t>
+    <t xml:space="preserve">14.3165426254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8295841217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5374097824097</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452373504639</t>
@@ -1151,58 +1151,58 @@
     <t xml:space="preserve">12.8556699752808</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3687143325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7582807540894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5634956359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1739311218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.686972618103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1026248931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93392658233643</t>
+    <t xml:space="preserve">12.3687133789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7582788467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5634965896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1739301681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6869745254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1026239395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93392753601074</t>
   </si>
   <si>
     <t xml:space="preserve">10.7130584716797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2000160217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9791469573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8817567825317</t>
+    <t xml:space="preserve">11.2000169754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9791479110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8817548751831</t>
   </si>
   <si>
     <t xml:space="preserve">10.9078416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2974061965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3947992324829</t>
+    <t xml:space="preserve">11.2974071502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3947982788086</t>
   </si>
   <si>
     <t xml:space="preserve">11.589581489563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0052318572998</t>
+    <t xml:space="preserve">11.0052328109741</t>
   </si>
   <si>
     <t xml:space="preserve">11.7843647003174</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4921903610229</t>
+    <t xml:space="preserve">11.4921913146973</t>
   </si>
   <si>
     <t xml:space="preserve">10.810450553894</t>
@@ -1214,7 +1214,7 @@
     <t xml:space="preserve">10.2261009216309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3234930038452</t>
+    <t xml:space="preserve">10.3234939575195</t>
   </si>
   <si>
     <t xml:space="preserve">10.1287097930908</t>
@@ -1226,16 +1226,16 @@
     <t xml:space="preserve">9.73914432525635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54436111450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83653545379639</t>
+    <t xml:space="preserve">9.54436206817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8365364074707</t>
   </si>
   <si>
     <t xml:space="preserve">9.34957885742188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49566650390625</t>
+    <t xml:space="preserve">9.49566555023193</t>
   </si>
   <si>
     <t xml:space="preserve">12.2713222503662</t>
@@ -1247,40 +1247,40 @@
     <t xml:space="preserve">15.6800231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7321949005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1704549789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3652381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0730628967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1443691253662</t>
+    <t xml:space="preserve">13.7321939468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1704559326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3652372360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0730638504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1443700790405</t>
   </si>
   <si>
     <t xml:space="preserve">15.5364561080933</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5854682922363</t>
+    <t xml:space="preserve">15.585467338562</t>
   </si>
   <si>
     <t xml:space="preserve">15.6344785690308</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1933813095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4874448776245</t>
+    <t xml:space="preserve">15.193380355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4874458312988</t>
   </si>
   <si>
     <t xml:space="preserve">15.4384346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2423915863037</t>
+    <t xml:space="preserve">15.2423906326294</t>
   </si>
   <si>
     <t xml:space="preserve">15.3894233703613</t>
@@ -1301,22 +1301,22 @@
     <t xml:space="preserve">13.9190969467163</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1641511917114</t>
+    <t xml:space="preserve">14.1641502380371</t>
   </si>
   <si>
     <t xml:space="preserve">13.7230529785156</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8210763931274</t>
+    <t xml:space="preserve">13.8210754394531</t>
   </si>
   <si>
     <t xml:space="preserve">14.3601951599121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6250305175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8700857162476</t>
+    <t xml:space="preserve">13.6250314712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8700847625732</t>
   </si>
   <si>
     <t xml:space="preserve">13.6740417480469</t>
@@ -1328,13 +1328,13 @@
     <t xml:space="preserve">14.0171184539795</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1839332580566</t>
+    <t xml:space="preserve">13.1839323043823</t>
   </si>
   <si>
     <t xml:space="preserve">13.5270099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9483261108398</t>
+    <t xml:space="preserve">14.9483251571655</t>
   </si>
   <si>
     <t xml:space="preserve">14.4092054367065</t>
@@ -1355,10 +1355,10 @@
     <t xml:space="preserve">14.5562391281128</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5072288513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0661296844482</t>
+    <t xml:space="preserve">14.507227897644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0661306381226</t>
   </si>
   <si>
     <t xml:space="preserve">13.3309659957886</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">13.4779987335205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2819547653198</t>
+    <t xml:space="preserve">13.2819557189941</t>
   </si>
   <si>
     <t xml:space="preserve">12.8898668289185</t>
@@ -1376,22 +1376,22 @@
     <t xml:space="preserve">12.7428350448608</t>
   </si>
   <si>
-    <t xml:space="preserve">12.987889289856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1349229812622</t>
+    <t xml:space="preserve">12.9878902435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1349220275879</t>
   </si>
   <si>
     <t xml:space="preserve">12.3507480621338</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7626161575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3215198516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3017377853394</t>
+    <t xml:space="preserve">11.7626171112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3215188980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.301736831665</t>
   </si>
   <si>
     <t xml:space="preserve">13.0859117507935</t>
@@ -1400,16 +1400,16 @@
     <t xml:space="preserve">13.4289875030518</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8305215835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7325000762939</t>
+    <t xml:space="preserve">15.8305225372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7324991226196</t>
   </si>
   <si>
     <t xml:space="preserve">15.8795328140259</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9775543212891</t>
+    <t xml:space="preserve">15.9775552749634</t>
   </si>
   <si>
     <t xml:space="preserve">16.3696422576904</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">15.7815113067627</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2226085662842</t>
+    <t xml:space="preserve">16.2226104736328</t>
   </si>
   <si>
     <t xml:space="preserve">16.0265655517578</t>
@@ -1430,25 +1430,25 @@
     <t xml:space="preserve">16.0755767822266</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9285449981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1735973358154</t>
+    <t xml:space="preserve">15.9285440444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1735992431641</t>
   </si>
   <si>
     <t xml:space="preserve">16.2716197967529</t>
   </si>
   <si>
-    <t xml:space="preserve">16.320629119873</t>
+    <t xml:space="preserve">16.3206310272217</t>
   </si>
   <si>
     <t xml:space="preserve">18.7221660614014</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0162315368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7023830413818</t>
+    <t xml:space="preserve">19.0162296295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7023849487305</t>
   </si>
   <si>
     <t xml:space="preserve">19.604362487793</t>
@@ -1460,52 +1460,52 @@
     <t xml:space="preserve">20.0944690704346</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9173221588135</t>
+    <t xml:space="preserve">23.9173202514648</t>
   </si>
   <si>
     <t xml:space="preserve">22.545015335083</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5252323150635</t>
+    <t xml:space="preserve">23.5252342224121</t>
   </si>
   <si>
     <t xml:space="preserve">24.7995166778564</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2311706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7806224822998</t>
+    <t xml:space="preserve">23.2311687469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7806243896484</t>
   </si>
   <si>
     <t xml:space="preserve">21.1727104187012</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4865589141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6826019287109</t>
+    <t xml:space="preserve">20.4865570068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6826038360596</t>
   </si>
   <si>
     <t xml:space="preserve">21.3687534332275</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6430397033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9955596923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2896270751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6034755706787</t>
+    <t xml:space="preserve">22.6430377960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9955615997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2896251678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6034736633301</t>
   </si>
   <si>
     <t xml:space="preserve">24.8975391387939</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5054512023926</t>
+    <t xml:space="preserve">24.5054531097412</t>
   </si>
   <si>
     <t xml:space="preserve">24.015344619751</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">22.9371032714844</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7212772369385</t>
+    <t xml:space="preserve">23.7212791442871</t>
   </si>
   <si>
     <t xml:space="preserve">24.1133651733398</t>
@@ -1532,28 +1532,28 @@
     <t xml:space="preserve">23.0351238250732</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1331481933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2113876342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4074287414551</t>
+    <t xml:space="preserve">23.1331462860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2113857269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4074306488037</t>
   </si>
   <si>
     <t xml:space="preserve">23.819299697876</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2509498596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7608432769775</t>
+    <t xml:space="preserve">22.2509517669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7608413696289</t>
   </si>
   <si>
     <t xml:space="preserve">21.9568843841553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1529273986816</t>
+    <t xml:space="preserve">22.1529293060303</t>
   </si>
   <si>
     <t xml:space="preserve">18.7711753845215</t>
@@ -1568,19 +1568,19 @@
     <t xml:space="preserve">18.5261211395264</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9964466094971</t>
+    <t xml:space="preserve">19.9964485168457</t>
   </si>
   <si>
     <t xml:space="preserve">20.5845794677734</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1924953460693</t>
+    <t xml:space="preserve">20.1924934387207</t>
   </si>
   <si>
     <t xml:space="preserve">19.8984260559082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3885364532471</t>
+    <t xml:space="preserve">20.3885345458984</t>
   </si>
   <si>
     <t xml:space="preserve">19.4049549102783</t>
@@ -1595,10 +1595,10 @@
     <t xml:space="preserve">19.5527095794678</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7989635467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6019592285156</t>
+    <t xml:space="preserve">19.7989654541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.601957321167</t>
   </si>
   <si>
     <t xml:space="preserve">18.9616947174072</t>
@@ -1628,13 +1628,13 @@
     <t xml:space="preserve">20.4884796142578</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5869827270508</t>
+    <t xml:space="preserve">20.5869808197021</t>
   </si>
   <si>
     <t xml:space="preserve">19.9959678649902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4542045593262</t>
+    <t xml:space="preserve">19.4542064666748</t>
   </si>
   <si>
     <t xml:space="preserve">19.5034561157227</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">19.207950592041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0259227752686</t>
+    <t xml:space="preserve">18.0259208679199</t>
   </si>
   <si>
     <t xml:space="preserve">18.075174331665</t>
@@ -1670,19 +1670,19 @@
     <t xml:space="preserve">17.9274196624756</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9766693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4349098205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.173677444458</t>
+    <t xml:space="preserve">17.9766712188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.434907913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1736755371094</t>
   </si>
   <si>
     <t xml:space="preserve">18.4199314117432</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7839870452881</t>
+    <t xml:space="preserve">20.7839889526367</t>
   </si>
   <si>
     <t xml:space="preserve">20.3899784088135</t>
@@ -1691,10 +1691,10 @@
     <t xml:space="preserve">19.7004623413086</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9124450683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.109447479248</t>
+    <t xml:space="preserve">18.9124431610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1094455718994</t>
   </si>
   <si>
     <t xml:space="preserve">18.8631916046143</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">18.5184326171875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7154369354248</t>
+    <t xml:space="preserve">18.7154388427734</t>
   </si>
   <si>
     <t xml:space="preserve">18.2229270935059</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">17.7796649932861</t>
   </si>
   <si>
-    <t xml:space="preserve">18.567684173584</t>
+    <t xml:space="preserve">18.5676860809326</t>
   </si>
   <si>
     <t xml:space="preserve">17.7304153442383</t>
@@ -1724,16 +1724,16 @@
     <t xml:space="preserve">18.2721767425537</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6811656951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8781681060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1244239807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6319122314453</t>
+    <t xml:space="preserve">17.6811637878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8781700134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1244258880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6319141387939</t>
   </si>
   <si>
     <t xml:space="preserve">17.4841594696045</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">17.3856582641602</t>
   </si>
   <si>
-    <t xml:space="preserve">17.533411026001</t>
+    <t xml:space="preserve">17.5334091186523</t>
   </si>
   <si>
     <t xml:space="preserve">17.1886520385742</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">16.4991359710693</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8931446075439</t>
+    <t xml:space="preserve">16.8931465148926</t>
   </si>
   <si>
     <t xml:space="preserve">16.4498863220215</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">16.6468906402588</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7946434020996</t>
+    <t xml:space="preserve">16.794641494751</t>
   </si>
   <si>
     <t xml:space="preserve">16.7453918457031</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">14.6275930404663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9723510742188</t>
+    <t xml:space="preserve">14.9723501205444</t>
   </si>
   <si>
     <t xml:space="preserve">14.7260942459106</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">15.1201047897339</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3663606643677</t>
+    <t xml:space="preserve">15.3663597106934</t>
   </si>
   <si>
     <t xml:space="preserve">15.464861869812</t>
@@ -1805,16 +1805,16 @@
     <t xml:space="preserve">14.7753458023071</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4798383712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2828350067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5783424377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0858297348022</t>
+    <t xml:space="preserve">14.4798393249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2828340530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5783414840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0858306884766</t>
   </si>
   <si>
     <t xml:space="preserve">14.2335834503174</t>
@@ -57331,27 +57331,105 @@
     </row>
     <row r="2111">
       <c r="A2111" s="1" t="n">
-        <v>45968.5900578704</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2111" t="n">
+        <v>14.6000003814697</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>14.6000003814697</v>
+      </c>
+      <c r="E2111" t="n">
+        <v>14.6000003814697</v>
+      </c>
+      <c r="F2111" t="n">
+        <v>14.6000003814697</v>
+      </c>
+      <c r="G2111" t="s">
+        <v>667</v>
+      </c>
+      <c r="H2111" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2112" t="n">
+        <v>750</v>
+      </c>
+      <c r="C2112" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="D2112" t="n">
+        <v>14</v>
+      </c>
+      <c r="E2112" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="F2112" t="n">
+        <v>14.1999998092651</v>
+      </c>
+      <c r="G2112" t="s">
+        <v>702</v>
+      </c>
+      <c r="H2112" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2113" t="n">
         <v>875</v>
       </c>
-      <c r="C2111" t="n">
+      <c r="C2113" t="n">
         <v>13.8999996185303</v>
       </c>
-      <c r="D2111" t="n">
+      <c r="D2113" t="n">
         <v>13.6000003814697</v>
       </c>
-      <c r="E2111" t="n">
+      <c r="E2113" t="n">
         <v>13.8999996185303</v>
       </c>
-      <c r="F2111" t="n">
+      <c r="F2113" t="n">
         <v>13.8000001907349</v>
       </c>
-      <c r="G2111" t="s">
+      <c r="G2113" t="s">
         <v>661</v>
       </c>
-      <c r="H2111" t="s">
+      <c r="H2113" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" s="1" t="n">
+        <v>45971.5196759259</v>
+      </c>
+      <c r="B2114" t="n">
+        <v>1875</v>
+      </c>
+      <c r="C2114" t="n">
+        <v>13.8999996185303</v>
+      </c>
+      <c r="D2114" t="n">
+        <v>13.3000001907349</v>
+      </c>
+      <c r="E2114" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F2114" t="n">
+        <v>13.8999996185303</v>
+      </c>
+      <c r="G2114" t="s">
+        <v>705</v>
+      </c>
+      <c r="H2114" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CULT.MI.xlsx
+++ b/data/CULT.MI.xlsx
@@ -44,31 +44,31 @@
     <t xml:space="preserve">CULT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57666730880737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59486484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60851383209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58576679229736</t>
+    <t xml:space="preserve">4.57666826248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59486532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60851287841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58576631546021</t>
   </si>
   <si>
     <t xml:space="preserve">4.48931932449341</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56301879882812</t>
+    <t xml:space="preserve">4.56301927566528</t>
   </si>
   <si>
     <t xml:space="preserve">4.51297616958618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46020364761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29824638366699</t>
+    <t xml:space="preserve">4.46020317077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29824590682983</t>
   </si>
   <si>
     <t xml:space="preserve">4.21271848678589</t>
@@ -77,10 +77,10 @@
     <t xml:space="preserve">4.18178224563599</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23091506958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36375665664673</t>
+    <t xml:space="preserve">4.23091602325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36375713348389</t>
   </si>
   <si>
     <t xml:space="preserve">4.38195419311523</t>
@@ -89,154 +89,154 @@
     <t xml:space="preserve">4.35101890563965</t>
   </si>
   <si>
-    <t xml:space="preserve">4.289146900177</t>
+    <t xml:space="preserve">4.28914737701416</t>
   </si>
   <si>
     <t xml:space="preserve">4.24183416366577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22909593582153</t>
+    <t xml:space="preserve">4.22909498214722</t>
   </si>
   <si>
     <t xml:space="preserve">4.10535287857056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09443378448486</t>
+    <t xml:space="preserve">4.09443426132202</t>
   </si>
   <si>
     <t xml:space="preserve">4.10899209976196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9961678981781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04712057113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0398416519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9634120464325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07441711425781</t>
+    <t xml:space="preserve">3.99616765975952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04712104797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03984212875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96341180801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07441663742065</t>
   </si>
   <si>
     <t xml:space="preserve">4.32008266448975</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24911260604858</t>
+    <t xml:space="preserve">4.2491135597229</t>
   </si>
   <si>
     <t xml:space="preserve">3.97979021072388</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06895780563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05439901351929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98524880409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0507607460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07259798049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03802347183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04530096054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03074312210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01254606246948</t>
+    <t xml:space="preserve">4.0689582824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0543999671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98524928092957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05076026916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07259750366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0380220413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04530143737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03074264526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01254510879517</t>
   </si>
   <si>
     <t xml:space="preserve">4.04894065856934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05985879898071</t>
+    <t xml:space="preserve">4.05985927581787</t>
   </si>
   <si>
     <t xml:space="preserve">4.07623720169067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91245913505554</t>
+    <t xml:space="preserve">3.91245937347412</t>
   </si>
   <si>
     <t xml:space="preserve">3.99070858955383</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01072645187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92155814170837</t>
+    <t xml:space="preserve">4.01072597503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92155790328979</t>
   </si>
   <si>
     <t xml:space="preserve">4.00162649154663</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05803918838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21635675430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2218165397644</t>
+    <t xml:space="preserve">4.05803966522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21635770797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22181606292725</t>
   </si>
   <si>
     <t xml:space="preserve">4.18542098999023</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16176557540894</t>
+    <t xml:space="preserve">4.16176462173462</t>
   </si>
   <si>
     <t xml:space="preserve">4.35465812683105</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28186798095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26731061935425</t>
+    <t xml:space="preserve">4.28186750411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26731109619141</t>
   </si>
   <si>
     <t xml:space="preserve">4.39287281036377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36739683151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17814302444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27458953857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3182635307312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35647821426392</t>
+    <t xml:space="preserve">4.36739730834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17814254760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27458906173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31826257705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35647773742676</t>
   </si>
   <si>
     <t xml:space="preserve">4.26549053192139</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26367092132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27640914916992</t>
+    <t xml:space="preserve">4.26367139816284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27640867233276</t>
   </si>
   <si>
     <t xml:space="preserve">4.14902639389038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35829782485962</t>
+    <t xml:space="preserve">4.35829734802246</t>
   </si>
   <si>
     <t xml:space="preserve">4.35283851623535</t>
@@ -245,43 +245,43 @@
     <t xml:space="preserve">4.29460573196411</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20361852645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24001407623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34010028839111</t>
+    <t xml:space="preserve">4.20361948013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24001359939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34009981155396</t>
   </si>
   <si>
     <t xml:space="preserve">4.42926836013794</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34919881820679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33646106719971</t>
+    <t xml:space="preserve">4.34919929504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33646011352539</t>
   </si>
   <si>
     <t xml:space="preserve">4.33100175857544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32190227508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4674825668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45838356018066</t>
+    <t xml:space="preserve">4.32190275192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46748208999634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45838451385498</t>
   </si>
   <si>
     <t xml:space="preserve">4.2855076789856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83057069778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90336060523987</t>
+    <t xml:space="preserve">3.83057117462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90336036682129</t>
   </si>
   <si>
     <t xml:space="preserve">3.88516330718994</t>
@@ -293,25 +293,25 @@
     <t xml:space="preserve">4.00344705581665</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93065643310547</t>
+    <t xml:space="preserve">3.93065714836121</t>
   </si>
   <si>
     <t xml:space="preserve">3.9943482875824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08533573150635</t>
+    <t xml:space="preserve">4.08533525466919</t>
   </si>
   <si>
     <t xml:space="preserve">3.96705174446106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86696553230286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84876775741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85786652565002</t>
+    <t xml:space="preserve">3.8669650554657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84876847267151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8578667640686</t>
   </si>
   <si>
     <t xml:space="preserve">3.81237316131592</t>
@@ -320,55 +320,55 @@
     <t xml:space="preserve">3.80327439308167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77597808837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97615051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94885492324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13992834091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16722393035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33528232574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21485948562622</t>
+    <t xml:space="preserve">3.77597832679749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97615003585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94885444641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13992786407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16722440719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33528280258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21485900878906</t>
   </si>
   <si>
     <t xml:space="preserve">4.31675672531128</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42791748046875</t>
+    <t xml:space="preserve">4.42791795730591</t>
   </si>
   <si>
     <t xml:space="preserve">4.19633197784424</t>
   </si>
   <si>
-    <t xml:space="preserve">4.168541431427</t>
+    <t xml:space="preserve">4.16854190826416</t>
   </si>
   <si>
     <t xml:space="preserve">4.29822969436646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30749273300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27970218658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39086389541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40012693405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35381031036377</t>
+    <t xml:space="preserve">4.30749320983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27970266342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3908634185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40012741088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35380935668945</t>
   </si>
   <si>
     <t xml:space="preserve">4.08517122268677</t>
@@ -377,22 +377,22 @@
     <t xml:space="preserve">3.93695592880249</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00179958343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97400975227356</t>
+    <t xml:space="preserve">4.00180101394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9740092754364</t>
   </si>
   <si>
     <t xml:space="preserve">4.03885364532471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94621968269348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95548319816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23338556289673</t>
+    <t xml:space="preserve">3.94621992111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95548343658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23338651657104</t>
   </si>
   <si>
     <t xml:space="preserve">4.22412204742432</t>
@@ -401,13 +401,13 @@
     <t xml:space="preserve">4.24264907836914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11296081542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26117515563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91842889785767</t>
+    <t xml:space="preserve">4.11296129226685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26117610931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91842913627625</t>
   </si>
   <si>
     <t xml:space="preserve">3.89990234375</t>
@@ -416,16 +416,16 @@
     <t xml:space="preserve">3.89063858985901</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07590770721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06664419174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7980043888092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73316049575806</t>
+    <t xml:space="preserve">4.0759072303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06664371490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79800462722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73316073417664</t>
   </si>
   <si>
     <t xml:space="preserve">3.86284852027893</t>
@@ -437,106 +437,106 @@
     <t xml:space="preserve">3.70537042617798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77021431922913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3904139995575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44599485397339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58494567871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68684363365173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60347270965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52010178565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37188720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46452116966248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53862881660461</t>
+    <t xml:space="preserve">3.77021479606628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39041423797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44599461555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58494544029236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68684339523315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60347294807434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52010202407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37188696861267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46452140808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53862857818604</t>
   </si>
   <si>
     <t xml:space="preserve">3.5293653011322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45525765419006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34409689903259</t>
+    <t xml:space="preserve">3.45525789260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34409642219543</t>
   </si>
   <si>
     <t xml:space="preserve">3.07545733451843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14956498146057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29777979850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31630635261536</t>
+    <t xml:space="preserve">3.14956545829773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29777956008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31630659103394</t>
   </si>
   <si>
     <t xml:space="preserve">3.23293566703796</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2421989440918</t>
+    <t xml:space="preserve">3.24219918251038</t>
   </si>
   <si>
     <t xml:space="preserve">3.02914023399353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20514559745789</t>
+    <t xml:space="preserve">3.20514535903931</t>
   </si>
   <si>
     <t xml:space="preserve">3.25146269798279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10324740409851</t>
+    <t xml:space="preserve">3.10324764251709</t>
   </si>
   <si>
     <t xml:space="preserve">3.15882849693298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9179790019989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74197435379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77902793884277</t>
+    <t xml:space="preserve">2.91797947883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74197387695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77902817726135</t>
   </si>
   <si>
     <t xml:space="preserve">2.87166213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9642961025238</t>
+    <t xml:space="preserve">2.96429634094238</t>
   </si>
   <si>
     <t xml:space="preserve">2.85313510894775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83460807800293</t>
+    <t xml:space="preserve">2.83460831642151</t>
   </si>
   <si>
     <t xml:space="preserve">2.84387183189392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72344732284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76050090789795</t>
+    <t xml:space="preserve">2.72344708442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76050114631653</t>
   </si>
   <si>
     <t xml:space="preserve">2.76976442337036</t>
@@ -545,40 +545,40 @@
     <t xml:space="preserve">2.63081312179565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67713046073914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38070011138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36217355728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29732966423035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31585645675659</t>
+    <t xml:space="preserve">2.67712998390198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38070034980774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36217379570007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29732942581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31585669517517</t>
   </si>
   <si>
     <t xml:space="preserve">2.35291028022766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26953911781311</t>
+    <t xml:space="preserve">2.26953935623169</t>
   </si>
   <si>
     <t xml:space="preserve">2.2324857711792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28806662559509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0842707157135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13058757781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22322249412537</t>
+    <t xml:space="preserve">2.28806638717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08427095413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13058805465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22322225570679</t>
   </si>
   <si>
     <t xml:space="preserve">2.24174928665161</t>
@@ -587,67 +587,67 @@
     <t xml:space="preserve">2.11206102371216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17690515518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03795385360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9916365146637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88047552108765</t>
+    <t xml:space="preserve">2.17690467834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0379536151886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99163663387299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88047564029694</t>
   </si>
   <si>
     <t xml:space="preserve">1.9453192949295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92679250240326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16764116287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13985109329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21395874023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40849089622498</t>
+    <t xml:space="preserve">1.92679238319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16764140129089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13985133171082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21395897865295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4084906578064</t>
   </si>
   <si>
     <t xml:space="preserve">2.48259806632996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42701768875122</t>
+    <t xml:space="preserve">2.42701721191406</t>
   </si>
   <si>
     <t xml:space="preserve">2.38996410369873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46583604812622</t>
+    <t xml:space="preserve">2.46583580970764</t>
   </si>
   <si>
     <t xml:space="preserve">2.50406551361084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65698552131653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71433067321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54229593276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58052587509155</t>
+    <t xml:space="preserve">2.65698575973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71433091163635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5422956943512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58052611351013</t>
   </si>
   <si>
     <t xml:space="preserve">2.52318096160889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42760610580444</t>
+    <t xml:space="preserve">2.42760586738586</t>
   </si>
   <si>
     <t xml:space="preserve">2.38937592506409</t>
@@ -668,22 +668,22 @@
     <t xml:space="preserve">2.73344588279724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69521570205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75256085395813</t>
+    <t xml:space="preserve">2.69521594047546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75256109237671</t>
   </si>
   <si>
     <t xml:space="preserve">2.80990552902222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82902097702026</t>
+    <t xml:space="preserve">2.82902073860168</t>
   </si>
   <si>
     <t xml:space="preserve">2.84813594818115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05840086936951</t>
+    <t xml:space="preserve">3.05840110778809</t>
   </si>
   <si>
     <t xml:space="preserve">2.86725091934204</t>
@@ -695,16 +695,16 @@
     <t xml:space="preserve">2.67610096931458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59964060783386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44672083854675</t>
+    <t xml:space="preserve">2.59964084625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44672060012817</t>
   </si>
   <si>
     <t xml:space="preserve">2.37026071548462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09663081169128</t>
+    <t xml:space="preserve">3.09663105010986</t>
   </si>
   <si>
     <t xml:space="preserve">3.34512591362</t>
@@ -716,16 +716,16 @@
     <t xml:space="preserve">3.74654150009155</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76565623283386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01415157318115</t>
+    <t xml:space="preserve">3.76565647125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01415109634399</t>
   </si>
   <si>
     <t xml:space="preserve">4.1097264289856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97592115402222</t>
+    <t xml:space="preserve">3.97592091560364</t>
   </si>
   <si>
     <t xml:space="preserve">3.88034629821777</t>
@@ -734,19 +734,19 @@
     <t xml:space="preserve">3.82300138473511</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44070100784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40247106552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36424088478088</t>
+    <t xml:space="preserve">3.4407012462616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40247082710266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36424112319946</t>
   </si>
   <si>
     <t xml:space="preserve">3.68919610977173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72742629051208</t>
+    <t xml:space="preserve">3.72742605209351</t>
   </si>
   <si>
     <t xml:space="preserve">3.70831155776978</t>
@@ -764,10 +764,10 @@
     <t xml:space="preserve">3.63185119628906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53627634048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61273622512817</t>
+    <t xml:space="preserve">3.53627586364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61273598670959</t>
   </si>
   <si>
     <t xml:space="preserve">3.65096592903137</t>
@@ -776,10 +776,10 @@
     <t xml:space="preserve">3.24955129623413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32601094245911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42158603668213</t>
+    <t xml:space="preserve">3.32601118087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42158627510071</t>
   </si>
   <si>
     <t xml:space="preserve">3.30689597129822</t>
@@ -788,16 +788,16 @@
     <t xml:space="preserve">3.38335633277893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59362149238586</t>
+    <t xml:space="preserve">3.59362125396729</t>
   </si>
   <si>
     <t xml:space="preserve">3.47893118858337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49804639816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28778123855591</t>
+    <t xml:space="preserve">3.49804663658142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28778100013733</t>
   </si>
   <si>
     <t xml:space="preserve">3.67008090019226</t>
@@ -806,19 +806,19 @@
     <t xml:space="preserve">3.80388617515564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9376916885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03326559066772</t>
+    <t xml:space="preserve">3.93769145011902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03326606750488</t>
   </si>
   <si>
     <t xml:space="preserve">4.18618679046631</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30087614059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53025579452515</t>
+    <t xml:space="preserve">4.30087661743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5302562713623</t>
   </si>
   <si>
     <t xml:space="preserve">4.51114130020142</t>
@@ -839,25 +839,25 @@
     <t xml:space="preserve">4.74052143096924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75963592529297</t>
+    <t xml:space="preserve">4.75963687896729</t>
   </si>
   <si>
     <t xml:space="preserve">4.70229148864746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68317699432373</t>
+    <t xml:space="preserve">4.68317651748657</t>
   </si>
   <si>
     <t xml:space="preserve">4.77875185012817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56848621368408</t>
+    <t xml:space="preserve">4.5684871673584</t>
   </si>
   <si>
     <t xml:space="preserve">4.66406202316284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72140693664551</t>
+    <t xml:space="preserve">4.72140741348267</t>
   </si>
   <si>
     <t xml:space="preserve">4.87432622909546</t>
@@ -869,28 +869,28 @@
     <t xml:space="preserve">4.92211437225342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11326360702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16105175018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20883941650391</t>
+    <t xml:space="preserve">5.1132640838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16105222702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20883893966675</t>
   </si>
   <si>
     <t xml:space="preserve">5.25662660598755</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30441427230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44777631759644</t>
+    <t xml:space="preserve">5.30441379547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44777679443359</t>
   </si>
   <si>
     <t xml:space="preserve">5.63892698287964</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59113931655884</t>
+    <t xml:space="preserve">5.59113883972168</t>
   </si>
   <si>
     <t xml:space="preserve">5.81332683563232</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">5.71643829345703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42577123641968</t>
+    <t xml:space="preserve">5.42577171325684</t>
   </si>
   <si>
     <t xml:space="preserve">5.1351056098938</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">4.8444390296936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82506084442139</t>
+    <t xml:space="preserve">4.82506132125854</t>
   </si>
   <si>
     <t xml:space="preserve">4.80568313598633</t>
@@ -944,19 +944,19 @@
     <t xml:space="preserve">4.74755001068115</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2804388999939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89288330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6312837600708</t>
+    <t xml:space="preserve">5.28043842315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89288282394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63128423690796</t>
   </si>
   <si>
     <t xml:space="preserve">4.53439474105835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67003965377808</t>
+    <t xml:space="preserve">4.67003917694092</t>
   </si>
   <si>
     <t xml:space="preserve">4.78630638122559</t>
@@ -971,13 +971,13 @@
     <t xml:space="preserve">5.91021537780762</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61954879760742</t>
+    <t xml:space="preserve">5.61954927444458</t>
   </si>
   <si>
     <t xml:space="preserve">5.32888269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37732744216919</t>
+    <t xml:space="preserve">5.37732696533203</t>
   </si>
   <si>
     <t xml:space="preserve">5.57110500335693</t>
@@ -986,13 +986,13 @@
     <t xml:space="preserve">5.47421598434448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66799354553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73376941680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29777050018311</t>
+    <t xml:space="preserve">5.66799306869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73376989364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29777097702026</t>
   </si>
   <si>
     <t xml:space="preserve">6.4431037902832</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">6.34621524810791</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53999280929565</t>
+    <t xml:space="preserve">6.5399923324585</t>
   </si>
   <si>
     <t xml:space="preserve">6.3946590423584</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">8.71999073028564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99332523345947</t>
+    <t xml:space="preserve">7.99332427978516</t>
   </si>
   <si>
     <t xml:space="preserve">8.09021377563477</t>
@@ -1058,19 +1058,19 @@
     <t xml:space="preserve">10.0764331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2390975952148</t>
+    <t xml:space="preserve">11.2390985488892</t>
   </si>
   <si>
     <t xml:space="preserve">11.6266536712646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0799856185913</t>
+    <t xml:space="preserve">13.079984664917</t>
   </si>
   <si>
     <t xml:space="preserve">13.2737617492676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9830951690674</t>
+    <t xml:space="preserve">12.9830961227417</t>
   </si>
   <si>
     <t xml:space="preserve">14.4364280700684</t>
@@ -57409,7 +57409,7 @@
     </row>
     <row r="2114">
       <c r="A2114" s="1" t="n">
-        <v>45971.5196759259</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2114" t="n">
         <v>1875</v>

--- a/data/CULT.MI.xlsx
+++ b/data/CULT.MI.xlsx
@@ -44,25 +44,25 @@
     <t xml:space="preserve">CULT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57666826248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59486532211304</t>
+    <t xml:space="preserve">4.57666730880737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5948657989502</t>
   </si>
   <si>
     <t xml:space="preserve">4.60851287841797</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58576631546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48931932449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56301927566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51297616958618</t>
+    <t xml:space="preserve">4.58576679229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48931980133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56301879882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5129771232605</t>
   </si>
   <si>
     <t xml:space="preserve">4.46020317077637</t>
@@ -80,13 +80,13 @@
     <t xml:space="preserve">4.23091602325439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36375713348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38195419311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35101890563965</t>
+    <t xml:space="preserve">4.36375665664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38195514678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35101842880249</t>
   </si>
   <si>
     <t xml:space="preserve">4.28914737701416</t>
@@ -98,52 +98,52 @@
     <t xml:space="preserve">4.22909498214722</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10535287857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09443426132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10899209976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99616765975952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04712104797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03984212875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96341180801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07441663742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32008266448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2491135597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97979021072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0689582824707</t>
+    <t xml:space="preserve">4.1053524017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09443473815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10899257659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99616813659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04712057113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0398416519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96341228485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07441759109497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32008361816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24911260604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97979044914246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06895780563354</t>
   </si>
   <si>
     <t xml:space="preserve">4.0543999671936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98524928092957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05076026916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07259750366211</t>
+    <t xml:space="preserve">3.98524951934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05075979232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07259654998779</t>
   </si>
   <si>
     <t xml:space="preserve">4.0380220413208</t>
@@ -158,172 +158,172 @@
     <t xml:space="preserve">4.01254510879517</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04894065856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05985927581787</t>
+    <t xml:space="preserve">4.04893970489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05985832214355</t>
   </si>
   <si>
     <t xml:space="preserve">4.07623720169067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91245937347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99070858955383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01072597503662</t>
+    <t xml:space="preserve">3.91245985031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99070882797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01072549819946</t>
   </si>
   <si>
     <t xml:space="preserve">3.92155790328979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00162649154663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05803966522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21635770797729</t>
+    <t xml:space="preserve">4.00162696838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05803918838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21635723114014</t>
   </si>
   <si>
     <t xml:space="preserve">4.22181606292725</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18542098999023</t>
+    <t xml:space="preserve">4.18542146682739</t>
   </si>
   <si>
     <t xml:space="preserve">4.16176462173462</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35465812683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28186750411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26731109619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39287281036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36739730834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17814254760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27458906173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31826257705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35647773742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26549053192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26367139816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27640867233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14902639389038</t>
+    <t xml:space="preserve">4.3546576499939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28186845779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26731014251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39287328720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36739635467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17814302444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27458953857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31826305389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35647821426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26549100875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26367092132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27640914916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14902591705322</t>
   </si>
   <si>
     <t xml:space="preserve">4.35829734802246</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35283851623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29460573196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20361948013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24001359939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34009981155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42926836013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34919929504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33646011352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33100175857544</t>
+    <t xml:space="preserve">4.35283756256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29460620880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2036190032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24001407623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34010028839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42926740646362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34919881820679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33646106719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3310022354126</t>
   </si>
   <si>
     <t xml:space="preserve">4.32190275192261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46748208999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45838451385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2855076789856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83057117462158</t>
+    <t xml:space="preserve">4.4674825668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45838356018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28550720214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83057069778442</t>
   </si>
   <si>
     <t xml:space="preserve">3.90336036682129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88516330718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87606453895569</t>
+    <t xml:space="preserve">3.88516354560852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87606477737427</t>
   </si>
   <si>
     <t xml:space="preserve">4.00344705581665</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93065714836121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9943482875824</t>
+    <t xml:space="preserve">3.93065690994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99434781074524</t>
   </si>
   <si>
     <t xml:space="preserve">4.08533525466919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96705174446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8669650554657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84876847267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8578667640686</t>
+    <t xml:space="preserve">3.96705150604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86696553230286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84876799583435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85786604881287</t>
   </si>
   <si>
     <t xml:space="preserve">3.81237316131592</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80327439308167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77597832679749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97615003585815</t>
+    <t xml:space="preserve">3.80327463150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77597880363464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97615075111389</t>
   </si>
   <si>
     <t xml:space="preserve">3.94885444641113</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">4.13992786407471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16722440719604</t>
+    <t xml:space="preserve">4.16722393035889</t>
   </si>
   <si>
     <t xml:space="preserve">4.33528280258179</t>
@@ -341,10 +341,10 @@
     <t xml:space="preserve">4.21485900878906</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31675672531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42791795730591</t>
+    <t xml:space="preserve">4.31675624847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42791748046875</t>
   </si>
   <si>
     <t xml:space="preserve">4.19633197784424</t>
@@ -368,16 +368,16 @@
     <t xml:space="preserve">4.40012741088867</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35380935668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08517122268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93695592880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00180101394653</t>
+    <t xml:space="preserve">4.35381078720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08517074584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93695569038391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00180006027222</t>
   </si>
   <si>
     <t xml:space="preserve">3.9740092754364</t>
@@ -386,16 +386,16 @@
     <t xml:space="preserve">4.03885364532471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94621992111206</t>
+    <t xml:space="preserve">3.94622015953064</t>
   </si>
   <si>
     <t xml:space="preserve">3.95548343658447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23338651657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22412204742432</t>
+    <t xml:space="preserve">4.23338508605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22412157058716</t>
   </si>
   <si>
     <t xml:space="preserve">4.24264907836914</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">4.11296129226685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26117610931396</t>
+    <t xml:space="preserve">4.26117563247681</t>
   </si>
   <si>
     <t xml:space="preserve">3.91842913627625</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">3.73316073417664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86284852027893</t>
+    <t xml:space="preserve">3.86284875869751</t>
   </si>
   <si>
     <t xml:space="preserve">3.71463394165039</t>
@@ -437,16 +437,16 @@
     <t xml:space="preserve">3.70537042617798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77021479606628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39041423797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44599461555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58494544029236</t>
+    <t xml:space="preserve">3.77021455764771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39041376113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44599437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58494567871094</t>
   </si>
   <si>
     <t xml:space="preserve">3.68684339523315</t>
@@ -455,109 +455,109 @@
     <t xml:space="preserve">3.60347294807434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52010202407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37188696861267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46452140808105</t>
+    <t xml:space="preserve">3.52010178565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37188720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46452116966248</t>
   </si>
   <si>
     <t xml:space="preserve">3.53862857818604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5293653011322</t>
+    <t xml:space="preserve">3.52936553955078</t>
   </si>
   <si>
     <t xml:space="preserve">3.45525789260864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34409642219543</t>
+    <t xml:space="preserve">3.34409666061401</t>
   </si>
   <si>
     <t xml:space="preserve">3.07545733451843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14956545829773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29777956008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31630659103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23293566703796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24219918251038</t>
+    <t xml:space="preserve">3.14956498146057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29777932167053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31630635261536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23293542861938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2421989440918</t>
   </si>
   <si>
     <t xml:space="preserve">3.02914023399353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20514535903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25146269798279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10324764251709</t>
+    <t xml:space="preserve">3.20514559745789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25146245956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10324740409851</t>
   </si>
   <si>
     <t xml:space="preserve">3.15882849693298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91797947883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74197387695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77902817726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87166213989258</t>
+    <t xml:space="preserve">2.91797924041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74197435379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77902770042419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.871661901474</t>
   </si>
   <si>
     <t xml:space="preserve">2.96429634094238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85313510894775</t>
+    <t xml:space="preserve">2.85313534736633</t>
   </si>
   <si>
     <t xml:space="preserve">2.83460831642151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84387183189392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72344708442688</t>
+    <t xml:space="preserve">2.8438720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72344732284546</t>
   </si>
   <si>
     <t xml:space="preserve">2.76050114631653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76976442337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63081312179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67712998390198</t>
+    <t xml:space="preserve">2.76976466178894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63081288337708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67713022232056</t>
   </si>
   <si>
     <t xml:space="preserve">2.38070034980774</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36217379570007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29732942581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31585669517517</t>
+    <t xml:space="preserve">2.36217331886292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29732966423035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31585645675659</t>
   </si>
   <si>
     <t xml:space="preserve">2.35291028022766</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">2.26953935623169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2324857711792</t>
+    <t xml:space="preserve">2.23248553276062</t>
   </si>
   <si>
     <t xml:space="preserve">2.28806638717651</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">2.08427095413208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13058805465698</t>
+    <t xml:space="preserve">2.1305878162384</t>
   </si>
   <si>
     <t xml:space="preserve">2.22322225570679</t>
@@ -584,25 +584,25 @@
     <t xml:space="preserve">2.24174928665161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11206102371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17690467834473</t>
+    <t xml:space="preserve">2.11206078529358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17690539360046</t>
   </si>
   <si>
     <t xml:space="preserve">2.0379536151886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99163663387299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88047564029694</t>
+    <t xml:space="preserve">1.99163687229156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88047552108765</t>
   </si>
   <si>
     <t xml:space="preserve">1.9453192949295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92679238319397</t>
+    <t xml:space="preserve">1.92679286003113</t>
   </si>
   <si>
     <t xml:space="preserve">2.16764140129089</t>
@@ -611,16 +611,16 @@
     <t xml:space="preserve">2.13985133171082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21395897865295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4084906578064</t>
+    <t xml:space="preserve">2.21395874023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40849089622498</t>
   </si>
   <si>
     <t xml:space="preserve">2.48259806632996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42701721191406</t>
+    <t xml:space="preserve">2.42701768875122</t>
   </si>
   <si>
     <t xml:space="preserve">2.38996410369873</t>
@@ -632,7 +632,7 @@
     <t xml:space="preserve">2.50406551361084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65698575973511</t>
+    <t xml:space="preserve">2.65698599815369</t>
   </si>
   <si>
     <t xml:space="preserve">2.71433091163635</t>
@@ -641,13 +641,13 @@
     <t xml:space="preserve">2.5422956943512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58052611351013</t>
+    <t xml:space="preserve">2.58052587509155</t>
   </si>
   <si>
     <t xml:space="preserve">2.52318096160889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42760586738586</t>
+    <t xml:space="preserve">2.42760562896729</t>
   </si>
   <si>
     <t xml:space="preserve">2.38937592506409</t>
@@ -656,25 +656,25 @@
     <t xml:space="preserve">2.48495078086853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61875581741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56141066551208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63787078857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73344588279724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69521594047546</t>
+    <t xml:space="preserve">2.61875605583191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56141114234924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6378710269928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73344612121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69521617889404</t>
   </si>
   <si>
     <t xml:space="preserve">2.75256109237671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80990552902222</t>
+    <t xml:space="preserve">2.80990600585938</t>
   </si>
   <si>
     <t xml:space="preserve">2.82902073860168</t>
@@ -683,13 +683,13 @@
     <t xml:space="preserve">2.84813594818115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05840110778809</t>
+    <t xml:space="preserve">3.05840086936951</t>
   </si>
   <si>
     <t xml:space="preserve">2.86725091934204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77167582511902</t>
+    <t xml:space="preserve">2.7716760635376</t>
   </si>
   <si>
     <t xml:space="preserve">2.67610096931458</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">2.59964084625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44672060012817</t>
+    <t xml:space="preserve">2.44672083854675</t>
   </si>
   <si>
     <t xml:space="preserve">2.37026071548462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09663105010986</t>
+    <t xml:space="preserve">3.09663081169128</t>
   </si>
   <si>
     <t xml:space="preserve">3.34512591362</t>
@@ -713,10 +713,10 @@
     <t xml:space="preserve">3.45981597900391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74654150009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76565647125244</t>
+    <t xml:space="preserve">3.74654126167297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76565623283386</t>
   </si>
   <si>
     <t xml:space="preserve">4.01415109634399</t>
@@ -725,16 +725,16 @@
     <t xml:space="preserve">4.1097264289856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97592091560364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88034629821777</t>
+    <t xml:space="preserve">3.97592115402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88034653663635</t>
   </si>
   <si>
     <t xml:space="preserve">3.82300138473511</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4407012462616</t>
+    <t xml:space="preserve">3.44070100784302</t>
   </si>
   <si>
     <t xml:space="preserve">3.40247082710266</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">3.68919610977173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72742605209351</t>
+    <t xml:space="preserve">3.72742629051208</t>
   </si>
   <si>
     <t xml:space="preserve">3.70831155776978</t>
@@ -758,88 +758,88 @@
     <t xml:space="preserve">3.55539107322693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51716089248657</t>
+    <t xml:space="preserve">3.51716113090515</t>
   </si>
   <si>
     <t xml:space="preserve">3.63185119628906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53627586364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61273598670959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65096592903137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24955129623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32601118087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42158627510071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30689597129822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38335633277893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59362125396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47893118858337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49804663658142</t>
+    <t xml:space="preserve">3.53627634048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61273622512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65096616744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24955105781555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32601094245911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42158603668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3068962097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38335609436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59362149238586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47893095016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49804615974426</t>
   </si>
   <si>
     <t xml:space="preserve">3.28778100013733</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67008090019226</t>
+    <t xml:space="preserve">3.67008137702942</t>
   </si>
   <si>
     <t xml:space="preserve">3.80388617515564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93769145011902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03326606750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18618679046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30087661743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5302562713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51114130020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58760166168213</t>
+    <t xml:space="preserve">3.93769073486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03326559066772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18618583679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30087614059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53025579452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51114177703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58760213851929</t>
   </si>
   <si>
     <t xml:space="preserve">4.49202585220337</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43468189239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62583208084106</t>
+    <t xml:space="preserve">4.43468141555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62583160400391</t>
   </si>
   <si>
     <t xml:space="preserve">4.74052143096924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75963687896729</t>
+    <t xml:space="preserve">4.75963640213013</t>
   </si>
   <si>
     <t xml:space="preserve">4.70229148864746</t>
@@ -851,28 +851,28 @@
     <t xml:space="preserve">4.77875185012817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5684871673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66406202316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72140741348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87432622909546</t>
+    <t xml:space="preserve">4.56848621368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72140598297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87432670593262</t>
   </si>
   <si>
     <t xml:space="preserve">4.96990156173706</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92211437225342</t>
+    <t xml:space="preserve">4.92211389541626</t>
   </si>
   <si>
     <t xml:space="preserve">5.1132640838623</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16105222702026</t>
+    <t xml:space="preserve">5.16105175018311</t>
   </si>
   <si>
     <t xml:space="preserve">5.20883893966675</t>
@@ -881,55 +881,55 @@
     <t xml:space="preserve">5.25662660598755</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30441379547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44777679443359</t>
+    <t xml:space="preserve">5.30441474914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44777631759644</t>
   </si>
   <si>
     <t xml:space="preserve">5.63892698287964</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59113883972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81332683563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71643829345703</t>
+    <t xml:space="preserve">5.59113931655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81332635879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71643781661987</t>
   </si>
   <si>
     <t xml:space="preserve">5.42577171325684</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1351056098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8444390296936</t>
+    <t xml:space="preserve">5.13510513305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84443855285645</t>
   </si>
   <si>
     <t xml:space="preserve">4.82506132125854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80568313598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59252786636353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55377197265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76692771911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03821659088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9897723197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08666086196899</t>
+    <t xml:space="preserve">4.80568361282349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59252738952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55377292633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76692819595337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03821611404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98977184295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08666038513184</t>
   </si>
   <si>
     <t xml:space="preserve">5.18354940414429</t>
@@ -938,19 +938,19 @@
     <t xml:space="preserve">4.9413275718689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23199462890625</t>
+    <t xml:space="preserve">5.23199367523193</t>
   </si>
   <si>
     <t xml:space="preserve">4.74755001068115</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28043842315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89288282394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63128423690796</t>
+    <t xml:space="preserve">5.28043794631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89288330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6312837600708</t>
   </si>
   <si>
     <t xml:space="preserve">4.53439474105835</t>
@@ -959,13 +959,13 @@
     <t xml:space="preserve">4.67003917694092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78630638122559</t>
+    <t xml:space="preserve">4.78630542755127</t>
   </si>
   <si>
     <t xml:space="preserve">4.72817277908325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70879507064819</t>
+    <t xml:space="preserve">4.70879411697388</t>
   </si>
   <si>
     <t xml:space="preserve">5.91021537780762</t>
@@ -974,25 +974,25 @@
     <t xml:space="preserve">5.61954927444458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32888269424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37732696533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57110500335693</t>
+    <t xml:space="preserve">5.32888221740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37732744216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57110452651978</t>
   </si>
   <si>
     <t xml:space="preserve">5.47421598434448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66799306869507</t>
+    <t xml:space="preserve">5.66799354553223</t>
   </si>
   <si>
     <t xml:space="preserve">6.73376989364624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29777097702026</t>
+    <t xml:space="preserve">6.29777050018311</t>
   </si>
   <si>
     <t xml:space="preserve">6.4431037902832</t>
@@ -1004,70 +1004,70 @@
     <t xml:space="preserve">6.58843755722046</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63688087463379</t>
+    <t xml:space="preserve">6.63688135147095</t>
   </si>
   <si>
     <t xml:space="preserve">6.24932622909546</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34621524810791</t>
+    <t xml:space="preserve">6.34621572494507</t>
   </si>
   <si>
     <t xml:space="preserve">6.5399923324585</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3946590423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71999073028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99332427978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09021377563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04176807403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94488000869751</t>
+    <t xml:space="preserve">6.39465951919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71998977661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.993323802948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09021282196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04176902770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94487953186035</t>
   </si>
   <si>
     <t xml:space="preserve">7.84799194335938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89643621444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38087844848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2702112197876</t>
+    <t xml:space="preserve">7.89643430709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38087940216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2702102661133</t>
   </si>
   <si>
     <t xml:space="preserve">9.88265514373779</t>
   </si>
   <si>
-    <t xml:space="preserve">10.173321723938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9795446395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0764331817627</t>
+    <t xml:space="preserve">10.1733207702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97954368591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0764322280884</t>
   </si>
   <si>
     <t xml:space="preserve">11.2390985488892</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6266536712646</t>
+    <t xml:space="preserve">11.6266527175903</t>
   </si>
   <si>
     <t xml:space="preserve">13.079984664917</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2737617492676</t>
+    <t xml:space="preserve">13.2737627029419</t>
   </si>
   <si>
     <t xml:space="preserve">12.9830961227417</t>
@@ -1076,16 +1076,16 @@
     <t xml:space="preserve">14.4364280700684</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3395385742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0177612304688</t>
+    <t xml:space="preserve">14.3395395278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0177602767944</t>
   </si>
   <si>
     <t xml:space="preserve">16.1669788360596</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1930656433105</t>
+    <t xml:space="preserve">15.1930665969849</t>
   </si>
   <si>
     <t xml:space="preserve">15.0956745147705</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">14.9008903503418</t>
   </si>
   <si>
-    <t xml:space="preserve">13.634801864624</t>
+    <t xml:space="preserve">13.6348009109497</t>
   </si>
   <si>
     <t xml:space="preserve">12.0765390396118</t>
@@ -1106,25 +1106,25 @@
     <t xml:space="preserve">13.4400196075439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9269771575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0243673324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2191524505615</t>
+    <t xml:space="preserve">13.9269762039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0243682861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2191514968872</t>
   </si>
   <si>
     <t xml:space="preserve">14.8035001754761</t>
   </si>
   <si>
-    <t xml:space="preserve">14.413932800293</t>
+    <t xml:space="preserve">14.4139347076416</t>
   </si>
   <si>
     <t xml:space="preserve">14.6087160110474</t>
   </si>
   <si>
-    <t xml:space="preserve">14.706109046936</t>
+    <t xml:space="preserve">14.7061080932617</t>
   </si>
   <si>
     <t xml:space="preserve">14.5113248825073</t>
@@ -1136,16 +1136,16 @@
     <t xml:space="preserve">14.1217594146729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3165426254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8295841217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5374097824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2452373504639</t>
+    <t xml:space="preserve">14.3165416717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8295850753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.537410736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2452363967896</t>
   </si>
   <si>
     <t xml:space="preserve">12.8556699752808</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">12.3687133789062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7582788467407</t>
+    <t xml:space="preserve">12.758279800415</t>
   </si>
   <si>
     <t xml:space="preserve">12.5634965896606</t>
@@ -1163,25 +1163,25 @@
     <t xml:space="preserve">12.1739301681519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6869745254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1026239395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93392753601074</t>
+    <t xml:space="preserve">11.686972618103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1026248931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93392658233643</t>
   </si>
   <si>
     <t xml:space="preserve">10.7130584716797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2000169754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9791479110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8817548751831</t>
+    <t xml:space="preserve">11.2000160217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9791469573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8817558288574</t>
   </si>
   <si>
     <t xml:space="preserve">10.9078416824341</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">11.2974071502686</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3947982788086</t>
+    <t xml:space="preserve">11.3947992324829</t>
   </si>
   <si>
     <t xml:space="preserve">11.589581489563</t>
@@ -1202,22 +1202,22 @@
     <t xml:space="preserve">11.7843647003174</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4921913146973</t>
+    <t xml:space="preserve">11.4921903610229</t>
   </si>
   <si>
     <t xml:space="preserve">10.810450553894</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4208841323853</t>
+    <t xml:space="preserve">10.4208850860596</t>
   </si>
   <si>
     <t xml:space="preserve">10.2261009216309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3234939575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1287097930908</t>
+    <t xml:space="preserve">10.3234920501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1287107467651</t>
   </si>
   <si>
     <t xml:space="preserve">10.0313196182251</t>
@@ -1226,16 +1226,16 @@
     <t xml:space="preserve">9.73914432525635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54436206817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8365364074707</t>
+    <t xml:space="preserve">9.54436111450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83653545379639</t>
   </si>
   <si>
     <t xml:space="preserve">9.34957885742188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49566555023193</t>
+    <t xml:space="preserve">9.49566650390625</t>
   </si>
   <si>
     <t xml:space="preserve">12.2713222503662</t>
@@ -1247,16 +1247,16 @@
     <t xml:space="preserve">15.6800231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7321939468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1704559326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3652372360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0730638504028</t>
+    <t xml:space="preserve">13.7321949005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1704549789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3652391433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0730628967285</t>
   </si>
   <si>
     <t xml:space="preserve">15.1443700790405</t>
@@ -1265,22 +1265,22 @@
     <t xml:space="preserve">15.5364561080933</t>
   </si>
   <si>
-    <t xml:space="preserve">15.585467338562</t>
+    <t xml:space="preserve">15.5854682922363</t>
   </si>
   <si>
     <t xml:space="preserve">15.6344785690308</t>
   </si>
   <si>
-    <t xml:space="preserve">15.193380355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4874458312988</t>
+    <t xml:space="preserve">15.1933813095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4874448776245</t>
   </si>
   <si>
     <t xml:space="preserve">15.4384346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2423906326294</t>
+    <t xml:space="preserve">15.2423915863037</t>
   </si>
   <si>
     <t xml:space="preserve">15.3894233703613</t>
@@ -1301,22 +1301,22 @@
     <t xml:space="preserve">13.9190969467163</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1641502380371</t>
+    <t xml:space="preserve">14.1641511917114</t>
   </si>
   <si>
     <t xml:space="preserve">13.7230529785156</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8210754394531</t>
+    <t xml:space="preserve">13.8210763931274</t>
   </si>
   <si>
     <t xml:space="preserve">14.3601951599121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6250314712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8700847625732</t>
+    <t xml:space="preserve">13.6250305175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8700857162476</t>
   </si>
   <si>
     <t xml:space="preserve">13.6740417480469</t>
@@ -1328,13 +1328,13 @@
     <t xml:space="preserve">14.0171184539795</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1839323043823</t>
+    <t xml:space="preserve">13.1839332580566</t>
   </si>
   <si>
     <t xml:space="preserve">13.5270099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9483251571655</t>
+    <t xml:space="preserve">14.9483261108398</t>
   </si>
   <si>
     <t xml:space="preserve">14.4092054367065</t>
@@ -1355,10 +1355,10 @@
     <t xml:space="preserve">14.5562391281128</t>
   </si>
   <si>
-    <t xml:space="preserve">14.507227897644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0661306381226</t>
+    <t xml:space="preserve">14.5072288513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0661296844482</t>
   </si>
   <si>
     <t xml:space="preserve">13.3309659957886</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">13.4779987335205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2819557189941</t>
+    <t xml:space="preserve">13.2819547653198</t>
   </si>
   <si>
     <t xml:space="preserve">12.8898668289185</t>
@@ -1376,22 +1376,22 @@
     <t xml:space="preserve">12.7428350448608</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9878902435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1349220275879</t>
+    <t xml:space="preserve">12.987889289856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1349229812622</t>
   </si>
   <si>
     <t xml:space="preserve">12.3507480621338</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7626171112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3215188980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.301736831665</t>
+    <t xml:space="preserve">11.7626161575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3215198516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3017377853394</t>
   </si>
   <si>
     <t xml:space="preserve">13.0859117507935</t>
@@ -1400,16 +1400,16 @@
     <t xml:space="preserve">13.4289875030518</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8305225372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7324991226196</t>
+    <t xml:space="preserve">15.8305215835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7325000762939</t>
   </si>
   <si>
     <t xml:space="preserve">15.8795328140259</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9775552749634</t>
+    <t xml:space="preserve">15.9775543212891</t>
   </si>
   <si>
     <t xml:space="preserve">16.3696422576904</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">15.7815113067627</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2226104736328</t>
+    <t xml:space="preserve">16.2226085662842</t>
   </si>
   <si>
     <t xml:space="preserve">16.0265655517578</t>
@@ -1430,25 +1430,25 @@
     <t xml:space="preserve">16.0755767822266</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9285440444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1735992431641</t>
+    <t xml:space="preserve">15.9285449981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1735973358154</t>
   </si>
   <si>
     <t xml:space="preserve">16.2716197967529</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3206310272217</t>
+    <t xml:space="preserve">16.320629119873</t>
   </si>
   <si>
     <t xml:space="preserve">18.7221660614014</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0162296295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7023849487305</t>
+    <t xml:space="preserve">19.0162315368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7023830413818</t>
   </si>
   <si>
     <t xml:space="preserve">19.604362487793</t>
@@ -1460,52 +1460,52 @@
     <t xml:space="preserve">20.0944690704346</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9173202514648</t>
+    <t xml:space="preserve">23.9173221588135</t>
   </si>
   <si>
     <t xml:space="preserve">22.545015335083</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5252342224121</t>
+    <t xml:space="preserve">23.5252323150635</t>
   </si>
   <si>
     <t xml:space="preserve">24.7995166778564</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2311687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7806243896484</t>
+    <t xml:space="preserve">23.2311706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7806224822998</t>
   </si>
   <si>
     <t xml:space="preserve">21.1727104187012</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4865570068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6826038360596</t>
+    <t xml:space="preserve">20.4865589141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6826019287109</t>
   </si>
   <si>
     <t xml:space="preserve">21.3687534332275</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6430377960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9955615997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2896251678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6034736633301</t>
+    <t xml:space="preserve">22.6430397033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9955596923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2896270751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6034755706787</t>
   </si>
   <si>
     <t xml:space="preserve">24.8975391387939</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5054531097412</t>
+    <t xml:space="preserve">24.5054512023926</t>
   </si>
   <si>
     <t xml:space="preserve">24.015344619751</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">22.9371032714844</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7212791442871</t>
+    <t xml:space="preserve">23.7212772369385</t>
   </si>
   <si>
     <t xml:space="preserve">24.1133651733398</t>
@@ -1532,28 +1532,28 @@
     <t xml:space="preserve">23.0351238250732</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1331462860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2113857269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4074306488037</t>
+    <t xml:space="preserve">23.1331481933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2113876342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4074287414551</t>
   </si>
   <si>
     <t xml:space="preserve">23.819299697876</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2509517669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7608413696289</t>
+    <t xml:space="preserve">22.2509498596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7608432769775</t>
   </si>
   <si>
     <t xml:space="preserve">21.9568843841553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1529293060303</t>
+    <t xml:space="preserve">22.1529273986816</t>
   </si>
   <si>
     <t xml:space="preserve">18.7711753845215</t>
@@ -1568,19 +1568,19 @@
     <t xml:space="preserve">18.5261211395264</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9964485168457</t>
+    <t xml:space="preserve">19.9964466094971</t>
   </si>
   <si>
     <t xml:space="preserve">20.5845794677734</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1924934387207</t>
+    <t xml:space="preserve">20.1924953460693</t>
   </si>
   <si>
     <t xml:space="preserve">19.8984260559082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3885345458984</t>
+    <t xml:space="preserve">20.3885364532471</t>
   </si>
   <si>
     <t xml:space="preserve">19.4049549102783</t>
@@ -1595,10 +1595,10 @@
     <t xml:space="preserve">19.5527095794678</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7989654541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.601957321167</t>
+    <t xml:space="preserve">19.7989635467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6019592285156</t>
   </si>
   <si>
     <t xml:space="preserve">18.9616947174072</t>
@@ -1628,13 +1628,13 @@
     <t xml:space="preserve">20.4884796142578</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5869808197021</t>
+    <t xml:space="preserve">20.5869827270508</t>
   </si>
   <si>
     <t xml:space="preserve">19.9959678649902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4542064666748</t>
+    <t xml:space="preserve">19.4542045593262</t>
   </si>
   <si>
     <t xml:space="preserve">19.5034561157227</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">19.207950592041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0259208679199</t>
+    <t xml:space="preserve">18.0259227752686</t>
   </si>
   <si>
     <t xml:space="preserve">18.075174331665</t>
@@ -1670,19 +1670,19 @@
     <t xml:space="preserve">17.9274196624756</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9766712188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.434907913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1736755371094</t>
+    <t xml:space="preserve">17.9766693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4349098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.173677444458</t>
   </si>
   <si>
     <t xml:space="preserve">18.4199314117432</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7839889526367</t>
+    <t xml:space="preserve">20.7839870452881</t>
   </si>
   <si>
     <t xml:space="preserve">20.3899784088135</t>
@@ -1691,10 +1691,10 @@
     <t xml:space="preserve">19.7004623413086</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9124431610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1094455718994</t>
+    <t xml:space="preserve">18.9124450683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.109447479248</t>
   </si>
   <si>
     <t xml:space="preserve">18.8631916046143</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">18.5184326171875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7154388427734</t>
+    <t xml:space="preserve">18.7154369354248</t>
   </si>
   <si>
     <t xml:space="preserve">18.2229270935059</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">17.7796649932861</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5676860809326</t>
+    <t xml:space="preserve">18.567684173584</t>
   </si>
   <si>
     <t xml:space="preserve">17.7304153442383</t>
@@ -1724,16 +1724,16 @@
     <t xml:space="preserve">18.2721767425537</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6811637878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8781700134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1244258880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6319141387939</t>
+    <t xml:space="preserve">17.6811656951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8781681060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1244239807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6319122314453</t>
   </si>
   <si>
     <t xml:space="preserve">17.4841594696045</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">17.3856582641602</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5334091186523</t>
+    <t xml:space="preserve">17.533411026001</t>
   </si>
   <si>
     <t xml:space="preserve">17.1886520385742</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">16.4991359710693</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8931465148926</t>
+    <t xml:space="preserve">16.8931446075439</t>
   </si>
   <si>
     <t xml:space="preserve">16.4498863220215</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">16.6468906402588</t>
   </si>
   <si>
-    <t xml:space="preserve">16.794641494751</t>
+    <t xml:space="preserve">16.7946434020996</t>
   </si>
   <si>
     <t xml:space="preserve">16.7453918457031</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">14.6275930404663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9723501205444</t>
+    <t xml:space="preserve">14.9723510742188</t>
   </si>
   <si>
     <t xml:space="preserve">14.7260942459106</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">15.1201047897339</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3663597106934</t>
+    <t xml:space="preserve">15.3663606643677</t>
   </si>
   <si>
     <t xml:space="preserve">15.464861869812</t>
@@ -1805,16 +1805,16 @@
     <t xml:space="preserve">14.7753458023071</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4798393249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2828340530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5783414840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0858306884766</t>
+    <t xml:space="preserve">14.4798383712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2828350067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5783424377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0858297348022</t>
   </si>
   <si>
     <t xml:space="preserve">14.2335834503174</t>
@@ -57433,6 +57433,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2115">
+      <c r="A2115" s="1" t="n">
+        <v>45972.3333333333</v>
+      </c>
+      <c r="B2115" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2115" t="n">
+        <v>13.8999996185303</v>
+      </c>
+      <c r="D2115" t="n">
+        <v>13.8999996185303</v>
+      </c>
+      <c r="E2115" t="n">
+        <v>13.8999996185303</v>
+      </c>
+      <c r="F2115" t="n">
+        <v>13.8999996185303</v>
+      </c>
+      <c r="G2115" t="s">
+        <v>705</v>
+      </c>
+      <c r="H2115" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" s="1" t="n">
+        <v>45973.6780555556</v>
+      </c>
+      <c r="B2116" t="n">
+        <v>1125</v>
+      </c>
+      <c r="C2116" t="n">
+        <v>14</v>
+      </c>
+      <c r="D2116" t="n">
+        <v>13.6999998092651</v>
+      </c>
+      <c r="E2116" t="n">
+        <v>13.6999998092651</v>
+      </c>
+      <c r="F2116" t="n">
+        <v>14</v>
+      </c>
+      <c r="G2116" t="s">
+        <v>703</v>
+      </c>
+      <c r="H2116" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CULT.MI.xlsx
+++ b/data/CULT.MI.xlsx
@@ -44,46 +44,46 @@
     <t xml:space="preserve">CULT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57666730880737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5948657989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60851287841797</t>
+    <t xml:space="preserve">4.57666778564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59486532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60851335525513</t>
   </si>
   <si>
     <t xml:space="preserve">4.58576679229736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48931980133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56301879882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5129771232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46020317077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29824590682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21271848678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18178224563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23091602325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36375665664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38195514678955</t>
+    <t xml:space="preserve">4.48931932449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56301927566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51297664642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46020364761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29824638366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21271753311157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18178176879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23091554641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36375713348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38195419311523</t>
   </si>
   <si>
     <t xml:space="preserve">4.35101842880249</t>
@@ -95,16 +95,16 @@
     <t xml:space="preserve">4.24183416366577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22909498214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1053524017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09443473815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10899257659912</t>
+    <t xml:space="preserve">4.22909545898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10535287857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09443426132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10899209976196</t>
   </si>
   <si>
     <t xml:space="preserve">3.99616813659668</t>
@@ -116,55 +116,55 @@
     <t xml:space="preserve">4.0398416519165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96341228485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07441759109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32008361816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24911260604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97979044914246</t>
+    <t xml:space="preserve">3.96341252326965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07441711425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32008266448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2491135597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97978925704956</t>
   </si>
   <si>
     <t xml:space="preserve">4.06895780563354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0543999671936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98524951934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05075979232788</t>
+    <t xml:space="preserve">4.05439949035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98524904251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05076026916504</t>
   </si>
   <si>
     <t xml:space="preserve">4.07259654998779</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0380220413208</t>
+    <t xml:space="preserve">4.03802299499512</t>
   </si>
   <si>
     <t xml:space="preserve">4.04530143737793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03074264526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01254510879517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04893970489502</t>
+    <t xml:space="preserve">4.03074312210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01254558563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04894065856934</t>
   </si>
   <si>
     <t xml:space="preserve">4.05985832214355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07623720169067</t>
+    <t xml:space="preserve">4.07623672485352</t>
   </si>
   <si>
     <t xml:space="preserve">3.91245985031128</t>
@@ -176,13 +176,13 @@
     <t xml:space="preserve">4.01072549819946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92155790328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00162696838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05803918838501</t>
+    <t xml:space="preserve">3.92155742645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00162649154663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05803966522217</t>
   </si>
   <si>
     <t xml:space="preserve">4.21635723114014</t>
@@ -191,28 +191,28 @@
     <t xml:space="preserve">4.22181606292725</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18542146682739</t>
+    <t xml:space="preserve">4.18542194366455</t>
   </si>
   <si>
     <t xml:space="preserve">4.16176462173462</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3546576499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28186845779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26731014251709</t>
+    <t xml:space="preserve">4.35465860366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28186798095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26730918884277</t>
   </si>
   <si>
     <t xml:space="preserve">4.39287328720093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36739635467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17814302444458</t>
+    <t xml:space="preserve">4.36739683151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17814350128174</t>
   </si>
   <si>
     <t xml:space="preserve">4.27458953857422</t>
@@ -224,46 +224,46 @@
     <t xml:space="preserve">4.35647821426392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26549100875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26367092132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27640914916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14902591705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35829734802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35283756256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29460620880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2036190032959</t>
+    <t xml:space="preserve">4.26549005508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26367044448853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27640819549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14902639389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35829782485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35283851623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29460668563843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20361852645874</t>
   </si>
   <si>
     <t xml:space="preserve">4.24001407623291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34010028839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42926740646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34919881820679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33646106719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3310022354126</t>
+    <t xml:space="preserve">4.34009885787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42926788330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34919929504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33646059036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33100128173828</t>
   </si>
   <si>
     <t xml:space="preserve">4.32190275192261</t>
@@ -272,19 +272,19 @@
     <t xml:space="preserve">4.4674825668335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45838356018066</t>
+    <t xml:space="preserve">4.45838403701782</t>
   </si>
   <si>
     <t xml:space="preserve">4.28550720214844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83057069778442</t>
+    <t xml:space="preserve">3.83057045936584</t>
   </si>
   <si>
     <t xml:space="preserve">3.90336036682129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88516354560852</t>
+    <t xml:space="preserve">3.88516306877136</t>
   </si>
   <si>
     <t xml:space="preserve">3.87606477737427</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">4.00344705581665</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93065690994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99434781074524</t>
+    <t xml:space="preserve">3.93065643310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9943482875824</t>
   </si>
   <si>
     <t xml:space="preserve">4.08533525466919</t>
@@ -311,31 +311,31 @@
     <t xml:space="preserve">3.84876799583435</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85786604881287</t>
+    <t xml:space="preserve">3.85786700248718</t>
   </si>
   <si>
     <t xml:space="preserve">3.81237316131592</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80327463150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77597880363464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97615075111389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94885444641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13992786407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16722393035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33528280258179</t>
+    <t xml:space="preserve">3.80327439308167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77597784996033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97614979743958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94885468482971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13992738723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16722440719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33528327941895</t>
   </si>
   <si>
     <t xml:space="preserve">4.21485900878906</t>
@@ -344,13 +344,13 @@
     <t xml:space="preserve">4.31675624847412</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42791748046875</t>
+    <t xml:space="preserve">4.42791795730591</t>
   </si>
   <si>
     <t xml:space="preserve">4.19633197784424</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16854190826416</t>
+    <t xml:space="preserve">4.168541431427</t>
   </si>
   <si>
     <t xml:space="preserve">4.29822969436646</t>
@@ -359,22 +359,22 @@
     <t xml:space="preserve">4.30749320983887</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27970266342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3908634185791</t>
+    <t xml:space="preserve">4.27970218658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39086389541626</t>
   </si>
   <si>
     <t xml:space="preserve">4.40012741088867</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35381078720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08517074584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93695569038391</t>
+    <t xml:space="preserve">4.35380983352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08517122268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93695616722107</t>
   </si>
   <si>
     <t xml:space="preserve">4.00180006027222</t>
@@ -383,28 +383,28 @@
     <t xml:space="preserve">3.9740092754364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03885364532471</t>
+    <t xml:space="preserve">4.03885316848755</t>
   </si>
   <si>
     <t xml:space="preserve">3.94622015953064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95548343658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23338508605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22412157058716</t>
+    <t xml:space="preserve">3.95548295974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23338556289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22412252426147</t>
   </si>
   <si>
     <t xml:space="preserve">4.24264907836914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11296129226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26117563247681</t>
+    <t xml:space="preserve">4.11296081542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26117610931396</t>
   </si>
   <si>
     <t xml:space="preserve">3.91842913627625</t>
@@ -413,13 +413,13 @@
     <t xml:space="preserve">3.89990234375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89063858985901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0759072303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06664371490479</t>
+    <t xml:space="preserve">3.89063930511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07590770721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06664419174194</t>
   </si>
   <si>
     <t xml:space="preserve">3.79800462722778</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">3.71463394165039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70537042617798</t>
+    <t xml:space="preserve">3.7053701877594</t>
   </si>
   <si>
     <t xml:space="preserve">3.77021455764771</t>
@@ -443,31 +443,31 @@
     <t xml:space="preserve">3.39041376113892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44599437713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58494567871094</t>
+    <t xml:space="preserve">3.44599461555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58494544029236</t>
   </si>
   <si>
     <t xml:space="preserve">3.68684339523315</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60347294807434</t>
+    <t xml:space="preserve">3.60347270965576</t>
   </si>
   <si>
     <t xml:space="preserve">3.52010178565979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37188720703125</t>
+    <t xml:space="preserve">3.37188696861267</t>
   </si>
   <si>
     <t xml:space="preserve">3.46452116966248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53862857818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52936553955078</t>
+    <t xml:space="preserve">3.53862881660461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5293653011322</t>
   </si>
   <si>
     <t xml:space="preserve">3.45525789260864</t>
@@ -476,25 +476,25 @@
     <t xml:space="preserve">3.34409666061401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07545733451843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14956498146057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29777932167053</t>
+    <t xml:space="preserve">3.07545757293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14956521987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29777956008911</t>
   </si>
   <si>
     <t xml:space="preserve">3.31630635261536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23293542861938</t>
+    <t xml:space="preserve">3.23293590545654</t>
   </si>
   <si>
     <t xml:space="preserve">3.2421989440918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02914023399353</t>
+    <t xml:space="preserve">3.02913999557495</t>
   </si>
   <si>
     <t xml:space="preserve">3.20514559745789</t>
@@ -506,118 +506,118 @@
     <t xml:space="preserve">3.10324740409851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15882849693298</t>
+    <t xml:space="preserve">3.1588282585144</t>
   </si>
   <si>
     <t xml:space="preserve">2.91797924041748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74197435379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77902770042419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.871661901474</t>
+    <t xml:space="preserve">2.74197387695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77902793884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87166213989258</t>
   </si>
   <si>
     <t xml:space="preserve">2.96429634094238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85313534736633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83460831642151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8438720703125</t>
+    <t xml:space="preserve">2.85313510894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83460807800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84387183189392</t>
   </si>
   <si>
     <t xml:space="preserve">2.72344732284546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76050114631653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76976466178894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63081288337708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67713022232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38070034980774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36217331886292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29732966423035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31585645675659</t>
+    <t xml:space="preserve">2.76050066947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76976442337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63081312179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67712998390198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38070058822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36217379570007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29732990264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31585669517517</t>
   </si>
   <si>
     <t xml:space="preserve">2.35291028022766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26953935623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23248553276062</t>
+    <t xml:space="preserve">2.26953959465027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2324857711792</t>
   </si>
   <si>
     <t xml:space="preserve">2.28806638717651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08427095413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1305878162384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22322225570679</t>
+    <t xml:space="preserve">2.0842707157135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13058805465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22322249412537</t>
   </si>
   <si>
     <t xml:space="preserve">2.24174928665161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11206078529358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17690539360046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0379536151886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99163687229156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88047552108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9453192949295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92679286003113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16764140129089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13985133171082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21395874023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40849089622498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48259806632996</t>
+    <t xml:space="preserve">2.11206126213074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17690491676331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03795385360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9916365146637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88047528266907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94531965255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92679238319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16764163970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13985109329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21395897865295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4084906578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48259830474854</t>
   </si>
   <si>
     <t xml:space="preserve">2.42701768875122</t>
@@ -626,28 +626,28 @@
     <t xml:space="preserve">2.38996410369873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46583580970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50406551361084</t>
+    <t xml:space="preserve">2.4658362865448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50406575202942</t>
   </si>
   <si>
     <t xml:space="preserve">2.65698599815369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71433091163635</t>
+    <t xml:space="preserve">2.71433067321777</t>
   </si>
   <si>
     <t xml:space="preserve">2.5422956943512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58052587509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52318096160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42760562896729</t>
+    <t xml:space="preserve">2.58052563667297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52318120002747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42760586738586</t>
   </si>
   <si>
     <t xml:space="preserve">2.38937592506409</t>
@@ -656,19 +656,19 @@
     <t xml:space="preserve">2.48495078086853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61875605583191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56141114234924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6378710269928</t>
+    <t xml:space="preserve">2.61875557899475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56141090393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63787078857422</t>
   </si>
   <si>
     <t xml:space="preserve">2.73344612121582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69521617889404</t>
+    <t xml:space="preserve">2.69521570205688</t>
   </si>
   <si>
     <t xml:space="preserve">2.75256109237671</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">2.82902073860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84813594818115</t>
+    <t xml:space="preserve">2.84813570976257</t>
   </si>
   <si>
     <t xml:space="preserve">3.05840086936951</t>
@@ -692,49 +692,49 @@
     <t xml:space="preserve">2.7716760635376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67610096931458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59964084625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44672083854675</t>
+    <t xml:space="preserve">2.676100730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59964108467102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44672060012817</t>
   </si>
   <si>
     <t xml:space="preserve">2.37026071548462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09663081169128</t>
+    <t xml:space="preserve">3.09663105010986</t>
   </si>
   <si>
     <t xml:space="preserve">3.34512591362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45981597900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74654126167297</t>
+    <t xml:space="preserve">3.45981621742249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74654102325439</t>
   </si>
   <si>
     <t xml:space="preserve">3.76565623283386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01415109634399</t>
+    <t xml:space="preserve">4.01415157318115</t>
   </si>
   <si>
     <t xml:space="preserve">4.1097264289856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97592115402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88034653663635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82300138473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44070100784302</t>
+    <t xml:space="preserve">3.97592091560364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88034605979919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82300114631653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44070076942444</t>
   </si>
   <si>
     <t xml:space="preserve">3.40247082710266</t>
@@ -743,25 +743,25 @@
     <t xml:space="preserve">3.36424112319946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68919610977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72742629051208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70831155776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57450604438782</t>
+    <t xml:space="preserve">3.68919587135315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72742605209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7083113193512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57450580596924</t>
   </si>
   <si>
     <t xml:space="preserve">3.55539107322693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51716113090515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63185119628906</t>
+    <t xml:space="preserve">3.51716136932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63185095787048</t>
   </si>
   <si>
     <t xml:space="preserve">3.53627634048462</t>
@@ -773,22 +773,22 @@
     <t xml:space="preserve">3.65096616744995</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24955105781555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32601094245911</t>
+    <t xml:space="preserve">3.24955129623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32601118087769</t>
   </si>
   <si>
     <t xml:space="preserve">3.42158603668213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3068962097168</t>
+    <t xml:space="preserve">3.30689597129822</t>
   </si>
   <si>
     <t xml:space="preserve">3.38335609436035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59362149238586</t>
+    <t xml:space="preserve">3.59362125396729</t>
   </si>
   <si>
     <t xml:space="preserve">3.47893095016479</t>
@@ -797,40 +797,40 @@
     <t xml:space="preserve">3.49804615974426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28778100013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67008137702942</t>
+    <t xml:space="preserve">3.28778123855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67008113861084</t>
   </si>
   <si>
     <t xml:space="preserve">3.80388617515564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93769073486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03326559066772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18618583679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30087614059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53025579452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51114177703857</t>
+    <t xml:space="preserve">3.93769121170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03326606750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18618679046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30087661743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5302562713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51114130020142</t>
   </si>
   <si>
     <t xml:space="preserve">4.58760213851929</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49202585220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43468141555786</t>
+    <t xml:space="preserve">4.49202632904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43468189239502</t>
   </si>
   <si>
     <t xml:space="preserve">4.62583160400391</t>
@@ -839,13 +839,13 @@
     <t xml:space="preserve">4.74052143096924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75963640213013</t>
+    <t xml:space="preserve">4.75963735580444</t>
   </si>
   <si>
     <t xml:space="preserve">4.70229148864746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68317651748657</t>
+    <t xml:space="preserve">4.68317699432373</t>
   </si>
   <si>
     <t xml:space="preserve">4.77875185012817</t>
@@ -854,10 +854,10 @@
     <t xml:space="preserve">4.56848621368408</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72140598297119</t>
+    <t xml:space="preserve">4.66406106948853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72140645980835</t>
   </si>
   <si>
     <t xml:space="preserve">4.87432670593262</t>
@@ -866,16 +866,16 @@
     <t xml:space="preserve">4.96990156173706</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92211389541626</t>
+    <t xml:space="preserve">4.92211437225342</t>
   </si>
   <si>
     <t xml:space="preserve">5.1132640838623</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16105175018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20883893966675</t>
+    <t xml:space="preserve">5.16105127334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20883941650391</t>
   </si>
   <si>
     <t xml:space="preserve">5.25662660598755</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">5.30441474914551</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44777631759644</t>
+    <t xml:space="preserve">5.44777679443359</t>
   </si>
   <si>
     <t xml:space="preserve">5.63892698287964</t>
@@ -893,31 +893,31 @@
     <t xml:space="preserve">5.59113931655884</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81332635879517</t>
+    <t xml:space="preserve">5.81332683563232</t>
   </si>
   <si>
     <t xml:space="preserve">5.71643781661987</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42577171325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13510513305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84443855285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82506132125854</t>
+    <t xml:space="preserve">5.42577123641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1351056098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84443950653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8250617980957</t>
   </si>
   <si>
     <t xml:space="preserve">4.80568361282349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59252738952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55377292633057</t>
+    <t xml:space="preserve">4.59252834320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55377244949341</t>
   </si>
   <si>
     <t xml:space="preserve">4.76692819595337</t>
@@ -926,25 +926,25 @@
     <t xml:space="preserve">5.03821611404419</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98977184295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08666038513184</t>
+    <t xml:space="preserve">4.9897723197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08666086196899</t>
   </si>
   <si>
     <t xml:space="preserve">5.18354940414429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9413275718689</t>
+    <t xml:space="preserve">4.94132709503174</t>
   </si>
   <si>
     <t xml:space="preserve">5.23199367523193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74755001068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28043794631958</t>
+    <t xml:space="preserve">4.74755096435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28043842315674</t>
   </si>
   <si>
     <t xml:space="preserve">4.89288330078125</t>
@@ -956,34 +956,34 @@
     <t xml:space="preserve">4.53439474105835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67003917694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78630542755127</t>
+    <t xml:space="preserve">4.67003965377808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78630590438843</t>
   </si>
   <si>
     <t xml:space="preserve">4.72817277908325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70879411697388</t>
+    <t xml:space="preserve">4.70879507064819</t>
   </si>
   <si>
     <t xml:space="preserve">5.91021537780762</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61954927444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32888221740723</t>
+    <t xml:space="preserve">5.61954879760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32888317108154</t>
   </si>
   <si>
     <t xml:space="preserve">5.37732744216919</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57110452651978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47421598434448</t>
+    <t xml:space="preserve">5.57110500335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47421550750732</t>
   </si>
   <si>
     <t xml:space="preserve">5.66799354553223</t>
@@ -998,22 +998,22 @@
     <t xml:space="preserve">6.4431037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68532562255859</t>
+    <t xml:space="preserve">6.68532609939575</t>
   </si>
   <si>
     <t xml:space="preserve">6.58843755722046</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63688135147095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24932622909546</t>
+    <t xml:space="preserve">6.63688087463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2493257522583</t>
   </si>
   <si>
     <t xml:space="preserve">6.34621572494507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5399923324585</t>
+    <t xml:space="preserve">6.53999280929565</t>
   </si>
   <si>
     <t xml:space="preserve">6.39465951919556</t>
@@ -1022,58 +1022,58 @@
     <t xml:space="preserve">8.71998977661133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.993323802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09021282196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04176902770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94487953186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84799194335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89643430709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38087940216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2702102661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88265514373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1733207702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97954368591309</t>
+    <t xml:space="preserve">7.99332427978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09021472930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04176807403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94488000869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84799098968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89643526077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38087844848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2702112197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88265419006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.173321723938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9795446395874</t>
   </si>
   <si>
     <t xml:space="preserve">10.0764322280884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2390985488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6266527175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.079984664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2737627029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9830961227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4364280700684</t>
+    <t xml:space="preserve">11.2390975952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6266536712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0799856185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2737617492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9830951690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.436427116394</t>
   </si>
   <si>
     <t xml:space="preserve">14.3395395278931</t>
@@ -1085,40 +1085,40 @@
     <t xml:space="preserve">16.1669788360596</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1930665969849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0956745147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9008903503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6348009109497</t>
+    <t xml:space="preserve">15.1930646896362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0956735610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9008913040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.634801864624</t>
   </si>
   <si>
     <t xml:space="preserve">12.0765390396118</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4661045074463</t>
+    <t xml:space="preserve">12.4661054611206</t>
   </si>
   <si>
     <t xml:space="preserve">13.4400196075439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9269762039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0243682861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2191514968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8035001754761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4139347076416</t>
+    <t xml:space="preserve">13.9269771575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0243673324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2191505432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8034982681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4139337539673</t>
   </si>
   <si>
     <t xml:space="preserve">14.6087160110474</t>
@@ -1133,22 +1133,22 @@
     <t xml:space="preserve">13.3426275253296</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1217594146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3165416717529</t>
+    <t xml:space="preserve">14.1217584609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3165426254272</t>
   </si>
   <si>
     <t xml:space="preserve">13.8295850753784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.537410736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2452363967896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8556699752808</t>
+    <t xml:space="preserve">13.5374097824097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2452373504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8556709289551</t>
   </si>
   <si>
     <t xml:space="preserve">12.3687133789062</t>
@@ -1157,37 +1157,37 @@
     <t xml:space="preserve">12.758279800415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5634965896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1739301681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.686972618103</t>
+    <t xml:space="preserve">12.5634956359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1739311218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6869735717773</t>
   </si>
   <si>
     <t xml:space="preserve">11.1026248931885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93392658233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7130584716797</t>
+    <t xml:space="preserve">9.93392562866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.713059425354</t>
   </si>
   <si>
     <t xml:space="preserve">11.2000160217285</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9791469573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8817558288574</t>
+    <t xml:space="preserve">11.9791479110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8817567825317</t>
   </si>
   <si>
     <t xml:space="preserve">10.9078416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2974071502686</t>
+    <t xml:space="preserve">11.2974081039429</t>
   </si>
   <si>
     <t xml:space="preserve">11.3947992324829</t>
@@ -1205,16 +1205,16 @@
     <t xml:space="preserve">11.4921903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.810450553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4208850860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2261009216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3234920501709</t>
+    <t xml:space="preserve">10.8104515075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4208841323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2261018753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3234939575195</t>
   </si>
   <si>
     <t xml:space="preserve">10.1287107467651</t>
@@ -1226,13 +1226,13 @@
     <t xml:space="preserve">9.73914432525635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54436111450195</t>
+    <t xml:space="preserve">9.54436206817627</t>
   </si>
   <si>
     <t xml:space="preserve">9.83653545379639</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34957885742188</t>
+    <t xml:space="preserve">9.34957790374756</t>
   </si>
   <si>
     <t xml:space="preserve">9.49566650390625</t>
@@ -1244,19 +1244,19 @@
     <t xml:space="preserve">12.9530620574951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6800231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7321949005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1704549789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3652391433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0730628967285</t>
+    <t xml:space="preserve">15.6800222396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7321939468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1704559326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3652381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0730638504028</t>
   </si>
   <si>
     <t xml:space="preserve">15.1443700790405</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">15.6344785690308</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1933813095093</t>
+    <t xml:space="preserve">15.193380355835</t>
   </si>
   <si>
     <t xml:space="preserve">15.4874448776245</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">14.9973373413086</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8993148803711</t>
+    <t xml:space="preserve">14.8993139266968</t>
   </si>
   <si>
     <t xml:space="preserve">15.0463485717773</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">13.7230529785156</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8210763931274</t>
+    <t xml:space="preserve">13.8210754394531</t>
   </si>
   <si>
     <t xml:space="preserve">14.3601951599121</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">13.7720651626587</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0171184539795</t>
+    <t xml:space="preserve">14.0171194076538</t>
   </si>
   <si>
     <t xml:space="preserve">13.1839332580566</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">14.9483261108398</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4092054367065</t>
+    <t xml:space="preserve">14.4092063903809</t>
   </si>
   <si>
     <t xml:space="preserve">14.8503036499023</t>
@@ -1355,19 +1355,19 @@
     <t xml:space="preserve">14.5562391281128</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5072288513184</t>
+    <t xml:space="preserve">14.507227897644</t>
   </si>
   <si>
     <t xml:space="preserve">14.0661296844482</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3309659957886</t>
+    <t xml:space="preserve">13.3309669494629</t>
   </si>
   <si>
     <t xml:space="preserve">13.4779987335205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2819547653198</t>
+    <t xml:space="preserve">13.2819557189941</t>
   </si>
   <si>
     <t xml:space="preserve">12.8898668289185</t>
@@ -1379,19 +1379,19 @@
     <t xml:space="preserve">12.987889289856</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1349229812622</t>
+    <t xml:space="preserve">13.1349220275879</t>
   </si>
   <si>
     <t xml:space="preserve">12.3507480621338</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7626161575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3215198516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3017377853394</t>
+    <t xml:space="preserve">11.7626171112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3215188980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.301736831665</t>
   </si>
   <si>
     <t xml:space="preserve">13.0859117507935</t>
@@ -1400,10 +1400,10 @@
     <t xml:space="preserve">13.4289875030518</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8305215835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7325000762939</t>
+    <t xml:space="preserve">15.8305225372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7324991226196</t>
   </si>
   <si>
     <t xml:space="preserve">15.8795328140259</t>
@@ -1430,7 +1430,7 @@
     <t xml:space="preserve">16.0755767822266</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9285449981689</t>
+    <t xml:space="preserve">15.9285430908203</t>
   </si>
   <si>
     <t xml:space="preserve">16.1735973358154</t>
@@ -1439,16 +1439,16 @@
     <t xml:space="preserve">16.2716197967529</t>
   </si>
   <si>
-    <t xml:space="preserve">16.320629119873</t>
+    <t xml:space="preserve">16.3206310272217</t>
   </si>
   <si>
     <t xml:space="preserve">18.7221660614014</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0162315368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7023830413818</t>
+    <t xml:space="preserve">19.0162296295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7023849487305</t>
   </si>
   <si>
     <t xml:space="preserve">19.604362487793</t>
@@ -1466,46 +1466,46 @@
     <t xml:space="preserve">22.545015335083</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5252323150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7995166778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2311706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7806224822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1727104187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4865589141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6826019287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3687534332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6430397033691</t>
+    <t xml:space="preserve">23.5252342224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7995147705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2311687469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7806243896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1727085113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4865570068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6826038360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3687553405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6430377960205</t>
   </si>
   <si>
     <t xml:space="preserve">24.9955596923828</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2896270751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6034755706787</t>
+    <t xml:space="preserve">25.2896251678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6034736633301</t>
   </si>
   <si>
     <t xml:space="preserve">24.8975391387939</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5054512023926</t>
+    <t xml:space="preserve">24.5054531097412</t>
   </si>
   <si>
     <t xml:space="preserve">24.015344619751</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">23.623254776001</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8390808105469</t>
+    <t xml:space="preserve">22.8390827178955</t>
   </si>
   <si>
     <t xml:space="preserve">23.3291893005371</t>
@@ -1529,22 +1529,22 @@
     <t xml:space="preserve">24.1133651733398</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0351238250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1331481933594</t>
+    <t xml:space="preserve">23.0351257324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1331462860107</t>
   </si>
   <si>
     <t xml:space="preserve">24.2113876342773</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4074287414551</t>
+    <t xml:space="preserve">24.4074306488037</t>
   </si>
   <si>
     <t xml:space="preserve">23.819299697876</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2509498596191</t>
+    <t xml:space="preserve">22.2509517669678</t>
   </si>
   <si>
     <t xml:space="preserve">21.7608432769775</t>
@@ -1595,10 +1595,10 @@
     <t xml:space="preserve">19.5527095794678</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7989635467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6019592285156</t>
+    <t xml:space="preserve">19.7989654541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.601957321167</t>
   </si>
   <si>
     <t xml:space="preserve">18.9616947174072</t>
@@ -1628,13 +1628,13 @@
     <t xml:space="preserve">20.4884796142578</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5869827270508</t>
+    <t xml:space="preserve">20.5869808197021</t>
   </si>
   <si>
     <t xml:space="preserve">19.9959678649902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4542045593262</t>
+    <t xml:space="preserve">19.4542064666748</t>
   </si>
   <si>
     <t xml:space="preserve">19.5034561157227</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">19.207950592041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0259227752686</t>
+    <t xml:space="preserve">18.0259208679199</t>
   </si>
   <si>
     <t xml:space="preserve">18.075174331665</t>
@@ -1670,19 +1670,19 @@
     <t xml:space="preserve">17.9274196624756</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9766693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4349098205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.173677444458</t>
+    <t xml:space="preserve">17.9766712188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.434907913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1736755371094</t>
   </si>
   <si>
     <t xml:space="preserve">18.4199314117432</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7839870452881</t>
+    <t xml:space="preserve">20.7839889526367</t>
   </si>
   <si>
     <t xml:space="preserve">20.3899784088135</t>
@@ -1691,10 +1691,10 @@
     <t xml:space="preserve">19.7004623413086</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9124450683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.109447479248</t>
+    <t xml:space="preserve">18.9124431610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1094455718994</t>
   </si>
   <si>
     <t xml:space="preserve">18.8631916046143</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">18.5184326171875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7154369354248</t>
+    <t xml:space="preserve">18.7154388427734</t>
   </si>
   <si>
     <t xml:space="preserve">18.2229270935059</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">17.7796649932861</t>
   </si>
   <si>
-    <t xml:space="preserve">18.567684173584</t>
+    <t xml:space="preserve">18.5676860809326</t>
   </si>
   <si>
     <t xml:space="preserve">17.7304153442383</t>
@@ -1724,16 +1724,16 @@
     <t xml:space="preserve">18.2721767425537</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6811656951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8781681060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1244239807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6319122314453</t>
+    <t xml:space="preserve">17.6811637878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8781700134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1244258880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6319141387939</t>
   </si>
   <si>
     <t xml:space="preserve">17.4841594696045</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">17.3856582641602</t>
   </si>
   <si>
-    <t xml:space="preserve">17.533411026001</t>
+    <t xml:space="preserve">17.5334091186523</t>
   </si>
   <si>
     <t xml:space="preserve">17.1886520385742</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">16.4991359710693</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8931446075439</t>
+    <t xml:space="preserve">16.8931465148926</t>
   </si>
   <si>
     <t xml:space="preserve">16.4498863220215</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">16.6468906402588</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7946434020996</t>
+    <t xml:space="preserve">16.794641494751</t>
   </si>
   <si>
     <t xml:space="preserve">16.7453918457031</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">14.6275930404663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9723510742188</t>
+    <t xml:space="preserve">14.9723501205444</t>
   </si>
   <si>
     <t xml:space="preserve">14.7260942459106</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">15.1201047897339</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3663606643677</t>
+    <t xml:space="preserve">15.3663597106934</t>
   </si>
   <si>
     <t xml:space="preserve">15.464861869812</t>
@@ -1805,16 +1805,16 @@
     <t xml:space="preserve">14.7753458023071</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4798383712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2828350067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5783424377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0858297348022</t>
+    <t xml:space="preserve">14.4798393249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2828340530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5783414840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0858306884766</t>
   </si>
   <si>
     <t xml:space="preserve">14.2335834503174</t>
@@ -57461,7 +57461,7 @@
     </row>
     <row r="2116">
       <c r="A2116" s="1" t="n">
-        <v>45973.6780555556</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2116" t="n">
         <v>1125</v>
@@ -57482,6 +57482,32 @@
         <v>703</v>
       </c>
       <c r="H2116" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" s="1" t="n">
+        <v>45974.5701967593</v>
+      </c>
+      <c r="B2117" t="n">
+        <v>125</v>
+      </c>
+      <c r="C2117" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="D2117" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="E2117" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="F2117" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="G2117" t="s">
+        <v>664</v>
+      </c>
+      <c r="H2117" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CULT.MI.xlsx
+++ b/data/CULT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68585252761841</t>
+    <t xml:space="preserve">4.68585300445557</t>
   </si>
   <si>
     <t xml:space="preserve">CULT.MI</t>
@@ -47,43 +47,43 @@
     <t xml:space="preserve">4.57666778564453</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59486532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60851335525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58576679229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48931932449341</t>
+    <t xml:space="preserve">4.59486484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60851383209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58576583862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48932027816772</t>
   </si>
   <si>
     <t xml:space="preserve">4.56301927566528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51297664642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46020364761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29824638366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21271753311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18178176879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23091554641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36375713348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38195419311523</t>
+    <t xml:space="preserve">4.51297616958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46020317077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29824542999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21271800994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18178272247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23091602325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36375761032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38195514678955</t>
   </si>
   <si>
     <t xml:space="preserve">4.35101842880249</t>
@@ -92,136 +92,136 @@
     <t xml:space="preserve">4.28914737701416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24183416366577</t>
+    <t xml:space="preserve">4.24183368682861</t>
   </si>
   <si>
     <t xml:space="preserve">4.22909545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10535287857056</t>
+    <t xml:space="preserve">4.10535335540771</t>
   </si>
   <si>
     <t xml:space="preserve">4.09443426132202</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10899209976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99616813659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04712057113647</t>
+    <t xml:space="preserve">4.10899257659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99616765975952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04712104797363</t>
   </si>
   <si>
     <t xml:space="preserve">4.0398416519165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96341252326965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07441711425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32008266448975</t>
+    <t xml:space="preserve">3.96341228485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07441759109497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3200831413269</t>
   </si>
   <si>
     <t xml:space="preserve">4.2491135597229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97978925704956</t>
+    <t xml:space="preserve">3.97979044914246</t>
   </si>
   <si>
     <t xml:space="preserve">4.06895780563354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05439949035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98524904251099</t>
+    <t xml:space="preserve">4.0543999671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98524951934814</t>
   </si>
   <si>
     <t xml:space="preserve">4.05076026916504</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07259654998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03802299499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04530143737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03074312210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01254558563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04894065856934</t>
+    <t xml:space="preserve">4.07259750366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03802251815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04530048370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03074264526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01254606246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04894018173218</t>
   </si>
   <si>
     <t xml:space="preserve">4.05985832214355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07623672485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91245985031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99070882797241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01072549819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92155742645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00162649154663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05803966522217</t>
+    <t xml:space="preserve">4.07623624801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91245889663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99070906639099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01072597503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92155790328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00162696838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05803918838501</t>
   </si>
   <si>
     <t xml:space="preserve">4.21635723114014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22181606292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18542194366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16176462173462</t>
+    <t xml:space="preserve">4.2218165397644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18542146682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16176414489746</t>
   </si>
   <si>
     <t xml:space="preserve">4.35465860366821</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28186798095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26730918884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39287328720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36739683151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17814350128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27458953857422</t>
+    <t xml:space="preserve">4.28186845779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26731061935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39287233352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36739635467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17814302444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27458906173706</t>
   </si>
   <si>
     <t xml:space="preserve">4.31826305389404</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35647821426392</t>
+    <t xml:space="preserve">4.35647869110107</t>
   </si>
   <si>
     <t xml:space="preserve">4.26549005508423</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">4.26367044448853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27640819549561</t>
+    <t xml:space="preserve">4.27640867233276</t>
   </si>
   <si>
     <t xml:space="preserve">4.14902639389038</t>
@@ -239,22 +239,22 @@
     <t xml:space="preserve">4.35829782485962</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35283851623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29460668563843</t>
+    <t xml:space="preserve">4.35283803939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29460573196411</t>
   </si>
   <si>
     <t xml:space="preserve">4.20361852645874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24001407623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34009885787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42926788330078</t>
+    <t xml:space="preserve">4.24001455307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34010028839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42926836013794</t>
   </si>
   <si>
     <t xml:space="preserve">4.34919929504395</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">4.33646059036255</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33100128173828</t>
+    <t xml:space="preserve">4.33100080490112</t>
   </si>
   <si>
     <t xml:space="preserve">4.32190275192261</t>
@@ -275,73 +275,73 @@
     <t xml:space="preserve">4.45838403701782</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28550720214844</t>
+    <t xml:space="preserve">4.2855076789856</t>
   </si>
   <si>
     <t xml:space="preserve">3.83057045936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90336036682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88516306877136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87606477737427</t>
+    <t xml:space="preserve">3.90336012840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8851637840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87606453895569</t>
   </si>
   <si>
     <t xml:space="preserve">4.00344705581665</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93065643310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9943482875824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08533525466919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96705150604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86696553230286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84876799583435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85786700248718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81237316131592</t>
+    <t xml:space="preserve">3.93065667152405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99434804916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08533573150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96705198287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86696577072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84876847267151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85786724090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8123733997345</t>
   </si>
   <si>
     <t xml:space="preserve">3.80327439308167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77597784996033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97614979743958</t>
+    <t xml:space="preserve">3.77597808837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97615075111389</t>
   </si>
   <si>
     <t xml:space="preserve">3.94885468482971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13992738723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16722440719604</t>
+    <t xml:space="preserve">4.13992786407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16722393035889</t>
   </si>
   <si>
     <t xml:space="preserve">4.33528327941895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21485900878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31675624847412</t>
+    <t xml:space="preserve">4.2148585319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31675672531128</t>
   </si>
   <si>
     <t xml:space="preserve">4.42791795730591</t>
@@ -350,19 +350,19 @@
     <t xml:space="preserve">4.19633197784424</t>
   </si>
   <si>
-    <t xml:space="preserve">4.168541431427</t>
+    <t xml:space="preserve">4.16854190826416</t>
   </si>
   <si>
     <t xml:space="preserve">4.29822969436646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30749320983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27970218658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39086389541626</t>
+    <t xml:space="preserve">4.30749368667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27970266342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3908634185791</t>
   </si>
   <si>
     <t xml:space="preserve">4.40012741088867</t>
@@ -383,22 +383,22 @@
     <t xml:space="preserve">3.9740092754364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03885316848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94622015953064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95548295974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23338556289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22412252426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24264907836914</t>
+    <t xml:space="preserve">4.03885364532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9462194442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95548319816589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23338603973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22412204742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24264860153198</t>
   </si>
   <si>
     <t xml:space="preserve">4.11296081542969</t>
@@ -407,46 +407,46 @@
     <t xml:space="preserve">4.26117610931396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91842913627625</t>
+    <t xml:space="preserve">3.9184296131134</t>
   </si>
   <si>
     <t xml:space="preserve">3.89990234375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89063930511475</t>
+    <t xml:space="preserve">3.89063906669617</t>
   </si>
   <si>
     <t xml:space="preserve">4.07590770721436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06664419174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79800462722778</t>
+    <t xml:space="preserve">4.06664371490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79800486564636</t>
   </si>
   <si>
     <t xml:space="preserve">3.73316073417664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86284875869751</t>
+    <t xml:space="preserve">3.86284852027893</t>
   </si>
   <si>
     <t xml:space="preserve">3.71463394165039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7053701877594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77021455764771</t>
+    <t xml:space="preserve">3.70537042617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77021431922913</t>
   </si>
   <si>
     <t xml:space="preserve">3.39041376113892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44599461555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58494544029236</t>
+    <t xml:space="preserve">3.44599437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58494567871094</t>
   </si>
   <si>
     <t xml:space="preserve">3.68684339523315</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">3.60347270965576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52010178565979</t>
+    <t xml:space="preserve">3.52010154724121</t>
   </si>
   <si>
     <t xml:space="preserve">3.37188696861267</t>
@@ -464,79 +464,79 @@
     <t xml:space="preserve">3.46452116966248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53862881660461</t>
+    <t xml:space="preserve">3.53862857818604</t>
   </si>
   <si>
     <t xml:space="preserve">3.5293653011322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45525789260864</t>
+    <t xml:space="preserve">3.45525813102722</t>
   </si>
   <si>
     <t xml:space="preserve">3.34409666061401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07545757293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14956521987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29777956008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31630635261536</t>
+    <t xml:space="preserve">3.07545733451843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14956498146057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29777979850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31630659103394</t>
   </si>
   <si>
     <t xml:space="preserve">3.23293590545654</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2421989440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02913999557495</t>
+    <t xml:space="preserve">3.24219918251038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02914047241211</t>
   </si>
   <si>
     <t xml:space="preserve">3.20514559745789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25146245956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10324740409851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1588282585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91797924041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74197387695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77902793884277</t>
+    <t xml:space="preserve">3.25146222114563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10324764251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15882849693298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91797947883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74197435379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77902746200562</t>
   </si>
   <si>
     <t xml:space="preserve">2.87166213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96429634094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85313510894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83460807800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84387183189392</t>
+    <t xml:space="preserve">2.96429657936096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85313534736633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83460831642151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84387159347534</t>
   </si>
   <si>
     <t xml:space="preserve">2.72344732284546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76050066947937</t>
+    <t xml:space="preserve">2.76050090789795</t>
   </si>
   <si>
     <t xml:space="preserve">2.76976442337036</t>
@@ -545,19 +545,19 @@
     <t xml:space="preserve">2.63081312179565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67712998390198</t>
+    <t xml:space="preserve">2.67713022232056</t>
   </si>
   <si>
     <t xml:space="preserve">2.38070058822632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36217379570007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29732990264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31585669517517</t>
+    <t xml:space="preserve">2.36217331886292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29732942581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31585645675659</t>
   </si>
   <si>
     <t xml:space="preserve">2.35291028022766</t>
@@ -566,25 +566,25 @@
     <t xml:space="preserve">2.26953959465027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2324857711792</t>
+    <t xml:space="preserve">2.23248553276062</t>
   </si>
   <si>
     <t xml:space="preserve">2.28806638717651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0842707157135</t>
+    <t xml:space="preserve">2.08427095413208</t>
   </si>
   <si>
     <t xml:space="preserve">2.13058805465698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22322249412537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24174928665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11206126213074</t>
+    <t xml:space="preserve">2.22322225570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24174880981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11206102371216</t>
   </si>
   <si>
     <t xml:space="preserve">2.17690491676331</t>
@@ -593,22 +593,22 @@
     <t xml:space="preserve">2.03795385360718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9916365146637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88047528266907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94531965255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92679238319397</t>
+    <t xml:space="preserve">1.99163639545441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88047540187836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94531953334808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92679262161255</t>
   </si>
   <si>
     <t xml:space="preserve">2.16764163970947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13985109329224</t>
+    <t xml:space="preserve">2.13985133171082</t>
   </si>
   <si>
     <t xml:space="preserve">2.21395897865295</t>
@@ -620,19 +620,19 @@
     <t xml:space="preserve">2.48259830474854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42701768875122</t>
+    <t xml:space="preserve">2.42701721191406</t>
   </si>
   <si>
     <t xml:space="preserve">2.38996410369873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4658362865448</t>
+    <t xml:space="preserve">2.46583604812622</t>
   </si>
   <si>
     <t xml:space="preserve">2.50406575202942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65698599815369</t>
+    <t xml:space="preserve">2.65698575973511</t>
   </si>
   <si>
     <t xml:space="preserve">2.71433067321777</t>
@@ -644,19 +644,19 @@
     <t xml:space="preserve">2.58052563667297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52318120002747</t>
+    <t xml:space="preserve">2.52318096160889</t>
   </si>
   <si>
     <t xml:space="preserve">2.42760586738586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38937592506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48495078086853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61875557899475</t>
+    <t xml:space="preserve">2.38937568664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48495101928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61875581741333</t>
   </si>
   <si>
     <t xml:space="preserve">2.56141090393066</t>
@@ -665,19 +665,19 @@
     <t xml:space="preserve">2.63787078857422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73344612121582</t>
+    <t xml:space="preserve">2.73344588279724</t>
   </si>
   <si>
     <t xml:space="preserve">2.69521570205688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75256109237671</t>
+    <t xml:space="preserve">2.75256085395813</t>
   </si>
   <si>
     <t xml:space="preserve">2.80990600585938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82902073860168</t>
+    <t xml:space="preserve">2.82902097702026</t>
   </si>
   <si>
     <t xml:space="preserve">2.84813570976257</t>
@@ -686,43 +686,43 @@
     <t xml:space="preserve">3.05840086936951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86725091934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7716760635376</t>
+    <t xml:space="preserve">2.86725115776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77167558670044</t>
   </si>
   <si>
     <t xml:space="preserve">2.676100730896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59964108467102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44672060012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37026071548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09663105010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34512591362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45981621742249</t>
+    <t xml:space="preserve">2.59964084625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44672083854675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3702609539032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09663057327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34512567520142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45981597900391</t>
   </si>
   <si>
     <t xml:space="preserve">3.74654102325439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76565623283386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01415157318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1097264289856</t>
+    <t xml:space="preserve">3.76565599441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01415109634399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10972690582275</t>
   </si>
   <si>
     <t xml:space="preserve">3.97592091560364</t>
@@ -734,34 +734,34 @@
     <t xml:space="preserve">3.82300114631653</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44070076942444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40247082710266</t>
+    <t xml:space="preserve">3.4407012462616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40247106552124</t>
   </si>
   <si>
     <t xml:space="preserve">3.36424112319946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68919587135315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72742605209351</t>
+    <t xml:space="preserve">3.68919634819031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72742629051208</t>
   </si>
   <si>
     <t xml:space="preserve">3.7083113193512</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57450580596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55539107322693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51716136932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63185095787048</t>
+    <t xml:space="preserve">3.57450604438782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55539131164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51716113090515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63185119628906</t>
   </si>
   <si>
     <t xml:space="preserve">3.53627634048462</t>
@@ -785,19 +785,19 @@
     <t xml:space="preserve">3.30689597129822</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38335609436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59362125396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47893095016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49804615974426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28778123855591</t>
+    <t xml:space="preserve">3.38335633277893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59362101554871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47893118858337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4980456829071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28778147697449</t>
   </si>
   <si>
     <t xml:space="preserve">3.67008113861084</t>
@@ -806,10 +806,10 @@
     <t xml:space="preserve">3.80388617515564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93769121170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03326606750488</t>
+    <t xml:space="preserve">3.93769192695618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03326511383057</t>
   </si>
   <si>
     <t xml:space="preserve">4.18618679046631</t>
@@ -818,55 +818,55 @@
     <t xml:space="preserve">4.30087661743164</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5302562713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51114130020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58760213851929</t>
+    <t xml:space="preserve">4.53025579452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51114082336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58760118484497</t>
   </si>
   <si>
     <t xml:space="preserve">4.49202632904053</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43468189239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62583160400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74052143096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75963735580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70229148864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68317699432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77875185012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56848621368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66406106948853</t>
+    <t xml:space="preserve">4.43468141555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62583112716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7405219078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75963640213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7022910118103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68317651748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77875137329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56848669052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66406202316284</t>
   </si>
   <si>
     <t xml:space="preserve">4.72140645980835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87432670593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96990156173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92211437225342</t>
+    <t xml:space="preserve">4.87432622909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96990203857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92211484909058</t>
   </si>
   <si>
     <t xml:space="preserve">5.1132640838623</t>
@@ -875,73 +875,73 @@
     <t xml:space="preserve">5.16105127334595</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20883941650391</t>
+    <t xml:space="preserve">5.20883893966675</t>
   </si>
   <si>
     <t xml:space="preserve">5.25662660598755</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30441474914551</t>
+    <t xml:space="preserve">5.30441427230835</t>
   </si>
   <si>
     <t xml:space="preserve">5.44777679443359</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63892698287964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59113931655884</t>
+    <t xml:space="preserve">5.63892650604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.591139793396</t>
   </si>
   <si>
     <t xml:space="preserve">5.81332683563232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71643781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42577123641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1351056098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84443950653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8250617980957</t>
+    <t xml:space="preserve">5.71643733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42577171325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13510513305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8444390296936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82506132125854</t>
   </si>
   <si>
     <t xml:space="preserve">4.80568361282349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59252834320068</t>
+    <t xml:space="preserve">4.59252786636353</t>
   </si>
   <si>
     <t xml:space="preserve">4.55377244949341</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76692819595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03821611404419</t>
+    <t xml:space="preserve">4.76692771911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03821659088135</t>
   </si>
   <si>
     <t xml:space="preserve">4.9897723197937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08666086196899</t>
+    <t xml:space="preserve">5.08666038513184</t>
   </si>
   <si>
     <t xml:space="preserve">5.18354940414429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94132709503174</t>
+    <t xml:space="preserve">4.9413275718689</t>
   </si>
   <si>
     <t xml:space="preserve">5.23199367523193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74755096435547</t>
+    <t xml:space="preserve">4.74755048751831</t>
   </si>
   <si>
     <t xml:space="preserve">5.28043842315674</t>
@@ -956,13 +956,13 @@
     <t xml:space="preserve">4.53439474105835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67003965377808</t>
+    <t xml:space="preserve">4.67003917694092</t>
   </si>
   <si>
     <t xml:space="preserve">4.78630590438843</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72817277908325</t>
+    <t xml:space="preserve">4.72817325592041</t>
   </si>
   <si>
     <t xml:space="preserve">4.70879507064819</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">5.61954879760742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32888317108154</t>
+    <t xml:space="preserve">5.32888269424438</t>
   </si>
   <si>
     <t xml:space="preserve">5.37732744216919</t>
@@ -983,13 +983,13 @@
     <t xml:space="preserve">5.57110500335693</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47421550750732</t>
+    <t xml:space="preserve">5.47421598434448</t>
   </si>
   <si>
     <t xml:space="preserve">5.66799354553223</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73376989364624</t>
+    <t xml:space="preserve">6.7337703704834</t>
   </si>
   <si>
     <t xml:space="preserve">6.29777050018311</t>
@@ -1004,13 +1004,13 @@
     <t xml:space="preserve">6.58843755722046</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63688087463379</t>
+    <t xml:space="preserve">6.63688135147095</t>
   </si>
   <si>
     <t xml:space="preserve">6.2493257522583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34621572494507</t>
+    <t xml:space="preserve">6.34621524810791</t>
   </si>
   <si>
     <t xml:space="preserve">6.53999280929565</t>
@@ -1019,19 +1019,19 @@
     <t xml:space="preserve">6.39465951919556</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71998977661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99332427978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09021472930908</t>
+    <t xml:space="preserve">8.71999073028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.993323802948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09021377563477</t>
   </si>
   <si>
     <t xml:space="preserve">8.04176807403564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94488000869751</t>
+    <t xml:space="preserve">7.94487953186035</t>
   </si>
   <si>
     <t xml:space="preserve">7.84799098968506</t>
@@ -1040,22 +1040,22 @@
     <t xml:space="preserve">7.89643526077271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38087844848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2702112197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88265419006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.173321723938</t>
+    <t xml:space="preserve">8.38087749481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2702102661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88265514373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1733207702637</t>
   </si>
   <si>
     <t xml:space="preserve">9.9795446395874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0764322280884</t>
+    <t xml:space="preserve">10.0764331817627</t>
   </si>
   <si>
     <t xml:space="preserve">11.2390975952148</t>
@@ -1067,13 +1067,13 @@
     <t xml:space="preserve">13.0799856185913</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2737617492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9830951690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.436427116394</t>
+    <t xml:space="preserve">13.2737627029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9830961227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4364280700684</t>
   </si>
   <si>
     <t xml:space="preserve">14.3395395278931</t>
@@ -1085,22 +1085,22 @@
     <t xml:space="preserve">16.1669788360596</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1930646896362</t>
+    <t xml:space="preserve">15.1930656433105</t>
   </si>
   <si>
     <t xml:space="preserve">15.0956735610962</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9008913040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.634801864624</t>
+    <t xml:space="preserve">14.9008903503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6348009109497</t>
   </si>
   <si>
     <t xml:space="preserve">12.0765390396118</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4661054611206</t>
+    <t xml:space="preserve">12.4661045074463</t>
   </si>
   <si>
     <t xml:space="preserve">13.4400196075439</t>
@@ -1109,13 +1109,13 @@
     <t xml:space="preserve">13.9269771575928</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0243673324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2191505432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8034982681274</t>
+    <t xml:space="preserve">14.0243682861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2191514968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8034992218018</t>
   </si>
   <si>
     <t xml:space="preserve">14.4139337539673</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">14.6087160110474</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7061080932617</t>
+    <t xml:space="preserve">14.706109046936</t>
   </si>
   <si>
     <t xml:space="preserve">14.5113248825073</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">13.8295850753784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5374097824097</t>
+    <t xml:space="preserve">13.537410736084</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452373504639</t>
@@ -1169,25 +1169,25 @@
     <t xml:space="preserve">11.1026248931885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93392562866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.713059425354</t>
+    <t xml:space="preserve">9.93392658233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7130584716797</t>
   </si>
   <si>
     <t xml:space="preserve">11.2000160217285</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9791479110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8817567825317</t>
+    <t xml:space="preserve">11.9791469573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8817558288574</t>
   </si>
   <si>
     <t xml:space="preserve">10.9078416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2974081039429</t>
+    <t xml:space="preserve">11.2974071502686</t>
   </si>
   <si>
     <t xml:space="preserve">11.3947992324829</t>
@@ -1202,19 +1202,19 @@
     <t xml:space="preserve">11.7843647003174</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4921903610229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8104515075684</t>
+    <t xml:space="preserve">11.4921894073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.810450553894</t>
   </si>
   <si>
     <t xml:space="preserve">10.4208841323853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2261018753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3234939575195</t>
+    <t xml:space="preserve">10.2261009216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3234930038452</t>
   </si>
   <si>
     <t xml:space="preserve">10.1287107467651</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">12.9530620574951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6800222396851</t>
+    <t xml:space="preserve">15.6800231933594</t>
   </si>
   <si>
     <t xml:space="preserve">13.7321939468384</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">14.3652381896973</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0730638504028</t>
+    <t xml:space="preserve">14.0730628967285</t>
   </si>
   <si>
     <t xml:space="preserve">15.1443700790405</t>
@@ -57487,7 +57487,7 @@
     </row>
     <row r="2117">
       <c r="A2117" s="1" t="n">
-        <v>45974.5701967593</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B2117" t="n">
         <v>125</v>
@@ -57508,6 +57508,32 @@
         <v>664</v>
       </c>
       <c r="H2117" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" s="1" t="n">
+        <v>45975.4350231482</v>
+      </c>
+      <c r="B2118" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2118" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="D2118" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="E2118" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="F2118" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="G2118" t="s">
+        <v>664</v>
+      </c>
+      <c r="H2118" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CULT.MI.xlsx
+++ b/data/CULT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68585205078125</t>
+    <t xml:space="preserve">4.68585252761841</t>
   </si>
   <si>
     <t xml:space="preserve">CULT.MI</t>
@@ -47,19 +47,19 @@
     <t xml:space="preserve">4.57666730880737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59486532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60851335525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58576726913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48931980133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56301927566528</t>
+    <t xml:space="preserve">4.5948657989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60851287841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58576631546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48931932449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56301879882812</t>
   </si>
   <si>
     <t xml:space="preserve">4.51297616958618</t>
@@ -68,91 +68,91 @@
     <t xml:space="preserve">4.46020317077637</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29824638366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21271753311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18178224563599</t>
+    <t xml:space="preserve">4.29824542999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21271848678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18178272247314</t>
   </si>
   <si>
     <t xml:space="preserve">4.23091554641724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36375665664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38195419311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35101842880249</t>
+    <t xml:space="preserve">4.36375713348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38195466995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35101890563965</t>
   </si>
   <si>
     <t xml:space="preserve">4.28914785385132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24183320999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22909498214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10535335540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09443426132202</t>
+    <t xml:space="preserve">4.24183368682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22909545898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1053524017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09443473815918</t>
   </si>
   <si>
     <t xml:space="preserve">4.10899209976196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99616861343384</t>
+    <t xml:space="preserve">3.99616813659668</t>
   </si>
   <si>
     <t xml:space="preserve">4.04712057113647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0398416519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96341276168823</t>
+    <t xml:space="preserve">4.03984212875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96341228485107</t>
   </si>
   <si>
     <t xml:space="preserve">4.07441711425781</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3200831413269</t>
+    <t xml:space="preserve">4.32008361816406</t>
   </si>
   <si>
     <t xml:space="preserve">4.24911260604858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97979021072388</t>
+    <t xml:space="preserve">3.9797899723053</t>
   </si>
   <si>
     <t xml:space="preserve">4.0689582824707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0543999671936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98524904251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0507607460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07259702682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0380220413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04530143737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03074359893799</t>
+    <t xml:space="preserve">4.05439949035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98524951934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05076122283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07259750366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03802251815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04530096054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03074312210083</t>
   </si>
   <si>
     <t xml:space="preserve">4.01254558563232</t>
@@ -161,46 +161,46 @@
     <t xml:space="preserve">4.04894018173218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05985832214355</t>
+    <t xml:space="preserve">4.05985927581787</t>
   </si>
   <si>
     <t xml:space="preserve">4.07623672485352</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91245913505554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99070835113525</t>
+    <t xml:space="preserve">3.91245985031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99070882797241</t>
   </si>
   <si>
     <t xml:space="preserve">4.01072549819946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92155838012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00162649154663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05803918838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21635723114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2218165397644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18542098999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16176509857178</t>
+    <t xml:space="preserve">3.92155861854553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00162696838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05804014205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21635675430298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22181701660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18542194366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16176414489746</t>
   </si>
   <si>
     <t xml:space="preserve">4.35465812683105</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28186845779419</t>
+    <t xml:space="preserve">4.28186798095703</t>
   </si>
   <si>
     <t xml:space="preserve">4.26731014251709</t>
@@ -209,13 +209,13 @@
     <t xml:space="preserve">4.39287328720093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36739635467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17814302444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27459001541138</t>
+    <t xml:space="preserve">4.36739730834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17814207077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27458953857422</t>
   </si>
   <si>
     <t xml:space="preserve">4.31826305389404</t>
@@ -224,34 +224,34 @@
     <t xml:space="preserve">4.35647821426392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26549053192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26366996765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27640819549561</t>
+    <t xml:space="preserve">4.26549100875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26367044448853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27640962600708</t>
   </si>
   <si>
     <t xml:space="preserve">4.14902687072754</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35829782485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35283756256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29460620880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2036190032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24001359939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3400993347168</t>
+    <t xml:space="preserve">4.35829830169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35283851623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29460716247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20361948013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24001407623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34010076522827</t>
   </si>
   <si>
     <t xml:space="preserve">4.42926788330078</t>
@@ -260,94 +260,94 @@
     <t xml:space="preserve">4.34919929504395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33646059036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33100128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32190275192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46748208999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45838356018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28550720214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83057022094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90336108207703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88516283035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87606453895569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00344705581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93065667152405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99434781074524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08533573150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96705174446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86696600914001</t>
+    <t xml:space="preserve">4.33646106719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33100271224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32190322875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4674825668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45838403701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28550815582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.830570936203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90336132049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88516354560852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87606501579285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00344753265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93065714836121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99434876441956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08533477783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96705198287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86696577072144</t>
   </si>
   <si>
     <t xml:space="preserve">3.84876847267151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85786628723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81237387657166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80327439308167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77597808837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97615122795105</t>
+    <t xml:space="preserve">3.8578667640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81237316131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80327463150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77597832679749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97615075111389</t>
   </si>
   <si>
     <t xml:space="preserve">3.94885468482971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13992786407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16722345352173</t>
+    <t xml:space="preserve">4.13992881774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16722440719604</t>
   </si>
   <si>
     <t xml:space="preserve">4.3352837562561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21485900878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31675624847412</t>
+    <t xml:space="preserve">4.21485948562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31675672531128</t>
   </si>
   <si>
     <t xml:space="preserve">4.42791748046875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1963324546814</t>
+    <t xml:space="preserve">4.19633197784424</t>
   </si>
   <si>
     <t xml:space="preserve">4.16854190826416</t>
@@ -356,85 +356,85 @@
     <t xml:space="preserve">4.29823017120361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30749320983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27970266342163</t>
+    <t xml:space="preserve">4.30749273300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27970314025879</t>
   </si>
   <si>
     <t xml:space="preserve">4.39086389541626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40012741088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35380935668945</t>
+    <t xml:space="preserve">4.40012788772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35381031036377</t>
   </si>
   <si>
     <t xml:space="preserve">4.08517074584961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93695616722107</t>
+    <t xml:space="preserve">3.93695592880249</t>
   </si>
   <si>
     <t xml:space="preserve">4.00180006027222</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97400999069214</t>
+    <t xml:space="preserve">3.9740104675293</t>
   </si>
   <si>
     <t xml:space="preserve">4.03885364532471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94621968269348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95548248291016</t>
+    <t xml:space="preserve">3.94621992111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95548295974731</t>
   </si>
   <si>
     <t xml:space="preserve">4.23338556289673</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22412252426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24264907836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.112961769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26117563247681</t>
+    <t xml:space="preserve">4.22412204742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2426495552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11296129226685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26117610931396</t>
   </si>
   <si>
     <t xml:space="preserve">3.91842937469482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89990210533142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89063882827759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0759072303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06664371490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79800415039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73316073417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86284899711609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71463394165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70537042617798</t>
+    <t xml:space="preserve">3.89990234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89063858985901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07590770721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06664419174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79800486564636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73316097259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86284923553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71463418006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7053701877594</t>
   </si>
   <si>
     <t xml:space="preserve">3.77021431922913</t>
@@ -446,22 +446,22 @@
     <t xml:space="preserve">3.44599437713623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58494544029236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68684339523315</t>
+    <t xml:space="preserve">3.58494567871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68684363365173</t>
   </si>
   <si>
     <t xml:space="preserve">3.60347294807434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52010178565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37188720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46452164649963</t>
+    <t xml:space="preserve">3.52010226249695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37188696861267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46452116966248</t>
   </si>
   <si>
     <t xml:space="preserve">3.53862881660461</t>
@@ -476,7 +476,7 @@
     <t xml:space="preserve">3.34409666061401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07545733451843</t>
+    <t xml:space="preserve">3.07545781135559</t>
   </si>
   <si>
     <t xml:space="preserve">3.14956498146057</t>
@@ -485,25 +485,25 @@
     <t xml:space="preserve">3.29777956008911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31630659103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23293590545654</t>
+    <t xml:space="preserve">3.31630635261536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23293542861938</t>
   </si>
   <si>
     <t xml:space="preserve">3.24219918251038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02914023399353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20514559745789</t>
+    <t xml:space="preserve">3.02914047241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20514512062073</t>
   </si>
   <si>
     <t xml:space="preserve">3.25146245956421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10324764251709</t>
+    <t xml:space="preserve">3.10324740409851</t>
   </si>
   <si>
     <t xml:space="preserve">3.1588282585144</t>
@@ -515,67 +515,67 @@
     <t xml:space="preserve">2.74197435379028</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77902746200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.871661901474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96429657936096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85313510894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83460831642151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84387159347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72344708442688</t>
+    <t xml:space="preserve">2.77902793884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87166213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96429634094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85313534736633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83460879325867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84387183189392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72344732284546</t>
   </si>
   <si>
     <t xml:space="preserve">2.76050090789795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76976466178894</t>
+    <t xml:space="preserve">2.76976442337036</t>
   </si>
   <si>
     <t xml:space="preserve">2.63081312179565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67713022232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38070058822632</t>
+    <t xml:space="preserve">2.67712998390198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38070034980774</t>
   </si>
   <si>
     <t xml:space="preserve">2.36217379570007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29732966423035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31585645675659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35291004180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26953911781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23248529434204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28806638717651</t>
+    <t xml:space="preserve">2.29732942581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31585621833801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3529098033905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26953935623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23248600959778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28806614875793</t>
   </si>
   <si>
     <t xml:space="preserve">2.08427095413208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1305878162384</t>
+    <t xml:space="preserve">2.13058805465698</t>
   </si>
   <si>
     <t xml:space="preserve">2.22322249412537</t>
@@ -584,22 +584,22 @@
     <t xml:space="preserve">2.24174928665161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11206126213074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17690467834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0379536151886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9916365146637</t>
+    <t xml:space="preserve">2.11206102371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17690515518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03795385360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99163687229156</t>
   </si>
   <si>
     <t xml:space="preserve">1.88047552108765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94531941413879</t>
+    <t xml:space="preserve">1.9453192949295</t>
   </si>
   <si>
     <t xml:space="preserve">1.92679250240326</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">2.16764187812805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13985133171082</t>
+    <t xml:space="preserve">2.13985157012939</t>
   </si>
   <si>
     <t xml:space="preserve">2.21395874023438</t>
@@ -617,16 +617,16 @@
     <t xml:space="preserve">2.40849041938782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48259806632996</t>
+    <t xml:space="preserve">2.48259782791138</t>
   </si>
   <si>
     <t xml:space="preserve">2.42701745033264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38996386528015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46583580970764</t>
+    <t xml:space="preserve">2.38996362686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46583557128906</t>
   </si>
   <si>
     <t xml:space="preserve">2.50406575202942</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">2.65698599815369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71433091163635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5422956943512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58052611351013</t>
+    <t xml:space="preserve">2.71433115005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54229593276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58052587509155</t>
   </si>
   <si>
     <t xml:space="preserve">2.52318096160889</t>
@@ -653,19 +653,19 @@
     <t xml:space="preserve">2.38937568664551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48495078086853</t>
+    <t xml:space="preserve">2.48495054244995</t>
   </si>
   <si>
     <t xml:space="preserve">2.61875581741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56141090393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63787078857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73344564437866</t>
+    <t xml:space="preserve">2.56141066551208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6378710269928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73344588279724</t>
   </si>
   <si>
     <t xml:space="preserve">2.69521594047546</t>
@@ -680,25 +680,25 @@
     <t xml:space="preserve">2.82902097702026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84813594818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05840110778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86725068092346</t>
+    <t xml:space="preserve">2.84813570976257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05840086936951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86725091934204</t>
   </si>
   <si>
     <t xml:space="preserve">2.7716760635376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67610049247742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59964084625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44672060012817</t>
+    <t xml:space="preserve">2.676100730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59964060783386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44672083854675</t>
   </si>
   <si>
     <t xml:space="preserve">2.40849089622498</t>
@@ -707,7 +707,7 @@
     <t xml:space="preserve">2.37026071548462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09663105010986</t>
+    <t xml:space="preserve">3.09663081169128</t>
   </si>
   <si>
     <t xml:space="preserve">3.34512615203857</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">3.45981597900391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74654102325439</t>
+    <t xml:space="preserve">3.74654150009155</t>
   </si>
   <si>
     <t xml:space="preserve">3.76565647125244</t>
@@ -725,28 +725,28 @@
     <t xml:space="preserve">4.01415109634399</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10972595214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97592091560364</t>
+    <t xml:space="preserve">4.1097264289856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97592115402222</t>
   </si>
   <si>
     <t xml:space="preserve">3.88034629821777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82300138473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44070100784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40247106552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36424112319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68919587135315</t>
+    <t xml:space="preserve">3.82300114631653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44070076942444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40247082710266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36424088478088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68919610977173</t>
   </si>
   <si>
     <t xml:space="preserve">3.72742605209351</t>
@@ -755,19 +755,19 @@
     <t xml:space="preserve">3.7083113193512</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5745062828064</t>
+    <t xml:space="preserve">3.57450604438782</t>
   </si>
   <si>
     <t xml:space="preserve">3.55539107322693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51716113090515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63185095787048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53627634048462</t>
+    <t xml:space="preserve">3.51716089248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63185143470764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53627610206604</t>
   </si>
   <si>
     <t xml:space="preserve">3.61273598670959</t>
@@ -776,79 +776,79 @@
     <t xml:space="preserve">3.65096616744995</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24955129623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32601118087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42158603668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3068962097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38335609436035</t>
+    <t xml:space="preserve">3.24955105781555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32601094245911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42158579826355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30689573287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38335585594177</t>
   </si>
   <si>
     <t xml:space="preserve">3.59362125396729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47893118858337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49804615974426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28778123855591</t>
+    <t xml:space="preserve">3.47893095016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49804592132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28778100013733</t>
   </si>
   <si>
     <t xml:space="preserve">3.67008113861084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80388617515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93769121170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03326606750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18618679046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30087661743164</t>
+    <t xml:space="preserve">3.80388641357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93769097328186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03326654434204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18618631362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30087614059448</t>
   </si>
   <si>
     <t xml:space="preserve">4.5302562713623</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51114082336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58760166168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49202585220337</t>
+    <t xml:space="preserve">4.51114130020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58760213851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49202632904053</t>
   </si>
   <si>
     <t xml:space="preserve">4.43468189239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62583160400391</t>
+    <t xml:space="preserve">4.62583208084106</t>
   </si>
   <si>
     <t xml:space="preserve">4.74052143096924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75963687896729</t>
+    <t xml:space="preserve">4.75963592529297</t>
   </si>
   <si>
     <t xml:space="preserve">4.70229148864746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68317699432373</t>
+    <t xml:space="preserve">4.68317604064941</t>
   </si>
   <si>
     <t xml:space="preserve">4.77875137329102</t>
@@ -857,94 +857,94 @@
     <t xml:space="preserve">4.56848621368408</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66406106948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72140693664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87432622909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96990156173706</t>
+    <t xml:space="preserve">4.66406202316284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72140598297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87432670593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9699010848999</t>
   </si>
   <si>
     <t xml:space="preserve">4.92211389541626</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1132640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16105222702026</t>
+    <t xml:space="preserve">5.11326456069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16105175018311</t>
   </si>
   <si>
     <t xml:space="preserve">5.20883846282959</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25662708282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30441474914551</t>
+    <t xml:space="preserve">5.25662660598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30441427230835</t>
   </si>
   <si>
     <t xml:space="preserve">5.44777679443359</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63892650604248</t>
+    <t xml:space="preserve">5.63892698287964</t>
   </si>
   <si>
     <t xml:space="preserve">5.59113931655884</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81332635879517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71643829345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42577171325684</t>
+    <t xml:space="preserve">5.81332683563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71643781661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42577123641968</t>
   </si>
   <si>
     <t xml:space="preserve">5.13510513305664</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84443950653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8250617980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80568361282349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59252738952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55377244949341</t>
+    <t xml:space="preserve">4.84443855285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82506084442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80568313598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59252786636353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55377292633057</t>
   </si>
   <si>
     <t xml:space="preserve">4.76692771911621</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03821659088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98977279663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08666086196899</t>
+    <t xml:space="preserve">5.03821563720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98977184295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08666038513184</t>
   </si>
   <si>
     <t xml:space="preserve">5.18354988098145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94132709503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23199415206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74755048751831</t>
+    <t xml:space="preserve">4.9413275718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23199367523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74754953384399</t>
   </si>
   <si>
     <t xml:space="preserve">5.28043794631958</t>
@@ -953,22 +953,22 @@
     <t xml:space="preserve">4.89288330078125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63128423690796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53439474105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67003917694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78630590438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72817230224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70879507064819</t>
+    <t xml:space="preserve">4.6312837600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53439521789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67003965377808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78630542755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72817277908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70879459381104</t>
   </si>
   <si>
     <t xml:space="preserve">5.91021585464478</t>
@@ -977,37 +977,37 @@
     <t xml:space="preserve">5.61954927444458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32888317108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37732744216919</t>
+    <t xml:space="preserve">5.32888269424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37732696533203</t>
   </si>
   <si>
     <t xml:space="preserve">5.57110452651978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47421550750732</t>
+    <t xml:space="preserve">5.47421598434448</t>
   </si>
   <si>
     <t xml:space="preserve">5.66799354553223</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73376941680908</t>
+    <t xml:space="preserve">6.73376989364624</t>
   </si>
   <si>
     <t xml:space="preserve">6.29777050018311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4431037902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68532609939575</t>
+    <t xml:space="preserve">6.44310426712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68532514572144</t>
   </si>
   <si>
     <t xml:space="preserve">6.5884370803833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63688087463379</t>
+    <t xml:space="preserve">6.63688135147095</t>
   </si>
   <si>
     <t xml:space="preserve">6.24932622909546</t>
@@ -1019,67 +1019,67 @@
     <t xml:space="preserve">6.53999280929565</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3946590423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71998977661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99332332611084</t>
+    <t xml:space="preserve">6.39465999603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71999073028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.993323802948</t>
   </si>
   <si>
     <t xml:space="preserve">8.09021377563477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04176807403564</t>
+    <t xml:space="preserve">8.04176902770996</t>
   </si>
   <si>
     <t xml:space="preserve">7.94488000869751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84799098968506</t>
+    <t xml:space="preserve">7.84799194335938</t>
   </si>
   <si>
     <t xml:space="preserve">7.89643478393555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38087844848633</t>
+    <t xml:space="preserve">8.38087940216064</t>
   </si>
   <si>
     <t xml:space="preserve">10.2702102661133</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88265419006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.173321723938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97954559326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0764331817627</t>
+    <t xml:space="preserve">9.88265514373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1733207702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97954368591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0764312744141</t>
   </si>
   <si>
     <t xml:space="preserve">11.2390985488892</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6266527175903</t>
+    <t xml:space="preserve">11.6266536712646</t>
   </si>
   <si>
     <t xml:space="preserve">13.0799856185913</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2737617492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.983097076416</t>
+    <t xml:space="preserve">13.2737627029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9830961227417</t>
   </si>
   <si>
     <t xml:space="preserve">14.436427116394</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3395404815674</t>
+    <t xml:space="preserve">14.3395395278931</t>
   </si>
   <si>
     <t xml:space="preserve">15.0177612304688</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">15.0956745147705</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9008913040161</t>
+    <t xml:space="preserve">14.9008903503418</t>
   </si>
   <si>
     <t xml:space="preserve">13.634801864624</t>
@@ -1103,34 +1103,34 @@
     <t xml:space="preserve">12.0765390396118</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4661054611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4400196075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9269762039185</t>
+    <t xml:space="preserve">12.4661045074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4400186538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9269771575928</t>
   </si>
   <si>
     <t xml:space="preserve">14.0243673324585</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2191505432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8034992218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4139347076416</t>
+    <t xml:space="preserve">14.2191524505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8035001754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4139337539673</t>
   </si>
   <si>
     <t xml:space="preserve">14.6087160110474</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7061071395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5113248825073</t>
+    <t xml:space="preserve">14.706109046936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5113258361816</t>
   </si>
   <si>
     <t xml:space="preserve">13.3426275253296</t>
@@ -1145,10 +1145,10 @@
     <t xml:space="preserve">13.8295850753784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5374097824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2452363967896</t>
+    <t xml:space="preserve">13.537410736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2452373504639</t>
   </si>
   <si>
     <t xml:space="preserve">12.8556699752808</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">12.758279800415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5634965896606</t>
+    <t xml:space="preserve">12.5634956359863</t>
   </si>
   <si>
     <t xml:space="preserve">12.1739301681519</t>
@@ -1169,64 +1169,64 @@
     <t xml:space="preserve">11.686972618103</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1026248931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93392562866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.713059425354</t>
+    <t xml:space="preserve">11.1026239395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93392753601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7130584716797</t>
   </si>
   <si>
     <t xml:space="preserve">11.2000160217285</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9791479110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8817567825317</t>
+    <t xml:space="preserve">11.9791469573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8817558288574</t>
   </si>
   <si>
     <t xml:space="preserve">10.9078416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2974081039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3947992324829</t>
+    <t xml:space="preserve">11.2974061965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3947982788086</t>
   </si>
   <si>
     <t xml:space="preserve">11.589581489563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0052328109741</t>
+    <t xml:space="preserve">11.0052318572998</t>
   </si>
   <si>
     <t xml:space="preserve">11.7843647003174</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4921913146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8104515075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4208850860596</t>
+    <t xml:space="preserve">11.4921903610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.810450553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4208841323853</t>
   </si>
   <si>
     <t xml:space="preserve">10.2261018753052</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3234930038452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1287107467651</t>
+    <t xml:space="preserve">10.3234939575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1287097930908</t>
   </si>
   <si>
     <t xml:space="preserve">10.0313196182251</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73914432525635</t>
+    <t xml:space="preserve">9.73914527893066</t>
   </si>
   <si>
     <t xml:space="preserve">9.54436111450195</t>
@@ -1247,22 +1247,22 @@
     <t xml:space="preserve">12.9530620574951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6800222396851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7321949005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1704549789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3652391433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0730638504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1443700790405</t>
+    <t xml:space="preserve">15.6800241470337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7321939468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1704559326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3652381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0730628967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1443691253662</t>
   </si>
   <si>
     <t xml:space="preserve">15.5364561080933</t>
@@ -57594,7 +57594,7 @@
     </row>
     <row r="2121">
       <c r="A2121" s="1" t="n">
-        <v>45980.5046990741</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2121" t="n">
         <v>250</v>
@@ -57615,6 +57615,32 @@
         <v>665</v>
       </c>
       <c r="H2121" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" s="1" t="n">
+        <v>45981.6911689815</v>
+      </c>
+      <c r="B2122" t="n">
+        <v>375</v>
+      </c>
+      <c r="C2122" t="n">
+        <v>14.1999998092651</v>
+      </c>
+      <c r="D2122" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="E2122" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="F2122" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="G2122" t="s">
+        <v>665</v>
+      </c>
+      <c r="H2122" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CULT.MI.xlsx
+++ b/data/CULT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="707">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68585300445557</t>
+    <t xml:space="preserve">4.68585252761841</t>
   </si>
   <si>
     <t xml:space="preserve">CULT.MI</t>
@@ -47,19 +47,19 @@
     <t xml:space="preserve">4.57666778564453</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5948657989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60851335525513</t>
+    <t xml:space="preserve">4.59486532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60851383209229</t>
   </si>
   <si>
     <t xml:space="preserve">4.58576631546021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48931884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56301975250244</t>
+    <t xml:space="preserve">4.48931980133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56301927566528</t>
   </si>
   <si>
     <t xml:space="preserve">4.51297664642334</t>
@@ -68,10 +68,10 @@
     <t xml:space="preserve">4.46020364761353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29824590682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21271848678589</t>
+    <t xml:space="preserve">4.29824542999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21271800994873</t>
   </si>
   <si>
     <t xml:space="preserve">4.1817831993103</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">4.23091554641724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36375761032104</t>
+    <t xml:space="preserve">4.36375665664673</t>
   </si>
   <si>
     <t xml:space="preserve">4.38195466995239</t>
@@ -89,16 +89,16 @@
     <t xml:space="preserve">4.35101890563965</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28914737701416</t>
+    <t xml:space="preserve">4.28914785385132</t>
   </si>
   <si>
     <t xml:space="preserve">4.24183368682861</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22909498214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10535335540771</t>
+    <t xml:space="preserve">4.22909545898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1053524017334</t>
   </si>
   <si>
     <t xml:space="preserve">4.09443426132202</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">4.10899257659912</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99616837501526</t>
+    <t xml:space="preserve">3.99616765975952</t>
   </si>
   <si>
     <t xml:space="preserve">4.04712057113647</t>
@@ -116,10 +116,10 @@
     <t xml:space="preserve">4.0398416519165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96341228485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07441663742065</t>
+    <t xml:space="preserve">3.96341252326965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07441759109497</t>
   </si>
   <si>
     <t xml:space="preserve">4.32008266448975</t>
@@ -131,22 +131,22 @@
     <t xml:space="preserve">3.97979044914246</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0689582824707</t>
+    <t xml:space="preserve">4.06895732879639</t>
   </si>
   <si>
     <t xml:space="preserve">4.05439949035645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98524928092957</t>
+    <t xml:space="preserve">3.98524951934814</t>
   </si>
   <si>
     <t xml:space="preserve">4.05076026916504</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07259750366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03802299499512</t>
+    <t xml:space="preserve">4.07259702682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0380220413208</t>
   </si>
   <si>
     <t xml:space="preserve">4.04530143737793</t>
@@ -161,46 +161,46 @@
     <t xml:space="preserve">4.04894065856934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05985832214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07623720169067</t>
+    <t xml:space="preserve">4.05985879898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07623672485352</t>
   </si>
   <si>
     <t xml:space="preserve">3.91245985031128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99070858955383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01072549819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92155861854553</t>
+    <t xml:space="preserve">3.99070906639099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01072645187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92155790328979</t>
   </si>
   <si>
     <t xml:space="preserve">4.00162696838379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05803871154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21635770797729</t>
+    <t xml:space="preserve">4.05803918838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21635723114014</t>
   </si>
   <si>
     <t xml:space="preserve">4.22181701660156</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18542194366455</t>
+    <t xml:space="preserve">4.18542146682739</t>
   </si>
   <si>
     <t xml:space="preserve">4.16176462173462</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35465717315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28186798095703</t>
+    <t xml:space="preserve">4.35465812683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28186845779419</t>
   </si>
   <si>
     <t xml:space="preserve">4.26731014251709</t>
@@ -209,139 +209,139 @@
     <t xml:space="preserve">4.39287281036377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36739730834961</t>
+    <t xml:space="preserve">4.36739635467529</t>
   </si>
   <si>
     <t xml:space="preserve">4.17814302444458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27458906173706</t>
+    <t xml:space="preserve">4.27458953857422</t>
   </si>
   <si>
     <t xml:space="preserve">4.3182635307312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35647821426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26548957824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26367044448853</t>
+    <t xml:space="preserve">4.35647773742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26549100875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26367092132568</t>
   </si>
   <si>
     <t xml:space="preserve">4.27640867233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14902639389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35829782485962</t>
+    <t xml:space="preserve">4.14902687072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35829830169678</t>
   </si>
   <si>
     <t xml:space="preserve">4.35283803939819</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29460716247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20361852645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24001407623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34009981155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42926788330078</t>
+    <t xml:space="preserve">4.29460620880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2036190032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24001359939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34010028839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4292688369751</t>
   </si>
   <si>
     <t xml:space="preserve">4.34919929504395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33646059036255</t>
+    <t xml:space="preserve">4.33646106719971</t>
   </si>
   <si>
     <t xml:space="preserve">4.33100175857544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32190275192261</t>
+    <t xml:space="preserve">4.32190322875977</t>
   </si>
   <si>
     <t xml:space="preserve">4.46748208999634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45838403701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28550720214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.830570936203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90336036682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88516283035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87606430053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00344705581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93065643310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99434781074524</t>
+    <t xml:space="preserve">4.45838451385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28550815582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83057069778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90336084365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8851625919342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87606549263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00344753265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93065690994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99434804916382</t>
   </si>
   <si>
     <t xml:space="preserve">4.08533525466919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96705174446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86696529388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84876823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85786700248718</t>
+    <t xml:space="preserve">3.96705198287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86696624755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84876847267151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8578667640686</t>
   </si>
   <si>
     <t xml:space="preserve">3.81237316131592</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80327415466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77597808837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97615027427673</t>
+    <t xml:space="preserve">3.80327463150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77597856521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97615098953247</t>
   </si>
   <si>
     <t xml:space="preserve">3.94885468482971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13992834091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16722393035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33528232574463</t>
+    <t xml:space="preserve">4.13992786407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16722440719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33528327941895</t>
   </si>
   <si>
     <t xml:space="preserve">4.21485900878906</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31675672531128</t>
+    <t xml:space="preserve">4.31675624847412</t>
   </si>
   <si>
     <t xml:space="preserve">4.42791795730591</t>
@@ -350,10 +350,10 @@
     <t xml:space="preserve">4.19633197784424</t>
   </si>
   <si>
-    <t xml:space="preserve">4.168541431427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29822969436646</t>
+    <t xml:space="preserve">4.16854190826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29823017120361</t>
   </si>
   <si>
     <t xml:space="preserve">4.30749320983887</t>
@@ -362,85 +362,85 @@
     <t xml:space="preserve">4.27970266342163</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39086389541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40012741088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35381031036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08517026901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93695569038391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00179958343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97400951385498</t>
+    <t xml:space="preserve">4.3908634185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40012788772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35380983352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08517074584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93695664405823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00180006027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97400975227356</t>
   </si>
   <si>
     <t xml:space="preserve">4.03885412216187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94621968269348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95548272132874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23338651657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22412157058716</t>
+    <t xml:space="preserve">3.94622039794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95548224449158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23338508605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22412252426147</t>
   </si>
   <si>
     <t xml:space="preserve">4.24264907836914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11296129226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26117563247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91842937469482</t>
+    <t xml:space="preserve">4.11296081542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26117610931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9184296131134</t>
   </si>
   <si>
     <t xml:space="preserve">3.89990234375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89063835144043</t>
+    <t xml:space="preserve">3.89063858985901</t>
   </si>
   <si>
     <t xml:space="preserve">4.07590770721436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06664323806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79800462722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73316121101379</t>
+    <t xml:space="preserve">4.06664371490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7980043888092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73316097259521</t>
   </si>
   <si>
     <t xml:space="preserve">3.86284875869751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71463418006897</t>
+    <t xml:space="preserve">3.71463394165039</t>
   </si>
   <si>
     <t xml:space="preserve">3.70537042617798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77021455764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39041376113892</t>
+    <t xml:space="preserve">3.77021431922913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3904139995575</t>
   </si>
   <si>
     <t xml:space="preserve">3.44599461555481</t>
@@ -449,22 +449,22 @@
     <t xml:space="preserve">3.58494567871094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68684387207031</t>
+    <t xml:space="preserve">3.68684339523315</t>
   </si>
   <si>
     <t xml:space="preserve">3.60347294807434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52010226249695</t>
+    <t xml:space="preserve">3.52010154724121</t>
   </si>
   <si>
     <t xml:space="preserve">3.37188720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46452140808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53862881660461</t>
+    <t xml:space="preserve">3.46452164649963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53862857818604</t>
   </si>
   <si>
     <t xml:space="preserve">3.5293653011322</t>
@@ -476,25 +476,25 @@
     <t xml:space="preserve">3.34409666061401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07545733451843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14956521987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29777979850769</t>
+    <t xml:space="preserve">3.07545757293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14956498146057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29777956008911</t>
   </si>
   <si>
     <t xml:space="preserve">3.31630635261536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23293590545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24219918251038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02914047241211</t>
+    <t xml:space="preserve">3.23293566703796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2421989440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02914023399353</t>
   </si>
   <si>
     <t xml:space="preserve">3.20514559745789</t>
@@ -503,13 +503,13 @@
     <t xml:space="preserve">3.25146245956421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10324764251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15882849693298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91797924041748</t>
+    <t xml:space="preserve">3.10324740409851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1588282585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91797947883606</t>
   </si>
   <si>
     <t xml:space="preserve">2.7419741153717</t>
@@ -518,19 +518,19 @@
     <t xml:space="preserve">2.77902793884277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87166213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96429634094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85313510894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83460855484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84387183189392</t>
+    <t xml:space="preserve">2.87166166305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96429657936096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85313487052917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83460831642151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84387159347534</t>
   </si>
   <si>
     <t xml:space="preserve">2.72344732284546</t>
@@ -539,25 +539,25 @@
     <t xml:space="preserve">2.76050114631653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76976418495178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63081288337708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67713046073914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38070011138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36217355728149</t>
+    <t xml:space="preserve">2.76976442337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63081312179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67713022232056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38070034980774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36217331886292</t>
   </si>
   <si>
     <t xml:space="preserve">2.29732966423035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31585621833801</t>
+    <t xml:space="preserve">2.31585645675659</t>
   </si>
   <si>
     <t xml:space="preserve">2.35291028022766</t>
@@ -566,16 +566,16 @@
     <t xml:space="preserve">2.26953959465027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2324857711792</t>
+    <t xml:space="preserve">2.23248529434204</t>
   </si>
   <si>
     <t xml:space="preserve">2.28806638717651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0842707157135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1305878162384</t>
+    <t xml:space="preserve">2.08427095413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13058805465698</t>
   </si>
   <si>
     <t xml:space="preserve">2.22322225570679</t>
@@ -584,28 +584,28 @@
     <t xml:space="preserve">2.24174928665161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11206078529358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17690515518188</t>
+    <t xml:space="preserve">2.11206126213074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17690491676331</t>
   </si>
   <si>
     <t xml:space="preserve">2.03795385360718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99163675308228</t>
+    <t xml:space="preserve">1.99163687229156</t>
   </si>
   <si>
     <t xml:space="preserve">1.88047552108765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94531917572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92679262161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16764116287231</t>
+    <t xml:space="preserve">1.9453192949295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92679238319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16764163970947</t>
   </si>
   <si>
     <t xml:space="preserve">2.13985133171082</t>
@@ -614,31 +614,31 @@
     <t xml:space="preserve">2.21395897865295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40849041938782</t>
+    <t xml:space="preserve">2.4084906578064</t>
   </si>
   <si>
     <t xml:space="preserve">2.48259830474854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42701768875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38996362686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46583557128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50406527519226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65698599815369</t>
+    <t xml:space="preserve">2.42701745033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38996386528015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46583580970764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50406575202942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65698575973511</t>
   </si>
   <si>
     <t xml:space="preserve">2.71433067321777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54229617118835</t>
+    <t xml:space="preserve">2.54229593276978</t>
   </si>
   <si>
     <t xml:space="preserve">2.58052587509155</t>
@@ -647,16 +647,16 @@
     <t xml:space="preserve">2.52318096160889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42760610580444</t>
+    <t xml:space="preserve">2.42760586738586</t>
   </si>
   <si>
     <t xml:space="preserve">2.38937568664551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48495078086853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61875557899475</t>
+    <t xml:space="preserve">2.48495101928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61875581741333</t>
   </si>
   <si>
     <t xml:space="preserve">2.56141114234924</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">2.73344564437866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69521594047546</t>
+    <t xml:space="preserve">2.69521570205688</t>
   </si>
   <si>
     <t xml:space="preserve">2.75256109237671</t>
@@ -683,31 +683,31 @@
     <t xml:space="preserve">2.84813594818115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05840134620667</t>
+    <t xml:space="preserve">3.05840110778809</t>
   </si>
   <si>
     <t xml:space="preserve">2.86725091934204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77167582511902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67610096931458</t>
+    <t xml:space="preserve">2.7716760635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.676100730896</t>
   </si>
   <si>
     <t xml:space="preserve">2.59964060783386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44672060012817</t>
+    <t xml:space="preserve">2.44672083854675</t>
   </si>
   <si>
     <t xml:space="preserve">2.37026071548462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09663105010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34512615203857</t>
+    <t xml:space="preserve">3.09663081169128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34512591362</t>
   </si>
   <si>
     <t xml:space="preserve">3.45981597900391</t>
@@ -725,13 +725,13 @@
     <t xml:space="preserve">4.10972690582275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9759213924408</t>
+    <t xml:space="preserve">3.97592091560364</t>
   </si>
   <si>
     <t xml:space="preserve">3.88034629821777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82300138473511</t>
+    <t xml:space="preserve">3.82300114631653</t>
   </si>
   <si>
     <t xml:space="preserve">3.44070100784302</t>
@@ -746,31 +746,31 @@
     <t xml:space="preserve">3.68919610977173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72742652893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7083113193512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57450604438782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55539107322693</t>
+    <t xml:space="preserve">3.72742629051208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70831155776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57450652122498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55539131164551</t>
   </si>
   <si>
     <t xml:space="preserve">3.51716113090515</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63185119628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5362765789032</t>
+    <t xml:space="preserve">3.6318507194519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53627634048462</t>
   </si>
   <si>
     <t xml:space="preserve">3.61273622512817</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65096569061279</t>
+    <t xml:space="preserve">3.65096592903137</t>
   </si>
   <si>
     <t xml:space="preserve">3.24955105781555</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">3.32601118087769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42158627510071</t>
+    <t xml:space="preserve">3.42158603668213</t>
   </si>
   <si>
     <t xml:space="preserve">3.3068962097168</t>
@@ -788,103 +788,103 @@
     <t xml:space="preserve">3.38335585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59362125396729</t>
+    <t xml:space="preserve">3.59362149238586</t>
   </si>
   <si>
     <t xml:space="preserve">3.47893118858337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49804615974426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28778123855591</t>
+    <t xml:space="preserve">3.49804592132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28778100013733</t>
   </si>
   <si>
     <t xml:space="preserve">3.67008113861084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80388641357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93769097328186</t>
+    <t xml:space="preserve">3.80388617515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93769121170044</t>
   </si>
   <si>
     <t xml:space="preserve">4.03326606750488</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18618726730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30087614059448</t>
+    <t xml:space="preserve">4.18618631362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30087661743164</t>
   </si>
   <si>
     <t xml:space="preserve">4.53025579452515</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51114130020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58760213851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49202585220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43468189239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62583160400391</t>
+    <t xml:space="preserve">4.51114082336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58760166168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49202632904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43468141555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62583112716675</t>
   </si>
   <si>
     <t xml:space="preserve">4.74052143096924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75963640213013</t>
+    <t xml:space="preserve">4.75963687896729</t>
   </si>
   <si>
     <t xml:space="preserve">4.70229148864746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68317651748657</t>
+    <t xml:space="preserve">4.68317699432373</t>
   </si>
   <si>
     <t xml:space="preserve">4.77875137329102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56848621368408</t>
+    <t xml:space="preserve">4.56848669052124</t>
   </si>
   <si>
     <t xml:space="preserve">4.66406106948853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72140693664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87432670593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96990156173706</t>
+    <t xml:space="preserve">4.72140645980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87432622909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96990203857422</t>
   </si>
   <si>
     <t xml:space="preserve">4.92211437225342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1132640838623</t>
+    <t xml:space="preserve">5.11326456069946</t>
   </si>
   <si>
     <t xml:space="preserve">5.16105175018311</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20883846282959</t>
+    <t xml:space="preserve">5.20883893966675</t>
   </si>
   <si>
     <t xml:space="preserve">5.25662708282471</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30441427230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44777631759644</t>
+    <t xml:space="preserve">5.30441474914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44777679443359</t>
   </si>
   <si>
     <t xml:space="preserve">5.63892698287964</t>
@@ -896,31 +896,31 @@
     <t xml:space="preserve">5.81332683563232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71643829345703</t>
+    <t xml:space="preserve">5.71643781661987</t>
   </si>
   <si>
     <t xml:space="preserve">5.42577171325684</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13510465621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84443855285645</t>
+    <t xml:space="preserve">5.1351056098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84443950653076</t>
   </si>
   <si>
     <t xml:space="preserve">4.82506132125854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80568313598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59252738952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55377244949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76692819595337</t>
+    <t xml:space="preserve">4.80568361282349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59252834320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55377197265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76692771911621</t>
   </si>
   <si>
     <t xml:space="preserve">5.03821611404419</t>
@@ -932,10 +932,10 @@
     <t xml:space="preserve">5.08666038513184</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18354988098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9413275718689</t>
+    <t xml:space="preserve">5.18354940414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94132804870605</t>
   </si>
   <si>
     <t xml:space="preserve">5.23199415206909</t>
@@ -947,55 +947,55 @@
     <t xml:space="preserve">5.28043842315674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89288330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6312837600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53439474105835</t>
+    <t xml:space="preserve">4.89288377761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63128423690796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53439426422119</t>
   </si>
   <si>
     <t xml:space="preserve">4.67003917694092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78630542755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72817230224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70879507064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91021585464478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61954879760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32888317108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37732744216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57110452651978</t>
+    <t xml:space="preserve">4.78630590438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72817277908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70879554748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91021490097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61954927444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32888269424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37732791900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57110548019409</t>
   </si>
   <si>
     <t xml:space="preserve">5.47421598434448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66799402236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73376989364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29777002334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44310426712036</t>
+    <t xml:space="preserve">5.66799306869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7337703704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29777097702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4431037902832</t>
   </si>
   <si>
     <t xml:space="preserve">6.68532609939575</t>
@@ -1016,13 +1016,13 @@
     <t xml:space="preserve">6.53999280929565</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39465951919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71998977661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99332332611084</t>
+    <t xml:space="preserve">6.3946590423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71999073028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.993323802948</t>
   </si>
   <si>
     <t xml:space="preserve">8.09021377563477</t>
@@ -1031,22 +1031,22 @@
     <t xml:space="preserve">8.04176902770996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94488048553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84799098968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89643478393555</t>
+    <t xml:space="preserve">7.94487905502319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84799242019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89643621444702</t>
   </si>
   <si>
     <t xml:space="preserve">8.38087844848633</t>
   </si>
   <si>
-    <t xml:space="preserve">10.270209312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88265514373779</t>
+    <t xml:space="preserve">10.2702112197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88265609741211</t>
   </si>
   <si>
     <t xml:space="preserve">10.1733207702637</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">10.0764322280884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2390975952148</t>
+    <t xml:space="preserve">11.2390985488892</t>
   </si>
   <si>
     <t xml:space="preserve">11.6266536712646</t>
@@ -1070,22 +1070,22 @@
     <t xml:space="preserve">13.2737617492676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.983097076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4364280700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3395404815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0177612304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1669788360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1930656433105</t>
+    <t xml:space="preserve">12.9830961227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4364290237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3395395278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0177602767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1669807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1930646896362</t>
   </si>
   <si>
     <t xml:space="preserve">15.0956735610962</t>
@@ -1106,10 +1106,10 @@
     <t xml:space="preserve">13.4400196075439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9269771575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0243663787842</t>
+    <t xml:space="preserve">13.9269781112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0243673324585</t>
   </si>
   <si>
     <t xml:space="preserve">14.2191514968872</t>
@@ -1118,25 +1118,25 @@
     <t xml:space="preserve">14.8034992218018</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4139347076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6087169647217</t>
+    <t xml:space="preserve">14.4139337539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6087160110474</t>
   </si>
   <si>
     <t xml:space="preserve">14.7061080932617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5113248825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3426275253296</t>
+    <t xml:space="preserve">14.5113258361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3426265716553</t>
   </si>
   <si>
     <t xml:space="preserve">14.1217594146729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3165407180786</t>
+    <t xml:space="preserve">14.3165416717529</t>
   </si>
   <si>
     <t xml:space="preserve">13.8295850753784</t>
@@ -1148,13 +1148,13 @@
     <t xml:space="preserve">13.2452363967896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8556709289551</t>
+    <t xml:space="preserve">12.8556699752808</t>
   </si>
   <si>
     <t xml:space="preserve">12.3687133789062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.758279800415</t>
+    <t xml:space="preserve">12.7582788467407</t>
   </si>
   <si>
     <t xml:space="preserve">12.5634956359863</t>
@@ -1169,73 +1169,73 @@
     <t xml:space="preserve">11.1026239395142</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93392658233643</t>
+    <t xml:space="preserve">9.93392753601074</t>
   </si>
   <si>
     <t xml:space="preserve">10.7130584716797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2000160217285</t>
+    <t xml:space="preserve">11.2000169754028</t>
   </si>
   <si>
     <t xml:space="preserve">11.9791479110718</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8817558288574</t>
+    <t xml:space="preserve">11.8817548751831</t>
   </si>
   <si>
     <t xml:space="preserve">10.9078416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2974071502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3947992324829</t>
+    <t xml:space="preserve">11.2974081039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3947982788086</t>
   </si>
   <si>
     <t xml:space="preserve">11.589581489563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0052318572998</t>
+    <t xml:space="preserve">11.0052328109741</t>
   </si>
   <si>
     <t xml:space="preserve">11.7843656539917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4921913146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.810450553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4208850860596</t>
+    <t xml:space="preserve">11.4921903610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8104515075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4208841323853</t>
   </si>
   <si>
     <t xml:space="preserve">10.2261009216309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3234930038452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1287107467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0313196182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73914432525635</t>
+    <t xml:space="preserve">10.3234939575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1287097930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0313186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73914527893066</t>
   </si>
   <si>
     <t xml:space="preserve">9.54436111450195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83653736114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34957885742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49566555023193</t>
+    <t xml:space="preserve">9.8365364074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34957981109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49566459655762</t>
   </si>
   <si>
     <t xml:space="preserve">12.2713222503662</t>
@@ -1244,19 +1244,19 @@
     <t xml:space="preserve">12.9530620574951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6800222396851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7321939468384</t>
+    <t xml:space="preserve">15.6800231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7321929931641</t>
   </si>
   <si>
     <t xml:space="preserve">14.1704549789429</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3652381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0730628967285</t>
+    <t xml:space="preserve">14.3652372360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0730638504028</t>
   </si>
   <si>
     <t xml:space="preserve">15.1443691253662</t>
@@ -1268,13 +1268,13 @@
     <t xml:space="preserve">15.585467338562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6344776153564</t>
+    <t xml:space="preserve">15.6344785690308</t>
   </si>
   <si>
     <t xml:space="preserve">15.193380355835</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4874458312988</t>
+    <t xml:space="preserve">15.4874467849731</t>
   </si>
   <si>
     <t xml:space="preserve">15.4384346008301</t>
@@ -1283,13 +1283,13 @@
     <t xml:space="preserve">15.2423915863037</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3894233703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9973373413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8993148803711</t>
+    <t xml:space="preserve">15.3894243240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9973363876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8993139266968</t>
   </si>
   <si>
     <t xml:space="preserve">15.0463485717773</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">13.7230529785156</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8210754394531</t>
+    <t xml:space="preserve">13.8210744857788</t>
   </si>
   <si>
     <t xml:space="preserve">14.3601942062378</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">13.6250314712524</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8700857162476</t>
+    <t xml:space="preserve">13.8700866699219</t>
   </si>
   <si>
     <t xml:space="preserve">13.6740427017212</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">14.9483261108398</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4092054367065</t>
+    <t xml:space="preserve">14.4092063903809</t>
   </si>
   <si>
     <t xml:space="preserve">14.8503036499023</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7522830963135</t>
+    <t xml:space="preserve">14.7522821426392</t>
   </si>
   <si>
     <t xml:space="preserve">14.6052494049072</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">14.5562391281128</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5072288513184</t>
+    <t xml:space="preserve">14.507227897644</t>
   </si>
   <si>
     <t xml:space="preserve">14.0661296844482</t>
@@ -1370,16 +1370,16 @@
     <t xml:space="preserve">13.2819547653198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8898668289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7428340911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9878902435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1349229812622</t>
+    <t xml:space="preserve">12.8898677825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7428350448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.987889289856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1349220275879</t>
   </si>
   <si>
     <t xml:space="preserve">12.3507480621338</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">13.0859127044678</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4289875030518</t>
+    <t xml:space="preserve">13.4289884567261</t>
   </si>
   <si>
     <t xml:space="preserve">15.8305215835571</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">16.2226085662842</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0265655517578</t>
+    <t xml:space="preserve">16.0265674591064</t>
   </si>
   <si>
     <t xml:space="preserve">16.0755767822266</t>
@@ -1439,31 +1439,31 @@
     <t xml:space="preserve">16.2716197967529</t>
   </si>
   <si>
-    <t xml:space="preserve">16.320629119873</t>
+    <t xml:space="preserve">16.3206310272217</t>
   </si>
   <si>
     <t xml:space="preserve">18.7221660614014</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0162296295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7023830413818</t>
+    <t xml:space="preserve">19.0162315368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7023849487305</t>
   </si>
   <si>
     <t xml:space="preserve">19.6043605804443</t>
   </si>
   <si>
-    <t xml:space="preserve">19.800407409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0944709777832</t>
+    <t xml:space="preserve">19.8004055023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0944690704346</t>
   </si>
   <si>
     <t xml:space="preserve">23.9173202514648</t>
   </si>
   <si>
-    <t xml:space="preserve">22.545015335083</t>
+    <t xml:space="preserve">22.5450172424316</t>
   </si>
   <si>
     <t xml:space="preserve">23.5252342224121</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">24.7995166778564</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2311706542969</t>
+    <t xml:space="preserve">23.2311687469482</t>
   </si>
   <si>
     <t xml:space="preserve">20.7806243896484</t>
@@ -1481,22 +1481,22 @@
     <t xml:space="preserve">21.1727104187012</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4865589141846</t>
+    <t xml:space="preserve">20.4865570068359</t>
   </si>
   <si>
     <t xml:space="preserve">20.6826019287109</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3687534332275</t>
+    <t xml:space="preserve">21.3687553405762</t>
   </si>
   <si>
     <t xml:space="preserve">22.6430377960205</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9955596923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2896251678467</t>
+    <t xml:space="preserve">24.9955615997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2896270751953</t>
   </si>
   <si>
     <t xml:space="preserve">24.6034755706787</t>
@@ -1505,16 +1505,16 @@
     <t xml:space="preserve">24.8975391387939</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5054531097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.015344619751</t>
+    <t xml:space="preserve">24.5054512023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0153427124023</t>
   </si>
   <si>
     <t xml:space="preserve">23.6232566833496</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8390808105469</t>
+    <t xml:space="preserve">22.8390789031982</t>
   </si>
   <si>
     <t xml:space="preserve">23.3291893005371</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">22.937105178833</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7212791442871</t>
+    <t xml:space="preserve">23.7212772369385</t>
   </si>
   <si>
     <t xml:space="preserve">24.1133651733398</t>
@@ -1541,10 +1541,10 @@
     <t xml:space="preserve">24.4074287414551</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8192977905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2509498596191</t>
+    <t xml:space="preserve">23.819299697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2509517669678</t>
   </si>
   <si>
     <t xml:space="preserve">21.7608413696289</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">22.1529273986816</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7711753845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.330078125</t>
+    <t xml:space="preserve">18.7711772918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3300800323486</t>
   </si>
   <si>
     <t xml:space="preserve">17.6439266204834</t>
@@ -1571,13 +1571,13 @@
     <t xml:space="preserve">19.9964485168457</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5845794677734</t>
+    <t xml:space="preserve">20.5845775604248</t>
   </si>
   <si>
     <t xml:space="preserve">20.1924934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8984279632568</t>
+    <t xml:space="preserve">19.8984260559082</t>
   </si>
   <si>
     <t xml:space="preserve">20.3885364532471</t>
@@ -1632,9 +1632,6 @@
   </si>
   <si>
     <t xml:space="preserve">19.9959678649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0944690704346</t>
   </si>
   <si>
     <t xml:space="preserve">19.4542045593262</t>
@@ -41440,7 +41437,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1499" t="s">
-        <v>540</v>
+        <v>481</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41492,7 +41489,7 @@
         <v>19.75</v>
       </c>
       <c r="G1501" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41596,7 +41593,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1505" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41622,7 +41619,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1506" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41674,7 +41671,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1508" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41700,7 +41697,7 @@
         <v>19.5</v>
       </c>
       <c r="G1509" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41726,7 +41723,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1510" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41752,7 +41749,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1511" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41778,7 +41775,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1512" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41804,7 +41801,7 @@
         <v>19.5</v>
       </c>
       <c r="G1513" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41830,7 +41827,7 @@
         <v>19.5</v>
       </c>
       <c r="G1514" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41856,7 +41853,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1515" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41882,7 +41879,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1516" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41908,7 +41905,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1517" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -41934,7 +41931,7 @@
         <v>18.75</v>
       </c>
       <c r="G1518" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -41960,7 +41957,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1519" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41986,7 +41983,7 @@
         <v>17.5</v>
       </c>
       <c r="G1520" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42012,7 +42009,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1521" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42038,7 +42035,7 @@
         <v>18.25</v>
       </c>
       <c r="G1522" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42064,7 +42061,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1523" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42090,7 +42087,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1524" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42116,7 +42113,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1525" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42142,7 +42139,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1526" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42168,7 +42165,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1527" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42194,7 +42191,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1528" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42220,7 +42217,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1529" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42350,7 +42347,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1534" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42376,7 +42373,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1535" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42428,7 +42425,7 @@
         <v>20</v>
       </c>
       <c r="G1537" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42506,7 +42503,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1540" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42532,7 +42529,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1541" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42558,7 +42555,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1542" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42610,7 +42607,7 @@
         <v>19.5</v>
       </c>
       <c r="G1544" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42636,7 +42633,7 @@
         <v>19.5</v>
       </c>
       <c r="G1545" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42714,7 +42711,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1548" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42740,7 +42737,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G1549" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42870,7 +42867,7 @@
         <v>19.5</v>
       </c>
       <c r="G1554" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42896,7 +42893,7 @@
         <v>19.5</v>
       </c>
       <c r="G1555" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42922,7 +42919,7 @@
         <v>19.5</v>
       </c>
       <c r="G1556" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42974,7 +42971,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1558" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43000,7 +42997,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1559" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43026,7 +43023,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1560" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43052,7 +43049,7 @@
         <v>19</v>
       </c>
       <c r="G1561" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43078,7 +43075,7 @@
         <v>19</v>
       </c>
       <c r="G1562" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43104,7 +43101,7 @@
         <v>19</v>
       </c>
       <c r="G1563" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43130,7 +43127,7 @@
         <v>19</v>
       </c>
       <c r="G1564" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43156,7 +43153,7 @@
         <v>19</v>
       </c>
       <c r="G1565" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43182,7 +43179,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1566" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43208,7 +43205,7 @@
         <v>19</v>
       </c>
       <c r="G1567" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43234,7 +43231,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1568" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43260,7 +43257,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1569" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43286,7 +43283,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1570" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43312,7 +43309,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1571" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -43338,7 +43335,7 @@
         <v>19</v>
       </c>
       <c r="G1572" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43364,7 +43361,7 @@
         <v>19</v>
       </c>
       <c r="G1573" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43390,7 +43387,7 @@
         <v>19</v>
       </c>
       <c r="G1574" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43416,7 +43413,7 @@
         <v>18.75</v>
       </c>
       <c r="G1575" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43442,7 +43439,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1576" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43468,7 +43465,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1577" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43494,7 +43491,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1578" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43520,7 +43517,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1579" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43546,7 +43543,7 @@
         <v>19</v>
       </c>
       <c r="G1580" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43572,7 +43569,7 @@
         <v>19</v>
       </c>
       <c r="G1581" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43598,7 +43595,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1582" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43624,7 +43621,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1583" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43650,7 +43647,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1584" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43676,7 +43673,7 @@
         <v>18.75</v>
       </c>
       <c r="G1585" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43702,7 +43699,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1586" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43728,7 +43725,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1587" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43754,7 +43751,7 @@
         <v>18.5</v>
       </c>
       <c r="G1588" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43780,7 +43777,7 @@
         <v>18.5</v>
       </c>
       <c r="G1589" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43806,7 +43803,7 @@
         <v>18.5</v>
       </c>
       <c r="G1590" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43832,7 +43829,7 @@
         <v>18.5</v>
       </c>
       <c r="G1591" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43858,7 +43855,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1592" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43884,7 +43881,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1593" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43910,7 +43907,7 @@
         <v>18</v>
       </c>
       <c r="G1594" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43936,7 +43933,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1595" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -43962,7 +43959,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1596" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43988,7 +43985,7 @@
         <v>18.5</v>
       </c>
       <c r="G1597" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44014,7 +44011,7 @@
         <v>18.5</v>
       </c>
       <c r="G1598" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44040,7 +44037,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1599" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44066,7 +44063,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1600" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44092,7 +44089,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1601" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44118,7 +44115,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1602" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44144,7 +44141,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1603" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44170,7 +44167,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1604" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44196,7 +44193,7 @@
         <v>18.25</v>
       </c>
       <c r="G1605" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44222,7 +44219,7 @@
         <v>18</v>
       </c>
       <c r="G1606" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -44248,7 +44245,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1607" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -44274,7 +44271,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1608" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -44300,7 +44297,7 @@
         <v>18</v>
       </c>
       <c r="G1609" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44326,7 +44323,7 @@
         <v>18.25</v>
       </c>
       <c r="G1610" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -44352,7 +44349,7 @@
         <v>18.25</v>
       </c>
       <c r="G1611" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44378,7 +44375,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1612" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44404,7 +44401,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1613" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44430,7 +44427,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1614" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44456,7 +44453,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1615" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44482,7 +44479,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1616" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44508,7 +44505,7 @@
         <v>18</v>
       </c>
       <c r="G1617" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44534,7 +44531,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1618" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44560,7 +44557,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1619" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44586,7 +44583,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1620" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44612,7 +44609,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1621" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44638,7 +44635,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1622" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44664,7 +44661,7 @@
         <v>18</v>
       </c>
       <c r="G1623" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44690,7 +44687,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1624" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44716,7 +44713,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1625" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44742,7 +44739,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1626" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44768,7 +44765,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1627" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44794,7 +44791,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1628" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44820,7 +44817,7 @@
         <v>18.25</v>
       </c>
       <c r="G1629" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44846,7 +44843,7 @@
         <v>18.25</v>
       </c>
       <c r="G1630" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44872,7 +44869,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1631" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44898,7 +44895,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1632" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44924,7 +44921,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1633" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44950,7 +44947,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1634" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44976,7 +44973,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1635" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45002,7 +44999,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1636" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45028,7 +45025,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1637" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45054,7 +45051,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1638" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45080,7 +45077,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1639" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45106,7 +45103,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1640" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45132,7 +45129,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1641" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -45158,7 +45155,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1642" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45184,7 +45181,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1643" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45210,7 +45207,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1644" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -45236,7 +45233,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1645" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -45262,7 +45259,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1646" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -45288,7 +45285,7 @@
         <v>18</v>
       </c>
       <c r="G1647" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -45314,7 +45311,7 @@
         <v>18.25</v>
       </c>
       <c r="G1648" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -45340,7 +45337,7 @@
         <v>18.25</v>
       </c>
       <c r="G1649" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -45366,7 +45363,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1650" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45392,7 +45389,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1651" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -45418,7 +45415,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1652" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45444,7 +45441,7 @@
         <v>18</v>
       </c>
       <c r="G1653" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45470,7 +45467,7 @@
         <v>18</v>
       </c>
       <c r="G1654" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45496,7 +45493,7 @@
         <v>18</v>
       </c>
       <c r="G1655" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45522,7 +45519,7 @@
         <v>18</v>
       </c>
       <c r="G1656" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45548,7 +45545,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1657" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45574,7 +45571,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1658" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45600,7 +45597,7 @@
         <v>17.75</v>
       </c>
       <c r="G1659" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45626,7 +45623,7 @@
         <v>18</v>
       </c>
       <c r="G1660" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45652,7 +45649,7 @@
         <v>18</v>
       </c>
       <c r="G1661" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45678,7 +45675,7 @@
         <v>18</v>
       </c>
       <c r="G1662" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45704,7 +45701,7 @@
         <v>18</v>
       </c>
       <c r="G1663" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45730,7 +45727,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1664" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45756,7 +45753,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1665" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45782,7 +45779,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1666" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45808,7 +45805,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1667" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45834,7 +45831,7 @@
         <v>17.5</v>
       </c>
       <c r="G1668" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45860,7 +45857,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1669" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45886,7 +45883,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1670" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45912,7 +45909,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1671" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45938,7 +45935,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1672" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45964,7 +45961,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1673" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45990,7 +45987,7 @@
         <v>16.75</v>
       </c>
       <c r="G1674" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -46016,7 +46013,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1675" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -46042,7 +46039,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1676" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -46068,7 +46065,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1677" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -46094,7 +46091,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1678" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -46120,7 +46117,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1679" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -46146,7 +46143,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1680" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -46172,7 +46169,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1681" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -46198,7 +46195,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1682" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -46224,7 +46221,7 @@
         <v>17</v>
       </c>
       <c r="G1683" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -46250,7 +46247,7 @@
         <v>17</v>
       </c>
       <c r="G1684" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -46276,7 +46273,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1685" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -46302,7 +46299,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1686" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -46328,7 +46325,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1687" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -46354,7 +46351,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46380,7 +46377,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1689" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -46406,7 +46403,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1690" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -46432,7 +46429,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1691" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46458,7 +46455,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1692" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46484,7 +46481,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1693" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -46510,7 +46507,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46536,7 +46533,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1695" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46562,7 +46559,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1696" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46588,7 +46585,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1697" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46614,7 +46611,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1698" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46640,7 +46637,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1699" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46666,7 +46663,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1700" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46692,7 +46689,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1701" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46718,7 +46715,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1702" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46744,7 +46741,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1703" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46770,7 +46767,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1704" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46796,7 +46793,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1705" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46822,7 +46819,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1706" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46848,7 +46845,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1707" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46874,7 +46871,7 @@
         <v>15</v>
       </c>
       <c r="G1708" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46900,7 +46897,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1709" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46926,7 +46923,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1710" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46952,7 +46949,7 @@
         <v>14.5</v>
       </c>
       <c r="G1711" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46978,7 +46975,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1712" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -47004,7 +47001,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1713" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47030,7 +47027,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1714" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -47056,7 +47053,7 @@
         <v>15</v>
       </c>
       <c r="G1715" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -47082,7 +47079,7 @@
         <v>15</v>
       </c>
       <c r="G1716" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47108,7 +47105,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1717" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -47134,7 +47131,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1718" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -47160,7 +47157,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -47186,7 +47183,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1720" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -47212,7 +47209,7 @@
         <v>14.25</v>
       </c>
       <c r="G1721" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -47238,7 +47235,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1722" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -47264,7 +47261,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1723" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -47290,7 +47287,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1724" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -47316,7 +47313,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1725" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -47342,7 +47339,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1726" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47368,7 +47365,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1727" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47394,7 +47391,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1728" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -47420,7 +47417,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1729" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47446,7 +47443,7 @@
         <v>14.75</v>
       </c>
       <c r="G1730" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47472,7 +47469,7 @@
         <v>14.75</v>
       </c>
       <c r="G1731" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47498,7 +47495,7 @@
         <v>14.75</v>
       </c>
       <c r="G1732" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47524,7 +47521,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1733" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47550,7 +47547,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1734" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47576,7 +47573,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1735" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47602,7 +47599,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1736" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47628,7 +47625,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1737" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47654,7 +47651,7 @@
         <v>13.25</v>
       </c>
       <c r="G1738" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47680,7 +47677,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1739" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47706,7 +47703,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1740" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47732,7 +47729,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1741" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47758,7 +47755,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1742" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47784,7 +47781,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1743" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47810,7 +47807,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1744" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47836,7 +47833,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1745" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47862,7 +47859,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1746" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47888,7 +47885,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1747" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47914,7 +47911,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1748" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47940,7 +47937,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1749" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47966,7 +47963,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1750" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47992,7 +47989,7 @@
         <v>12.75</v>
       </c>
       <c r="G1751" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -48018,7 +48015,7 @@
         <v>12.5</v>
       </c>
       <c r="G1752" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -48044,7 +48041,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1753" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -48070,7 +48067,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1754" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -48096,7 +48093,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1755" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -48122,7 +48119,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1756" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -48148,7 +48145,7 @@
         <v>12.25</v>
       </c>
       <c r="G1757" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -48174,7 +48171,7 @@
         <v>12.25</v>
       </c>
       <c r="G1758" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -48200,7 +48197,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1759" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -48226,7 +48223,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1760" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -48252,7 +48249,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1761" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -48278,7 +48275,7 @@
         <v>12.75</v>
       </c>
       <c r="G1762" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -48304,7 +48301,7 @@
         <v>12.75</v>
       </c>
       <c r="G1763" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -48330,7 +48327,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1764" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -48356,7 +48353,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1765" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48382,7 +48379,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1766" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48408,7 +48405,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1767" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48434,7 +48431,7 @@
         <v>12.5</v>
       </c>
       <c r="G1768" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48460,7 +48457,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1769" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48486,7 +48483,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1770" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48512,7 +48509,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1771" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48538,7 +48535,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1772" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48564,7 +48561,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1773" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48590,7 +48587,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1774" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48616,7 +48613,7 @@
         <v>12.75</v>
       </c>
       <c r="G1775" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48642,7 +48639,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1776" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48668,7 +48665,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1777" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48694,7 +48691,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1778" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48720,7 +48717,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1779" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48746,7 +48743,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1780" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48772,7 +48769,7 @@
         <v>13</v>
       </c>
       <c r="G1781" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48798,7 +48795,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1782" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48824,7 +48821,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1783" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48850,7 +48847,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1784" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48876,7 +48873,7 @@
         <v>12.75</v>
       </c>
       <c r="G1785" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48902,7 +48899,7 @@
         <v>12.75</v>
       </c>
       <c r="G1786" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48928,7 +48925,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48954,7 +48951,7 @@
         <v>12.5</v>
       </c>
       <c r="G1788" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48980,7 +48977,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1789" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -49006,7 +49003,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1790" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -49032,7 +49029,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1791" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -49058,7 +49055,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1792" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -49084,7 +49081,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1793" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -49110,7 +49107,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1794" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -49136,7 +49133,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1795" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -49162,7 +49159,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1796" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -49188,7 +49185,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1797" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -49214,7 +49211,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1798" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -49240,7 +49237,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1799" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -49266,7 +49263,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1800" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -49292,7 +49289,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1801" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -49318,7 +49315,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1802" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -49344,7 +49341,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1803" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49370,7 +49367,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1804" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49396,7 +49393,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1805" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49422,7 +49419,7 @@
         <v>12.75</v>
       </c>
       <c r="G1806" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49448,7 +49445,7 @@
         <v>12.75</v>
       </c>
       <c r="G1807" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49474,7 +49471,7 @@
         <v>12.75</v>
       </c>
       <c r="G1808" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49500,7 +49497,7 @@
         <v>12.75</v>
       </c>
       <c r="G1809" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49526,7 +49523,7 @@
         <v>12.75</v>
       </c>
       <c r="G1810" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49552,7 +49549,7 @@
         <v>12.75</v>
       </c>
       <c r="G1811" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49578,7 +49575,7 @@
         <v>12.75</v>
       </c>
       <c r="G1812" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49604,7 +49601,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1813" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49630,7 +49627,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1814" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49656,7 +49653,7 @@
         <v>12.75</v>
       </c>
       <c r="G1815" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49682,7 +49679,7 @@
         <v>12.75</v>
       </c>
       <c r="G1816" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49708,7 +49705,7 @@
         <v>12.75</v>
       </c>
       <c r="G1817" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49734,7 +49731,7 @@
         <v>12.75</v>
       </c>
       <c r="G1818" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49760,7 +49757,7 @@
         <v>12.75</v>
       </c>
       <c r="G1819" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49786,7 +49783,7 @@
         <v>12.75</v>
       </c>
       <c r="G1820" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49812,7 +49809,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1821" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49838,7 +49835,7 @@
         <v>12.5</v>
       </c>
       <c r="G1822" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49864,7 +49861,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1823" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49890,7 +49887,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1824" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49916,7 +49913,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1825" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49942,7 +49939,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1826" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49968,7 +49965,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1827" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49994,7 +49991,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1828" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -50020,7 +50017,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1829" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -50046,7 +50043,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1830" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -50072,7 +50069,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1831" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -50098,7 +50095,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1832" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -50124,7 +50121,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1833" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -50150,7 +50147,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1834" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -50176,7 +50173,7 @@
         <v>12.5</v>
       </c>
       <c r="G1835" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -50202,7 +50199,7 @@
         <v>12.5</v>
       </c>
       <c r="G1836" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -50228,7 +50225,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1837" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -50254,7 +50251,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1838" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -50280,7 +50277,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1839" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -50306,7 +50303,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -50332,7 +50329,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1841" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50358,7 +50355,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1842" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50384,7 +50381,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1843" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50410,7 +50407,7 @@
         <v>12.75</v>
       </c>
       <c r="G1844" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50436,7 +50433,7 @@
         <v>12.75</v>
       </c>
       <c r="G1845" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50462,7 +50459,7 @@
         <v>12.75</v>
       </c>
       <c r="G1846" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50488,7 +50485,7 @@
         <v>12.75</v>
       </c>
       <c r="G1847" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50514,7 +50511,7 @@
         <v>12.75</v>
       </c>
       <c r="G1848" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50540,7 +50537,7 @@
         <v>12.75</v>
       </c>
       <c r="G1849" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50566,7 +50563,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1850" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50592,7 +50589,7 @@
         <v>13.25</v>
       </c>
       <c r="G1851" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50618,7 +50615,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1852" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50644,7 +50641,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1853" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50670,7 +50667,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1854" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50696,7 +50693,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1855" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50722,7 +50719,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1856" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50748,7 +50745,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1857" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50774,7 +50771,7 @@
         <v>13</v>
       </c>
       <c r="G1858" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50800,7 +50797,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1859" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50826,7 +50823,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1860" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50852,7 +50849,7 @@
         <v>13.25</v>
       </c>
       <c r="G1861" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50878,7 +50875,7 @@
         <v>13.25</v>
       </c>
       <c r="G1862" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50904,7 +50901,7 @@
         <v>13.25</v>
       </c>
       <c r="G1863" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50930,7 +50927,7 @@
         <v>13.25</v>
       </c>
       <c r="G1864" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50956,7 +50953,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1865" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50982,7 +50979,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1866" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -51008,7 +51005,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1867" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -51034,7 +51031,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1868" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -51060,7 +51057,7 @@
         <v>12.5</v>
       </c>
       <c r="G1869" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -51086,7 +51083,7 @@
         <v>12.5</v>
       </c>
       <c r="G1870" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -51112,7 +51109,7 @@
         <v>12.5</v>
       </c>
       <c r="G1871" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -51138,7 +51135,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1872" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -51164,7 +51161,7 @@
         <v>12.5</v>
       </c>
       <c r="G1873" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -51190,7 +51187,7 @@
         <v>12.5</v>
       </c>
       <c r="G1874" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -51216,7 +51213,7 @@
         <v>12.5</v>
       </c>
       <c r="G1875" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -51242,7 +51239,7 @@
         <v>12.5</v>
       </c>
       <c r="G1876" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -51268,7 +51265,7 @@
         <v>12.25</v>
       </c>
       <c r="G1877" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -51294,7 +51291,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1878" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -51320,7 +51317,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1879" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -51346,7 +51343,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1880" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51372,7 +51369,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1881" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51398,7 +51395,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1882" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51424,7 +51421,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1883" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51450,7 +51447,7 @@
         <v>12.5</v>
       </c>
       <c r="G1884" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51476,7 +51473,7 @@
         <v>12.5</v>
       </c>
       <c r="G1885" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51502,7 +51499,7 @@
         <v>12.5</v>
       </c>
       <c r="G1886" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51528,7 +51525,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1887" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51554,7 +51551,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1888" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51580,7 +51577,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1889" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51606,7 +51603,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1890" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51632,7 +51629,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1891" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51658,7 +51655,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1892" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51684,7 +51681,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1893" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51710,7 +51707,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1894" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51736,7 +51733,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1895" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51762,7 +51759,7 @@
         <v>14.75</v>
       </c>
       <c r="G1896" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51788,7 +51785,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1897" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51814,7 +51811,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1898" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51840,7 +51837,7 @@
         <v>14.25</v>
       </c>
       <c r="G1899" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51866,7 +51863,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1900" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51892,7 +51889,7 @@
         <v>14</v>
       </c>
       <c r="G1901" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51918,7 +51915,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1902" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51944,7 +51941,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1903" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51970,7 +51967,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1904" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51996,7 +51993,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1905" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52022,7 +52019,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1906" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52048,7 +52045,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52074,7 +52071,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1908" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52100,7 +52097,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1909" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52126,7 +52123,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1910" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -52152,7 +52149,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1911" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -52178,7 +52175,7 @@
         <v>13.25</v>
       </c>
       <c r="G1912" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -52204,7 +52201,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1913" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -52230,7 +52227,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1914" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -52256,7 +52253,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1915" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -52282,7 +52279,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1916" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -52308,7 +52305,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1917" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -52334,7 +52331,7 @@
         <v>12.75</v>
       </c>
       <c r="G1918" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52360,7 +52357,7 @@
         <v>13</v>
       </c>
       <c r="G1919" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52386,7 +52383,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1920" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52412,7 +52409,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1921" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52438,7 +52435,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1922" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52464,7 +52461,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1923" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52490,7 +52487,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1924" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52516,7 +52513,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1925" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52542,7 +52539,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1926" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52568,7 +52565,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1927" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52594,7 +52591,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1928" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52620,7 +52617,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1929" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52646,7 +52643,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1930" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52672,7 +52669,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1931" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52698,7 +52695,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1932" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52724,7 +52721,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1933" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52750,7 +52747,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1934" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52776,7 +52773,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1935" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52802,7 +52799,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1936" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52828,7 +52825,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1937" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52854,7 +52851,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1938" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52880,7 +52877,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1939" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52906,7 +52903,7 @@
         <v>12.5</v>
       </c>
       <c r="G1940" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52932,7 +52929,7 @@
         <v>12.75</v>
       </c>
       <c r="G1941" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52958,7 +52955,7 @@
         <v>12.75</v>
       </c>
       <c r="G1942" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52984,7 +52981,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1943" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53010,7 +53007,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1944" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53036,7 +53033,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1945" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53062,7 +53059,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1946" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53088,7 +53085,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1947" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53114,7 +53111,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1948" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -53140,7 +53137,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1949" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -53166,7 +53163,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1950" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -53192,7 +53189,7 @@
         <v>12.25</v>
       </c>
       <c r="G1951" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -53218,7 +53215,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1952" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -53244,7 +53241,7 @@
         <v>12.5</v>
       </c>
       <c r="G1953" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -53270,7 +53267,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1954" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -53296,7 +53293,7 @@
         <v>12.25</v>
       </c>
       <c r="G1955" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -53322,7 +53319,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1956" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -53348,7 +53345,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1957" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53374,7 +53371,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1958" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53400,7 +53397,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1959" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53426,7 +53423,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1960" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53452,7 +53449,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1961" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53478,7 +53475,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1962" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53504,7 +53501,7 @@
         <v>10.5</v>
       </c>
       <c r="G1963" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53530,7 +53527,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1964" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53556,7 +53553,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1965" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53582,7 +53579,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1966" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53608,7 +53605,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1967" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53634,7 +53631,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1968" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53660,7 +53657,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1969" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53686,7 +53683,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1970" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53712,7 +53709,7 @@
         <v>12</v>
       </c>
       <c r="G1971" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53738,7 +53735,7 @@
         <v>12</v>
       </c>
       <c r="G1972" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53764,7 +53761,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1973" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53790,7 +53787,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1974" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53816,7 +53813,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1975" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53842,7 +53839,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1976" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53868,7 +53865,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1977" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53894,7 +53891,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1978" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53920,7 +53917,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1979" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53946,7 +53943,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1980" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53972,7 +53969,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1981" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53998,7 +53995,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1982" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54024,7 +54021,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54050,7 +54047,7 @@
         <v>13</v>
       </c>
       <c r="G1984" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54076,7 +54073,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1985" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54102,7 +54099,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1986" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -54128,7 +54125,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1987" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -54154,7 +54151,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1988" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -54180,7 +54177,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1989" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -54206,7 +54203,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1990" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -54232,7 +54229,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1991" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -54258,7 +54255,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1992" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -54284,7 +54281,7 @@
         <v>13.5</v>
       </c>
       <c r="G1993" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -54310,7 +54307,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1994" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -54336,7 +54333,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1995" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54362,7 +54359,7 @@
         <v>14.5</v>
       </c>
       <c r="G1996" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54388,7 +54385,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1997" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54414,7 +54411,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1998" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54440,7 +54437,7 @@
         <v>15</v>
       </c>
       <c r="G1999" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54466,7 +54463,7 @@
         <v>15.5</v>
       </c>
       <c r="G2000" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54492,7 +54489,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2001" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54518,7 +54515,7 @@
         <v>15.5</v>
       </c>
       <c r="G2002" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54544,7 +54541,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2003" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54570,7 +54567,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2004" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54596,7 +54593,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2005" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54622,7 +54619,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2006" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54648,7 +54645,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2007" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54674,7 +54671,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2008" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54700,7 +54697,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2009" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54726,7 +54723,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2010" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54752,7 +54749,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2011" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54778,7 +54775,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2012" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54804,7 +54801,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2013" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54830,7 +54827,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2014" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54856,7 +54853,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2015" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54882,7 +54879,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2016" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54908,7 +54905,7 @@
         <v>16</v>
       </c>
       <c r="G2017" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54934,7 +54931,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2018" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54960,7 +54957,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2019" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54986,7 +54983,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2020" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55012,7 +55009,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2021" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55038,7 +55035,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2022" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55064,7 +55061,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2023" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55090,7 +55087,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2024" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -55116,7 +55113,7 @@
         <v>17.5</v>
       </c>
       <c r="G2025" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -55142,7 +55139,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2026" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -55168,7 +55165,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2027" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -55194,7 +55191,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2028" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -55220,7 +55217,7 @@
         <v>17.5</v>
       </c>
       <c r="G2029" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -55246,7 +55243,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2030" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -55272,7 +55269,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2031" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -55298,7 +55295,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2032" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -55324,7 +55321,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2033" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -55350,7 +55347,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2034" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -55376,7 +55373,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2035" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -55402,7 +55399,7 @@
         <v>17.5</v>
       </c>
       <c r="G2036" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -55428,7 +55425,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2037" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55454,7 +55451,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2038" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55480,7 +55477,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2039" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55506,7 +55503,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2040" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55532,7 +55529,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2041" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55558,7 +55555,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2042" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55584,7 +55581,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2043" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55610,7 +55607,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2044" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55636,7 +55633,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2045" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55662,7 +55659,7 @@
         <v>13</v>
       </c>
       <c r="G2046" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55688,7 +55685,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2047" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55714,7 +55711,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2048" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55740,7 +55737,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2049" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55766,7 +55763,7 @@
         <v>12</v>
       </c>
       <c r="G2050" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55792,7 +55789,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2051" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55818,7 +55815,7 @@
         <v>12</v>
       </c>
       <c r="G2052" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55844,7 +55841,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2053" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55870,7 +55867,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2054" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55896,7 +55893,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2055" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55922,7 +55919,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2056" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55948,7 +55945,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2057" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55974,7 +55971,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2058" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -56000,7 +55997,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2059" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -56026,7 +56023,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2060" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -56052,7 +56049,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2061" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -56078,7 +56075,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2062" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -56104,7 +56101,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2063" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -56130,7 +56127,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2064" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -56156,7 +56153,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2065" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -56182,7 +56179,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2066" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -56208,7 +56205,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2067" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -56234,7 +56231,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2068" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -56260,7 +56257,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2069" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -56286,7 +56283,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2070" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -56312,7 +56309,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2071" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -56338,7 +56335,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2072" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -56364,7 +56361,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2073" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -56390,7 +56387,7 @@
         <v>14</v>
       </c>
       <c r="G2074" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -56416,7 +56413,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2075" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56442,7 +56439,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2076" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56468,7 +56465,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2077" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56494,7 +56491,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2078" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56520,7 +56517,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2079" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -56546,7 +56543,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2080" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -56572,7 +56569,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2081" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56598,7 +56595,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2082" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56624,7 +56621,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2083" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56650,7 +56647,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2084" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56676,7 +56673,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2085" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56702,7 +56699,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2086" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56728,7 +56725,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2087" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56754,7 +56751,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2088" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56780,7 +56777,7 @@
         <v>15.5</v>
       </c>
       <c r="G2089" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56806,7 +56803,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2090" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56832,7 +56829,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2091" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56858,7 +56855,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2092" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56884,7 +56881,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2093" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56910,7 +56907,7 @@
         <v>14.5</v>
       </c>
       <c r="G2094" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56936,7 +56933,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2095" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56962,7 +56959,7 @@
         <v>15</v>
       </c>
       <c r="G2096" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56988,7 +56985,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2097" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -57014,7 +57011,7 @@
         <v>15</v>
       </c>
       <c r="G2098" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -57040,7 +57037,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2099" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -57066,7 +57063,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2100" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -57092,7 +57089,7 @@
         <v>15</v>
       </c>
       <c r="G2101" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -57118,7 +57115,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2102" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -57144,7 +57141,7 @@
         <v>15</v>
       </c>
       <c r="G2103" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -57170,7 +57167,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2104" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -57196,7 +57193,7 @@
         <v>15</v>
       </c>
       <c r="G2105" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -57222,7 +57219,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2106" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -57248,7 +57245,7 @@
         <v>15</v>
       </c>
       <c r="G2107" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -57274,7 +57271,7 @@
         <v>15</v>
       </c>
       <c r="G2108" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -57300,7 +57297,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2109" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -57326,7 +57323,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2110" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -57352,7 +57349,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2111" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -57378,7 +57375,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2112" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -57404,7 +57401,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2113" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -57430,7 +57427,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2114" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -57456,7 +57453,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2115" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -57482,7 +57479,7 @@
         <v>14</v>
       </c>
       <c r="G2116" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -57508,7 +57505,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2117" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57534,7 +57531,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2118" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -57560,7 +57557,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2119" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57586,7 +57583,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2120" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57612,7 +57609,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2121" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57638,7 +57635,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2122" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57664,7 +57661,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2123" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57690,7 +57687,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2124" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57698,7 +57695,7 @@
     </row>
     <row r="2125">
       <c r="A2125" s="1" t="n">
-        <v>45986.6480787037</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B2125" t="n">
         <v>2000</v>
@@ -57716,9 +57713,35 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2125" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H2125" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" s="1" t="n">
+        <v>45987.6847222222</v>
+      </c>
+      <c r="B2126" t="n">
+        <v>1875</v>
+      </c>
+      <c r="C2126" t="n">
+        <v>13.3000001907349</v>
+      </c>
+      <c r="D2126" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="E2126" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="F2126" t="n">
+        <v>13</v>
+      </c>
+      <c r="G2126" t="s">
+        <v>659</v>
+      </c>
+      <c r="H2126" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CULT.MI.xlsx
+++ b/data/CULT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="708">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68585252761841</t>
+    <t xml:space="preserve">4.68585300445557</t>
   </si>
   <si>
     <t xml:space="preserve">CULT.MI</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">4.59486532211304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60851383209229</t>
+    <t xml:space="preserve">4.60851335525513</t>
   </si>
   <si>
     <t xml:space="preserve">4.58576631546021</t>
@@ -59,28 +59,28 @@
     <t xml:space="preserve">4.48931980133057</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56301927566528</t>
+    <t xml:space="preserve">4.56301975250244</t>
   </si>
   <si>
     <t xml:space="preserve">4.51297664642334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46020364761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29824542999268</t>
+    <t xml:space="preserve">4.46020412445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29824638366699</t>
   </si>
   <si>
     <t xml:space="preserve">4.21271800994873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1817831993103</t>
+    <t xml:space="preserve">4.18178272247314</t>
   </si>
   <si>
     <t xml:space="preserve">4.23091554641724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36375665664673</t>
+    <t xml:space="preserve">4.36375713348389</t>
   </si>
   <si>
     <t xml:space="preserve">4.38195466995239</t>
@@ -92,37 +92,37 @@
     <t xml:space="preserve">4.28914785385132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24183368682861</t>
+    <t xml:space="preserve">4.24183416366577</t>
   </si>
   <si>
     <t xml:space="preserve">4.22909545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1053524017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09443426132202</t>
+    <t xml:space="preserve">4.10535287857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09443473815918</t>
   </si>
   <si>
     <t xml:space="preserve">4.10899257659912</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99616765975952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04712057113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0398416519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96341252326965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07441759109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32008266448975</t>
+    <t xml:space="preserve">3.99616837501526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04712152481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03984212875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96341228485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07441663742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32008361816406</t>
   </si>
   <si>
     <t xml:space="preserve">4.24911308288574</t>
@@ -131,22 +131,22 @@
     <t xml:space="preserve">3.97979044914246</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06895732879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05439949035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98524951934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05076026916504</t>
+    <t xml:space="preserve">4.06895780563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05439901351929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98524928092957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0507607460022</t>
   </si>
   <si>
     <t xml:space="preserve">4.07259702682495</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0380220413208</t>
+    <t xml:space="preserve">4.03802251815796</t>
   </si>
   <si>
     <t xml:space="preserve">4.04530143737793</t>
@@ -155,37 +155,37 @@
     <t xml:space="preserve">4.03074312210083</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01254510879517</t>
+    <t xml:space="preserve">4.01254558563232</t>
   </si>
   <si>
     <t xml:space="preserve">4.04894065856934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05985879898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07623672485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91245985031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99070906639099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01072645187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92155790328979</t>
+    <t xml:space="preserve">4.05985927581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07623624801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91245937347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99070858955383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01072597503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92155766487122</t>
   </si>
   <si>
     <t xml:space="preserve">4.00162696838379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05803918838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21635723114014</t>
+    <t xml:space="preserve">4.05803871154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21635675430298</t>
   </si>
   <si>
     <t xml:space="preserve">4.22181701660156</t>
@@ -200,16 +200,16 @@
     <t xml:space="preserve">4.35465812683105</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28186845779419</t>
+    <t xml:space="preserve">4.28186893463135</t>
   </si>
   <si>
     <t xml:space="preserve">4.26731014251709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39287281036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36739635467529</t>
+    <t xml:space="preserve">4.39287328720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36739683151245</t>
   </si>
   <si>
     <t xml:space="preserve">4.17814302444458</t>
@@ -218,31 +218,31 @@
     <t xml:space="preserve">4.27458953857422</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3182635307312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35647773742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26549100875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26367092132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27640867233276</t>
+    <t xml:space="preserve">4.31826305389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35647821426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26549053192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26366996765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27640819549561</t>
   </si>
   <si>
     <t xml:space="preserve">4.14902687072754</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35829830169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35283803939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29460620880127</t>
+    <t xml:space="preserve">4.35829782485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35283851623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29460668563843</t>
   </si>
   <si>
     <t xml:space="preserve">4.2036190032959</t>
@@ -251,19 +251,19 @@
     <t xml:space="preserve">4.24001359939575</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34010028839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4292688369751</t>
+    <t xml:space="preserve">4.34009981155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42926788330078</t>
   </si>
   <si>
     <t xml:space="preserve">4.34919929504395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33646106719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33100175857544</t>
+    <t xml:space="preserve">4.33646059036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33100128173828</t>
   </si>
   <si>
     <t xml:space="preserve">4.32190322875977</t>
@@ -272,13 +272,13 @@
     <t xml:space="preserve">4.46748208999634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45838451385498</t>
+    <t xml:space="preserve">4.45838403701782</t>
   </si>
   <si>
     <t xml:space="preserve">4.28550815582275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83057069778442</t>
+    <t xml:space="preserve">3.830570936203</t>
   </si>
   <si>
     <t xml:space="preserve">3.90336084365845</t>
@@ -287,28 +287,28 @@
     <t xml:space="preserve">3.8851625919342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87606549263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00344753265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93065690994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99434804916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08533525466919</t>
+    <t xml:space="preserve">3.87606453895569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00344657897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93065643310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99434781074524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08533573150635</t>
   </si>
   <si>
     <t xml:space="preserve">3.96705198287964</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86696624755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84876847267151</t>
+    <t xml:space="preserve">3.86696553230286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84876823425293</t>
   </si>
   <si>
     <t xml:space="preserve">3.8578667640686</t>
@@ -317,13 +317,13 @@
     <t xml:space="preserve">3.81237316131592</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80327463150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77597856521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97615098953247</t>
+    <t xml:space="preserve">3.80327391624451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77597880363464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97615075111389</t>
   </si>
   <si>
     <t xml:space="preserve">3.94885468482971</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">4.16722440719604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33528327941895</t>
+    <t xml:space="preserve">4.33528280258179</t>
   </si>
   <si>
     <t xml:space="preserve">4.21485900878906</t>
@@ -353,13 +353,13 @@
     <t xml:space="preserve">4.16854190826416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29823017120361</t>
+    <t xml:space="preserve">4.29822969436646</t>
   </si>
   <si>
     <t xml:space="preserve">4.30749320983887</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27970266342163</t>
+    <t xml:space="preserve">4.27970314025879</t>
   </si>
   <si>
     <t xml:space="preserve">4.3908634185791</t>
@@ -371,64 +371,64 @@
     <t xml:space="preserve">4.35380983352661</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08517074584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93695664405823</t>
+    <t xml:space="preserve">4.08517122268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93695616722107</t>
   </si>
   <si>
     <t xml:space="preserve">4.00180006027222</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97400975227356</t>
+    <t xml:space="preserve">3.9740104675293</t>
   </si>
   <si>
     <t xml:space="preserve">4.03885412216187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94622039794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95548224449158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23338508605957</t>
+    <t xml:space="preserve">3.94621992111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95548295974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23338651657104</t>
   </si>
   <si>
     <t xml:space="preserve">4.22412252426147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24264907836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11296081542969</t>
+    <t xml:space="preserve">4.2426495552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11296129226685</t>
   </si>
   <si>
     <t xml:space="preserve">4.26117610931396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9184296131134</t>
+    <t xml:space="preserve">3.91842937469482</t>
   </si>
   <si>
     <t xml:space="preserve">3.89990234375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89063858985901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07590770721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06664371490479</t>
+    <t xml:space="preserve">3.89063906669617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0759072303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06664419174194</t>
   </si>
   <si>
     <t xml:space="preserve">3.7980043888092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73316097259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86284875869751</t>
+    <t xml:space="preserve">3.73316073417664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86284804344177</t>
   </si>
   <si>
     <t xml:space="preserve">3.71463394165039</t>
@@ -437,76 +437,76 @@
     <t xml:space="preserve">3.70537042617798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77021431922913</t>
+    <t xml:space="preserve">3.77021455764771</t>
   </si>
   <si>
     <t xml:space="preserve">3.3904139995575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44599461555481</t>
+    <t xml:space="preserve">3.44599437713623</t>
   </si>
   <si>
     <t xml:space="preserve">3.58494567871094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68684339523315</t>
+    <t xml:space="preserve">3.68684363365173</t>
   </si>
   <si>
     <t xml:space="preserve">3.60347294807434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52010154724121</t>
+    <t xml:space="preserve">3.52010202407837</t>
   </si>
   <si>
     <t xml:space="preserve">3.37188720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46452164649963</t>
+    <t xml:space="preserve">3.46452140808105</t>
   </si>
   <si>
     <t xml:space="preserve">3.53862857818604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5293653011322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45525789260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34409666061401</t>
+    <t xml:space="preserve">3.52936553955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45525813102722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34409642219543</t>
   </si>
   <si>
     <t xml:space="preserve">3.07545757293701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14956498146057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29777956008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31630635261536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23293566703796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2421989440918</t>
+    <t xml:space="preserve">3.14956521987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29778003692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31630659103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23293542861938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24219870567322</t>
   </si>
   <si>
     <t xml:space="preserve">3.02914023399353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20514559745789</t>
+    <t xml:space="preserve">3.20514535903931</t>
   </si>
   <si>
     <t xml:space="preserve">3.25146245956421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10324740409851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1588282585144</t>
+    <t xml:space="preserve">3.10324716567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15882873535156</t>
   </si>
   <si>
     <t xml:space="preserve">2.91797947883606</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">2.77902793884277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87166166305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96429657936096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85313487052917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83460831642151</t>
+    <t xml:space="preserve">2.87166213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9642961025238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85313510894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83460855484009</t>
   </si>
   <si>
     <t xml:space="preserve">2.84387159347534</t>
@@ -536,13 +536,13 @@
     <t xml:space="preserve">2.72344732284546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76050114631653</t>
+    <t xml:space="preserve">2.76050090789795</t>
   </si>
   <si>
     <t xml:space="preserve">2.76976442337036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63081312179565</t>
+    <t xml:space="preserve">2.63081288337708</t>
   </si>
   <si>
     <t xml:space="preserve">2.67713022232056</t>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">2.38070034980774</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36217331886292</t>
+    <t xml:space="preserve">2.36217355728149</t>
   </si>
   <si>
     <t xml:space="preserve">2.29732966423035</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">2.26953959465027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23248529434204</t>
+    <t xml:space="preserve">2.23248553276062</t>
   </si>
   <si>
     <t xml:space="preserve">2.28806638717651</t>
@@ -578,10 +578,10 @@
     <t xml:space="preserve">2.13058805465698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22322225570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24174928665161</t>
+    <t xml:space="preserve">2.22322249412537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24174904823303</t>
   </si>
   <si>
     <t xml:space="preserve">2.11206126213074</t>
@@ -590,49 +590,49 @@
     <t xml:space="preserve">2.17690491676331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03795385360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99163687229156</t>
+    <t xml:space="preserve">2.0379536151886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99163675308228</t>
   </si>
   <si>
     <t xml:space="preserve">1.88047552108765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9453192949295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92679238319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16764163970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13985133171082</t>
+    <t xml:space="preserve">1.94531953334808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92679262161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16764140129089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13985157012939</t>
   </si>
   <si>
     <t xml:space="preserve">2.21395897865295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4084906578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48259830474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42701745033264</t>
+    <t xml:space="preserve">2.40849041938782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48259806632996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42701768875122</t>
   </si>
   <si>
     <t xml:space="preserve">2.38996386528015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46583580970764</t>
+    <t xml:space="preserve">2.46583557128906</t>
   </si>
   <si>
     <t xml:space="preserve">2.50406575202942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65698575973511</t>
+    <t xml:space="preserve">2.65698599815369</t>
   </si>
   <si>
     <t xml:space="preserve">2.71433067321777</t>
@@ -653,49 +653,49 @@
     <t xml:space="preserve">2.38937568664551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48495101928711</t>
+    <t xml:space="preserve">2.48495054244995</t>
   </si>
   <si>
     <t xml:space="preserve">2.61875581741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56141114234924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63787078857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73344564437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69521570205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75256109237671</t>
+    <t xml:space="preserve">2.56141090393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6378710269928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73344588279724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69521546363831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75256085395813</t>
   </si>
   <si>
     <t xml:space="preserve">2.80990600585938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82902097702026</t>
+    <t xml:space="preserve">2.82902073860168</t>
   </si>
   <si>
     <t xml:space="preserve">2.84813594818115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05840110778809</t>
+    <t xml:space="preserve">3.05840086936951</t>
   </si>
   <si>
     <t xml:space="preserve">2.86725091934204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7716760635376</t>
+    <t xml:space="preserve">2.77167582511902</t>
   </si>
   <si>
     <t xml:space="preserve">2.676100730896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59964060783386</t>
+    <t xml:space="preserve">2.59964084625244</t>
   </si>
   <si>
     <t xml:space="preserve">2.44672083854675</t>
@@ -704,10 +704,10 @@
     <t xml:space="preserve">2.37026071548462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09663081169128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34512591362</t>
+    <t xml:space="preserve">3.09663105010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34512567520142</t>
   </si>
   <si>
     <t xml:space="preserve">3.45981597900391</t>
@@ -716,52 +716,52 @@
     <t xml:space="preserve">3.74654126167297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76565599441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01415109634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10972690582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97592091560364</t>
+    <t xml:space="preserve">3.76565623283386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01415157318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1097264289856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9759213924408</t>
   </si>
   <si>
     <t xml:space="preserve">3.88034629821777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82300114631653</t>
+    <t xml:space="preserve">3.82300138473511</t>
   </si>
   <si>
     <t xml:space="preserve">3.44070100784302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40247106552124</t>
+    <t xml:space="preserve">3.40247130393982</t>
   </si>
   <si>
     <t xml:space="preserve">3.36424088478088</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68919610977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72742629051208</t>
+    <t xml:space="preserve">3.68919587135315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72742652893066</t>
   </si>
   <si>
     <t xml:space="preserve">3.70831155776978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57450652122498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55539131164551</t>
+    <t xml:space="preserve">3.57450604438782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55539107322693</t>
   </si>
   <si>
     <t xml:space="preserve">3.51716113090515</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6318507194519</t>
+    <t xml:space="preserve">3.63185095787048</t>
   </si>
   <si>
     <t xml:space="preserve">3.53627634048462</t>
@@ -773,28 +773,28 @@
     <t xml:space="preserve">3.65096592903137</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24955105781555</t>
+    <t xml:space="preserve">3.24955129623413</t>
   </si>
   <si>
     <t xml:space="preserve">3.32601118087769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42158603668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3068962097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38335585594177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59362149238586</t>
+    <t xml:space="preserve">3.42158627510071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30689597129822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38335633277893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59362125396729</t>
   </si>
   <si>
     <t xml:space="preserve">3.47893118858337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49804592132568</t>
+    <t xml:space="preserve">3.49804639816284</t>
   </si>
   <si>
     <t xml:space="preserve">3.28778100013733</t>
@@ -803,10 +803,10 @@
     <t xml:space="preserve">3.67008113861084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80388617515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93769121170044</t>
+    <t xml:space="preserve">3.80388593673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93769145011902</t>
   </si>
   <si>
     <t xml:space="preserve">4.03326606750488</t>
@@ -821,31 +821,31 @@
     <t xml:space="preserve">4.53025579452515</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51114082336426</t>
+    <t xml:space="preserve">4.51114130020142</t>
   </si>
   <si>
     <t xml:space="preserve">4.58760166168213</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49202632904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43468141555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62583112716675</t>
+    <t xml:space="preserve">4.49202585220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43468189239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62583160400391</t>
   </si>
   <si>
     <t xml:space="preserve">4.74052143096924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75963687896729</t>
+    <t xml:space="preserve">4.75963640213013</t>
   </si>
   <si>
     <t xml:space="preserve">4.70229148864746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68317699432373</t>
+    <t xml:space="preserve">4.68317651748657</t>
   </si>
   <si>
     <t xml:space="preserve">4.77875137329102</t>
@@ -854,16 +854,16 @@
     <t xml:space="preserve">4.56848669052124</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66406106948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72140645980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87432622909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96990203857422</t>
+    <t xml:space="preserve">4.66406202316284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72140693664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87432670593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9699010848999</t>
   </si>
   <si>
     <t xml:space="preserve">4.92211437225342</t>
@@ -878,25 +878,25 @@
     <t xml:space="preserve">5.20883893966675</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25662708282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30441474914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44777679443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63892698287964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.591139793396</t>
+    <t xml:space="preserve">5.25662660598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30441427230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44777631759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6389274597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59113883972168</t>
   </si>
   <si>
     <t xml:space="preserve">5.81332683563232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71643781661987</t>
+    <t xml:space="preserve">5.71643829345703</t>
   </si>
   <si>
     <t xml:space="preserve">5.42577171325684</t>
@@ -905,16 +905,16 @@
     <t xml:space="preserve">5.1351056098938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84443950653076</t>
+    <t xml:space="preserve">4.8444390296936</t>
   </si>
   <si>
     <t xml:space="preserve">4.82506132125854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80568361282349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59252834320068</t>
+    <t xml:space="preserve">4.80568313598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59252738952637</t>
   </si>
   <si>
     <t xml:space="preserve">4.55377197265625</t>
@@ -929,13 +929,13 @@
     <t xml:space="preserve">4.9897723197937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08666038513184</t>
+    <t xml:space="preserve">5.08666086196899</t>
   </si>
   <si>
     <t xml:space="preserve">5.18354940414429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94132804870605</t>
+    <t xml:space="preserve">4.9413275718689</t>
   </si>
   <si>
     <t xml:space="preserve">5.23199415206909</t>
@@ -944,16 +944,16 @@
     <t xml:space="preserve">4.74755001068115</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28043842315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89288377761841</t>
+    <t xml:space="preserve">5.2804388999939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89288330078125</t>
   </si>
   <si>
     <t xml:space="preserve">4.63128423690796</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53439426422119</t>
+    <t xml:space="preserve">4.53439474105835</t>
   </si>
   <si>
     <t xml:space="preserve">4.67003917694092</t>
@@ -965,40 +965,40 @@
     <t xml:space="preserve">4.72817277908325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70879554748535</t>
+    <t xml:space="preserve">4.70879459381104</t>
   </si>
   <si>
     <t xml:space="preserve">5.91021490097046</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61954927444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32888269424438</t>
+    <t xml:space="preserve">5.61954879760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32888317108154</t>
   </si>
   <si>
     <t xml:space="preserve">5.37732791900635</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57110548019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47421598434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66799306869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7337703704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29777097702026</t>
+    <t xml:space="preserve">5.57110500335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47421550750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66799354553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73376989364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29777050018311</t>
   </si>
   <si>
     <t xml:space="preserve">6.4431037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68532609939575</t>
+    <t xml:space="preserve">6.68532562255859</t>
   </si>
   <si>
     <t xml:space="preserve">6.5884370803833</t>
@@ -1007,13 +1007,13 @@
     <t xml:space="preserve">6.63688087463379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2493257522583</t>
+    <t xml:space="preserve">6.24932622909546</t>
   </si>
   <si>
     <t xml:space="preserve">6.34621477127075</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53999280929565</t>
+    <t xml:space="preserve">6.5399923324585</t>
   </si>
   <si>
     <t xml:space="preserve">6.3946590423584</t>
@@ -1022,34 +1022,34 @@
     <t xml:space="preserve">8.71999073028564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.993323802948</t>
+    <t xml:space="preserve">7.99332427978516</t>
   </si>
   <si>
     <t xml:space="preserve">8.09021377563477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04176902770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94487905502319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84799242019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89643621444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38087844848633</t>
+    <t xml:space="preserve">8.04176807403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94487953186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84799194335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89643526077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38087940216064</t>
   </si>
   <si>
     <t xml:space="preserve">10.2702112197876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88265609741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1733207702637</t>
+    <t xml:space="preserve">9.88265514373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.173321723938</t>
   </si>
   <si>
     <t xml:space="preserve">9.9795446395874</t>
@@ -1058,34 +1058,34 @@
     <t xml:space="preserve">10.0764322280884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2390985488892</t>
+    <t xml:space="preserve">11.2390975952148</t>
   </si>
   <si>
     <t xml:space="preserve">11.6266536712646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0799856185913</t>
+    <t xml:space="preserve">13.079984664917</t>
   </si>
   <si>
     <t xml:space="preserve">13.2737617492676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9830961227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4364290237427</t>
+    <t xml:space="preserve">12.9830951690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.436427116394</t>
   </si>
   <si>
     <t xml:space="preserve">14.3395395278931</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0177602767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1669807434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1930646896362</t>
+    <t xml:space="preserve">15.0177612304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1669788360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1930656433105</t>
   </si>
   <si>
     <t xml:space="preserve">15.0956735610962</t>
@@ -1094,19 +1094,19 @@
     <t xml:space="preserve">14.9008913040161</t>
   </si>
   <si>
-    <t xml:space="preserve">13.634801864624</t>
+    <t xml:space="preserve">13.6348009109497</t>
   </si>
   <si>
     <t xml:space="preserve">12.0765390396118</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4661045074463</t>
+    <t xml:space="preserve">12.466103553772</t>
   </si>
   <si>
     <t xml:space="preserve">13.4400196075439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9269781112671</t>
+    <t xml:space="preserve">13.9269771575928</t>
   </si>
   <si>
     <t xml:space="preserve">14.0243673324585</t>
@@ -1121,13 +1121,13 @@
     <t xml:space="preserve">14.4139337539673</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6087160110474</t>
+    <t xml:space="preserve">14.6087169647217</t>
   </si>
   <si>
     <t xml:space="preserve">14.7061080932617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5113258361816</t>
+    <t xml:space="preserve">14.5113248825073</t>
   </si>
   <si>
     <t xml:space="preserve">13.3426265716553</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">12.5634956359863</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1739301681519</t>
+    <t xml:space="preserve">12.1739292144775</t>
   </si>
   <si>
     <t xml:space="preserve">11.6869735717773</t>
@@ -1175,7 +1175,7 @@
     <t xml:space="preserve">10.7130584716797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2000169754028</t>
+    <t xml:space="preserve">11.2000160217285</t>
   </si>
   <si>
     <t xml:space="preserve">11.9791479110718</t>
@@ -1187,19 +1187,19 @@
     <t xml:space="preserve">10.9078416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2974081039429</t>
+    <t xml:space="preserve">11.2974071502686</t>
   </si>
   <si>
     <t xml:space="preserve">11.3947982788086</t>
   </si>
   <si>
-    <t xml:space="preserve">11.589581489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0052328109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7843656539917</t>
+    <t xml:space="preserve">11.5895805358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0052318572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7843647003174</t>
   </si>
   <si>
     <t xml:space="preserve">11.4921903610229</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">10.4208841323853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2261009216309</t>
+    <t xml:space="preserve">10.2261018753052</t>
   </si>
   <si>
     <t xml:space="preserve">10.3234939575195</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">10.1287097930908</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0313186645508</t>
+    <t xml:space="preserve">10.0313196182251</t>
   </si>
   <si>
     <t xml:space="preserve">9.73914527893066</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">9.34957981109619</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49566459655762</t>
+    <t xml:space="preserve">9.49566555023193</t>
   </si>
   <si>
     <t xml:space="preserve">12.2713222503662</t>
@@ -1247,16 +1247,16 @@
     <t xml:space="preserve">15.6800231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7321929931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1704549789429</t>
+    <t xml:space="preserve">13.7321939468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1704559326172</t>
   </si>
   <si>
     <t xml:space="preserve">14.3652372360229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0730638504028</t>
+    <t xml:space="preserve">14.0730628967285</t>
   </si>
   <si>
     <t xml:space="preserve">15.1443691253662</t>
@@ -1268,13 +1268,13 @@
     <t xml:space="preserve">15.585467338562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6344785690308</t>
+    <t xml:space="preserve">15.6344776153564</t>
   </si>
   <si>
     <t xml:space="preserve">15.193380355835</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4874467849731</t>
+    <t xml:space="preserve">15.4874458312988</t>
   </si>
   <si>
     <t xml:space="preserve">15.4384346008301</t>
@@ -1283,13 +1283,13 @@
     <t xml:space="preserve">15.2423915863037</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3894243240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9973363876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8993139266968</t>
+    <t xml:space="preserve">15.3894233703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9973373413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8993148803711</t>
   </si>
   <si>
     <t xml:space="preserve">15.0463485717773</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">13.7230529785156</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8210744857788</t>
+    <t xml:space="preserve">13.8210754394531</t>
   </si>
   <si>
     <t xml:space="preserve">14.3601942062378</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">13.6250314712524</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8700866699219</t>
+    <t xml:space="preserve">13.8700857162476</t>
   </si>
   <si>
     <t xml:space="preserve">13.6740427017212</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">14.9483261108398</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4092063903809</t>
+    <t xml:space="preserve">14.4092054367065</t>
   </si>
   <si>
     <t xml:space="preserve">14.8503036499023</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7522821426392</t>
+    <t xml:space="preserve">14.7522830963135</t>
   </si>
   <si>
     <t xml:space="preserve">14.6052494049072</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">14.5562391281128</t>
   </si>
   <si>
-    <t xml:space="preserve">14.507227897644</t>
+    <t xml:space="preserve">14.5072288513184</t>
   </si>
   <si>
     <t xml:space="preserve">14.0661296844482</t>
@@ -1370,16 +1370,16 @@
     <t xml:space="preserve">13.2819547653198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8898677825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7428350448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.987889289856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1349220275879</t>
+    <t xml:space="preserve">12.8898668289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7428340911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9878902435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1349229812622</t>
   </si>
   <si>
     <t xml:space="preserve">12.3507480621338</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">13.0859127044678</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4289884567261</t>
+    <t xml:space="preserve">13.4289875030518</t>
   </si>
   <si>
     <t xml:space="preserve">15.8305215835571</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">16.2226085662842</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0265674591064</t>
+    <t xml:space="preserve">16.0265655517578</t>
   </si>
   <si>
     <t xml:space="preserve">16.0755767822266</t>
@@ -1439,199 +1439,202 @@
     <t xml:space="preserve">16.2716197967529</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3206310272217</t>
+    <t xml:space="preserve">16.320629119873</t>
   </si>
   <si>
     <t xml:space="preserve">18.7221660614014</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0162315368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7023849487305</t>
+    <t xml:space="preserve">19.0162296295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7023830413818</t>
   </si>
   <si>
     <t xml:space="preserve">19.6043605804443</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8004055023193</t>
+    <t xml:space="preserve">19.800407409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0944709777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9173202514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.545015335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5252342224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7995166778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2311706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7806243896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1727104187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4865589141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6826019287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3687534332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6430377960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9955596923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2896251678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6034755706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8975391387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5054531097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.015344619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6232566833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8390808105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3291893005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.937105178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7212791442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1133651733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0351257324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1331481933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2113876342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4074287414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8192977905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2509498596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7608413696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9568843841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1529273986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7711753845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6439266204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5261211395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9964485168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5845794677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1924934387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8984279632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3885364532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4049549102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6512107849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3557014465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5527095794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7989635467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6019592285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9616947174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0601978302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0109443664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1586990356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2914772033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1929721832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1779956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9809913635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4884796142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5869827270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9959678649902</t>
   </si>
   <si>
     <t xml:space="preserve">20.0944690704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9173202514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5450172424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5252342224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7995166778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2311687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7806243896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1727104187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4865570068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6826019287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3687553405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6430377960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9955615997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2896270751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6034755706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8975391387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5054512023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0153427124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6232566833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8390789031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3291893005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.937105178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7212772369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1133651733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0351257324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1331481933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2113876342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4074287414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.819299697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2509517669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7608413696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9568843841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1529273986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7711772918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3300800323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6439266204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5261211395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9964485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5845775604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1924934387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8984260559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3885364532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4049549102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6512107849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3557014465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5527095794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7989635467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6019592285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9616947174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0601978302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0109443664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1586990356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2914772033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1929721832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1779956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9809913635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4884796142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5869827270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9959678649902</t>
   </si>
   <si>
     <t xml:space="preserve">19.4542045593262</t>
@@ -41437,7 +41440,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1499" t="s">
-        <v>481</v>
+        <v>540</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41489,7 +41492,7 @@
         <v>19.75</v>
       </c>
       <c r="G1501" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41593,7 +41596,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1505" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41619,7 +41622,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1506" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41671,7 +41674,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1508" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41697,7 +41700,7 @@
         <v>19.5</v>
       </c>
       <c r="G1509" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41723,7 +41726,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1510" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41749,7 +41752,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1511" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41775,7 +41778,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1512" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41801,7 +41804,7 @@
         <v>19.5</v>
       </c>
       <c r="G1513" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41827,7 +41830,7 @@
         <v>19.5</v>
       </c>
       <c r="G1514" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41853,7 +41856,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1515" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41879,7 +41882,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1516" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41905,7 +41908,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1517" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -41931,7 +41934,7 @@
         <v>18.75</v>
       </c>
       <c r="G1518" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -41957,7 +41960,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1519" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41983,7 +41986,7 @@
         <v>17.5</v>
       </c>
       <c r="G1520" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42009,7 +42012,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1521" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42035,7 +42038,7 @@
         <v>18.25</v>
       </c>
       <c r="G1522" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42061,7 +42064,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1523" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42087,7 +42090,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1524" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42113,7 +42116,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1525" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42139,7 +42142,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1526" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42165,7 +42168,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1527" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42191,7 +42194,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1528" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42217,7 +42220,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1529" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42347,7 +42350,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1534" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42373,7 +42376,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1535" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42425,7 +42428,7 @@
         <v>20</v>
       </c>
       <c r="G1537" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42503,7 +42506,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1540" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42529,7 +42532,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1541" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42555,7 +42558,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1542" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42607,7 +42610,7 @@
         <v>19.5</v>
       </c>
       <c r="G1544" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42633,7 +42636,7 @@
         <v>19.5</v>
       </c>
       <c r="G1545" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42711,7 +42714,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1548" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42737,7 +42740,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G1549" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42867,7 +42870,7 @@
         <v>19.5</v>
       </c>
       <c r="G1554" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42893,7 +42896,7 @@
         <v>19.5</v>
       </c>
       <c r="G1555" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42919,7 +42922,7 @@
         <v>19.5</v>
       </c>
       <c r="G1556" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42971,7 +42974,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1558" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -42997,7 +43000,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1559" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43023,7 +43026,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1560" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43049,7 +43052,7 @@
         <v>19</v>
       </c>
       <c r="G1561" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43075,7 +43078,7 @@
         <v>19</v>
       </c>
       <c r="G1562" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43101,7 +43104,7 @@
         <v>19</v>
       </c>
       <c r="G1563" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43127,7 +43130,7 @@
         <v>19</v>
       </c>
       <c r="G1564" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43153,7 +43156,7 @@
         <v>19</v>
       </c>
       <c r="G1565" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43179,7 +43182,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1566" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43205,7 +43208,7 @@
         <v>19</v>
       </c>
       <c r="G1567" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43231,7 +43234,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1568" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43257,7 +43260,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1569" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43283,7 +43286,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1570" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43309,7 +43312,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1571" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -43335,7 +43338,7 @@
         <v>19</v>
       </c>
       <c r="G1572" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43361,7 +43364,7 @@
         <v>19</v>
       </c>
       <c r="G1573" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43387,7 +43390,7 @@
         <v>19</v>
       </c>
       <c r="G1574" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43413,7 +43416,7 @@
         <v>18.75</v>
       </c>
       <c r="G1575" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43439,7 +43442,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1576" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43465,7 +43468,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1577" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43491,7 +43494,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1578" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43517,7 +43520,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1579" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43543,7 +43546,7 @@
         <v>19</v>
       </c>
       <c r="G1580" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43569,7 +43572,7 @@
         <v>19</v>
       </c>
       <c r="G1581" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43595,7 +43598,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1582" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43621,7 +43624,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1583" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43647,7 +43650,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1584" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43673,7 +43676,7 @@
         <v>18.75</v>
       </c>
       <c r="G1585" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43699,7 +43702,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1586" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43725,7 +43728,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1587" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43751,7 +43754,7 @@
         <v>18.5</v>
       </c>
       <c r="G1588" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43777,7 +43780,7 @@
         <v>18.5</v>
       </c>
       <c r="G1589" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43803,7 +43806,7 @@
         <v>18.5</v>
       </c>
       <c r="G1590" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43829,7 +43832,7 @@
         <v>18.5</v>
       </c>
       <c r="G1591" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43855,7 +43858,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1592" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43881,7 +43884,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1593" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43907,7 +43910,7 @@
         <v>18</v>
       </c>
       <c r="G1594" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43933,7 +43936,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1595" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -43959,7 +43962,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1596" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43985,7 +43988,7 @@
         <v>18.5</v>
       </c>
       <c r="G1597" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44011,7 +44014,7 @@
         <v>18.5</v>
       </c>
       <c r="G1598" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44037,7 +44040,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1599" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44063,7 +44066,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1600" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44089,7 +44092,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1601" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44115,7 +44118,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1602" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44141,7 +44144,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1603" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44167,7 +44170,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1604" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44193,7 +44196,7 @@
         <v>18.25</v>
       </c>
       <c r="G1605" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44219,7 +44222,7 @@
         <v>18</v>
       </c>
       <c r="G1606" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -44245,7 +44248,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1607" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -44271,7 +44274,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1608" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -44297,7 +44300,7 @@
         <v>18</v>
       </c>
       <c r="G1609" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44323,7 +44326,7 @@
         <v>18.25</v>
       </c>
       <c r="G1610" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -44349,7 +44352,7 @@
         <v>18.25</v>
       </c>
       <c r="G1611" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44375,7 +44378,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1612" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44401,7 +44404,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1613" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44427,7 +44430,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1614" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44453,7 +44456,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1615" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44479,7 +44482,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1616" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44505,7 +44508,7 @@
         <v>18</v>
       </c>
       <c r="G1617" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44531,7 +44534,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1618" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44557,7 +44560,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1619" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44583,7 +44586,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1620" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44609,7 +44612,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1621" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44635,7 +44638,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1622" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44661,7 +44664,7 @@
         <v>18</v>
       </c>
       <c r="G1623" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44687,7 +44690,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1624" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44713,7 +44716,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1625" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44739,7 +44742,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1626" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44765,7 +44768,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1627" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44791,7 +44794,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1628" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44817,7 +44820,7 @@
         <v>18.25</v>
       </c>
       <c r="G1629" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44843,7 +44846,7 @@
         <v>18.25</v>
       </c>
       <c r="G1630" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44869,7 +44872,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1631" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44895,7 +44898,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1632" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44921,7 +44924,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1633" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44947,7 +44950,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1634" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44973,7 +44976,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1635" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44999,7 +45002,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1636" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45025,7 +45028,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1637" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45051,7 +45054,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1638" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45077,7 +45080,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1639" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45103,7 +45106,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1640" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45129,7 +45132,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1641" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -45155,7 +45158,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1642" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45181,7 +45184,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1643" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45207,7 +45210,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1644" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -45233,7 +45236,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1645" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -45259,7 +45262,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1646" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -45285,7 +45288,7 @@
         <v>18</v>
       </c>
       <c r="G1647" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -45311,7 +45314,7 @@
         <v>18.25</v>
       </c>
       <c r="G1648" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -45337,7 +45340,7 @@
         <v>18.25</v>
       </c>
       <c r="G1649" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -45363,7 +45366,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1650" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45389,7 +45392,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1651" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -45415,7 +45418,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1652" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45441,7 +45444,7 @@
         <v>18</v>
       </c>
       <c r="G1653" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45467,7 +45470,7 @@
         <v>18</v>
       </c>
       <c r="G1654" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45493,7 +45496,7 @@
         <v>18</v>
       </c>
       <c r="G1655" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45519,7 +45522,7 @@
         <v>18</v>
       </c>
       <c r="G1656" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45545,7 +45548,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1657" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45571,7 +45574,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1658" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45597,7 +45600,7 @@
         <v>17.75</v>
       </c>
       <c r="G1659" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45623,7 +45626,7 @@
         <v>18</v>
       </c>
       <c r="G1660" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45649,7 +45652,7 @@
         <v>18</v>
       </c>
       <c r="G1661" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45675,7 +45678,7 @@
         <v>18</v>
       </c>
       <c r="G1662" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45701,7 +45704,7 @@
         <v>18</v>
       </c>
       <c r="G1663" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45727,7 +45730,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1664" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45753,7 +45756,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1665" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45779,7 +45782,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1666" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45805,7 +45808,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1667" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45831,7 +45834,7 @@
         <v>17.5</v>
       </c>
       <c r="G1668" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45857,7 +45860,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1669" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45883,7 +45886,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1670" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45909,7 +45912,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1671" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45935,7 +45938,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1672" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45961,7 +45964,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1673" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45987,7 +45990,7 @@
         <v>16.75</v>
       </c>
       <c r="G1674" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -46013,7 +46016,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1675" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -46039,7 +46042,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1676" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -46065,7 +46068,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1677" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -46091,7 +46094,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1678" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -46117,7 +46120,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1679" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -46143,7 +46146,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1680" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -46169,7 +46172,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1681" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -46195,7 +46198,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1682" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -46221,7 +46224,7 @@
         <v>17</v>
       </c>
       <c r="G1683" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -46247,7 +46250,7 @@
         <v>17</v>
       </c>
       <c r="G1684" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -46273,7 +46276,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1685" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -46299,7 +46302,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1686" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -46325,7 +46328,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1687" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -46351,7 +46354,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46377,7 +46380,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1689" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -46403,7 +46406,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1690" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -46429,7 +46432,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1691" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46455,7 +46458,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1692" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46481,7 +46484,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1693" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -46507,7 +46510,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46533,7 +46536,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1695" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46559,7 +46562,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1696" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46585,7 +46588,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1697" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46611,7 +46614,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1698" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46637,7 +46640,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1699" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46663,7 +46666,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1700" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46689,7 +46692,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1701" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46715,7 +46718,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1702" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46741,7 +46744,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1703" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46767,7 +46770,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1704" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46793,7 +46796,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1705" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46819,7 +46822,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1706" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46845,7 +46848,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1707" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46871,7 +46874,7 @@
         <v>15</v>
       </c>
       <c r="G1708" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46897,7 +46900,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1709" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46923,7 +46926,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1710" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46949,7 +46952,7 @@
         <v>14.5</v>
       </c>
       <c r="G1711" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46975,7 +46978,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1712" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -47001,7 +47004,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1713" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47027,7 +47030,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1714" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -47053,7 +47056,7 @@
         <v>15</v>
       </c>
       <c r="G1715" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -47079,7 +47082,7 @@
         <v>15</v>
       </c>
       <c r="G1716" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47105,7 +47108,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1717" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -47131,7 +47134,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1718" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -47157,7 +47160,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -47183,7 +47186,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1720" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -47209,7 +47212,7 @@
         <v>14.25</v>
       </c>
       <c r="G1721" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -47235,7 +47238,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1722" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -47261,7 +47264,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1723" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -47287,7 +47290,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1724" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -47313,7 +47316,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1725" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -47339,7 +47342,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1726" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47365,7 +47368,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1727" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47391,7 +47394,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1728" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -47417,7 +47420,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1729" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47443,7 +47446,7 @@
         <v>14.75</v>
       </c>
       <c r="G1730" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47469,7 +47472,7 @@
         <v>14.75</v>
       </c>
       <c r="G1731" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47495,7 +47498,7 @@
         <v>14.75</v>
       </c>
       <c r="G1732" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47521,7 +47524,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1733" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47547,7 +47550,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1734" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47573,7 +47576,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1735" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47599,7 +47602,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1736" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47625,7 +47628,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1737" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47651,7 +47654,7 @@
         <v>13.25</v>
       </c>
       <c r="G1738" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47677,7 +47680,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1739" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47703,7 +47706,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1740" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47729,7 +47732,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1741" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47755,7 +47758,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1742" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47781,7 +47784,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1743" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47807,7 +47810,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1744" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47833,7 +47836,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1745" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47859,7 +47862,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1746" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47885,7 +47888,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1747" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47911,7 +47914,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1748" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47937,7 +47940,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1749" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47963,7 +47966,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1750" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47989,7 +47992,7 @@
         <v>12.75</v>
       </c>
       <c r="G1751" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -48015,7 +48018,7 @@
         <v>12.5</v>
       </c>
       <c r="G1752" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -48041,7 +48044,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1753" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -48067,7 +48070,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1754" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -48093,7 +48096,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1755" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -48119,7 +48122,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1756" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -48145,7 +48148,7 @@
         <v>12.25</v>
       </c>
       <c r="G1757" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -48171,7 +48174,7 @@
         <v>12.25</v>
       </c>
       <c r="G1758" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -48197,7 +48200,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1759" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -48223,7 +48226,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1760" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -48249,7 +48252,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1761" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -48275,7 +48278,7 @@
         <v>12.75</v>
       </c>
       <c r="G1762" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -48301,7 +48304,7 @@
         <v>12.75</v>
       </c>
       <c r="G1763" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -48327,7 +48330,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1764" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -48353,7 +48356,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1765" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48379,7 +48382,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1766" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48405,7 +48408,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1767" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48431,7 +48434,7 @@
         <v>12.5</v>
       </c>
       <c r="G1768" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48457,7 +48460,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1769" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48483,7 +48486,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1770" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48509,7 +48512,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1771" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48535,7 +48538,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1772" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48561,7 +48564,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1773" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48587,7 +48590,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1774" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48613,7 +48616,7 @@
         <v>12.75</v>
       </c>
       <c r="G1775" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48639,7 +48642,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1776" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48665,7 +48668,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1777" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48691,7 +48694,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1778" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48717,7 +48720,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1779" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48743,7 +48746,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1780" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48769,7 +48772,7 @@
         <v>13</v>
       </c>
       <c r="G1781" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48795,7 +48798,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1782" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48821,7 +48824,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1783" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48847,7 +48850,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1784" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48873,7 +48876,7 @@
         <v>12.75</v>
       </c>
       <c r="G1785" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48899,7 +48902,7 @@
         <v>12.75</v>
       </c>
       <c r="G1786" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48925,7 +48928,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48951,7 +48954,7 @@
         <v>12.5</v>
       </c>
       <c r="G1788" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48977,7 +48980,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1789" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -49003,7 +49006,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1790" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -49029,7 +49032,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1791" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -49055,7 +49058,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1792" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -49081,7 +49084,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1793" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -49107,7 +49110,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1794" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -49133,7 +49136,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1795" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -49159,7 +49162,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1796" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -49185,7 +49188,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1797" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -49211,7 +49214,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1798" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -49237,7 +49240,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1799" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -49263,7 +49266,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1800" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -49289,7 +49292,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1801" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -49315,7 +49318,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1802" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -49341,7 +49344,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1803" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49367,7 +49370,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1804" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49393,7 +49396,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1805" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49419,7 +49422,7 @@
         <v>12.75</v>
       </c>
       <c r="G1806" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49445,7 +49448,7 @@
         <v>12.75</v>
       </c>
       <c r="G1807" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49471,7 +49474,7 @@
         <v>12.75</v>
       </c>
       <c r="G1808" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49497,7 +49500,7 @@
         <v>12.75</v>
       </c>
       <c r="G1809" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49523,7 +49526,7 @@
         <v>12.75</v>
       </c>
       <c r="G1810" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49549,7 +49552,7 @@
         <v>12.75</v>
       </c>
       <c r="G1811" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49575,7 +49578,7 @@
         <v>12.75</v>
       </c>
       <c r="G1812" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49601,7 +49604,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1813" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49627,7 +49630,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1814" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49653,7 +49656,7 @@
         <v>12.75</v>
       </c>
       <c r="G1815" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49679,7 +49682,7 @@
         <v>12.75</v>
       </c>
       <c r="G1816" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49705,7 +49708,7 @@
         <v>12.75</v>
       </c>
       <c r="G1817" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49731,7 +49734,7 @@
         <v>12.75</v>
       </c>
       <c r="G1818" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49757,7 +49760,7 @@
         <v>12.75</v>
       </c>
       <c r="G1819" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49783,7 +49786,7 @@
         <v>12.75</v>
       </c>
       <c r="G1820" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49809,7 +49812,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1821" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49835,7 +49838,7 @@
         <v>12.5</v>
       </c>
       <c r="G1822" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49861,7 +49864,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1823" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49887,7 +49890,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1824" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49913,7 +49916,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1825" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49939,7 +49942,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1826" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49965,7 +49968,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1827" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49991,7 +49994,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1828" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -50017,7 +50020,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1829" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -50043,7 +50046,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1830" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -50069,7 +50072,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1831" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -50095,7 +50098,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1832" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -50121,7 +50124,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1833" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -50147,7 +50150,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1834" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -50173,7 +50176,7 @@
         <v>12.5</v>
       </c>
       <c r="G1835" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -50199,7 +50202,7 @@
         <v>12.5</v>
       </c>
       <c r="G1836" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -50225,7 +50228,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1837" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -50251,7 +50254,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1838" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -50277,7 +50280,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1839" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -50303,7 +50306,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -50329,7 +50332,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1841" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50355,7 +50358,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1842" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50381,7 +50384,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1843" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50407,7 +50410,7 @@
         <v>12.75</v>
       </c>
       <c r="G1844" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50433,7 +50436,7 @@
         <v>12.75</v>
       </c>
       <c r="G1845" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50459,7 +50462,7 @@
         <v>12.75</v>
       </c>
       <c r="G1846" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50485,7 +50488,7 @@
         <v>12.75</v>
       </c>
       <c r="G1847" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50511,7 +50514,7 @@
         <v>12.75</v>
       </c>
       <c r="G1848" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50537,7 +50540,7 @@
         <v>12.75</v>
       </c>
       <c r="G1849" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50563,7 +50566,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1850" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50589,7 +50592,7 @@
         <v>13.25</v>
       </c>
       <c r="G1851" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50615,7 +50618,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1852" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50641,7 +50644,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1853" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50667,7 +50670,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1854" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50693,7 +50696,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1855" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50719,7 +50722,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1856" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50745,7 +50748,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1857" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50771,7 +50774,7 @@
         <v>13</v>
       </c>
       <c r="G1858" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50797,7 +50800,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1859" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50823,7 +50826,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1860" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50849,7 +50852,7 @@
         <v>13.25</v>
       </c>
       <c r="G1861" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50875,7 +50878,7 @@
         <v>13.25</v>
       </c>
       <c r="G1862" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50901,7 +50904,7 @@
         <v>13.25</v>
       </c>
       <c r="G1863" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50927,7 +50930,7 @@
         <v>13.25</v>
       </c>
       <c r="G1864" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50953,7 +50956,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1865" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50979,7 +50982,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1866" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -51005,7 +51008,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1867" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -51031,7 +51034,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1868" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -51057,7 +51060,7 @@
         <v>12.5</v>
       </c>
       <c r="G1869" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -51083,7 +51086,7 @@
         <v>12.5</v>
       </c>
       <c r="G1870" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -51109,7 +51112,7 @@
         <v>12.5</v>
       </c>
       <c r="G1871" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -51135,7 +51138,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1872" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -51161,7 +51164,7 @@
         <v>12.5</v>
       </c>
       <c r="G1873" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -51187,7 +51190,7 @@
         <v>12.5</v>
       </c>
       <c r="G1874" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -51213,7 +51216,7 @@
         <v>12.5</v>
       </c>
       <c r="G1875" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -51239,7 +51242,7 @@
         <v>12.5</v>
       </c>
       <c r="G1876" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -51265,7 +51268,7 @@
         <v>12.25</v>
       </c>
       <c r="G1877" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -51291,7 +51294,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1878" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -51317,7 +51320,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1879" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -51343,7 +51346,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1880" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51369,7 +51372,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1881" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51395,7 +51398,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1882" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51421,7 +51424,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1883" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51447,7 +51450,7 @@
         <v>12.5</v>
       </c>
       <c r="G1884" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51473,7 +51476,7 @@
         <v>12.5</v>
       </c>
       <c r="G1885" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51499,7 +51502,7 @@
         <v>12.5</v>
       </c>
       <c r="G1886" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51525,7 +51528,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1887" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51551,7 +51554,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1888" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51577,7 +51580,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1889" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51603,7 +51606,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1890" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51629,7 +51632,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1891" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51655,7 +51658,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1892" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51681,7 +51684,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1893" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51707,7 +51710,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1894" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51733,7 +51736,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1895" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51759,7 +51762,7 @@
         <v>14.75</v>
       </c>
       <c r="G1896" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51785,7 +51788,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1897" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51811,7 +51814,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1898" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51837,7 +51840,7 @@
         <v>14.25</v>
       </c>
       <c r="G1899" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51863,7 +51866,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1900" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51889,7 +51892,7 @@
         <v>14</v>
       </c>
       <c r="G1901" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51915,7 +51918,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1902" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51941,7 +51944,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1903" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51967,7 +51970,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1904" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51993,7 +51996,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1905" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52019,7 +52022,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1906" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52045,7 +52048,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52071,7 +52074,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1908" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52097,7 +52100,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1909" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52123,7 +52126,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1910" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -52149,7 +52152,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1911" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -52175,7 +52178,7 @@
         <v>13.25</v>
       </c>
       <c r="G1912" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -52201,7 +52204,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1913" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -52227,7 +52230,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1914" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -52253,7 +52256,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1915" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -52279,7 +52282,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1916" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -52305,7 +52308,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1917" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -52331,7 +52334,7 @@
         <v>12.75</v>
       </c>
       <c r="G1918" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52357,7 +52360,7 @@
         <v>13</v>
       </c>
       <c r="G1919" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52383,7 +52386,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1920" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52409,7 +52412,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1921" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52435,7 +52438,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1922" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52461,7 +52464,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1923" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52487,7 +52490,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1924" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52513,7 +52516,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1925" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52539,7 +52542,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1926" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52565,7 +52568,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1927" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52591,7 +52594,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1928" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52617,7 +52620,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1929" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52643,7 +52646,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1930" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52669,7 +52672,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1931" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52695,7 +52698,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1932" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52721,7 +52724,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1933" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52747,7 +52750,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1934" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52773,7 +52776,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1935" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52799,7 +52802,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1936" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52825,7 +52828,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1937" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52851,7 +52854,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1938" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52877,7 +52880,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1939" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52903,7 +52906,7 @@
         <v>12.5</v>
       </c>
       <c r="G1940" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52929,7 +52932,7 @@
         <v>12.75</v>
       </c>
       <c r="G1941" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52955,7 +52958,7 @@
         <v>12.75</v>
       </c>
       <c r="G1942" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52981,7 +52984,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1943" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53007,7 +53010,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1944" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53033,7 +53036,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1945" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53059,7 +53062,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1946" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53085,7 +53088,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1947" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53111,7 +53114,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1948" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -53137,7 +53140,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1949" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -53163,7 +53166,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1950" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -53189,7 +53192,7 @@
         <v>12.25</v>
       </c>
       <c r="G1951" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -53215,7 +53218,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1952" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -53241,7 +53244,7 @@
         <v>12.5</v>
       </c>
       <c r="G1953" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -53267,7 +53270,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1954" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -53293,7 +53296,7 @@
         <v>12.25</v>
       </c>
       <c r="G1955" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -53319,7 +53322,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1956" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -53345,7 +53348,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1957" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53371,7 +53374,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1958" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53397,7 +53400,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1959" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53423,7 +53426,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1960" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53449,7 +53452,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1961" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53475,7 +53478,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1962" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53501,7 +53504,7 @@
         <v>10.5</v>
       </c>
       <c r="G1963" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53527,7 +53530,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1964" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53553,7 +53556,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1965" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53579,7 +53582,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1966" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53605,7 +53608,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1967" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53631,7 +53634,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1968" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53657,7 +53660,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1969" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53683,7 +53686,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1970" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53709,7 +53712,7 @@
         <v>12</v>
       </c>
       <c r="G1971" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53735,7 +53738,7 @@
         <v>12</v>
       </c>
       <c r="G1972" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53761,7 +53764,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1973" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53787,7 +53790,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1974" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53813,7 +53816,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1975" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53839,7 +53842,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1976" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53865,7 +53868,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1977" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53891,7 +53894,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1978" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53917,7 +53920,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1979" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53943,7 +53946,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1980" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53969,7 +53972,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1981" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53995,7 +53998,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1982" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54021,7 +54024,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54047,7 +54050,7 @@
         <v>13</v>
       </c>
       <c r="G1984" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54073,7 +54076,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1985" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54099,7 +54102,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1986" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -54125,7 +54128,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1987" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -54151,7 +54154,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1988" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -54177,7 +54180,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1989" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -54203,7 +54206,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1990" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -54229,7 +54232,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1991" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -54255,7 +54258,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1992" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -54281,7 +54284,7 @@
         <v>13.5</v>
       </c>
       <c r="G1993" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -54307,7 +54310,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1994" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -54333,7 +54336,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1995" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54359,7 +54362,7 @@
         <v>14.5</v>
       </c>
       <c r="G1996" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54385,7 +54388,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1997" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54411,7 +54414,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1998" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54437,7 +54440,7 @@
         <v>15</v>
       </c>
       <c r="G1999" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54463,7 +54466,7 @@
         <v>15.5</v>
       </c>
       <c r="G2000" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54489,7 +54492,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2001" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54515,7 +54518,7 @@
         <v>15.5</v>
       </c>
       <c r="G2002" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54541,7 +54544,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2003" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54567,7 +54570,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2004" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54593,7 +54596,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2005" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54619,7 +54622,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2006" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54645,7 +54648,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2007" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54671,7 +54674,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2008" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54697,7 +54700,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2009" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54723,7 +54726,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2010" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54749,7 +54752,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2011" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54775,7 +54778,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2012" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54801,7 +54804,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2013" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54827,7 +54830,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2014" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54853,7 +54856,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2015" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54879,7 +54882,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2016" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54905,7 +54908,7 @@
         <v>16</v>
       </c>
       <c r="G2017" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54931,7 +54934,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2018" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54957,7 +54960,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2019" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54983,7 +54986,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2020" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55009,7 +55012,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2021" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55035,7 +55038,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2022" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55061,7 +55064,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2023" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55087,7 +55090,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2024" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -55113,7 +55116,7 @@
         <v>17.5</v>
       </c>
       <c r="G2025" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -55139,7 +55142,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2026" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -55165,7 +55168,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2027" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -55191,7 +55194,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2028" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -55217,7 +55220,7 @@
         <v>17.5</v>
       </c>
       <c r="G2029" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -55243,7 +55246,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2030" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -55269,7 +55272,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2031" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -55295,7 +55298,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2032" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -55321,7 +55324,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2033" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -55347,7 +55350,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2034" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -55373,7 +55376,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2035" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -55399,7 +55402,7 @@
         <v>17.5</v>
       </c>
       <c r="G2036" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -55425,7 +55428,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2037" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55451,7 +55454,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2038" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55477,7 +55480,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2039" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55503,7 +55506,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2040" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55529,7 +55532,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2041" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55555,7 +55558,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2042" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55581,7 +55584,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2043" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55607,7 +55610,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2044" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55633,7 +55636,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2045" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55659,7 +55662,7 @@
         <v>13</v>
       </c>
       <c r="G2046" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55685,7 +55688,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2047" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55711,7 +55714,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2048" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55737,7 +55740,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2049" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55763,7 +55766,7 @@
         <v>12</v>
       </c>
       <c r="G2050" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55789,7 +55792,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2051" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55815,7 +55818,7 @@
         <v>12</v>
       </c>
       <c r="G2052" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55841,7 +55844,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2053" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55867,7 +55870,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2054" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55893,7 +55896,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2055" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55919,7 +55922,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2056" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55945,7 +55948,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2057" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55971,7 +55974,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2058" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55997,7 +56000,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2059" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -56023,7 +56026,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2060" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -56049,7 +56052,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2061" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -56075,7 +56078,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2062" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -56101,7 +56104,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2063" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -56127,7 +56130,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2064" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -56153,7 +56156,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2065" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -56179,7 +56182,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2066" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -56205,7 +56208,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2067" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -56231,7 +56234,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2068" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -56257,7 +56260,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2069" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -56283,7 +56286,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2070" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -56309,7 +56312,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2071" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -56335,7 +56338,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2072" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -56361,7 +56364,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2073" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -56387,7 +56390,7 @@
         <v>14</v>
       </c>
       <c r="G2074" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -56413,7 +56416,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2075" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56439,7 +56442,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2076" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56465,7 +56468,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2077" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56491,7 +56494,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2078" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56517,7 +56520,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2079" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -56543,7 +56546,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2080" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -56569,7 +56572,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2081" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56595,7 +56598,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2082" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56621,7 +56624,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2083" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56647,7 +56650,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2084" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56673,7 +56676,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2085" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56699,7 +56702,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2086" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56725,7 +56728,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2087" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56751,7 +56754,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2088" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56777,7 +56780,7 @@
         <v>15.5</v>
       </c>
       <c r="G2089" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56803,7 +56806,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2090" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56829,7 +56832,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2091" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56855,7 +56858,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2092" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56881,7 +56884,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2093" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56907,7 +56910,7 @@
         <v>14.5</v>
       </c>
       <c r="G2094" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56933,7 +56936,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2095" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56959,7 +56962,7 @@
         <v>15</v>
       </c>
       <c r="G2096" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56985,7 +56988,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2097" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -57011,7 +57014,7 @@
         <v>15</v>
       </c>
       <c r="G2098" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -57037,7 +57040,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2099" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -57063,7 +57066,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2100" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -57089,7 +57092,7 @@
         <v>15</v>
       </c>
       <c r="G2101" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -57115,7 +57118,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2102" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -57141,7 +57144,7 @@
         <v>15</v>
       </c>
       <c r="G2103" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -57167,7 +57170,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2104" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -57193,7 +57196,7 @@
         <v>15</v>
       </c>
       <c r="G2105" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -57219,7 +57222,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2106" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -57245,7 +57248,7 @@
         <v>15</v>
       </c>
       <c r="G2107" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -57271,7 +57274,7 @@
         <v>15</v>
       </c>
       <c r="G2108" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -57297,7 +57300,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2109" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -57323,7 +57326,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2110" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -57349,7 +57352,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2111" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -57375,7 +57378,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2112" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -57401,7 +57404,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2113" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -57427,7 +57430,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2114" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -57453,7 +57456,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2115" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -57479,7 +57482,7 @@
         <v>14</v>
       </c>
       <c r="G2116" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -57505,7 +57508,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2117" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57531,7 +57534,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2118" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -57557,7 +57560,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2119" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57583,7 +57586,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2120" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57609,7 +57612,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2121" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57635,7 +57638,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2122" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57661,7 +57664,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2123" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57687,7 +57690,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2124" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57713,7 +57716,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2125" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57721,7 +57724,7 @@
     </row>
     <row r="2126">
       <c r="A2126" s="1" t="n">
-        <v>45987.6847222222</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B2126" t="n">
         <v>1875</v>
@@ -57739,9 +57742,35 @@
         <v>13</v>
       </c>
       <c r="G2126" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H2126" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" s="1" t="n">
+        <v>45988.6638541667</v>
+      </c>
+      <c r="B2127" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C2127" t="n">
+        <v>13.6999998092651</v>
+      </c>
+      <c r="D2127" t="n">
+        <v>13.3000001907349</v>
+      </c>
+      <c r="E2127" t="n">
+        <v>13.3000001907349</v>
+      </c>
+      <c r="F2127" t="n">
+        <v>13.6999998092651</v>
+      </c>
+      <c r="G2127" t="s">
+        <v>700</v>
+      </c>
+      <c r="H2127" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CULT.MI.xlsx
+++ b/data/CULT.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">4.57666778564453</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59486532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60851335525513</t>
+    <t xml:space="preserve">4.5948657989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60851383209229</t>
   </si>
   <si>
     <t xml:space="preserve">4.58576631546021</t>
@@ -59,13 +59,13 @@
     <t xml:space="preserve">4.48931980133057</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56301975250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51297664642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46020412445068</t>
+    <t xml:space="preserve">4.56301927566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5129771232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46020364761353</t>
   </si>
   <si>
     <t xml:space="preserve">4.29824638366699</t>
@@ -74,22 +74,22 @@
     <t xml:space="preserve">4.21271800994873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18178272247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23091554641724</t>
+    <t xml:space="preserve">4.18178224563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23091602325439</t>
   </si>
   <si>
     <t xml:space="preserve">4.36375713348389</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38195466995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35101890563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28914785385132</t>
+    <t xml:space="preserve">4.38195419311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35101842880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28914737701416</t>
   </si>
   <si>
     <t xml:space="preserve">4.24183416366577</t>
@@ -98,28 +98,28 @@
     <t xml:space="preserve">4.22909545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10535287857056</t>
+    <t xml:space="preserve">4.10535335540771</t>
   </si>
   <si>
     <t xml:space="preserve">4.09443473815918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10899257659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99616837501526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04712152481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03984212875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96341228485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07441663742065</t>
+    <t xml:space="preserve">4.10899209976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9961678981781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04712104797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0398416519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96341300010681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07441711425781</t>
   </si>
   <si>
     <t xml:space="preserve">4.32008361816406</t>
@@ -128,13 +128,13 @@
     <t xml:space="preserve">4.24911308288574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97979044914246</t>
+    <t xml:space="preserve">3.9797899723053</t>
   </si>
   <si>
     <t xml:space="preserve">4.06895780563354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05439901351929</t>
+    <t xml:space="preserve">4.0543999671936</t>
   </si>
   <si>
     <t xml:space="preserve">3.98524928092957</t>
@@ -143,10 +143,10 @@
     <t xml:space="preserve">4.0507607460022</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07259702682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03802251815796</t>
+    <t xml:space="preserve">4.07259654998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0380220413208</t>
   </si>
   <si>
     <t xml:space="preserve">4.04530143737793</t>
@@ -161,13 +161,13 @@
     <t xml:space="preserve">4.04894065856934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05985927581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07623624801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91245937347412</t>
+    <t xml:space="preserve">4.05985879898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0762357711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91245913505554</t>
   </si>
   <si>
     <t xml:space="preserve">3.99070858955383</t>
@@ -176,19 +176,19 @@
     <t xml:space="preserve">4.01072597503662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92155766487122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00162696838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05803871154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21635675430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22181701660156</t>
+    <t xml:space="preserve">3.92155861854553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00162649154663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05803918838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21635723114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2218165397644</t>
   </si>
   <si>
     <t xml:space="preserve">4.18542146682739</t>
@@ -197,19 +197,19 @@
     <t xml:space="preserve">4.16176462173462</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35465812683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28186893463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26731014251709</t>
+    <t xml:space="preserve">4.35465860366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28186845779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26730966567993</t>
   </si>
   <si>
     <t xml:space="preserve">4.39287328720093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36739683151245</t>
+    <t xml:space="preserve">4.36739730834961</t>
   </si>
   <si>
     <t xml:space="preserve">4.17814302444458</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">4.27458953857422</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31826305389404</t>
+    <t xml:space="preserve">4.3182635307312</t>
   </si>
   <si>
     <t xml:space="preserve">4.35647821426392</t>
@@ -227,73 +227,73 @@
     <t xml:space="preserve">4.26549053192139</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26366996765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27640819549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14902687072754</t>
+    <t xml:space="preserve">4.26367044448853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27640867233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1490273475647</t>
   </si>
   <si>
     <t xml:space="preserve">4.35829782485962</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35283851623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29460668563843</t>
+    <t xml:space="preserve">4.35283946990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29460573196411</t>
   </si>
   <si>
     <t xml:space="preserve">4.2036190032959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24001359939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34009981155396</t>
+    <t xml:space="preserve">4.24001407623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3400993347168</t>
   </si>
   <si>
     <t xml:space="preserve">4.42926788330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34919929504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33646059036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33100128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32190322875977</t>
+    <t xml:space="preserve">4.34919881820679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33646011352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33100175857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32190227508545</t>
   </si>
   <si>
     <t xml:space="preserve">4.46748208999634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45838403701782</t>
+    <t xml:space="preserve">4.45838499069214</t>
   </si>
   <si>
     <t xml:space="preserve">4.28550815582275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.830570936203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90336084365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8851625919342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87606453895569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00344657897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93065643310547</t>
+    <t xml:space="preserve">3.83057117462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90336036682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88516330718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87606477737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00344705581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93065667152405</t>
   </si>
   <si>
     <t xml:space="preserve">3.99434781074524</t>
@@ -305,13 +305,13 @@
     <t xml:space="preserve">3.96705198287964</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86696553230286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84876823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8578667640686</t>
+    <t xml:space="preserve">3.86696529388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84876799583435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85786652565002</t>
   </si>
   <si>
     <t xml:space="preserve">3.81237316131592</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">3.80327391624451</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77597880363464</t>
+    <t xml:space="preserve">3.77597832679749</t>
   </si>
   <si>
     <t xml:space="preserve">3.97615075111389</t>
@@ -329,25 +329,25 @@
     <t xml:space="preserve">3.94885468482971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13992786407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16722440719604</t>
+    <t xml:space="preserve">4.13992834091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16722393035889</t>
   </si>
   <si>
     <t xml:space="preserve">4.33528280258179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21485900878906</t>
+    <t xml:space="preserve">4.21485948562622</t>
   </si>
   <si>
     <t xml:space="preserve">4.31675624847412</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42791795730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19633197784424</t>
+    <t xml:space="preserve">4.42791748046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1963324546814</t>
   </si>
   <si>
     <t xml:space="preserve">4.16854190826416</t>
@@ -356,31 +356,31 @@
     <t xml:space="preserve">4.29822969436646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30749320983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27970314025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3908634185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40012788772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35380983352661</t>
+    <t xml:space="preserve">4.30749368667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27970266342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39086389541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40012693405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35381031036377</t>
   </si>
   <si>
     <t xml:space="preserve">4.08517122268677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93695616722107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00180006027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9740104675293</t>
+    <t xml:space="preserve">3.93695592880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00179958343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97400951385498</t>
   </si>
   <si>
     <t xml:space="preserve">4.03885412216187</t>
@@ -392,43 +392,43 @@
     <t xml:space="preserve">3.95548295974731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23338651657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22412252426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2426495552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11296129226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26117610931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91842937469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89990234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89063906669617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0759072303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06664419174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7980043888092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73316073417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86284804344177</t>
+    <t xml:space="preserve">4.23338603973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22412300109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24264907836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11296081542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26117563247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91842913627625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89990258216858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89063882827759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07590770721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06664371490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79800462722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73316049575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86284852027893</t>
   </si>
   <si>
     <t xml:space="preserve">3.71463394165039</t>
@@ -437,91 +437,91 @@
     <t xml:space="preserve">3.70537042617798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77021455764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3904139995575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44599437713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58494567871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68684363365173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60347294807434</t>
+    <t xml:space="preserve">3.77021503448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39041423797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44599461555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58494544029236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68684387207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60347270965576</t>
   </si>
   <si>
     <t xml:space="preserve">3.52010202407837</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37188720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46452140808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53862857818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52936553955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45525813102722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34409642219543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07545757293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14956521987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29778003692627</t>
+    <t xml:space="preserve">3.37188744544983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46452116966248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53862881660461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52936577796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4552583694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34409666061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07545733451843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14956474304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29777979850769</t>
   </si>
   <si>
     <t xml:space="preserve">3.31630659103394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23293542861938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24219870567322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02914023399353</t>
+    <t xml:space="preserve">3.23293566703796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2421989440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02913999557495</t>
   </si>
   <si>
     <t xml:space="preserve">3.20514535903931</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25146245956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10324716567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15882873535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91797947883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7419741153717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77902793884277</t>
+    <t xml:space="preserve">3.25146269798279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10324740409851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15882849693298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91797924041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74197435379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77902770042419</t>
   </si>
   <si>
     <t xml:space="preserve">2.87166213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9642961025238</t>
+    <t xml:space="preserve">2.96429634094238</t>
   </si>
   <si>
     <t xml:space="preserve">2.85313510894775</t>
@@ -530,10 +530,10 @@
     <t xml:space="preserve">2.83460855484009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84387159347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72344732284546</t>
+    <t xml:space="preserve">2.8438720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72344708442688</t>
   </si>
   <si>
     <t xml:space="preserve">2.76050090789795</t>
@@ -548,22 +548,22 @@
     <t xml:space="preserve">2.67713022232056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38070034980774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36217355728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29732966423035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31585645675659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35291028022766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26953959465027</t>
+    <t xml:space="preserve">2.38070058822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36217379570007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29732990264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31585669517517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35291051864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26953983306885</t>
   </si>
   <si>
     <t xml:space="preserve">2.23248553276062</t>
@@ -575,31 +575,31 @@
     <t xml:space="preserve">2.08427095413208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13058805465698</t>
+    <t xml:space="preserve">2.1305878162384</t>
   </si>
   <si>
     <t xml:space="preserve">2.22322249412537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24174904823303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11206126213074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17690491676331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0379536151886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99163675308228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88047552108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94531953334808</t>
+    <t xml:space="preserve">2.24174928665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11206150054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17690515518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03795385360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9916365146637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88047564029694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94531941413879</t>
   </si>
   <si>
     <t xml:space="preserve">1.92679262161255</t>
@@ -608,37 +608,37 @@
     <t xml:space="preserve">2.16764140129089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13985157012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21395897865295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40849041938782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48259806632996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42701768875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38996386528015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46583557128906</t>
+    <t xml:space="preserve">2.13985133171082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21395874023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40849089622498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48259782791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4270179271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38996362686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46583580970764</t>
   </si>
   <si>
     <t xml:space="preserve">2.50406575202942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65698599815369</t>
+    <t xml:space="preserve">2.65698552131653</t>
   </si>
   <si>
     <t xml:space="preserve">2.71433067321777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54229593276978</t>
+    <t xml:space="preserve">2.5422956943512</t>
   </si>
   <si>
     <t xml:space="preserve">2.58052587509155</t>
@@ -650,43 +650,43 @@
     <t xml:space="preserve">2.42760586738586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38937568664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48495054244995</t>
+    <t xml:space="preserve">2.38937616348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48495078086853</t>
   </si>
   <si>
     <t xml:space="preserve">2.61875581741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56141090393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6378710269928</t>
+    <t xml:space="preserve">2.56141066551208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63787078857422</t>
   </si>
   <si>
     <t xml:space="preserve">2.73344588279724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69521546363831</t>
+    <t xml:space="preserve">2.69521570205688</t>
   </si>
   <si>
     <t xml:space="preserve">2.75256085395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80990600585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82902073860168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84813594818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05840086936951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86725091934204</t>
+    <t xml:space="preserve">2.8099057674408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82902097702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84813570976257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05840110778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86725068092346</t>
   </si>
   <si>
     <t xml:space="preserve">2.77167582511902</t>
@@ -695,7 +695,7 @@
     <t xml:space="preserve">2.676100730896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59964084625244</t>
+    <t xml:space="preserve">2.59964060783386</t>
   </si>
   <si>
     <t xml:space="preserve">2.44672083854675</t>
@@ -704,10 +704,10 @@
     <t xml:space="preserve">2.37026071548462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09663105010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34512567520142</t>
+    <t xml:space="preserve">3.09663081169128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34512591362</t>
   </si>
   <si>
     <t xml:space="preserve">3.45981597900391</t>
@@ -722,13 +722,13 @@
     <t xml:space="preserve">4.01415157318115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1097264289856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9759213924408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88034629821777</t>
+    <t xml:space="preserve">4.10972595214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97592091560364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88034653663635</t>
   </si>
   <si>
     <t xml:space="preserve">3.82300138473511</t>
@@ -737,16 +737,16 @@
     <t xml:space="preserve">3.44070100784302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40247130393982</t>
+    <t xml:space="preserve">3.40247106552124</t>
   </si>
   <si>
     <t xml:space="preserve">3.36424088478088</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68919587135315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72742652893066</t>
+    <t xml:space="preserve">3.68919610977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72742629051208</t>
   </si>
   <si>
     <t xml:space="preserve">3.70831155776978</t>
@@ -761,25 +761,25 @@
     <t xml:space="preserve">3.51716113090515</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63185095787048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53627634048462</t>
+    <t xml:space="preserve">3.63185119628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53627610206604</t>
   </si>
   <si>
     <t xml:space="preserve">3.61273622512817</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65096592903137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24955129623413</t>
+    <t xml:space="preserve">3.65096616744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24955105781555</t>
   </si>
   <si>
     <t xml:space="preserve">3.32601118087769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42158627510071</t>
+    <t xml:space="preserve">3.42158603668213</t>
   </si>
   <si>
     <t xml:space="preserve">3.30689597129822</t>
@@ -788,22 +788,22 @@
     <t xml:space="preserve">3.38335633277893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59362125396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47893118858337</t>
+    <t xml:space="preserve">3.59362173080444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47893095016479</t>
   </si>
   <si>
     <t xml:space="preserve">3.49804639816284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28778100013733</t>
+    <t xml:space="preserve">3.28778123855591</t>
   </si>
   <si>
     <t xml:space="preserve">3.67008113861084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80388593673706</t>
+    <t xml:space="preserve">3.80388617515564</t>
   </si>
   <si>
     <t xml:space="preserve">3.93769145011902</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">4.18618631362915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30087661743164</t>
+    <t xml:space="preserve">4.30087614059448</t>
   </si>
   <si>
     <t xml:space="preserve">4.53025579452515</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">4.51114130020142</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58760166168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49202585220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43468189239502</t>
+    <t xml:space="preserve">4.58760213851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49202632904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43468141555786</t>
   </si>
   <si>
     <t xml:space="preserve">4.62583160400391</t>
@@ -839,16 +839,16 @@
     <t xml:space="preserve">4.74052143096924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75963640213013</t>
+    <t xml:space="preserve">4.75963592529297</t>
   </si>
   <si>
     <t xml:space="preserve">4.70229148864746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68317651748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77875137329102</t>
+    <t xml:space="preserve">4.68317699432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77875232696533</t>
   </si>
   <si>
     <t xml:space="preserve">4.56848669052124</t>
@@ -863,40 +863,40 @@
     <t xml:space="preserve">4.87432670593262</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9699010848999</t>
+    <t xml:space="preserve">4.96990156173706</t>
   </si>
   <si>
     <t xml:space="preserve">4.92211437225342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11326456069946</t>
+    <t xml:space="preserve">5.1132640838623</t>
   </si>
   <si>
     <t xml:space="preserve">5.16105175018311</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20883893966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25662660598755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30441427230835</t>
+    <t xml:space="preserve">5.20883941650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25662708282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30441474914551</t>
   </si>
   <si>
     <t xml:space="preserve">5.44777631759644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6389274597168</t>
+    <t xml:space="preserve">5.63892650604248</t>
   </si>
   <si>
     <t xml:space="preserve">5.59113883972168</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81332683563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71643829345703</t>
+    <t xml:space="preserve">5.81332635879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71643781661987</t>
   </si>
   <si>
     <t xml:space="preserve">5.42577171325684</t>
@@ -905,10 +905,10 @@
     <t xml:space="preserve">5.1351056098938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8444390296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82506132125854</t>
+    <t xml:space="preserve">4.84443950653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82506084442139</t>
   </si>
   <si>
     <t xml:space="preserve">4.80568313598633</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">4.59252738952637</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55377197265625</t>
+    <t xml:space="preserve">4.55377244949341</t>
   </si>
   <si>
     <t xml:space="preserve">4.76692771911621</t>
@@ -941,7 +941,7 @@
     <t xml:space="preserve">5.23199415206909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74755001068115</t>
+    <t xml:space="preserve">4.74755048751831</t>
   </si>
   <si>
     <t xml:space="preserve">5.2804388999939</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">5.91021490097046</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61954879760742</t>
+    <t xml:space="preserve">5.61954927444458</t>
   </si>
   <si>
     <t xml:space="preserve">5.32888317108154</t>
@@ -983,16 +983,16 @@
     <t xml:space="preserve">5.57110500335693</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47421550750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66799354553223</t>
+    <t xml:space="preserve">5.47421598434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66799306869507</t>
   </si>
   <si>
     <t xml:space="preserve">6.73376989364624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29777050018311</t>
+    <t xml:space="preserve">6.29777097702026</t>
   </si>
   <si>
     <t xml:space="preserve">6.4431037902832</t>
@@ -1010,16 +1010,16 @@
     <t xml:space="preserve">6.24932622909546</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34621477127075</t>
+    <t xml:space="preserve">6.34621524810791</t>
   </si>
   <si>
     <t xml:space="preserve">6.5399923324585</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3946590423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71999073028564</t>
+    <t xml:space="preserve">6.39465951919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71998977661133</t>
   </si>
   <si>
     <t xml:space="preserve">7.99332427978516</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">8.09021377563477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04176807403564</t>
+    <t xml:space="preserve">8.04176902770996</t>
   </si>
   <si>
     <t xml:space="preserve">7.94487953186035</t>
@@ -1037,10 +1037,10 @@
     <t xml:space="preserve">7.84799194335938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89643526077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38087940216064</t>
+    <t xml:space="preserve">7.89643573760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38087844848633</t>
   </si>
   <si>
     <t xml:space="preserve">10.2702112197876</t>
@@ -1058,10 +1058,10 @@
     <t xml:space="preserve">10.0764322280884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2390975952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6266536712646</t>
+    <t xml:space="preserve">11.2390985488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6266527175903</t>
   </si>
   <si>
     <t xml:space="preserve">13.079984664917</t>
@@ -1076,7 +1076,7 @@
     <t xml:space="preserve">14.436427116394</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3395395278931</t>
+    <t xml:space="preserve">14.3395385742188</t>
   </si>
   <si>
     <t xml:space="preserve">15.0177612304688</t>
@@ -57750,7 +57750,7 @@
     </row>
     <row r="2127">
       <c r="A2127" s="1" t="n">
-        <v>45988.6638541667</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B2127" t="n">
         <v>1000</v>
@@ -57771,6 +57771,32 @@
         <v>700</v>
       </c>
       <c r="H2127" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" s="1" t="n">
+        <v>45989.3352777778</v>
+      </c>
+      <c r="B2128" t="n">
+        <v>125</v>
+      </c>
+      <c r="C2128" t="n">
+        <v>13.8000001907349</v>
+      </c>
+      <c r="D2128" t="n">
+        <v>13.8000001907349</v>
+      </c>
+      <c r="E2128" t="n">
+        <v>13.8000001907349</v>
+      </c>
+      <c r="F2128" t="n">
+        <v>13.8000001907349</v>
+      </c>
+      <c r="G2128" t="s">
+        <v>662</v>
+      </c>
+      <c r="H2128" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CULT.MI.xlsx
+++ b/data/CULT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="707">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,52 +44,52 @@
     <t xml:space="preserve">CULT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57666778564453</t>
+    <t xml:space="preserve">4.57666730880737</t>
   </si>
   <si>
     <t xml:space="preserve">4.5948657989502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60851383209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58576631546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48931980133057</t>
+    <t xml:space="preserve">4.60851335525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58576583862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48931884765625</t>
   </si>
   <si>
     <t xml:space="preserve">4.56301927566528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5129771232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46020364761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29824638366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21271800994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18178224563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23091602325439</t>
+    <t xml:space="preserve">4.51297616958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46020412445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29824542999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21271848678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18178272247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23091506958008</t>
   </si>
   <si>
     <t xml:space="preserve">4.36375713348389</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38195419311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35101842880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28914737701416</t>
+    <t xml:space="preserve">4.38195466995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35101890563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28914785385132</t>
   </si>
   <si>
     <t xml:space="preserve">4.24183416366577</t>
@@ -107,28 +107,28 @@
     <t xml:space="preserve">4.10899209976196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9961678981781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04712104797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0398416519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96341300010681</t>
+    <t xml:space="preserve">3.99616765975952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04712057113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03984212875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96341228485107</t>
   </si>
   <si>
     <t xml:space="preserve">4.07441711425781</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32008361816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24911308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9797899723053</t>
+    <t xml:space="preserve">4.32008409500122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24911260604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97978973388672</t>
   </si>
   <si>
     <t xml:space="preserve">4.06895780563354</t>
@@ -137,40 +137,40 @@
     <t xml:space="preserve">4.0543999671936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98524928092957</t>
+    <t xml:space="preserve">3.98524951934814</t>
   </si>
   <si>
     <t xml:space="preserve">4.0507607460022</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07259654998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0380220413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04530143737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03074312210083</t>
+    <t xml:space="preserve">4.07259702682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03802299499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04530096054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03074216842651</t>
   </si>
   <si>
     <t xml:space="preserve">4.01254558563232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04894065856934</t>
+    <t xml:space="preserve">4.04894018173218</t>
   </si>
   <si>
     <t xml:space="preserve">4.05985879898071</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0762357711792</t>
+    <t xml:space="preserve">4.07623624801636</t>
   </si>
   <si>
     <t xml:space="preserve">3.91245913505554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99070858955383</t>
+    <t xml:space="preserve">3.99070930480957</t>
   </si>
   <si>
     <t xml:space="preserve">4.01072597503662</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">3.92155861854553</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00162649154663</t>
+    <t xml:space="preserve">4.00162696838379</t>
   </si>
   <si>
     <t xml:space="preserve">4.05803918838501</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">4.21635723114014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2218165397644</t>
+    <t xml:space="preserve">4.22181606292725</t>
   </si>
   <si>
     <t xml:space="preserve">4.18542146682739</t>
@@ -197,25 +197,25 @@
     <t xml:space="preserve">4.16176462173462</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35465860366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28186845779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26730966567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39287328720093</t>
+    <t xml:space="preserve">4.35465717315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28186798095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26731014251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39287376403809</t>
   </si>
   <si>
     <t xml:space="preserve">4.36739730834961</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17814302444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27458953857422</t>
+    <t xml:space="preserve">4.17814254760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27459001541138</t>
   </si>
   <si>
     <t xml:space="preserve">4.3182635307312</t>
@@ -227,31 +227,31 @@
     <t xml:space="preserve">4.26549053192139</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26367044448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27640867233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1490273475647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35829782485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35283946990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29460573196411</t>
+    <t xml:space="preserve">4.26367092132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27640914916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14902591705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35829830169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35283803939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29460668563843</t>
   </si>
   <si>
     <t xml:space="preserve">4.2036190032959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24001407623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3400993347168</t>
+    <t xml:space="preserve">4.24001359939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34010076522827</t>
   </si>
   <si>
     <t xml:space="preserve">4.42926788330078</t>
@@ -260,10 +260,10 @@
     <t xml:space="preserve">4.34919881820679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33646011352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33100175857544</t>
+    <t xml:space="preserve">4.33646106719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3310022354126</t>
   </si>
   <si>
     <t xml:space="preserve">4.32190227508545</t>
@@ -272,16 +272,16 @@
     <t xml:space="preserve">4.46748208999634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45838499069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28550815582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83057117462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90336036682129</t>
+    <t xml:space="preserve">4.45838403701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2855076789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83057069778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90336084365845</t>
   </si>
   <si>
     <t xml:space="preserve">3.88516330718994</t>
@@ -290,61 +290,61 @@
     <t xml:space="preserve">3.87606477737427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00344705581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93065667152405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99434781074524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08533573150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96705198287964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86696529388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84876799583435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85786652565002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81237316131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80327391624451</t>
+    <t xml:space="preserve">4.00344657897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93065690994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9943482875824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08533525466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96705150604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86696600914001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84876823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85786628723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81237292289734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80327463150024</t>
   </si>
   <si>
     <t xml:space="preserve">3.77597832679749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97615075111389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94885468482971</t>
+    <t xml:space="preserve">3.97615051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94885492324829</t>
   </si>
   <si>
     <t xml:space="preserve">4.13992834091187</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16722393035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33528280258179</t>
+    <t xml:space="preserve">4.16722440719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3352837562561</t>
   </si>
   <si>
     <t xml:space="preserve">4.21485948562622</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31675624847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42791748046875</t>
+    <t xml:space="preserve">4.31675672531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42791700363159</t>
   </si>
   <si>
     <t xml:space="preserve">4.1963324546814</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">4.29822969436646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30749368667603</t>
+    <t xml:space="preserve">4.30749225616455</t>
   </si>
   <si>
     <t xml:space="preserve">4.27970266342163</t>
@@ -365,37 +365,37 @@
     <t xml:space="preserve">4.39086389541626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40012693405151</t>
+    <t xml:space="preserve">4.40012741088867</t>
   </si>
   <si>
     <t xml:space="preserve">4.35381031036377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08517122268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93695592880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00179958343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97400951385498</t>
+    <t xml:space="preserve">4.08517074584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93695640563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00180006027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97400975227356</t>
   </si>
   <si>
     <t xml:space="preserve">4.03885412216187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94621992111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95548295974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23338603973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22412300109863</t>
+    <t xml:space="preserve">3.94622015953064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95548272132874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23338556289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22412204742432</t>
   </si>
   <si>
     <t xml:space="preserve">4.24264907836914</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">4.26117563247681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91842913627625</t>
+    <t xml:space="preserve">3.91842937469482</t>
   </si>
   <si>
     <t xml:space="preserve">3.89990258216858</t>
@@ -416,76 +416,76 @@
     <t xml:space="preserve">3.89063882827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07590770721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06664371490479</t>
+    <t xml:space="preserve">4.07590675354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06664419174194</t>
   </si>
   <si>
     <t xml:space="preserve">3.79800462722778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73316049575806</t>
+    <t xml:space="preserve">3.73316073417664</t>
   </si>
   <si>
     <t xml:space="preserve">3.86284852027893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71463394165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70537042617798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77021503448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39041423797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44599461555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58494544029236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68684387207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60347270965576</t>
+    <t xml:space="preserve">3.71463418006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7053701877594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77021455764771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3904139995575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44599437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58494567871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68684339523315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60347294807434</t>
   </si>
   <si>
     <t xml:space="preserve">3.52010202407837</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37188744544983</t>
+    <t xml:space="preserve">3.37188720703125</t>
   </si>
   <si>
     <t xml:space="preserve">3.46452116966248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53862881660461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52936577796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4552583694458</t>
+    <t xml:space="preserve">3.53862857818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5293653011322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45525765419006</t>
   </si>
   <si>
     <t xml:space="preserve">3.34409666061401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07545733451843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14956474304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29777979850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31630659103394</t>
+    <t xml:space="preserve">3.07545781135559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14956498146057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29777956008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31630635261536</t>
   </si>
   <si>
     <t xml:space="preserve">3.23293566703796</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">3.2421989440918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02913999557495</t>
+    <t xml:space="preserve">3.02914023399353</t>
   </si>
   <si>
     <t xml:space="preserve">3.20514535903931</t>
@@ -506,70 +506,70 @@
     <t xml:space="preserve">3.10324740409851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15882849693298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91797924041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74197435379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77902770042419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87166213989258</t>
+    <t xml:space="preserve">3.1588282585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9179790019989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7419741153717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77902793884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.871661901474</t>
   </si>
   <si>
     <t xml:space="preserve">2.96429634094238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85313510894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83460855484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8438720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72344708442688</t>
+    <t xml:space="preserve">2.85313534736633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83460831642151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84387183189392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72344732284546</t>
   </si>
   <si>
     <t xml:space="preserve">2.76050090789795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76976442337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63081288337708</t>
+    <t xml:space="preserve">2.76976418495178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63081312179565</t>
   </si>
   <si>
     <t xml:space="preserve">2.67713022232056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38070058822632</t>
+    <t xml:space="preserve">2.38070034980774</t>
   </si>
   <si>
     <t xml:space="preserve">2.36217379570007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29732990264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31585669517517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35291051864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26953983306885</t>
+    <t xml:space="preserve">2.29732942581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31585645675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35291004180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26953935623169</t>
   </si>
   <si>
     <t xml:space="preserve">2.23248553276062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28806638717651</t>
+    <t xml:space="preserve">2.28806591033936</t>
   </si>
   <si>
     <t xml:space="preserve">2.08427095413208</t>
@@ -578,52 +578,52 @@
     <t xml:space="preserve">2.1305878162384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22322249412537</t>
+    <t xml:space="preserve">2.22322225570679</t>
   </si>
   <si>
     <t xml:space="preserve">2.24174928665161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11206150054932</t>
+    <t xml:space="preserve">2.11206102371216</t>
   </si>
   <si>
     <t xml:space="preserve">2.17690515518188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03795385360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9916365146637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88047564029694</t>
+    <t xml:space="preserve">2.03795337677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99163663387299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88047552108765</t>
   </si>
   <si>
     <t xml:space="preserve">1.94531941413879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92679262161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16764140129089</t>
+    <t xml:space="preserve">1.92679274082184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16764187812805</t>
   </si>
   <si>
     <t xml:space="preserve">2.13985133171082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21395874023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40849089622498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48259782791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4270179271698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38996362686157</t>
+    <t xml:space="preserve">2.2139585018158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4084906578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48259806632996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42701745033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38996386528015</t>
   </si>
   <si>
     <t xml:space="preserve">2.46583580970764</t>
@@ -632,13 +632,13 @@
     <t xml:space="preserve">2.50406575202942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65698552131653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71433067321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5422956943512</t>
+    <t xml:space="preserve">2.65698599815369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71433091163635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54229593276978</t>
   </si>
   <si>
     <t xml:space="preserve">2.58052587509155</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">2.42760586738586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38937616348267</t>
+    <t xml:space="preserve">2.38937592506409</t>
   </si>
   <si>
     <t xml:space="preserve">2.48495078086853</t>
@@ -659,52 +659,52 @@
     <t xml:space="preserve">2.61875581741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56141066551208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63787078857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73344588279724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69521570205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75256085395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8099057674408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82902097702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84813570976257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05840110778809</t>
+    <t xml:space="preserve">2.56141114234924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63787126541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73344612121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69521594047546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75256109237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80990624427795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82902073860168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84813594818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05840086936951</t>
   </si>
   <si>
     <t xml:space="preserve">2.86725068092346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77167582511902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.676100730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59964060783386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44672083854675</t>
+    <t xml:space="preserve">2.77167630195618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67610120773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59964108467102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44672060012817</t>
   </si>
   <si>
     <t xml:space="preserve">2.37026071548462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09663081169128</t>
+    <t xml:space="preserve">3.09663057327271</t>
   </si>
   <si>
     <t xml:space="preserve">3.34512591362</t>
@@ -713,25 +713,25 @@
     <t xml:space="preserve">3.45981597900391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74654126167297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76565623283386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01415157318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10972595214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97592091560364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88034653663635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82300138473511</t>
+    <t xml:space="preserve">3.74654150009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76565647125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01415109634399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1097264289856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97592115402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88034629821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82300114631653</t>
   </si>
   <si>
     <t xml:space="preserve">3.44070100784302</t>
@@ -746,10 +746,10 @@
     <t xml:space="preserve">3.68919610977173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72742629051208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70831155776978</t>
+    <t xml:space="preserve">3.72742652893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7083113193512</t>
   </si>
   <si>
     <t xml:space="preserve">3.57450604438782</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">3.53627610206604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61273622512817</t>
+    <t xml:space="preserve">3.61273646354675</t>
   </si>
   <si>
     <t xml:space="preserve">3.65096616744995</t>
@@ -776,34 +776,34 @@
     <t xml:space="preserve">3.24955105781555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32601118087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42158603668213</t>
+    <t xml:space="preserve">3.32601094245911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42158579826355</t>
   </si>
   <si>
     <t xml:space="preserve">3.30689597129822</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38335633277893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59362173080444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47893095016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49804639816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28778123855591</t>
+    <t xml:space="preserve">3.38335585594177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59362125396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47893118858337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49804615974426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28778100013733</t>
   </si>
   <si>
     <t xml:space="preserve">3.67008113861084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80388617515564</t>
+    <t xml:space="preserve">3.80388641357422</t>
   </si>
   <si>
     <t xml:space="preserve">3.93769145011902</t>
@@ -812,16 +812,16 @@
     <t xml:space="preserve">4.03326606750488</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18618631362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30087614059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53025579452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51114130020142</t>
+    <t xml:space="preserve">4.18618679046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30087661743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5302562713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51114177703857</t>
   </si>
   <si>
     <t xml:space="preserve">4.58760213851929</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">4.43468141555786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62583160400391</t>
+    <t xml:space="preserve">4.62583208084106</t>
   </si>
   <si>
     <t xml:space="preserve">4.74052143096924</t>
@@ -842,22 +842,22 @@
     <t xml:space="preserve">4.75963592529297</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70229148864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68317699432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77875232696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56848669052124</t>
+    <t xml:space="preserve">4.70229196548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68317604064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77875185012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56848573684692</t>
   </si>
   <si>
     <t xml:space="preserve">4.66406202316284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72140693664551</t>
+    <t xml:space="preserve">4.72140550613403</t>
   </si>
   <si>
     <t xml:space="preserve">4.87432670593262</t>
@@ -875,25 +875,25 @@
     <t xml:space="preserve">5.16105175018311</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20883941650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25662708282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30441474914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44777631759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63892650604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59113883972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81332635879517</t>
+    <t xml:space="preserve">5.20883893966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25662612915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30441427230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44777679443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63892698287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59113931655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81332683563232</t>
   </si>
   <si>
     <t xml:space="preserve">5.71643781661987</t>
@@ -902,10 +902,10 @@
     <t xml:space="preserve">5.42577171325684</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1351056098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84443950653076</t>
+    <t xml:space="preserve">5.13510513305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84443855285645</t>
   </si>
   <si>
     <t xml:space="preserve">4.82506084442139</t>
@@ -914,22 +914,22 @@
     <t xml:space="preserve">4.80568313598633</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59252738952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55377244949341</t>
+    <t xml:space="preserve">4.59252786636353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55377292633057</t>
   </si>
   <si>
     <t xml:space="preserve">4.76692771911621</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03821611404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9897723197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08666086196899</t>
+    <t xml:space="preserve">5.03821563720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98977184295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08666038513184</t>
   </si>
   <si>
     <t xml:space="preserve">5.18354940414429</t>
@@ -938,28 +938,28 @@
     <t xml:space="preserve">4.9413275718689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23199415206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74755048751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2804388999939</t>
+    <t xml:space="preserve">5.23199367523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74754953384399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28043794631958</t>
   </si>
   <si>
     <t xml:space="preserve">4.89288330078125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63128423690796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53439474105835</t>
+    <t xml:space="preserve">4.6312837600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53439521789551</t>
   </si>
   <si>
     <t xml:space="preserve">4.67003917694092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78630590438843</t>
+    <t xml:space="preserve">4.78630495071411</t>
   </si>
   <si>
     <t xml:space="preserve">4.72817277908325</t>
@@ -968,28 +968,28 @@
     <t xml:space="preserve">4.70879459381104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91021490097046</t>
+    <t xml:space="preserve">5.91021537780762</t>
   </si>
   <si>
     <t xml:space="preserve">5.61954927444458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32888317108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37732791900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57110500335693</t>
+    <t xml:space="preserve">5.32888221740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37732744216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57110452651978</t>
   </si>
   <si>
     <t xml:space="preserve">5.47421598434448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66799306869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73376989364624</t>
+    <t xml:space="preserve">5.66799354553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73376941680908</t>
   </si>
   <si>
     <t xml:space="preserve">6.29777097702026</t>
@@ -1004,25 +1004,25 @@
     <t xml:space="preserve">6.5884370803833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63688087463379</t>
+    <t xml:space="preserve">6.63688135147095</t>
   </si>
   <si>
     <t xml:space="preserve">6.24932622909546</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34621524810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5399923324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39465951919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71998977661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99332427978516</t>
+    <t xml:space="preserve">6.34621572494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53999280929565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39465999603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71999073028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.993323802948</t>
   </si>
   <si>
     <t xml:space="preserve">8.09021377563477</t>
@@ -1031,52 +1031,52 @@
     <t xml:space="preserve">8.04176902770996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94487953186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84799194335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89643573760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38087844848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2702112197876</t>
+    <t xml:space="preserve">7.94488000869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84799146652222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89643430709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38087940216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2702102661133</t>
   </si>
   <si>
     <t xml:space="preserve">9.88265514373779</t>
   </si>
   <si>
-    <t xml:space="preserve">10.173321723938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9795446395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0764322280884</t>
+    <t xml:space="preserve">10.1733207702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97954368591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0764312744141</t>
   </si>
   <si>
     <t xml:space="preserve">11.2390985488892</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6266527175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.079984664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2737617492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9830951690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.436427116394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3395385742188</t>
+    <t xml:space="preserve">11.6266536712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0799856185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2737627029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9830961227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4364280700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3395395278931</t>
   </si>
   <si>
     <t xml:space="preserve">15.0177612304688</t>
@@ -1088,49 +1088,49 @@
     <t xml:space="preserve">15.1930656433105</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0956735610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9008913040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6348009109497</t>
+    <t xml:space="preserve">15.0956745147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9008903503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.634801864624</t>
   </si>
   <si>
     <t xml:space="preserve">12.0765390396118</t>
   </si>
   <si>
-    <t xml:space="preserve">12.466103553772</t>
+    <t xml:space="preserve">12.4661054611206</t>
   </si>
   <si>
     <t xml:space="preserve">13.4400196075439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9269771575928</t>
+    <t xml:space="preserve">13.9269762039185</t>
   </si>
   <si>
     <t xml:space="preserve">14.0243673324585</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2191514968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8034992218018</t>
+    <t xml:space="preserve">14.2191524505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8035001754761</t>
   </si>
   <si>
     <t xml:space="preserve">14.4139337539673</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6087169647217</t>
+    <t xml:space="preserve">14.6087160110474</t>
   </si>
   <si>
     <t xml:space="preserve">14.7061080932617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5113248825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3426265716553</t>
+    <t xml:space="preserve">14.5113258361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3426275253296</t>
   </si>
   <si>
     <t xml:space="preserve">14.1217594146729</t>
@@ -1145,31 +1145,31 @@
     <t xml:space="preserve">13.537410736084</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2452363967896</t>
+    <t xml:space="preserve">13.2452373504639</t>
   </si>
   <si>
     <t xml:space="preserve">12.8556699752808</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3687133789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7582788467407</t>
+    <t xml:space="preserve">12.3687143325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7582807540894</t>
   </si>
   <si>
     <t xml:space="preserve">12.5634956359863</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1739292144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6869735717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1026239395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93392753601074</t>
+    <t xml:space="preserve">12.1739311218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.686972618103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1026248931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93392658233643</t>
   </si>
   <si>
     <t xml:space="preserve">10.7130584716797</t>
@@ -1178,22 +1178,22 @@
     <t xml:space="preserve">11.2000160217285</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9791479110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8817548751831</t>
+    <t xml:space="preserve">11.9791469573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8817567825317</t>
   </si>
   <si>
     <t xml:space="preserve">10.9078416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2974071502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3947982788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5895805358887</t>
+    <t xml:space="preserve">11.2974061965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3947992324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.589581489563</t>
   </si>
   <si>
     <t xml:space="preserve">11.0052318572998</t>
@@ -1205,16 +1205,16 @@
     <t xml:space="preserve">11.4921903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8104515075684</t>
+    <t xml:space="preserve">10.810450553894</t>
   </si>
   <si>
     <t xml:space="preserve">10.4208841323853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2261018753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3234939575195</t>
+    <t xml:space="preserve">10.2261009216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3234930038452</t>
   </si>
   <si>
     <t xml:space="preserve">10.1287097930908</t>
@@ -1223,19 +1223,19 @@
     <t xml:space="preserve">10.0313196182251</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73914527893066</t>
+    <t xml:space="preserve">9.73914432525635</t>
   </si>
   <si>
     <t xml:space="preserve">9.54436111450195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8365364074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34957981109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49566555023193</t>
+    <t xml:space="preserve">9.83653545379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34957885742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49566650390625</t>
   </si>
   <si>
     <t xml:space="preserve">12.2713222503662</t>
@@ -1247,13 +1247,13 @@
     <t xml:space="preserve">15.6800231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7321939468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1704559326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3652372360229</t>
+    <t xml:space="preserve">13.7321949005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1704549789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3652381896973</t>
   </si>
   <si>
     <t xml:space="preserve">14.0730628967285</t>
@@ -1262,19 +1262,19 @@
     <t xml:space="preserve">15.1443691253662</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5364570617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.585467338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6344776153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.193380355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4874458312988</t>
+    <t xml:space="preserve">15.5364561080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5854682922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6344785690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1933813095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4874448776245</t>
   </si>
   <si>
     <t xml:space="preserve">15.4384346008301</t>
@@ -1307,22 +1307,22 @@
     <t xml:space="preserve">13.7230529785156</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8210754394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3601942062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6250314712524</t>
+    <t xml:space="preserve">13.8210763931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3601951599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6250305175781</t>
   </si>
   <si>
     <t xml:space="preserve">13.8700857162476</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6740427017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7720642089844</t>
+    <t xml:space="preserve">13.6740417480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7720651626587</t>
   </si>
   <si>
     <t xml:space="preserve">14.0171184539795</t>
@@ -1343,13 +1343,13 @@
     <t xml:space="preserve">14.8503036499023</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7522830963135</t>
+    <t xml:space="preserve">14.7522821426392</t>
   </si>
   <si>
     <t xml:space="preserve">14.6052494049072</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7032718658447</t>
+    <t xml:space="preserve">14.7032709121704</t>
   </si>
   <si>
     <t xml:space="preserve">14.5562391281128</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">14.0661296844482</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3309669494629</t>
+    <t xml:space="preserve">13.3309659957886</t>
   </si>
   <si>
     <t xml:space="preserve">13.4779987335205</t>
@@ -1373,10 +1373,10 @@
     <t xml:space="preserve">12.8898668289185</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7428340911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9878902435303</t>
+    <t xml:space="preserve">12.7428350448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.987889289856</t>
   </si>
   <si>
     <t xml:space="preserve">13.1349229812622</t>
@@ -1385,16 +1385,16 @@
     <t xml:space="preserve">12.3507480621338</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7626171112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3215188980103</t>
+    <t xml:space="preserve">11.7626161575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3215198516846</t>
   </si>
   <si>
     <t xml:space="preserve">12.3017377853394</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0859127044678</t>
+    <t xml:space="preserve">13.0859117507935</t>
   </si>
   <si>
     <t xml:space="preserve">13.4289875030518</t>
@@ -1403,19 +1403,19 @@
     <t xml:space="preserve">15.8305215835571</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7324991226196</t>
+    <t xml:space="preserve">15.7325000762939</t>
   </si>
   <si>
     <t xml:space="preserve">15.8795328140259</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9775533676147</t>
+    <t xml:space="preserve">15.9775543212891</t>
   </si>
   <si>
     <t xml:space="preserve">16.3696422576904</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6834888458252</t>
+    <t xml:space="preserve">15.6834897994995</t>
   </si>
   <si>
     <t xml:space="preserve">15.7815113067627</t>
@@ -1430,7 +1430,7 @@
     <t xml:space="preserve">16.0755767822266</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9285440444946</t>
+    <t xml:space="preserve">15.9285449981689</t>
   </si>
   <si>
     <t xml:space="preserve">16.1735973358154</t>
@@ -1445,28 +1445,28 @@
     <t xml:space="preserve">18.7221660614014</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0162296295166</t>
+    <t xml:space="preserve">19.0162315368652</t>
   </si>
   <si>
     <t xml:space="preserve">19.7023830413818</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6043605804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.800407409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0944709777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9173202514648</t>
+    <t xml:space="preserve">19.604362487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8004055023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0944690704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9173221588135</t>
   </si>
   <si>
     <t xml:space="preserve">22.545015335083</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5252342224121</t>
+    <t xml:space="preserve">23.5252323150635</t>
   </si>
   <si>
     <t xml:space="preserve">24.7995166778564</t>
@@ -1475,7 +1475,7 @@
     <t xml:space="preserve">23.2311706542969</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7806243896484</t>
+    <t xml:space="preserve">20.7806224822998</t>
   </si>
   <si>
     <t xml:space="preserve">21.1727104187012</t>
@@ -1490,13 +1490,13 @@
     <t xml:space="preserve">21.3687534332275</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6430377960205</t>
+    <t xml:space="preserve">22.6430397033691</t>
   </si>
   <si>
     <t xml:space="preserve">24.9955596923828</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2896251678467</t>
+    <t xml:space="preserve">25.2896270751953</t>
   </si>
   <si>
     <t xml:space="preserve">24.6034755706787</t>
@@ -1505,13 +1505,13 @@
     <t xml:space="preserve">24.8975391387939</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5054531097412</t>
+    <t xml:space="preserve">24.5054512023926</t>
   </si>
   <si>
     <t xml:space="preserve">24.015344619751</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6232566833496</t>
+    <t xml:space="preserve">23.623254776001</t>
   </si>
   <si>
     <t xml:space="preserve">22.8390808105469</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">23.3291893005371</t>
   </si>
   <si>
-    <t xml:space="preserve">22.937105178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7212791442871</t>
+    <t xml:space="preserve">22.9371032714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7212772369385</t>
   </si>
   <si>
     <t xml:space="preserve">24.1133651733398</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0351257324219</t>
+    <t xml:space="preserve">23.0351238250732</t>
   </si>
   <si>
     <t xml:space="preserve">23.1331481933594</t>
@@ -1541,13 +1541,13 @@
     <t xml:space="preserve">24.4074287414551</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8192977905273</t>
+    <t xml:space="preserve">23.819299697876</t>
   </si>
   <si>
     <t xml:space="preserve">22.2509498596191</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7608413696289</t>
+    <t xml:space="preserve">21.7608432769775</t>
   </si>
   <si>
     <t xml:space="preserve">21.9568843841553</t>
@@ -1562,22 +1562,22 @@
     <t xml:space="preserve">18.330078125</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6439266204834</t>
+    <t xml:space="preserve">17.6439247131348</t>
   </si>
   <si>
     <t xml:space="preserve">18.5261211395264</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9964485168457</t>
+    <t xml:space="preserve">19.9964466094971</t>
   </si>
   <si>
     <t xml:space="preserve">20.5845794677734</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1924934387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8984279632568</t>
+    <t xml:space="preserve">20.1924953460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8984260559082</t>
   </si>
   <si>
     <t xml:space="preserve">20.3885364532471</t>
@@ -1632,9 +1632,6 @@
   </si>
   <si>
     <t xml:space="preserve">19.9959678649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0944690704346</t>
   </si>
   <si>
     <t xml:space="preserve">19.4542045593262</t>
@@ -41440,7 +41437,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1499" t="s">
-        <v>540</v>
+        <v>481</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41492,7 +41489,7 @@
         <v>19.75</v>
       </c>
       <c r="G1501" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41596,7 +41593,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1505" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41622,7 +41619,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1506" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41674,7 +41671,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1508" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41700,7 +41697,7 @@
         <v>19.5</v>
       </c>
       <c r="G1509" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41726,7 +41723,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1510" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41752,7 +41749,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1511" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41778,7 +41775,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1512" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41804,7 +41801,7 @@
         <v>19.5</v>
       </c>
       <c r="G1513" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41830,7 +41827,7 @@
         <v>19.5</v>
       </c>
       <c r="G1514" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41856,7 +41853,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1515" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41882,7 +41879,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1516" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41908,7 +41905,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1517" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -41934,7 +41931,7 @@
         <v>18.75</v>
       </c>
       <c r="G1518" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -41960,7 +41957,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1519" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41986,7 +41983,7 @@
         <v>17.5</v>
       </c>
       <c r="G1520" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42012,7 +42009,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1521" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42038,7 +42035,7 @@
         <v>18.25</v>
       </c>
       <c r="G1522" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42064,7 +42061,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1523" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42090,7 +42087,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1524" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42116,7 +42113,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1525" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42142,7 +42139,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1526" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42168,7 +42165,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1527" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42194,7 +42191,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1528" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42220,7 +42217,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1529" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42350,7 +42347,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1534" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42376,7 +42373,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1535" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42428,7 +42425,7 @@
         <v>20</v>
       </c>
       <c r="G1537" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42506,7 +42503,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1540" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42532,7 +42529,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1541" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42558,7 +42555,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1542" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42610,7 +42607,7 @@
         <v>19.5</v>
       </c>
       <c r="G1544" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42636,7 +42633,7 @@
         <v>19.5</v>
       </c>
       <c r="G1545" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42714,7 +42711,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1548" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42740,7 +42737,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G1549" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42870,7 +42867,7 @@
         <v>19.5</v>
       </c>
       <c r="G1554" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42896,7 +42893,7 @@
         <v>19.5</v>
       </c>
       <c r="G1555" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42922,7 +42919,7 @@
         <v>19.5</v>
       </c>
       <c r="G1556" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42974,7 +42971,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1558" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43000,7 +42997,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1559" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43026,7 +43023,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1560" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43052,7 +43049,7 @@
         <v>19</v>
       </c>
       <c r="G1561" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43078,7 +43075,7 @@
         <v>19</v>
       </c>
       <c r="G1562" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43104,7 +43101,7 @@
         <v>19</v>
       </c>
       <c r="G1563" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43130,7 +43127,7 @@
         <v>19</v>
       </c>
       <c r="G1564" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43156,7 +43153,7 @@
         <v>19</v>
       </c>
       <c r="G1565" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43182,7 +43179,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1566" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43208,7 +43205,7 @@
         <v>19</v>
       </c>
       <c r="G1567" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43234,7 +43231,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1568" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43260,7 +43257,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1569" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43286,7 +43283,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1570" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43312,7 +43309,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1571" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -43338,7 +43335,7 @@
         <v>19</v>
       </c>
       <c r="G1572" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43364,7 +43361,7 @@
         <v>19</v>
       </c>
       <c r="G1573" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43390,7 +43387,7 @@
         <v>19</v>
       </c>
       <c r="G1574" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43416,7 +43413,7 @@
         <v>18.75</v>
       </c>
       <c r="G1575" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43442,7 +43439,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1576" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43468,7 +43465,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1577" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43494,7 +43491,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1578" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43520,7 +43517,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1579" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43546,7 +43543,7 @@
         <v>19</v>
       </c>
       <c r="G1580" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43572,7 +43569,7 @@
         <v>19</v>
       </c>
       <c r="G1581" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43598,7 +43595,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1582" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43624,7 +43621,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1583" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43650,7 +43647,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1584" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43676,7 +43673,7 @@
         <v>18.75</v>
       </c>
       <c r="G1585" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43702,7 +43699,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1586" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43728,7 +43725,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1587" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43754,7 +43751,7 @@
         <v>18.5</v>
       </c>
       <c r="G1588" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43780,7 +43777,7 @@
         <v>18.5</v>
       </c>
       <c r="G1589" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43806,7 +43803,7 @@
         <v>18.5</v>
       </c>
       <c r="G1590" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43832,7 +43829,7 @@
         <v>18.5</v>
       </c>
       <c r="G1591" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43858,7 +43855,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1592" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43884,7 +43881,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1593" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43910,7 +43907,7 @@
         <v>18</v>
       </c>
       <c r="G1594" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43936,7 +43933,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1595" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -43962,7 +43959,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1596" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43988,7 +43985,7 @@
         <v>18.5</v>
       </c>
       <c r="G1597" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44014,7 +44011,7 @@
         <v>18.5</v>
       </c>
       <c r="G1598" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44040,7 +44037,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1599" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44066,7 +44063,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1600" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44092,7 +44089,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1601" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44118,7 +44115,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1602" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44144,7 +44141,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1603" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44170,7 +44167,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1604" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44196,7 +44193,7 @@
         <v>18.25</v>
       </c>
       <c r="G1605" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44222,7 +44219,7 @@
         <v>18</v>
       </c>
       <c r="G1606" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -44248,7 +44245,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1607" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -44274,7 +44271,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1608" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -44300,7 +44297,7 @@
         <v>18</v>
       </c>
       <c r="G1609" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44326,7 +44323,7 @@
         <v>18.25</v>
       </c>
       <c r="G1610" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -44352,7 +44349,7 @@
         <v>18.25</v>
       </c>
       <c r="G1611" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44378,7 +44375,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1612" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44404,7 +44401,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1613" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44430,7 +44427,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1614" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44456,7 +44453,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1615" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44482,7 +44479,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1616" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44508,7 +44505,7 @@
         <v>18</v>
       </c>
       <c r="G1617" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44534,7 +44531,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1618" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44560,7 +44557,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1619" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44586,7 +44583,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1620" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44612,7 +44609,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1621" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44638,7 +44635,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1622" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44664,7 +44661,7 @@
         <v>18</v>
       </c>
       <c r="G1623" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44690,7 +44687,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1624" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44716,7 +44713,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1625" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44742,7 +44739,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1626" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44768,7 +44765,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1627" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44794,7 +44791,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1628" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44820,7 +44817,7 @@
         <v>18.25</v>
       </c>
       <c r="G1629" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44846,7 +44843,7 @@
         <v>18.25</v>
       </c>
       <c r="G1630" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44872,7 +44869,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1631" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44898,7 +44895,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1632" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44924,7 +44921,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1633" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44950,7 +44947,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1634" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44976,7 +44973,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1635" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45002,7 +44999,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1636" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45028,7 +45025,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1637" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45054,7 +45051,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1638" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45080,7 +45077,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1639" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45106,7 +45103,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1640" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45132,7 +45129,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1641" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -45158,7 +45155,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1642" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45184,7 +45181,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1643" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45210,7 +45207,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1644" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -45236,7 +45233,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1645" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -45262,7 +45259,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1646" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -45288,7 +45285,7 @@
         <v>18</v>
       </c>
       <c r="G1647" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -45314,7 +45311,7 @@
         <v>18.25</v>
       </c>
       <c r="G1648" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -45340,7 +45337,7 @@
         <v>18.25</v>
       </c>
       <c r="G1649" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -45366,7 +45363,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1650" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45392,7 +45389,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1651" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -45418,7 +45415,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1652" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45444,7 +45441,7 @@
         <v>18</v>
       </c>
       <c r="G1653" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45470,7 +45467,7 @@
         <v>18</v>
       </c>
       <c r="G1654" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45496,7 +45493,7 @@
         <v>18</v>
       </c>
       <c r="G1655" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45522,7 +45519,7 @@
         <v>18</v>
       </c>
       <c r="G1656" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45548,7 +45545,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1657" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45574,7 +45571,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1658" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45600,7 +45597,7 @@
         <v>17.75</v>
       </c>
       <c r="G1659" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45626,7 +45623,7 @@
         <v>18</v>
       </c>
       <c r="G1660" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45652,7 +45649,7 @@
         <v>18</v>
       </c>
       <c r="G1661" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45678,7 +45675,7 @@
         <v>18</v>
       </c>
       <c r="G1662" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45704,7 +45701,7 @@
         <v>18</v>
       </c>
       <c r="G1663" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45730,7 +45727,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1664" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45756,7 +45753,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1665" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45782,7 +45779,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1666" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45808,7 +45805,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1667" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45834,7 +45831,7 @@
         <v>17.5</v>
       </c>
       <c r="G1668" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45860,7 +45857,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1669" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45886,7 +45883,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1670" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45912,7 +45909,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1671" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45938,7 +45935,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1672" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45964,7 +45961,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1673" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45990,7 +45987,7 @@
         <v>16.75</v>
       </c>
       <c r="G1674" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -46016,7 +46013,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1675" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -46042,7 +46039,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1676" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -46068,7 +46065,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1677" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -46094,7 +46091,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1678" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -46120,7 +46117,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1679" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -46146,7 +46143,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1680" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -46172,7 +46169,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1681" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -46198,7 +46195,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1682" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -46224,7 +46221,7 @@
         <v>17</v>
       </c>
       <c r="G1683" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -46250,7 +46247,7 @@
         <v>17</v>
       </c>
       <c r="G1684" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -46276,7 +46273,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1685" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -46302,7 +46299,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1686" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -46328,7 +46325,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1687" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -46354,7 +46351,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46380,7 +46377,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1689" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -46406,7 +46403,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1690" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -46432,7 +46429,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1691" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46458,7 +46455,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1692" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46484,7 +46481,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1693" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -46510,7 +46507,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46536,7 +46533,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1695" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46562,7 +46559,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1696" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46588,7 +46585,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1697" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46614,7 +46611,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1698" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46640,7 +46637,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1699" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46666,7 +46663,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1700" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46692,7 +46689,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1701" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46718,7 +46715,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1702" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46744,7 +46741,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1703" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46770,7 +46767,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1704" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46796,7 +46793,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1705" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46822,7 +46819,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1706" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46848,7 +46845,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1707" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46874,7 +46871,7 @@
         <v>15</v>
       </c>
       <c r="G1708" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46900,7 +46897,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1709" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46926,7 +46923,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1710" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46952,7 +46949,7 @@
         <v>14.5</v>
       </c>
       <c r="G1711" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46978,7 +46975,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1712" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -47004,7 +47001,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1713" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47030,7 +47027,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1714" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -47056,7 +47053,7 @@
         <v>15</v>
       </c>
       <c r="G1715" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -47082,7 +47079,7 @@
         <v>15</v>
       </c>
       <c r="G1716" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47108,7 +47105,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1717" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -47134,7 +47131,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1718" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -47160,7 +47157,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -47186,7 +47183,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1720" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -47212,7 +47209,7 @@
         <v>14.25</v>
       </c>
       <c r="G1721" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -47238,7 +47235,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1722" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -47264,7 +47261,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1723" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -47290,7 +47287,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1724" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -47316,7 +47313,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1725" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -47342,7 +47339,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1726" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47368,7 +47365,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1727" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47394,7 +47391,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1728" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -47420,7 +47417,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1729" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47446,7 +47443,7 @@
         <v>14.75</v>
       </c>
       <c r="G1730" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47472,7 +47469,7 @@
         <v>14.75</v>
       </c>
       <c r="G1731" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47498,7 +47495,7 @@
         <v>14.75</v>
       </c>
       <c r="G1732" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47524,7 +47521,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1733" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47550,7 +47547,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1734" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47576,7 +47573,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1735" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47602,7 +47599,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1736" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47628,7 +47625,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1737" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47654,7 +47651,7 @@
         <v>13.25</v>
       </c>
       <c r="G1738" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47680,7 +47677,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1739" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47706,7 +47703,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1740" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47732,7 +47729,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1741" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47758,7 +47755,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1742" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47784,7 +47781,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1743" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47810,7 +47807,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1744" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47836,7 +47833,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1745" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47862,7 +47859,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1746" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47888,7 +47885,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1747" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47914,7 +47911,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1748" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47940,7 +47937,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1749" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47966,7 +47963,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1750" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47992,7 +47989,7 @@
         <v>12.75</v>
       </c>
       <c r="G1751" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -48018,7 +48015,7 @@
         <v>12.5</v>
       </c>
       <c r="G1752" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -48044,7 +48041,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1753" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -48070,7 +48067,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1754" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -48096,7 +48093,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1755" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -48122,7 +48119,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1756" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -48148,7 +48145,7 @@
         <v>12.25</v>
       </c>
       <c r="G1757" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -48174,7 +48171,7 @@
         <v>12.25</v>
       </c>
       <c r="G1758" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -48200,7 +48197,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1759" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -48226,7 +48223,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1760" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -48252,7 +48249,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1761" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -48278,7 +48275,7 @@
         <v>12.75</v>
       </c>
       <c r="G1762" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -48304,7 +48301,7 @@
         <v>12.75</v>
       </c>
       <c r="G1763" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -48330,7 +48327,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1764" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -48356,7 +48353,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1765" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48382,7 +48379,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1766" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48408,7 +48405,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1767" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48434,7 +48431,7 @@
         <v>12.5</v>
       </c>
       <c r="G1768" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48460,7 +48457,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1769" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48486,7 +48483,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1770" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48512,7 +48509,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1771" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48538,7 +48535,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1772" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48564,7 +48561,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1773" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48590,7 +48587,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1774" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48616,7 +48613,7 @@
         <v>12.75</v>
       </c>
       <c r="G1775" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48642,7 +48639,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1776" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48668,7 +48665,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1777" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48694,7 +48691,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1778" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48720,7 +48717,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1779" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48746,7 +48743,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1780" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48772,7 +48769,7 @@
         <v>13</v>
       </c>
       <c r="G1781" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48798,7 +48795,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1782" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48824,7 +48821,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1783" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48850,7 +48847,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1784" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48876,7 +48873,7 @@
         <v>12.75</v>
       </c>
       <c r="G1785" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48902,7 +48899,7 @@
         <v>12.75</v>
       </c>
       <c r="G1786" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48928,7 +48925,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48954,7 +48951,7 @@
         <v>12.5</v>
       </c>
       <c r="G1788" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48980,7 +48977,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1789" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -49006,7 +49003,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1790" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -49032,7 +49029,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1791" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -49058,7 +49055,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1792" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -49084,7 +49081,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1793" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -49110,7 +49107,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1794" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -49136,7 +49133,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1795" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -49162,7 +49159,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1796" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -49188,7 +49185,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1797" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -49214,7 +49211,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1798" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -49240,7 +49237,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1799" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -49266,7 +49263,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1800" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -49292,7 +49289,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1801" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -49318,7 +49315,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1802" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -49344,7 +49341,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1803" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49370,7 +49367,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1804" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49396,7 +49393,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1805" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49422,7 +49419,7 @@
         <v>12.75</v>
       </c>
       <c r="G1806" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49448,7 +49445,7 @@
         <v>12.75</v>
       </c>
       <c r="G1807" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49474,7 +49471,7 @@
         <v>12.75</v>
       </c>
       <c r="G1808" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49500,7 +49497,7 @@
         <v>12.75</v>
       </c>
       <c r="G1809" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49526,7 +49523,7 @@
         <v>12.75</v>
       </c>
       <c r="G1810" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49552,7 +49549,7 @@
         <v>12.75</v>
       </c>
       <c r="G1811" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49578,7 +49575,7 @@
         <v>12.75</v>
       </c>
       <c r="G1812" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49604,7 +49601,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1813" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49630,7 +49627,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1814" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49656,7 +49653,7 @@
         <v>12.75</v>
       </c>
       <c r="G1815" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49682,7 +49679,7 @@
         <v>12.75</v>
       </c>
       <c r="G1816" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49708,7 +49705,7 @@
         <v>12.75</v>
       </c>
       <c r="G1817" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49734,7 +49731,7 @@
         <v>12.75</v>
       </c>
       <c r="G1818" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49760,7 +49757,7 @@
         <v>12.75</v>
       </c>
       <c r="G1819" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49786,7 +49783,7 @@
         <v>12.75</v>
       </c>
       <c r="G1820" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49812,7 +49809,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1821" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49838,7 +49835,7 @@
         <v>12.5</v>
       </c>
       <c r="G1822" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49864,7 +49861,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1823" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49890,7 +49887,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1824" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49916,7 +49913,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1825" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49942,7 +49939,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1826" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49968,7 +49965,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1827" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49994,7 +49991,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1828" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -50020,7 +50017,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1829" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -50046,7 +50043,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1830" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -50072,7 +50069,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1831" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -50098,7 +50095,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1832" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -50124,7 +50121,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1833" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -50150,7 +50147,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1834" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -50176,7 +50173,7 @@
         <v>12.5</v>
       </c>
       <c r="G1835" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -50202,7 +50199,7 @@
         <v>12.5</v>
       </c>
       <c r="G1836" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -50228,7 +50225,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1837" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -50254,7 +50251,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1838" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -50280,7 +50277,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1839" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -50306,7 +50303,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -50332,7 +50329,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1841" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50358,7 +50355,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1842" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50384,7 +50381,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1843" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50410,7 +50407,7 @@
         <v>12.75</v>
       </c>
       <c r="G1844" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50436,7 +50433,7 @@
         <v>12.75</v>
       </c>
       <c r="G1845" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50462,7 +50459,7 @@
         <v>12.75</v>
       </c>
       <c r="G1846" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50488,7 +50485,7 @@
         <v>12.75</v>
       </c>
       <c r="G1847" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50514,7 +50511,7 @@
         <v>12.75</v>
       </c>
       <c r="G1848" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50540,7 +50537,7 @@
         <v>12.75</v>
       </c>
       <c r="G1849" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50566,7 +50563,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1850" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50592,7 +50589,7 @@
         <v>13.25</v>
       </c>
       <c r="G1851" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50618,7 +50615,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1852" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50644,7 +50641,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1853" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50670,7 +50667,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1854" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50696,7 +50693,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1855" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50722,7 +50719,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1856" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50748,7 +50745,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1857" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50774,7 +50771,7 @@
         <v>13</v>
       </c>
       <c r="G1858" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50800,7 +50797,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1859" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50826,7 +50823,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1860" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50852,7 +50849,7 @@
         <v>13.25</v>
       </c>
       <c r="G1861" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50878,7 +50875,7 @@
         <v>13.25</v>
       </c>
       <c r="G1862" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50904,7 +50901,7 @@
         <v>13.25</v>
       </c>
       <c r="G1863" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50930,7 +50927,7 @@
         <v>13.25</v>
       </c>
       <c r="G1864" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50956,7 +50953,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1865" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50982,7 +50979,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1866" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -51008,7 +51005,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1867" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -51034,7 +51031,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1868" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -51060,7 +51057,7 @@
         <v>12.5</v>
       </c>
       <c r="G1869" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -51086,7 +51083,7 @@
         <v>12.5</v>
       </c>
       <c r="G1870" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -51112,7 +51109,7 @@
         <v>12.5</v>
       </c>
       <c r="G1871" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -51138,7 +51135,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1872" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -51164,7 +51161,7 @@
         <v>12.5</v>
       </c>
       <c r="G1873" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -51190,7 +51187,7 @@
         <v>12.5</v>
       </c>
       <c r="G1874" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -51216,7 +51213,7 @@
         <v>12.5</v>
       </c>
       <c r="G1875" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -51242,7 +51239,7 @@
         <v>12.5</v>
       </c>
       <c r="G1876" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -51268,7 +51265,7 @@
         <v>12.25</v>
       </c>
       <c r="G1877" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -51294,7 +51291,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1878" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -51320,7 +51317,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1879" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -51346,7 +51343,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1880" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51372,7 +51369,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1881" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51398,7 +51395,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1882" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51424,7 +51421,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1883" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51450,7 +51447,7 @@
         <v>12.5</v>
       </c>
       <c r="G1884" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51476,7 +51473,7 @@
         <v>12.5</v>
       </c>
       <c r="G1885" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51502,7 +51499,7 @@
         <v>12.5</v>
       </c>
       <c r="G1886" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51528,7 +51525,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1887" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51554,7 +51551,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1888" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51580,7 +51577,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1889" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51606,7 +51603,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1890" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51632,7 +51629,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1891" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51658,7 +51655,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1892" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51684,7 +51681,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1893" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51710,7 +51707,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1894" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51736,7 +51733,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1895" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51762,7 +51759,7 @@
         <v>14.75</v>
       </c>
       <c r="G1896" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51788,7 +51785,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1897" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51814,7 +51811,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1898" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51840,7 +51837,7 @@
         <v>14.25</v>
       </c>
       <c r="G1899" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51866,7 +51863,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1900" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51892,7 +51889,7 @@
         <v>14</v>
       </c>
       <c r="G1901" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51918,7 +51915,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1902" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51944,7 +51941,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1903" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51970,7 +51967,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1904" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51996,7 +51993,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1905" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52022,7 +52019,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1906" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52048,7 +52045,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52074,7 +52071,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1908" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52100,7 +52097,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1909" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52126,7 +52123,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1910" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -52152,7 +52149,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1911" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -52178,7 +52175,7 @@
         <v>13.25</v>
       </c>
       <c r="G1912" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -52204,7 +52201,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1913" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -52230,7 +52227,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1914" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -52256,7 +52253,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1915" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -52282,7 +52279,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1916" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -52308,7 +52305,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1917" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -52334,7 +52331,7 @@
         <v>12.75</v>
       </c>
       <c r="G1918" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52360,7 +52357,7 @@
         <v>13</v>
       </c>
       <c r="G1919" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52386,7 +52383,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1920" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52412,7 +52409,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1921" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52438,7 +52435,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1922" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52464,7 +52461,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1923" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52490,7 +52487,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1924" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52516,7 +52513,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1925" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52542,7 +52539,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1926" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52568,7 +52565,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1927" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52594,7 +52591,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1928" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52620,7 +52617,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1929" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52646,7 +52643,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1930" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52672,7 +52669,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1931" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52698,7 +52695,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1932" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52724,7 +52721,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1933" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52750,7 +52747,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1934" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52776,7 +52773,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1935" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52802,7 +52799,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1936" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52828,7 +52825,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1937" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52854,7 +52851,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1938" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52880,7 +52877,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1939" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52906,7 +52903,7 @@
         <v>12.5</v>
       </c>
       <c r="G1940" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52932,7 +52929,7 @@
         <v>12.75</v>
       </c>
       <c r="G1941" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52958,7 +52955,7 @@
         <v>12.75</v>
       </c>
       <c r="G1942" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52984,7 +52981,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1943" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53010,7 +53007,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1944" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53036,7 +53033,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1945" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53062,7 +53059,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1946" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53088,7 +53085,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1947" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53114,7 +53111,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1948" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -53140,7 +53137,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1949" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -53166,7 +53163,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1950" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -53192,7 +53189,7 @@
         <v>12.25</v>
       </c>
       <c r="G1951" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -53218,7 +53215,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1952" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -53244,7 +53241,7 @@
         <v>12.5</v>
       </c>
       <c r="G1953" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -53270,7 +53267,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1954" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -53296,7 +53293,7 @@
         <v>12.25</v>
       </c>
       <c r="G1955" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -53322,7 +53319,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1956" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -53348,7 +53345,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1957" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53374,7 +53371,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1958" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53400,7 +53397,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1959" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53426,7 +53423,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1960" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53452,7 +53449,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1961" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53478,7 +53475,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1962" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53504,7 +53501,7 @@
         <v>10.5</v>
       </c>
       <c r="G1963" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53530,7 +53527,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1964" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53556,7 +53553,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1965" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53582,7 +53579,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1966" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53608,7 +53605,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1967" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53634,7 +53631,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1968" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53660,7 +53657,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1969" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53686,7 +53683,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1970" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53712,7 +53709,7 @@
         <v>12</v>
       </c>
       <c r="G1971" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53738,7 +53735,7 @@
         <v>12</v>
       </c>
       <c r="G1972" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53764,7 +53761,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1973" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53790,7 +53787,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1974" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53816,7 +53813,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1975" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53842,7 +53839,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1976" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53868,7 +53865,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1977" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53894,7 +53891,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1978" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53920,7 +53917,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1979" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53946,7 +53943,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1980" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53972,7 +53969,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1981" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53998,7 +53995,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1982" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54024,7 +54021,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54050,7 +54047,7 @@
         <v>13</v>
       </c>
       <c r="G1984" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54076,7 +54073,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1985" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54102,7 +54099,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1986" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -54128,7 +54125,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1987" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -54154,7 +54151,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1988" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -54180,7 +54177,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1989" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -54206,7 +54203,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1990" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -54232,7 +54229,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1991" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -54258,7 +54255,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1992" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -54284,7 +54281,7 @@
         <v>13.5</v>
       </c>
       <c r="G1993" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -54310,7 +54307,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1994" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -54336,7 +54333,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1995" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54362,7 +54359,7 @@
         <v>14.5</v>
       </c>
       <c r="G1996" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54388,7 +54385,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1997" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54414,7 +54411,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1998" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54440,7 +54437,7 @@
         <v>15</v>
       </c>
       <c r="G1999" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54466,7 +54463,7 @@
         <v>15.5</v>
       </c>
       <c r="G2000" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54492,7 +54489,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2001" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54518,7 +54515,7 @@
         <v>15.5</v>
       </c>
       <c r="G2002" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54544,7 +54541,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2003" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54570,7 +54567,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2004" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54596,7 +54593,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2005" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54622,7 +54619,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2006" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54648,7 +54645,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2007" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54674,7 +54671,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2008" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54700,7 +54697,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2009" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54726,7 +54723,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2010" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54752,7 +54749,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2011" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54778,7 +54775,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2012" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54804,7 +54801,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2013" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54830,7 +54827,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2014" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54856,7 +54853,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2015" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54882,7 +54879,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2016" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54908,7 +54905,7 @@
         <v>16</v>
       </c>
       <c r="G2017" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54934,7 +54931,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2018" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54960,7 +54957,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2019" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54986,7 +54983,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2020" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55012,7 +55009,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2021" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55038,7 +55035,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2022" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55064,7 +55061,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2023" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55090,7 +55087,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2024" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -55116,7 +55113,7 @@
         <v>17.5</v>
       </c>
       <c r="G2025" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -55142,7 +55139,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2026" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -55168,7 +55165,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2027" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -55194,7 +55191,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2028" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -55220,7 +55217,7 @@
         <v>17.5</v>
       </c>
       <c r="G2029" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -55246,7 +55243,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2030" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -55272,7 +55269,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2031" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -55298,7 +55295,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2032" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -55324,7 +55321,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2033" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -55350,7 +55347,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2034" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -55376,7 +55373,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2035" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -55402,7 +55399,7 @@
         <v>17.5</v>
       </c>
       <c r="G2036" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -55428,7 +55425,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2037" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55454,7 +55451,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2038" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55480,7 +55477,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2039" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55506,7 +55503,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2040" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55532,7 +55529,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2041" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55558,7 +55555,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2042" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55584,7 +55581,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2043" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55610,7 +55607,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2044" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55636,7 +55633,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2045" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55662,7 +55659,7 @@
         <v>13</v>
       </c>
       <c r="G2046" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55688,7 +55685,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2047" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55714,7 +55711,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2048" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55740,7 +55737,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2049" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55766,7 +55763,7 @@
         <v>12</v>
       </c>
       <c r="G2050" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55792,7 +55789,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2051" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55818,7 +55815,7 @@
         <v>12</v>
       </c>
       <c r="G2052" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55844,7 +55841,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2053" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55870,7 +55867,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2054" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55896,7 +55893,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2055" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55922,7 +55919,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2056" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55948,7 +55945,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2057" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55974,7 +55971,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2058" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -56000,7 +55997,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2059" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -56026,7 +56023,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2060" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -56052,7 +56049,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2061" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -56078,7 +56075,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2062" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -56104,7 +56101,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2063" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -56130,7 +56127,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2064" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -56156,7 +56153,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2065" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -56182,7 +56179,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2066" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -56208,7 +56205,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2067" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -56234,7 +56231,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2068" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -56260,7 +56257,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2069" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -56286,7 +56283,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2070" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -56312,7 +56309,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2071" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -56338,7 +56335,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2072" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -56364,7 +56361,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2073" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -56390,7 +56387,7 @@
         <v>14</v>
       </c>
       <c r="G2074" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -56416,7 +56413,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2075" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56442,7 +56439,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2076" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56468,7 +56465,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2077" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56494,7 +56491,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2078" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56520,7 +56517,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2079" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -56546,7 +56543,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2080" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -56572,7 +56569,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2081" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56598,7 +56595,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2082" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56624,7 +56621,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2083" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56650,7 +56647,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2084" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56676,7 +56673,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2085" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56702,7 +56699,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2086" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56728,7 +56725,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2087" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56754,7 +56751,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2088" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56780,7 +56777,7 @@
         <v>15.5</v>
       </c>
       <c r="G2089" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56806,7 +56803,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2090" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56832,7 +56829,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2091" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56858,7 +56855,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2092" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56884,7 +56881,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2093" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56910,7 +56907,7 @@
         <v>14.5</v>
       </c>
       <c r="G2094" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56936,7 +56933,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2095" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56962,7 +56959,7 @@
         <v>15</v>
       </c>
       <c r="G2096" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56988,7 +56985,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2097" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -57014,7 +57011,7 @@
         <v>15</v>
       </c>
       <c r="G2098" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -57040,7 +57037,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2099" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -57066,7 +57063,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2100" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -57092,7 +57089,7 @@
         <v>15</v>
       </c>
       <c r="G2101" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -57118,7 +57115,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2102" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -57144,7 +57141,7 @@
         <v>15</v>
       </c>
       <c r="G2103" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -57170,7 +57167,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2104" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -57196,7 +57193,7 @@
         <v>15</v>
       </c>
       <c r="G2105" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -57222,7 +57219,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2106" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -57248,7 +57245,7 @@
         <v>15</v>
       </c>
       <c r="G2107" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -57274,7 +57271,7 @@
         <v>15</v>
       </c>
       <c r="G2108" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -57300,7 +57297,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2109" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -57326,7 +57323,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2110" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -57352,7 +57349,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2111" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -57378,7 +57375,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2112" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -57404,7 +57401,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2113" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -57430,7 +57427,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2114" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -57456,7 +57453,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2115" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -57482,7 +57479,7 @@
         <v>14</v>
       </c>
       <c r="G2116" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -57508,7 +57505,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2117" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57534,7 +57531,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2118" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -57560,7 +57557,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2119" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57586,7 +57583,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2120" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57612,7 +57609,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2121" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57638,7 +57635,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2122" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57664,7 +57661,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2123" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57690,7 +57687,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2124" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57716,7 +57713,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2125" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57742,7 +57739,7 @@
         <v>13</v>
       </c>
       <c r="G2126" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -57768,7 +57765,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2127" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57776,7 +57773,7 @@
     </row>
     <row r="2128">
       <c r="A2128" s="1" t="n">
-        <v>45989.3352777778</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B2128" t="n">
         <v>125</v>
@@ -57794,9 +57791,35 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2128" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H2128" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" s="1" t="n">
+        <v>45992.6536226852</v>
+      </c>
+      <c r="B2129" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C2129" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="D2129" t="n">
+        <v>13.6999998092651</v>
+      </c>
+      <c r="E2129" t="n">
+        <v>13.6999998092651</v>
+      </c>
+      <c r="F2129" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="G2129" t="s">
+        <v>666</v>
+      </c>
+      <c r="H2129" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CULT.MI.xlsx
+++ b/data/CULT.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68585205078125</t>
+    <t xml:space="preserve">4.68585252761841</t>
   </si>
   <si>
     <t xml:space="preserve">CULT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57666730880737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59486532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60851240158081</t>
+    <t xml:space="preserve">4.57666778564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59486484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60851287841797</t>
   </si>
   <si>
     <t xml:space="preserve">4.58576631546021</t>
@@ -68,13 +68,13 @@
     <t xml:space="preserve">4.46020364761353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29824590682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21271800994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18178272247314</t>
+    <t xml:space="preserve">4.29824638366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21271848678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18178224563599</t>
   </si>
   <si>
     <t xml:space="preserve">4.23091554641724</t>
@@ -83,13 +83,13 @@
     <t xml:space="preserve">4.36375713348389</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38195466995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35101938247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28914785385132</t>
+    <t xml:space="preserve">4.38195371627808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35101890563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28914737701416</t>
   </si>
   <si>
     <t xml:space="preserve">4.24183416366577</t>
@@ -101,85 +101,85 @@
     <t xml:space="preserve">4.10535287857056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09443378448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10899257659912</t>
+    <t xml:space="preserve">4.09443426132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10899209976196</t>
   </si>
   <si>
     <t xml:space="preserve">3.99616813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04712152481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0398416519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96341180801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07441663742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32008361816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24911308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97979068756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06895875930786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05439901351929</t>
+    <t xml:space="preserve">4.04712104797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03984212875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96341228485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0744161605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3200831413269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2491135597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97979021072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06895780563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0543999671936</t>
   </si>
   <si>
     <t xml:space="preserve">3.98524928092957</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0507607460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07259798049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03802156448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04530096054077</t>
+    <t xml:space="preserve">4.05075979232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07259702682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0380220413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04530143737793</t>
   </si>
   <si>
     <t xml:space="preserve">4.03074264526367</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01254558563232</t>
+    <t xml:space="preserve">4.01254510879517</t>
   </si>
   <si>
     <t xml:space="preserve">4.04894018173218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05985879898071</t>
+    <t xml:space="preserve">4.05985927581787</t>
   </si>
   <si>
     <t xml:space="preserve">4.07623672485352</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9124596118927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99070906639099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01072549819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92155814170837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00162744522095</t>
+    <t xml:space="preserve">3.91245937347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99070811271667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01072597503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92155790328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00162649154663</t>
   </si>
   <si>
     <t xml:space="preserve">4.05803918838501</t>
@@ -188,34 +188,34 @@
     <t xml:space="preserve">4.21635770797729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2218165397644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18542146682739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16176414489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3546576499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28186750411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26731061935425</t>
+    <t xml:space="preserve">4.22181606292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18542098999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16176462173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35465812683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28186798095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26731109619141</t>
   </si>
   <si>
     <t xml:space="preserve">4.39287281036377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36739635467529</t>
+    <t xml:space="preserve">4.36739683151245</t>
   </si>
   <si>
     <t xml:space="preserve">4.17814254760742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27458906173706</t>
+    <t xml:space="preserve">4.27458953857422</t>
   </si>
   <si>
     <t xml:space="preserve">4.31826257705688</t>
@@ -224,19 +224,19 @@
     <t xml:space="preserve">4.35647773742676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26549100875854</t>
+    <t xml:space="preserve">4.26549053192139</t>
   </si>
   <si>
     <t xml:space="preserve">4.26367092132568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27640914916992</t>
+    <t xml:space="preserve">4.27640867233276</t>
   </si>
   <si>
     <t xml:space="preserve">4.14902639389038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35829782485962</t>
+    <t xml:space="preserve">4.35829734802246</t>
   </si>
   <si>
     <t xml:space="preserve">4.35283851623535</t>
@@ -245,10 +245,10 @@
     <t xml:space="preserve">4.29460620880127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2036190032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24001407623291</t>
+    <t xml:space="preserve">4.20361948013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24001359939575</t>
   </si>
   <si>
     <t xml:space="preserve">4.34010028839111</t>
@@ -257,13 +257,13 @@
     <t xml:space="preserve">4.42926836013794</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34919929504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33646059036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3310022354126</t>
+    <t xml:space="preserve">4.34919881820679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33646011352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33100175857544</t>
   </si>
   <si>
     <t xml:space="preserve">4.32190275192261</t>
@@ -272,25 +272,25 @@
     <t xml:space="preserve">4.46748208999634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45838403701782</t>
+    <t xml:space="preserve">4.45838451385498</t>
   </si>
   <si>
     <t xml:space="preserve">4.2855076789856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83057069778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90336060523987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88516354560852</t>
+    <t xml:space="preserve">3.83057117462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90336036682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88516330718994</t>
   </si>
   <si>
     <t xml:space="preserve">3.87606453895569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00344657897949</t>
+    <t xml:space="preserve">4.00344705581665</t>
   </si>
   <si>
     <t xml:space="preserve">3.93065762519836</t>
@@ -302,19 +302,19 @@
     <t xml:space="preserve">4.08533525466919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9670512676239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86696600914001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84876823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85786628723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81237292289734</t>
+    <t xml:space="preserve">3.96705174446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8669650554657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84876847267151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8578667640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81237316131592</t>
   </si>
   <si>
     <t xml:space="preserve">3.80327439308167</t>
@@ -323,13 +323,13 @@
     <t xml:space="preserve">3.77597832679749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97615051269531</t>
+    <t xml:space="preserve">3.97615003585815</t>
   </si>
   <si>
     <t xml:space="preserve">3.94885492324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13992881774902</t>
+    <t xml:space="preserve">4.13992786407471</t>
   </si>
   <si>
     <t xml:space="preserve">4.16722440719604</t>
@@ -338,10 +338,10 @@
     <t xml:space="preserve">4.33528280258179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21485948562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31675624847412</t>
+    <t xml:space="preserve">4.21485900878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31675672531128</t>
   </si>
   <si>
     <t xml:space="preserve">4.42791795730591</t>
@@ -350,22 +350,22 @@
     <t xml:space="preserve">4.19633197784424</t>
   </si>
   <si>
-    <t xml:space="preserve">4.168541431427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29822969436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30749273300171</t>
+    <t xml:space="preserve">4.16854190826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2982292175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30749320983887</t>
   </si>
   <si>
     <t xml:space="preserve">4.27970266342163</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3908634185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40012741088867</t>
+    <t xml:space="preserve">4.39086389541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40012788772583</t>
   </si>
   <si>
     <t xml:space="preserve">4.35380983352661</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">3.95548343658447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23338603973389</t>
+    <t xml:space="preserve">4.23338651657104</t>
   </si>
   <si>
     <t xml:space="preserve">4.22412204742432</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">4.24264907836914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11296081542969</t>
+    <t xml:space="preserve">4.11296129226685</t>
   </si>
   <si>
     <t xml:space="preserve">4.26117610931396</t>
@@ -431,31 +431,31 @@
     <t xml:space="preserve">3.86284899711609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71463441848755</t>
+    <t xml:space="preserve">3.71463418006897</t>
   </si>
   <si>
     <t xml:space="preserve">3.70537042617798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77021455764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39041376113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44599437713623</t>
+    <t xml:space="preserve">3.77021479606628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3904139995575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44599461555481</t>
   </si>
   <si>
     <t xml:space="preserve">3.58494544029236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68684387207031</t>
+    <t xml:space="preserve">3.68684339523315</t>
   </si>
   <si>
     <t xml:space="preserve">3.60347294807434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52010202407837</t>
+    <t xml:space="preserve">3.52010178565979</t>
   </si>
   <si>
     <t xml:space="preserve">3.37188696861267</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">3.53862881660461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52936506271362</t>
+    <t xml:space="preserve">3.5293653011322</t>
   </si>
   <si>
     <t xml:space="preserve">3.45525789260864</t>
@@ -485,31 +485,31 @@
     <t xml:space="preserve">3.29777979850769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31630635261536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23293542861938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24219942092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02914047241211</t>
+    <t xml:space="preserve">3.31630659103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23293566703796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24219918251038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02914023399353</t>
   </si>
   <si>
     <t xml:space="preserve">3.20514535903931</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25146269798279</t>
+    <t xml:space="preserve">3.25146245956421</t>
   </si>
   <si>
     <t xml:space="preserve">3.10324764251709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1588282585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91797971725464</t>
+    <t xml:space="preserve">3.15882849693298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91797947883606</t>
   </si>
   <si>
     <t xml:space="preserve">2.74197387695312</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">2.84387183189392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72344732284546</t>
+    <t xml:space="preserve">2.72344708442688</t>
   </si>
   <si>
     <t xml:space="preserve">2.76050114631653</t>
@@ -545,16 +545,16 @@
     <t xml:space="preserve">2.63081288337708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67712998390198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38070058822632</t>
+    <t xml:space="preserve">2.67713022232056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38070034980774</t>
   </si>
   <si>
     <t xml:space="preserve">2.36217379570007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29732966423035</t>
+    <t xml:space="preserve">2.29732942581177</t>
   </si>
   <si>
     <t xml:space="preserve">2.31585669517517</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">2.28806614875793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0842707157135</t>
+    <t xml:space="preserve">2.08427095413208</t>
   </si>
   <si>
     <t xml:space="preserve">2.13058805465698</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">1.99163663387299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88047552108765</t>
+    <t xml:space="preserve">1.88047540187836</t>
   </si>
   <si>
     <t xml:space="preserve">1.9453192949295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92679238319397</t>
+    <t xml:space="preserve">1.92679262161255</t>
   </si>
   <si>
     <t xml:space="preserve">2.16764140129089</t>
@@ -620,31 +620,31 @@
     <t xml:space="preserve">2.48259806632996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42701721191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38996386528015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46583557128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50406551361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65698575973511</t>
+    <t xml:space="preserve">2.42701745033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38996410369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46583580970764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50406575202942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65698599815369</t>
   </si>
   <si>
     <t xml:space="preserve">2.71433067321777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5422956943512</t>
+    <t xml:space="preserve">2.54229545593262</t>
   </si>
   <si>
     <t xml:space="preserve">2.58052587509155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52318096160889</t>
+    <t xml:space="preserve">2.52318120002747</t>
   </si>
   <si>
     <t xml:space="preserve">2.42760586738586</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">2.56141066551208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6378710269928</t>
+    <t xml:space="preserve">2.63787078857422</t>
   </si>
   <si>
     <t xml:space="preserve">2.73344588279724</t>
@@ -671,10 +671,10 @@
     <t xml:space="preserve">2.69521617889404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75256133079529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8099057674408</t>
+    <t xml:space="preserve">2.75256109237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80990552902222</t>
   </si>
   <si>
     <t xml:space="preserve">2.82902073860168</t>
@@ -695,19 +695,19 @@
     <t xml:space="preserve">2.67610096931458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59964060783386</t>
+    <t xml:space="preserve">2.59964084625244</t>
   </si>
   <si>
     <t xml:space="preserve">2.44672060012817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3702609539032</t>
+    <t xml:space="preserve">2.37026071548462</t>
   </si>
   <si>
     <t xml:space="preserve">3.09663105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34512615203857</t>
+    <t xml:space="preserve">3.34512591362</t>
   </si>
   <si>
     <t xml:space="preserve">3.45981597900391</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">3.74654150009155</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76565647125244</t>
+    <t xml:space="preserve">3.76565623283386</t>
   </si>
   <si>
     <t xml:space="preserve">4.01415109634399</t>
@@ -725,10 +725,10 @@
     <t xml:space="preserve">4.1097264289856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97592091560364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88034629821777</t>
+    <t xml:space="preserve">3.9759213924408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88034605979919</t>
   </si>
   <si>
     <t xml:space="preserve">3.82300138473511</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">3.40247106552124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36424088478088</t>
+    <t xml:space="preserve">3.36424112319946</t>
   </si>
   <si>
     <t xml:space="preserve">3.68919634819031</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">3.57450604438782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55539083480835</t>
+    <t xml:space="preserve">3.55539131164551</t>
   </si>
   <si>
     <t xml:space="preserve">3.51716113090515</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63185119628906</t>
+    <t xml:space="preserve">3.63185095787048</t>
   </si>
   <si>
     <t xml:space="preserve">3.53627586364746</t>
@@ -779,46 +779,46 @@
     <t xml:space="preserve">3.32601118087769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42158603668213</t>
+    <t xml:space="preserve">3.42158627510071</t>
   </si>
   <si>
     <t xml:space="preserve">3.30689597129822</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38335609436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59362125396729</t>
+    <t xml:space="preserve">3.38335633277893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59362101554871</t>
   </si>
   <si>
     <t xml:space="preserve">3.47893118858337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49804615974426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28778123855591</t>
+    <t xml:space="preserve">3.49804639816284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28778100013733</t>
   </si>
   <si>
     <t xml:space="preserve">3.67008090019226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8038866519928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93769097328186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03326654434204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18618631362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30087614059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5302562713623</t>
+    <t xml:space="preserve">3.80388617515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93769145011902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03326606750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18618679046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30087661743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53025674819946</t>
   </si>
   <si>
     <t xml:space="preserve">4.51114130020142</t>
@@ -830,16 +830,16 @@
     <t xml:space="preserve">4.49202632904053</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43468189239502</t>
+    <t xml:space="preserve">4.43468141555786</t>
   </si>
   <si>
     <t xml:space="preserve">4.62583208084106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7405219078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75963687896729</t>
+    <t xml:space="preserve">4.74052143096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75963735580444</t>
   </si>
   <si>
     <t xml:space="preserve">4.70229148864746</t>
@@ -866,10 +866,10 @@
     <t xml:space="preserve">4.96990156173706</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92211389541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11326456069946</t>
+    <t xml:space="preserve">4.92211437225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1132640838623</t>
   </si>
   <si>
     <t xml:space="preserve">5.16105175018311</t>
@@ -908,13 +908,13 @@
     <t xml:space="preserve">4.8444390296936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82506132125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80568361282349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59252786636353</t>
+    <t xml:space="preserve">4.8250617980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80568313598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59252834320068</t>
   </si>
   <si>
     <t xml:space="preserve">4.55377244949341</t>
@@ -926,13 +926,13 @@
     <t xml:space="preserve">5.03821659088135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98977184295654</t>
+    <t xml:space="preserve">4.9897723197937</t>
   </si>
   <si>
     <t xml:space="preserve">5.08666086196899</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18354988098145</t>
+    <t xml:space="preserve">5.18354940414429</t>
   </si>
   <si>
     <t xml:space="preserve">4.9413275718689</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">5.28043794631958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89288330078125</t>
+    <t xml:space="preserve">4.89288282394409</t>
   </si>
   <si>
     <t xml:space="preserve">4.6312837600708</t>
@@ -992,13 +992,13 @@
     <t xml:space="preserve">6.73376989364624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29777050018311</t>
+    <t xml:space="preserve">6.29777097702026</t>
   </si>
   <si>
     <t xml:space="preserve">6.4431037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68532562255859</t>
+    <t xml:space="preserve">6.68532609939575</t>
   </si>
   <si>
     <t xml:space="preserve">6.5884370803833</t>
@@ -1007,7 +1007,7 @@
     <t xml:space="preserve">6.63688087463379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2493257522583</t>
+    <t xml:space="preserve">6.24932622909546</t>
   </si>
   <si>
     <t xml:space="preserve">6.34621524810791</t>
@@ -1016,16 +1016,16 @@
     <t xml:space="preserve">6.5399923324585</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39465999603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71998977661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99332332611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09021282196045</t>
+    <t xml:space="preserve">6.39465951919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71999073028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99332427978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09021377563477</t>
   </si>
   <si>
     <t xml:space="preserve">8.04176807403564</t>
@@ -1034,13 +1034,13 @@
     <t xml:space="preserve">7.94488000869751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84799194335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89643478393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38087844848633</t>
+    <t xml:space="preserve">7.84799098968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89643621444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38087749481201</t>
   </si>
   <si>
     <t xml:space="preserve">10.2702112197876</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">10.173321723938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97954368591309</t>
+    <t xml:space="preserve">9.9795446395874</t>
   </si>
   <si>
     <t xml:space="preserve">10.0764331817627</t>
@@ -1073,13 +1073,13 @@
     <t xml:space="preserve">12.9830961227417</t>
   </si>
   <si>
-    <t xml:space="preserve">14.436427116394</t>
+    <t xml:space="preserve">14.4364280700684</t>
   </si>
   <si>
     <t xml:space="preserve">14.3395385742188</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0177602767944</t>
+    <t xml:space="preserve">15.0177612304688</t>
   </si>
   <si>
     <t xml:space="preserve">16.1669788360596</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">12.4661045074463</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4400196075439</t>
+    <t xml:space="preserve">13.4400205612183</t>
   </si>
   <si>
     <t xml:space="preserve">13.9269771575928</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">14.2191524505615</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8035001754761</t>
+    <t xml:space="preserve">14.8034992218018</t>
   </si>
   <si>
     <t xml:space="preserve">14.413932800293</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">13.3426275253296</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1217594146729</t>
+    <t xml:space="preserve">14.1217584609985</t>
   </si>
   <si>
     <t xml:space="preserve">14.3165426254272</t>
@@ -1145,10 +1145,10 @@
     <t xml:space="preserve">13.5374097824097</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2452373504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8556699752808</t>
+    <t xml:space="preserve">13.2452363967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8556709289551</t>
   </si>
   <si>
     <t xml:space="preserve">12.3687133789062</t>
@@ -1175,13 +1175,13 @@
     <t xml:space="preserve">10.7130584716797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2000169754028</t>
+    <t xml:space="preserve">11.2000160217285</t>
   </si>
   <si>
     <t xml:space="preserve">11.9791479110718</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8817548751831</t>
+    <t xml:space="preserve">11.8817558288574</t>
   </si>
   <si>
     <t xml:space="preserve">10.9078416824341</t>
@@ -1202,10 +1202,10 @@
     <t xml:space="preserve">11.7843647003174</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4921913146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.810450553894</t>
+    <t xml:space="preserve">11.4921903610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8104515075684</t>
   </si>
   <si>
     <t xml:space="preserve">10.4208841323853</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">9.34957885742188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49566555023193</t>
+    <t xml:space="preserve">9.49566650390625</t>
   </si>
   <si>
     <t xml:space="preserve">12.2713222503662</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">12.9530620574951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6800231933594</t>
+    <t xml:space="preserve">15.6800222396851</t>
   </si>
   <si>
     <t xml:space="preserve">13.7321939468384</t>
@@ -57854,7 +57854,7 @@
     </row>
     <row r="2131">
       <c r="A2131" s="1" t="n">
-        <v>45994.6447685185</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B2131" t="n">
         <v>2500</v>
@@ -57875,6 +57875,32 @@
         <v>666</v>
       </c>
       <c r="H2131" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" s="1" t="n">
+        <v>45995.4574537037</v>
+      </c>
+      <c r="B2132" t="n">
+        <v>125</v>
+      </c>
+      <c r="C2132" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="D2132" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="E2132" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="F2132" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="G2132" t="s">
+        <v>666</v>
+      </c>
+      <c r="H2132" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CULT.MI.xlsx
+++ b/data/CULT.MI.xlsx
@@ -44,25 +44,25 @@
     <t xml:space="preserve">CULT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57666730880737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59486484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60851335525513</t>
+    <t xml:space="preserve">4.57666778564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59486532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60851287841797</t>
   </si>
   <si>
     <t xml:space="preserve">4.58576631546021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48931932449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56301975250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51297616958618</t>
+    <t xml:space="preserve">4.48931980133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56301927566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51297664642334</t>
   </si>
   <si>
     <t xml:space="preserve">4.46020317077637</t>
@@ -71,70 +71,70 @@
     <t xml:space="preserve">4.29824638366699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21271753311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18178176879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23091506958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36375665664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38195371627808</t>
+    <t xml:space="preserve">4.21271800994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18178272247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23091554641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36375617980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38195466995239</t>
   </si>
   <si>
     <t xml:space="preserve">4.35101842880249</t>
   </si>
   <si>
-    <t xml:space="preserve">4.289146900177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24183368682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22909498214722</t>
+    <t xml:space="preserve">4.28914833068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24183416366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22909545898438</t>
   </si>
   <si>
     <t xml:space="preserve">4.10535287857056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09443473815918</t>
+    <t xml:space="preserve">4.09443426132202</t>
   </si>
   <si>
     <t xml:space="preserve">4.10899209976196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99616765975952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04712057113647</t>
+    <t xml:space="preserve">3.99616813659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04712104797363</t>
   </si>
   <si>
     <t xml:space="preserve">4.0398416519165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96341228485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07441711425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3200831413269</t>
+    <t xml:space="preserve">3.96341276168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07441663742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32008361816406</t>
   </si>
   <si>
     <t xml:space="preserve">4.24911308288574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97978973388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0689582824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05439949035645</t>
+    <t xml:space="preserve">3.97979044914246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06895780563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05439901351929</t>
   </si>
   <si>
     <t xml:space="preserve">3.98524904251099</t>
@@ -143,67 +143,67 @@
     <t xml:space="preserve">4.0507607460022</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07259654998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0380220413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04530096054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03074359893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01254558563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04894065856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05985832214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07623624801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9124596118927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99070882797241</t>
+    <t xml:space="preserve">4.07259750366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03802299499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04530048370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03074312210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01254606246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04894018173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05985879898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0762357711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91245985031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99070858955383</t>
   </si>
   <si>
     <t xml:space="preserve">4.01072597503662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92155790328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00162744522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05803871154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21635627746582</t>
+    <t xml:space="preserve">3.92155814170837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00162696838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05803918838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21635770797729</t>
   </si>
   <si>
     <t xml:space="preserve">4.22181701660156</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18542146682739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16176414489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35465860366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28186845779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26730918884277</t>
+    <t xml:space="preserve">4.18542098999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16176462173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35465717315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28186750411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26731014251709</t>
   </si>
   <si>
     <t xml:space="preserve">4.39287328720093</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">4.17814254760742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27458953857422</t>
+    <t xml:space="preserve">4.27458906173706</t>
   </si>
   <si>
     <t xml:space="preserve">4.31826305389404</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">4.35647821426392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26549053192139</t>
+    <t xml:space="preserve">4.26549100875854</t>
   </si>
   <si>
     <t xml:space="preserve">4.26367092132568</t>
@@ -242,61 +242,61 @@
     <t xml:space="preserve">4.35283851623535</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29460668563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2036190032959</t>
+    <t xml:space="preserve">4.29460620880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20361948013306</t>
   </si>
   <si>
     <t xml:space="preserve">4.24001359939575</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34009981155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42926788330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34919929504395</t>
+    <t xml:space="preserve">4.34010028839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4292688369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34919881820679</t>
   </si>
   <si>
     <t xml:space="preserve">4.33646059036255</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33100128173828</t>
+    <t xml:space="preserve">4.3310022354126</t>
   </si>
   <si>
     <t xml:space="preserve">4.32190275192261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4674825668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45838451385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28550720214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83057045936584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90336012840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8851625919342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87606430053711</t>
+    <t xml:space="preserve">4.46748208999634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45838356018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28550815582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83057069778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90336084365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88516354560852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87606501579285</t>
   </si>
   <si>
     <t xml:space="preserve">4.00344705581665</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93065690994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9943482875824</t>
+    <t xml:space="preserve">3.93065667152405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99434781074524</t>
   </si>
   <si>
     <t xml:space="preserve">4.08533525466919</t>
@@ -305,37 +305,37 @@
     <t xml:space="preserve">3.9670512676239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86696553230286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84876847267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85786628723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8123733997345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80327463150024</t>
+    <t xml:space="preserve">3.86696577072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84876871109009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85786652565002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81237244606018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80327391624451</t>
   </si>
   <si>
     <t xml:space="preserve">3.77597832679749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97615027427673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94885492324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13992786407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16722440719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3352837562561</t>
+    <t xml:space="preserve">3.97615003585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94885444641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13992834091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1672248840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33528327941895</t>
   </si>
   <si>
     <t xml:space="preserve">4.21485900878906</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">4.31675624847412</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42791795730591</t>
+    <t xml:space="preserve">4.42791748046875</t>
   </si>
   <si>
     <t xml:space="preserve">4.19633197784424</t>
@@ -353,49 +353,49 @@
     <t xml:space="preserve">4.168541431427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29822969436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30749320983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27970314025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39086437225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40012788772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35380983352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08517074584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93695569038391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00180053710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97400951385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03885364532471</t>
+    <t xml:space="preserve">4.29823017120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30749273300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27970266342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3908634185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40012741088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35381031036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08517169952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93695592880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00180006027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97401022911072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03885316848755</t>
   </si>
   <si>
     <t xml:space="preserve">3.94622015953064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95548295974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23338603973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22412204742432</t>
+    <t xml:space="preserve">3.95548343658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23338556289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22412252426147</t>
   </si>
   <si>
     <t xml:space="preserve">4.2426495552063</t>
@@ -404,25 +404,25 @@
     <t xml:space="preserve">4.11296129226685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26117610931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91842937469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89990210533142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89063906669617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0759072303772</t>
+    <t xml:space="preserve">4.26117563247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9184296131134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89990234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89063882827759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07590770721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.06664371490479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79800462722778</t>
+    <t xml:space="preserve">3.79800486564636</t>
   </si>
   <si>
     <t xml:space="preserve">3.73316073417664</t>
@@ -431,52 +431,52 @@
     <t xml:space="preserve">3.86284899711609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71463418006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7053701877594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77021479606628</t>
+    <t xml:space="preserve">3.71463394165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70537042617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77021455764771</t>
   </si>
   <si>
     <t xml:space="preserve">3.39041376113892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44599485397339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58494544029236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68684363365173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60347270965576</t>
+    <t xml:space="preserve">3.44599437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58494567871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68684387207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60347294807434</t>
   </si>
   <si>
     <t xml:space="preserve">3.52010202407837</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37188720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46452140808105</t>
+    <t xml:space="preserve">3.37188696861267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4645209312439</t>
   </si>
   <si>
     <t xml:space="preserve">3.53862881660461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5293653011322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45525813102722</t>
+    <t xml:space="preserve">3.52936506271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45525789260864</t>
   </si>
   <si>
     <t xml:space="preserve">3.34409666061401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07545757293701</t>
+    <t xml:space="preserve">3.07545709609985</t>
   </si>
   <si>
     <t xml:space="preserve">3.14956498146057</t>
@@ -488,31 +488,31 @@
     <t xml:space="preserve">3.31630659103394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23293566703796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2421989440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02913999557495</t>
+    <t xml:space="preserve">3.23293542861938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24219942092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02914023399353</t>
   </si>
   <si>
     <t xml:space="preserve">3.20514535903931</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25146269798279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10324740409851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1588282585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91797947883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74197435379028</t>
+    <t xml:space="preserve">3.25146293640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10324788093567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15882849693298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91797971725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7419741153717</t>
   </si>
   <si>
     <t xml:space="preserve">2.77902770042419</t>
@@ -521,22 +521,22 @@
     <t xml:space="preserve">2.871661901474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96429657936096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85313487052917</t>
+    <t xml:space="preserve">2.96429634094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85313534736633</t>
   </si>
   <si>
     <t xml:space="preserve">2.83460831642151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84387183189392</t>
+    <t xml:space="preserve">2.84387159347534</t>
   </si>
   <si>
     <t xml:space="preserve">2.72344732284546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76050066947937</t>
+    <t xml:space="preserve">2.76050090789795</t>
   </si>
   <si>
     <t xml:space="preserve">2.76976442337036</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">2.36217379570007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29732966423035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31585669517517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35291028022766</t>
+    <t xml:space="preserve">2.29732990264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31585645675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35291004180908</t>
   </si>
   <si>
     <t xml:space="preserve">2.26953911781311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23248553276062</t>
+    <t xml:space="preserve">2.23248600959778</t>
   </si>
   <si>
     <t xml:space="preserve">2.28806638717651</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">2.0842707157135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13058805465698</t>
+    <t xml:space="preserve">2.1305878162384</t>
   </si>
   <si>
     <t xml:space="preserve">2.22322225570679</t>
@@ -584,34 +584,34 @@
     <t xml:space="preserve">2.24174928665161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11206102371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17690491676331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0379536151886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99163675308228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88047528266907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94531953334808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92679250240326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16764187812805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13985157012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21395897865295</t>
+    <t xml:space="preserve">2.11206126213074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17690515518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03795385360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99163687229156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88047540187836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94531941413879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92679262161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16764163970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13985133171082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21395874023438</t>
   </si>
   <si>
     <t xml:space="preserve">2.40849041938782</t>
@@ -620,19 +620,19 @@
     <t xml:space="preserve">2.48259806632996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42701768875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38996410369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46583604812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50406575202942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65698599815369</t>
+    <t xml:space="preserve">2.42701745033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38996386528015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46583580970764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50406551361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65698575973511</t>
   </si>
   <si>
     <t xml:space="preserve">2.71433067321777</t>
@@ -641,34 +641,34 @@
     <t xml:space="preserve">2.5422956943512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58052611351013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52318072319031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42760586738586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38937592506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48495101928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61875557899475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56141090393066</t>
+    <t xml:space="preserve">2.58052587509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52318096160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42760562896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38937568664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48495054244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61875581741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56141066551208</t>
   </si>
   <si>
     <t xml:space="preserve">2.6378710269928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73344588279724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69521570205688</t>
+    <t xml:space="preserve">2.73344564437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69521594047546</t>
   </si>
   <si>
     <t xml:space="preserve">2.75256109237671</t>
@@ -683,13 +683,13 @@
     <t xml:space="preserve">2.84813594818115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05840110778809</t>
+    <t xml:space="preserve">3.05840086936951</t>
   </si>
   <si>
     <t xml:space="preserve">2.86725091934204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7716760635376</t>
+    <t xml:space="preserve">2.77167630195618</t>
   </si>
   <si>
     <t xml:space="preserve">2.676100730896</t>
@@ -698,37 +698,37 @@
     <t xml:space="preserve">2.59964084625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44672060012817</t>
+    <t xml:space="preserve">2.44672083854675</t>
   </si>
   <si>
     <t xml:space="preserve">2.4084906578064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37026071548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09663081169128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34512591362</t>
+    <t xml:space="preserve">2.3702609539032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09663128852844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34512639045715</t>
   </si>
   <si>
     <t xml:space="preserve">3.45981597900391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74654102325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76565647125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01415157318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1097264289856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97592091560364</t>
+    <t xml:space="preserve">3.74654150009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76565623283386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01415109634399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10972690582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97592115402222</t>
   </si>
   <si>
     <t xml:space="preserve">3.88034605979919</t>
@@ -746,31 +746,31 @@
     <t xml:space="preserve">3.36424112319946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68919610977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72742581367493</t>
+    <t xml:space="preserve">3.68919658660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72742605209351</t>
   </si>
   <si>
     <t xml:space="preserve">3.7083113193512</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57450604438782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55539131164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51716136932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63185095787048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53627610206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61273646354675</t>
+    <t xml:space="preserve">3.57450580596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55539107322693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51716113090515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63185119628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53627634048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61273622512817</t>
   </si>
   <si>
     <t xml:space="preserve">3.65096616744995</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">3.24955105781555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32601118087769</t>
+    <t xml:space="preserve">3.32601070404053</t>
   </si>
   <si>
     <t xml:space="preserve">3.42158603668213</t>
@@ -788,40 +788,40 @@
     <t xml:space="preserve">3.30689597129822</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38335633277893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59362125396729</t>
+    <t xml:space="preserve">3.38335585594177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59362149238586</t>
   </si>
   <si>
     <t xml:space="preserve">3.47893095016479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49804615974426</t>
+    <t xml:space="preserve">3.49804592132568</t>
   </si>
   <si>
     <t xml:space="preserve">3.28778123855591</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67008090019226</t>
+    <t xml:space="preserve">3.67008113861084</t>
   </si>
   <si>
     <t xml:space="preserve">3.80388641357422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93769097328186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03326559066772</t>
+    <t xml:space="preserve">3.93769121170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03326606750488</t>
   </si>
   <si>
     <t xml:space="preserve">4.18618631362915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30087661743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5302562713623</t>
+    <t xml:space="preserve">4.30087614059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53025579452515</t>
   </si>
   <si>
     <t xml:space="preserve">4.51114130020142</t>
@@ -833,25 +833,25 @@
     <t xml:space="preserve">4.49202632904053</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43468141555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62583112716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74052143096924</t>
+    <t xml:space="preserve">4.43468189239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62583208084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7405219078064</t>
   </si>
   <si>
     <t xml:space="preserve">4.75963640213013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7022910118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68317699432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77875185012817</t>
+    <t xml:space="preserve">4.70229196548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68317604064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77875137329102</t>
   </si>
   <si>
     <t xml:space="preserve">4.56848621368408</t>
@@ -860,34 +860,34 @@
     <t xml:space="preserve">4.66406154632568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72140645980835</t>
+    <t xml:space="preserve">4.72140693664551</t>
   </si>
   <si>
     <t xml:space="preserve">4.87432670593262</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96990203857422</t>
+    <t xml:space="preserve">4.9699010848999</t>
   </si>
   <si>
     <t xml:space="preserve">4.92211389541626</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1132640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16105222702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20883846282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25662708282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30441474914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44777679443359</t>
+    <t xml:space="preserve">5.11326456069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16105175018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20883941650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25662660598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30441427230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44777631759644</t>
   </si>
   <si>
     <t xml:space="preserve">5.63892650604248</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">5.1351056098938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84443950653076</t>
+    <t xml:space="preserve">4.8444390296936</t>
   </si>
   <si>
     <t xml:space="preserve">4.82506132125854</t>
@@ -926,10 +926,10 @@
     <t xml:space="preserve">4.76692771911621</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03821611404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9897723197937</t>
+    <t xml:space="preserve">5.03821659088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98977184295654</t>
   </si>
   <si>
     <t xml:space="preserve">5.08666086196899</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">5.23199415206909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74755048751831</t>
+    <t xml:space="preserve">4.74755001068115</t>
   </si>
   <si>
     <t xml:space="preserve">5.28043794631958</t>
@@ -956,13 +956,13 @@
     <t xml:space="preserve">4.6312837600708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53439521789551</t>
+    <t xml:space="preserve">4.53439474105835</t>
   </si>
   <si>
     <t xml:space="preserve">4.67003917694092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78630542755127</t>
+    <t xml:space="preserve">4.78630590438843</t>
   </si>
   <si>
     <t xml:space="preserve">4.72817277908325</t>
@@ -971,16 +971,16 @@
     <t xml:space="preserve">4.70879459381104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91021537780762</t>
+    <t xml:space="preserve">5.91021585464478</t>
   </si>
   <si>
     <t xml:space="preserve">5.61954927444458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32888317108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37732696533203</t>
+    <t xml:space="preserve">5.32888269424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37732744216919</t>
   </si>
   <si>
     <t xml:space="preserve">5.57110452651978</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">5.47421598434448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66799354553223</t>
+    <t xml:space="preserve">5.66799306869507</t>
   </si>
   <si>
     <t xml:space="preserve">6.73376989364624</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">6.4431037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68532609939575</t>
+    <t xml:space="preserve">6.68532562255859</t>
   </si>
   <si>
     <t xml:space="preserve">6.5884370803833</t>
@@ -1016,19 +1016,19 @@
     <t xml:space="preserve">6.34621524810791</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53999280929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39465951919556</t>
+    <t xml:space="preserve">6.5399923324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39465999603271</t>
   </si>
   <si>
     <t xml:space="preserve">8.71998977661133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99332427978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09021377563477</t>
+    <t xml:space="preserve">7.99332332611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09021282196045</t>
   </si>
   <si>
     <t xml:space="preserve">8.04176807403564</t>
@@ -1037,10 +1037,10 @@
     <t xml:space="preserve">7.94488000869751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84799098968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89643526077271</t>
+    <t xml:space="preserve">7.84799194335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89643478393555</t>
   </si>
   <si>
     <t xml:space="preserve">8.38087844848633</t>
@@ -1055,10 +1055,10 @@
     <t xml:space="preserve">10.173321723938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9795446395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0764322280884</t>
+    <t xml:space="preserve">9.97954368591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0764331817627</t>
   </si>
   <si>
     <t xml:space="preserve">11.2390985488892</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">11.6266536712646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0799856185913</t>
+    <t xml:space="preserve">13.079984664917</t>
   </si>
   <si>
     <t xml:space="preserve">13.2737617492676</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">14.436427116394</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3395395278931</t>
+    <t xml:space="preserve">14.3395385742188</t>
   </si>
   <si>
     <t xml:space="preserve">15.0177602767944</t>
@@ -1088,13 +1088,13 @@
     <t xml:space="preserve">16.1669788360596</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1930646896362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0956735610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9008913040161</t>
+    <t xml:space="preserve">15.1930656433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0956745147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9008903503418</t>
   </si>
   <si>
     <t xml:space="preserve">13.634801864624</t>
@@ -1103,31 +1103,31 @@
     <t xml:space="preserve">12.0765390396118</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4661054611206</t>
+    <t xml:space="preserve">12.4661045074463</t>
   </si>
   <si>
     <t xml:space="preserve">13.4400196075439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9269762039185</t>
+    <t xml:space="preserve">13.9269771575928</t>
   </si>
   <si>
     <t xml:space="preserve">14.0243673324585</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2191514968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8034992218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4139337539673</t>
+    <t xml:space="preserve">14.2191524505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8035001754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.413932800293</t>
   </si>
   <si>
     <t xml:space="preserve">14.6087160110474</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7061080932617</t>
+    <t xml:space="preserve">14.706109046936</t>
   </si>
   <si>
     <t xml:space="preserve">14.5113248825073</t>
@@ -1139,82 +1139,82 @@
     <t xml:space="preserve">14.1217594146729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3165416717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8295850753784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.537410736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2452363967896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8556709289551</t>
+    <t xml:space="preserve">14.3165426254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8295841217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5374097824097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2452373504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8556699752808</t>
   </si>
   <si>
     <t xml:space="preserve">12.3687133789062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.758279800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5634956359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1739311218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6869735717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1026248931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93392658233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.713059425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2000160217285</t>
+    <t xml:space="preserve">12.7582788467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5634965896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1739301681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6869745254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1026239395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93392753601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7130584716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2000169754028</t>
   </si>
   <si>
     <t xml:space="preserve">11.9791479110718</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8817558288574</t>
+    <t xml:space="preserve">11.8817548751831</t>
   </si>
   <si>
     <t xml:space="preserve">10.9078416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2974081039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3947992324829</t>
+    <t xml:space="preserve">11.2974071502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3947982788086</t>
   </si>
   <si>
     <t xml:space="preserve">11.589581489563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0052337646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7843656539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4921903610229</t>
+    <t xml:space="preserve">11.0052328109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7843647003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4921913146973</t>
   </si>
   <si>
     <t xml:space="preserve">10.810450553894</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4208850860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2261018753052</t>
+    <t xml:space="preserve">10.4208841323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2261009216309</t>
   </si>
   <si>
     <t xml:space="preserve">10.3234939575195</t>
@@ -1223,22 +1223,22 @@
     <t xml:space="preserve">10.1287097930908</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0313186645508</t>
+    <t xml:space="preserve">10.0313196182251</t>
   </si>
   <si>
     <t xml:space="preserve">9.73914432525635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54436111450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83653545379639</t>
+    <t xml:space="preserve">9.54436206817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8365364074707</t>
   </si>
   <si>
     <t xml:space="preserve">9.34957885742188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49566650390625</t>
+    <t xml:space="preserve">9.49566555023193</t>
   </si>
   <si>
     <t xml:space="preserve">12.2713222503662</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">12.9530620574951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6800222396851</t>
+    <t xml:space="preserve">15.6800231933594</t>
   </si>
   <si>
     <t xml:space="preserve">13.7321939468384</t>
@@ -1256,13 +1256,13 @@
     <t xml:space="preserve">14.1704559326172</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3652381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0730628967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1443691253662</t>
+    <t xml:space="preserve">14.3652372360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0730638504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1443700790405</t>
   </si>
   <si>
     <t xml:space="preserve">15.5364561080933</t>
@@ -57909,7 +57909,7 @@
     </row>
     <row r="2133">
       <c r="A2133" s="1" t="n">
-        <v>45996.3670717593</v>
+        <v>45996.3333333333</v>
       </c>
       <c r="B2133" t="n">
         <v>125</v>

--- a/data/CULT.MI.xlsx
+++ b/data/CULT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68585252761841</t>
+    <t xml:space="preserve">4.68585205078125</t>
   </si>
   <si>
     <t xml:space="preserve">CULT.MI</t>
@@ -47,25 +47,25 @@
     <t xml:space="preserve">4.57666778564453</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59486532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60851287841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58576631546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48931980133057</t>
+    <t xml:space="preserve">4.59486484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60851335525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58576679229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48931932449341</t>
   </si>
   <si>
     <t xml:space="preserve">4.56301927566528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51297664642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46020317077637</t>
+    <t xml:space="preserve">4.51297616958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46020364761353</t>
   </si>
   <si>
     <t xml:space="preserve">4.29824638366699</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">4.21271800994873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18178272247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23091554641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36375617980957</t>
+    <t xml:space="preserve">4.18178224563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23091506958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36375713348389</t>
   </si>
   <si>
     <t xml:space="preserve">4.38195466995239</t>
@@ -89,10 +89,10 @@
     <t xml:space="preserve">4.35101842880249</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28914833068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24183416366577</t>
+    <t xml:space="preserve">4.28914737701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24183464050293</t>
   </si>
   <si>
     <t xml:space="preserve">4.22909545898438</t>
@@ -107,109 +107,109 @@
     <t xml:space="preserve">4.10899209976196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99616813659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04712104797363</t>
+    <t xml:space="preserve">3.99616765975952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04712057113647</t>
   </si>
   <si>
     <t xml:space="preserve">4.0398416519165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96341276168823</t>
+    <t xml:space="preserve">3.96341180801392</t>
   </si>
   <si>
     <t xml:space="preserve">4.07441663742065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32008361816406</t>
+    <t xml:space="preserve">4.3200831413269</t>
   </si>
   <si>
     <t xml:space="preserve">4.24911308288574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97979044914246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06895780563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05439901351929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98524904251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0507607460022</t>
+    <t xml:space="preserve">3.97979021072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0689582824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05439853668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98524928092957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05076026916504</t>
   </si>
   <si>
     <t xml:space="preserve">4.07259750366211</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03802299499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04530048370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03074312210083</t>
+    <t xml:space="preserve">4.03802156448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04530143737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03074264526367</t>
   </si>
   <si>
     <t xml:space="preserve">4.01254606246948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04894018173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05985879898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0762357711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91245985031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99070858955383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01072597503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92155814170837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00162696838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05803918838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21635770797729</t>
+    <t xml:space="preserve">4.04894113540649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05985975265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07623720169067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9124596118927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99070906639099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01072549819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92155838012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00162649154663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05803966522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21635723114014</t>
   </si>
   <si>
     <t xml:space="preserve">4.22181701660156</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18542098999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16176462173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35465717315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28186750411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26731014251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39287328720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36739683151245</t>
+    <t xml:space="preserve">4.18542146682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16176509857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35465812683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28186845779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26731061935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39287281036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36739730834961</t>
   </si>
   <si>
     <t xml:space="preserve">4.17814254760742</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">4.35647821426392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26549100875854</t>
+    <t xml:space="preserve">4.2654914855957</t>
   </si>
   <si>
     <t xml:space="preserve">4.26367092132568</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">4.27640914916992</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14902687072754</t>
+    <t xml:space="preserve">4.1490273475647</t>
   </si>
   <si>
     <t xml:space="preserve">4.35829782485962</t>
@@ -245,34 +245,34 @@
     <t xml:space="preserve">4.29460620880127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20361948013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24001359939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34010028839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4292688369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34919881820679</t>
+    <t xml:space="preserve">4.20361852645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24001407623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34009981155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42926788330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34919929504395</t>
   </si>
   <si>
     <t xml:space="preserve">4.33646059036255</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3310022354126</t>
+    <t xml:space="preserve">4.33100128173828</t>
   </si>
   <si>
     <t xml:space="preserve">4.32190275192261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46748208999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45838356018066</t>
+    <t xml:space="preserve">4.46748161315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45838451385498</t>
   </si>
   <si>
     <t xml:space="preserve">4.28550815582275</t>
@@ -281,22 +281,22 @@
     <t xml:space="preserve">3.83057069778442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90336084365845</t>
+    <t xml:space="preserve">3.90336060523987</t>
   </si>
   <si>
     <t xml:space="preserve">3.88516354560852</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87606501579285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00344705581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93065667152405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99434781074524</t>
+    <t xml:space="preserve">3.87606406211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00344657897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93065714836121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99434733390808</t>
   </si>
   <si>
     <t xml:space="preserve">4.08533525466919</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">3.86696577072144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84876871109009</t>
+    <t xml:space="preserve">3.84876775741577</t>
   </si>
   <si>
     <t xml:space="preserve">3.85786652565002</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81237244606018</t>
+    <t xml:space="preserve">3.81237292289734</t>
   </si>
   <si>
     <t xml:space="preserve">3.80327391624451</t>
@@ -326,52 +326,52 @@
     <t xml:space="preserve">3.97615003585815</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94885444641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13992834091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1672248840332</t>
+    <t xml:space="preserve">3.94885492324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13992786407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16722440719604</t>
   </si>
   <si>
     <t xml:space="preserve">4.33528327941895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21485900878906</t>
+    <t xml:space="preserve">4.21485948562622</t>
   </si>
   <si>
     <t xml:space="preserve">4.31675624847412</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42791748046875</t>
+    <t xml:space="preserve">4.42791795730591</t>
   </si>
   <si>
     <t xml:space="preserve">4.19633197784424</t>
   </si>
   <si>
-    <t xml:space="preserve">4.168541431427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29823017120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30749273300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27970266342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3908634185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40012741088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35381031036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08517169952393</t>
+    <t xml:space="preserve">4.16854190826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29822969436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30749320983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27970314025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39086389541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40012788772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35380983352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08517074584961</t>
   </si>
   <si>
     <t xml:space="preserve">3.93695592880249</t>
@@ -380,19 +380,19 @@
     <t xml:space="preserve">4.00180006027222</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97401022911072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03885316848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94622015953064</t>
+    <t xml:space="preserve">3.97400975227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03885364532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9462194442749</t>
   </si>
   <si>
     <t xml:space="preserve">3.95548343658447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23338556289673</t>
+    <t xml:space="preserve">4.23338603973389</t>
   </si>
   <si>
     <t xml:space="preserve">4.22412252426147</t>
@@ -404,16 +404,16 @@
     <t xml:space="preserve">4.11296129226685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26117563247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9184296131134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89990234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89063882827759</t>
+    <t xml:space="preserve">4.26117610931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91842913627625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89990258216858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89063858985901</t>
   </si>
   <si>
     <t xml:space="preserve">4.07590770721436</t>
@@ -422,16 +422,16 @@
     <t xml:space="preserve">4.06664371490479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79800486564636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73316073417664</t>
+    <t xml:space="preserve">3.79800462722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73316097259521</t>
   </si>
   <si>
     <t xml:space="preserve">3.86284899711609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71463394165039</t>
+    <t xml:space="preserve">3.71463418006897</t>
   </si>
   <si>
     <t xml:space="preserve">3.70537042617798</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">3.77021455764771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39041376113892</t>
+    <t xml:space="preserve">3.3904139995575</t>
   </si>
   <si>
     <t xml:space="preserve">3.44599437713623</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">3.58494567871094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68684387207031</t>
+    <t xml:space="preserve">3.68684363365173</t>
   </si>
   <si>
     <t xml:space="preserve">3.60347294807434</t>
@@ -458,10 +458,10 @@
     <t xml:space="preserve">3.52010202407837</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37188696861267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4645209312439</t>
+    <t xml:space="preserve">3.37188720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46452116966248</t>
   </si>
   <si>
     <t xml:space="preserve">3.53862881660461</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">3.52936506271362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45525789260864</t>
+    <t xml:space="preserve">3.45525765419006</t>
   </si>
   <si>
     <t xml:space="preserve">3.34409666061401</t>
@@ -479,43 +479,43 @@
     <t xml:space="preserve">3.07545709609985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14956498146057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29777956008911</t>
+    <t xml:space="preserve">3.14956521987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29777979850769</t>
   </si>
   <si>
     <t xml:space="preserve">3.31630659103394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23293542861938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24219942092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02914023399353</t>
+    <t xml:space="preserve">3.23293566703796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24219918251038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02914047241211</t>
   </si>
   <si>
     <t xml:space="preserve">3.20514535903931</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25146293640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10324788093567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15882849693298</t>
+    <t xml:space="preserve">3.25146245956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10324764251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1588282585144</t>
   </si>
   <si>
     <t xml:space="preserve">2.91797971725464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7419741153717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77902770042419</t>
+    <t xml:space="preserve">2.74197387695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77902793884277</t>
   </si>
   <si>
     <t xml:space="preserve">2.871661901474</t>
@@ -524,10 +524,10 @@
     <t xml:space="preserve">2.96429634094238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85313534736633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83460831642151</t>
+    <t xml:space="preserve">2.85313510894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83460807800293</t>
   </si>
   <si>
     <t xml:space="preserve">2.84387159347534</t>
@@ -551,73 +551,73 @@
     <t xml:space="preserve">2.38070058822632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36217379570007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29732990264893</t>
+    <t xml:space="preserve">2.36217355728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29732942581177</t>
   </si>
   <si>
     <t xml:space="preserve">2.31585645675659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35291004180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26953911781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23248600959778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28806638717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0842707157135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1305878162384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22322225570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24174928665161</t>
+    <t xml:space="preserve">2.35291028022766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26953983306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2324857711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28806614875793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08427095413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13058805465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22322249412537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24174952507019</t>
   </si>
   <si>
     <t xml:space="preserve">2.11206126213074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17690515518188</t>
+    <t xml:space="preserve">2.17690491676331</t>
   </si>
   <si>
     <t xml:space="preserve">2.03795385360718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99163687229156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88047540187836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94531941413879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92679262161255</t>
+    <t xml:space="preserve">1.99163663387299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88047552108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9453192949295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92679226398468</t>
   </si>
   <si>
     <t xml:space="preserve">2.16764163970947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13985133171082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21395874023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40849041938782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48259806632996</t>
+    <t xml:space="preserve">2.13985157012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21395897865295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4084906578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48259830474854</t>
   </si>
   <si>
     <t xml:space="preserve">2.42701745033264</t>
@@ -626,16 +626,16 @@
     <t xml:space="preserve">2.38996386528015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46583580970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50406551361084</t>
+    <t xml:space="preserve">2.46583557128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50406575202942</t>
   </si>
   <si>
     <t xml:space="preserve">2.65698575973511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71433067321777</t>
+    <t xml:space="preserve">2.71433091163635</t>
   </si>
   <si>
     <t xml:space="preserve">2.5422956943512</t>
@@ -644,10 +644,10 @@
     <t xml:space="preserve">2.58052587509155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52318096160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42760562896729</t>
+    <t xml:space="preserve">2.52318120002747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42760586738586</t>
   </si>
   <si>
     <t xml:space="preserve">2.38937568664551</t>
@@ -662,58 +662,58 @@
     <t xml:space="preserve">2.56141066551208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6378710269928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73344564437866</t>
+    <t xml:space="preserve">2.63787078857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73344588279724</t>
   </si>
   <si>
     <t xml:space="preserve">2.69521594047546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75256109237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80990600585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82902097702026</t>
+    <t xml:space="preserve">2.75256085395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8099057674408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82902050018311</t>
   </si>
   <si>
     <t xml:space="preserve">2.84813594818115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05840086936951</t>
+    <t xml:space="preserve">3.05840110778809</t>
   </si>
   <si>
     <t xml:space="preserve">2.86725091934204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77167630195618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.676100730896</t>
+    <t xml:space="preserve">2.77167582511902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67610096931458</t>
   </si>
   <si>
     <t xml:space="preserve">2.59964084625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44672083854675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4084906578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3702609539032</t>
+    <t xml:space="preserve">2.44672060012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40849089622498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37026071548462</t>
   </si>
   <si>
     <t xml:space="preserve">3.09663128852844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34512639045715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45981597900391</t>
+    <t xml:space="preserve">3.34512615203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45981621742249</t>
   </si>
   <si>
     <t xml:space="preserve">3.74654150009155</t>
@@ -725,16 +725,16 @@
     <t xml:space="preserve">4.01415109634399</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10972690582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97592115402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88034605979919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82300114631653</t>
+    <t xml:space="preserve">4.10972595214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97592091560364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88034629821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82300138473511</t>
   </si>
   <si>
     <t xml:space="preserve">3.44070100784302</t>
@@ -743,19 +743,19 @@
     <t xml:space="preserve">3.40247106552124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36424112319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68919658660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72742605209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7083113193512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57450580596924</t>
+    <t xml:space="preserve">3.36424088478088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68919587135315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72742629051208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70831108093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57450604438782</t>
   </si>
   <si>
     <t xml:space="preserve">3.55539107322693</t>
@@ -767,10 +767,10 @@
     <t xml:space="preserve">3.63185119628906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53627634048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61273622512817</t>
+    <t xml:space="preserve">3.53627610206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61273574829102</t>
   </si>
   <si>
     <t xml:space="preserve">3.65096616744995</t>
@@ -779,25 +779,25 @@
     <t xml:space="preserve">3.24955105781555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32601070404053</t>
+    <t xml:space="preserve">3.32601118087769</t>
   </si>
   <si>
     <t xml:space="preserve">3.42158603668213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30689597129822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38335585594177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59362149238586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47893095016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49804592132568</t>
+    <t xml:space="preserve">3.3068962097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38335609436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59362077713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47893142700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49804615974426</t>
   </si>
   <si>
     <t xml:space="preserve">3.28778123855591</t>
@@ -806,70 +806,70 @@
     <t xml:space="preserve">3.67008113861084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80388641357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93769121170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03326606750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18618631362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30087614059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53025579452515</t>
+    <t xml:space="preserve">3.80388593673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93769073486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03326654434204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18618583679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30087661743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5302562713623</t>
   </si>
   <si>
     <t xml:space="preserve">4.51114130020142</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58760166168213</t>
+    <t xml:space="preserve">4.58760213851929</t>
   </si>
   <si>
     <t xml:space="preserve">4.49202632904053</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43468189239502</t>
+    <t xml:space="preserve">4.43468141555786</t>
   </si>
   <si>
     <t xml:space="preserve">4.62583208084106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7405219078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75963640213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70229196548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68317604064941</t>
+    <t xml:space="preserve">4.74052143096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75963735580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70229148864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68317699432373</t>
   </si>
   <si>
     <t xml:space="preserve">4.77875137329102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56848621368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66406154632568</t>
+    <t xml:space="preserve">4.5684871673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6640625</t>
   </si>
   <si>
     <t xml:space="preserve">4.72140693664551</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87432670593262</t>
+    <t xml:space="preserve">4.8743257522583</t>
   </si>
   <si>
     <t xml:space="preserve">4.9699010848999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92211389541626</t>
+    <t xml:space="preserve">4.9221134185791</t>
   </si>
   <si>
     <t xml:space="preserve">5.11326456069946</t>
@@ -881,40 +881,40 @@
     <t xml:space="preserve">5.20883941650391</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25662660598755</t>
+    <t xml:space="preserve">5.25662708282471</t>
   </si>
   <si>
     <t xml:space="preserve">5.30441427230835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44777631759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63892650604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59113931655884</t>
+    <t xml:space="preserve">5.44777679443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63892698287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.591139793396</t>
   </si>
   <si>
     <t xml:space="preserve">5.81332683563232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71643781661987</t>
+    <t xml:space="preserve">5.71643829345703</t>
   </si>
   <si>
     <t xml:space="preserve">5.42577171325684</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1351056098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8444390296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82506132125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80568361282349</t>
+    <t xml:space="preserve">5.13510513305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84443855285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8250617980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80568313598633</t>
   </si>
   <si>
     <t xml:space="preserve">4.59252786636353</t>
@@ -926,37 +926,37 @@
     <t xml:space="preserve">4.76692771911621</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03821659088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98977184295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08666086196899</t>
+    <t xml:space="preserve">5.03821611404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98977136611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08665990829468</t>
   </si>
   <si>
     <t xml:space="preserve">5.18354988098145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9413275718689</t>
+    <t xml:space="preserve">4.94132709503174</t>
   </si>
   <si>
     <t xml:space="preserve">5.23199415206909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74755001068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28043794631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89288330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6312837600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53439474105835</t>
+    <t xml:space="preserve">4.74755048751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2804388999939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89288282394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63128423690796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53439521789551</t>
   </si>
   <si>
     <t xml:space="preserve">4.67003917694092</t>
@@ -965,31 +965,31 @@
     <t xml:space="preserve">4.78630590438843</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72817277908325</t>
+    <t xml:space="preserve">4.72817325592041</t>
   </si>
   <si>
     <t xml:space="preserve">4.70879459381104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91021585464478</t>
+    <t xml:space="preserve">5.91021537780762</t>
   </si>
   <si>
     <t xml:space="preserve">5.61954927444458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32888269424438</t>
+    <t xml:space="preserve">5.32888317108154</t>
   </si>
   <si>
     <t xml:space="preserve">5.37732744216919</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57110452651978</t>
+    <t xml:space="preserve">5.57110548019409</t>
   </si>
   <si>
     <t xml:space="preserve">5.47421598434448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66799306869507</t>
+    <t xml:space="preserve">5.66799402236938</t>
   </si>
   <si>
     <t xml:space="preserve">6.73376989364624</t>
@@ -998,7 +998,7 @@
     <t xml:space="preserve">6.29777050018311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4431037902832</t>
+    <t xml:space="preserve">6.44310331344604</t>
   </si>
   <si>
     <t xml:space="preserve">6.68532562255859</t>
@@ -1007,58 +1007,58 @@
     <t xml:space="preserve">6.5884370803833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63688087463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2493257522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34621524810791</t>
+    <t xml:space="preserve">6.63688135147095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24932622909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34621477127075</t>
   </si>
   <si>
     <t xml:space="preserve">6.5399923324585</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39465999603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71998977661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99332332611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09021282196045</t>
+    <t xml:space="preserve">6.3946590423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71999073028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99332427978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09021472930908</t>
   </si>
   <si>
     <t xml:space="preserve">8.04176807403564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94488000869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84799194335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89643478393555</t>
+    <t xml:space="preserve">7.94487953186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84799098968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89643621444702</t>
   </si>
   <si>
     <t xml:space="preserve">8.38087844848633</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2702112197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88265514373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.173321723938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97954368591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0764331817627</t>
+    <t xml:space="preserve">10.2702102661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88265419006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1733198165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97954273223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0764322280884</t>
   </si>
   <si>
     <t xml:space="preserve">11.2390985488892</t>
@@ -1070,31 +1070,31 @@
     <t xml:space="preserve">13.079984664917</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2737617492676</t>
+    <t xml:space="preserve">13.2737627029419</t>
   </si>
   <si>
     <t xml:space="preserve">12.9830961227417</t>
   </si>
   <si>
-    <t xml:space="preserve">14.436427116394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3395385742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0177602767944</t>
+    <t xml:space="preserve">14.4364280700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3395395278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0177612304688</t>
   </si>
   <si>
     <t xml:space="preserve">16.1669788360596</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1930656433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0956745147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9008903503418</t>
+    <t xml:space="preserve">15.1930646896362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0956735610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9008913040161</t>
   </si>
   <si>
     <t xml:space="preserve">13.634801864624</t>
@@ -1115,22 +1115,22 @@
     <t xml:space="preserve">14.0243673324585</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2191524505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8035001754761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.413932800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6087160110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.706109046936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5113248825073</t>
+    <t xml:space="preserve">14.2191514968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8034992218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4139337539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6087169647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7061080932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5113258361816</t>
   </si>
   <si>
     <t xml:space="preserve">13.3426275253296</t>
@@ -1142,13 +1142,13 @@
     <t xml:space="preserve">14.3165426254272</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8295841217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5374097824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2452373504639</t>
+    <t xml:space="preserve">13.8295850753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.537410736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2452363967896</t>
   </si>
   <si>
     <t xml:space="preserve">12.8556699752808</t>
@@ -1160,19 +1160,19 @@
     <t xml:space="preserve">12.7582788467407</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5634965896606</t>
+    <t xml:space="preserve">12.5634956359863</t>
   </si>
   <si>
     <t xml:space="preserve">12.1739301681519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6869745254517</t>
+    <t xml:space="preserve">11.6869735717773</t>
   </si>
   <si>
     <t xml:space="preserve">11.1026239395142</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93392753601074</t>
+    <t xml:space="preserve">9.93392658233643</t>
   </si>
   <si>
     <t xml:space="preserve">10.7130584716797</t>
@@ -1184,19 +1184,19 @@
     <t xml:space="preserve">11.9791479110718</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8817548751831</t>
+    <t xml:space="preserve">11.8817558288574</t>
   </si>
   <si>
     <t xml:space="preserve">10.9078416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2974071502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3947982788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.589581489563</t>
+    <t xml:space="preserve">11.2974081039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3947992324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5895824432373</t>
   </si>
   <si>
     <t xml:space="preserve">11.0052328109741</t>
@@ -1205,25 +1205,25 @@
     <t xml:space="preserve">11.7843647003174</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4921913146973</t>
+    <t xml:space="preserve">11.4921903610229</t>
   </si>
   <si>
     <t xml:space="preserve">10.810450553894</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4208841323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2261009216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3234939575195</t>
+    <t xml:space="preserve">10.4208850860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2260999679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3234930038452</t>
   </si>
   <si>
     <t xml:space="preserve">10.1287097930908</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0313196182251</t>
+    <t xml:space="preserve">10.0313177108765</t>
   </si>
   <si>
     <t xml:space="preserve">9.73914432525635</t>
@@ -1232,40 +1232,40 @@
     <t xml:space="preserve">9.54436206817627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8365364074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34957885742188</t>
+    <t xml:space="preserve">9.83653545379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34957981109619</t>
   </si>
   <si>
     <t xml:space="preserve">9.49566555023193</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2713222503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9530620574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6800231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7321939468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1704559326172</t>
+    <t xml:space="preserve">12.2713232040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9530611038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6800222396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7321929931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1704549789429</t>
   </si>
   <si>
     <t xml:space="preserve">14.3652372360229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0730638504028</t>
+    <t xml:space="preserve">14.0730628967285</t>
   </si>
   <si>
     <t xml:space="preserve">15.1443700790405</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5364561080933</t>
+    <t xml:space="preserve">15.5364570617676</t>
   </si>
   <si>
     <t xml:space="preserve">15.585467338562</t>
@@ -1277,22 +1277,22 @@
     <t xml:space="preserve">15.193380355835</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4874458312988</t>
+    <t xml:space="preserve">15.4874467849731</t>
   </si>
   <si>
     <t xml:space="preserve">15.4384346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2423906326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3894233703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9973373413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8993148803711</t>
+    <t xml:space="preserve">15.2423915863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3894243240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9973363876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8993139266968</t>
   </si>
   <si>
     <t xml:space="preserve">15.0463485717773</t>
@@ -1304,43 +1304,43 @@
     <t xml:space="preserve">13.9190969467163</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1641502380371</t>
+    <t xml:space="preserve">14.1641511917114</t>
   </si>
   <si>
     <t xml:space="preserve">13.7230529785156</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8210754394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3601951599121</t>
+    <t xml:space="preserve">13.8210744857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3601942062378</t>
   </si>
   <si>
     <t xml:space="preserve">13.6250314712524</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8700847625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6740417480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7720651626587</t>
+    <t xml:space="preserve">13.8700866699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6740427017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7720642089844</t>
   </si>
   <si>
     <t xml:space="preserve">14.0171184539795</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1839323043823</t>
+    <t xml:space="preserve">13.1839332580566</t>
   </si>
   <si>
     <t xml:space="preserve">13.5270099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9483251571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4092054367065</t>
+    <t xml:space="preserve">14.9483261108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4092063903809</t>
   </si>
   <si>
     <t xml:space="preserve">14.8503036499023</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">14.6052494049072</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7032709121704</t>
+    <t xml:space="preserve">14.7032718658447</t>
   </si>
   <si>
     <t xml:space="preserve">14.5562391281128</t>
@@ -1361,25 +1361,25 @@
     <t xml:space="preserve">14.507227897644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0661306381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3309659957886</t>
+    <t xml:space="preserve">14.0661296844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3309669494629</t>
   </si>
   <si>
     <t xml:space="preserve">13.4779987335205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2819557189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8898668289185</t>
+    <t xml:space="preserve">13.2819547653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8898677825928</t>
   </si>
   <si>
     <t xml:space="preserve">12.7428350448608</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9878902435303</t>
+    <t xml:space="preserve">12.987889289856</t>
   </si>
   <si>
     <t xml:space="preserve">13.1349220275879</t>
@@ -1394,16 +1394,16 @@
     <t xml:space="preserve">11.3215188980103</t>
   </si>
   <si>
-    <t xml:space="preserve">12.301736831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0859117507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4289875030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8305225372314</t>
+    <t xml:space="preserve">12.3017377853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0859127044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4289884567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8305215835571</t>
   </si>
   <si>
     <t xml:space="preserve">15.7324991226196</t>
@@ -1412,22 +1412,22 @@
     <t xml:space="preserve">15.8795328140259</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9775552749634</t>
+    <t xml:space="preserve">15.9775533676147</t>
   </si>
   <si>
     <t xml:space="preserve">16.3696422576904</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6834897994995</t>
+    <t xml:space="preserve">15.6834888458252</t>
   </si>
   <si>
     <t xml:space="preserve">15.7815113067627</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2226104736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0265655517578</t>
+    <t xml:space="preserve">16.2226085662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0265674591064</t>
   </si>
   <si>
     <t xml:space="preserve">16.0755767822266</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">15.9285440444946</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1735992431641</t>
+    <t xml:space="preserve">16.1735973358154</t>
   </si>
   <si>
     <t xml:space="preserve">16.2716197967529</t>
@@ -1448,13 +1448,13 @@
     <t xml:space="preserve">18.7221660614014</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0162296295166</t>
+    <t xml:space="preserve">19.0162315368652</t>
   </si>
   <si>
     <t xml:space="preserve">19.7023849487305</t>
   </si>
   <si>
-    <t xml:space="preserve">19.604362487793</t>
+    <t xml:space="preserve">19.6043605804443</t>
   </si>
   <si>
     <t xml:space="preserve">19.8004055023193</t>
@@ -1466,7 +1466,7 @@
     <t xml:space="preserve">23.9173202514648</t>
   </si>
   <si>
-    <t xml:space="preserve">22.545015335083</t>
+    <t xml:space="preserve">22.5450172424316</t>
   </si>
   <si>
     <t xml:space="preserve">23.5252342224121</t>
@@ -1487,10 +1487,10 @@
     <t xml:space="preserve">20.4865570068359</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6826038360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3687534332275</t>
+    <t xml:space="preserve">20.6826019287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3687553405762</t>
   </si>
   <si>
     <t xml:space="preserve">22.6430377960205</t>
@@ -1499,49 +1499,49 @@
     <t xml:space="preserve">24.9955615997314</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2896251678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6034736633301</t>
+    <t xml:space="preserve">25.2896270751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6034755706787</t>
   </si>
   <si>
     <t xml:space="preserve">24.8975391387939</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5054531097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.015344619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.623254776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8390808105469</t>
+    <t xml:space="preserve">24.5054512023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0153427124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6232566833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8390789031982</t>
   </si>
   <si>
     <t xml:space="preserve">23.3291893005371</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9371032714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7212791442871</t>
+    <t xml:space="preserve">22.937105178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7212772369385</t>
   </si>
   <si>
     <t xml:space="preserve">24.1133651733398</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0351238250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1331462860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2113857269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4074306488037</t>
+    <t xml:space="preserve">23.0351257324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1331481933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2113876342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4074287414551</t>
   </si>
   <si>
     <t xml:space="preserve">23.819299697876</t>
@@ -1556,16 +1556,16 @@
     <t xml:space="preserve">21.9568843841553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1529293060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7711753845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6439247131348</t>
+    <t xml:space="preserve">22.1529273986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7711772918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3300800323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6439266204834</t>
   </si>
   <si>
     <t xml:space="preserve">18.5261211395264</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">19.9964485168457</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5845794677734</t>
+    <t xml:space="preserve">20.5845775604248</t>
   </si>
   <si>
     <t xml:space="preserve">20.1924934387207</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">19.8984260559082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3885345458984</t>
+    <t xml:space="preserve">20.3885364532471</t>
   </si>
   <si>
     <t xml:space="preserve">19.4049549102783</t>
@@ -1598,10 +1598,10 @@
     <t xml:space="preserve">19.5527095794678</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7989654541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.601957321167</t>
+    <t xml:space="preserve">19.7989635467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6019592285156</t>
   </si>
   <si>
     <t xml:space="preserve">18.9616947174072</t>
@@ -1631,13 +1631,13 @@
     <t xml:space="preserve">20.4884796142578</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5869808197021</t>
+    <t xml:space="preserve">20.5869827270508</t>
   </si>
   <si>
     <t xml:space="preserve">19.9959678649902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4542064666748</t>
+    <t xml:space="preserve">19.4542045593262</t>
   </si>
   <si>
     <t xml:space="preserve">19.5034561157227</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">19.207950592041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0259208679199</t>
+    <t xml:space="preserve">18.0259227752686</t>
   </si>
   <si>
     <t xml:space="preserve">18.075174331665</t>
@@ -1673,19 +1673,19 @@
     <t xml:space="preserve">17.9274196624756</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9766712188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.434907913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1736755371094</t>
+    <t xml:space="preserve">17.9766693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4349098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.173677444458</t>
   </si>
   <si>
     <t xml:space="preserve">18.4199314117432</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7839889526367</t>
+    <t xml:space="preserve">20.7839870452881</t>
   </si>
   <si>
     <t xml:space="preserve">20.3899784088135</t>
@@ -1694,10 +1694,10 @@
     <t xml:space="preserve">19.7004623413086</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9124431610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1094455718994</t>
+    <t xml:space="preserve">18.9124450683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.109447479248</t>
   </si>
   <si>
     <t xml:space="preserve">18.8631916046143</t>
@@ -1706,7 +1706,7 @@
     <t xml:space="preserve">18.5184326171875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7154388427734</t>
+    <t xml:space="preserve">18.7154369354248</t>
   </si>
   <si>
     <t xml:space="preserve">18.2229270935059</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">17.7796649932861</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5676860809326</t>
+    <t xml:space="preserve">18.567684173584</t>
   </si>
   <si>
     <t xml:space="preserve">17.7304153442383</t>
@@ -1727,16 +1727,16 @@
     <t xml:space="preserve">18.2721767425537</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6811637878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8781700134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1244258880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6319141387939</t>
+    <t xml:space="preserve">17.6811656951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8781681060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1244239807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6319122314453</t>
   </si>
   <si>
     <t xml:space="preserve">17.4841594696045</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">17.3856582641602</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5334091186523</t>
+    <t xml:space="preserve">17.533411026001</t>
   </si>
   <si>
     <t xml:space="preserve">17.1886520385742</t>
@@ -1760,7 +1760,7 @@
     <t xml:space="preserve">16.4991359710693</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8931465148926</t>
+    <t xml:space="preserve">16.8931446075439</t>
   </si>
   <si>
     <t xml:space="preserve">16.4498863220215</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">16.6468906402588</t>
   </si>
   <si>
-    <t xml:space="preserve">16.794641494751</t>
+    <t xml:space="preserve">16.7946434020996</t>
   </si>
   <si>
     <t xml:space="preserve">16.7453918457031</t>
@@ -1784,7 +1784,7 @@
     <t xml:space="preserve">14.6275930404663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9723501205444</t>
+    <t xml:space="preserve">14.9723510742188</t>
   </si>
   <si>
     <t xml:space="preserve">14.7260942459106</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">15.1201047897339</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3663597106934</t>
+    <t xml:space="preserve">15.3663606643677</t>
   </si>
   <si>
     <t xml:space="preserve">15.464861869812</t>
@@ -1808,16 +1808,16 @@
     <t xml:space="preserve">14.7753458023071</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4798393249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2828340530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5783414840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0858306884766</t>
+    <t xml:space="preserve">14.4798383712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2828350067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5783424377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0858297348022</t>
   </si>
   <si>
     <t xml:space="preserve">14.2335834503174</t>
@@ -57933,6 +57933,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2134">
+      <c r="A2134" s="1" t="n">
+        <v>45999.3333333333</v>
+      </c>
+      <c r="B2134" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2134" t="n">
+        <v>14.8999996185303</v>
+      </c>
+      <c r="D2134" t="n">
+        <v>14.8999996185303</v>
+      </c>
+      <c r="E2134" t="n">
+        <v>14.8999996185303</v>
+      </c>
+      <c r="F2134" t="n">
+        <v>14.8999996185303</v>
+      </c>
+      <c r="G2134" t="s">
+        <v>701</v>
+      </c>
+      <c r="H2134" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" s="1" t="n">
+        <v>46000.3753587963</v>
+      </c>
+      <c r="B2135" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2135" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="D2135" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="E2135" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F2135" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="G2135" t="s">
+        <v>708</v>
+      </c>
+      <c r="H2135" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CULT.MI.xlsx
+++ b/data/CULT.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68585205078125</t>
+    <t xml:space="preserve">4.68585157394409</t>
   </si>
   <si>
     <t xml:space="preserve">CULT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57666826248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59486484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60851335525513</t>
+    <t xml:space="preserve">4.57666778564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5948657989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60851240158081</t>
   </si>
   <si>
     <t xml:space="preserve">4.58576631546021</t>
@@ -59,10 +59,10 @@
     <t xml:space="preserve">4.48932027816772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56301879882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51297664642334</t>
+    <t xml:space="preserve">4.56301975250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51297616958618</t>
   </si>
   <si>
     <t xml:space="preserve">4.46020364761353</t>
@@ -77,34 +77,34 @@
     <t xml:space="preserve">4.18178224563599</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23091506958008</t>
+    <t xml:space="preserve">4.23091459274292</t>
   </si>
   <si>
     <t xml:space="preserve">4.36375665664673</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38195419311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35101842880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.289146900177</t>
+    <t xml:space="preserve">4.38195514678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35101890563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28914737701416</t>
   </si>
   <si>
     <t xml:space="preserve">4.24183416366577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22909545898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10535287857056</t>
+    <t xml:space="preserve">4.22909498214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1053524017334</t>
   </si>
   <si>
     <t xml:space="preserve">4.09443426132202</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10899209976196</t>
+    <t xml:space="preserve">4.1089916229248</t>
   </si>
   <si>
     <t xml:space="preserve">3.99616813659668</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">4.0398416519165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96341180801392</t>
+    <t xml:space="preserve">3.96341228485107</t>
   </si>
   <si>
     <t xml:space="preserve">4.07441759109497</t>
@@ -125,34 +125,34 @@
     <t xml:space="preserve">4.32008266448975</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24911403656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97978973388672</t>
+    <t xml:space="preserve">4.24911308288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97979021072388</t>
   </si>
   <si>
     <t xml:space="preserve">4.06895780563354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05439949035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9852499961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05076122283936</t>
+    <t xml:space="preserve">4.05439901351929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98524951934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0507607460022</t>
   </si>
   <si>
     <t xml:space="preserve">4.07259702682495</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03802156448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04530143737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03074216842651</t>
+    <t xml:space="preserve">4.0380220413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04530048370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03074264526367</t>
   </si>
   <si>
     <t xml:space="preserve">4.01254558563232</t>
@@ -164,10 +164,10 @@
     <t xml:space="preserve">4.05985879898071</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07623720169067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91245913505554</t>
+    <t xml:space="preserve">4.07623624801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9124596118927</t>
   </si>
   <si>
     <t xml:space="preserve">3.99070906639099</t>
@@ -176,22 +176,22 @@
     <t xml:space="preserve">4.01072549819946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92155838012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00162649154663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05803966522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21635675430298</t>
+    <t xml:space="preserve">3.92155814170837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00162696838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05804014205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21635723114014</t>
   </si>
   <si>
     <t xml:space="preserve">4.2218165397644</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18542146682739</t>
+    <t xml:space="preserve">4.18542194366455</t>
   </si>
   <si>
     <t xml:space="preserve">4.16176462173462</t>
@@ -203,16 +203,16 @@
     <t xml:space="preserve">4.28186845779419</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26731061935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39287328720093</t>
+    <t xml:space="preserve">4.26731109619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39287281036377</t>
   </si>
   <si>
     <t xml:space="preserve">4.36739730834961</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17814254760742</t>
+    <t xml:space="preserve">4.17814302444458</t>
   </si>
   <si>
     <t xml:space="preserve">4.27458953857422</t>
@@ -221,25 +221,25 @@
     <t xml:space="preserve">4.31826305389404</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35647869110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26549053192139</t>
+    <t xml:space="preserve">4.35647821426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26549100875854</t>
   </si>
   <si>
     <t xml:space="preserve">4.26367044448853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27640867233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14902687072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35829830169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35283756256104</t>
+    <t xml:space="preserve">4.27640914916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14902639389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35829782485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35283851623535</t>
   </si>
   <si>
     <t xml:space="preserve">4.29460620880127</t>
@@ -248,10 +248,10 @@
     <t xml:space="preserve">4.2036190032959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24001359939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34010076522827</t>
+    <t xml:space="preserve">4.24001407623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34010028839111</t>
   </si>
   <si>
     <t xml:space="preserve">4.42926836013794</t>
@@ -260,82 +260,82 @@
     <t xml:space="preserve">4.34919929504395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33646059036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33100128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32190227508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4674825668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45838451385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28550815582275</t>
+    <t xml:space="preserve">4.33646011352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33100175857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32190275192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46748208999634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45838356018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2855076789856</t>
   </si>
   <si>
     <t xml:space="preserve">3.830570936203</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90336036682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88516330718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87606453895569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00344657897949</t>
+    <t xml:space="preserve">3.90336132049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8851637840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87606477737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00344705581665</t>
   </si>
   <si>
     <t xml:space="preserve">3.93065714836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99434804916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08533477783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96705222129822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86696577072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84876823425293</t>
+    <t xml:space="preserve">3.99434757232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08533525466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9670512676239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86696529388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84876799583435</t>
   </si>
   <si>
     <t xml:space="preserve">3.85786652565002</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81237316131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80327415466309</t>
+    <t xml:space="preserve">3.81237268447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80327439308167</t>
   </si>
   <si>
     <t xml:space="preserve">3.77597832679749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97615003585815</t>
+    <t xml:space="preserve">3.97615051269531</t>
   </si>
   <si>
     <t xml:space="preserve">3.94885444641113</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13992786407471</t>
+    <t xml:space="preserve">4.13992834091187</t>
   </si>
   <si>
     <t xml:space="preserve">4.16722440719604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33528280258179</t>
+    <t xml:space="preserve">4.33528327941895</t>
   </si>
   <si>
     <t xml:space="preserve">4.21485948562622</t>
@@ -347,49 +347,49 @@
     <t xml:space="preserve">4.42791748046875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19633197784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16854095458984</t>
+    <t xml:space="preserve">4.19633150100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.168541431427</t>
   </si>
   <si>
     <t xml:space="preserve">4.29822969436646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30749320983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27970218658447</t>
+    <t xml:space="preserve">4.30749225616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27970266342163</t>
   </si>
   <si>
     <t xml:space="preserve">4.3908634185791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40012693405151</t>
+    <t xml:space="preserve">4.40012741088867</t>
   </si>
   <si>
     <t xml:space="preserve">4.35381031036377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08517122268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93695592880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00179958343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97401022911072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03885364532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94621968269348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95548272132874</t>
+    <t xml:space="preserve">4.08517074584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93695569038391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00180006027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97401070594788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03885316848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94621992111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95548343658447</t>
   </si>
   <si>
     <t xml:space="preserve">4.23338556289673</t>
@@ -398,67 +398,67 @@
     <t xml:space="preserve">4.22412157058716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24264860153198</t>
+    <t xml:space="preserve">4.2426495552063</t>
   </si>
   <si>
     <t xml:space="preserve">4.11296129226685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26117563247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91842913627625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89990210533142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89063811302185</t>
+    <t xml:space="preserve">4.26117610931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91842889785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89990282058716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89063882827759</t>
   </si>
   <si>
     <t xml:space="preserve">4.07590770721436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0666446685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79800462722778</t>
+    <t xml:space="preserve">4.06664371490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79800510406494</t>
   </si>
   <si>
     <t xml:space="preserve">3.73316073417664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86284852027893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71463394165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70537066459656</t>
+    <t xml:space="preserve">3.86284899711609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71463441848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70537042617798</t>
   </si>
   <si>
     <t xml:space="preserve">3.77021431922913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39041423797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44599461555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58494567871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68684339523315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60347270965576</t>
+    <t xml:space="preserve">3.39041376113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44599437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58494591712952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68684387207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60347294807434</t>
   </si>
   <si>
     <t xml:space="preserve">3.52010202407837</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37188720703125</t>
+    <t xml:space="preserve">3.37188696861267</t>
   </si>
   <si>
     <t xml:space="preserve">3.46452140808105</t>
@@ -467,16 +467,16 @@
     <t xml:space="preserve">3.53862857818604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5293653011322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45525789260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34409689903259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07545733451843</t>
+    <t xml:space="preserve">3.52936506271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45525765419006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34409666061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07545757293701</t>
   </si>
   <si>
     <t xml:space="preserve">3.14956498146057</t>
@@ -485,19 +485,19 @@
     <t xml:space="preserve">3.29777956008911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31630611419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23293566703796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24219918251038</t>
+    <t xml:space="preserve">3.31630635261536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23293542861938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24219942092896</t>
   </si>
   <si>
     <t xml:space="preserve">3.02914023399353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20514583587646</t>
+    <t xml:space="preserve">3.20514559745789</t>
   </si>
   <si>
     <t xml:space="preserve">3.25146269798279</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">3.10324740409851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15882849693298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91797924041748</t>
+    <t xml:space="preserve">3.1588282585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91797947883606</t>
   </si>
   <si>
     <t xml:space="preserve">2.7419741153717</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">2.77902770042419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87166213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9642961025238</t>
+    <t xml:space="preserve">2.871661901474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96429634094238</t>
   </si>
   <si>
     <t xml:space="preserve">2.85313534736633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83460807800293</t>
+    <t xml:space="preserve">2.83460831642151</t>
   </si>
   <si>
     <t xml:space="preserve">2.84387183189392</t>
@@ -542,46 +542,46 @@
     <t xml:space="preserve">2.76976442337036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63081312179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67713046073914</t>
+    <t xml:space="preserve">2.63081288337708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67712998390198</t>
   </si>
   <si>
     <t xml:space="preserve">2.38070058822632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36217331886292</t>
+    <t xml:space="preserve">2.36217355728149</t>
   </si>
   <si>
     <t xml:space="preserve">2.29732966423035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31585621833801</t>
+    <t xml:space="preserve">2.31585669517517</t>
   </si>
   <si>
     <t xml:space="preserve">2.35291004180908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26953959465027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23248600959778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28806638717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08427047729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1305878162384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22322249412537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24174928665161</t>
+    <t xml:space="preserve">2.26953911781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2324857711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28806614875793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0842707157135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13058805465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22322273254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24174904823303</t>
   </si>
   <si>
     <t xml:space="preserve">2.11206078529358</t>
@@ -596,19 +596,19 @@
     <t xml:space="preserve">1.99163675308228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88047552108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94531905651093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92679262161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16764140129089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13985109329224</t>
+    <t xml:space="preserve">1.88047564029694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94531941413879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92679238319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16764163970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13985133171082</t>
   </si>
   <si>
     <t xml:space="preserve">2.21395874023438</t>
@@ -620,19 +620,19 @@
     <t xml:space="preserve">2.48259806632996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42701768875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38996410369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46583604812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50406551361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65698575973511</t>
+    <t xml:space="preserve">2.42701721191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38996386528015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46583580970764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50406527519226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65698599815369</t>
   </si>
   <si>
     <t xml:space="preserve">2.71433067321777</t>
@@ -647,25 +647,25 @@
     <t xml:space="preserve">2.52318096160889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42760610580444</t>
+    <t xml:space="preserve">2.42760562896729</t>
   </si>
   <si>
     <t xml:space="preserve">2.38937592506409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48495054244995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61875557899475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56141090393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63787078857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73344612121582</t>
+    <t xml:space="preserve">2.48495078086853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61875581741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56141066551208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6378710269928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73344588279724</t>
   </si>
   <si>
     <t xml:space="preserve">2.69521594047546</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">2.75256109237671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80990552902222</t>
+    <t xml:space="preserve">2.80990600585938</t>
   </si>
   <si>
     <t xml:space="preserve">2.82902097702026</t>
@@ -686,28 +686,28 @@
     <t xml:space="preserve">3.05840086936951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86725091934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77167582511902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67610096931458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59964084625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44672083854675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37026071548462</t>
+    <t xml:space="preserve">2.86725068092346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7716760635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.676100730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59964060783386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44672060012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3702609539032</t>
   </si>
   <si>
     <t xml:space="preserve">3.09663105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34512591362</t>
+    <t xml:space="preserve">3.34512639045715</t>
   </si>
   <si>
     <t xml:space="preserve">3.45981597900391</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">3.74654150009155</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76565599441528</t>
+    <t xml:space="preserve">3.76565623283386</t>
   </si>
   <si>
     <t xml:space="preserve">4.01415157318115</t>
@@ -725,13 +725,13 @@
     <t xml:space="preserve">4.1097264289856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97592115402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88034605979919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82300138473511</t>
+    <t xml:space="preserve">3.97592067718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88034629821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82300114631653</t>
   </si>
   <si>
     <t xml:space="preserve">3.44070100784302</t>
@@ -746,13 +746,13 @@
     <t xml:space="preserve">3.68919610977173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72742629051208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7083113193512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57450580596924</t>
+    <t xml:space="preserve">3.72742605209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70831155776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57450604438782</t>
   </si>
   <si>
     <t xml:space="preserve">3.55539107322693</t>
@@ -767,49 +767,49 @@
     <t xml:space="preserve">3.53627634048462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61273646354675</t>
+    <t xml:space="preserve">3.61273622512817</t>
   </si>
   <si>
     <t xml:space="preserve">3.65096616744995</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24955129623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32601094245911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42158603668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30689597129822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38335633277893</t>
+    <t xml:space="preserve">3.24955105781555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32601070404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42158579826355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3068962097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38335609436035</t>
   </si>
   <si>
     <t xml:space="preserve">3.59362125396729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47893118858337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49804615974426</t>
+    <t xml:space="preserve">3.47893095016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49804592132568</t>
   </si>
   <si>
     <t xml:space="preserve">3.28778123855591</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67008090019226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80388617515564</t>
+    <t xml:space="preserve">3.67008113861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80388641357422</t>
   </si>
   <si>
     <t xml:space="preserve">3.93769121170044</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03326559066772</t>
+    <t xml:space="preserve">4.03326606750488</t>
   </si>
   <si>
     <t xml:space="preserve">4.18618679046631</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">4.53025579452515</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51114082336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58760166168213</t>
+    <t xml:space="preserve">4.51114130020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58760213851929</t>
   </si>
   <si>
     <t xml:space="preserve">4.49202632904053</t>
@@ -833,28 +833,28 @@
     <t xml:space="preserve">4.43468141555786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62583208084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74052143096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75963640213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7022910118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68317699432373</t>
+    <t xml:space="preserve">4.62583160400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7405219078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75963592529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70229148864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68317604064941</t>
   </si>
   <si>
     <t xml:space="preserve">4.77875185012817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56848573684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66406154632568</t>
+    <t xml:space="preserve">4.56848621368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66406202316284</t>
   </si>
   <si>
     <t xml:space="preserve">4.72140645980835</t>
@@ -863,13 +863,13 @@
     <t xml:space="preserve">4.87432622909546</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9699010848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92211437225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11326360702515</t>
+    <t xml:space="preserve">4.96990156173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9221134185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1132640838623</t>
   </si>
   <si>
     <t xml:space="preserve">5.16105175018311</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">5.30441427230835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44777631759644</t>
+    <t xml:space="preserve">5.44777679443359</t>
   </si>
   <si>
     <t xml:space="preserve">5.63892698287964</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">5.59113931655884</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81332683563232</t>
+    <t xml:space="preserve">5.81332635879517</t>
   </si>
   <si>
     <t xml:space="preserve">5.71643781661987</t>
@@ -908,31 +908,31 @@
     <t xml:space="preserve">4.8444390296936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82506132125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80568313598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59252834320068</t>
+    <t xml:space="preserve">4.82506084442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80568361282349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59252786636353</t>
   </si>
   <si>
     <t xml:space="preserve">4.55377244949341</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76692771911621</t>
+    <t xml:space="preserve">4.76692819595337</t>
   </si>
   <si>
     <t xml:space="preserve">5.03821659088135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9897723197937</t>
+    <t xml:space="preserve">4.98977184295654</t>
   </si>
   <si>
     <t xml:space="preserve">5.08666086196899</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18354940414429</t>
+    <t xml:space="preserve">5.18354988098145</t>
   </si>
   <si>
     <t xml:space="preserve">4.9413275718689</t>
@@ -941,13 +941,13 @@
     <t xml:space="preserve">5.23199415206909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74755001068115</t>
+    <t xml:space="preserve">4.74754953384399</t>
   </si>
   <si>
     <t xml:space="preserve">5.28043842315674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89288330078125</t>
+    <t xml:space="preserve">4.89288377761841</t>
   </si>
   <si>
     <t xml:space="preserve">4.63128328323364</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">4.53439474105835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67003965377808</t>
+    <t xml:space="preserve">4.67003917694092</t>
   </si>
   <si>
     <t xml:space="preserve">4.78630590438843</t>
@@ -965,31 +965,31 @@
     <t xml:space="preserve">4.72817277908325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70879459381104</t>
+    <t xml:space="preserve">4.70879507064819</t>
   </si>
   <si>
     <t xml:space="preserve">5.91021585464478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61954879760742</t>
+    <t xml:space="preserve">5.61954927444458</t>
   </si>
   <si>
     <t xml:space="preserve">5.32888269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37732791900635</t>
+    <t xml:space="preserve">5.37732744216919</t>
   </si>
   <si>
     <t xml:space="preserve">5.57110452651978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47421598434448</t>
+    <t xml:space="preserve">5.47421646118164</t>
   </si>
   <si>
     <t xml:space="preserve">5.66799354553223</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73376941680908</t>
+    <t xml:space="preserve">6.73376989364624</t>
   </si>
   <si>
     <t xml:space="preserve">6.29777050018311</t>
@@ -998,16 +998,16 @@
     <t xml:space="preserve">6.4431037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68532609939575</t>
+    <t xml:space="preserve">6.68532514572144</t>
   </si>
   <si>
     <t xml:space="preserve">6.5884370803833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63688087463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24932622909546</t>
+    <t xml:space="preserve">6.63688135147095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2493257522583</t>
   </si>
   <si>
     <t xml:space="preserve">6.34621524810791</t>
@@ -1019,28 +1019,28 @@
     <t xml:space="preserve">6.39465951919556</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71999073028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99332523345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09021377563477</t>
+    <t xml:space="preserve">8.71998977661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99332427978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09021282196045</t>
   </si>
   <si>
     <t xml:space="preserve">8.04176807403564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94488000869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84799098968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89643621444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38087749481201</t>
+    <t xml:space="preserve">7.94488096237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84799242019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89643526077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38087940216064</t>
   </si>
   <si>
     <t xml:space="preserve">10.2702112197876</t>
@@ -1052,49 +1052,49 @@
     <t xml:space="preserve">10.173321723938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9795446395874</t>
+    <t xml:space="preserve">9.97954368591309</t>
   </si>
   <si>
     <t xml:space="preserve">10.0764331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2390975952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6266536712646</t>
+    <t xml:space="preserve">11.2390985488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6266527175903</t>
   </si>
   <si>
     <t xml:space="preserve">13.0799856185913</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2737617492676</t>
+    <t xml:space="preserve">13.2737627029419</t>
   </si>
   <si>
     <t xml:space="preserve">12.9830951690674</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4364280700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3395385742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0177612304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1669788360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1930656433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0956745147705</t>
+    <t xml:space="preserve">14.436427116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3395395278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0177602767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1669807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1930646896362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0956735610962</t>
   </si>
   <si>
     <t xml:space="preserve">14.9008903503418</t>
   </si>
   <si>
-    <t xml:space="preserve">13.634801864624</t>
+    <t xml:space="preserve">13.6348028182983</t>
   </si>
   <si>
     <t xml:space="preserve">12.0765390396118</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">12.4661045074463</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4400205612183</t>
+    <t xml:space="preserve">13.4400196075439</t>
   </si>
   <si>
     <t xml:space="preserve">13.9269771575928</t>
@@ -1112,13 +1112,13 @@
     <t xml:space="preserve">14.0243673324585</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2191524505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8034992218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.413932800293</t>
+    <t xml:space="preserve">14.2191514968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8035001754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4139337539673</t>
   </si>
   <si>
     <t xml:space="preserve">14.6087160110474</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">14.706109046936</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5113248825073</t>
+    <t xml:space="preserve">14.5113258361816</t>
   </si>
   <si>
     <t xml:space="preserve">13.3426275253296</t>
@@ -1136,25 +1136,25 @@
     <t xml:space="preserve">14.1217584609985</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3165426254272</t>
+    <t xml:space="preserve">14.3165416717529</t>
   </si>
   <si>
     <t xml:space="preserve">13.8295841217041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5374097824097</t>
+    <t xml:space="preserve">13.537410736084</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452363967896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8556709289551</t>
+    <t xml:space="preserve">12.8556699752808</t>
   </si>
   <si>
     <t xml:space="preserve">12.3687133789062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7582788467407</t>
+    <t xml:space="preserve">12.7582778930664</t>
   </si>
   <si>
     <t xml:space="preserve">12.5634965896606</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">12.1739301681519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6869745254517</t>
+    <t xml:space="preserve">11.6869735717773</t>
   </si>
   <si>
     <t xml:space="preserve">11.1026239395142</t>
@@ -1175,46 +1175,46 @@
     <t xml:space="preserve">10.7130584716797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2000160217285</t>
+    <t xml:space="preserve">11.2000169754028</t>
   </si>
   <si>
     <t xml:space="preserve">11.9791479110718</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8817558288574</t>
+    <t xml:space="preserve">11.8817548751831</t>
   </si>
   <si>
     <t xml:space="preserve">10.9078416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2974071502686</t>
+    <t xml:space="preserve">11.2974081039429</t>
   </si>
   <si>
     <t xml:space="preserve">11.3947982788086</t>
   </si>
   <si>
-    <t xml:space="preserve">11.589581489563</t>
+    <t xml:space="preserve">11.5895805358887</t>
   </si>
   <si>
     <t xml:space="preserve">11.0052328109741</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7843647003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4921903610229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8104515075684</t>
+    <t xml:space="preserve">11.7843656539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4921913146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.810450553894</t>
   </si>
   <si>
     <t xml:space="preserve">10.4208841323853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2261009216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3234939575195</t>
+    <t xml:space="preserve">10.2261018753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3234949111938</t>
   </si>
   <si>
     <t xml:space="preserve">10.1287097930908</t>
@@ -1226,16 +1226,16 @@
     <t xml:space="preserve">9.73914432525635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54436206817627</t>
+    <t xml:space="preserve">9.54436111450195</t>
   </si>
   <si>
     <t xml:space="preserve">9.8365364074707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34957885742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49566650390625</t>
+    <t xml:space="preserve">9.34957981109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49566459655762</t>
   </si>
   <si>
     <t xml:space="preserve">12.2713222503662</t>
@@ -1244,22 +1244,22 @@
     <t xml:space="preserve">12.9530620574951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6800222396851</t>
+    <t xml:space="preserve">15.6800231933594</t>
   </si>
   <si>
     <t xml:space="preserve">13.7321939468384</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1704559326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3652372360229</t>
+    <t xml:space="preserve">14.1704549789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3652381896973</t>
   </si>
   <si>
     <t xml:space="preserve">14.0730638504028</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1443700790405</t>
+    <t xml:space="preserve">15.1443691253662</t>
   </si>
   <si>
     <t xml:space="preserve">15.5364561080933</t>
@@ -1277,10 +1277,10 @@
     <t xml:space="preserve">15.4874458312988</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4384346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2423906326294</t>
+    <t xml:space="preserve">15.4384355545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2423915863037</t>
   </si>
   <si>
     <t xml:space="preserve">15.3894233703613</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">15.0463485717773</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6542596817017</t>
+    <t xml:space="preserve">14.654260635376</t>
   </si>
   <si>
     <t xml:space="preserve">13.9190969467163</t>
@@ -1310,19 +1310,19 @@
     <t xml:space="preserve">13.8210754394531</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3601951599121</t>
+    <t xml:space="preserve">14.3601942062378</t>
   </si>
   <si>
     <t xml:space="preserve">13.6250314712524</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8700847625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6740417480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7720651626587</t>
+    <t xml:space="preserve">13.8700857162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6740427017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7720642089844</t>
   </si>
   <si>
     <t xml:space="preserve">14.0171184539795</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">14.7032709121704</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5562391281128</t>
+    <t xml:space="preserve">14.5562381744385</t>
   </si>
   <si>
     <t xml:space="preserve">14.507227897644</t>
@@ -1370,13 +1370,13 @@
     <t xml:space="preserve">13.2819557189941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8898668289185</t>
+    <t xml:space="preserve">12.8898677825928</t>
   </si>
   <si>
     <t xml:space="preserve">12.7428350448608</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9878902435303</t>
+    <t xml:space="preserve">12.987889289856</t>
   </si>
   <si>
     <t xml:space="preserve">13.1349220275879</t>
@@ -1388,19 +1388,19 @@
     <t xml:space="preserve">11.7626171112061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3215188980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.301736831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0859117507935</t>
+    <t xml:space="preserve">11.3215198516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3017377853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0859127044678</t>
   </si>
   <si>
     <t xml:space="preserve">13.4289875030518</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8305225372314</t>
+    <t xml:space="preserve">15.8305215835571</t>
   </si>
   <si>
     <t xml:space="preserve">15.7324991226196</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">15.9775552749634</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3696422576904</t>
+    <t xml:space="preserve">16.3696441650391</t>
   </si>
   <si>
     <t xml:space="preserve">15.6834897994995</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">15.7815113067627</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2226104736328</t>
+    <t xml:space="preserve">16.2226085662842</t>
   </si>
   <si>
     <t xml:space="preserve">16.0265655517578</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">15.9285440444946</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1735992431641</t>
+    <t xml:space="preserve">16.1735973358154</t>
   </si>
   <si>
     <t xml:space="preserve">16.2716197967529</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">19.0162296295166</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7023849487305</t>
+    <t xml:space="preserve">19.7023830413818</t>
   </si>
   <si>
     <t xml:space="preserve">19.604362487793</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">21.3687534332275</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6430377960205</t>
+    <t xml:space="preserve">22.6430397033691</t>
   </si>
   <si>
     <t xml:space="preserve">24.9955615997314</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">25.2896251678467</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6034736633301</t>
+    <t xml:space="preserve">24.6034755706787</t>
   </si>
   <si>
     <t xml:space="preserve">24.8975391387939</t>
@@ -1508,13 +1508,13 @@
     <t xml:space="preserve">24.5054531097412</t>
   </si>
   <si>
-    <t xml:space="preserve">24.015344619751</t>
+    <t xml:space="preserve">24.0153427124023</t>
   </si>
   <si>
     <t xml:space="preserve">23.623254776001</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8390808105469</t>
+    <t xml:space="preserve">22.8390789031982</t>
   </si>
   <si>
     <t xml:space="preserve">23.3291893005371</t>
@@ -1529,16 +1529,16 @@
     <t xml:space="preserve">24.1133651733398</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0351238250732</t>
+    <t xml:space="preserve">23.0351257324219</t>
   </si>
   <si>
     <t xml:space="preserve">23.1331462860107</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2113857269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4074306488037</t>
+    <t xml:space="preserve">24.2113876342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4074287414551</t>
   </si>
   <si>
     <t xml:space="preserve">23.819299697876</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">18.7711753845215</t>
   </si>
   <si>
-    <t xml:space="preserve">18.330078125</t>
+    <t xml:space="preserve">18.3300800323486</t>
   </si>
   <si>
     <t xml:space="preserve">17.6439247131348</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">20.1924934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8984260559082</t>
+    <t xml:space="preserve">19.8984279632568</t>
   </si>
   <si>
     <t xml:space="preserve">20.3885345458984</t>
@@ -58036,7 +58036,7 @@
     </row>
     <row r="2138">
       <c r="A2138" s="1" t="n">
-        <v>46003.4068402778</v>
+        <v>46003.3333333333</v>
       </c>
       <c r="B2138" t="n">
         <v>125</v>

--- a/data/CULT.MI.xlsx
+++ b/data/CULT.MI.xlsx
@@ -38,46 +38,46 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68585205078125</t>
+    <t xml:space="preserve">4.68585300445557</t>
   </si>
   <si>
     <t xml:space="preserve">CULT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57666730880737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59486484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60851335525513</t>
+    <t xml:space="preserve">4.57666778564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5948657989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60851240158081</t>
   </si>
   <si>
     <t xml:space="preserve">4.58576631546021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48931980133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56301975250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51297569274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46020364761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29824638366699</t>
+    <t xml:space="preserve">4.48932027816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56301832199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51297616958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46020317077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29824590682983</t>
   </si>
   <si>
     <t xml:space="preserve">4.21271800994873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18178272247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23091506958008</t>
+    <t xml:space="preserve">4.18178224563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23091554641724</t>
   </si>
   <si>
     <t xml:space="preserve">4.36375665664673</t>
@@ -86,13 +86,13 @@
     <t xml:space="preserve">4.38195514678955</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35101842880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.289146900177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24183368682861</t>
+    <t xml:space="preserve">4.35101890563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28914737701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24183416366577</t>
   </si>
   <si>
     <t xml:space="preserve">4.22909545898438</t>
@@ -110,16 +110,16 @@
     <t xml:space="preserve">3.99616765975952</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04712104797363</t>
+    <t xml:space="preserve">4.04712057113647</t>
   </si>
   <si>
     <t xml:space="preserve">4.03984117507935</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96341180801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07441759109497</t>
+    <t xml:space="preserve">3.96341252326965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07441711425781</t>
   </si>
   <si>
     <t xml:space="preserve">4.32008266448975</t>
@@ -128,16 +128,16 @@
     <t xml:space="preserve">4.24911308288574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97979068756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06895780563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05439901351929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98524951934814</t>
+    <t xml:space="preserve">3.97978973388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0689582824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05439949035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9852499961853</t>
   </si>
   <si>
     <t xml:space="preserve">4.05076026916504</t>
@@ -146,28 +146,28 @@
     <t xml:space="preserve">4.07259702682495</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0380220413208</t>
+    <t xml:space="preserve">4.03802251815796</t>
   </si>
   <si>
     <t xml:space="preserve">4.04530096054077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03074264526367</t>
+    <t xml:space="preserve">4.03074312210083</t>
   </si>
   <si>
     <t xml:space="preserve">4.01254558563232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04894113540649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05985879898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07623720169067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9124596118927</t>
+    <t xml:space="preserve">4.04894065856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05985927581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07623672485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91245913505554</t>
   </si>
   <si>
     <t xml:space="preserve">3.99070811271667</t>
@@ -176,34 +176,34 @@
     <t xml:space="preserve">4.01072597503662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92155814170837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00162696838379</t>
+    <t xml:space="preserve">3.92155790328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00162649154663</t>
   </si>
   <si>
     <t xml:space="preserve">4.05803918838501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21635675430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2218165397644</t>
+    <t xml:space="preserve">4.21635770797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22181701660156</t>
   </si>
   <si>
     <t xml:space="preserve">4.18542146682739</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16176462173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35465812683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28186750411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26731109619141</t>
+    <t xml:space="preserve">4.16176414489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3546576499939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28186893463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26731014251709</t>
   </si>
   <si>
     <t xml:space="preserve">4.39287328720093</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">4.27458906173706</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31826305389404</t>
+    <t xml:space="preserve">4.31826257705688</t>
   </si>
   <si>
     <t xml:space="preserve">4.35647821426392</t>
@@ -230,13 +230,13 @@
     <t xml:space="preserve">4.26367044448853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27640962600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14902639389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35829734802246</t>
+    <t xml:space="preserve">4.27640867233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14902687072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35829782485962</t>
   </si>
   <si>
     <t xml:space="preserve">4.35283851623535</t>
@@ -245,13 +245,13 @@
     <t xml:space="preserve">4.29460620880127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2036190032959</t>
+    <t xml:space="preserve">4.20361852645874</t>
   </si>
   <si>
     <t xml:space="preserve">4.24001455307007</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34009981155396</t>
+    <t xml:space="preserve">4.34010028839111</t>
   </si>
   <si>
     <t xml:space="preserve">4.42926836013794</t>
@@ -260,91 +260,91 @@
     <t xml:space="preserve">4.34919929504395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33646011352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33100175857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32190227508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4674825668335</t>
+    <t xml:space="preserve">4.33646059036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33100128173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32190275192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46748208999634</t>
   </si>
   <si>
     <t xml:space="preserve">4.45838403701782</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2855076789856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83057045936584</t>
+    <t xml:space="preserve">4.28550815582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83057069778442</t>
   </si>
   <si>
     <t xml:space="preserve">3.90336084365845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88516354560852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87606477737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00344705581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93065714836121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99434804916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08533477783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96705150604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86696577072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84876799583435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8578667640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81237292289734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80327439308167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77597832679749</t>
+    <t xml:space="preserve">3.88516330718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87606501579285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00344657897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93065667152405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99434757232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08533525466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96705222129822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86696529388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84876823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85786700248718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8123733997345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80327391624451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77597808837891</t>
   </si>
   <si>
     <t xml:space="preserve">3.97615051269531</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94885492324829</t>
+    <t xml:space="preserve">3.94885420799255</t>
   </si>
   <si>
     <t xml:space="preserve">4.13992786407471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16722345352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33528280258179</t>
+    <t xml:space="preserve">4.16722440719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33528327941895</t>
   </si>
   <si>
     <t xml:space="preserve">4.21485900878906</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31675672531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42791748046875</t>
+    <t xml:space="preserve">4.31675720214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42791795730591</t>
   </si>
   <si>
     <t xml:space="preserve">4.19633150100708</t>
@@ -353,61 +353,61 @@
     <t xml:space="preserve">4.168541431427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29822969436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30749273300171</t>
+    <t xml:space="preserve">4.29823017120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30749368667603</t>
   </si>
   <si>
     <t xml:space="preserve">4.27970266342163</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3908634185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40012693405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35381078720093</t>
+    <t xml:space="preserve">4.39086437225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40012741088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35380983352661</t>
   </si>
   <si>
     <t xml:space="preserve">4.08517074584961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93695616722107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00180006027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97401022911072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03885364532471</t>
+    <t xml:space="preserve">3.93695569038391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00179958343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97400975227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03885412216187</t>
   </si>
   <si>
     <t xml:space="preserve">3.94621992111206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95548319816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23338556289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22412157058716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24264860153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11296081542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26117563247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91842889785767</t>
+    <t xml:space="preserve">3.95548272132874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23338603973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22412252426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2426495552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11296033859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26117610931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91842913627625</t>
   </si>
   <si>
     <t xml:space="preserve">3.89990234375</t>
@@ -422,16 +422,16 @@
     <t xml:space="preserve">4.06664419174194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7980043888092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73316073417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86284852027893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71463370323181</t>
+    <t xml:space="preserve">3.79800462722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73316049575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86284828186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71463394165039</t>
   </si>
   <si>
     <t xml:space="preserve">3.70537042617798</t>
@@ -440,55 +440,55 @@
     <t xml:space="preserve">3.77021455764771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3904139995575</t>
+    <t xml:space="preserve">3.39041423797607</t>
   </si>
   <si>
     <t xml:space="preserve">3.44599461555481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58494544029236</t>
+    <t xml:space="preserve">3.58494567871094</t>
   </si>
   <si>
     <t xml:space="preserve">3.68684339523315</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60347270965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52010178565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37188696861267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46452140808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53862881660461</t>
+    <t xml:space="preserve">3.60347294807434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52010202407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37188744544983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46452164649963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53862857818604</t>
   </si>
   <si>
     <t xml:space="preserve">3.5293653011322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45525765419006</t>
+    <t xml:space="preserve">3.45525789260864</t>
   </si>
   <si>
     <t xml:space="preserve">3.34409666061401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07545757293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14956474304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29777956008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31630611419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23293566703796</t>
+    <t xml:space="preserve">3.07545733451843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14956521987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29777932167053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31630635261536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23293542861938</t>
   </si>
   <si>
     <t xml:space="preserve">3.2421989440918</t>
@@ -497,28 +497,28 @@
     <t xml:space="preserve">3.02914023399353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20514559745789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25146245956421</t>
+    <t xml:space="preserve">3.20514512062073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25146269798279</t>
   </si>
   <si>
     <t xml:space="preserve">3.10324764251709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1588282585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91797924041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74197459220886</t>
+    <t xml:space="preserve">3.15882849693298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9179790019989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74197435379028</t>
   </si>
   <si>
     <t xml:space="preserve">2.77902793884277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87166237831116</t>
+    <t xml:space="preserve">2.87166213989258</t>
   </si>
   <si>
     <t xml:space="preserve">2.96429634094238</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">2.85313510894775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83460831642151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8438720703125</t>
+    <t xml:space="preserve">2.83460855484009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84387183189392</t>
   </si>
   <si>
     <t xml:space="preserve">2.72344732284546</t>
@@ -542,19 +542,19 @@
     <t xml:space="preserve">2.76976442337036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63081312179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67713046073914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38070011138916</t>
+    <t xml:space="preserve">2.63081288337708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67712998390198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38070034980774</t>
   </si>
   <si>
     <t xml:space="preserve">2.36217379570007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29732942581177</t>
+    <t xml:space="preserve">2.29732966423035</t>
   </si>
   <si>
     <t xml:space="preserve">2.31585645675659</t>
@@ -569,13 +569,13 @@
     <t xml:space="preserve">2.2324857711792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28806638717651</t>
+    <t xml:space="preserve">2.28806662559509</t>
   </si>
   <si>
     <t xml:space="preserve">2.0842707157135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1305878162384</t>
+    <t xml:space="preserve">2.13058805465698</t>
   </si>
   <si>
     <t xml:space="preserve">2.22322249412537</t>
@@ -584,55 +584,55 @@
     <t xml:space="preserve">2.24174928665161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11206078529358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17690539360046</t>
+    <t xml:space="preserve">2.11206126213074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17690491676331</t>
   </si>
   <si>
     <t xml:space="preserve">2.03795385360718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99163675308228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88047552108765</t>
+    <t xml:space="preserve">1.9916365146637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88047564029694</t>
   </si>
   <si>
     <t xml:space="preserve">1.9453192949295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92679262161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16764140129089</t>
+    <t xml:space="preserve">1.92679226398468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16764163970947</t>
   </si>
   <si>
     <t xml:space="preserve">2.13985133171082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21395874023438</t>
+    <t xml:space="preserve">2.21395897865295</t>
   </si>
   <si>
     <t xml:space="preserve">2.4084906578064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48259830474854</t>
+    <t xml:space="preserve">2.48259806632996</t>
   </si>
   <si>
     <t xml:space="preserve">2.42701745033264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38996386528015</t>
+    <t xml:space="preserve">2.38996410369873</t>
   </si>
   <si>
     <t xml:space="preserve">2.46583604812622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50406575202942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65698575973511</t>
+    <t xml:space="preserve">2.50406551361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65698552131653</t>
   </si>
   <si>
     <t xml:space="preserve">2.71433067321777</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">2.73344564437866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69521594047546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75256109237671</t>
+    <t xml:space="preserve">2.69521570205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75256061553955</t>
   </si>
   <si>
     <t xml:space="preserve">2.8099057674408</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">2.82902097702026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84813570976257</t>
+    <t xml:space="preserve">2.84813594818115</t>
   </si>
   <si>
     <t xml:space="preserve">3.05840086936951</t>
@@ -692,13 +692,13 @@
     <t xml:space="preserve">2.7716760635376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67610096931458</t>
+    <t xml:space="preserve">2.676100730896</t>
   </si>
   <si>
     <t xml:space="preserve">2.59964084625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44672060012817</t>
+    <t xml:space="preserve">2.44672083854675</t>
   </si>
   <si>
     <t xml:space="preserve">2.3702609539032</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">3.74654150009155</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76565599441528</t>
+    <t xml:space="preserve">3.76565647125244</t>
   </si>
   <si>
     <t xml:space="preserve">4.01415109634399</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">4.1097264289856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97592115402222</t>
+    <t xml:space="preserve">3.97592067718506</t>
   </si>
   <si>
     <t xml:space="preserve">3.88034629821777</t>
@@ -734,19 +734,19 @@
     <t xml:space="preserve">3.82300114631653</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4407012462616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40247106552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36424088478088</t>
+    <t xml:space="preserve">3.44070100784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40247082710266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36424112319946</t>
   </si>
   <si>
     <t xml:space="preserve">3.68919610977173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72742629051208</t>
+    <t xml:space="preserve">3.72742605209351</t>
   </si>
   <si>
     <t xml:space="preserve">3.7083113193512</t>
@@ -755,34 +755,34 @@
     <t xml:space="preserve">3.57450604438782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55539083480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51716089248657</t>
+    <t xml:space="preserve">3.55539107322693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51716113090515</t>
   </si>
   <si>
     <t xml:space="preserve">3.63185119628906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5362765789032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61273598670959</t>
+    <t xml:space="preserve">3.53627634048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61273622512817</t>
   </si>
   <si>
     <t xml:space="preserve">3.65096592903137</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24955129623413</t>
+    <t xml:space="preserve">3.24955105781555</t>
   </si>
   <si>
     <t xml:space="preserve">3.32601094245911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42158579826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3068962097168</t>
+    <t xml:space="preserve">3.42158603668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30689597129822</t>
   </si>
   <si>
     <t xml:space="preserve">3.38335633277893</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">3.59362149238586</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47893118858337</t>
+    <t xml:space="preserve">3.47893095016479</t>
   </si>
   <si>
     <t xml:space="preserve">3.49804639816284</t>
@@ -806,46 +806,46 @@
     <t xml:space="preserve">3.80388617515564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93769121170044</t>
+    <t xml:space="preserve">3.9376916885376</t>
   </si>
   <si>
     <t xml:space="preserve">4.03326559066772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18618679046631</t>
+    <t xml:space="preserve">4.18618631362915</t>
   </si>
   <si>
     <t xml:space="preserve">4.30087614059448</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5302562713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51114130020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58760118484497</t>
+    <t xml:space="preserve">4.53025579452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51114082336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58760213851929</t>
   </si>
   <si>
     <t xml:space="preserve">4.49202585220337</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43468141555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62583160400391</t>
+    <t xml:space="preserve">4.43468189239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62583208084106</t>
   </si>
   <si>
     <t xml:space="preserve">4.7405219078064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75963640213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7022910118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68317699432373</t>
+    <t xml:space="preserve">4.75963592529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70229196548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68317651748657</t>
   </si>
   <si>
     <t xml:space="preserve">4.77875185012817</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">4.66406202316284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72140645980835</t>
+    <t xml:space="preserve">4.72140693664551</t>
   </si>
   <si>
     <t xml:space="preserve">4.87432670593262</t>
@@ -866,55 +866,55 @@
     <t xml:space="preserve">4.96990156173706</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92211389541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11326360702515</t>
+    <t xml:space="preserve">4.92211437225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1132640838623</t>
   </si>
   <si>
     <t xml:space="preserve">5.16105175018311</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20883941650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25662660598755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30441474914551</t>
+    <t xml:space="preserve">5.20883989334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25662612915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30441427230835</t>
   </si>
   <si>
     <t xml:space="preserve">5.44777679443359</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6389274597168</t>
+    <t xml:space="preserve">5.63892698287964</t>
   </si>
   <si>
     <t xml:space="preserve">5.59113883972168</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81332635879517</t>
+    <t xml:space="preserve">5.81332683563232</t>
   </si>
   <si>
     <t xml:space="preserve">5.71643829345703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42577123641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13510608673096</t>
+    <t xml:space="preserve">5.42577171325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1351056098938</t>
   </si>
   <si>
     <t xml:space="preserve">4.8444390296936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82506084442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80568361282349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59252834320068</t>
+    <t xml:space="preserve">4.82506132125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80568313598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59252786636353</t>
   </si>
   <si>
     <t xml:space="preserve">4.55377197265625</t>
@@ -926,10 +926,10 @@
     <t xml:space="preserve">5.03821659088135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98977184295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08666133880615</t>
+    <t xml:space="preserve">4.9897723197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08666086196899</t>
   </si>
   <si>
     <t xml:space="preserve">5.18354940414429</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">4.9413275718689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23199415206909</t>
+    <t xml:space="preserve">5.23199462890625</t>
   </si>
   <si>
     <t xml:space="preserve">4.74755001068115</t>
@@ -947,25 +947,25 @@
     <t xml:space="preserve">5.28043842315674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89288330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6312837600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53439426422119</t>
+    <t xml:space="preserve">4.89288282394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63128423690796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53439474105835</t>
   </si>
   <si>
     <t xml:space="preserve">4.67003917694092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78630590438843</t>
+    <t xml:space="preserve">4.78630638122559</t>
   </si>
   <si>
     <t xml:space="preserve">4.72817277908325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70879554748535</t>
+    <t xml:space="preserve">4.70879507064819</t>
   </si>
   <si>
     <t xml:space="preserve">5.91021537780762</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">5.32888269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37732744216919</t>
+    <t xml:space="preserve">5.37732696533203</t>
   </si>
   <si>
     <t xml:space="preserve">5.57110500335693</t>
@@ -986,13 +986,13 @@
     <t xml:space="preserve">5.47421598434448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66799354553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7337703704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29777050018311</t>
+    <t xml:space="preserve">5.66799306869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73376989364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29777097702026</t>
   </si>
   <si>
     <t xml:space="preserve">6.4431037902832</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">6.68532562255859</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5884370803833</t>
+    <t xml:space="preserve">6.58843755722046</t>
   </si>
   <si>
     <t xml:space="preserve">6.63688087463379</t>
@@ -1010,25 +1010,25 @@
     <t xml:space="preserve">6.24932622909546</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34621477127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53999280929565</t>
+    <t xml:space="preserve">6.34621524810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5399923324585</t>
   </si>
   <si>
     <t xml:space="preserve">6.3946590423584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71998977661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99332523345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09021282196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04176902770996</t>
+    <t xml:space="preserve">8.71999073028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99332427978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09021377563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04176807403564</t>
   </si>
   <si>
     <t xml:space="preserve">7.94488000869751</t>
@@ -1040,19 +1040,19 @@
     <t xml:space="preserve">7.89643621444702</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38087940216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2702121734619</t>
+    <t xml:space="preserve">8.38087844848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2702112197876</t>
   </si>
   <si>
     <t xml:space="preserve">9.88265514373779</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1733226776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97954368591309</t>
+    <t xml:space="preserve">10.173321723938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9795446395874</t>
   </si>
   <si>
     <t xml:space="preserve">10.0764331817627</t>
@@ -1061,40 +1061,40 @@
     <t xml:space="preserve">11.2390985488892</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6266527175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0799856185913</t>
+    <t xml:space="preserve">11.6266536712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.079984664917</t>
   </si>
   <si>
     <t xml:space="preserve">13.2737617492676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9830951690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4364290237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3395404815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0177602767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1669807434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1930646896362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0956735610962</t>
+    <t xml:space="preserve">12.9830961227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4364280700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3395385742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0177612304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1669788360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1930656433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0956745147705</t>
   </si>
   <si>
     <t xml:space="preserve">14.9008903503418</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6348028182983</t>
+    <t xml:space="preserve">13.634801864624</t>
   </si>
   <si>
     <t xml:space="preserve">12.0765390396118</t>
@@ -1112,13 +1112,13 @@
     <t xml:space="preserve">14.0243673324585</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2191514968872</t>
+    <t xml:space="preserve">14.2191524505615</t>
   </si>
   <si>
     <t xml:space="preserve">14.8035001754761</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4139337539673</t>
+    <t xml:space="preserve">14.413932800293</t>
   </si>
   <si>
     <t xml:space="preserve">14.6087160110474</t>
@@ -1127,25 +1127,25 @@
     <t xml:space="preserve">14.706109046936</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5113258361816</t>
+    <t xml:space="preserve">14.5113248825073</t>
   </si>
   <si>
     <t xml:space="preserve">13.3426275253296</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1217584609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3165416717529</t>
+    <t xml:space="preserve">14.1217594146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3165426254272</t>
   </si>
   <si>
     <t xml:space="preserve">13.8295841217041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.537410736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2452363967896</t>
+    <t xml:space="preserve">13.5374097824097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2452373504639</t>
   </si>
   <si>
     <t xml:space="preserve">12.8556699752808</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">12.3687133789062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7582778930664</t>
+    <t xml:space="preserve">12.7582788467407</t>
   </si>
   <si>
     <t xml:space="preserve">12.5634965896606</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">12.1739301681519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6869735717773</t>
+    <t xml:space="preserve">11.6869745254517</t>
   </si>
   <si>
     <t xml:space="preserve">11.1026239395142</t>
@@ -1187,19 +1187,19 @@
     <t xml:space="preserve">10.9078416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2974081039429</t>
+    <t xml:space="preserve">11.2974071502686</t>
   </si>
   <si>
     <t xml:space="preserve">11.3947982788086</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5895805358887</t>
+    <t xml:space="preserve">11.589581489563</t>
   </si>
   <si>
     <t xml:space="preserve">11.0052328109741</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7843656539917</t>
+    <t xml:space="preserve">11.7843647003174</t>
   </si>
   <si>
     <t xml:space="preserve">11.4921913146973</t>
@@ -1211,10 +1211,10 @@
     <t xml:space="preserve">10.4208841323853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2261018753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3234949111938</t>
+    <t xml:space="preserve">10.2261009216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3234939575195</t>
   </si>
   <si>
     <t xml:space="preserve">10.1287097930908</t>
@@ -1226,16 +1226,16 @@
     <t xml:space="preserve">9.73914432525635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54436111450195</t>
+    <t xml:space="preserve">9.54436206817627</t>
   </si>
   <si>
     <t xml:space="preserve">9.8365364074707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34957981109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49566459655762</t>
+    <t xml:space="preserve">9.34957885742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49566555023193</t>
   </si>
   <si>
     <t xml:space="preserve">12.2713222503662</t>
@@ -1250,16 +1250,16 @@
     <t xml:space="preserve">13.7321939468384</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1704549789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3652381896973</t>
+    <t xml:space="preserve">14.1704559326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3652372360229</t>
   </si>
   <si>
     <t xml:space="preserve">14.0730638504028</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1443691253662</t>
+    <t xml:space="preserve">15.1443700790405</t>
   </si>
   <si>
     <t xml:space="preserve">15.5364561080933</t>
@@ -1277,10 +1277,10 @@
     <t xml:space="preserve">15.4874458312988</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4384355545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2423915863037</t>
+    <t xml:space="preserve">15.4384346008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2423906326294</t>
   </si>
   <si>
     <t xml:space="preserve">15.3894233703613</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">15.0463485717773</t>
   </si>
   <si>
-    <t xml:space="preserve">14.654260635376</t>
+    <t xml:space="preserve">14.6542596817017</t>
   </si>
   <si>
     <t xml:space="preserve">13.9190969467163</t>
@@ -1310,19 +1310,19 @@
     <t xml:space="preserve">13.8210754394531</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3601942062378</t>
+    <t xml:space="preserve">14.3601951599121</t>
   </si>
   <si>
     <t xml:space="preserve">13.6250314712524</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8700857162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6740427017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7720642089844</t>
+    <t xml:space="preserve">13.8700847625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6740417480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7720651626587</t>
   </si>
   <si>
     <t xml:space="preserve">14.0171184539795</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">14.7032709121704</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5562381744385</t>
+    <t xml:space="preserve">14.5562391281128</t>
   </si>
   <si>
     <t xml:space="preserve">14.507227897644</t>
@@ -1370,13 +1370,13 @@
     <t xml:space="preserve">13.2819557189941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8898677825928</t>
+    <t xml:space="preserve">12.8898668289185</t>
   </si>
   <si>
     <t xml:space="preserve">12.7428350448608</t>
   </si>
   <si>
-    <t xml:space="preserve">12.987889289856</t>
+    <t xml:space="preserve">12.9878902435303</t>
   </si>
   <si>
     <t xml:space="preserve">13.1349220275879</t>
@@ -1388,19 +1388,19 @@
     <t xml:space="preserve">11.7626171112061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3215198516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3017377853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0859127044678</t>
+    <t xml:space="preserve">11.3215188980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.301736831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0859117507935</t>
   </si>
   <si>
     <t xml:space="preserve">13.4289875030518</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8305215835571</t>
+    <t xml:space="preserve">15.8305225372314</t>
   </si>
   <si>
     <t xml:space="preserve">15.7324991226196</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">15.9775552749634</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3696441650391</t>
+    <t xml:space="preserve">16.3696422576904</t>
   </si>
   <si>
     <t xml:space="preserve">15.6834897994995</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">15.7815113067627</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2226085662842</t>
+    <t xml:space="preserve">16.2226104736328</t>
   </si>
   <si>
     <t xml:space="preserve">16.0265655517578</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">15.9285440444946</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1735973358154</t>
+    <t xml:space="preserve">16.1735992431641</t>
   </si>
   <si>
     <t xml:space="preserve">16.2716197967529</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">19.0162296295166</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7023830413818</t>
+    <t xml:space="preserve">19.7023849487305</t>
   </si>
   <si>
     <t xml:space="preserve">19.604362487793</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">21.3687534332275</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6430397033691</t>
+    <t xml:space="preserve">22.6430377960205</t>
   </si>
   <si>
     <t xml:space="preserve">24.9955615997314</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">25.2896251678467</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6034755706787</t>
+    <t xml:space="preserve">24.6034736633301</t>
   </si>
   <si>
     <t xml:space="preserve">24.8975391387939</t>
@@ -1508,13 +1508,13 @@
     <t xml:space="preserve">24.5054531097412</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0153427124023</t>
+    <t xml:space="preserve">24.015344619751</t>
   </si>
   <si>
     <t xml:space="preserve">23.623254776001</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8390789031982</t>
+    <t xml:space="preserve">22.8390808105469</t>
   </si>
   <si>
     <t xml:space="preserve">23.3291893005371</t>
@@ -1529,16 +1529,16 @@
     <t xml:space="preserve">24.1133651733398</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0351257324219</t>
+    <t xml:space="preserve">23.0351238250732</t>
   </si>
   <si>
     <t xml:space="preserve">23.1331462860107</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2113876342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4074287414551</t>
+    <t xml:space="preserve">24.2113857269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4074306488037</t>
   </si>
   <si>
     <t xml:space="preserve">23.819299697876</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">18.7711753845215</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3300800323486</t>
+    <t xml:space="preserve">18.330078125</t>
   </si>
   <si>
     <t xml:space="preserve">17.6439247131348</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">20.1924934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8984279632568</t>
+    <t xml:space="preserve">19.8984260559082</t>
   </si>
   <si>
     <t xml:space="preserve">20.3885345458984</t>
@@ -58221,7 +58221,7 @@
     </row>
     <row r="2145">
       <c r="A2145" s="1" t="n">
-        <v>46014.6912731481</v>
+        <v>46014.3333333333</v>
       </c>
       <c r="B2145" t="n">
         <v>41375</v>

--- a/data/CULT.MI.xlsx
+++ b/data/CULT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="711">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68585205078125</t>
+    <t xml:space="preserve">4.68585252761841</t>
   </si>
   <si>
     <t xml:space="preserve">CULT.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">4.57666826248169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59486436843872</t>
+    <t xml:space="preserve">4.59486484527588</t>
   </si>
   <si>
     <t xml:space="preserve">4.60851335525513</t>
@@ -56,22 +56,22 @@
     <t xml:space="preserve">4.58576679229736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48931980133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56301927566528</t>
+    <t xml:space="preserve">4.48931932449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56301975250244</t>
   </si>
   <si>
     <t xml:space="preserve">4.51297616958618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46020412445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29824638366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21271753311157</t>
+    <t xml:space="preserve">4.46020317077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29824590682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21271800994873</t>
   </si>
   <si>
     <t xml:space="preserve">4.18178224563599</t>
@@ -80,19 +80,19 @@
     <t xml:space="preserve">4.23091554641724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36375665664673</t>
+    <t xml:space="preserve">4.36375713348389</t>
   </si>
   <si>
     <t xml:space="preserve">4.38195466995239</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35101842880249</t>
+    <t xml:space="preserve">4.35101938247681</t>
   </si>
   <si>
     <t xml:space="preserve">4.28914737701416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24183464050293</t>
+    <t xml:space="preserve">4.24183416366577</t>
   </si>
   <si>
     <t xml:space="preserve">4.22909545898438</t>
@@ -101,10 +101,10 @@
     <t xml:space="preserve">4.10535287857056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09443473815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1089916229248</t>
+    <t xml:space="preserve">4.09443426132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10899209976196</t>
   </si>
   <si>
     <t xml:space="preserve">3.99616765975952</t>
@@ -116,10 +116,10 @@
     <t xml:space="preserve">4.0398416519165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96341180801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07441759109497</t>
+    <t xml:space="preserve">3.96341228485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07441711425781</t>
   </si>
   <si>
     <t xml:space="preserve">4.3200831413269</t>
@@ -131,22 +131,22 @@
     <t xml:space="preserve">3.9797899723053</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06895780563354</t>
+    <t xml:space="preserve">4.06895732879639</t>
   </si>
   <si>
     <t xml:space="preserve">4.05439901351929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98524951934814</t>
+    <t xml:space="preserve">3.98524904251099</t>
   </si>
   <si>
     <t xml:space="preserve">4.05076026916504</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07259750366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0380220413208</t>
+    <t xml:space="preserve">4.07259702682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03802251815796</t>
   </si>
   <si>
     <t xml:space="preserve">4.04530143737793</t>
@@ -155,19 +155,19 @@
     <t xml:space="preserve">4.03074264526367</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01254606246948</t>
+    <t xml:space="preserve">4.01254558563232</t>
   </si>
   <si>
     <t xml:space="preserve">4.04894065856934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05985975265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07623720169067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91245985031128</t>
+    <t xml:space="preserve">4.05985927581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07623624801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91245937347412</t>
   </si>
   <si>
     <t xml:space="preserve">3.99070858955383</t>
@@ -176,31 +176,31 @@
     <t xml:space="preserve">4.01072549819946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92155861854553</t>
+    <t xml:space="preserve">3.92155814170837</t>
   </si>
   <si>
     <t xml:space="preserve">4.00162696838379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05804014205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21635675430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22181701660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18542146682739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16176509857178</t>
+    <t xml:space="preserve">4.05803918838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21635770797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2218165397644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18542194366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16176462173462</t>
   </si>
   <si>
     <t xml:space="preserve">4.35465812683105</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28186845779419</t>
+    <t xml:space="preserve">4.28186798095703</t>
   </si>
   <si>
     <t xml:space="preserve">4.26731061935425</t>
@@ -209,31 +209,31 @@
     <t xml:space="preserve">4.39287328720093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36739730834961</t>
+    <t xml:space="preserve">4.36739683151245</t>
   </si>
   <si>
     <t xml:space="preserve">4.17814302444458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27458906173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31826257705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35647869110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2654914855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26367139816284</t>
+    <t xml:space="preserve">4.27458953857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31826305389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35647821426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26549100875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26367092132568</t>
   </si>
   <si>
     <t xml:space="preserve">4.27640914916992</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14902687072754</t>
+    <t xml:space="preserve">4.14902639389038</t>
   </si>
   <si>
     <t xml:space="preserve">4.35829734802246</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">4.35283899307251</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29460620880127</t>
+    <t xml:space="preserve">4.29460668563843</t>
   </si>
   <si>
     <t xml:space="preserve">4.2036190032959</t>
@@ -260,82 +260,82 @@
     <t xml:space="preserve">4.34919929504395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33646106719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33100128173828</t>
+    <t xml:space="preserve">4.33646059036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33100175857544</t>
   </si>
   <si>
     <t xml:space="preserve">4.32190275192261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46748208999634</t>
+    <t xml:space="preserve">4.4674825668335</t>
   </si>
   <si>
     <t xml:space="preserve">4.45838403701782</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2855076789856</t>
+    <t xml:space="preserve">4.28550815582275</t>
   </si>
   <si>
     <t xml:space="preserve">3.83057069778442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90336036682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88516354560852</t>
+    <t xml:space="preserve">3.90336084365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88516306877136</t>
   </si>
   <si>
     <t xml:space="preserve">3.87606430053711</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00344657897949</t>
+    <t xml:space="preserve">4.00344610214233</t>
   </si>
   <si>
     <t xml:space="preserve">3.93065667152405</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99434781074524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08533525466919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9670512676239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86696553230286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84876799583435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85786628723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81237292289734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80327391624451</t>
+    <t xml:space="preserve">3.99434733390808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08533573150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96705222129822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86696577072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84876823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85786652565002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81237316131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80327415466309</t>
   </si>
   <si>
     <t xml:space="preserve">3.77597832679749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97615003585815</t>
+    <t xml:space="preserve">3.97615098953247</t>
   </si>
   <si>
     <t xml:space="preserve">3.94885444641113</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13992738723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16722440719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3352837562561</t>
+    <t xml:space="preserve">4.13992786407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16722393035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33528327941895</t>
   </si>
   <si>
     <t xml:space="preserve">4.21485900878906</t>
@@ -344,19 +344,19 @@
     <t xml:space="preserve">4.31675672531128</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42791843414307</t>
+    <t xml:space="preserve">4.42791795730591</t>
   </si>
   <si>
     <t xml:space="preserve">4.19633197784424</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16854190826416</t>
+    <t xml:space="preserve">4.168541431427</t>
   </si>
   <si>
     <t xml:space="preserve">4.29822969436646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30749273300171</t>
+    <t xml:space="preserve">4.30749320983887</t>
   </si>
   <si>
     <t xml:space="preserve">4.27970266342163</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">3.93695592880249</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00180006027222</t>
+    <t xml:space="preserve">4.00179958343506</t>
   </si>
   <si>
     <t xml:space="preserve">3.97400975227356</t>
@@ -386,10 +386,10 @@
     <t xml:space="preserve">4.03885364532471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94621920585632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95548343658447</t>
+    <t xml:space="preserve">3.94621968269348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95548295974731</t>
   </si>
   <si>
     <t xml:space="preserve">4.23338603973389</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">4.22412252426147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2426495552063</t>
+    <t xml:space="preserve">4.24264860153198</t>
   </si>
   <si>
     <t xml:space="preserve">4.11296081542969</t>
@@ -407,16 +407,16 @@
     <t xml:space="preserve">4.26117610931396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91842865943909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89990282058716</t>
+    <t xml:space="preserve">3.91842913627625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89990234375</t>
   </si>
   <si>
     <t xml:space="preserve">3.89063882827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0759072303772</t>
+    <t xml:space="preserve">4.07590675354004</t>
   </si>
   <si>
     <t xml:space="preserve">4.06664371490479</t>
@@ -425,19 +425,19 @@
     <t xml:space="preserve">3.7980043888092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73316121101379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86284923553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71463418006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70537066459656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77021455764771</t>
+    <t xml:space="preserve">3.73316073417664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86284852027893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71463394165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70537042617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77021431922913</t>
   </si>
   <si>
     <t xml:space="preserve">3.3904139995575</t>
@@ -458,28 +458,28 @@
     <t xml:space="preserve">3.52010202407837</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37188744544983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46452116966248</t>
+    <t xml:space="preserve">3.37188720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46452140808105</t>
   </si>
   <si>
     <t xml:space="preserve">3.53862881660461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52936506271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45525765419006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34409666061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07545709609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14956498146057</t>
+    <t xml:space="preserve">3.5293653011322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45525813102722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34409642219543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07545757293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14956521987915</t>
   </si>
   <si>
     <t xml:space="preserve">3.29777956008911</t>
@@ -488,70 +488,70 @@
     <t xml:space="preserve">3.31630659103394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23293590545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24219918251038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02914047241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20514559745789</t>
+    <t xml:space="preserve">3.23293566703796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2421989440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02914023399353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20514535903931</t>
   </si>
   <si>
     <t xml:space="preserve">3.25146269798279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10324764251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1588282585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91797971725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74197363853455</t>
+    <t xml:space="preserve">3.10324788093567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15882849693298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91797924041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74197387695312</t>
   </si>
   <si>
     <t xml:space="preserve">2.77902770042419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.871661901474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96429657936096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85313510894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83460807800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84387159347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72344708442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76050090789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76976418495178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63081312179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67713022232056</t>
+    <t xml:space="preserve">2.87166213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96429634094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85313487052917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83460855484009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84387135505676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72344732284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76050066947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76976442337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63081288337708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67712998390198</t>
   </si>
   <si>
     <t xml:space="preserve">2.38070058822632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36217331886292</t>
+    <t xml:space="preserve">2.36217379570007</t>
   </si>
   <si>
     <t xml:space="preserve">2.29732966423035</t>
@@ -569,16 +569,16 @@
     <t xml:space="preserve">2.2324857711792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28806638717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08427095413208</t>
+    <t xml:space="preserve">2.28806662559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0842707157135</t>
   </si>
   <si>
     <t xml:space="preserve">2.13058805465698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22322249412537</t>
+    <t xml:space="preserve">2.22322225570679</t>
   </si>
   <si>
     <t xml:space="preserve">2.24174928665161</t>
@@ -590,13 +590,13 @@
     <t xml:space="preserve">2.17690515518188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0379536151886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99163639545441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88047552108765</t>
+    <t xml:space="preserve">2.03795337677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99163663387299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88047540187836</t>
   </si>
   <si>
     <t xml:space="preserve">1.94531941413879</t>
@@ -605,13 +605,13 @@
     <t xml:space="preserve">1.92679250240326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16764187812805</t>
+    <t xml:space="preserve">2.16764163970947</t>
   </si>
   <si>
     <t xml:space="preserve">2.13985133171082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21395921707153</t>
+    <t xml:space="preserve">2.21395897865295</t>
   </si>
   <si>
     <t xml:space="preserve">2.40849041938782</t>
@@ -623,10 +623,10 @@
     <t xml:space="preserve">2.42701768875122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38996362686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46583557128906</t>
+    <t xml:space="preserve">2.38996410369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46583604812622</t>
   </si>
   <si>
     <t xml:space="preserve">2.50406575202942</t>
@@ -635,16 +635,16 @@
     <t xml:space="preserve">2.65698575973511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71433091163635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5422956943512</t>
+    <t xml:space="preserve">2.71433067321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54229593276978</t>
   </si>
   <si>
     <t xml:space="preserve">2.58052587509155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52318120002747</t>
+    <t xml:space="preserve">2.52318096160889</t>
   </si>
   <si>
     <t xml:space="preserve">2.42760586738586</t>
@@ -662,28 +662,28 @@
     <t xml:space="preserve">2.56141066551208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63787078857422</t>
+    <t xml:space="preserve">2.63787126541138</t>
   </si>
   <si>
     <t xml:space="preserve">2.73344588279724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69521594047546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75256085395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8099057674408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82902050018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84813594818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05840110778809</t>
+    <t xml:space="preserve">2.69521570205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75256109237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80990600585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82902073860168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84813570976257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05840086936951</t>
   </si>
   <si>
     <t xml:space="preserve">2.86725091934204</t>
@@ -692,58 +692,58 @@
     <t xml:space="preserve">2.77167582511902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67610096931458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59964084625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44672060012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40849089622498</t>
+    <t xml:space="preserve">2.676100730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59964060783386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44672083854675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4084906578064</t>
   </si>
   <si>
     <t xml:space="preserve">2.37026071548462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09663128852844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34512615203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45981621742249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74654150009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76565623283386</t>
+    <t xml:space="preserve">3.09663105010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34512591362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45981597900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74654126167297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76565599441528</t>
   </si>
   <si>
     <t xml:space="preserve">4.01415109634399</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10972595214844</t>
+    <t xml:space="preserve">4.1097264289856</t>
   </si>
   <si>
     <t xml:space="preserve">3.97592091560364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88034629821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82300138473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44070100784302</t>
+    <t xml:space="preserve">3.88034605979919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82300114631653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44070076942444</t>
   </si>
   <si>
     <t xml:space="preserve">3.40247106552124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36424088478088</t>
+    <t xml:space="preserve">3.36424112319946</t>
   </si>
   <si>
     <t xml:space="preserve">3.68919587135315</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">3.72742629051208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70831108093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57450604438782</t>
+    <t xml:space="preserve">3.7083113193512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5745062828064</t>
   </si>
   <si>
     <t xml:space="preserve">3.55539107322693</t>
@@ -767,34 +767,34 @@
     <t xml:space="preserve">3.63185119628906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53627610206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61273574829102</t>
+    <t xml:space="preserve">3.53627634048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61273598670959</t>
   </si>
   <si>
     <t xml:space="preserve">3.65096616744995</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24955105781555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32601118087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42158603668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3068962097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38335609436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59362077713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47893142700195</t>
+    <t xml:space="preserve">3.24955129623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32601094245911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42158627510071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30689597129822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38335633277893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59362125396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47893118858337</t>
   </si>
   <si>
     <t xml:space="preserve">3.49804615974426</t>
@@ -809,25 +809,25 @@
     <t xml:space="preserve">3.80388593673706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93769073486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03326654434204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18618583679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30087661743164</t>
+    <t xml:space="preserve">3.93769145011902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03326606750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18618631362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30087614059448</t>
   </si>
   <si>
     <t xml:space="preserve">4.5302562713623</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51114130020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58760213851929</t>
+    <t xml:space="preserve">4.51114177703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58760166168213</t>
   </si>
   <si>
     <t xml:space="preserve">4.49202632904053</t>
@@ -842,10 +842,10 @@
     <t xml:space="preserve">4.74052143096924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75963735580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70229148864746</t>
+    <t xml:space="preserve">4.75963592529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70229196548462</t>
   </si>
   <si>
     <t xml:space="preserve">4.68317699432373</t>
@@ -854,46 +854,46 @@
     <t xml:space="preserve">4.77875137329102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5684871673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72140693664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8743257522583</t>
+    <t xml:space="preserve">4.56848669052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66406202316284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72140741348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87432670593262</t>
   </si>
   <si>
     <t xml:space="preserve">4.9699010848999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9221134185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11326456069946</t>
+    <t xml:space="preserve">4.92211437225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1132640838623</t>
   </si>
   <si>
     <t xml:space="preserve">5.16105175018311</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20883941650391</t>
+    <t xml:space="preserve">5.20883846282959</t>
   </si>
   <si>
     <t xml:space="preserve">5.25662708282471</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30441427230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44777679443359</t>
+    <t xml:space="preserve">5.30441474914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44777631759644</t>
   </si>
   <si>
     <t xml:space="preserve">5.63892698287964</t>
   </si>
   <si>
-    <t xml:space="preserve">5.591139793396</t>
+    <t xml:space="preserve">5.59113931655884</t>
   </si>
   <si>
     <t xml:space="preserve">5.81332683563232</t>
@@ -905,76 +905,76 @@
     <t xml:space="preserve">5.42577171325684</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13510513305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84443855285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8250617980957</t>
+    <t xml:space="preserve">5.1351056098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8444390296936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82506084442139</t>
   </si>
   <si>
     <t xml:space="preserve">4.80568313598633</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59252786636353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55377244949341</t>
+    <t xml:space="preserve">4.59252738952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55377197265625</t>
   </si>
   <si>
     <t xml:space="preserve">4.76692771911621</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03821611404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98977136611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08665990829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18354988098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94132709503174</t>
+    <t xml:space="preserve">5.03821563720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9897723197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08666038513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18354940414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9413275718689</t>
   </si>
   <si>
     <t xml:space="preserve">5.23199415206909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74755048751831</t>
+    <t xml:space="preserve">4.74755001068115</t>
   </si>
   <si>
     <t xml:space="preserve">5.2804388999939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89288282394409</t>
+    <t xml:space="preserve">4.89288330078125</t>
   </si>
   <si>
     <t xml:space="preserve">4.63128423690796</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53439521789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67003917694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78630590438843</t>
+    <t xml:space="preserve">4.53439474105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67003965377808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78630542755127</t>
   </si>
   <si>
     <t xml:space="preserve">4.72817325592041</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70879459381104</t>
+    <t xml:space="preserve">4.70879507064819</t>
   </si>
   <si>
     <t xml:space="preserve">5.91021537780762</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61954927444458</t>
+    <t xml:space="preserve">5.61954975128174</t>
   </si>
   <si>
     <t xml:space="preserve">5.32888317108154</t>
@@ -983,13 +983,13 @@
     <t xml:space="preserve">5.37732744216919</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57110548019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47421598434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66799402236938</t>
+    <t xml:space="preserve">5.57110500335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47421646118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66799354553223</t>
   </si>
   <si>
     <t xml:space="preserve">6.73376989364624</t>
@@ -998,7 +998,7 @@
     <t xml:space="preserve">6.29777050018311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44310331344604</t>
+    <t xml:space="preserve">6.4431037902832</t>
   </si>
   <si>
     <t xml:space="preserve">6.68532562255859</t>
@@ -1007,37 +1007,37 @@
     <t xml:space="preserve">6.5884370803833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63688135147095</t>
+    <t xml:space="preserve">6.63688087463379</t>
   </si>
   <si>
     <t xml:space="preserve">6.24932622909546</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34621477127075</t>
+    <t xml:space="preserve">6.34621524810791</t>
   </si>
   <si>
     <t xml:space="preserve">6.5399923324585</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3946590423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71999073028564</t>
+    <t xml:space="preserve">6.39465951919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71998977661133</t>
   </si>
   <si>
     <t xml:space="preserve">7.99332427978516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09021472930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04176807403564</t>
+    <t xml:space="preserve">8.09021377563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04176902770996</t>
   </si>
   <si>
     <t xml:space="preserve">7.94487953186035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84799098968506</t>
+    <t xml:space="preserve">7.84799242019653</t>
   </si>
   <si>
     <t xml:space="preserve">7.89643621444702</t>
@@ -1046,22 +1046,22 @@
     <t xml:space="preserve">8.38087844848633</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2702102661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88265419006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1733198165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97954273223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0764322280884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2390985488892</t>
+    <t xml:space="preserve">10.2702112197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88265514373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1733207702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9795446395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0764312744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2390995025635</t>
   </si>
   <si>
     <t xml:space="preserve">11.6266536712646</t>
@@ -1070,16 +1070,16 @@
     <t xml:space="preserve">13.079984664917</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2737627029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9830961227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4364280700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3395395278931</t>
+    <t xml:space="preserve">13.2737617492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9830951690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.436427116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3395385742188</t>
   </si>
   <si>
     <t xml:space="preserve">15.0177612304688</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">16.1669788360596</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1930646896362</t>
+    <t xml:space="preserve">15.1930656433105</t>
   </si>
   <si>
     <t xml:space="preserve">15.0956735610962</t>
@@ -1097,13 +1097,13 @@
     <t xml:space="preserve">14.9008913040161</t>
   </si>
   <si>
-    <t xml:space="preserve">13.634801864624</t>
+    <t xml:space="preserve">13.6348009109497</t>
   </si>
   <si>
     <t xml:space="preserve">12.0765390396118</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4661045074463</t>
+    <t xml:space="preserve">12.466103553772</t>
   </si>
   <si>
     <t xml:space="preserve">13.4400196075439</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">14.7061080932617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5113258361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3426275253296</t>
+    <t xml:space="preserve">14.5113248825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3426265716553</t>
   </si>
   <si>
     <t xml:space="preserve">14.1217594146729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3165426254272</t>
+    <t xml:space="preserve">14.3165416717529</t>
   </si>
   <si>
     <t xml:space="preserve">13.8295850753784</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">12.5634956359863</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1739301681519</t>
+    <t xml:space="preserve">12.1739292144775</t>
   </si>
   <si>
     <t xml:space="preserve">11.6869735717773</t>
@@ -1172,34 +1172,34 @@
     <t xml:space="preserve">11.1026239395142</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93392658233643</t>
+    <t xml:space="preserve">9.93392753601074</t>
   </si>
   <si>
     <t xml:space="preserve">10.7130584716797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2000169754028</t>
+    <t xml:space="preserve">11.2000160217285</t>
   </si>
   <si>
     <t xml:space="preserve">11.9791479110718</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8817558288574</t>
+    <t xml:space="preserve">11.8817548751831</t>
   </si>
   <si>
     <t xml:space="preserve">10.9078416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2974081039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3947992324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5895824432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0052328109741</t>
+    <t xml:space="preserve">11.2974071502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3947982788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5895805358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0052318572998</t>
   </si>
   <si>
     <t xml:space="preserve">11.7843647003174</t>
@@ -1208,31 +1208,31 @@
     <t xml:space="preserve">11.4921903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.810450553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4208850860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2260999679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3234930038452</t>
+    <t xml:space="preserve">10.8104515075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4208841323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2261018753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3234939575195</t>
   </si>
   <si>
     <t xml:space="preserve">10.1287097930908</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0313177108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73914432525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54436206817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83653545379639</t>
+    <t xml:space="preserve">10.0313196182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73914527893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54436111450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8365364074707</t>
   </si>
   <si>
     <t xml:space="preserve">9.34957981109619</t>
@@ -1241,19 +1241,19 @@
     <t xml:space="preserve">9.49566555023193</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2713232040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9530611038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6800222396851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7321929931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1704549789429</t>
+    <t xml:space="preserve">12.2713222503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9530620574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6800231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7321939468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1704559326172</t>
   </si>
   <si>
     <t xml:space="preserve">14.3652372360229</t>
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">14.0730628967285</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1443700790405</t>
+    <t xml:space="preserve">15.1443691253662</t>
   </si>
   <si>
     <t xml:space="preserve">15.5364570617676</t>
@@ -1271,13 +1271,13 @@
     <t xml:space="preserve">15.585467338562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6344785690308</t>
+    <t xml:space="preserve">15.6344776153564</t>
   </si>
   <si>
     <t xml:space="preserve">15.193380355835</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4874467849731</t>
+    <t xml:space="preserve">15.4874458312988</t>
   </si>
   <si>
     <t xml:space="preserve">15.4384346008301</t>
@@ -1286,13 +1286,13 @@
     <t xml:space="preserve">15.2423915863037</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3894243240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9973363876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8993139266968</t>
+    <t xml:space="preserve">15.3894233703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9973373413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8993148803711</t>
   </si>
   <si>
     <t xml:space="preserve">15.0463485717773</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">13.7230529785156</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8210744857788</t>
+    <t xml:space="preserve">13.8210754394531</t>
   </si>
   <si>
     <t xml:space="preserve">14.3601942062378</t>
@@ -1319,7 +1319,7 @@
     <t xml:space="preserve">13.6250314712524</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8700866699219</t>
+    <t xml:space="preserve">13.8700857162476</t>
   </si>
   <si>
     <t xml:space="preserve">13.6740427017212</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">14.9483261108398</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4092063903809</t>
+    <t xml:space="preserve">14.4092054367065</t>
   </si>
   <si>
     <t xml:space="preserve">14.8503036499023</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7522821426392</t>
+    <t xml:space="preserve">14.7522830963135</t>
   </si>
   <si>
     <t xml:space="preserve">14.6052494049072</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">14.5562391281128</t>
   </si>
   <si>
-    <t xml:space="preserve">14.507227897644</t>
+    <t xml:space="preserve">14.5072288513184</t>
   </si>
   <si>
     <t xml:space="preserve">14.0661296844482</t>
@@ -1373,16 +1373,16 @@
     <t xml:space="preserve">13.2819547653198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8898677825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7428350448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.987889289856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1349220275879</t>
+    <t xml:space="preserve">12.8898668289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7428340911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9878902435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1349229812622</t>
   </si>
   <si>
     <t xml:space="preserve">12.3507480621338</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">13.0859127044678</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4289884567261</t>
+    <t xml:space="preserve">13.4289875030518</t>
   </si>
   <si>
     <t xml:space="preserve">15.8305215835571</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">16.2226085662842</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0265674591064</t>
+    <t xml:space="preserve">16.0265655517578</t>
   </si>
   <si>
     <t xml:space="preserve">16.0755767822266</t>
@@ -1442,199 +1442,202 @@
     <t xml:space="preserve">16.2716197967529</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3206310272217</t>
+    <t xml:space="preserve">16.320629119873</t>
   </si>
   <si>
     <t xml:space="preserve">18.7221660614014</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0162315368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7023849487305</t>
+    <t xml:space="preserve">19.0162296295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7023830413818</t>
   </si>
   <si>
     <t xml:space="preserve">19.6043605804443</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8004055023193</t>
+    <t xml:space="preserve">19.800407409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0944709777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9173202514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.545015335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5252342224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7995166778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2311706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7806243896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1727104187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4865589141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6826019287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3687534332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6430377960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9955596923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2896251678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6034755706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8975391387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5054531097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.015344619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6232566833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8390808105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3291893005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.937105178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7212791442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1133651733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0351257324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1331481933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2113876342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4074287414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8192977905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2509498596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7608413696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9568843841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1529273986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7711753845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6439266204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5261211395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9964485168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5845794677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1924934387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8984279632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3885364532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4049549102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6512107849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3557014465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5527095794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7989635467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6019592285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9616947174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0601978302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0109443664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1586990356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2914772033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1929721832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1779956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9809913635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4884796142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5869827270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9959678649902</t>
   </si>
   <si>
     <t xml:space="preserve">20.0944690704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9173202514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5450172424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5252342224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7995166778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2311687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7806243896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1727104187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4865570068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6826019287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3687553405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6430377960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9955615997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2896270751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6034755706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8975391387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5054512023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0153427124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6232566833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8390789031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3291893005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.937105178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7212772369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1133651733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0351257324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1331481933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2113876342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4074287414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.819299697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2509517669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7608413696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9568843841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1529273986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7711772918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3300800323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6439266204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5261211395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9964485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5845775604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1924934387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8984260559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3885364532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4049549102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6512107849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3557014465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5527095794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7989635467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6019592285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9616947174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0601978302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0109443664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1586990356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2914772033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1929721832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1779956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9809913635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4884796142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5869827270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9959678649902</t>
   </si>
   <si>
     <t xml:space="preserve">19.4542045593262</t>
@@ -41446,7 +41449,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1499" t="s">
-        <v>482</v>
+        <v>541</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41498,7 +41501,7 @@
         <v>19.75</v>
       </c>
       <c r="G1501" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41602,7 +41605,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1505" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41628,7 +41631,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1506" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41680,7 +41683,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1508" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41706,7 +41709,7 @@
         <v>19.5</v>
       </c>
       <c r="G1509" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41732,7 +41735,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1510" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41758,7 +41761,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1511" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41784,7 +41787,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1512" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41810,7 +41813,7 @@
         <v>19.5</v>
       </c>
       <c r="G1513" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41836,7 +41839,7 @@
         <v>19.5</v>
       </c>
       <c r="G1514" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41862,7 +41865,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1515" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41888,7 +41891,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1516" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41914,7 +41917,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1517" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -41940,7 +41943,7 @@
         <v>18.75</v>
       </c>
       <c r="G1518" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -41966,7 +41969,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1519" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41992,7 +41995,7 @@
         <v>17.5</v>
       </c>
       <c r="G1520" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42018,7 +42021,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1521" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42044,7 +42047,7 @@
         <v>18.25</v>
       </c>
       <c r="G1522" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42070,7 +42073,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1523" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42096,7 +42099,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1524" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42122,7 +42125,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1525" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42148,7 +42151,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1526" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42174,7 +42177,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1527" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42200,7 +42203,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1528" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42226,7 +42229,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1529" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42356,7 +42359,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1534" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42382,7 +42385,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1535" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42434,7 +42437,7 @@
         <v>20</v>
       </c>
       <c r="G1537" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42512,7 +42515,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1540" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42538,7 +42541,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1541" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42564,7 +42567,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1542" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42616,7 +42619,7 @@
         <v>19.5</v>
       </c>
       <c r="G1544" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42642,7 +42645,7 @@
         <v>19.5</v>
       </c>
       <c r="G1545" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42720,7 +42723,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1548" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42746,7 +42749,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G1549" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42876,7 +42879,7 @@
         <v>19.5</v>
       </c>
       <c r="G1554" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42902,7 +42905,7 @@
         <v>19.5</v>
       </c>
       <c r="G1555" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42928,7 +42931,7 @@
         <v>19.5</v>
       </c>
       <c r="G1556" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42980,7 +42983,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1558" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43006,7 +43009,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1559" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43032,7 +43035,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1560" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43058,7 +43061,7 @@
         <v>19</v>
       </c>
       <c r="G1561" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43084,7 +43087,7 @@
         <v>19</v>
       </c>
       <c r="G1562" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43110,7 +43113,7 @@
         <v>19</v>
       </c>
       <c r="G1563" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43136,7 +43139,7 @@
         <v>19</v>
       </c>
       <c r="G1564" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43162,7 +43165,7 @@
         <v>19</v>
       </c>
       <c r="G1565" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43188,7 +43191,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1566" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43214,7 +43217,7 @@
         <v>19</v>
       </c>
       <c r="G1567" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43240,7 +43243,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1568" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43266,7 +43269,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1569" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43292,7 +43295,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1570" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43318,7 +43321,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1571" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -43344,7 +43347,7 @@
         <v>19</v>
       </c>
       <c r="G1572" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43370,7 +43373,7 @@
         <v>19</v>
       </c>
       <c r="G1573" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43396,7 +43399,7 @@
         <v>19</v>
       </c>
       <c r="G1574" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43422,7 +43425,7 @@
         <v>18.75</v>
       </c>
       <c r="G1575" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43448,7 +43451,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1576" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43474,7 +43477,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1577" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43500,7 +43503,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1578" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43526,7 +43529,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1579" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43552,7 +43555,7 @@
         <v>19</v>
       </c>
       <c r="G1580" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43578,7 +43581,7 @@
         <v>19</v>
       </c>
       <c r="G1581" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43604,7 +43607,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1582" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43630,7 +43633,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1583" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43656,7 +43659,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1584" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43682,7 +43685,7 @@
         <v>18.75</v>
       </c>
       <c r="G1585" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43708,7 +43711,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1586" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43734,7 +43737,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1587" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43760,7 +43763,7 @@
         <v>18.5</v>
       </c>
       <c r="G1588" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43786,7 +43789,7 @@
         <v>18.5</v>
       </c>
       <c r="G1589" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43812,7 +43815,7 @@
         <v>18.5</v>
       </c>
       <c r="G1590" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43838,7 +43841,7 @@
         <v>18.5</v>
       </c>
       <c r="G1591" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43864,7 +43867,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1592" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43890,7 +43893,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1593" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43916,7 +43919,7 @@
         <v>18</v>
       </c>
       <c r="G1594" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43942,7 +43945,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1595" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -43968,7 +43971,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1596" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43994,7 +43997,7 @@
         <v>18.5</v>
       </c>
       <c r="G1597" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44020,7 +44023,7 @@
         <v>18.5</v>
       </c>
       <c r="G1598" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44046,7 +44049,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1599" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44072,7 +44075,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1600" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44098,7 +44101,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1601" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44124,7 +44127,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1602" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44150,7 +44153,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1603" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44176,7 +44179,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1604" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44202,7 +44205,7 @@
         <v>18.25</v>
       </c>
       <c r="G1605" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44228,7 +44231,7 @@
         <v>18</v>
       </c>
       <c r="G1606" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -44254,7 +44257,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1607" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -44280,7 +44283,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1608" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -44306,7 +44309,7 @@
         <v>18</v>
       </c>
       <c r="G1609" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44332,7 +44335,7 @@
         <v>18.25</v>
       </c>
       <c r="G1610" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -44358,7 +44361,7 @@
         <v>18.25</v>
       </c>
       <c r="G1611" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44384,7 +44387,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1612" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44410,7 +44413,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1613" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44436,7 +44439,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1614" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44462,7 +44465,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1615" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44488,7 +44491,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1616" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44514,7 +44517,7 @@
         <v>18</v>
       </c>
       <c r="G1617" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44540,7 +44543,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1618" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44566,7 +44569,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1619" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44592,7 +44595,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1620" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44618,7 +44621,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1621" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44644,7 +44647,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1622" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44670,7 +44673,7 @@
         <v>18</v>
       </c>
       <c r="G1623" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44696,7 +44699,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1624" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44722,7 +44725,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1625" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44748,7 +44751,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1626" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44774,7 +44777,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1627" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44800,7 +44803,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1628" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44826,7 +44829,7 @@
         <v>18.25</v>
       </c>
       <c r="G1629" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44852,7 +44855,7 @@
         <v>18.25</v>
       </c>
       <c r="G1630" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44878,7 +44881,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1631" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44904,7 +44907,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1632" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44930,7 +44933,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1633" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44956,7 +44959,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1634" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44982,7 +44985,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1635" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45008,7 +45011,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1636" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45034,7 +45037,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1637" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45060,7 +45063,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1638" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45086,7 +45089,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1639" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45112,7 +45115,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1640" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45138,7 +45141,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1641" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -45164,7 +45167,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1642" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45190,7 +45193,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1643" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45216,7 +45219,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1644" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -45242,7 +45245,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1645" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -45268,7 +45271,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1646" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -45294,7 +45297,7 @@
         <v>18</v>
       </c>
       <c r="G1647" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -45320,7 +45323,7 @@
         <v>18.25</v>
       </c>
       <c r="G1648" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -45346,7 +45349,7 @@
         <v>18.25</v>
       </c>
       <c r="G1649" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -45372,7 +45375,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1650" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45398,7 +45401,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1651" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -45424,7 +45427,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1652" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45450,7 +45453,7 @@
         <v>18</v>
       </c>
       <c r="G1653" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45476,7 +45479,7 @@
         <v>18</v>
       </c>
       <c r="G1654" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45502,7 +45505,7 @@
         <v>18</v>
       </c>
       <c r="G1655" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45528,7 +45531,7 @@
         <v>18</v>
       </c>
       <c r="G1656" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45554,7 +45557,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1657" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45580,7 +45583,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1658" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45606,7 +45609,7 @@
         <v>17.75</v>
       </c>
       <c r="G1659" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45632,7 +45635,7 @@
         <v>18</v>
       </c>
       <c r="G1660" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45658,7 +45661,7 @@
         <v>18</v>
       </c>
       <c r="G1661" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45684,7 +45687,7 @@
         <v>18</v>
       </c>
       <c r="G1662" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45710,7 +45713,7 @@
         <v>18</v>
       </c>
       <c r="G1663" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45736,7 +45739,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1664" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45762,7 +45765,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1665" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45788,7 +45791,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1666" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45814,7 +45817,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1667" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45840,7 +45843,7 @@
         <v>17.5</v>
       </c>
       <c r="G1668" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45866,7 +45869,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1669" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45892,7 +45895,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1670" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45918,7 +45921,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1671" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45944,7 +45947,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1672" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45970,7 +45973,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1673" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45996,7 +45999,7 @@
         <v>16.75</v>
       </c>
       <c r="G1674" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -46022,7 +46025,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1675" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -46048,7 +46051,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1676" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -46074,7 +46077,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1677" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -46100,7 +46103,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1678" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -46126,7 +46129,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1679" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -46152,7 +46155,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1680" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -46178,7 +46181,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1681" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -46204,7 +46207,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1682" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -46230,7 +46233,7 @@
         <v>17</v>
       </c>
       <c r="G1683" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -46256,7 +46259,7 @@
         <v>17</v>
       </c>
       <c r="G1684" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -46282,7 +46285,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1685" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -46308,7 +46311,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1686" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -46334,7 +46337,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1687" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -46360,7 +46363,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46386,7 +46389,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1689" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -46412,7 +46415,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1690" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -46438,7 +46441,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1691" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46464,7 +46467,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1692" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46490,7 +46493,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1693" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -46516,7 +46519,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46542,7 +46545,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1695" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46568,7 +46571,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1696" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46594,7 +46597,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1697" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46620,7 +46623,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1698" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46646,7 +46649,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1699" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46672,7 +46675,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1700" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46698,7 +46701,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1701" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46724,7 +46727,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1702" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46750,7 +46753,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1703" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46776,7 +46779,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1704" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46802,7 +46805,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1705" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46828,7 +46831,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1706" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46854,7 +46857,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1707" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46880,7 +46883,7 @@
         <v>15</v>
       </c>
       <c r="G1708" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46906,7 +46909,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1709" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46932,7 +46935,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1710" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46958,7 +46961,7 @@
         <v>14.5</v>
       </c>
       <c r="G1711" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46984,7 +46987,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1712" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -47010,7 +47013,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1713" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47036,7 +47039,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1714" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -47062,7 +47065,7 @@
         <v>15</v>
       </c>
       <c r="G1715" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -47088,7 +47091,7 @@
         <v>15</v>
       </c>
       <c r="G1716" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47114,7 +47117,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1717" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -47140,7 +47143,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1718" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -47166,7 +47169,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -47192,7 +47195,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1720" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -47218,7 +47221,7 @@
         <v>14.25</v>
       </c>
       <c r="G1721" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -47244,7 +47247,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1722" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -47270,7 +47273,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1723" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -47296,7 +47299,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1724" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -47322,7 +47325,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1725" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -47348,7 +47351,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1726" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47374,7 +47377,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1727" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47400,7 +47403,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1728" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -47426,7 +47429,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1729" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47452,7 +47455,7 @@
         <v>14.75</v>
       </c>
       <c r="G1730" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47478,7 +47481,7 @@
         <v>14.75</v>
       </c>
       <c r="G1731" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47504,7 +47507,7 @@
         <v>14.75</v>
       </c>
       <c r="G1732" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47530,7 +47533,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1733" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47556,7 +47559,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1734" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47582,7 +47585,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1735" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47608,7 +47611,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1736" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47634,7 +47637,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1737" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47660,7 +47663,7 @@
         <v>13.25</v>
       </c>
       <c r="G1738" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47686,7 +47689,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1739" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47712,7 +47715,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1740" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47738,7 +47741,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1741" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47764,7 +47767,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1742" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47790,7 +47793,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1743" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47816,7 +47819,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1744" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47842,7 +47845,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1745" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47868,7 +47871,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1746" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47894,7 +47897,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1747" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47920,7 +47923,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1748" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47946,7 +47949,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1749" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47972,7 +47975,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1750" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47998,7 +48001,7 @@
         <v>12.75</v>
       </c>
       <c r="G1751" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -48024,7 +48027,7 @@
         <v>12.5</v>
       </c>
       <c r="G1752" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -48050,7 +48053,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1753" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -48076,7 +48079,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1754" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -48102,7 +48105,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1755" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -48128,7 +48131,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1756" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -48154,7 +48157,7 @@
         <v>12.25</v>
       </c>
       <c r="G1757" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -48180,7 +48183,7 @@
         <v>12.25</v>
       </c>
       <c r="G1758" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -48206,7 +48209,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1759" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -48232,7 +48235,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1760" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -48258,7 +48261,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1761" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -48284,7 +48287,7 @@
         <v>12.75</v>
       </c>
       <c r="G1762" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -48310,7 +48313,7 @@
         <v>12.75</v>
       </c>
       <c r="G1763" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -48336,7 +48339,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1764" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -48362,7 +48365,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1765" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48388,7 +48391,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1766" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48414,7 +48417,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1767" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48440,7 +48443,7 @@
         <v>12.5</v>
       </c>
       <c r="G1768" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48466,7 +48469,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1769" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48492,7 +48495,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1770" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48518,7 +48521,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1771" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48544,7 +48547,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1772" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48570,7 +48573,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1773" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48596,7 +48599,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1774" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48622,7 +48625,7 @@
         <v>12.75</v>
       </c>
       <c r="G1775" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48648,7 +48651,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1776" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48674,7 +48677,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1777" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48700,7 +48703,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1778" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48726,7 +48729,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1779" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48752,7 +48755,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1780" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48778,7 +48781,7 @@
         <v>13</v>
       </c>
       <c r="G1781" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48804,7 +48807,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1782" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48830,7 +48833,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1783" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48856,7 +48859,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1784" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48882,7 +48885,7 @@
         <v>12.75</v>
       </c>
       <c r="G1785" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48908,7 +48911,7 @@
         <v>12.75</v>
       </c>
       <c r="G1786" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48934,7 +48937,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48960,7 +48963,7 @@
         <v>12.5</v>
       </c>
       <c r="G1788" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48986,7 +48989,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1789" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -49012,7 +49015,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1790" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -49038,7 +49041,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1791" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -49064,7 +49067,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1792" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -49090,7 +49093,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1793" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -49116,7 +49119,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1794" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -49142,7 +49145,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1795" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -49168,7 +49171,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1796" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -49194,7 +49197,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1797" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -49220,7 +49223,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1798" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -49246,7 +49249,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1799" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -49272,7 +49275,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1800" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -49298,7 +49301,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1801" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -49324,7 +49327,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1802" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -49350,7 +49353,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1803" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49376,7 +49379,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1804" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49402,7 +49405,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1805" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49428,7 +49431,7 @@
         <v>12.75</v>
       </c>
       <c r="G1806" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49454,7 +49457,7 @@
         <v>12.75</v>
       </c>
       <c r="G1807" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49480,7 +49483,7 @@
         <v>12.75</v>
       </c>
       <c r="G1808" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49506,7 +49509,7 @@
         <v>12.75</v>
       </c>
       <c r="G1809" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49532,7 +49535,7 @@
         <v>12.75</v>
       </c>
       <c r="G1810" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49558,7 +49561,7 @@
         <v>12.75</v>
       </c>
       <c r="G1811" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49584,7 +49587,7 @@
         <v>12.75</v>
       </c>
       <c r="G1812" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49610,7 +49613,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1813" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49636,7 +49639,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1814" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49662,7 +49665,7 @@
         <v>12.75</v>
       </c>
       <c r="G1815" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49688,7 +49691,7 @@
         <v>12.75</v>
       </c>
       <c r="G1816" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49714,7 +49717,7 @@
         <v>12.75</v>
       </c>
       <c r="G1817" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49740,7 +49743,7 @@
         <v>12.75</v>
       </c>
       <c r="G1818" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49766,7 +49769,7 @@
         <v>12.75</v>
       </c>
       <c r="G1819" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49792,7 +49795,7 @@
         <v>12.75</v>
       </c>
       <c r="G1820" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49818,7 +49821,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1821" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49844,7 +49847,7 @@
         <v>12.5</v>
       </c>
       <c r="G1822" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49870,7 +49873,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1823" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49896,7 +49899,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1824" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49922,7 +49925,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1825" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49948,7 +49951,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1826" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49974,7 +49977,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1827" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -50000,7 +50003,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1828" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -50026,7 +50029,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1829" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -50052,7 +50055,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1830" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -50078,7 +50081,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1831" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -50104,7 +50107,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1832" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -50130,7 +50133,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1833" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -50156,7 +50159,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1834" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -50182,7 +50185,7 @@
         <v>12.5</v>
       </c>
       <c r="G1835" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -50208,7 +50211,7 @@
         <v>12.5</v>
       </c>
       <c r="G1836" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -50234,7 +50237,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1837" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -50260,7 +50263,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1838" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -50286,7 +50289,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1839" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -50312,7 +50315,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -50338,7 +50341,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1841" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50364,7 +50367,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1842" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50390,7 +50393,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1843" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50416,7 +50419,7 @@
         <v>12.75</v>
       </c>
       <c r="G1844" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50442,7 +50445,7 @@
         <v>12.75</v>
       </c>
       <c r="G1845" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50468,7 +50471,7 @@
         <v>12.75</v>
       </c>
       <c r="G1846" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50494,7 +50497,7 @@
         <v>12.75</v>
       </c>
       <c r="G1847" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50520,7 +50523,7 @@
         <v>12.75</v>
       </c>
       <c r="G1848" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50546,7 +50549,7 @@
         <v>12.75</v>
       </c>
       <c r="G1849" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50572,7 +50575,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1850" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50598,7 +50601,7 @@
         <v>13.25</v>
       </c>
       <c r="G1851" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50624,7 +50627,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1852" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50650,7 +50653,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1853" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50676,7 +50679,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1854" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50702,7 +50705,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1855" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50728,7 +50731,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1856" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50754,7 +50757,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1857" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50780,7 +50783,7 @@
         <v>13</v>
       </c>
       <c r="G1858" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50806,7 +50809,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1859" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50832,7 +50835,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1860" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50858,7 +50861,7 @@
         <v>13.25</v>
       </c>
       <c r="G1861" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50884,7 +50887,7 @@
         <v>13.25</v>
       </c>
       <c r="G1862" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50910,7 +50913,7 @@
         <v>13.25</v>
       </c>
       <c r="G1863" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50936,7 +50939,7 @@
         <v>13.25</v>
       </c>
       <c r="G1864" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50962,7 +50965,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1865" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50988,7 +50991,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1866" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -51014,7 +51017,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1867" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -51040,7 +51043,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1868" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -51066,7 +51069,7 @@
         <v>12.5</v>
       </c>
       <c r="G1869" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -51092,7 +51095,7 @@
         <v>12.5</v>
       </c>
       <c r="G1870" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -51118,7 +51121,7 @@
         <v>12.5</v>
       </c>
       <c r="G1871" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -51144,7 +51147,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1872" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -51170,7 +51173,7 @@
         <v>12.5</v>
       </c>
       <c r="G1873" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -51196,7 +51199,7 @@
         <v>12.5</v>
       </c>
       <c r="G1874" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -51222,7 +51225,7 @@
         <v>12.5</v>
       </c>
       <c r="G1875" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -51248,7 +51251,7 @@
         <v>12.5</v>
       </c>
       <c r="G1876" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -51274,7 +51277,7 @@
         <v>12.25</v>
       </c>
       <c r="G1877" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -51300,7 +51303,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1878" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -51326,7 +51329,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1879" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -51352,7 +51355,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1880" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51378,7 +51381,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1881" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51404,7 +51407,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1882" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51430,7 +51433,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1883" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51456,7 +51459,7 @@
         <v>12.5</v>
       </c>
       <c r="G1884" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51482,7 +51485,7 @@
         <v>12.5</v>
       </c>
       <c r="G1885" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51508,7 +51511,7 @@
         <v>12.5</v>
       </c>
       <c r="G1886" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51534,7 +51537,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1887" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51560,7 +51563,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1888" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51586,7 +51589,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1889" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51612,7 +51615,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1890" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51638,7 +51641,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1891" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51664,7 +51667,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1892" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51690,7 +51693,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1893" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51716,7 +51719,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1894" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51742,7 +51745,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1895" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51768,7 +51771,7 @@
         <v>14.75</v>
       </c>
       <c r="G1896" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51794,7 +51797,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1897" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51820,7 +51823,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1898" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51846,7 +51849,7 @@
         <v>14.25</v>
       </c>
       <c r="G1899" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51872,7 +51875,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1900" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51898,7 +51901,7 @@
         <v>14</v>
       </c>
       <c r="G1901" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51924,7 +51927,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1902" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51950,7 +51953,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1903" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51976,7 +51979,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1904" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -52002,7 +52005,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1905" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52028,7 +52031,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1906" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52054,7 +52057,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52080,7 +52083,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1908" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52106,7 +52109,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1909" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52132,7 +52135,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1910" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -52158,7 +52161,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1911" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -52184,7 +52187,7 @@
         <v>13.25</v>
       </c>
       <c r="G1912" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -52210,7 +52213,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1913" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -52236,7 +52239,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1914" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -52262,7 +52265,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1915" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -52288,7 +52291,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1916" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -52314,7 +52317,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1917" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -52340,7 +52343,7 @@
         <v>12.75</v>
       </c>
       <c r="G1918" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52366,7 +52369,7 @@
         <v>13</v>
       </c>
       <c r="G1919" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52392,7 +52395,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1920" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52418,7 +52421,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1921" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52444,7 +52447,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1922" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52470,7 +52473,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1923" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52496,7 +52499,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1924" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52522,7 +52525,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1925" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52548,7 +52551,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1926" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52574,7 +52577,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1927" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52600,7 +52603,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1928" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52626,7 +52629,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1929" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52652,7 +52655,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1930" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52678,7 +52681,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1931" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52704,7 +52707,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1932" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52730,7 +52733,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1933" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52756,7 +52759,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1934" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52782,7 +52785,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1935" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52808,7 +52811,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1936" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52834,7 +52837,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1937" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52860,7 +52863,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1938" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52886,7 +52889,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1939" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52912,7 +52915,7 @@
         <v>12.5</v>
       </c>
       <c r="G1940" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52938,7 +52941,7 @@
         <v>12.75</v>
       </c>
       <c r="G1941" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52964,7 +52967,7 @@
         <v>12.75</v>
       </c>
       <c r="G1942" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52990,7 +52993,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1943" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53016,7 +53019,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1944" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53042,7 +53045,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1945" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53068,7 +53071,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1946" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53094,7 +53097,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1947" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53120,7 +53123,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1948" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -53146,7 +53149,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1949" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -53172,7 +53175,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1950" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -53198,7 +53201,7 @@
         <v>12.25</v>
       </c>
       <c r="G1951" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -53224,7 +53227,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1952" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -53250,7 +53253,7 @@
         <v>12.5</v>
       </c>
       <c r="G1953" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -53276,7 +53279,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1954" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -53302,7 +53305,7 @@
         <v>12.25</v>
       </c>
       <c r="G1955" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -53328,7 +53331,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1956" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -53354,7 +53357,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1957" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53380,7 +53383,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1958" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53406,7 +53409,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1959" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53432,7 +53435,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1960" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53458,7 +53461,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1961" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53484,7 +53487,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1962" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53510,7 +53513,7 @@
         <v>10.5</v>
       </c>
       <c r="G1963" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53536,7 +53539,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1964" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53562,7 +53565,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1965" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53588,7 +53591,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1966" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53614,7 +53617,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1967" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53640,7 +53643,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1968" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53666,7 +53669,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1969" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53692,7 +53695,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1970" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53718,7 +53721,7 @@
         <v>12</v>
       </c>
       <c r="G1971" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53744,7 +53747,7 @@
         <v>12</v>
       </c>
       <c r="G1972" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53770,7 +53773,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1973" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53796,7 +53799,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1974" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53822,7 +53825,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1975" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53848,7 +53851,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1976" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53874,7 +53877,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1977" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53900,7 +53903,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1978" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53926,7 +53929,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1979" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53952,7 +53955,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1980" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53978,7 +53981,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1981" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -54004,7 +54007,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1982" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54030,7 +54033,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54056,7 +54059,7 @@
         <v>13</v>
       </c>
       <c r="G1984" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54082,7 +54085,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1985" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54108,7 +54111,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1986" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -54134,7 +54137,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1987" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -54160,7 +54163,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1988" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -54186,7 +54189,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1989" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -54212,7 +54215,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1990" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -54238,7 +54241,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1991" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -54264,7 +54267,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1992" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -54290,7 +54293,7 @@
         <v>13.5</v>
       </c>
       <c r="G1993" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -54316,7 +54319,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1994" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -54342,7 +54345,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1995" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54368,7 +54371,7 @@
         <v>14.5</v>
       </c>
       <c r="G1996" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54394,7 +54397,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1997" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54420,7 +54423,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1998" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54446,7 +54449,7 @@
         <v>15</v>
       </c>
       <c r="G1999" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54472,7 +54475,7 @@
         <v>15.5</v>
       </c>
       <c r="G2000" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54498,7 +54501,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2001" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54524,7 +54527,7 @@
         <v>15.5</v>
       </c>
       <c r="G2002" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54550,7 +54553,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2003" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54576,7 +54579,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2004" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54602,7 +54605,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2005" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54628,7 +54631,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2006" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54654,7 +54657,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2007" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54680,7 +54683,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2008" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54706,7 +54709,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2009" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54732,7 +54735,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2010" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54758,7 +54761,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2011" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54784,7 +54787,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2012" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54810,7 +54813,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2013" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54836,7 +54839,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2014" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54862,7 +54865,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2015" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54888,7 +54891,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2016" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54914,7 +54917,7 @@
         <v>16</v>
       </c>
       <c r="G2017" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54940,7 +54943,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2018" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54966,7 +54969,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2019" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54992,7 +54995,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2020" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55018,7 +55021,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2021" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55044,7 +55047,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2022" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55070,7 +55073,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2023" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55096,7 +55099,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2024" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -55122,7 +55125,7 @@
         <v>17.5</v>
       </c>
       <c r="G2025" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -55148,7 +55151,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2026" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -55174,7 +55177,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2027" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -55200,7 +55203,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2028" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -55226,7 +55229,7 @@
         <v>17.5</v>
       </c>
       <c r="G2029" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -55252,7 +55255,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2030" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -55278,7 +55281,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2031" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -55304,7 +55307,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2032" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -55330,7 +55333,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G2033" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -55356,7 +55359,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2034" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -55382,7 +55385,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2035" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -55408,7 +55411,7 @@
         <v>17.5</v>
       </c>
       <c r="G2036" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -55434,7 +55437,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2037" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55460,7 +55463,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2038" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55486,7 +55489,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2039" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55512,7 +55515,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2040" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55538,7 +55541,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2041" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55564,7 +55567,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2042" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55590,7 +55593,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2043" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55616,7 +55619,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2044" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55642,7 +55645,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2045" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55668,7 +55671,7 @@
         <v>13</v>
       </c>
       <c r="G2046" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55694,7 +55697,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2047" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55720,7 +55723,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2048" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55746,7 +55749,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2049" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55772,7 +55775,7 @@
         <v>12</v>
       </c>
       <c r="G2050" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55798,7 +55801,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2051" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55824,7 +55827,7 @@
         <v>12</v>
       </c>
       <c r="G2052" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55850,7 +55853,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2053" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55876,7 +55879,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2054" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55902,7 +55905,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2055" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55928,7 +55931,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2056" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55954,7 +55957,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2057" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55980,7 +55983,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2058" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -56006,7 +56009,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2059" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -56032,7 +56035,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2060" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -56058,7 +56061,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2061" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -56084,7 +56087,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2062" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -56110,7 +56113,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2063" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -56136,7 +56139,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2064" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -56162,7 +56165,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2065" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -56188,7 +56191,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2066" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -56214,7 +56217,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2067" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -56240,7 +56243,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2068" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -56266,7 +56269,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2069" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -56292,7 +56295,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2070" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -56318,7 +56321,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2071" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -56344,7 +56347,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2072" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -56370,7 +56373,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2073" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -56396,7 +56399,7 @@
         <v>14</v>
       </c>
       <c r="G2074" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -56422,7 +56425,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2075" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56448,7 +56451,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2076" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56474,7 +56477,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2077" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56500,7 +56503,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2078" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56526,7 +56529,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2079" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -56552,7 +56555,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2080" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -56578,7 +56581,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2081" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56604,7 +56607,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2082" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56630,7 +56633,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2083" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56656,7 +56659,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2084" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56682,7 +56685,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2085" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56708,7 +56711,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2086" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56734,7 +56737,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2087" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56760,7 +56763,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2088" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56786,7 +56789,7 @@
         <v>15.5</v>
       </c>
       <c r="G2089" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56812,7 +56815,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G2090" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56838,7 +56841,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2091" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56864,7 +56867,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2092" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56890,7 +56893,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2093" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56916,7 +56919,7 @@
         <v>14.5</v>
       </c>
       <c r="G2094" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56942,7 +56945,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2095" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56968,7 +56971,7 @@
         <v>15</v>
       </c>
       <c r="G2096" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56994,7 +56997,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2097" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -57020,7 +57023,7 @@
         <v>15</v>
       </c>
       <c r="G2098" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -57046,7 +57049,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2099" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -57072,7 +57075,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2100" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -57098,7 +57101,7 @@
         <v>15</v>
       </c>
       <c r="G2101" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -57124,7 +57127,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2102" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -57150,7 +57153,7 @@
         <v>15</v>
       </c>
       <c r="G2103" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -57176,7 +57179,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2104" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -57202,7 +57205,7 @@
         <v>15</v>
       </c>
       <c r="G2105" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -57228,7 +57231,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2106" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -57254,7 +57257,7 @@
         <v>15</v>
       </c>
       <c r="G2107" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -57280,7 +57283,7 @@
         <v>15</v>
       </c>
       <c r="G2108" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -57306,7 +57309,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2109" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -57332,7 +57335,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2110" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -57358,7 +57361,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G2111" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -57384,7 +57387,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2112" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -57410,7 +57413,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2113" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -57436,7 +57439,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2114" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -57462,7 +57465,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2115" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -57488,7 +57491,7 @@
         <v>14</v>
       </c>
       <c r="G2116" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -57514,7 +57517,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2117" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57540,7 +57543,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2118" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -57566,7 +57569,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2119" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57592,7 +57595,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2120" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57618,7 +57621,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2121" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57644,7 +57647,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2122" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57670,7 +57673,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2123" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57696,7 +57699,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2124" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57722,7 +57725,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2125" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57748,7 +57751,7 @@
         <v>13</v>
       </c>
       <c r="G2126" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -57774,7 +57777,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2127" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57800,7 +57803,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G2128" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57826,7 +57829,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2129" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57852,7 +57855,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2130" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57878,7 +57881,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2131" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57904,7 +57907,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G2132" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57930,7 +57933,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2133" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57956,7 +57959,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2134" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57982,7 +57985,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G2135" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -58008,7 +58011,7 @@
         <v>14.5</v>
       </c>
       <c r="G2136" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -58034,7 +58037,7 @@
         <v>14</v>
       </c>
       <c r="G2137" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -58060,7 +58063,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2138" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -58086,7 +58089,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2139" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -58112,7 +58115,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2140" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -58138,7 +58141,7 @@
         <v>14</v>
       </c>
       <c r="G2141" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -58164,7 +58167,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2142" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -58190,7 +58193,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2143" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -58216,7 +58219,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2144" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -58242,7 +58245,7 @@
         <v>18.5</v>
       </c>
       <c r="G2145" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>

--- a/data/CULT.MI.xlsx
+++ b/data/CULT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="711">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68585252761841</t>
+    <t xml:space="preserve">4.68585300445557</t>
   </si>
   <si>
     <t xml:space="preserve">CULT.MI</t>
@@ -47,58 +47,58 @@
     <t xml:space="preserve">4.57666683197021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59486532211304</t>
+    <t xml:space="preserve">4.5948657989502</t>
   </si>
   <si>
     <t xml:space="preserve">4.60851287841797</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58576679229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48931932449341</t>
+    <t xml:space="preserve">4.58576631546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48931980133057</t>
   </si>
   <si>
     <t xml:space="preserve">4.56301927566528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51297616958618</t>
+    <t xml:space="preserve">4.51297569274902</t>
   </si>
   <si>
     <t xml:space="preserve">4.46020412445068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29824590682983</t>
+    <t xml:space="preserve">4.29824638366699</t>
   </si>
   <si>
     <t xml:space="preserve">4.21271800994873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18178224563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23091554641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36375665664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38195466995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35101938247681</t>
+    <t xml:space="preserve">4.18178176879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23091506958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36375617980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38195419311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35101842880249</t>
   </si>
   <si>
     <t xml:space="preserve">4.28914785385132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24183464050293</t>
+    <t xml:space="preserve">4.24183368682861</t>
   </si>
   <si>
     <t xml:space="preserve">4.22909545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10535287857056</t>
+    <t xml:space="preserve">4.10535335540771</t>
   </si>
   <si>
     <t xml:space="preserve">4.09443426132202</t>
@@ -113,19 +113,19 @@
     <t xml:space="preserve">4.04712057113647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03984117507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96341252326965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07441711425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3200831413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24911308288574</t>
+    <t xml:space="preserve">4.0398416519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96341228485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07441806793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32008266448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24911260604858</t>
   </si>
   <si>
     <t xml:space="preserve">3.97979021072388</t>
@@ -134,25 +134,25 @@
     <t xml:space="preserve">4.0689582824707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05439949035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98524928092957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0507607460022</t>
+    <t xml:space="preserve">4.05439901351929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98524951934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05075979232788</t>
   </si>
   <si>
     <t xml:space="preserve">4.07259702682495</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03802299499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04530143737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03074264526367</t>
+    <t xml:space="preserve">4.0380220413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04530191421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03074359893799</t>
   </si>
   <si>
     <t xml:space="preserve">4.01254558563232</t>
@@ -161,37 +161,37 @@
     <t xml:space="preserve">4.04894065856934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05985832214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07623672485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91246008872986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99070906639099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01072597503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92155814170837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00162696838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05803966522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21635723114014</t>
+    <t xml:space="preserve">4.05985879898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07623720169067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9124596118927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99070835113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01072549819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92155766487122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00162744522095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05803918838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21635675430298</t>
   </si>
   <si>
     <t xml:space="preserve">4.2218165397644</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18542146682739</t>
+    <t xml:space="preserve">4.18542098999023</t>
   </si>
   <si>
     <t xml:space="preserve">4.16176462173462</t>
@@ -200,22 +200,22 @@
     <t xml:space="preserve">4.35465812683105</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28186845779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26730966567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39287328720093</t>
+    <t xml:space="preserve">4.28186798095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26731014251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39287281036377</t>
   </si>
   <si>
     <t xml:space="preserve">4.36739683151245</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17814254760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27458906173706</t>
+    <t xml:space="preserve">4.17814302444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27458953857422</t>
   </si>
   <si>
     <t xml:space="preserve">4.31826305389404</t>
@@ -224,73 +224,73 @@
     <t xml:space="preserve">4.35647821426392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26549005508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26367044448853</t>
+    <t xml:space="preserve">4.26549053192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26367092132568</t>
   </si>
   <si>
     <t xml:space="preserve">4.27640914916992</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14902639389038</t>
+    <t xml:space="preserve">4.14902591705322</t>
   </si>
   <si>
     <t xml:space="preserve">4.35829782485962</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35283851623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29460620880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2036190032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24001359939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34010076522827</t>
+    <t xml:space="preserve">4.35283803939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29460668563843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20361948013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24001407623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34010028839111</t>
   </si>
   <si>
     <t xml:space="preserve">4.42926836013794</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34919834136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33646059036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33100271224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32190275192261</t>
+    <t xml:space="preserve">4.34919929504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33646106719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33100175857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32190322875977</t>
   </si>
   <si>
     <t xml:space="preserve">4.46748208999634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45838308334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2855076789856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83057069778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90336060523987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88516330718994</t>
+    <t xml:space="preserve">4.45838451385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28550720214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83057045936584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90336084365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8851625919342</t>
   </si>
   <si>
     <t xml:space="preserve">3.87606453895569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00344705581665</t>
+    <t xml:space="preserve">4.00344657897949</t>
   </si>
   <si>
     <t xml:space="preserve">3.93065643310547</t>
@@ -299,157 +299,157 @@
     <t xml:space="preserve">3.9943482875824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08533573150635</t>
+    <t xml:space="preserve">4.08533477783203</t>
   </si>
   <si>
     <t xml:space="preserve">3.96705222129822</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86696553230286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84876728057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8578667640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81237292289734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8032751083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77597808837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97615051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94885444641113</t>
+    <t xml:space="preserve">3.86696577072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84876847267151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85786628723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81237316131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80327439308167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77597832679749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97615027427673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94885468482971</t>
   </si>
   <si>
     <t xml:space="preserve">4.13992786407471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16722440719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33528280258179</t>
+    <t xml:space="preserve">4.16722393035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33528327941895</t>
   </si>
   <si>
     <t xml:space="preserve">4.21485900878906</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31675624847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42791700363159</t>
+    <t xml:space="preserve">4.31675672531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42791748046875</t>
   </si>
   <si>
     <t xml:space="preserve">4.19633197784424</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16854190826416</t>
+    <t xml:space="preserve">4.168541431427</t>
   </si>
   <si>
     <t xml:space="preserve">4.29822969436646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30749320983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27970266342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39086437225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40012741088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35381031036377</t>
+    <t xml:space="preserve">4.30749273300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27970314025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3908634185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40012788772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35380983352661</t>
   </si>
   <si>
     <t xml:space="preserve">4.08517074584961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93695592880249</t>
+    <t xml:space="preserve">3.93695616722107</t>
   </si>
   <si>
     <t xml:space="preserve">4.00179958343506</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97400975227356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03885412216187</t>
+    <t xml:space="preserve">3.97400999069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03885364532471</t>
   </si>
   <si>
     <t xml:space="preserve">3.94621968269348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95548319816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23338556289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22412204742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2426495552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11296033859253</t>
+    <t xml:space="preserve">3.95548248291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23338603973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22412157058716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24264907836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.112961769104</t>
   </si>
   <si>
     <t xml:space="preserve">4.26117563247681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91842842102051</t>
+    <t xml:space="preserve">3.91842937469482</t>
   </si>
   <si>
     <t xml:space="preserve">3.89990234375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89063835144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07590770721436</t>
+    <t xml:space="preserve">3.89063906669617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07590675354004</t>
   </si>
   <si>
     <t xml:space="preserve">4.06664419174194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79800462722778</t>
+    <t xml:space="preserve">3.79800415039062</t>
   </si>
   <si>
     <t xml:space="preserve">3.73316073417664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86284875869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71463418006897</t>
+    <t xml:space="preserve">3.86284852027893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71463394165039</t>
   </si>
   <si>
     <t xml:space="preserve">3.70537042617798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77021431922913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39041376113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44599437713623</t>
+    <t xml:space="preserve">3.77021455764771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3904139995575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44599461555481</t>
   </si>
   <si>
     <t xml:space="preserve">3.58494591712952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68684363365173</t>
+    <t xml:space="preserve">3.68684339523315</t>
   </si>
   <si>
     <t xml:space="preserve">3.60347294807434</t>
@@ -464,22 +464,22 @@
     <t xml:space="preserve">3.46452140808105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53862857818604</t>
+    <t xml:space="preserve">3.53862905502319</t>
   </si>
   <si>
     <t xml:space="preserve">3.5293653011322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45525765419006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34409689903259</t>
+    <t xml:space="preserve">3.45525813102722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34409666061401</t>
   </si>
   <si>
     <t xml:space="preserve">3.07545757293701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14956521987915</t>
+    <t xml:space="preserve">3.14956498146057</t>
   </si>
   <si>
     <t xml:space="preserve">3.29777956008911</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">3.31630659103394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23293542861938</t>
+    <t xml:space="preserve">3.23293590545654</t>
   </si>
   <si>
     <t xml:space="preserve">3.24219918251038</t>
@@ -500,52 +500,52 @@
     <t xml:space="preserve">3.20514559745789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25146269798279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10324764251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15882849693298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91797924041748</t>
+    <t xml:space="preserve">3.25146245956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10324740409851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1588282585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9179790019989</t>
   </si>
   <si>
     <t xml:space="preserve">2.74197435379028</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77902770042419</t>
+    <t xml:space="preserve">2.77902793884277</t>
   </si>
   <si>
     <t xml:space="preserve">2.871661901474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96429634094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85313510894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83460855484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8438720703125</t>
+    <t xml:space="preserve">2.9642961025238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85313487052917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83460831642151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84387183189392</t>
   </si>
   <si>
     <t xml:space="preserve">2.72344732284546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76050090789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76976418495178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63081336021423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67712998390198</t>
+    <t xml:space="preserve">2.76050114631653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76976442337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6308126449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67713022232056</t>
   </si>
   <si>
     <t xml:space="preserve">2.38070034980774</t>
@@ -554,25 +554,25 @@
     <t xml:space="preserve">2.36217379570007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29732966423035</t>
+    <t xml:space="preserve">2.29732942581177</t>
   </si>
   <si>
     <t xml:space="preserve">2.31585645675659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35291004180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26953887939453</t>
+    <t xml:space="preserve">2.35291028022766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26953935623169</t>
   </si>
   <si>
     <t xml:space="preserve">2.23248553276062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28806638717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08427095413208</t>
+    <t xml:space="preserve">2.28806662559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0842707157135</t>
   </si>
   <si>
     <t xml:space="preserve">2.1305878162384</t>
@@ -584,43 +584,43 @@
     <t xml:space="preserve">2.24174928665161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11206102371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17690515518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03795385360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99163699150085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88047564029694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94531917572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92679250240326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16764140129089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13985133171082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2139585018158</t>
+    <t xml:space="preserve">2.11206078529358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17690491676331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03795337677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99163675308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88047540187836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94531953334808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92679262161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16764163970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13985157012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21395874023438</t>
   </si>
   <si>
     <t xml:space="preserve">2.4084906578064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48259806632996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42701745033264</t>
+    <t xml:space="preserve">2.48259782791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42701768875122</t>
   </si>
   <si>
     <t xml:space="preserve">2.38996386528015</t>
@@ -629,28 +629,28 @@
     <t xml:space="preserve">2.46583580970764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50406527519226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65698599815369</t>
+    <t xml:space="preserve">2.50406575202942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65698575973511</t>
   </si>
   <si>
     <t xml:space="preserve">2.71433091163635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54229593276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58052587509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52318096160889</t>
+    <t xml:space="preserve">2.5422956943512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58052611351013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52318072319031</t>
   </si>
   <si>
     <t xml:space="preserve">2.42760562896729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38937592506409</t>
+    <t xml:space="preserve">2.38937568664551</t>
   </si>
   <si>
     <t xml:space="preserve">2.48495078086853</t>
@@ -659,16 +659,16 @@
     <t xml:space="preserve">2.61875581741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56141066551208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6378710269928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73344588279724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69521594047546</t>
+    <t xml:space="preserve">2.56141090393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63787078857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73344564437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69521570205688</t>
   </si>
   <si>
     <t xml:space="preserve">2.75256109237671</t>
@@ -677,19 +677,19 @@
     <t xml:space="preserve">2.80990600585938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82902121543884</t>
+    <t xml:space="preserve">2.82902097702026</t>
   </si>
   <si>
     <t xml:space="preserve">2.84813594818115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05840086936951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86725091934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77167630195618</t>
+    <t xml:space="preserve">3.05840110778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86725068092346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7716760635376</t>
   </si>
   <si>
     <t xml:space="preserve">2.676100730896</t>
@@ -701,40 +701,40 @@
     <t xml:space="preserve">2.44672083854675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3702609539032</t>
+    <t xml:space="preserve">2.37026071548462</t>
   </si>
   <si>
     <t xml:space="preserve">3.09663105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34512639045715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45981574058533</t>
+    <t xml:space="preserve">3.34512591362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45981597900391</t>
   </si>
   <si>
     <t xml:space="preserve">3.74654126167297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76565647125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01415061950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10972690582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97592115402222</t>
+    <t xml:space="preserve">3.76565623283386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01415109634399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1097264289856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97592091560364</t>
   </si>
   <si>
     <t xml:space="preserve">3.88034629821777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82300090789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44070076942444</t>
+    <t xml:space="preserve">3.82300114631653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44070100784302</t>
   </si>
   <si>
     <t xml:space="preserve">3.40247106552124</t>
@@ -743,43 +743,43 @@
     <t xml:space="preserve">3.36424112319946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68919610977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72742605209351</t>
+    <t xml:space="preserve">3.68919587135315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72742581367493</t>
   </si>
   <si>
     <t xml:space="preserve">3.7083113193512</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57450580596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55539083480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51716113090515</t>
+    <t xml:space="preserve">3.5745062828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55539107322693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51716136932373</t>
   </si>
   <si>
     <t xml:space="preserve">3.63185119628906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53627610206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61273598670959</t>
+    <t xml:space="preserve">3.53627634048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61273622512817</t>
   </si>
   <si>
     <t xml:space="preserve">3.65096616744995</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24955129623413</t>
+    <t xml:space="preserve">3.24955105781555</t>
   </si>
   <si>
     <t xml:space="preserve">3.32601118087769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42158627510071</t>
+    <t xml:space="preserve">3.42158579826355</t>
   </si>
   <si>
     <t xml:space="preserve">3.3068962097168</t>
@@ -788,13 +788,13 @@
     <t xml:space="preserve">3.38335609436035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59362149238586</t>
+    <t xml:space="preserve">3.59362101554871</t>
   </si>
   <si>
     <t xml:space="preserve">3.47893095016479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49804592132568</t>
+    <t xml:space="preserve">3.49804639816284</t>
   </si>
   <si>
     <t xml:space="preserve">3.28778123855591</t>
@@ -803,10 +803,10 @@
     <t xml:space="preserve">3.67008113861084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80388617515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93769121170044</t>
+    <t xml:space="preserve">3.80388641357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93769145011902</t>
   </si>
   <si>
     <t xml:space="preserve">4.03326606750488</t>
@@ -815,40 +815,40 @@
     <t xml:space="preserve">4.18618679046631</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30087661743164</t>
+    <t xml:space="preserve">4.3008770942688</t>
   </si>
   <si>
     <t xml:space="preserve">4.5302562713623</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51114082336426</t>
+    <t xml:space="preserve">4.51114130020142</t>
   </si>
   <si>
     <t xml:space="preserve">4.58760166168213</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49202632904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43468189239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62583208084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7405219078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75963592529297</t>
+    <t xml:space="preserve">4.49202585220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43468141555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62583160400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74052143096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75963687896729</t>
   </si>
   <si>
     <t xml:space="preserve">4.70229148864746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68317604064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77875185012817</t>
+    <t xml:space="preserve">4.68317699432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77875137329102</t>
   </si>
   <si>
     <t xml:space="preserve">4.56848621368408</t>
@@ -857,46 +857,46 @@
     <t xml:space="preserve">4.66406154632568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72140645980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87432670593262</t>
+    <t xml:space="preserve">4.72140693664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87432622909546</t>
   </si>
   <si>
     <t xml:space="preserve">4.96990156173706</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92211389541626</t>
+    <t xml:space="preserve">4.92211437225342</t>
   </si>
   <si>
     <t xml:space="preserve">5.1132640838623</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16105175018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20883989334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25662612915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30441427230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44777584075928</t>
+    <t xml:space="preserve">5.16105222702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20883893966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25662708282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30441474914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44777631759644</t>
   </si>
   <si>
     <t xml:space="preserve">5.63892650604248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59113931655884</t>
+    <t xml:space="preserve">5.59113883972168</t>
   </si>
   <si>
     <t xml:space="preserve">5.81332683563232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71643781661987</t>
+    <t xml:space="preserve">5.71643829345703</t>
   </si>
   <si>
     <t xml:space="preserve">5.42577171325684</t>
@@ -908,13 +908,13 @@
     <t xml:space="preserve">4.8444390296936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82506132125854</t>
+    <t xml:space="preserve">4.8250617980957</t>
   </si>
   <si>
     <t xml:space="preserve">4.80568361282349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59252834320068</t>
+    <t xml:space="preserve">4.59252786636353</t>
   </si>
   <si>
     <t xml:space="preserve">4.55377244949341</t>
@@ -926,13 +926,13 @@
     <t xml:space="preserve">5.03821659088135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98977184295654</t>
+    <t xml:space="preserve">4.9897723197937</t>
   </si>
   <si>
     <t xml:space="preserve">5.08666086196899</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18354940414429</t>
+    <t xml:space="preserve">5.18354988098145</t>
   </si>
   <si>
     <t xml:space="preserve">4.9413275718689</t>
@@ -941,64 +941,64 @@
     <t xml:space="preserve">5.23199415206909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74754953384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28043842315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89288330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63128328323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53439474105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67003870010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78630542755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72817277908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70879459381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91021585464478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61954975128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32888269424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37732744216919</t>
+    <t xml:space="preserve">4.74755048751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28043794631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89288377761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6312837600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53439426422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67003917694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78630590438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72817230224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70879507064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91021537780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61954879760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32888317108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37732696533203</t>
   </si>
   <si>
     <t xml:space="preserve">5.57110452651978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47421598434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66799354553223</t>
+    <t xml:space="preserve">5.47421550750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66799402236938</t>
   </si>
   <si>
     <t xml:space="preserve">6.73376989364624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29777097702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44310331344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68532562255859</t>
+    <t xml:space="preserve">6.29777002334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4431037902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68532609939575</t>
   </si>
   <si>
     <t xml:space="preserve">6.58843755722046</t>
@@ -1013,16 +1013,16 @@
     <t xml:space="preserve">6.34621524810791</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5399923324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39465999603271</t>
+    <t xml:space="preserve">6.53999280929565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39465951919556</t>
   </si>
   <si>
     <t xml:space="preserve">8.71999073028564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99332427978516</t>
+    <t xml:space="preserve">7.99332332611084</t>
   </si>
   <si>
     <t xml:space="preserve">8.09021377563477</t>
@@ -1034,10 +1034,10 @@
     <t xml:space="preserve">7.94488000869751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84799194335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89643478393555</t>
+    <t xml:space="preserve">7.84799098968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89643430709839</t>
   </si>
   <si>
     <t xml:space="preserve">8.38087844848633</t>
@@ -1052,34 +1052,34 @@
     <t xml:space="preserve">10.173321723938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97954368591309</t>
+    <t xml:space="preserve">9.9795446395874</t>
   </si>
   <si>
     <t xml:space="preserve">10.0764331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2390995025635</t>
+    <t xml:space="preserve">11.2390975952148</t>
   </si>
   <si>
     <t xml:space="preserve">11.6266536712646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.079984664917</t>
+    <t xml:space="preserve">13.0799856185913</t>
   </si>
   <si>
     <t xml:space="preserve">13.2737617492676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9830961227417</t>
+    <t xml:space="preserve">12.983097076416</t>
   </si>
   <si>
     <t xml:space="preserve">14.436427116394</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3395385742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0177612304688</t>
+    <t xml:space="preserve">14.3395404815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0177602767944</t>
   </si>
   <si>
     <t xml:space="preserve">16.1669788360596</t>
@@ -1088,10 +1088,10 @@
     <t xml:space="preserve">15.1930656433105</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0956745147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9008903503418</t>
+    <t xml:space="preserve">15.0956735610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9008913040161</t>
   </si>
   <si>
     <t xml:space="preserve">13.634801864624</t>
@@ -1100,31 +1100,31 @@
     <t xml:space="preserve">12.0765390396118</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4661045074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4400205612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9269771575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0243673324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2191524505615</t>
+    <t xml:space="preserve">12.4661054611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4400196075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9269762039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0243663787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2191505432129</t>
   </si>
   <si>
     <t xml:space="preserve">14.8034992218018</t>
   </si>
   <si>
-    <t xml:space="preserve">14.413932800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6087160110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.706109046936</t>
+    <t xml:space="preserve">14.4139347076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6087169647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7061080932617</t>
   </si>
   <si>
     <t xml:space="preserve">14.5113248825073</t>
@@ -1133,19 +1133,19 @@
     <t xml:space="preserve">13.3426275253296</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1217584609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3165426254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8295841217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5374097824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2452363967896</t>
+    <t xml:space="preserve">14.1217594146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3165416717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8295850753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.537410736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2452373504639</t>
   </si>
   <si>
     <t xml:space="preserve">12.8556709289551</t>
@@ -1154,25 +1154,25 @@
     <t xml:space="preserve">12.3687133789062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7582788467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5634965896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1739301681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6869745254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1026239395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93392753601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7130584716797</t>
+    <t xml:space="preserve">12.758279800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5634956359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1739311218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6869735717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1026248931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93392658233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.713059425354</t>
   </si>
   <si>
     <t xml:space="preserve">11.2000160217285</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">11.2974071502686</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3947982788086</t>
+    <t xml:space="preserve">11.3948001861572</t>
   </si>
   <si>
     <t xml:space="preserve">11.589581489563</t>
@@ -1199,34 +1199,34 @@
     <t xml:space="preserve">11.0052328109741</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7843647003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4921903610229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8104515075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4208841323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2261009216309</t>
+    <t xml:space="preserve">11.7843656539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4921913146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.810450553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4208850860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2261018753052</t>
   </si>
   <si>
     <t xml:space="preserve">10.3234939575195</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1287097930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0313196182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73914432525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54436206817627</t>
+    <t xml:space="preserve">10.1287107467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0313186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73914337158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54436111450195</t>
   </si>
   <si>
     <t xml:space="preserve">9.8365364074707</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">9.34957885742188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49566650390625</t>
+    <t xml:space="preserve">9.49566555023193</t>
   </si>
   <si>
     <t xml:space="preserve">12.2713222503662</t>
@@ -1250,10 +1250,10 @@
     <t xml:space="preserve">13.7321939468384</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1704559326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3652372360229</t>
+    <t xml:space="preserve">14.1704549789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3652391433716</t>
   </si>
   <si>
     <t xml:space="preserve">14.0730638504028</t>
@@ -1262,13 +1262,13 @@
     <t xml:space="preserve">15.1443700790405</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5364561080933</t>
+    <t xml:space="preserve">15.5364570617676</t>
   </si>
   <si>
     <t xml:space="preserve">15.585467338562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6344785690308</t>
+    <t xml:space="preserve">15.6344776153564</t>
   </si>
   <si>
     <t xml:space="preserve">15.193380355835</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">15.4384346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2423906326294</t>
+    <t xml:space="preserve">15.2423915863037</t>
   </si>
   <si>
     <t xml:space="preserve">15.3894233703613</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">13.9190969467163</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1641502380371</t>
+    <t xml:space="preserve">14.1641511917114</t>
   </si>
   <si>
     <t xml:space="preserve">13.7230529785156</t>
@@ -1310,31 +1310,31 @@
     <t xml:space="preserve">13.8210754394531</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3601951599121</t>
+    <t xml:space="preserve">14.3601942062378</t>
   </si>
   <si>
     <t xml:space="preserve">13.6250314712524</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8700847625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6740417480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7720651626587</t>
+    <t xml:space="preserve">13.8700857162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6740427017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7720642089844</t>
   </si>
   <si>
     <t xml:space="preserve">14.0171184539795</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1839323043823</t>
+    <t xml:space="preserve">13.1839332580566</t>
   </si>
   <si>
     <t xml:space="preserve">13.5270099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9483251571655</t>
+    <t xml:space="preserve">14.9483261108398</t>
   </si>
   <si>
     <t xml:space="preserve">14.4092054367065</t>
@@ -1343,43 +1343,43 @@
     <t xml:space="preserve">14.8503036499023</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7522821426392</t>
+    <t xml:space="preserve">14.7522830963135</t>
   </si>
   <si>
     <t xml:space="preserve">14.6052494049072</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7032709121704</t>
+    <t xml:space="preserve">14.7032718658447</t>
   </si>
   <si>
     <t xml:space="preserve">14.5562391281128</t>
   </si>
   <si>
-    <t xml:space="preserve">14.507227897644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0661306381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3309659957886</t>
+    <t xml:space="preserve">14.5072288513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0661296844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3309669494629</t>
   </si>
   <si>
     <t xml:space="preserve">13.4779987335205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2819557189941</t>
+    <t xml:space="preserve">13.2819547653198</t>
   </si>
   <si>
     <t xml:space="preserve">12.8898668289185</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7428350448608</t>
+    <t xml:space="preserve">12.7428340911865</t>
   </si>
   <si>
     <t xml:space="preserve">12.9878902435303</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1349220275879</t>
+    <t xml:space="preserve">13.1349229812622</t>
   </si>
   <si>
     <t xml:space="preserve">12.3507480621338</t>
@@ -1391,16 +1391,16 @@
     <t xml:space="preserve">11.3215188980103</t>
   </si>
   <si>
-    <t xml:space="preserve">12.301736831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0859117507935</t>
+    <t xml:space="preserve">12.3017377853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0859127044678</t>
   </si>
   <si>
     <t xml:space="preserve">13.4289875030518</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8305225372314</t>
+    <t xml:space="preserve">15.8305215835571</t>
   </si>
   <si>
     <t xml:space="preserve">15.7324991226196</t>
@@ -1409,19 +1409,19 @@
     <t xml:space="preserve">15.8795328140259</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9775552749634</t>
+    <t xml:space="preserve">15.9775533676147</t>
   </si>
   <si>
     <t xml:space="preserve">16.3696422576904</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6834897994995</t>
+    <t xml:space="preserve">15.6834888458252</t>
   </si>
   <si>
     <t xml:space="preserve">15.7815113067627</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2226104736328</t>
+    <t xml:space="preserve">16.2226085662842</t>
   </si>
   <si>
     <t xml:space="preserve">16.0265655517578</t>
@@ -1433,13 +1433,13 @@
     <t xml:space="preserve">15.9285440444946</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1735992431641</t>
+    <t xml:space="preserve">16.1735973358154</t>
   </si>
   <si>
     <t xml:space="preserve">16.2716197967529</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3206310272217</t>
+    <t xml:space="preserve">16.320629119873</t>
   </si>
   <si>
     <t xml:space="preserve">18.7221660614014</t>
@@ -1448,193 +1448,196 @@
     <t xml:space="preserve">19.0162296295166</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7023849487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.604362487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8004055023193</t>
+    <t xml:space="preserve">19.7023830413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6043605804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.800407409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0944709777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9173202514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.545015335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5252342224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7995166778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2311706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7806243896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1727104187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4865589141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6826019287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3687534332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6430377960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9955596923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2896251678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6034755706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8975391387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5054531097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.015344619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6232566833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8390808105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3291893005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.937105178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7212791442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1133651733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0351257324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1331481933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2113876342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4074287414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8192977905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2509498596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7608413696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9568843841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1529273986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7711753845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6439266204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5261211395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9964485168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5845794677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1924934387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8984279632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3885364532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4049549102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6512107849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3557014465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5527095794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7989635467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6019592285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9616947174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0601978302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0109443664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1586990356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2914772033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1929721832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1779956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9809913635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4884796142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5869827270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9959678649902</t>
   </si>
   <si>
     <t xml:space="preserve">20.0944690704346</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9173202514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.545015335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5252342224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7995166778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2311687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7806243896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1727104187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4865570068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6826038360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3687534332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6430377960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9955615997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2896251678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6034736633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8975391387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5054531097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.015344619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.623254776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8390808105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3291893005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9371032714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7212791442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1133651733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0351238250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1331462860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2113857269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4074306488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.819299697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2509517669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7608413696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9568843841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1529293060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7711753845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6439247131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5261211395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9964485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5845794677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1924934387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8984260559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3885345458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4049549102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6512107849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3557014465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5527095794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7989654541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.601957321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9616947174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0601978302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0109443664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1586990356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2914772033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1929721832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1779956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9809913635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4884796142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5869808197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9959678649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4542064666748</t>
+    <t xml:space="preserve">19.4542045593262</t>
   </si>
   <si>
     <t xml:space="preserve">19.5034561157227</t>
@@ -1646,7 +1649,7 @@
     <t xml:space="preserve">19.207950592041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0259208679199</t>
+    <t xml:space="preserve">18.0259227752686</t>
   </si>
   <si>
     <t xml:space="preserve">18.075174331665</t>
@@ -1670,19 +1673,19 @@
     <t xml:space="preserve">17.9274196624756</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9766712188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.434907913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1736755371094</t>
+    <t xml:space="preserve">17.9766693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4349098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.173677444458</t>
   </si>
   <si>
     <t xml:space="preserve">18.4199314117432</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7839889526367</t>
+    <t xml:space="preserve">20.7839870452881</t>
   </si>
   <si>
     <t xml:space="preserve">20.3899784088135</t>
@@ -1691,10 +1694,10 @@
     <t xml:space="preserve">19.7004623413086</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9124431610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1094455718994</t>
+    <t xml:space="preserve">18.9124450683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.109447479248</t>
   </si>
   <si>
     <t xml:space="preserve">18.8631916046143</t>
@@ -1703,7 +1706,7 @@
     <t xml:space="preserve">18.5184326171875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7154388427734</t>
+    <t xml:space="preserve">18.7154369354248</t>
   </si>
   <si>
     <t xml:space="preserve">18.2229270935059</t>
@@ -1712,7 +1715,7 @@
     <t xml:space="preserve">17.7796649932861</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5676860809326</t>
+    <t xml:space="preserve">18.567684173584</t>
   </si>
   <si>
     <t xml:space="preserve">17.7304153442383</t>
@@ -1724,16 +1727,16 @@
     <t xml:space="preserve">18.2721767425537</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6811637878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8781700134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1244258880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6319141387939</t>
+    <t xml:space="preserve">17.6811656951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8781681060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1244239807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6319122314453</t>
   </si>
   <si>
     <t xml:space="preserve">17.4841594696045</t>
@@ -1742,7 +1745,7 @@
     <t xml:space="preserve">17.3856582641602</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5334091186523</t>
+    <t xml:space="preserve">17.533411026001</t>
   </si>
   <si>
     <t xml:space="preserve">17.1886520385742</t>
@@ -1757,7 +1760,7 @@
     <t xml:space="preserve">16.4991359710693</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8931465148926</t>
+    <t xml:space="preserve">16.8931446075439</t>
   </si>
   <si>
     <t xml:space="preserve">16.4498863220215</t>
@@ -1769,7 +1772,7 @@
     <t xml:space="preserve">16.6468906402588</t>
   </si>
   <si>
-    <t xml:space="preserve">16.794641494751</t>
+    <t xml:space="preserve">16.7946434020996</t>
   </si>
   <si>
     <t xml:space="preserve">16.7453918457031</t>
@@ -1781,7 +1784,7 @@
     <t xml:space="preserve">14.6275930404663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9723501205444</t>
+    <t xml:space="preserve">14.9723510742188</t>
   </si>
   <si>
     <t xml:space="preserve">14.7260942459106</t>
@@ -1796,7 +1799,7 @@
     <t xml:space="preserve">15.1201047897339</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3663597106934</t>
+    <t xml:space="preserve">15.3663606643677</t>
   </si>
   <si>
     <t xml:space="preserve">15.464861869812</t>
@@ -1805,16 +1808,16 @@
     <t xml:space="preserve">14.7753458023071</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4798393249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2828340530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5783414840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0858306884766</t>
+    <t xml:space="preserve">14.4798383712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2828350067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5783424377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0858297348022</t>
   </si>
   <si>
     <t xml:space="preserve">14.2335834503174</t>
@@ -41446,7 +41449,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1499" t="s">
-        <v>481</v>
+        <v>540</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41498,7 +41501,7 @@
         <v>19.75</v>
       </c>
       <c r="G1501" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41602,7 +41605,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1505" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41628,7 +41631,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1506" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41680,7 +41683,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1508" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41706,7 +41709,7 @@
         <v>19.5</v>
       </c>
       <c r="G1509" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41732,7 +41735,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1510" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41758,7 +41761,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1511" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41784,7 +41787,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1512" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41810,7 +41813,7 @@
         <v>19.5</v>
       </c>
       <c r="G1513" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41836,7 +41839,7 @@
         <v>19.5</v>
       </c>
       <c r="G1514" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41862,7 +41865,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1515" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41888,7 +41891,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1516" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41914,7 +41917,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1517" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -41940,7 +41943,7 @@
         <v>18.75</v>
       </c>
       <c r="G1518" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -41966,7 +41969,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1519" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41992,7 +41995,7 @@
         <v>17.5</v>
       </c>
       <c r="G1520" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42018,7 +42021,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1521" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42044,7 +42047,7 @@
         <v>18.25</v>
       </c>
       <c r="G1522" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42070,7 +42073,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1523" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42096,7 +42099,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1524" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42122,7 +42125,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1525" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42148,7 +42151,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1526" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42174,7 +42177,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1527" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42200,7 +42203,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1528" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42226,7 +42229,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1529" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42356,7 +42359,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1534" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42382,7 +42385,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1535" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42434,7 +42437,7 @@
         <v>20</v>
       </c>
       <c r="G1537" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42512,7 +42515,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1540" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42538,7 +42541,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1541" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42564,7 +42567,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1542" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42616,7 +42619,7 @@
         <v>19.5</v>
       </c>
       <c r="G1544" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42642,7 +42645,7 @@
         <v>19.5</v>
       </c>
       <c r="G1545" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42720,7 +42723,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1548" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42746,7 +42749,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G1549" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42876,7 +42879,7 @@
         <v>19.5</v>
       </c>
       <c r="G1554" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42902,7 +42905,7 @@
         <v>19.5</v>
       </c>
       <c r="G1555" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42928,7 +42931,7 @@
         <v>19.5</v>
       </c>
       <c r="G1556" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42980,7 +42983,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1558" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43006,7 +43009,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1559" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43032,7 +43035,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1560" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43058,7 +43061,7 @@
         <v>19</v>
       </c>
       <c r="G1561" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43084,7 +43087,7 @@
         <v>19</v>
       </c>
       <c r="G1562" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43110,7 +43113,7 @@
         <v>19</v>
       </c>
       <c r="G1563" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43136,7 +43139,7 @@
         <v>19</v>
       </c>
       <c r="G1564" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43162,7 +43165,7 @@
         <v>19</v>
       </c>
       <c r="G1565" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43188,7 +43191,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1566" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43214,7 +43217,7 @@
         <v>19</v>
       </c>
       <c r="G1567" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43240,7 +43243,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1568" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43266,7 +43269,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1569" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43292,7 +43295,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1570" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43318,7 +43321,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1571" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -43344,7 +43347,7 @@
         <v>19</v>
       </c>
       <c r="G1572" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43370,7 +43373,7 @@
         <v>19</v>
       </c>
       <c r="G1573" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43396,7 +43399,7 @@
         <v>19</v>
       </c>
       <c r="G1574" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43422,7 +43425,7 @@
         <v>18.75</v>
       </c>
       <c r="G1575" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43448,7 +43451,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1576" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43474,7 +43477,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1577" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43500,7 +43503,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1578" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43526,7 +43529,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1579" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43552,7 +43555,7 @@
         <v>19</v>
       </c>
       <c r="G1580" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43578,7 +43581,7 @@
         <v>19</v>
       </c>
       <c r="G1581" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43604,7 +43607,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1582" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43630,7 +43633,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1583" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43656,7 +43659,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1584" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43682,7 +43685,7 @@
         <v>18.75</v>
       </c>
       <c r="G1585" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43708,7 +43711,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1586" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43734,7 +43737,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1587" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43760,7 +43763,7 @@
         <v>18.5</v>
       </c>
       <c r="G1588" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43786,7 +43789,7 @@
         <v>18.5</v>
       </c>
       <c r="G1589" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43812,7 +43815,7 @@
         <v>18.5</v>
       </c>
       <c r="G1590" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43838,7 +43841,7 @@
         <v>18.5</v>
       </c>
       <c r="G1591" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43864,7 +43867,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1592" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43890,7 +43893,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1593" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43916,7 +43919,7 @@
         <v>18</v>
       </c>
       <c r="G1594" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43942,7 +43945,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1595" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -43968,7 +43971,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1596" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43994,7 +43997,7 @@
         <v>18.5</v>
       </c>
       <c r="G1597" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44020,7 +44023,7 @@
         <v>18.5</v>
       </c>
       <c r="G1598" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44046,7 +44049,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1599" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44072,7 +44075,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1600" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44098,7 +44101,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1601" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44124,7 +44127,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1602" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44150,7 +44153,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1603" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44176,7 +44179,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1604" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44202,7 +44205,7 @@
         <v>18.25</v>
       </c>
       <c r="G1605" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44228,7 +44231,7 @@
         <v>18</v>
       </c>
       <c r="G1606" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -44254,7 +44257,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1607" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -44280,7 +44283,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1608" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -44306,7 +44309,7 @@
         <v>18</v>
       </c>
       <c r="G1609" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44332,7 +44335,7 @@
         <v>18.25</v>
       </c>
       <c r="G1610" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -44358,7 +44361,7 @@
         <v>18.25</v>
       </c>
       <c r="G1611" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44384,7 +44387,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1612" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44410,7 +44413,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1613" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44436,7 +44439,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1614" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44462,7 +44465,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1615" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44488,7 +44491,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1616" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44514,7 +44517,7 @@
         <v>18</v>
       </c>
       <c r="G1617" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44540,7 +44543,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1618" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44566,7 +44569,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1619" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44592,7 +44595,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1620" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44618,7 +44621,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1621" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44644,7 +44647,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1622" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44670,7 +44673,7 @@
         <v>18</v>
       </c>
       <c r="G1623" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44696,7 +44699,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1624" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44722,7 +44725,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1625" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44748,7 +44751,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1626" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44774,7 +44777,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1627" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44800,7 +44803,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1628" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44826,7 +44829,7 @@
         <v>18.25</v>
       </c>
       <c r="G1629" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44852,7 +44855,7 @@
         <v>18.25</v>
       </c>
       <c r="G1630" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44878,7 +44881,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1631" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44904,7 +44907,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1632" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44930,7 +44933,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1633" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44956,7 +44959,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1634" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44982,7 +44985,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1635" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45008,7 +45011,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1636" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45034,7 +45037,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1637" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45060,7 +45063,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1638" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45086,7 +45089,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1639" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45112,7 +45115,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1640" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45138,7 +45141,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1641" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -45164,7 +45167,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1642" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45190,7 +45193,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1643" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45216,7 +45219,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1644" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -45242,7 +45245,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1645" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -45268,7 +45271,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1646" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -45294,7 +45297,7 @@
         <v>18</v>
       </c>
       <c r="G1647" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -45320,7 +45323,7 @@
         <v>18.25</v>
       </c>
       <c r="G1648" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -45346,7 +45349,7 @@
         <v>18.25</v>
       </c>
       <c r="G1649" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -45372,7 +45375,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1650" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45398,7 +45401,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1651" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -45424,7 +45427,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1652" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45450,7 +45453,7 @@
         <v>18</v>
       </c>
       <c r="G1653" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45476,7 +45479,7 @@
         <v>18</v>
       </c>
       <c r="G1654" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45502,7 +45505,7 @@
         <v>18</v>
       </c>
       <c r="G1655" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45528,7 +45531,7 @@
         <v>18</v>
       </c>
       <c r="G1656" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45554,7 +45557,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1657" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45580,7 +45583,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1658" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45606,7 +45609,7 @@
         <v>17.75</v>
       </c>
       <c r="G1659" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45632,7 +45635,7 @@
         <v>18</v>
       </c>
       <c r="G1660" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45658,7 +45661,7 @@
         <v>18</v>
       </c>
       <c r="G1661" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45684,7 +45687,7 @@
         <v>18</v>
       </c>
       <c r="G1662" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45710,7 +45713,7 @@
         <v>18</v>
       </c>
       <c r="G1663" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45736,7 +45739,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1664" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45762,7 +45765,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1665" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45788,7 +45791,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1666" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45814,7 +45817,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1667" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45840,7 +45843,7 @@
         <v>17.5</v>
       </c>
       <c r="G1668" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45866,7 +45869,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1669" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45892,7 +45895,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1670" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45918,7 +45921,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1671" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45944,7 +45947,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1672" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45970,7 +45973,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1673" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45996,7 +45999,7 @@
         <v>16.75</v>
       </c>
       <c r="G1674" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -46022,7 +46025,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1675" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -46048,7 +46051,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1676" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -46074,7 +46077,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1677" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -46100,7 +46103,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1678" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -46126,7 +46129,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1679" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -46152,7 +46155,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1680" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -46178,7 +46181,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1681" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -46204,7 +46207,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1682" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -46230,7 +46233,7 @@
         <v>17</v>
       </c>
       <c r="G1683" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -46256,7 +46259,7 @@
         <v>17</v>
       </c>
       <c r="G1684" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -46282,7 +46285,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1685" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -46308,7 +46311,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1686" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -46334,7 +46337,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1687" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -46360,7 +46363,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46386,7 +46389,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1689" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -46412,7 +46415,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1690" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -46438,7 +46441,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1691" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46464,7 +46467,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1692" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46490,7 +46493,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1693" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -46516,7 +46519,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46542,7 +46545,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1695" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46568,7 +46571,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1696" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46594,7 +46597,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1697" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46620,7 +46623,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1698" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46646,7 +46649,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1699" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46672,7 +46675,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1700" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46698,7 +46701,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1701" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46724,7 +46727,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1702" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46750,7 +46753,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1703" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46776,7 +46779,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1704" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46802,7 +46805,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1705" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46828,7 +46831,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1706" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46854,7 +46857,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1707" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46880,7 +46883,7 @@
         <v>15</v>
       </c>
       <c r="G1708" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46906,7 +46909,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1709" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46932,7 +46935,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1710" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46958,7 +46961,7 @@
         <v>14.5</v>
       </c>
       <c r="G1711" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46984,7 +46987,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1712" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -47010,7 +47013,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1713" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47036,7 +47039,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1714" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -47062,7 +47065,7 @@
         <v>15</v>
       </c>
       <c r="G1715" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -47088,7 +47091,7 @@
         <v>15</v>
       </c>
       <c r="G1716" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47114,7 +47117,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1717" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -47140,7 +47143,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1718" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -47166,7 +47169,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -47192,7 +47195,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1720" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -47218,7 +47221,7 @@
         <v>14.25</v>
       </c>
       <c r="G1721" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -47244,7 +47247,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1722" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -47270,7 +47273,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1723" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -47296,7 +47299,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1724" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -47322,7 +47325,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1725" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -47348,7 +47351,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1726" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47374,7 +47377,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1727" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47400,7 +47403,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1728" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -47426,7 +47429,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1729" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47452,7 +47455,7 @@
         <v>14.75</v>
       </c>
       <c r="G1730" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47478,7 +47481,7 @@
         <v>14.75</v>
       </c>
       <c r="G1731" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47504,7 +47507,7 @@
         <v>14.75</v>
       </c>
       <c r="G1732" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47530,7 +47533,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1733" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47556,7 +47559,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1734" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47582,7 +47585,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1735" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47608,7 +47611,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1736" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47634,7 +47637,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1737" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47660,7 +47663,7 @@
         <v>13.25</v>
       </c>
       <c r="G1738" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47686,7 +47689,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1739" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47712,7 +47715,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1740" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47738,7 +47741,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1741" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47764,7 +47767,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1742" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47790,7 +47793,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1743" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47816,7 +47819,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1744" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47842,7 +47845,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1745" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47868,7 +47871,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1746" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47894,7 +47897,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1747" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47920,7 +47923,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1748" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47946,7 +47949,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1749" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47972,7 +47975,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1750" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47998,7 +48001,7 @@
         <v>12.75</v>
       </c>
       <c r="G1751" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -48024,7 +48027,7 @@
         <v>12.5</v>
       </c>
       <c r="G1752" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -48050,7 +48053,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1753" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -48076,7 +48079,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1754" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -48102,7 +48105,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1755" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -48128,7 +48131,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1756" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -48154,7 +48157,7 @@
         <v>12.25</v>
       </c>
       <c r="G1757" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -48180,7 +48183,7 @@
         <v>12.25</v>
       </c>
       <c r="G1758" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -48206,7 +48209,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1759" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -48232,7 +48235,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1760" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -48258,7 +48261,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1761" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -48284,7 +48287,7 @@
         <v>12.75</v>
       </c>
       <c r="G1762" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -48310,7 +48313,7 @@
         <v>12.75</v>
       </c>
       <c r="G1763" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -48336,7 +48339,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1764" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -48362,7 +48365,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1765" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48388,7 +48391,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1766" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48414,7 +48417,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1767" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48440,7 +48443,7 @@
         <v>12.5</v>
       </c>
       <c r="G1768" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48466,7 +48469,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1769" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48492,7 +48495,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1770" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48518,7 +48521,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1771" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48544,7 +48547,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1772" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48570,7 +48573,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1773" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48596,7 +48599,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1774" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48622,7 +48625,7 @@
         <v>12.75</v>
       </c>
       <c r="G1775" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48648,7 +48651,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1776" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48674,7 +48677,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1777" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48700,7 +48703,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1778" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48726,7 +48729,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1779" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48752,7 +48755,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1780" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48778,7 +48781,7 @@
         <v>13</v>
       </c>
       <c r="G1781" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48804,7 +48807,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1782" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48830,7 +48833,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1783" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48856,7 +48859,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1784" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48882,7 +48885,7 @@
         <v>12.75</v>
       </c>
       <c r="G1785" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48908,7 +48911,7 @@
         <v>12.75</v>
       </c>
       <c r="G1786" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48934,7 +48937,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48960,7 +48963,7 @@
         <v>12.5</v>
       </c>
       <c r="G1788" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48986,7 +48989,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1789" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -49012,7 +49015,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1790" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -49038,7 +49041,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1791" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -49064,7 +49067,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1792" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -49090,7 +49093,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1793" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -49116,7 +49119,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1794" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -49142,7 +49145,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1795" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -49168,7 +49171,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1796" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -49194,7 +49197,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1797" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -49220,7 +49223,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1798" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -49246,7 +49249,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1799" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -49272,7 +49275,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1800" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -49298,7 +49301,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1801" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -49324,7 +49327,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1802" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -49350,7 +49353,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1803" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49376,7 +49379,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1804" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49402,7 +49405,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1805" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49428,7 +49431,7 @@
         <v>12.75</v>
       </c>
       <c r="G1806" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49454,7 +49457,7 @@
         <v>12.75</v>
       </c>
       <c r="G1807" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49480,7 +49483,7 @@
         <v>12.75</v>
       </c>
       <c r="G1808" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49506,7 +49509,7 @@
         <v>12.75</v>
       </c>
       <c r="G1809" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49532,7 +49535,7 @@
         <v>12.75</v>
       </c>
       <c r="G1810" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49558,7 +49561,7 @@
         <v>12.75</v>
       </c>
       <c r="G1811" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49584,7 +49587,7 @@
         <v>12.75</v>
       </c>
       <c r="G1812" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49610,7 +49613,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1813" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49636,7 +49639,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1814" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49662,7 +49665,7 @@
         <v>12.75</v>
       </c>
       <c r="G1815" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49688,7 +49691,7 @@
         <v>12.75</v>
       </c>
       <c r="G1816" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49714,7 +49717,7 @@
         <v>12.75</v>
       </c>
       <c r="G1817" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49740,7 +49743,7 @@
         <v>12.75</v>
       </c>
       <c r="G1818" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49766,7 +49769,7 @@
         <v>12.75</v>
       </c>
       <c r="G1819" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49792,7 +49795,7 @@
         <v>12.75</v>
       </c>
       <c r="G1820" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49818,7 +49821,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1821" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49844,7 +49847,7 @@
         <v>12.5</v>
       </c>
       <c r="G1822" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49870,7 +49873,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1823" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49896,7 +49899,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1824" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49922,7 +49925,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1825" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49948,7 +49951,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1826" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49974,7 +49977,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1827" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -50000,7 +50003,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1828" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -50026,7 +50029,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1829" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -50052,7 +50055,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1830" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -50078,7 +50081,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1831" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -50104,7 +50107,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1832" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -50130,7 +50133,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1833" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -50156,7 +50159,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1834" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -50182,7 +50185,7 @@
         <v>12.5</v>
       </c>
       <c r="G1835" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -50208,7 +50211,7 @@
         <v>12.5</v>
       </c>
       <c r="G1836" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -50234,7 +50237,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1837" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -50260,7 +50263,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1838" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -50286,7 +50289,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1839" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -50312,7 +50315,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -50338,7 +50341,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1841" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50364,7 +50367,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1842" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50390,7 +50393,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1843" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50416,7 +50419,7 @@
         <v>12.75</v>
       </c>
       <c r="G1844" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50442,7 +50445,7 @@
         <v>12.75</v>
       </c>
       <c r="G1845" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50468,7 +50471,7 @@
         <v>12.75</v>
       </c>
       <c r="G1846" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50494,7 +50497,7 @@
         <v>12.75</v>
       </c>
       <c r="G1847" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50520,7 +50523,7 @@
         <v>12.75</v>
       </c>
       <c r="G1848" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50546,7 +50549,7 @@
         <v>12.75</v>
       </c>
       <c r="G1849" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50572,7 +50575,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1850" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50598,7 +50601,7 @@
         <v>13.25</v>
       </c>
       <c r="G1851" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50624,7 +50627,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1852" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50650,7 +50653,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1853" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50676,7 +50679,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1854" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50702,7 +50705,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1855" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50728,7 +50731,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1856" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50754,7 +50757,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1857" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50780,7 +50783,7 @@
         <v>13</v>
       </c>
       <c r="G1858" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50806,7 +50809,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1859" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50832,7 +50835,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1860" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50858,7 +50861,7 @@
         <v>13.25</v>
       </c>
       <c r="G1861" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50884,7 +50887,7 @@
         <v>13.25</v>
       </c>
       <c r="G1862" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50910,7 +50913,7 @@
         <v>13.25</v>
       </c>
       <c r="G1863" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50936,7 +50939,7 @@
         <v>13.25</v>
       </c>
       <c r="G1864" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50962,7 +50965,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1865" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50988,7 +50991,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1866" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -51014,7 +51017,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1867" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -51040,7 +51043,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1868" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -51066,7 +51069,7 @@
         <v>12.5</v>
       </c>
       <c r="G1869" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -51092,7 +51095,7 @@
         <v>12.5</v>
       </c>
       <c r="G1870" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -51118,7 +51121,7 @@
         <v>12.5</v>
       </c>
       <c r="G1871" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -51144,7 +51147,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1872" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -51170,7 +51173,7 @@
         <v>12.5</v>
       </c>
       <c r="G1873" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -51196,7 +51199,7 @@
         <v>12.5</v>
       </c>
       <c r="G1874" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -51222,7 +51225,7 @@
         <v>12.5</v>
       </c>
       <c r="G1875" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -51248,7 +51251,7 @@
         <v>12.5</v>
       </c>
       <c r="G1876" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -51274,7 +51277,7 @@
         <v>12.25</v>
       </c>
       <c r="G1877" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -51300,7 +51303,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1878" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -51326,7 +51329,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1879" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -51352,7 +51355,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1880" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51378,7 +51381,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1881" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51404,7 +51407,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1882" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51430,7 +51433,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1883" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51456,7 +51459,7 @@
         <v>12.5</v>
       </c>
       <c r="G1884" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51482,7 +51485,7 @@
         <v>12.5</v>
       </c>
       <c r="G1885" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51508,7 +51511,7 @@
         <v>12.5</v>
       </c>
       <c r="G1886" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51534,7 +51537,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1887" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51560,7 +51563,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1888" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51586,7 +51589,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1889" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51612,7 +51615,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1890" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51638,7 +51641,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1891" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51664,7 +51667,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1892" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51690,7 +51693,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1893" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51716,7 +51719,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1894" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51742,7 +51745,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1895" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51768,7 +51771,7 @@
         <v>14.75</v>
       </c>
       <c r="G1896" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51794,7 +51797,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1897" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51820,7 +51823,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1898" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51846,7 +51849,7 @@
         <v>14.25</v>
       </c>
       <c r="G1899" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51872,7 +51875,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1900" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51898,7 +51901,7 @@
         <v>14</v>
       </c>
       <c r="G1901" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51924,7 +51927,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1902" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51950,7 +51953,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1903" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51976,7 +51979,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1904" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -52002,7 +52005,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1905" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52028,7 +52031,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1906" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52054,7 +52057,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52080,7 +52083,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1908" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52106,7 +52109,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1909" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52132,7 +52135,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1910" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -52158,7 +52161,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1911" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -52184,7 +52187,7 @@
         <v>13.25</v>
       </c>
       <c r="G1912" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -52210,7 +52213,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1913" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -52236,7 +52239,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1914" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -52262,7 +52265,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1915" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -52288,7 +52291,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1916" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -52314,7 +52317,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1917" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -52340,7 +52343,7 @@
         <v>12.75</v>
       </c>
       <c r="G1918" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52366,7 +52369,7 @@
         <v>13</v>
       </c>
       <c r="G1919" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52392,7 +52395,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1920" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52418,7 +52421,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1921" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52444,7 +52447,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1922" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52470,7 +52473,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1923" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52496,7 +52499,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1924" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52522,7 +52525,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1925" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52548,7 +52551,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1926" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52574,7 +52577,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1927" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52600,7 +52603,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1928" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52626,7 +52629,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1929" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52652,7 +52655,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1930" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52678,7 +52681,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1931" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52704,7 +52707,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1932" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52730,7 +52733,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1933" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52756,7 +52759,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1934" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52782,7 +52785,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1935" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52808,7 +52811,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1936" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52834,7 +52837,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1937" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52860,7 +52863,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1938" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52886,7 +52889,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1939" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52912,7 +52915,7 @@
         <v>12.5</v>
       </c>
       <c r="G1940" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52938,7 +52941,7 @@
         <v>12.75</v>
       </c>
       <c r="G1941" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52964,7 +52967,7 @@
         <v>12.75</v>
       </c>
       <c r="G1942" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52990,7 +52993,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1943" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53016,7 +53019,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1944" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53042,7 +53045,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1945" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53068,7 +53071,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1946" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53094,7 +53097,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1947" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53120,7 +53123,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1948" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -53146,7 +53149,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1949" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -53172,7 +53175,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1950" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -53198,7 +53201,7 @@
         <v>12.25</v>
       </c>
       <c r="G1951" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -53224,7 +53227,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1952" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -53250,7 +53253,7 @@
         <v>12.5</v>
       </c>
       <c r="G1953" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -53276,7 +53279,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1954" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -53302,7 +53305,7 @@
         <v>12.25</v>
       </c>
       <c r="G1955" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -53328,7 +53331,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1956" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -53354,7 +53357,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1957" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53380,7 +53383,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1958" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53406,7 +53409,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1959" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53432,7 +53435,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1960" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53458,7 +53461,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1961" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53484,7 +53487,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1962" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53510,7 +53513,7 @@
         <v>10.5</v>
       </c>
       <c r="G1963" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53536,7 +53539,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1964" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53562,7 +53565,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1965" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53588,7 +53591,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1966" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53614,7 +53617,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1967" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53640,7 +53643,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1968" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53666,7 +53669,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1969" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53692,7 +53695,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1970" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53718,7 +53721,7 @@
         <v>12</v>
       </c>
       <c r="G1971" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53744,7 +53747,7 @@
         <v>12</v>
       </c>
       <c r="G1972" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53770,7 +53773,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1973" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53796,7 +53799,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1974" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53822,7 +53825,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1975" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53848,7 +53851,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1976" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53874,7 +53877,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1977" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53900,7 +53903,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1978" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53926,7 +53929,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1979" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53952,7 +53955,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1980" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53978,7 +53981,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1981" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -54004,7 +54007,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1982" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54030,7 +54033,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54056,7 +54059,7 @@
         <v>13</v>
       </c>
       <c r="G1984" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54082,7 +54085,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1985" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54108,7 +54111,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1986" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -54134,7 +54137,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1987" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -54160,7 +54163,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1988" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -54186,7 +54189,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1989" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -54212,7 +54215,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1990" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -54238,7 +54241,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1991" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -54264,7 +54267,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1992" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -54290,7 +54293,7 @@
         <v>13.5</v>
       </c>
       <c r="G1993" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -54316,7 +54319,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1994" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -54342,7 +54345,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1995" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54368,7 +54371,7 @@
         <v>14.5</v>
       </c>
       <c r="G1996" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54394,7 +54397,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1997" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54420,7 +54423,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1998" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54446,7 +54449,7 @@
         <v>15</v>
       </c>
       <c r="G1999" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54472,7 +54475,7 @@
         <v>15.5</v>
       </c>
       <c r="G2000" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54498,7 +54501,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2001" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54524,7 +54527,7 @@
         <v>15.5</v>
       </c>
       <c r="G2002" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54550,7 +54553,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2003" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54576,7 +54579,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2004" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54602,7 +54605,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2005" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54628,7 +54631,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2006" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54654,7 +54657,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G2007" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54680,7 +54683,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2008" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54706,7 +54709,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2009" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54732,7 +54735,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2010" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54758,7 +54761,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G2011" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54784,7 +54787,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2012" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54810,7 +54813,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2013" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54836,7 +54839,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2014" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54862,7 +54865,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2015" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54888,7 +54891,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2016" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54914,7 +54917,7 @@
         <v>16</v>
     